--- a/amazon_products.xlsx
+++ b/amazon_products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E316"/>
+  <dimension ref="A1:E317"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7058,6 +7058,27 @@
         </is>
       </c>
     </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>Acer Smartchoice Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X / 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr"/>
+      <c r="C317" t="n">
+        <v>32990</v>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>Acer Smartchoice Aspire One, Intel</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/amazon_products.xlsx
+++ b/amazon_products.xlsx
@@ -7061,12 +7061,12 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Acer Smartchoice Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X / 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="B317" t="inlineStr"/>
       <c r="C317" t="n">
-        <v>32990</v>
+        <v>44999</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -7075,7 +7075,7 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Acer Smartchoice Aspire One, Intel</t>
+          <t>Lenovo V15 G4 AMD Athlon</t>
         </is>
       </c>
     </row>

--- a/amazon_products.xlsx
+++ b/amazon_products.xlsx
@@ -7061,12 +7061,12 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Acer Smartchoice Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X / 512GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="B317" t="inlineStr"/>
       <c r="C317" t="n">
-        <v>44999</v>
+        <v>34990</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -7075,7 +7075,7 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon</t>
+          <t>Acer Smartchoice Aspire One, Intel</t>
         </is>
       </c>
     </row>

--- a/amazon_products.xlsx
+++ b/amazon_products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E344"/>
+  <dimension ref="A1:E352"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2546,21 +2546,21 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Neo 13″</t>
+          <t>acer_travellite_thin_laptop_amd</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Citrus</t>
+          <t>Acer TravelLite Thin Laptop AMD Ryzen 5 7430U (6-Core) 16GB RAM, 512GB SSD 14" Full HD Anti-Glare Display Privacy Shutter Windows 11 MS Office Metal Body 1.34Kg Black 30M Warranty</t>
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="n">
-        <v>65000</v>
+        <v>52999</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -2572,16 +2572,16 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Indigo</t>
+          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Citrus</t>
         </is>
       </c>
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="n">
-        <v>67900</v>
+        <v>65000</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
@@ -2598,11 +2598,11 @@
       </c>
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="n">
-        <v>65000</v>
+        <v>67900</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -2619,11 +2619,11 @@
       </c>
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="n">
-        <v>65700</v>
+        <v>65000</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
@@ -2640,11 +2640,11 @@
       </c>
       <c r="C106" t="inlineStr"/>
       <c r="D106" t="n">
-        <v>65000</v>
+        <v>65700</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-28</t>
         </is>
       </c>
     </row>
@@ -2665,7 +2665,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -2686,7 +2686,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
@@ -2698,7 +2698,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Silver</t>
+          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Indigo</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
@@ -2707,7 +2707,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -2728,7 +2728,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-24</t>
         </is>
       </c>
     </row>
@@ -2745,11 +2745,11 @@
       </c>
       <c r="C111" t="inlineStr"/>
       <c r="D111" t="n">
-        <v>65700</v>
+        <v>65000</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -2766,11 +2766,11 @@
       </c>
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="n">
-        <v>67900</v>
+        <v>65700</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-27</t>
         </is>
       </c>
     </row>
@@ -2787,11 +2787,11 @@
       </c>
       <c r="C113" t="inlineStr"/>
       <c r="D113" t="n">
-        <v>65000</v>
+        <v>67900</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-31</t>
         </is>
       </c>
     </row>
@@ -2808,11 +2808,11 @@
       </c>
       <c r="C114" t="inlineStr"/>
       <c r="D114" t="n">
-        <v>64990</v>
+        <v>65000</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
     </row>
@@ -2829,11 +2829,11 @@
       </c>
       <c r="C115" t="inlineStr"/>
       <c r="D115" t="n">
-        <v>63990</v>
+        <v>64990</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
@@ -2854,7 +2854,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
@@ -2875,28 +2875,28 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Pro Laptop</t>
+          <t>Apple 2026 MacBook Neo 13″</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Pro Laptop with M5 Max chip with 18‑core CPU and 40‑core GPU: Built for AI, 41.05 cm (16.2″) Liquid Retina XDR Display, 48GB Unified Memory, 2TB SSD Storage; Space Black</t>
+          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Silver</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="n">
-        <v>499900</v>
+        <v>63990</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-12</t>
         </is>
       </c>
     </row>
@@ -2917,7 +2917,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
@@ -2938,7 +2938,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-28</t>
         </is>
       </c>
     </row>
@@ -2950,16 +2950,16 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Pro Laptop with M5 Pro chip with 15‑core CPU and 16‑core GPU: Built for AI, 35.97 cm (14.2″) Liquid Retina XDR Display, 24GB Unified Memory, 1TB SSD Storage; Silver</t>
+          <t>Apple 2026 MacBook Pro Laptop with M5 Max chip with 18‑core CPU and 40‑core GPU: Built for AI, 41.05 cm (16.2″) Liquid Retina XDR Display, 48GB Unified Memory, 2TB SSD Storage; Space Black</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
       <c r="D121" t="n">
-        <v>234900</v>
+        <v>499900</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-02</t>
         </is>
       </c>
     </row>
@@ -2976,32 +2976,32 @@
       </c>
       <c r="C122" t="inlineStr"/>
       <c r="D122" t="n">
-        <v>227400</v>
+        <v>234900</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>BrowseBook 14.1" FHD IPS Laptop</t>
+          <t>Apple 2026 MacBook Pro Laptop</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>BrowseBook 14.1" FHD IPS Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB RAM | 128GB SSD | Windows 11 | 38Wh | 1.3kg | Grey</t>
+          <t>Apple 2026 MacBook Pro Laptop with M5 Pro chip with 15‑core CPU and 16‑core GPU: Built for AI, 35.97 cm (14.2″) Liquid Retina XDR Display, 24GB Unified Memory, 1TB SSD Storage; Silver</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
       <c r="D123" t="n">
-        <v>13990</v>
+        <v>227400</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
@@ -3022,7 +3022,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -3043,7 +3043,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-16</t>
         </is>
       </c>
     </row>
@@ -3060,11 +3060,11 @@
       </c>
       <c r="C126" t="inlineStr"/>
       <c r="D126" t="n">
-        <v>20990</v>
+        <v>13990</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -3076,37 +3076,37 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>BrowseBook 14.1" FHD IPS Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 8GB RAM | 256GB SSD | Windows 11 | 38Wh | 1.3kg | Grey</t>
+          <t>BrowseBook 14.1" FHD IPS Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB RAM | 128GB SSD | Windows 11 | 38Wh | 1.3kg | Grey</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
       <c r="D127" t="n">
-        <v>18990</v>
+        <v>20990</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron) Laptop,</t>
+          <t>BrowseBook 14.1" FHD IPS Laptop</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core 3 100U Processor, 8GB DDR4, 512 SSD, 15.6" NT FHD 120Hz IPS AG 250 nit Display, Win 11 + Office H&amp;S 2024, Carbon Black, Thin &amp; Light- 1.63Kg</t>
+          <t>BrowseBook 14.1" FHD IPS Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 8GB RAM | 256GB SSD | Windows 11 | 38Wh | 1.3kg | Grey</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
       <c r="D128" t="n">
-        <v>46490</v>
+        <v>18990</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-15</t>
         </is>
       </c>
     </row>
@@ -3118,16 +3118,16 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 8GB DDR4, 512 SSD, 15.6" FHD 120Hz IPS 250 nit Display, Win 11 + Office H&amp;S 2024, Carbon Black, Thin &amp; Light 1.63Kg</t>
+          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core 3 100U Processor, 8GB DDR4, 512 SSD, 15.6" NT FHD 120Hz IPS AG 250 nit Display, Win 11 + Office H&amp;S 2024, Carbon Black, Thin &amp; Light- 1.63Kg</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
       <c r="D129" t="n">
-        <v>45490</v>
+        <v>46490</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
@@ -3144,11 +3144,11 @@
       </c>
       <c r="C130" t="inlineStr"/>
       <c r="D130" t="n">
-        <v>44990</v>
+        <v>45490</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-17</t>
         </is>
       </c>
     </row>
@@ -3169,7 +3169,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
@@ -3186,11 +3186,11 @@
       </c>
       <c r="C132" t="inlineStr"/>
       <c r="D132" t="n">
-        <v>45490</v>
+        <v>44990</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
@@ -3211,7 +3211,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -3232,7 +3232,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
@@ -3249,11 +3249,11 @@
       </c>
       <c r="C135" t="inlineStr"/>
       <c r="D135" t="n">
-        <v>46490</v>
+        <v>45490</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
@@ -3270,116 +3270,116 @@
       </c>
       <c r="C136" t="inlineStr"/>
       <c r="D136" t="n">
-        <v>46990</v>
+        <v>46490</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>dell_15_(previously_inspiron)_laptop,</t>
+          <t>Dell 15 (Previously Inspiron) Laptop,</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 8GB, 512GB, Intel UHD Graphics, 15.6" FHD IPS 250nit Display, 12m Mcafee, Win 11 + MSO'24, Platinum Silver, 1.63kg</t>
+          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 8GB DDR4, 512 SSD, 15.6" FHD 120Hz IPS 250 nit Display, Win 11 + Office H&amp;S 2024, Carbon Black, Thin &amp; Light 1.63Kg</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
       <c r="D137" t="n">
-        <v>50490</v>
+        <v>46990</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron), 13th</t>
+          <t>dell_15_(previously_inspiron)_laptop,</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron), 13th Gen Intel Core i5-1334U (16GB RAM, 1TB SSD) FHD, Anti-Glare 15.6"/39.62cm, Windows 11 MSO'24, Silver, 1.62kg, 12 Month McAfee, Thin &amp; Light, Backlit Keyboard Laptop</t>
+          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 8GB, 512GB, Intel UHD Graphics, 15.6" FHD IPS 250nit Display, 12m Mcafee, Win 11 + MSO'24, Platinum Silver, 1.63kg</t>
         </is>
       </c>
       <c r="C138" t="inlineStr"/>
       <c r="D138" t="n">
-        <v>63990</v>
+        <v>50490</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Dell 15 AI Powered Laptop,</t>
+          <t>Dell 15 (Previously Inspiron), 13th</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Dell 15 AI Powered Laptop, Intel Core Ultra 5 225H, 8GB DDR5 RAM, 512GB SSD, 15.6" FHD Anti-Glare Display, Intel Arc Graphics, Standard Keyboard, Dedicated Copilot Key, Black, Win11 Home + MSO H&amp;S'24</t>
+          <t>Dell 15 (Previously Inspiron), 13th Gen Intel Core i5-1334U (16GB RAM, 1TB SSD) FHD, Anti-Glare 15.6"/39.62cm, Windows 11 MSO'24, Silver, 1.62kg, 12 Month McAfee, Thin &amp; Light, Backlit Keyboard Laptop</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
       <c r="D139" t="n">
-        <v>68990</v>
+        <v>63990</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-17</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>dell_15_ai_powered_laptop,</t>
+          <t>Dell 15 AI Powered Laptop,</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Dell 15 Ai Powered Laptop, Intel Core Ultra 7 255H, 16GB DDR5 RAM, 512GB SSD, 15.6" FHD Anti-Glare Display, Intel Arc Graphics, Backlit Keyboard, Dedicated Copilot Key, Silver, Win11 Home + MSO H&amp;S'24</t>
+          <t>Dell 15 AI Powered Laptop, Intel Core Ultra 5 225H, 8GB DDR5 RAM, 512GB SSD, 15.6" FHD Anti-Glare Display, Intel Arc Graphics, Standard Keyboard, Dedicated Copilot Key, Black, Win11 Home + MSO H&amp;S'24</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
       <c r="D140" t="n">
-        <v>103990</v>
+        <v>68990</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-15</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Dell 15 Smart Choice (Previously</t>
+          <t>dell_15_ai_powered_laptop,</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Dell 15 Smart Choice (Previously Inspiron), 13th Gen Intel Core i5-1334U (16GB RAM, 1TB SSD) FHD, 15.6"/39.62cm, Windows 11 MSO'24, Silver, 1.62kg, 12 Month McAfee, Backlit KB, Thin &amp; Light Laptop</t>
+          <t>Dell 15 Ai Powered Laptop, Intel Core Ultra 7 255H, 16GB DDR5 RAM, 512GB SSD, 15.6" FHD Anti-Glare Display, Intel Arc Graphics, Backlit Keyboard, Dedicated Copilot Key, Silver, Win11 Home + MSO H&amp;S'24</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
       <c r="D141" t="n">
-        <v>66990</v>
+        <v>103990</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -3396,11 +3396,11 @@
       </c>
       <c r="C142" t="inlineStr"/>
       <c r="D142" t="n">
-        <v>67990</v>
+        <v>66990</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-28</t>
         </is>
       </c>
     </row>
@@ -3421,7 +3421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-31</t>
         </is>
       </c>
     </row>
@@ -3438,11 +3438,11 @@
       </c>
       <c r="C144" t="inlineStr"/>
       <c r="D144" t="n">
-        <v>69990</v>
+        <v>67990</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -3459,32 +3459,32 @@
       </c>
       <c r="C145" t="inlineStr"/>
       <c r="D145" t="n">
-        <v>67990</v>
+        <v>69990</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-02</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Dell 15, 13th Gen Intel</t>
+          <t>Dell 15 Smart Choice (Previously</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Dell 15, 13th Gen Intel Core i5-1334U (16GB DDR4, 512GB SSD) Anti-Glare FHD 15.6"/39.62cm, Windows 11, Microsoft Office Home 2024, Grey, 1.66kg, [Vostro 3530], 12 Month McAfee, Thin &amp; Light Laptop</t>
+          <t>Dell 15 Smart Choice (Previously Inspiron), 13th Gen Intel Core i5-1334U (16GB RAM, 1TB SSD) FHD, 15.6"/39.62cm, Windows 11 MSO'24, Silver, 1.62kg, 12 Month McAfee, Backlit KB, Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
       <c r="D146" t="n">
-        <v>61490</v>
+        <v>67990</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-06-14</t>
         </is>
       </c>
     </row>
@@ -3501,32 +3501,32 @@
       </c>
       <c r="C147" t="inlineStr"/>
       <c r="D147" t="n">
-        <v>63490</v>
+        <v>61490</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Dell 15, AMD Ryzen 7-7730U,</t>
+          <t>Dell 15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Dell 15, AMD Ryzen 7-7730U, 16GB DDR4, 512GB SSD, FHD, 15.6"/39.6cm, Windows 11, Microsoft Office Home 2024, Platinum Silver, 1.63Kg, [Dell 15], 120Hz 250nits, AMD Radeon Graphics,Thin &amp; Light, Laptop</t>
+          <t>Dell 15, 13th Gen Intel Core i5-1334U (16GB DDR4, 512GB SSD) Anti-Glare FHD 15.6"/39.62cm, Windows 11, Microsoft Office Home 2024, Grey, 1.66kg, [Vostro 3530], 12 Month McAfee, Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
       <c r="D148" t="n">
-        <v>59957</v>
+        <v>63490</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
@@ -3543,116 +3543,116 @@
       </c>
       <c r="C149" t="inlineStr"/>
       <c r="D149" t="n">
-        <v>58490</v>
+        <v>59957</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Dell 15, Intel Core 3</t>
+          <t>Dell 15, AMD Ryzen 7-7730U,</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Dell 15, Intel Core 3 14th Gen-100U, 16GB DDR4, 512GB SSD, FHD IPS, 15.6"/39.62cm, Windows 11, Microsoft Office Home 2024, Carbon Black, 1.63Kg, Thin &amp; Light, Laptop Model NO - Dell 15 DCU5250</t>
+          <t>Dell 15, AMD Ryzen 7-7730U, 16GB DDR4, 512GB SSD, FHD, 15.6"/39.6cm, Windows 11, Microsoft Office Home 2024, Platinum Silver, 1.63Kg, [Dell 15], 120Hz 250nits, AMD Radeon Graphics,Thin &amp; Light, Laptop</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
       <c r="D150" t="n">
-        <v>51868</v>
+        <v>58490</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-05-17</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Dell 15, Intel Core i3/Core</t>
+          <t>Dell 15, Intel Core 3</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Dell 15, Intel Core i3/Core 3 14th Gen-100U, 16GB DDR4, 512GB SSD, FHD IPS, 15.6"/39.62cm, Windows 11, Microsoft Office Home 2024, Carbon Black, 1.63Kg, Thin &amp; Light, Laptop Model NO - Dell 15 DCU5250</t>
+          <t>Dell 15, Intel Core 3 14th Gen-100U, 16GB DDR4, 512GB SSD, FHD IPS, 15.6"/39.62cm, Windows 11, Microsoft Office Home 2024, Carbon Black, 1.63Kg, Thin &amp; Light, Laptop Model NO - Dell 15 DCU5250</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
       <c r="D151" t="n">
-        <v>48990</v>
+        <v>51868</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Dell 15, R5-7520U Processor, 8GB</t>
+          <t>Dell 15, Intel Core i3/Core</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Dell 15, R5-7520U Processor, 8GB LPDDR5 RAM, 512GB SSD, FHD 15.6"/39.62 cm Display, Windows 11, MSO'24, Carbon Black, 1.63kg, Standard Keyboard, 15 Month McAfee, Thin &amp; Light Laptop</t>
+          <t>Dell 15, Intel Core i3/Core 3 14th Gen-100U, 16GB DDR4, 512GB SSD, FHD IPS, 15.6"/39.62cm, Windows 11, Microsoft Office Home 2024, Carbon Black, 1.63Kg, Thin &amp; Light, Laptop Model NO - Dell 15 DCU5250</t>
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="n">
-        <v>53990</v>
+        <v>48990</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>dell_g_series,_intel_core</t>
+          <t>Dell 15, R5-7520U Processor, 8GB</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Dell G Series, Intel Core i5-13450HX, 13th Gen, NVIDIA RTX 3050-6GB, 16GB, 512GB SSD, FHD, 15.6"/39.62cm, Windows 11, MSO'24, Dark Shadow Gray, 2.65KG, [G15-5530], Backlit Keyboard, Gaming Laptop</t>
+          <t>Dell 15, R5-7520U Processor, 8GB LPDDR5 RAM, 512GB SSD, FHD 15.6"/39.62 cm Display, Windows 11, MSO'24, Carbon Black, 1.63kg, Standard Keyboard, 15 Month McAfee, Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
       <c r="D153" t="n">
-        <v>89990</v>
+        <v>53990</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-04-16</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Dell G15, 13th Gen Intel</t>
+          <t>dell_g_series,_intel_core</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Dell G15, 13th Gen Intel Core i5-13450HX Processor, NVIDIA RTX 3050-6GB, (16GB RAM 1TB SSD) FHD 15.6"/39.62 cm, Orange Backlit Keyboard, Win 11, MS Office'24, Dark Shadow Grey, 2.65Kg Gaming Laptop</t>
+          <t>Dell G Series, Intel Core i5-13450HX, 13th Gen, NVIDIA RTX 3050-6GB, 16GB, 512GB SSD, FHD, 15.6"/39.62cm, Windows 11, MSO'24, Dark Shadow Gray, 2.65KG, [G15-5530], Backlit Keyboard, Gaming Laptop</t>
         </is>
       </c>
       <c r="C154" t="inlineStr"/>
       <c r="D154" t="n">
-        <v>79590</v>
+        <v>89990</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -3669,32 +3669,32 @@
       </c>
       <c r="C155" t="inlineStr"/>
       <c r="D155" t="n">
-        <v>79990</v>
+        <v>79590</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>EBook 11.6" HD Laptop |</t>
+          <t>Dell G15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>EBook 11.6" HD Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB DDR4 | 128GB eMMC + M.2 SSD Expandable Slot | Win 11 Home |31Wh Battery | UHD Graphics 600 | Black</t>
+          <t>Dell G15, 13th Gen Intel Core i5-13450HX Processor, NVIDIA RTX 3050-6GB, (16GB RAM 1TB SSD) FHD 15.6"/39.62 cm, Orange Backlit Keyboard, Win 11, MS Office'24, Dark Shadow Grey, 2.65Kg Gaming Laptop</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
       <c r="D156" t="n">
-        <v>11990</v>
+        <v>79990</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-08</t>
         </is>
       </c>
     </row>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-16</t>
         </is>
       </c>
     </row>
@@ -3736,7 +3736,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -3757,7 +3757,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
     </row>
@@ -3799,7 +3799,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-21</t>
         </is>
       </c>
     </row>
@@ -3841,7 +3841,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-31</t>
         </is>
       </c>
     </row>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -3883,7 +3883,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
     </row>
@@ -3900,11 +3900,11 @@
       </c>
       <c r="C166" t="inlineStr"/>
       <c r="D166" t="n">
-        <v>16990</v>
+        <v>11990</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
@@ -3925,14 +3925,14 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>ebook_11.6"_hd_laptop_|</t>
+          <t>EBook 11.6" HD Laptop |</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -3942,28 +3942,28 @@
       </c>
       <c r="C168" t="inlineStr"/>
       <c r="D168" t="n">
-        <v>10603</v>
+        <v>16990</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>hp_14_smartchoice,_intel_core</t>
+          <t>ebook_11.6"_hd_laptop_|</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>HP 14 Smartchoice, Intel Core Ultra 5 125H 12 TOPS, 24GB DDR5 (Upgradeable) 1TB SSD, Anti-Glare, FHD, 14''/35.6cm,Win11, M365*Office24, Silver, 1.4kg, ep1180tu, FHD Camera w/Shutter, Backlit AI Laptop</t>
+          <t>EBook 11.6" HD Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB DDR4 | 128GB eMMC + M.2 SSD Expandable Slot | Win 11 Home |31Wh Battery | UHD Graphics 600 | Black</t>
         </is>
       </c>
       <c r="C169" t="inlineStr"/>
       <c r="D169" t="n">
-        <v>77990</v>
+        <v>10603</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
@@ -3974,17 +3974,17 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>hp_14,_amd_ryzen_7</t>
+          <t>hp_14_smartchoice,_intel_core</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>HP 14, AMD Ryzen 7 7730U (16GB DDR4, 512GB SSD) FHD, Anti-Glare, Micro-Edge, 14''/35.6cm, Win11, M365 Basic(1yr), Office Home24, Silver,1.4kg, EM0104AU, FHD Camera w/Privacy Shutter, Backlit Laptop</t>
+          <t>HP 14 Smartchoice, Intel Core Ultra 5 125H 12 TOPS, 24GB DDR5 (Upgradeable) 1TB SSD, Anti-Glare, FHD, 14''/35.6cm,Win11, M365*Office24, Silver, 1.4kg, ep1180tu, FHD Camera w/Shutter, Backlit AI Laptop</t>
         </is>
       </c>
       <c r="C170" t="inlineStr"/>
       <c r="D170" t="n">
-        <v>59990</v>
+        <v>77990</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
@@ -3995,42 +3995,42 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>HP 14s Intel Celeron Dual</t>
+          <t>hp_14,_amd_ryzen_7</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>HP 14s Intel Celeron Dual Core N4500 Laptop (8GB/512GB SSD/Win 11) 14.0" HD Display, MSO 24, Black, 1.46kg, DQ3149TU Thin and Light Business Laptop</t>
+          <t>HP 14, AMD Ryzen 7 7730U (16GB DDR4, 512GB SSD) FHD, Anti-Glare, Micro-Edge, 14''/35.6cm, Win11, M365 Basic(1yr), Office Home24, Silver,1.4kg, EM0104AU, FHD Camera w/Privacy Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C171" t="inlineStr"/>
       <c r="D171" t="n">
-        <v>40400</v>
+        <v>59990</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>HP 15 (2026), AMD Athlon</t>
+          <t>HP 14s Intel Celeron Dual</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>HP 15 (2026), AMD Athlon Dual Core 7120U - (8 GB DDR5/512 GB SSD/AMD Radeon 610M Graphics/DOS) Thin and Light Business Laptop/15.6" HD Display/Turbo Silver/Copilot Key/1.5kg</t>
+          <t>HP 14s Intel Celeron Dual Core N4500 Laptop (8GB/512GB SSD/Win 11) 14.0" HD Display, MSO 24, Black, 1.46kg, DQ3149TU Thin and Light Business Laptop</t>
         </is>
       </c>
       <c r="C172" t="inlineStr"/>
       <c r="D172" t="n">
-        <v>39999</v>
+        <v>40400</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-16</t>
         </is>
       </c>
     </row>
@@ -4042,23 +4042,23 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>HP 15 (2026), AMD Athlon Dual Core 7120U - (8 GB DDR5/512 GB SSD/AMD Radeon 610M Graphics/Windows 11 Pro) Thin and Light Business Laptop/15.6" HD Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
+          <t>HP 15 (2026), AMD Athlon Dual Core 7120U - (8 GB DDR5/512 GB SSD/AMD Radeon 610M Graphics/DOS) Thin and Light Business Laptop/15.6" HD Display/Turbo Silver/Copilot Key/1.5kg</t>
         </is>
       </c>
       <c r="C173" t="inlineStr"/>
       <c r="D173" t="n">
-        <v>39660</v>
+        <v>39999</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-05-08</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>hp_15_(2026),_amd_athlon</t>
+          <t>HP 15 (2026), AMD Athlon</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -4068,70 +4068,70 @@
       </c>
       <c r="C174" t="inlineStr"/>
       <c r="D174" t="n">
-        <v>41999</v>
+        <v>39660</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>HP 15 (2026), AMD Ryzen</t>
+          <t>hp_15_(2026),_amd_athlon</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>HP 15 (2026), AMD Ryzen 3 Quad Core 7335U - (8 GB DDR5/512 GB SSD/AMD Radeon 660M Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
+          <t>HP 15 (2026), AMD Athlon Dual Core 7120U - (8 GB DDR5/512 GB SSD/AMD Radeon 610M Graphics/Windows 11 Pro) Thin and Light Business Laptop/15.6" HD Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
         </is>
       </c>
       <c r="C175" t="inlineStr"/>
       <c r="D175" t="n">
-        <v>42780</v>
+        <v>41999</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>hp_15_(i5_14th_gen),</t>
+          <t>HP 15 (2026), AMD Ryzen</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>HP 15 (i5 14th Gen), Intel Core 5, 16GB RAM (Upgradeable), 512GB SSD, FHD, Anti-Glare, 15.6''/39.6cm, Win11, M365 Basic(1yr), Office24, Silver,1.59kg, fd0682tu, FHD Camera w/Shutter, Backlit Laptop</t>
+          <t>HP 15 (2026), AMD Ryzen 3 Quad Core 7335U - (8 GB DDR5/512 GB SSD/AMD Radeon 660M Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
         </is>
       </c>
       <c r="C176" t="inlineStr"/>
       <c r="D176" t="n">
-        <v>63990</v>
+        <v>42780</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>hp_15_laptop_|_intel</t>
+          <t>hp_15_(i5_14th_gen),</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>HP 15 Laptop | Intel Core i5-13420H,13th Gen |16GB RAM | 512GB SSD | Win 11 |M365 Basic(1yr)* Office24|Anti-Glare, Micro-Edge, 15.6''/39.6cm|Backlit KB|FHD Camera w/Shutter|1.65kg, Silver -FR0045TU</t>
+          <t>HP 15 (i5 14th Gen), Intel Core 5, 16GB RAM (Upgradeable), 512GB SSD, FHD, Anti-Glare, 15.6''/39.6cm, Win11, M365 Basic(1yr), Office24, Silver,1.59kg, fd0682tu, FHD Camera w/Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C177" t="inlineStr"/>
       <c r="D177" t="n">
-        <v>68990</v>
+        <v>63990</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
@@ -4142,17 +4142,17 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>hp_15_laptop,_(14th_gen</t>
+          <t>hp_15_laptop_|_intel</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>HP 15 Laptop, (14th Gen Core i5) Intel Core 5-120U (24GB RAM, 512GB SSD, Win 11, M365 Basic(1yr)* Office24,15.6''/39.6cm FHD Anti-Glare Display, Backlit KB, FHD Camera, Dual Speakers, Silver, 1.59kg)</t>
+          <t>HP 15 Laptop | Intel Core i5-13420H,13th Gen |16GB RAM | 512GB SSD | Win 11 |M365 Basic(1yr)* Office24|Anti-Glare, Micro-Edge, 15.6''/39.6cm|Backlit KB|FHD Camera w/Shutter|1.65kg, Silver -FR0045TU</t>
         </is>
       </c>
       <c r="C178" t="inlineStr"/>
       <c r="D178" t="n">
-        <v>72800</v>
+        <v>68990</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
@@ -4163,42 +4163,42 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>HP 15 Laptop, Intel (14th</t>
+          <t>hp_15_laptop,_(14th_gen</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>HP 15 Laptop, Intel (14th Gen) Core 5 120U (24GB DDR5, 512GB SSD), Micro-Edge, Anti-Glare, 15.6''/39.6cm, Win11, M365* Office24, Silver, 1.59kg, fd0262TU, FHD Camera, Backlit, Dual Speakers</t>
+          <t>HP 15 Laptop, (14th Gen Core i5) Intel Core 5-120U (24GB RAM, 512GB SSD, Win 11, M365 Basic(1yr)* Office24,15.6''/39.6cm FHD Anti-Glare Display, Backlit KB, FHD Camera, Dual Speakers, Silver, 1.59kg)</t>
         </is>
       </c>
       <c r="C179" t="inlineStr"/>
       <c r="D179" t="n">
-        <v>67990</v>
+        <v>72800</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, 13th Gen</t>
+          <t>HP 15 Laptop, Intel (14th</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U (12GB DDR4, 512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver, 1.59kg, fd0573TU, FHD Camera w/Shutter Laptop</t>
+          <t>HP 15 Laptop, Intel (14th Gen) Core 5 120U (24GB DDR5, 512GB SSD), Micro-Edge, Anti-Glare, 15.6''/39.6cm, Win11, M365* Office24, Silver, 1.59kg, fd0262TU, FHD Camera, Backlit, Dual Speakers</t>
         </is>
       </c>
       <c r="C180" t="inlineStr"/>
       <c r="D180" t="n">
-        <v>55990</v>
+        <v>67990</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -4210,16 +4210,16 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U(8GB DDR4,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
+          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U (12GB DDR4, 512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver, 1.59kg, fd0573TU, FHD Camera w/Shutter Laptop</t>
         </is>
       </c>
       <c r="C181" t="inlineStr"/>
       <c r="D181" t="n">
-        <v>51990</v>
+        <v>55990</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-12</t>
         </is>
       </c>
     </row>
@@ -4240,7 +4240,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -4261,7 +4261,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
@@ -4282,7 +4282,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
@@ -4303,14 +4303,14 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>hp_15_smartchoice,_13th_gen</t>
+          <t>HP 15 Smartchoice, 13th Gen</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -4320,28 +4320,28 @@
       </c>
       <c r="C186" t="inlineStr"/>
       <c r="D186" t="n">
-        <v>49990</v>
+        <v>51990</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>hp_15_smartchoice,_intel_core</t>
+          <t>hp_15_smartchoice,_13th_gen</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, Intel Core Ultra 5 125H, 12 Tops (16GB DDR5, 512GB SSD) FHD, IPS, 15.6''/39.6cm, Win11, M365(1yr)* Office24, Silver, 1.65kg, fd1254TU, FHD Camera w/Shutter, AI Powered Laptop</t>
+          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U(8GB DDR4,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C187" t="inlineStr"/>
       <c r="D187" t="n">
-        <v>69990</v>
+        <v>49990</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
@@ -4352,21 +4352,21 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel</t>
+          <t>hp_15_smartchoice,_intel_core</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U (8GB DDR4, 512GB SSD), FHD, Micro -Edge, Anti-Glare, 15.6''/39.6cm, Win11, M365* Office24, Silver, 1.59kg, fd0624tu, FHD Camera, UHD Graphics Laptop</t>
+          <t>HP 15 Smartchoice, Intel Core Ultra 5 125H, 12 Tops (16GB DDR5, 512GB SSD) FHD, IPS, 15.6''/39.6cm, Win11, M365(1yr)* Office24, Silver, 1.65kg, fd1254TU, FHD Camera w/Shutter, AI Powered Laptop</t>
         </is>
       </c>
       <c r="C188" t="inlineStr"/>
       <c r="D188" t="n">
-        <v>47490</v>
+        <v>69990</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -4378,16 +4378,16 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U (8GB DDR4, 512GB SSD), FHD, Micro -Edge, Anti-Glare, 15.6''/39.6cm, Win11, M365* Office24, Silver, 1.59kg, fd0624tu, FHD Camera, UHD Graphics Laptop</t>
         </is>
       </c>
       <c r="C189" t="inlineStr"/>
       <c r="D189" t="n">
-        <v>47990</v>
+        <v>47490</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-16</t>
         </is>
       </c>
     </row>
@@ -4408,7 +4408,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -4425,11 +4425,11 @@
       </c>
       <c r="C191" t="inlineStr"/>
       <c r="D191" t="n">
-        <v>46990</v>
+        <v>47990</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -4450,7 +4450,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-08</t>
         </is>
       </c>
     </row>
@@ -4471,7 +4471,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
@@ -4492,7 +4492,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-10</t>
         </is>
       </c>
     </row>
@@ -4513,7 +4513,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
     </row>
@@ -4534,7 +4534,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-15</t>
         </is>
       </c>
     </row>
@@ -4551,11 +4551,11 @@
       </c>
       <c r="C197" t="inlineStr"/>
       <c r="D197" t="n">
-        <v>48900</v>
+        <v>46990</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-17</t>
         </is>
       </c>
     </row>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
     </row>
@@ -4593,11 +4593,11 @@
       </c>
       <c r="C199" t="inlineStr"/>
       <c r="D199" t="n">
-        <v>50000</v>
+        <v>48900</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
     </row>
@@ -4614,11 +4614,11 @@
       </c>
       <c r="C200" t="inlineStr"/>
       <c r="D200" t="n">
-        <v>49850</v>
+        <v>50000</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
     </row>
@@ -4635,11 +4635,11 @@
       </c>
       <c r="C201" t="inlineStr"/>
       <c r="D201" t="n">
-        <v>49990</v>
+        <v>49850</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-22</t>
         </is>
       </c>
     </row>
@@ -4656,11 +4656,11 @@
       </c>
       <c r="C202" t="inlineStr"/>
       <c r="D202" t="n">
-        <v>49820</v>
+        <v>49990</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>
@@ -4681,7 +4681,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-24</t>
         </is>
       </c>
     </row>
@@ -4698,11 +4698,11 @@
       </c>
       <c r="C204" t="inlineStr"/>
       <c r="D204" t="n">
-        <v>50400</v>
+        <v>49820</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -4719,11 +4719,11 @@
       </c>
       <c r="C205" t="inlineStr"/>
       <c r="D205" t="n">
-        <v>50390</v>
+        <v>50400</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
@@ -4740,11 +4740,11 @@
       </c>
       <c r="C206" t="inlineStr"/>
       <c r="D206" t="n">
-        <v>50150</v>
+        <v>50390</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
     </row>
@@ -4761,11 +4761,11 @@
       </c>
       <c r="C207" t="inlineStr"/>
       <c r="D207" t="n">
-        <v>50040</v>
+        <v>50150</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-28</t>
         </is>
       </c>
     </row>
@@ -4786,7 +4786,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
@@ -4803,11 +4803,11 @@
       </c>
       <c r="C209" t="inlineStr"/>
       <c r="D209" t="n">
-        <v>49670</v>
+        <v>50040</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
@@ -4824,11 +4824,11 @@
       </c>
       <c r="C210" t="inlineStr"/>
       <c r="D210" t="n">
-        <v>49480</v>
+        <v>49670</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
@@ -4845,11 +4845,11 @@
       </c>
       <c r="C211" t="inlineStr"/>
       <c r="D211" t="n">
-        <v>49470</v>
+        <v>49480</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
@@ -4866,11 +4866,11 @@
       </c>
       <c r="C212" t="inlineStr"/>
       <c r="D212" t="n">
-        <v>49300</v>
+        <v>49470</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
     </row>
@@ -4882,37 +4882,37 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U, (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge, FHD,15.6''/39.6cm, Win11,M365 Basic(1yr),Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
         </is>
       </c>
       <c r="C213" t="inlineStr"/>
       <c r="D213" t="n">
-        <v>47990</v>
+        <v>49300</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>HP 15, AMD Ryzen 5</t>
+          <t>HP 15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>HP 15, AMD Ryzen 5 7520U,(16GB LPDDR5, 512GB SSD), Anti-Glare, Micro-Edge, FHD, 15.6''/39.6cm, Win 11, Office 24,M365 Basic(1yr)*,Silver, 1.59kg, fc0690au, FHD Camera, Backlit KB Laptop</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U, (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge, FHD,15.6''/39.6cm, Win11,M365 Basic(1yr),Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C214" t="inlineStr"/>
       <c r="D214" t="n">
-        <v>53990</v>
+        <v>47990</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4933,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-08</t>
         </is>
       </c>
     </row>
@@ -4950,18 +4950,18 @@
       </c>
       <c r="C216" t="inlineStr"/>
       <c r="D216" t="n">
-        <v>54990</v>
+        <v>53990</v>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>hp_15,_amd_ryzen_5</t>
+          <t>HP 15, AMD Ryzen 5</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -4971,116 +4971,116 @@
       </c>
       <c r="C217" t="inlineStr"/>
       <c r="D217" t="n">
-        <v>61250</v>
+        <v>54990</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-24</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>HP 15, AMD Ryzen 7</t>
+          <t>hp_15,_amd_ryzen_5</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>HP 15, AMD Ryzen 7 7735HS (16GB DDR5,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365 Basic(1yr)* Office24, Silver, 1.59kg, fc1038AU, AMD Radeon FHD Camera w/Shutter, Backlit Laptop</t>
+          <t>HP 15, AMD Ryzen 5 7520U,(16GB LPDDR5, 512GB SSD), Anti-Glare, Micro-Edge, FHD, 15.6''/39.6cm, Win 11, Office 24,M365 Basic(1yr)*,Silver, 1.59kg, fc0690au, FHD Camera, Backlit KB Laptop</t>
         </is>
       </c>
       <c r="C218" t="inlineStr"/>
       <c r="D218" t="n">
-        <v>59990</v>
+        <v>61250</v>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>HP 15, Intel Core 5</t>
+          <t>HP 15, AMD Ryzen 7</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>HP 15, Intel Core 5 120U (14th Gen) 16GB DDR4, 512GB SSD, FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365 Basic(1yr), Office24, Silver,1.59kg, FD0640TU/682tu, FHD Camera w/Shutter, BL Laptop</t>
+          <t>HP 15, AMD Ryzen 7 7735HS (16GB DDR5,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365 Basic(1yr)* Office24, Silver, 1.59kg, fc1038AU, AMD Radeon FHD Camera w/Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C219" t="inlineStr"/>
       <c r="D219" t="n">
-        <v>65990</v>
+        <v>59990</v>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-14</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>HP 15, Intel Core Ultra</t>
+          <t>HP 15, Intel Core 5</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>HP 15, Intel Core Ultra 5 125H (24GB DDR5, 1TB SSD), Micro-Edge, Anti-Glare, FHD, 15''/39.6cm, Win11, M365* Office24, Silver, 1.65kg, FD1458TU, FHD Camera, Backlit Laptop</t>
+          <t>HP 15, Intel Core 5 120U (14th Gen) 16GB DDR4, 512GB SSD, FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365 Basic(1yr), Office24, Silver,1.59kg, FD0640TU/682tu, FHD Camera w/Shutter, BL Laptop</t>
         </is>
       </c>
       <c r="C220" t="inlineStr"/>
       <c r="D220" t="n">
-        <v>84990</v>
+        <v>65990</v>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>hp_15,_intel_core_i3-1315u-13th</t>
+          <t>HP 15, Intel Core Ultra</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>HP 15, Intel Core i3-1315U-13th Gen Laptop (8GB DDR4 Ram,512GB SSD) Anti-Glare, Micro-Edge,15.6'" FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera Shutter, 15-fd0569TU</t>
+          <t>HP 15, Intel Core Ultra 5 125H (24GB DDR5, 1TB SSD), Micro-Edge, Anti-Glare, FHD, 15''/39.6cm, Win11, M365* Office24, Silver, 1.65kg, FD1458TU, FHD Camera, Backlit Laptop</t>
         </is>
       </c>
       <c r="C221" t="inlineStr"/>
       <c r="D221" t="n">
-        <v>49490</v>
+        <v>84990</v>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>HP 255R G10 Notebook (AMD</t>
+          <t>hp_15,_intel_core_i3-1315u-13th</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>HP 255R G10 Notebook (AMD Athlon Silver 7120U /8GB/512GB/DOS) 15.6-inch(39.6cm), Anti-Glare, HD Laptop, Radeon Graphics, Silver,1.52kg</t>
+          <t>HP 15, Intel Core i3-1315U-13th Gen Laptop (8GB DDR4 Ram,512GB SSD) Anti-Glare, Micro-Edge,15.6'" FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera Shutter, 15-fd0569TU</t>
         </is>
       </c>
       <c r="C222" t="inlineStr"/>
       <c r="D222" t="n">
-        <v>41700</v>
+        <v>49490</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -5097,11 +5097,11 @@
       </c>
       <c r="C223" t="inlineStr"/>
       <c r="D223" t="n">
-        <v>39340</v>
+        <v>41700</v>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-04-16</t>
         </is>
       </c>
     </row>
@@ -5118,11 +5118,11 @@
       </c>
       <c r="C224" t="inlineStr"/>
       <c r="D224" t="n">
-        <v>40409</v>
+        <v>39340</v>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-10</t>
         </is>
       </c>
     </row>
@@ -5139,11 +5139,11 @@
       </c>
       <c r="C225" t="inlineStr"/>
       <c r="D225" t="n">
-        <v>39618</v>
+        <v>40409</v>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-20</t>
         </is>
       </c>
     </row>
@@ -5160,65 +5160,65 @@
       </c>
       <c r="C226" t="inlineStr"/>
       <c r="D226" t="n">
-        <v>39525</v>
+        <v>39618</v>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>HP Omen, Intel Core Ultra</t>
+          <t>HP 255R G10 Notebook (AMD</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>HP Omen, Intel Core Ultra 7 255H, 8GB RTX 5050, 24GB DDR5(Upgradeable) 1TB SSD, 2K, 165Hz, 3ms Response time, IPS, 16''/40.6cm, Win11, M365*Office24, Shadow Black, 2.43kg, am0240tx, RGB Gaming Laptop</t>
+          <t>HP 255R G10 Notebook (AMD Athlon Silver 7120U /8GB/512GB/DOS) 15.6-inch(39.6cm), Anti-Glare, HD Laptop, Radeon Graphics, Silver,1.52kg</t>
         </is>
       </c>
       <c r="C227" t="inlineStr"/>
       <c r="D227" t="n">
-        <v>129990</v>
+        <v>39525</v>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>HP OmniBook 3, AMD Ryzen</t>
+          <t>HP Omen, Intel Core Ultra</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>HP OmniBook 3, AMD Ryzen AI 5 330 (24GB DDR5 RAM, 1TB SSD) FHD, Anti-Glare, 15.6''/39.6cm, Win11, Office24, Glacier Silver,1.7kg, fn0074AU, FHD Camera w/Shutter, FPR, Backlit KB, Next Gen AI Laptop</t>
+          <t>HP Omen, Intel Core Ultra 7 255H, 8GB RTX 5050, 24GB DDR5(Upgradeable) 1TB SSD, 2K, 165Hz, 3ms Response time, IPS, 16''/40.6cm, Win11, M365*Office24, Shadow Black, 2.43kg, am0240tx, RGB Gaming Laptop</t>
         </is>
       </c>
       <c r="C228" t="inlineStr"/>
       <c r="D228" t="n">
-        <v>69990</v>
+        <v>129990</v>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-05-10</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>HP OmniBook 5 OLED (Previously</t>
+          <t>HP OmniBook 3, AMD Ryzen</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>HP OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x, 1TB SSD) 2K, 14''/35.6cm, Win11, M365 Basic(1yr)* Office24, Silver, 1.35kg, he0015QU, Light-Weight, Next-Gen AI Laptop</t>
+          <t>HP OmniBook 3, AMD Ryzen AI 5 330 (24GB DDR5 RAM, 1TB SSD) FHD, Anti-Glare, 15.6''/39.6cm, Win11, Office24, Glacier Silver,1.7kg, fn0074AU, FHD Camera w/Shutter, FPR, Backlit KB, Next Gen AI Laptop</t>
         </is>
       </c>
       <c r="C229" t="inlineStr"/>
@@ -5227,7 +5227,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
@@ -5239,16 +5239,16 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>HP OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x, 512GB SSD) 2K, 14''/35.6cm, Win11, M365 Basic(1yr)* Office24, Silver, 1.35kg, he0014QU, Light-Weight, Next-Gen AI Laptop</t>
+          <t>HP OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x, 1TB SSD) 2K, 14''/35.6cm, Win11, M365 Basic(1yr)* Office24, Silver, 1.35kg, he0015QU, Light-Weight, Next-Gen AI Laptop</t>
         </is>
       </c>
       <c r="C230" t="inlineStr"/>
       <c r="D230" t="n">
-        <v>78990</v>
+        <v>69990</v>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-05-14</t>
         </is>
       </c>
     </row>
@@ -5265,154 +5265,154 @@
       </c>
       <c r="C231" t="inlineStr"/>
       <c r="D231" t="n">
-        <v>66990</v>
+        <v>78990</v>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>hp_omnibook_3,_snapdragon_x</t>
+          <t>HP OmniBook 5 OLED (Previously</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>HP Omnibook 3, Snapdragon X Processor 45 TOPS (16GB LPDDR5x,512GB SSD) 2K WUXGA, Anti-Glare, 14''/35.6cm, Win 11, M365*Office 24,Silver,1.42kg, hz0026QU, Lighter mini Charger, FHD IR Camera, AI Laptop</t>
+          <t>HP OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x, 512GB SSD) 2K, 14''/35.6cm, Win11, M365 Basic(1yr)* Office24, Silver, 1.35kg, he0014QU, Light-Weight, Next-Gen AI Laptop</t>
         </is>
       </c>
       <c r="C232" t="inlineStr"/>
       <c r="D232" t="n">
-        <v>79990</v>
+        <v>66990</v>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>HP Omnibook 3, Snapdragon X</t>
+          <t>hp_omnibook_x_flip_oled</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>HP Omnibook 3, Snapdragon X Processor, 45 TOPS (16GB LPDDR5x, 512GB SSD) 2K, WUXGA, IPS, 14''/35.6cm, Win 11, Office 24, Silver, 1.4kg, hz0026QU, FHD IR Camera, 42% Lighter mini GaN Charger, AI Laptop</t>
+          <t>HP OmniBook X Flip OLED Intel Core Ultra 5 226V, 40 Tops (16GB LPDDR5x,1TB SSD) 3K, Touch, 120hz, 14''/35.6cm, Intel ARC Graphic,Win11, Office24, Meteor Silver, 1.38kg, fm0099TU,Pen, 2 in 1 AI Laptop</t>
         </is>
       </c>
       <c r="C233" t="inlineStr"/>
       <c r="D233" t="n">
-        <v>69990</v>
+        <v>115990</v>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>HP Omnibook 3, Snapdragon X</t>
+          <t>hp_omnibook_3,_snapdragon_x</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>HP Omnibook 3, Snapdragon X Processor, 45 TOPS (16GB LPDDR5x, 512GB SSD) 2K, WUXGA, IPS, 14''/35.6cm, Win 11, Office 24, Silver, 1.4kg, hz0026QU, FHD IR Camera, 42% Lighter mini GaN Charger, AI Laptop</t>
+          <t>HP Omnibook 3, Snapdragon X Processor 45 TOPS (16GB LPDDR5x,512GB SSD) 2K WUXGA, Anti-Glare, 14''/35.6cm, Win 11, M365*Office 24,Silver,1.42kg, hz0026QU, Lighter mini Charger, FHD IR Camera, AI Laptop</t>
         </is>
       </c>
       <c r="C234" t="inlineStr"/>
       <c r="D234" t="n">
-        <v>73990</v>
+        <v>79990</v>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>HP Omnibook 5 OLED (Previously</t>
+          <t>HP Omnibook 3, Snapdragon X</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>HP Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x,1TB SSD) 2K OLED,16''/40.6cm, Win11, M365*Office24, Glacier Silver, 1.59kg, fb0001QU, Backlit, Next-Gen AI Laptop</t>
+          <t>HP Omnibook 3, Snapdragon X Processor, 45 TOPS (16GB LPDDR5x, 512GB SSD) 2K, WUXGA, IPS, 14''/35.6cm, Win 11, Office 24, Silver, 1.4kg, hz0026QU, FHD IR Camera, 42% Lighter mini GaN Charger, AI Laptop</t>
         </is>
       </c>
       <c r="C235" t="inlineStr"/>
       <c r="D235" t="n">
-        <v>78850</v>
+        <v>69990</v>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-05-27</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>hp_omnibook_5_oled_(previously</t>
+          <t>HP Omnibook 3, Snapdragon X</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>HP Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor 45 Tops (16GB LPDDR5x, 1TB SSD) 2K,16''/40.6cm, Win11, Office24, Silver, 1.59kg, fb0001QU, Multi-Day Battery AI Laptop</t>
+          <t>HP Omnibook 3, Snapdragon X Processor, 45 TOPS (16GB LPDDR5x, 512GB SSD) 2K, WUXGA, IPS, 14''/35.6cm, Win 11, Office 24, Silver, 1.4kg, hz0026QU, FHD IR Camera, 42% Lighter mini GaN Charger, AI Laptop</t>
         </is>
       </c>
       <c r="C236" t="inlineStr"/>
       <c r="D236" t="n">
-        <v>77900</v>
+        <v>73990</v>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>hp_pavilion_plus,_intel_core</t>
+          <t>HP Omnibook 5 OLED (Previously</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>HP Pavilion Plus, Intel Core i5-1335U-13th Gen Laptop, (16GB LPDDR5x,512GB SSD),IPS, 300 nits, 14''(35.6cm) 2K,Win 11, M365 Basic(1yr), Office Home 24, Silver,1.38kg, 5MP Camera w/Shutter, ew0107TU</t>
+          <t>HP Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x,1TB SSD) 2K OLED,16''/40.6cm, Win11, M365*Office24, Glacier Silver, 1.59kg, fb0001QU, Backlit, Next-Gen AI Laptop</t>
         </is>
       </c>
       <c r="C237" t="inlineStr"/>
       <c r="D237" t="n">
-        <v>63990</v>
+        <v>78850</v>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>hp_professional_15_(2026),_intel</t>
+          <t>hp_omnibook_5_oled_(previously</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>HP Professional 15 (2026), Intel (i3 14th Gen) Core 3 100U - (8 GB/512 GB SSD/Intel UHD Graphics/Windows 11 Home) Thin &amp; Light Business Laptop/15.6" Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
+          <t>HP Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor 45 Tops (16GB LPDDR5x, 1TB SSD) 2K,16''/40.6cm, Win11, Office24, Silver, 1.59kg, fb0001QU, Multi-Day Battery AI Laptop</t>
         </is>
       </c>
       <c r="C238" t="inlineStr"/>
       <c r="D238" t="n">
-        <v>48990</v>
+        <v>77900</v>
       </c>
       <c r="E238" t="inlineStr">
         <is>
@@ -5423,42 +5423,42 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>HP Smartchoice OmniBook 5 OLED</t>
+          <t>hp_pavilion_plus,_intel_core</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>HP Smartchoice OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x, 1TB SSD) 2K, 14''/35.6cm, Win11, M365(1yr)*Office24, Silver,1.35kg, he0015QU,Light-Weight,Next-Gen AI Laptop</t>
+          <t>HP Pavilion Plus, Intel Core i5-1335U-13th Gen Laptop, (16GB LPDDR5x,512GB SSD),IPS, 300 nits, 14''(35.6cm) 2K,Win 11, M365 Basic(1yr), Office Home 24, Silver,1.38kg, 5MP Camera w/Shutter, ew0107TU</t>
         </is>
       </c>
       <c r="C239" t="inlineStr"/>
       <c r="D239" t="n">
-        <v>82990</v>
+        <v>63990</v>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>HP Smartchoice OmniBook 5 OLED</t>
+          <t>hp_professional_15_(2026),_intel</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>HP Smartchoice OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x, 1TB SSD) 2K, 14''/35.6cm, Win11, M365(1yr)*Office24, Silver,1.35kg, he0015QU,Light-Weight,Next-Gen AI Laptop</t>
+          <t>HP Professional 15 (2026), Intel (i3 14th Gen) Core 3 100U - (8 GB/512 GB SSD/Intel UHD Graphics/Windows 11 Home) Thin &amp; Light Business Laptop/15.6" Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
         </is>
       </c>
       <c r="C240" t="inlineStr"/>
       <c r="D240" t="n">
-        <v>76990</v>
+        <v>48990</v>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -5470,16 +5470,16 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>HP Smartchoice OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x, 512GB SSD) 2K, 14''/35.6cm, Win11, M365(1yr)* Office24, Silver, 1.35kg, he0014QU, Next-Gen AI Laptop</t>
+          <t>HP Smartchoice OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x, 1TB SSD) 2K, 14''/35.6cm, Win11, M365(1yr)*Office24, Silver,1.35kg, he0015QU,Light-Weight,Next-Gen AI Laptop</t>
         </is>
       </c>
       <c r="C241" t="inlineStr"/>
       <c r="D241" t="n">
-        <v>78990</v>
+        <v>82990</v>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
@@ -5491,58 +5491,58 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>HP Smartchoice OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x, 512GB SSD) 2K, 14''/35.6cm, Win11, M365(1yr)* Office24, Silver, 1.35kg, he0014QU, Next-Gen AI Laptop</t>
+          <t>HP Smartchoice OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x, 1TB SSD) 2K, 14''/35.6cm, Win11, M365(1yr)*Office24, Silver,1.35kg, he0015QU,Light-Weight,Next-Gen AI Laptop</t>
         </is>
       </c>
       <c r="C242" t="inlineStr"/>
       <c r="D242" t="n">
-        <v>79990</v>
+        <v>76990</v>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>HP Smartchoice Omnibook 5 OLED</t>
+          <t>HP Smartchoice OmniBook 5 OLED</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>HP Smartchoice Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x,1TB SSD) 2K OLED,16''/40.6cm, Win11, M365(1yr)*Office24, Glacier Silver, 1.59kg, fb0001QU,Next-Gen AI Laptop</t>
+          <t>HP Smartchoice OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x, 512GB SSD) 2K, 14''/35.6cm, Win11, M365(1yr)* Office24, Silver, 1.35kg, he0014QU, Next-Gen AI Laptop</t>
         </is>
       </c>
       <c r="C243" t="inlineStr"/>
       <c r="D243" t="n">
-        <v>68739</v>
+        <v>78990</v>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-24</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>HP Smartchoice Omnibook 5 OLED</t>
+          <t>HP Smartchoice OmniBook 5 OLED</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>HP Smartchoice Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x,1TB SSD) 2K OLED,16''/40.6cm, Win11, M365(1yr)*Office24, Glacier Silver, 1.59kg, fb0001QU,Next-Gen AI Laptop</t>
+          <t>HP Smartchoice OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x, 512GB SSD) 2K, 14''/35.6cm, Win11, M365(1yr)* Office24, Silver, 1.35kg, he0014QU, Next-Gen AI Laptop</t>
         </is>
       </c>
       <c r="C244" t="inlineStr"/>
       <c r="D244" t="n">
-        <v>68739</v>
+        <v>79990</v>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
@@ -5563,7 +5563,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -5580,11 +5580,11 @@
       </c>
       <c r="C246" t="inlineStr"/>
       <c r="D246" t="n">
-        <v>68323</v>
+        <v>68739</v>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
@@ -5601,11 +5601,11 @@
       </c>
       <c r="C247" t="inlineStr"/>
       <c r="D247" t="n">
-        <v>67940</v>
+        <v>68739</v>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-27</t>
         </is>
       </c>
     </row>
@@ -5622,74 +5622,74 @@
       </c>
       <c r="C248" t="inlineStr"/>
       <c r="D248" t="n">
-        <v>67940</v>
+        <v>68323</v>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-31</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>HP Smartchoice Victus, 13th Gen</t>
+          <t>HP Smartchoice Omnibook 5 OLED</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>HP Smartchoice Victus, 13th Gen Intel Core i7-13620H, 8GB RTX 5050, 24GB DDR5(Upgradeable) 1TB SSD, 144Hz, FHD, 15.6''/39.6cm, Win11, M365* Office24, Mica Silver, 2.29kg, fa2309TX, RGB Gaming Laptop</t>
+          <t>HP Smartchoice Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x,1TB SSD) 2K OLED,16''/40.6cm, Win11, M365(1yr)*Office24, Glacier Silver, 1.59kg, fb0001QU,Next-Gen AI Laptop</t>
         </is>
       </c>
       <c r="C249" t="inlineStr"/>
       <c r="D249" t="n">
-        <v>112990</v>
+        <v>67940</v>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>HP Smartchoice Victus, AMD Ryzen</t>
+          <t>HP Smartchoice Omnibook 5 OLED</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>HP Smartchoice Victus, AMD Ryzen 7 7445HS, 6GB RTX 3050, 16GB DDR5(Upgradeable) 512GB SSD, FHD, 144Hz, 300 nits, 15.6''/39.6cm, Win 11, M365* Office24, Blue, 2.29kg, fb3134AX/3120ax, Gaming Laptop</t>
+          <t>HP Smartchoice Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x,1TB SSD) 2K OLED,16''/40.6cm, Win11, M365(1yr)*Office24, Glacier Silver, 1.59kg, fb0001QU,Next-Gen AI Laptop</t>
         </is>
       </c>
       <c r="C250" t="inlineStr"/>
       <c r="D250" t="n">
-        <v>78990</v>
+        <v>67940</v>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-02</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>HP Smartchoice Victus, AMD Ryzen</t>
+          <t>HP Smartchoice Victus, 13th Gen</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>HP Smartchoice Victus, AMD Ryzen 7 7445HS, 6GB RTX 3050, 16GB DDR5(Upgradeable) 512GB SSD, FHD, 144Hz, 300 nits, 15.6''/39.6cm, Win 11, M365* Office24, Blue, 2.29kg, fb3134AX/3120ax, Gaming Laptop</t>
+          <t>HP Smartchoice Victus, 13th Gen Intel Core i7-13620H, 8GB RTX 5050, 24GB DDR5(Upgradeable) 1TB SSD, 144Hz, FHD, 15.6''/39.6cm, Win11, M365* Office24, Mica Silver, 2.29kg, fa2309TX, RGB Gaming Laptop</t>
         </is>
       </c>
       <c r="C251" t="inlineStr"/>
       <c r="D251" t="n">
-        <v>86990</v>
+        <v>112990</v>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-05-10</t>
         </is>
       </c>
     </row>
@@ -5706,74 +5706,74 @@
       </c>
       <c r="C252" t="inlineStr"/>
       <c r="D252" t="n">
-        <v>86990</v>
+        <v>78990</v>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>HP Victus, 14th Gen Intel</t>
+          <t>HP Smartchoice Victus, AMD Ryzen</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>HP Victus, 14th Gen Intel Core i5-14450HX, 6GB RTX 3050, 24GB DDR5, 512GB SSD, FHD, 144Hz, 300 nits, IPS,15.6''/39.6cm, Win11, M365* Office24, Mica Silver, 2.3kg, fa2303tx/fa2315tx, RGB Gaming Laptop</t>
+          <t>HP Smartchoice Victus, AMD Ryzen 7 7445HS, 6GB RTX 3050, 16GB DDR5(Upgradeable) 512GB SSD, FHD, 144Hz, 300 nits, 15.6''/39.6cm, Win 11, M365* Office24, Blue, 2.29kg, fb3134AX/3120ax, Gaming Laptop</t>
         </is>
       </c>
       <c r="C253" t="inlineStr"/>
       <c r="D253" t="n">
-        <v>103990</v>
+        <v>86990</v>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>HP Victus, AMD Ryzen 7</t>
+          <t>HP Smartchoice Victus, AMD Ryzen</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>HP Victus, AMD Ryzen 7 7445HS, 4GB RTX 2050, 16GB DDR5(Upgradeable) 512GB SSD, FHD, 144Hz, 300 nits, IPS, 15.6'', Win11, M365* Office24, Blue, 2.29kg, fb3189ax /3122/ 23ax Backlit, Gaming Laptop</t>
+          <t>HP Smartchoice Victus, AMD Ryzen 7 7445HS, 6GB RTX 3050, 16GB DDR5(Upgradeable) 512GB SSD, FHD, 144Hz, 300 nits, 15.6''/39.6cm, Win 11, M365* Office24, Blue, 2.29kg, fb3134AX/3120ax, Gaming Laptop</t>
         </is>
       </c>
       <c r="C254" t="inlineStr"/>
       <c r="D254" t="n">
-        <v>65990</v>
+        <v>86990</v>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>HP Victus, AMD Ryzen 7</t>
+          <t>HP Victus, 14th Gen Intel</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>HP Victus, AMD Ryzen 7 7445HS, 4GB RTX 2050, 16GB DDR5(Upgradeable) 512GB SSD, FHD, 144Hz, 300 nits, IPS, 15.6'', Win11, M365* Office24, Blue, 2.29kg, fb3189ax /3122/ 23ax Backlit, Gaming Laptop</t>
+          <t>HP Victus, 14th Gen Intel Core i5-14450HX, 6GB RTX 3050, 24GB DDR5, 512GB SSD, FHD, 144Hz, 300 nits, IPS,15.6''/39.6cm, Win11, M365* Office24, Mica Silver, 2.3kg, fa2303tx/fa2315tx, RGB Gaming Laptop</t>
         </is>
       </c>
       <c r="C255" t="inlineStr"/>
       <c r="D255" t="n">
-        <v>65990</v>
+        <v>103990</v>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-10</t>
         </is>
       </c>
     </row>
@@ -5785,16 +5785,16 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>HP Victus, AMD Ryzen 7 7445HS, 6GB RTX 4050, 16GB DDR5(Upgradeable) 512GB SSD, 144Hz, IPS, 300nits, FHD, 15.6''/39.6cm, Win11, M365* Office24, Blue, 2.29kg, fb3130AX, Backlit, DTS Audio, Gaming Laptop</t>
+          <t>HP Victus, AMD Ryzen 7 7445HS, 4GB RTX 2050, 16GB DDR5(Upgradeable) 512GB SSD, FHD, 144Hz, 300 nits, IPS, 15.6'', Win11, M365* Office24, Blue, 2.29kg, fb3189ax /3122/ 23ax Backlit, Gaming Laptop</t>
         </is>
       </c>
       <c r="C256" t="inlineStr"/>
       <c r="D256" t="n">
-        <v>90990</v>
+        <v>65990</v>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-21</t>
         </is>
       </c>
     </row>
@@ -5806,138 +5806,138 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>HP Victus, AMD Ryzen 7 7445HS, 6GB RTX 4050, 16GB DDR5(Upgradeable) 512GB SSD, 144Hz, IPS, 300nits, FHD, 15.6''/39.6cm, Win11, M365* Office24, Blue, 2.29kg, fb3130AX, Backlit, DTS Audio, Gaming Laptop</t>
+          <t>HP Victus, AMD Ryzen 7 7445HS, 4GB RTX 2050, 16GB DDR5(Upgradeable) 512GB SSD, FHD, 144Hz, 300 nits, IPS, 15.6'', Win11, M365* Office24, Blue, 2.29kg, fb3189ax /3122/ 23ax Backlit, Gaming Laptop</t>
         </is>
       </c>
       <c r="C257" t="inlineStr"/>
       <c r="D257" t="n">
-        <v>91990</v>
+        <v>65990</v>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-05-22</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Lenovo Chromebook Intel Celeron N4500</t>
+          <t>HP Victus, AMD Ryzen 7</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Lenovo Chromebook Intel Celeron N4500 (4GB RAM/64GB eMMC 5.1/11.6 Inch (29.46cm)/HD Display/2Wx2 Stereo Speakers/HD Camera/Chrome OS/Blue/1.21Kg), 82UY0014HA</t>
+          <t>HP Victus, AMD Ryzen 7 7445HS, 6GB RTX 4050, 16GB DDR5(Upgradeable) 512GB SSD, 144Hz, IPS, 300nits, FHD, 15.6''/39.6cm, Win11, M365* Office24, Blue, 2.29kg, fb3130AX, Backlit, DTS Audio, Gaming Laptop</t>
         </is>
       </c>
       <c r="C258" t="inlineStr"/>
       <c r="D258" t="n">
-        <v>21990</v>
+        <v>90990</v>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Lenovo Chromebook Intel Celeron N4500</t>
+          <t>HP Victus, AMD Ryzen 7</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Lenovo Chromebook Intel Celeron N4500 (4GB RAM/64GB eMMC 5.1/11.6 Inch (29.46cm)/HD Display/2Wx2 Stereo Speakers/HD Camera/Chrome OS/Blue/1.21Kg), 82UY0014HA</t>
+          <t>HP Victus, AMD Ryzen 7 7445HS, 6GB RTX 4050, 16GB DDR5(Upgradeable) 512GB SSD, 144Hz, IPS, 300nits, FHD, 15.6''/39.6cm, Win11, M365* Office24, Blue, 2.29kg, fb3130AX, Backlit, DTS Audio, Gaming Laptop</t>
         </is>
       </c>
       <c r="C259" t="inlineStr"/>
       <c r="D259" t="n">
-        <v>18990</v>
+        <v>91990</v>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Lenovo IdeaPad Slim 3 13th</t>
+          <t>Lenovo Chromebook Intel Celeron N4500</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Lenovo IdeaPad Slim 3 13th Gen Intel Core i5-13420H 15.3 inch (38.8cm) WUXGA IPS Laptop (16GB RAM/1TB SSD/Windows 11/MSO 365 Basic+Office 2024/Top Metal Cover/Backlit KB/Grey/1.6Kg), 83K100S0IN</t>
+          <t>Lenovo Chromebook Intel Celeron N4500 (4GB RAM/64GB eMMC 5.1/11.6 Inch (29.46cm)/HD Display/2Wx2 Stereo Speakers/HD Camera/Chrome OS/Blue/1.21Kg), 82UY0014HA</t>
         </is>
       </c>
       <c r="C260" t="inlineStr"/>
       <c r="D260" t="n">
-        <v>70990</v>
+        <v>21990</v>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>lenovo_ideapad_slim_3_13th</t>
+          <t>Lenovo Chromebook Intel Celeron N4500</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Lenovo IdeaPad Slim 3 13th Gen Intel Core i7 13620H, 16GB RAM, 512GB SSD, WUXGA IPS, 15.3"/38.8cm, Win 11, Office 2024, Top Metal Cover Grey, 1.6Kg, 83K100CJIN/S1IN, Backlit KB, Laptop</t>
+          <t>Lenovo Chromebook Intel Celeron N4500 (4GB RAM/64GB eMMC 5.1/11.6 Inch (29.46cm)/HD Display/2Wx2 Stereo Speakers/HD Camera/Chrome OS/Blue/1.21Kg), 82UY0014HA</t>
         </is>
       </c>
       <c r="C261" t="inlineStr"/>
       <c r="D261" t="n">
-        <v>81990</v>
+        <v>18990</v>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>lenovo_ideapad_slim_3,_13th</t>
+          <t>Lenovo IdeaPad Slim 3 13th</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Lenovo IdeaPad Slim 3, 13th Gen Intel Core i5 13420H, 24GB RAM, 1TB SSD, WUXGA IPS, 15.3"/38.8cm, Windows 11, Office Home 2024, Grey, 1.6Kg, Backlit Keyboard, 1Yr ADP Free, 83K100PLIN, Laptop</t>
+          <t>Lenovo IdeaPad Slim 3 13th Gen Intel Core i5-13420H 15.3 inch (38.8cm) WUXGA IPS Laptop (16GB RAM/1TB SSD/Windows 11/MSO 365 Basic+Office 2024/Top Metal Cover/Backlit KB/Grey/1.6Kg), 83K100S0IN</t>
         </is>
       </c>
       <c r="C262" t="inlineStr"/>
       <c r="D262" t="n">
-        <v>79990</v>
+        <v>70990</v>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-08</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>lenovo_ideapad_slim_3,_amd</t>
+          <t>lenovo_ideapad_slim_3_13th</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Lenovo IdeaPad Slim 3, AMD Ryzen 7 8840HS, 24GB RAM, 1TB SSD, WUXGA IPS, AI PC, 15.3"/38.8cm, Backlit Keyboard, Windows 11, Office Home 2024, Grey, 1.6Kg, 1Yr ADP Free, 83KA004TIN, AI Powered Laptop</t>
+          <t>Lenovo IdeaPad Slim 3 13th Gen Intel Core i5-13420H 15.3 inch (38.8cm) WUXGA IPS Laptop (16GB RAM/512GB SSD/Windows 11/Office 2024/Top Metal Cover/Backlit KB/Luna Grey/1.6Kg), 83K101JEIN</t>
         </is>
       </c>
       <c r="C263" t="inlineStr"/>
       <c r="D263" t="n">
-        <v>87990</v>
+        <v>74990</v>
       </c>
       <c r="E263" t="inlineStr">
         <is>
@@ -5948,210 +5948,210 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Lenovo Ideapad Slim 3 AMD</t>
+          <t>lenovo_ideapad_slim_3,_13th</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Lenovo Ideapad Slim 3 AMD Ryzen 5 7520U 15.6" (39.6cm) FHD Thin and Light Laptop (16GB/512GB SSD/Windows 11/Microsoft 365 Basic + Office Home 2024/Backlit Keyboard/Grey/1.6Kg), 82XQ00XDIN</t>
+          <t>Lenovo IdeaPad Slim 3, 13th Gen Intel Core i5 13420H, 24GB RAM, 1TB SSD, WUXGA IPS, 15.3"/38.8cm, Windows 11, Office Home 2024, Grey, 1.6Kg, Backlit Keyboard, 1Yr ADP Free, 83K100PLIN, Laptop</t>
         </is>
       </c>
       <c r="C264" t="inlineStr"/>
       <c r="D264" t="n">
-        <v>50750</v>
+        <v>79990</v>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Lenovo LOQ 2024, Intel Core</t>
+          <t>lenovo_ideapad_slim_3,_amd</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Lenovo LOQ 2024, Intel Core i5-13450HX, 13th Gen, NVIDIA RTX 4050-6GB, 16GB RAM, 512GB SSD, FHD 144Hz, 15.6"/39.6cm, Windows 11, Office Home 2024, Grey, 2.4Kg, 83DV018JIN, 1Yr ADP Free Gaming Laptop</t>
+          <t>Lenovo IdeaPad Slim 3, AMD Ryzen 7 8840HS, 24GB RAM, 1TB SSD, WUXGA IPS, AI PC, 15.3"/38.8cm, Backlit Keyboard, Windows 11, Office Home 2024, Grey, 1.6Kg, 1Yr ADP Free, 83KA004TIN, AI Powered Laptop</t>
         </is>
       </c>
       <c r="C265" t="inlineStr"/>
       <c r="D265" t="n">
-        <v>100544</v>
+        <v>87990</v>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Lenovo LOQ 2025 AMD Ryzen</t>
+          <t>lenovo_ideapad_slim_5,_amd</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Lenovo LOQ 2025 AMD Ryzen 7 250| NVIDIA RTX 5050 8GB (16GB RAM/1TB SSD/144Hz Refresh Rate/440 AI TOPS/15.6" (39.6cm)/Windows 11/Office 2024/3 Mon. Game Pass/Grey/2.4Kg), 83JG008KIN</t>
+          <t>Lenovo IdeaPad Slim 5, AMD Ryzen 5 7535HS, 16GB RAM, 512GB SSD, WUXGA IPS, 13.3"/33.7cm, Windows 11, Microsoft 365 Basic + Office 2024, Grey, 1.6Kg, Backlit KB, 1Yr ADP Free, 83J2004HIN, Laptop</t>
         </is>
       </c>
       <c r="C266" t="inlineStr"/>
       <c r="D266" t="n">
-        <v>134990</v>
+        <v>72990</v>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Lenovo LOQ 2025 Intel Core</t>
+          <t>Lenovo Ideapad Slim 3 AMD</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Lenovo LOQ 2025 Intel Core i7-14700HX| NVIDIA RTX 5060 8GB (32GB RAM/1TB SSD/144Hz Refresh Rate/572 AI TOPS/15.6" (39.6cm)/Windows 11/Office 2024/3 Mon. Game Pass/Grey/2.4Kg), 83JE00T3IN</t>
+          <t>Lenovo Ideapad Slim 3 AMD Ryzen 5 7520U 15.6" (39.6cm) FHD Thin and Light Laptop (16GB/512GB SSD/Windows 11/Microsoft 365 Basic + Office Home 2024/Backlit Keyboard/Grey/1.6Kg), 82XQ00XDIN</t>
         </is>
       </c>
       <c r="C267" t="inlineStr"/>
       <c r="D267" t="n">
-        <v>157990</v>
+        <v>50750</v>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-14</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Lenovo LOQ AMD Ryzen 5</t>
+          <t>Lenovo LOQ 2024, Intel Core</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Lenovo LOQ AMD Ryzen 5 7235HS | NVIDIA RTX 4050 6GB (16GB RAM/512GB SSD/144Hz Refresh Rate/15.6" (39.6cm)/Windows 11/Office Home 2024/3 Mon. Game Pass/Grey/2.4Kg), 83JC00NYIN AI Gaming Laptop</t>
+          <t>Lenovo LOQ 2024, Intel Core i5-13450HX, 13th Gen, NVIDIA RTX 4050-6GB, 16GB RAM, 512GB SSD, FHD 144Hz, 15.6"/39.6cm, Windows 11, Office Home 2024, Grey, 2.4Kg, 83DV018JIN, 1Yr ADP Free Gaming Laptop</t>
         </is>
       </c>
       <c r="C268" t="inlineStr"/>
       <c r="D268" t="n">
-        <v>88990</v>
+        <v>100544</v>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Lenovo LOQ, 13th Gen Intel</t>
+          <t>Lenovo LOQ 2025 AMD Ryzen</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Lenovo LOQ, 13th Gen Intel Core i7 13700HX, RTX 5050-8GB, 16GB RAM, 1TB SSD, FHD, 15.6"/39.6cm, 144Hz, Windows 11, Office 2024, Grey, 2.4Kg, 440 AI Tops, 3 Mon. Game Pass, 83JE00U7IN, AI Gaming Laptop</t>
+          <t>Lenovo LOQ 2025 AMD Ryzen 7 250| NVIDIA RTX 5050 8GB (16GB RAM/1TB SSD/144Hz Refresh Rate/440 AI TOPS/15.6" (39.6cm)/Windows 11/Office 2024/3 Mon. Game Pass/Grey/2.4Kg), 83JG008KIN</t>
         </is>
       </c>
       <c r="C269" t="inlineStr"/>
       <c r="D269" t="n">
-        <v>121869</v>
+        <v>134990</v>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Lenovo Legion 7 2025 Intel</t>
+          <t>Lenovo LOQ 2025 Intel Core</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Lenovo Legion 7 2025 Intel Core Ultra 9 275HX| NVIDIA RTX 5070 8GB (32GB RAM/1TB SSD/WQXGA OLED/240Hz/16(40.64cm)/Windows 11/Office 2024+AI Now/White/2.0Kg), 83KY001GIN AI Powered Gaming Laptop</t>
+          <t>Lenovo LOQ 2025 Intel Core i7-14700HX| NVIDIA RTX 5060 8GB (32GB RAM/1TB SSD/144Hz Refresh Rate/572 AI TOPS/15.6" (39.6cm)/Windows 11/Office 2024/3 Mon. Game Pass/Grey/2.4Kg), 83JE00T3IN</t>
         </is>
       </c>
       <c r="C270" t="inlineStr"/>
       <c r="D270" t="n">
-        <v>239391</v>
+        <v>157990</v>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Lenovo Legion Pro 5 2025</t>
+          <t>Lenovo LOQ AMD Ryzen 5</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Lenovo Legion Pro 5 2025 AMD Ryzen 9 9955HX | NVIDIA RTX 5060 8GB (32GB RAM/1TB SSD/WQXGA OLED/165Hz/16 (40.6cm)/Windows 11/Office 2024+AI Now/Black/2.3Kg), 83F2004CIN AI Powered Gaming Laptop</t>
+          <t>Lenovo LOQ AMD Ryzen 5 7235HS | NVIDIA RTX 4050 6GB (16GB RAM/512GB SSD/144Hz Refresh Rate/15.6" (39.6cm)/Windows 11/Office Home 2024/3 Mon. Game Pass/Grey/2.4Kg), 83JC00NYIN AI Gaming Laptop</t>
         </is>
       </c>
       <c r="C271" t="inlineStr"/>
       <c r="D271" t="n">
-        <v>245490</v>
+        <v>88990</v>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-19</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Lenovo Legion Pro 5 2025</t>
+          <t>Lenovo LOQ, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Lenovo Legion Pro 5 2025 AMD Ryzen 9 9955HX | NVIDIA RTX 5060 8GB (32GB RAM/1TB SSD/WQXGA OLED/165Hz/16 (40.6cm)/Windows 11/Office 2024+AI Now/Black/2.3Kg), 83F2004CIN AI Powered Gaming Laptop</t>
+          <t>Lenovo LOQ, 13th Gen Intel Core i7 13700HX, RTX 5050-8GB, 16GB RAM, 1TB SSD, FHD, 15.6"/39.6cm, 144Hz, Windows 11, Office 2024, Grey, 2.4Kg, 440 AI Tops, 3 Mon. Game Pass, 83JE00U7IN, AI Gaming Laptop</t>
         </is>
       </c>
       <c r="C272" t="inlineStr"/>
       <c r="D272" t="n">
-        <v>245490</v>
+        <v>121869</v>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Lenovo Legion Pro 5 2025</t>
+          <t>Lenovo Legion 7 2025 Intel</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Lenovo Legion Pro 5 2025 AMD Ryzen 9 9955HX | NVIDIA RTX 5060 8GB (32GB RAM/1TB SSD/WQXGA OLED/165Hz/16 (40.6cm)/Windows 11/Office 2024+AI Now/Black/2.3Kg), 83F2004CIN AI Powered Gaming Laptop</t>
+          <t>Lenovo Legion 7 2025 Intel Core Ultra 9 275HX| NVIDIA RTX 5070 8GB (32GB RAM/1TB SSD/WQXGA OLED/240Hz/16(40.64cm)/Windows 11/Office 2024+AI Now/White/2.0Kg), 83KY001GIN AI Powered Gaming Laptop</t>
         </is>
       </c>
       <c r="C273" t="inlineStr"/>
       <c r="D273" t="n">
-        <v>245490</v>
+        <v>239391</v>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-08</t>
         </is>
       </c>
     </row>
@@ -6172,150 +6172,150 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-22</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Lenovo Legion Pro 7 FIFA</t>
+          <t>Lenovo Legion Pro 5 2025</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Lenovo Legion Pro 7 FIFA World Cup 26 Edition Intel Core Ultra 9 275HX | NVIDIA RTX 5070Ti 12GB (32GB RAM/1TB SSD/WQXGA OLED/240Hz/16(40.6cm)/Windows 11/Black/2.4Kg), 83F500HPIN AI Gaming Laptop</t>
+          <t>Lenovo Legion Pro 5 2025 AMD Ryzen 9 9955HX | NVIDIA RTX 5060 8GB (32GB RAM/1TB SSD/WQXGA OLED/165Hz/16 (40.6cm)/Windows 11/Office 2024+AI Now/Black/2.3Kg), 83F2004CIN AI Powered Gaming Laptop</t>
         </is>
       </c>
       <c r="C275" t="inlineStr"/>
       <c r="D275" t="n">
-        <v>319990</v>
+        <v>245490</v>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-24</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Lenovo Smartchoice Ideapad 5 2-in-1</t>
+          <t>Lenovo Legion Pro 5 2025</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Lenovo Smartchoice Ideapad 5 2-in-1 13th Gen Intel Core i5-13420H (16GB RAM/512GB SSD/Windows 11/Office Home 2024/WUXGA IPS/14 (35.5cm)/Touchscreen 2-in-1/3Mon.Game Pass/Grey/1.6kg), 83KX0059IN Laptop</t>
+          <t>Lenovo Legion Pro 5 2025 AMD Ryzen 9 9955HX | NVIDIA RTX 5060 8GB (32GB RAM/1TB SSD/WQXGA OLED/165Hz/16 (40.6cm)/Windows 11/Office 2024+AI Now/Black/2.3Kg), 83F2004CIN AI Powered Gaming Laptop</t>
         </is>
       </c>
       <c r="C276" t="inlineStr"/>
       <c r="D276" t="n">
-        <v>74490</v>
+        <v>245490</v>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Lenovo ThinkBook 15 G5 AMD</t>
+          <t>Lenovo Legion Pro 5 2025</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Lenovo ThinkBook 15 G5 AMD Ryzen 7 7730U 15.6" FHD Antiglare 250 Nits Thin and Light Laptop (8GB RAM/512GB SSD/Windows 11 Home/Fingerprint Reader/Backlit/Mineral Grey/1 Year Onsite/1.7 kg), 21JFA00BIN</t>
+          <t>Lenovo Legion Pro 5 2025 AMD Ryzen 9 9955HX | NVIDIA RTX 5060 8GB (32GB RAM/1TB SSD/WQXGA OLED/165Hz/16 (40.6cm)/Windows 11/Office 2024+AI Now/Black/2.3Kg), 83F2004CIN AI Powered Gaming Laptop</t>
         </is>
       </c>
       <c r="C277" t="inlineStr"/>
       <c r="D277" t="n">
-        <v>59999</v>
+        <v>245490</v>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Lenovo ThinkBook 16, Intel Core</t>
+          <t>Lenovo Legion Pro 7 FIFA</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Lenovo ThinkBook 16, Intel Core Ultra 9 185H, 16GB RAM, 512GB SSD, WUXGA IPS 16” (40.64cm), Win 11 Home, Arctic Grey, 1.7Kg, 21SKA0J5IG, Fingerprint, Backlit, 300 Nits, 1Y Warranty, AI Powered Laptop</t>
+          <t>Lenovo Legion Pro 7 FIFA World Cup 26 Edition Intel Core Ultra 9 275HX | NVIDIA RTX 5070Ti 12GB (32GB RAM/1TB SSD/WQXGA OLED/240Hz/16(40.6cm)/Windows 11/Black/2.4Kg), 83F500HPIN AI Gaming Laptop</t>
         </is>
       </c>
       <c r="C278" t="inlineStr"/>
       <c r="D278" t="n">
-        <v>94990</v>
+        <v>319990</v>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-15</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Lenovo V14 Intel Core i3</t>
+          <t>Lenovo Smartchoice Ideapad 5 2-in-1</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Lenovo V14 Intel Core i3 13th Gen 14" FHD (1920x1080) Antiglare 250 Nits Thin and Light Laptop (16GB RAM/512GB SSD/Windows 11 Home/Office Home 2024/Iron Grey/1.43 kg), 83A0A0PCIN</t>
+          <t>Lenovo Smartchoice Ideapad 5 2-in-1 13th Gen Intel Core i5-13420H (16GB RAM/512GB SSD/Windows 11/Office Home 2024/WUXGA IPS/14 (35.5cm)/Touchscreen 2-in-1/3Mon.Game Pass/Grey/1.6kg), 83KX0059IN Laptop</t>
         </is>
       </c>
       <c r="C279" t="inlineStr"/>
       <c r="D279" t="n">
-        <v>70990</v>
+        <v>74490</v>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Lenovo V14 Intel Core i3</t>
+          <t>lenovo_thinkbook_14,_amd_ryzen</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Lenovo V14 Intel Core i3 13th Gen 14" FHD (1920x1080) Antiglare 250 Nits Thin and Light Laptop (16GB RAM/512GB SSD/Windows 11 Home/Office Home 2024/Iron Grey/1.43 kg), 83A0A0PCIN</t>
+          <t>Lenovo ThinkBook 14, AMD Ryzen 5 220, 16GB RAM, 1TB SSD, WUXGA IPS 14” (35.56cm), Windows 11 Home, Arctic Grey, 1.36Kg, 21V0A01SIG, Fingerprint, Backlit, 400 Nits, 1Y Warranty, Laptop</t>
         </is>
       </c>
       <c r="C280" t="inlineStr"/>
       <c r="D280" t="n">
-        <v>70990</v>
+        <v>90990</v>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 (2024), AMD</t>
+          <t>Lenovo ThinkBook 15 G5 AMD</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 (2024), AMD Ryzen 3 7320U Quad Core - (8GB/512GB SSD/AMD Radeon Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" FHD Display/Arctic Grey/1.57 kg/MS Office 2021</t>
+          <t>Lenovo ThinkBook 15 G5 AMD Ryzen 7 7730U 15.6" FHD Antiglare 250 Nits Thin and Light Laptop (8GB RAM/512GB SSD/Windows 11 Home/Fingerprint Reader/Backlit/Mineral Grey/1 Year Onsite/1.7 kg), 21JFA00BIN</t>
         </is>
       </c>
       <c r="C281" t="inlineStr"/>
       <c r="D281" t="n">
-        <v>44200</v>
+        <v>59999</v>
       </c>
       <c r="E281" t="inlineStr">
         <is>
@@ -6326,231 +6326,231 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 (2024), AMD</t>
+          <t>lenovo_thinkbook_16_amd_ryzen</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 (2024), AMD Ryzen 3 7320U Quad Core - (8GB/512GB SSD/AMD Radeon Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" FHD Display/Arctic Grey/1.57 kg/MS Office 2021</t>
+          <t>Lenovo ThinkBook 16 AMD Ryzen 5 7535HS (8GB RAM/512GB SSD/Win 11 Home/Office 2024/Backlit Keyboard/Fingerprint) 16" WUXGA IPS 300 Nits Thin &amp; Light Laptop/1Y Warranty/Aluminium Top/1.7kg, 21MWA0BRIN</t>
         </is>
       </c>
       <c r="C282" t="inlineStr"/>
       <c r="D282" t="n">
-        <v>44490</v>
+        <v>65063</v>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 (2024), AMD</t>
+          <t>Lenovo ThinkBook 16, Intel Core</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 (2024), AMD Ryzen 3 7320U Quad Core - (8GB/512GB SSD/AMD Radeon Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" FHD Display/Arctic Grey/1.57 kg/MS Office 2021</t>
+          <t>Lenovo ThinkBook 16, Intel Core Ultra 9 185H, 16GB RAM, 512GB SSD, WUXGA IPS 16” (40.64cm), Win 11 Home, Arctic Grey, 1.7Kg, 21SKA0J5IG, Fingerprint, Backlit, 300 Nits, 1Y Warranty, AI Powered Laptop</t>
         </is>
       </c>
       <c r="C283" t="inlineStr"/>
       <c r="D283" t="n">
-        <v>44490</v>
+        <v>94990</v>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-20</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 (2024), AMD</t>
+          <t>Lenovo V14 Intel Core i3</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 (2024), AMD Ryzen 3 7320U Quad Core - (8GB/512GB SSD/AMD Radeon Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" FHD Display/Arctic Grey/1.57 kg/MS Office 2021</t>
+          <t>Lenovo V14 Intel Core i3 13th Gen 14" FHD (1920x1080) Antiglare 250 Nits Thin and Light Laptop (16GB RAM/512GB SSD/Windows 11 Home/Office Home 2024/Iron Grey/1.43 kg), 83A0A0PCIN</t>
         </is>
       </c>
       <c r="C284" t="inlineStr"/>
       <c r="D284" t="n">
-        <v>44500</v>
+        <v>70990</v>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-20</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 (2024), AMD</t>
+          <t>Lenovo V14 Intel Core i3</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 (2024), AMD Ryzen 3 7320U Quad Core - (8GB/512GB SSD/AMD Radeon Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" FHD Display/Arctic Grey/1.57 kg/MS Office 2021</t>
+          <t>Lenovo V14 Intel Core i3 13th Gen 14" FHD (1920x1080) Antiglare 250 Nits Thin and Light Laptop (16GB RAM/512GB SSD/Windows 11 Home/Office Home 2024/Iron Grey/1.43 kg), 83A0A0PCIN</t>
         </is>
       </c>
       <c r="C285" t="inlineStr"/>
       <c r="D285" t="n">
-        <v>49999</v>
+        <v>70990</v>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 (2024), AMD</t>
+          <t>lenovo_v14_intel_core_i3</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 (2024), AMD Ryzen 3 7320U Quad Core - (8GB/512GB SSD/AMD Radeon Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" FHD Display/Arctic Grey/1.57 kg/MS Office 2021</t>
+          <t>Lenovo V14 Intel Core i3 13th Gen 14" FHD (1920x1080) Antiglare 250 Nits Thin and Light Laptop (16GB RAM/512GB SSD/Windows 11 Home/Office Home 2024/Iron Grey/1.43 kg), 83A0A0PCIN</t>
         </is>
       </c>
       <c r="C286" t="inlineStr"/>
       <c r="D286" t="n">
-        <v>49890</v>
+        <v>70990</v>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon</t>
+          <t>Lenovo V15 G4 (2024), AMD</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo V15 G4 (2024), AMD Ryzen 3 7320U Quad Core - (8GB/512GB SSD/AMD Radeon Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" FHD Display/Arctic Grey/1.57 kg/MS Office 2021</t>
         </is>
       </c>
       <c r="C287" t="inlineStr"/>
       <c r="D287" t="n">
-        <v>41999</v>
+        <v>44200</v>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-22</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon</t>
+          <t>Lenovo V15 G4 (2024), AMD</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo V15 G4 (2024), AMD Ryzen 3 7320U Quad Core - (8GB/512GB SSD/AMD Radeon Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" FHD Display/Arctic Grey/1.57 kg/MS Office 2021</t>
         </is>
       </c>
       <c r="C288" t="inlineStr"/>
       <c r="D288" t="n">
-        <v>41999</v>
+        <v>44490</v>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-24</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon</t>
+          <t>Lenovo V15 G4 (2024), AMD</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo V15 G4 (2024), AMD Ryzen 3 7320U Quad Core - (8GB/512GB SSD/AMD Radeon Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" FHD Display/Arctic Grey/1.57 kg/MS Office 2021</t>
         </is>
       </c>
       <c r="C289" t="inlineStr"/>
       <c r="D289" t="n">
-        <v>41999</v>
+        <v>44490</v>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon</t>
+          <t>Lenovo V15 G4 (2024), AMD</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo V15 G4 (2024), AMD Ryzen 3 7320U Quad Core - (8GB/512GB SSD/AMD Radeon Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" FHD Display/Arctic Grey/1.57 kg/MS Office 2021</t>
         </is>
       </c>
       <c r="C290" t="inlineStr"/>
       <c r="D290" t="n">
-        <v>42999</v>
+        <v>44500</v>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon</t>
+          <t>Lenovo V15 G4 (2024), AMD</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo V15 G4 (2024), AMD Ryzen 3 7320U Quad Core - (8GB/512GB SSD/AMD Radeon Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" FHD Display/Arctic Grey/1.57 kg/MS Office 2021</t>
         </is>
       </c>
       <c r="C291" t="inlineStr"/>
       <c r="D291" t="n">
-        <v>42999</v>
+        <v>49999</v>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon</t>
+          <t>Lenovo V15 G4 (2024), AMD</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo V15 G4 (2024), AMD Ryzen 3 7320U Quad Core - (8GB/512GB SSD/AMD Radeon Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" FHD Display/Arctic Grey/1.57 kg/MS Office 2021</t>
         </is>
       </c>
       <c r="C292" t="inlineStr"/>
       <c r="D292" t="n">
-        <v>42999</v>
+        <v>49890</v>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
@@ -6567,11 +6567,11 @@
       </c>
       <c r="C293" t="inlineStr"/>
       <c r="D293" t="n">
-        <v>42999</v>
+        <v>41999</v>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
@@ -6588,11 +6588,11 @@
       </c>
       <c r="C294" t="inlineStr"/>
       <c r="D294" t="n">
-        <v>42999</v>
+        <v>41999</v>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-05-28</t>
         </is>
       </c>
     </row>
@@ -6609,11 +6609,11 @@
       </c>
       <c r="C295" t="inlineStr"/>
       <c r="D295" t="n">
-        <v>44999</v>
+        <v>41999</v>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-31</t>
         </is>
       </c>
     </row>
@@ -6630,11 +6630,11 @@
       </c>
       <c r="C296" t="inlineStr"/>
       <c r="D296" t="n">
-        <v>43999</v>
+        <v>42999</v>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -6651,11 +6651,11 @@
       </c>
       <c r="C297" t="inlineStr"/>
       <c r="D297" t="n">
-        <v>43999</v>
+        <v>42999</v>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-02</t>
         </is>
       </c>
     </row>
@@ -6672,11 +6672,11 @@
       </c>
       <c r="C298" t="inlineStr"/>
       <c r="D298" t="n">
-        <v>43999</v>
+        <v>42999</v>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
@@ -6693,11 +6693,11 @@
       </c>
       <c r="C299" t="inlineStr"/>
       <c r="D299" t="n">
-        <v>44999</v>
+        <v>42999</v>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
@@ -6714,18 +6714,18 @@
       </c>
       <c r="C300" t="inlineStr"/>
       <c r="D300" t="n">
-        <v>44999</v>
+        <v>42999</v>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>lenovo_v15_g4_amd_athlon</t>
+          <t>Lenovo V15 G4 AMD Athlon</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -6739,133 +6739,133 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen</t>
+          <t>Lenovo V15 G4 AMD Athlon</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C302" t="inlineStr"/>
       <c r="D302" t="n">
-        <v>49999</v>
+        <v>43999</v>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen</t>
+          <t>Lenovo V15 G4 AMD Athlon</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C303" t="inlineStr"/>
       <c r="D303" t="n">
-        <v>52760</v>
+        <v>43999</v>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen</t>
+          <t>Lenovo V15 G4 AMD Athlon</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C304" t="inlineStr"/>
       <c r="D304" t="n">
-        <v>52300</v>
+        <v>43999</v>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen</t>
+          <t>Lenovo V15 G4 AMD Athlon</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C305" t="inlineStr"/>
       <c r="D305" t="n">
-        <v>52490</v>
+        <v>44999</v>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-12</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen</t>
+          <t>Lenovo V15 G4 AMD Athlon</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C306" t="inlineStr"/>
       <c r="D306" t="n">
-        <v>52300</v>
+        <v>44999</v>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen</t>
+          <t>lenovo_v15_g4_amd_athlon</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C307" t="inlineStr"/>
       <c r="D307" t="n">
-        <v>52890</v>
+        <v>44999</v>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -6882,11 +6882,11 @@
       </c>
       <c r="C308" t="inlineStr"/>
       <c r="D308" t="n">
-        <v>53999</v>
+        <v>49999</v>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-21</t>
         </is>
       </c>
     </row>
@@ -6903,11 +6903,11 @@
       </c>
       <c r="C309" t="inlineStr"/>
       <c r="D309" t="n">
-        <v>53999</v>
+        <v>52760</v>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-24</t>
         </is>
       </c>
     </row>
@@ -6924,322 +6924,322 @@
       </c>
       <c r="C310" t="inlineStr"/>
       <c r="D310" t="n">
-        <v>54790</v>
+        <v>52300</v>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>lenovo_v15_g6_amd_ryzen</t>
+          <t>Lenovo V15 G4 AMD Ryzen</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Lenovo V15 G6 AMD Ryzen 7 170 (Coequal 7735HS) 15.6" (39.62cm) FHD Thin and Light Business Laptop (16GB RAM DDR5/ 512GB SSD/Windows 11/ MS Office 2024/ AMD Radeon Graphics/Luna Grey/ 1.6 kg)</t>
+          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
         </is>
       </c>
       <c r="C311" t="inlineStr"/>
       <c r="D311" t="n">
-        <v>64999</v>
+        <v>52490</v>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Lenovo Yoga Slim 7 (Smartchoice)</t>
+          <t>Lenovo V15 G4 AMD Ryzen</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Lenovo Yoga Slim 7 (Smartchoice) Aura Edition, Intel Core Ultra 5 226V, 16GB RAM, 1TB SSD, WUXGA OLED, Copilot+ AI PC, 40 TOPS, 14"/35.5cm, Windows 11, Office 2024, Grey, 1.19Kg, 83JX005FIN, AI Laptop</t>
+          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
         </is>
       </c>
       <c r="C312" t="inlineStr"/>
       <c r="D312" t="n">
-        <v>99990</v>
+        <v>52300</v>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-27</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Lenovo Yoga Slim 7 (Smartchoice)</t>
+          <t>Lenovo V15 G4 AMD Ryzen</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Lenovo Yoga Slim 7 (Smartchoice) Aura Edition, Intel Core Ultra 5 226V, 16GB RAM, 1TB SSD, WUXGA OLED, Copilot+ AI PC, 40 TOPS, 14"/35.5cm, Windows 11, Office 2024, Grey, 1.19Kg, 83JX005FIN, AI Laptop</t>
+          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
         </is>
       </c>
       <c r="C313" t="inlineStr"/>
       <c r="D313" t="n">
-        <v>105939</v>
+        <v>52890</v>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-31</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Lenovo Yoga Slim 7, Intel</t>
+          <t>Lenovo V15 G4 AMD Ryzen</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Lenovo Yoga Slim 7, Intel Core Ultra 5 125H, 16GB RAM, 512GB SSD, AI PC, WUXGA-OLED, 14"/35.5cm, Windows 11, Microsoft 365 Basic + Office 2024, Grey, 1.39Kg, 83CV00DFIN, AI Powered Laptop</t>
+          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
         </is>
       </c>
       <c r="C314" t="inlineStr"/>
       <c r="D314" t="n">
-        <v>77990</v>
+        <v>53999</v>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Lenovo Yoga Slim 7, Intel</t>
+          <t>Lenovo V15 G4 AMD Ryzen</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Lenovo Yoga Slim 7, Intel Core Ultra 5 125H, 16GB RAM, 512GB SSD, AI PC, WUXGA-OLED, 14"/35.5cm, Windows 11, Microsoft 365 Basic + Office 2024, Grey, 1.39Kg, 83CV00DFIN, AI Powered Laptop</t>
+          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
         </is>
       </c>
       <c r="C315" t="inlineStr"/>
       <c r="D315" t="n">
-        <v>84990</v>
+        <v>53999</v>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-02</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Lenovo {SmartChoice Chromebook, Intel Celeron</t>
+          <t>Lenovo V15 G4 AMD Ryzen</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Lenovo {SmartChoice Chromebook, Intel Celeron N4500, 4GB RAM, 64GB eMMC, HD, 11.6"/29.46cm, Chrome OS, Blue, 1.21Kg, 2Wx2 Stereo Speakers, HD Camera, 82UY0014HA, Laptop</t>
+          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
         </is>
       </c>
       <c r="C316" t="inlineStr"/>
       <c r="D316" t="n">
-        <v>21990</v>
+        <v>54790</v>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Lenovo {SmartChoice Chromebook, Intel Celeron</t>
+          <t>lenovo_v15_g6_amd_ryzen</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Lenovo {SmartChoice Chromebook, Intel Celeron N4500, 4GB RAM, 64GB eMMC, HD, 11.6"/29.46cm, Chrome OS, Blue, 1.21Kg, 2Wx2 Stereo Speakers, HD Camera, 82UY0014HA, Laptop</t>
+          <t>Lenovo V15 G6 AMD Ryzen 7 170 (Coequal 7735HS) 15.6" (39.62cm) FHD Thin and Light Business Laptop (16GB RAM DDR5/ 512GB SSD/Windows 11/ MS Office 2024/ AMD Radeon Graphics/Luna Grey/ 1.6 kg)</t>
         </is>
       </c>
       <c r="C317" t="inlineStr"/>
       <c r="D317" t="n">
-        <v>17990</v>
+        <v>64999</v>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Samsung Galaxy Book6 (Gray, 16GB</t>
+          <t>Lenovo Yoga Slim 7 (Smartchoice)</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Samsung Galaxy Book6 (Gray, 16GB RAM, 1TB SSD) | Intel Core Ultra 5 (Series 3) | 16" WUXGA+ Display with Touchscreen | 24Hrs Battery Life | 120 Hz Refresh Rate | Dolby Atmos Stereo Speakers | AI PC</t>
+          <t>Lenovo Yoga Slim 7 (Smartchoice) Aura Edition, Intel Core Ultra 5 226V, 16GB RAM, 1TB SSD, WUXGA OLED, Copilot+ AI PC, 40 TOPS, 14"/35.5cm, Windows 11, Office 2024, Grey, 1.19Kg, 83JX005FIN, AI Laptop</t>
         </is>
       </c>
       <c r="C318" t="inlineStr"/>
       <c r="D318" t="n">
-        <v>146990</v>
+        <v>99990</v>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-15</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Thomson NEO 14.1 Inch IN-P14C</t>
+          <t>Lenovo Yoga Slim 7 (Smartchoice)</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Thomson NEO 14.1 Inch IN-P14C Intel Celeron Dual Core N4020 Processor &amp; Window 11 Home Notebook (4 GB RAM DDR4/ 128 GB SSD/Numeric Touch Pad/Thin &amp; Light Weight/Silver)</t>
+          <t>Lenovo Yoga Slim 7 (Smartchoice) Aura Edition, Intel Core Ultra 5 226V, 16GB RAM, 1TB SSD, WUXGA OLED, Copilot+ AI PC, 40 TOPS, 14"/35.5cm, Windows 11, Office 2024, Grey, 1.19Kg, 83JX005FIN, AI Laptop</t>
         </is>
       </c>
       <c r="C319" t="inlineStr"/>
       <c r="D319" t="n">
-        <v>12990</v>
+        <v>105939</v>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-19</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Thomson NEO 14.1 Inch IN-P14C</t>
+          <t>Lenovo Yoga Slim 7, Intel</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Thomson NEO 14.1 Inch IN-P14C Intel Celeron Dual Core N4020 Processor &amp; Window 11 Home Notebook (4 GB RAM DDR4/ 128 GB SSD/Numeric Touch Pad/Thin &amp; Light Weight/Silver)</t>
+          <t>Lenovo Yoga Slim 7, Intel Core Ultra 5 125H, 16GB RAM, 512GB SSD, AI PC, WUXGA-OLED, 14"/35.5cm, Windows 11, Microsoft 365 Basic + Office 2024, Grey, 1.39Kg, 83CV00DFIN, AI Powered Laptop</t>
         </is>
       </c>
       <c r="C320" t="inlineStr"/>
       <c r="D320" t="n">
-        <v>12990</v>
+        <v>77990</v>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-05-15</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Thomson NEO 14.1 Inch IN-P14C</t>
+          <t>Lenovo Yoga Slim 7, Intel</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Thomson NEO 14.1 Inch IN-P14C Intel Celeron Dual Core N4020 Processor &amp; Window 11 Home Notebook (4 GB RAM DDR4/ 128 GB SSD/Numeric Touch Pad/Thin &amp; Light Weight/Silver)</t>
+          <t>Lenovo Yoga Slim 7, Intel Core Ultra 5 125H, 16GB RAM, 512GB SSD, AI PC, WUXGA-OLED, 14"/35.5cm, Windows 11, Microsoft 365 Basic + Office 2024, Grey, 1.39Kg, 83CV00DFIN, AI Powered Laptop</t>
         </is>
       </c>
       <c r="C321" t="inlineStr"/>
       <c r="D321" t="n">
-        <v>22990</v>
+        <v>84990</v>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-19</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Thomson NEO 14.1 Inch IN-P14C</t>
+          <t>Lenovo {SmartChoice Chromebook, Intel Celeron</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Thomson NEO 14.1 Inch IN-P14C Intel Celeron Dual Core N4020 Processor &amp; Window 11 Home Notebook (4 GB RAM DDR4/ 128 GB SSD/Numeric Touch Pad/Thin &amp; Light Weight/Silver)</t>
+          <t>Lenovo {SmartChoice Chromebook, Intel Celeron N4500, 4GB RAM, 64GB eMMC, HD, 11.6"/29.46cm, Chrome OS, Blue, 1.21Kg, 2Wx2 Stereo Speakers, HD Camera, 82UY0014HA, Laptop</t>
         </is>
       </c>
       <c r="C322" t="inlineStr"/>
       <c r="D322" t="n">
-        <v>22990</v>
+        <v>21990</v>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>acer Aspire 3, Intel Core</t>
+          <t>Lenovo {SmartChoice Chromebook, Intel Celeron</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>acer Aspire 3, Intel Core Celeron N4500, 12GB LPDDR4X RAM, 512GB SSD, HD, 15.6"/39.62cm, Windows 11 Home, Pure Silver, 1.5KG, A325-45, Thin and Light Laptop</t>
+          <t>Lenovo {SmartChoice Chromebook, Intel Celeron N4500, 4GB RAM, 64GB eMMC, HD, 11.6"/29.46cm, Chrome OS, Blue, 1.21Kg, 2Wx2 Stereo Speakers, HD Camera, 82UY0014HA, Laptop</t>
         </is>
       </c>
       <c r="C323" t="inlineStr"/>
       <c r="D323" t="n">
-        <v>39890</v>
+        <v>17990</v>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-05-08</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>acer Aspire Lite, AMD Ryzen</t>
+          <t>primebook_2_max_(2026)_|</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>acer Aspire Lite, AMD Ryzen 3 5300U Processor, 16 GB RAM, 512GB SSD, Full HD, 15.6"/39.62cm, Windows 11 Home, Steel Gray, 1.59KG, AL15-41, Metal Body, Premium Thin and Light Laptop</t>
+          <t>Primebook 2 Max (2026) | 8GB RAM, 256GB UFS Storage | 15.6-Inch Full HD IPS Display | 12hrs Battery | MediaTek Helio G99 | Android 15 (PrimeOS 3.0) | Backlit Keyboard | in-Built AI (Gray)</t>
         </is>
       </c>
       <c r="C324" t="inlineStr"/>
       <c r="D324" t="n">
-        <v>42990</v>
+        <v>29990</v>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD</t>
+          <t>Samsung Galaxy Book6 (Gray, 16GB</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
+          <t>Samsung Galaxy Book6 (Gray, 16GB RAM, 1TB SSD) | Intel Core Ultra 5 (Series 3) | 16" WUXGA+ Display with Touchscreen | 24Hrs Battery Life | 120 Hz Refresh Rate | Dolby Atmos Stereo Speakers | AI PC</t>
         </is>
       </c>
       <c r="C325" t="inlineStr"/>
       <c r="D325" t="n">
-        <v>45990</v>
+        <v>146990</v>
       </c>
       <c r="E325" t="inlineStr">
         <is>
@@ -7250,59 +7250,59 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD</t>
+          <t>Thomson NEO 14.1 Inch IN-P14C</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
+          <t>Thomson NEO 14.1 Inch IN-P14C Intel Celeron Dual Core N4020 Processor &amp; Window 11 Home Notebook (4 GB RAM DDR4/ 128 GB SSD/Numeric Touch Pad/Thin &amp; Light Weight/Silver)</t>
         </is>
       </c>
       <c r="C326" t="inlineStr"/>
       <c r="D326" t="n">
-        <v>45990</v>
+        <v>12990</v>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD</t>
+          <t>Thomson NEO 14.1 Inch IN-P14C</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
+          <t>Thomson NEO 14.1 Inch IN-P14C Intel Celeron Dual Core N4020 Processor &amp; Window 11 Home Notebook (4 GB RAM DDR4/ 128 GB SSD/Numeric Touch Pad/Thin &amp; Light Weight/Silver)</t>
         </is>
       </c>
       <c r="C327" t="inlineStr"/>
       <c r="D327" t="n">
-        <v>45990</v>
+        <v>12990</v>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD</t>
+          <t>Thomson NEO 14.1 Inch IN-P14C</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
+          <t>Thomson NEO 14.1 Inch IN-P14C Intel Celeron Dual Core N4020 Processor &amp; Window 11 Home Notebook (4 GB RAM DDR4/ 128 GB SSD/Numeric Touch Pad/Thin &amp; Light Weight/Silver)</t>
         </is>
       </c>
       <c r="C328" t="inlineStr"/>
       <c r="D328" t="n">
-        <v>43990</v>
+        <v>22990</v>
       </c>
       <c r="E328" t="inlineStr">
         <is>
@@ -7313,63 +7313,63 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD</t>
+          <t>Thomson NEO 14.1 Inch IN-P14C</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
+          <t>Thomson NEO 14.1 Inch IN-P14C Intel Celeron Dual Core N4020 Processor &amp; Window 11 Home Notebook (4 GB RAM DDR4/ 128 GB SSD/Numeric Touch Pad/Thin &amp; Light Weight/Silver)</t>
         </is>
       </c>
       <c r="C329" t="inlineStr"/>
       <c r="D329" t="n">
-        <v>43990</v>
+        <v>22990</v>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD</t>
+          <t>acer Aspire 3, Intel Core</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
+          <t>acer Aspire 3, Intel Core Celeron N4500, 12GB LPDDR4X RAM, 512GB SSD, HD, 15.6"/39.62cm, Windows 11 Home, Pure Silver, 1.5KG, A325-45, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C330" t="inlineStr"/>
       <c r="D330" t="n">
-        <v>43990</v>
+        <v>39890</v>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD</t>
+          <t>acer Aspire Lite, AMD Ryzen</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
+          <t>acer Aspire Lite, AMD Ryzen 3 5300U Processor, 16 GB RAM, 512GB SSD, Full HD, 15.6"/39.62cm, Windows 11 Home, Steel Gray, 1.59KG, AL15-41, Metal Body, Premium Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C331" t="inlineStr"/>
       <c r="D331" t="n">
-        <v>43990</v>
+        <v>42990</v>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-04-16</t>
         </is>
       </c>
     </row>
@@ -7386,238 +7386,238 @@
       </c>
       <c r="C332" t="inlineStr"/>
       <c r="D332" t="n">
-        <v>43990</v>
+        <v>45990</v>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop ModeI 7410 Laptop |</t>
+          <t>acer SmartChoice Aspire Lite, AMD</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop ModeI 7410 Laptop | InteI Core i5 10th Gen | 16GB DDR4 RAM | 256GB SSD | 14" Full HD Display | Win 10 Pro | InteI UHD Graphics 620 | 3 Months Seller Warranty | A+ Condition (Refab)</t>
+          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C333" t="inlineStr"/>
       <c r="D333" t="n">
-        <v>27299</v>
+        <v>45990</v>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-16</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5</t>
+          <t>acer SmartChoice Aspire Lite, AMD</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5 11th Gen Processor |8GB DDR4 RAM |256GB SSD |14" FHD Display | Win10 | A+ Condition Laptop (Refab)</t>
+          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C334" t="inlineStr"/>
       <c r="D334" t="n">
-        <v>26999</v>
+        <v>45990</v>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5</t>
+          <t>acer SmartChoice Aspire Lite, AMD</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5 11th Gen Processor |8GB DDR4 RAM |256GB SSD |14" FHD Display | Win10 | A+ Condition Laptop (Refab)</t>
+          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C335" t="inlineStr"/>
       <c r="D335" t="n">
-        <v>26400</v>
+        <v>43990</v>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-08</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5</t>
+          <t>acer SmartChoice Aspire Lite, AMD</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5 11th Gen Processor |8GB DDR4 RAM |256GB SSD |14" FHD Display | Win10 | A+ Condition Laptop (Refab)</t>
+          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C336" t="inlineStr"/>
       <c r="D336" t="n">
-        <v>28599</v>
+        <v>43990</v>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5</t>
+          <t>acer SmartChoice Aspire Lite, AMD</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5 11th Gen Processor |8GB DDR4 RAM |256GB SSD |14" FHD Display | Win10 | A+ Condition Laptop (Refab)</t>
+          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C337" t="inlineStr"/>
       <c r="D337" t="n">
-        <v>28999</v>
+        <v>43990</v>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-10</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5</t>
+          <t>acer SmartChoice Aspire Lite, AMD</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5 11th Gen Processor |8GB DDR4 RAM |256GB SSD |14" FHD Display | Win10 | A+ Condition Laptop (Refab)</t>
+          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C338" t="inlineStr"/>
       <c r="D338" t="n">
-        <v>31990</v>
+        <v>43990</v>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-14</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5</t>
+          <t>acer SmartChoice Aspire Lite, AMD</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5 11th Gen Processor |8GB DDR4 RAM |256GB SSD |14" FHD Display | Win10 | A+ Condition Laptop (Refab)</t>
+          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C339" t="inlineStr"/>
       <c r="D339" t="n">
-        <v>35490</v>
+        <v>43990</v>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-15</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5</t>
+          <t>𝗗𝗲𝗹𝗹Laptop ModeI 7410 Laptop |</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5 11th Gen Processor |8GB DDR4 RAM |256GB SSD |14" FHD Display | Win10 | A+ Condition Laptop (Refab)</t>
+          <t>𝗗𝗲𝗹𝗹Laptop ModeI 7410 Laptop | InteI Core i5 10th Gen | 16GB DDR4 RAM | 256GB SSD | 14" Full HD Display | Win 10 Pro | InteI UHD Graphics 620 | 3 Months Seller Warranty | A+ Condition (Refab)</t>
         </is>
       </c>
       <c r="C340" t="inlineStr"/>
       <c r="D340" t="n">
-        <v>37490</v>
+        <v>27299</v>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Model E5570 Laptop | Core</t>
+          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Model E5570 Laptop | Core i7 6th Gen | 8GB Fast RAM | 256GB SSD | 15.6" HD Display | HD Graphics | Win 10 | WiFi| (Pre-Owned &amp; Tested)</t>
+          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5 11th Gen Processor |8GB DDR4 RAM |256GB SSD |14" FHD Display | Win10 | A+ Condition Laptop (Refab)</t>
         </is>
       </c>
       <c r="C341" t="inlineStr"/>
       <c r="D341" t="n">
-        <v>20599</v>
+        <v>26999</v>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-10</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>𝗛𝗣𝗣𝗿𝗼𝗯𝗼𝗼𝗸Model 430 G3 Business Laptop</t>
+          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>𝗛𝗣𝗣𝗿𝗼𝗯𝗼𝗼𝗸Model 430 G3 Business Laptop | InteI i5 6th Gen | 8GB RAM | 256GB SSD | WiFi | Webcam | Win10 Pro (Refab)</t>
+          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5 11th Gen Processor |8GB DDR4 RAM |256GB SSD |14" FHD Display | Win10 | A+ Condition Laptop (Refab)</t>
         </is>
       </c>
       <c r="C342" t="inlineStr"/>
       <c r="D342" t="n">
-        <v>20299</v>
+        <v>26400</v>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-20</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>𝗛𝗣𝗣𝗿𝗼𝗯𝗼𝗼𝗸Model 430 G3 Business Laptop</t>
+          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>𝗛𝗣𝗣𝗿𝗼𝗯𝗼𝗼𝗸Model 430 G3 Business Laptop | 𝗜𝗡𝗧𝗘𝗟i5 6th Gen | 8GB RAM | 256GB SSD | WiFi | Webcam | Win10 Pro (Refab)</t>
+          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5 11th Gen Processor |8GB DDR4 RAM |256GB SSD |14" FHD Display | Win10 | A+ Condition Laptop (Refab)</t>
         </is>
       </c>
       <c r="C343" t="inlineStr"/>
       <c r="D343" t="n">
-        <v>20499</v>
+        <v>28599</v>
       </c>
       <c r="E343" t="inlineStr">
         <is>
@@ -7628,21 +7628,189 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>𝗛𝗣𝗣𝗿𝗼𝗯𝗼𝗼𝗸Model 430 G3 Business Laptop</t>
+          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>𝗛𝗣𝗣𝗿𝗼𝗯𝗼𝗼𝗸Model 430 G3 Business Laptop | 𝗜𝗡𝗧𝗘𝗟i5 6th Gen | 8GB RAM | 256GB SSD | WiFi | Webcam | Win10 Pro (Refab)</t>
+          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5 11th Gen Processor |8GB DDR4 RAM |256GB SSD |14" FHD Display | Win10 | A+ Condition Laptop (Refab)</t>
         </is>
       </c>
       <c r="C344" t="inlineStr"/>
       <c r="D344" t="n">
+        <v>28999</v>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5 11th Gen Processor |8GB DDR4 RAM |256GB SSD |14" FHD Display | Win10 | A+ Condition Laptop (Refab)</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr"/>
+      <c r="D345" t="n">
+        <v>31990</v>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5 11th Gen Processor |8GB DDR4 RAM |256GB SSD |14" FHD Display | Win10 | A+ Condition Laptop (Refab)</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr"/>
+      <c r="D346" t="n">
+        <v>35490</v>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5 11th Gen Processor |8GB DDR4 RAM |256GB SSD |14" FHD Display | Win10 | A+ Condition Laptop (Refab)</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr"/>
+      <c r="D347" t="n">
+        <v>37490</v>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Model E5570 Laptop | Core</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Model E5570 Laptop | Core i7 6th Gen | 8GB Fast RAM | 256GB SSD | 15.6" HD Display | HD Graphics | Win 10 | WiFi| (Pre-Owned &amp; Tested)</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr"/>
+      <c r="D348" t="n">
+        <v>20599</v>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>𝗛𝗣𝗣𝗿𝗼𝗯𝗼𝗼𝗸Model 430 G3 Business Laptop</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>𝗛𝗣𝗣𝗿𝗼𝗯𝗼𝗼𝗸Model 430 G3 Business Laptop | InteI i5 6th Gen | 8GB RAM | 256GB SSD | WiFi | Webcam | Win10 Pro (Refab)</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr"/>
+      <c r="D349" t="n">
+        <v>20299</v>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>𝗛𝗣𝗣𝗿𝗼𝗯𝗼𝗼𝗸Model 430 G3 Business Laptop</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>𝗛𝗣𝗣𝗿𝗼𝗯𝗼𝗼𝗸Model 430 G3 Business Laptop | 𝗜𝗡𝗧𝗘𝗟i5 6th Gen | 8GB RAM | 256GB SSD | WiFi | Webcam | Win10 Pro (Refab)</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr"/>
+      <c r="D350" t="n">
+        <v>20499</v>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>𝗛𝗣𝗣𝗿𝗼𝗯𝗼𝗼𝗸Model 430 G3 Business Laptop</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>𝗛𝗣𝗣𝗿𝗼𝗯𝗼𝗼𝗸Model 430 G3 Business Laptop | 𝗜𝗡𝗧𝗘𝗟i5 6th Gen | 8GB RAM | 256GB SSD | WiFi | Webcam | Win10 Pro (Refab)</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr"/>
+      <c r="D351" t="n">
         <v>19999</v>
       </c>
-      <c r="E344" t="inlineStr">
+      <c r="E351" t="inlineStr">
         <is>
           <t>2026-05-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>𝗟𝗲𝗻𝗼𝘃𝗼model_l14_laptop|_core_i5</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>𝗟𝗲𝗻𝗼𝘃𝗼Model L14 Laptop| Core i5 11th Gen Processor | 16GB Fast RAM/ 256GB SSD | 14″ HD Display | A+ (Pre-Owned &amp; Tested)</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr"/>
+      <c r="D352" t="n">
+        <v>31599</v>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>

--- a/amazon_products.xlsx
+++ b/amazon_products.xlsx
@@ -2483,28 +2483,28 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>acer_smartchoice_aspire_one,_intel</t>
+          <t>Acer Smartchoice Aspire One, Intel</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Acer Smartchoice Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X / 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
+          <t>Acer Smartchoice Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X / 512GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
       <c r="D99" t="n">
-        <v>33990</v>
+        <v>34990</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-12</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Acer Smartchoice Aspire One, Intel</t>
+          <t>acer_smartchoice_aspire_one,_intel</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -2514,11 +2514,11 @@
       </c>
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="n">
-        <v>34990</v>
+        <v>37990</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -2556,7 +2556,7 @@
       </c>
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="n">
-        <v>52999</v>
+        <v>53450</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -3134,21 +3134,21 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron) Laptop,</t>
+          <t>dell_15_(previously_inspiron)_laptop,</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 8GB DDR4, 512 SSD, 15.6" FHD 120Hz IPS 250 nit Display, Win 11 + Office H&amp;S 2024, Carbon Black, Thin &amp; Light 1.63Kg</t>
+          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 16GB DDR4, 512 SSD, Intel UHD Graphics, 15.6" FHD 120Hz IPS AG 250 nit Display, Win 11 + Office 2024, Black, 1.63Kg</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
       <c r="D130" t="n">
-        <v>45490</v>
+        <v>58990</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -3165,11 +3165,11 @@
       </c>
       <c r="C131" t="inlineStr"/>
       <c r="D131" t="n">
-        <v>44990</v>
+        <v>45490</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-17</t>
         </is>
       </c>
     </row>
@@ -3190,7 +3190,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
@@ -3207,11 +3207,11 @@
       </c>
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="n">
-        <v>45490</v>
+        <v>44990</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
@@ -3232,7 +3232,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -3253,7 +3253,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
@@ -3270,11 +3270,11 @@
       </c>
       <c r="C136" t="inlineStr"/>
       <c r="D136" t="n">
-        <v>46490</v>
+        <v>45490</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
@@ -3291,32 +3291,32 @@
       </c>
       <c r="C137" t="inlineStr"/>
       <c r="D137" t="n">
-        <v>46990</v>
+        <v>46490</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>dell_15_(previously_inspiron)_laptop,</t>
+          <t>Dell 15 (Previously Inspiron) Laptop,</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 8GB, 512GB, Intel UHD Graphics, 15.6" FHD IPS 250nit Display, 12m Mcafee, Win 11 + MSO'24, Platinum Silver, 1.63kg</t>
+          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 8GB DDR4, 512 SSD, 15.6" FHD 120Hz IPS 250 nit Display, Win 11 + Office H&amp;S 2024, Carbon Black, Thin &amp; Light 1.63Kg</t>
         </is>
       </c>
       <c r="C138" t="inlineStr"/>
       <c r="D138" t="n">
-        <v>50490</v>
+        <v>46990</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
@@ -4992,7 +4992,7 @@
       </c>
       <c r="C218" t="inlineStr"/>
       <c r="D218" t="n">
-        <v>61250</v>
+        <v>56830</v>
       </c>
       <c r="E218" t="inlineStr">
         <is>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Lenovo IdeaPad Slim 3 13th Gen Intel Core i5-13420H 15.3 inch (38.8cm) WUXGA IPS Laptop (16GB RAM/512GB SSD/Windows 11/Office 2024/Top Metal Cover/Backlit KB/Luna Grey/1.6Kg), 83K101JEIN</t>
+          <t>Lenovo IdeaPad Slim 3 13th Gen Intel Core i7 13620H, 16GB RAM, 512GB SSD, WUXGA IPS, 15.3"/38.8cm, Win 11, Office 2024, Top Metal Cover Grey, 1.6Kg, 83K100CJIN/S1IN, Backlit KB, Laptop</t>
         </is>
       </c>
       <c r="C263" t="inlineStr"/>
       <c r="D263" t="n">
-        <v>74990</v>
+        <v>81990</v>
       </c>
       <c r="E263" t="inlineStr">
         <is>

--- a/amazon_products.xlsx
+++ b/amazon_products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E352"/>
+  <dimension ref="A1:E373"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2273,21 +2273,21 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Acer Smartchoice Aspire One, AMD</t>
+          <t>acer_one_14_laptop_z14-55m</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Acer Smartchoice Aspire One, AMD Ryzen 3-7320U, 8GB LPDDR5 RAM/ 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.48KG, A114-43, Thin and Light Laptop</t>
+          <t>Acer One 14 Laptop Z14-55M | 14" HD Display | AMD Ryzen 3 7320U | 8GB LPDDR5 RAM | 256GB NVMe SSD | Windows 11 | Thin &amp; Light Design | AMD Radeon Graphics | Silver</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="n">
-        <v>39990</v>
+        <v>38500</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -2308,28 +2308,28 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Acer Smartchoice Aspire One, Intel</t>
+          <t>Acer Smartchoice Aspire One, AMD</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Acer Smartchoice Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X / 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
+          <t>Acer Smartchoice Aspire One, AMD Ryzen 3-7320U, 8GB LPDDR5 RAM/ 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.48KG, A114-43, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
       <c r="D91" t="n">
-        <v>32990</v>
+        <v>39990</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-06-12</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>
@@ -2371,7 +2371,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-24</t>
         </is>
       </c>
     </row>
@@ -2392,7 +2392,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -2413,7 +2413,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
     </row>
@@ -2430,11 +2430,11 @@
       </c>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="n">
-        <v>35990</v>
+        <v>32990</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-28</t>
         </is>
       </c>
     </row>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
     </row>
@@ -2488,23 +2488,23 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Acer Smartchoice Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X / 512GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
+          <t>Acer Smartchoice Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X / 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
       <c r="D99" t="n">
-        <v>34990</v>
+        <v>35990</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>acer_smartchoice_aspire_one,_intel</t>
+          <t>Acer Smartchoice Aspire One, Intel</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -2514,74 +2514,74 @@
       </c>
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="n">
-        <v>37990</v>
+        <v>34990</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-12</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Acer Swift Go 14 AI</t>
+          <t>acer_smartchoice_aspire_one,_intel</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Acer Swift Go 14 AI PC, Qualcomm SnapdragonX Plus X1P-42-100,Office 2024 + M365 Basic,(16GB LPDDR5X/ 512GB SSD/14.5-inch WUXGA//Qualcomm Adreno/1440p IR Camera with Shutter/Win11) 1.32 kg, Steel Grey.</t>
+          <t>Acer Smartchoice Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X / 512GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
       <c r="D101" t="n">
-        <v>79990</v>
+        <v>37990</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>acer_travellite_thin_laptop_amd</t>
+          <t>Acer Swift Go 14 AI</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Acer TravelLite Thin Laptop AMD Ryzen 5 7430U (6-Core) 16GB RAM, 512GB SSD 14" Full HD Anti-Glare Display Privacy Shutter Windows 11 MS Office Metal Body 1.34Kg Black 30M Warranty</t>
+          <t>Acer Swift Go 14 AI PC, Qualcomm SnapdragonX Plus X1P-42-100,Office 2024 + M365 Basic,(16GB LPDDR5X/ 512GB SSD/14.5-inch WUXGA//Qualcomm Adreno/1440p IR Camera with Shutter/Win11) 1.32 kg, Steel Grey.</t>
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="n">
-        <v>53450</v>
+        <v>79990</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Neo 13″</t>
+          <t>acer_travellite_thin_laptop_amd</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Citrus</t>
+          <t>Acer TravelLite Thin Laptop AMD Ryzen 5 7430U (6-Core) 16GB RAM, 512GB SSD 14" Full HD Anti-Glare Display Privacy Shutter Windows 11 MS Office Metal Body 1.34Kg Black 30M Warranty</t>
         </is>
       </c>
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="n">
-        <v>65000</v>
+        <v>53450</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -2593,16 +2593,16 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Indigo</t>
+          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Citrus</t>
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="n">
-        <v>67900</v>
+        <v>65000</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
@@ -2619,11 +2619,11 @@
       </c>
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="n">
-        <v>65000</v>
+        <v>67900</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -2640,11 +2640,11 @@
       </c>
       <c r="C106" t="inlineStr"/>
       <c r="D106" t="n">
-        <v>65700</v>
+        <v>65000</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
@@ -2661,11 +2661,11 @@
       </c>
       <c r="C107" t="inlineStr"/>
       <c r="D107" t="n">
-        <v>65000</v>
+        <v>65700</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-28</t>
         </is>
       </c>
     </row>
@@ -2686,7 +2686,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -2707,7 +2707,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Silver</t>
+          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Indigo</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
@@ -2728,7 +2728,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -2749,7 +2749,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-24</t>
         </is>
       </c>
     </row>
@@ -2766,11 +2766,11 @@
       </c>
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="n">
-        <v>65700</v>
+        <v>65000</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -2787,11 +2787,11 @@
       </c>
       <c r="C113" t="inlineStr"/>
       <c r="D113" t="n">
-        <v>67900</v>
+        <v>65700</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-27</t>
         </is>
       </c>
     </row>
@@ -2808,11 +2808,11 @@
       </c>
       <c r="C114" t="inlineStr"/>
       <c r="D114" t="n">
-        <v>65000</v>
+        <v>67900</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-31</t>
         </is>
       </c>
     </row>
@@ -2829,11 +2829,11 @@
       </c>
       <c r="C115" t="inlineStr"/>
       <c r="D115" t="n">
-        <v>64990</v>
+        <v>65000</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
     </row>
@@ -2850,11 +2850,11 @@
       </c>
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="n">
-        <v>63990</v>
+        <v>64990</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
@@ -2875,7 +2875,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
@@ -2896,28 +2896,28 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Pro Laptop</t>
+          <t>Apple 2026 MacBook Neo 13″</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Pro Laptop with M5 Max chip with 18‑core CPU and 40‑core GPU: Built for AI, 41.05 cm (16.2″) Liquid Retina XDR Display, 48GB Unified Memory, 2TB SSD Storage; Space Black</t>
+          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Silver</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="n">
-        <v>499900</v>
+        <v>63990</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-12</t>
         </is>
       </c>
     </row>
@@ -2938,7 +2938,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-28</t>
         </is>
       </c>
     </row>
@@ -2971,16 +2971,16 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Pro Laptop with M5 Pro chip with 15‑core CPU and 16‑core GPU: Built for AI, 35.97 cm (14.2″) Liquid Retina XDR Display, 24GB Unified Memory, 1TB SSD Storage; Silver</t>
+          <t>Apple 2026 MacBook Pro Laptop with M5 Max chip with 18‑core CPU and 40‑core GPU: Built for AI, 41.05 cm (16.2″) Liquid Retina XDR Display, 48GB Unified Memory, 2TB SSD Storage; Space Black</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
       <c r="D122" t="n">
-        <v>234900</v>
+        <v>499900</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-02</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="C123" t="inlineStr"/>
       <c r="D123" t="n">
-        <v>227400</v>
+        <v>234900</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>BrowseBook 14.1" FHD IPS Laptop</t>
+          <t>Apple 2026 MacBook Pro Laptop</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>BrowseBook 14.1" FHD IPS Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB RAM | 128GB SSD | Windows 11 | 38Wh | 1.3kg | Grey</t>
+          <t>Apple 2026 MacBook Pro Laptop with M5 Pro chip with 15‑core CPU and 16‑core GPU: Built for AI, 35.97 cm (14.2″) Liquid Retina XDR Display, 24GB Unified Memory, 1TB SSD Storage; Silver</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="n">
-        <v>13990</v>
+        <v>227400</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
@@ -3043,7 +3043,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -3064,7 +3064,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-16</t>
         </is>
       </c>
     </row>
@@ -3081,11 +3081,11 @@
       </c>
       <c r="C127" t="inlineStr"/>
       <c r="D127" t="n">
-        <v>20990</v>
+        <v>13990</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -3097,79 +3097,79 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>BrowseBook 14.1" FHD IPS Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 8GB RAM | 256GB SSD | Windows 11 | 38Wh | 1.3kg | Grey</t>
+          <t>BrowseBook 14.1" FHD IPS Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB RAM | 128GB SSD | Windows 11 | 38Wh | 1.3kg | Grey</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
       <c r="D128" t="n">
-        <v>18990</v>
+        <v>20990</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron) Laptop,</t>
+          <t>BrowseBook 14.1" FHD IPS Laptop</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core 3 100U Processor, 8GB DDR4, 512 SSD, 15.6" NT FHD 120Hz IPS AG 250 nit Display, Win 11 + Office H&amp;S 2024, Carbon Black, Thin &amp; Light- 1.63Kg</t>
+          <t>BrowseBook 14.1" FHD IPS Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 8GB RAM | 256GB SSD | Windows 11 | 38Wh | 1.3kg | Grey</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
       <c r="D129" t="n">
-        <v>46490</v>
+        <v>18990</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-15</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>dell_15_(previously_inspiron)_laptop,</t>
+          <t>Dell 15 (Previously Inspiron) Laptop,</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 16GB DDR4, 512 SSD, Intel UHD Graphics, 15.6" FHD 120Hz IPS AG 250 nit Display, Win 11 + Office 2024, Black, 1.63Kg</t>
+          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core 3 100U Processor, 8GB DDR4, 512 SSD, 15.6" NT FHD 120Hz IPS AG 250 nit Display, Win 11 + Office H&amp;S 2024, Carbon Black, Thin &amp; Light- 1.63Kg</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
       <c r="D130" t="n">
-        <v>58990</v>
+        <v>46490</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron) Laptop,</t>
+          <t>dell_15_(previously_inspiron)_laptop,</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 8GB DDR4, 512 SSD, 15.6" FHD 120Hz IPS 250 nit Display, Win 11 + Office H&amp;S 2024, Carbon Black, Thin &amp; Light 1.63Kg</t>
+          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 16GB DDR4, 512 SSD, Intel UHD Graphics, 15.6" FHD 120Hz IPS AG 250 nit Display, Win 11 + Office 2024, Black, 1.63Kg</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
       <c r="D131" t="n">
-        <v>45490</v>
+        <v>58990</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -3186,11 +3186,11 @@
       </c>
       <c r="C132" t="inlineStr"/>
       <c r="D132" t="n">
-        <v>44990</v>
+        <v>45490</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-17</t>
         </is>
       </c>
     </row>
@@ -3211,7 +3211,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
@@ -3228,11 +3228,11 @@
       </c>
       <c r="C134" t="inlineStr"/>
       <c r="D134" t="n">
-        <v>45490</v>
+        <v>44990</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
@@ -3253,7 +3253,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
@@ -3291,11 +3291,11 @@
       </c>
       <c r="C137" t="inlineStr"/>
       <c r="D137" t="n">
-        <v>46490</v>
+        <v>45490</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
@@ -3312,137 +3312,137 @@
       </c>
       <c r="C138" t="inlineStr"/>
       <c r="D138" t="n">
-        <v>46990</v>
+        <v>46490</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron), 13th</t>
+          <t>Dell 15 (Previously Inspiron) Laptop,</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron), 13th Gen Intel Core i5-1334U (16GB RAM, 1TB SSD) FHD, Anti-Glare 15.6"/39.62cm, Windows 11 MSO'24, Silver, 1.62kg, 12 Month McAfee, Thin &amp; Light, Backlit Keyboard Laptop</t>
+          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 8GB DDR4, 512 SSD, 15.6" FHD 120Hz IPS 250 nit Display, Win 11 + Office H&amp;S 2024, Carbon Black, Thin &amp; Light 1.63Kg</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
       <c r="D139" t="n">
-        <v>63990</v>
+        <v>46990</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Dell 15 AI Powered Laptop,</t>
+          <t>dell_15_(previously_inspiron)_laptop,</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Dell 15 AI Powered Laptop, Intel Core Ultra 5 225H, 8GB DDR5 RAM, 512GB SSD, 15.6" FHD Anti-Glare Display, Intel Arc Graphics, Standard Keyboard, Dedicated Copilot Key, Black, Win11 Home + MSO H&amp;S'24</t>
+          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 8GB, 512GB, Intel UHD Graphics, 15.6" FHD IPS 250nit Display, 12m Mcafee, Win 11 + MSO'24, Platinum Silver, 1.63kg</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
       <c r="D140" t="n">
-        <v>68990</v>
+        <v>47499</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>dell_15_ai_powered_laptop,</t>
+          <t>Dell 15 (Previously Inspiron), 13th</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Dell 15 Ai Powered Laptop, Intel Core Ultra 7 255H, 16GB DDR5 RAM, 512GB SSD, 15.6" FHD Anti-Glare Display, Intel Arc Graphics, Backlit Keyboard, Dedicated Copilot Key, Silver, Win11 Home + MSO H&amp;S'24</t>
+          <t>Dell 15 (Previously Inspiron), 13th Gen Intel Core i5-1334U (16GB RAM, 1TB SSD) FHD, Anti-Glare 15.6"/39.62cm, Windows 11 MSO'24, Silver, 1.62kg, 12 Month McAfee, Thin &amp; Light, Backlit Keyboard Laptop</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
       <c r="D141" t="n">
-        <v>103990</v>
+        <v>63990</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-17</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Dell 15 Smart Choice (Previously</t>
+          <t>dell_15_(previously_inspiron),_amd</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Dell 15 Smart Choice (Previously Inspiron), 13th Gen Intel Core i5-1334U (16GB RAM, 1TB SSD) FHD, 15.6"/39.62cm, Windows 11 MSO'24, Silver, 1.62kg, 12 Month McAfee, Backlit KB, Thin &amp; Light Laptop</t>
+          <t>Dell 15 (Previously Inspiron), AMD Ryzen 5-7530U, 16GB RAM, 512GB SSD, FHD IPS, 15.6"/39.62cm, Win 11, MSO 2024, Platinum Silver, 1.67kg,Standard Keyboard, 12 Month McAfee, Thin &amp; Light, Laptop</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
       <c r="D142" t="n">
-        <v>66990</v>
+        <v>56086</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Dell 15 Smart Choice (Previously</t>
+          <t>Dell 15 AI Powered Laptop,</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Dell 15 Smart Choice (Previously Inspiron), 13th Gen Intel Core i5-1334U (16GB RAM, 1TB SSD) FHD, 15.6"/39.62cm, Windows 11 MSO'24, Silver, 1.62kg, 12 Month McAfee, Backlit KB, Thin &amp; Light Laptop</t>
+          <t>Dell 15 AI Powered Laptop, Intel Core Ultra 5 225H, 8GB DDR5 RAM, 512GB SSD, 15.6" FHD Anti-Glare Display, Intel Arc Graphics, Standard Keyboard, Dedicated Copilot Key, Black, Win11 Home + MSO H&amp;S'24</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
       <c r="D143" t="n">
-        <v>67990</v>
+        <v>68990</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-15</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Dell 15 Smart Choice (Previously</t>
+          <t>dell_15_ai_powered_laptop,</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Dell 15 Smart Choice (Previously Inspiron), 13th Gen Intel Core i5-1334U (16GB RAM, 1TB SSD) FHD, 15.6"/39.62cm, Windows 11 MSO'24, Silver, 1.62kg, 12 Month McAfee, Backlit KB, Thin &amp; Light Laptop</t>
+          <t>Dell 15 Ai Powered Laptop, Intel Core Ultra 7 255H, 16GB DDR5 RAM, 512GB SSD, 15.6" FHD Anti-Glare Display, Intel Arc Graphics, Backlit Keyboard, Dedicated Copilot Key, Silver, Win11 Home + MSO H&amp;S'24</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
       <c r="D144" t="n">
-        <v>67990</v>
+        <v>103990</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -3459,11 +3459,11 @@
       </c>
       <c r="C145" t="inlineStr"/>
       <c r="D145" t="n">
-        <v>69990</v>
+        <v>66990</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-28</t>
         </is>
       </c>
     </row>
@@ -3484,234 +3484,234 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-05-31</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Dell 15, 13th Gen Intel</t>
+          <t>Dell 15 Smart Choice (Previously</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Dell 15, 13th Gen Intel Core i5-1334U (16GB DDR4, 512GB SSD) Anti-Glare FHD 15.6"/39.62cm, Windows 11, Microsoft Office Home 2024, Grey, 1.66kg, [Vostro 3530], 12 Month McAfee, Thin &amp; Light Laptop</t>
+          <t>Dell 15 Smart Choice (Previously Inspiron), 13th Gen Intel Core i5-1334U (16GB RAM, 1TB SSD) FHD, 15.6"/39.62cm, Windows 11 MSO'24, Silver, 1.62kg, 12 Month McAfee, Backlit KB, Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
       <c r="D147" t="n">
-        <v>61490</v>
+        <v>67990</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Dell 15, 13th Gen Intel</t>
+          <t>Dell 15 Smart Choice (Previously</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Dell 15, 13th Gen Intel Core i5-1334U (16GB DDR4, 512GB SSD) Anti-Glare FHD 15.6"/39.62cm, Windows 11, Microsoft Office Home 2024, Grey, 1.66kg, [Vostro 3530], 12 Month McAfee, Thin &amp; Light Laptop</t>
+          <t>Dell 15 Smart Choice (Previously Inspiron), 13th Gen Intel Core i5-1334U (16GB RAM, 1TB SSD) FHD, 15.6"/39.62cm, Windows 11 MSO'24, Silver, 1.62kg, 12 Month McAfee, Backlit KB, Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
       <c r="D148" t="n">
-        <v>63490</v>
+        <v>69990</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-02</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Dell 15, AMD Ryzen 7-7730U,</t>
+          <t>Dell 15 Smart Choice (Previously</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Dell 15, AMD Ryzen 7-7730U, 16GB DDR4, 512GB SSD, FHD, 15.6"/39.6cm, Windows 11, Microsoft Office Home 2024, Platinum Silver, 1.63Kg, [Dell 15], 120Hz 250nits, AMD Radeon Graphics,Thin &amp; Light, Laptop</t>
+          <t>Dell 15 Smart Choice (Previously Inspiron), 13th Gen Intel Core i5-1334U (16GB RAM, 1TB SSD) FHD, 15.6"/39.62cm, Windows 11 MSO'24, Silver, 1.62kg, 12 Month McAfee, Backlit KB, Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C149" t="inlineStr"/>
       <c r="D149" t="n">
-        <v>59957</v>
+        <v>67990</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-06-14</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Dell 15, AMD Ryzen 7-7730U,</t>
+          <t>Dell 15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Dell 15, AMD Ryzen 7-7730U, 16GB DDR4, 512GB SSD, FHD, 15.6"/39.6cm, Windows 11, Microsoft Office Home 2024, Platinum Silver, 1.63Kg, [Dell 15], 120Hz 250nits, AMD Radeon Graphics,Thin &amp; Light, Laptop</t>
+          <t>Dell 15, 13th Gen Intel Core i5-1334U (16GB DDR4, 512GB SSD) Anti-Glare FHD 15.6"/39.62cm, Windows 11, Microsoft Office Home 2024, Grey, 1.66kg, [Vostro 3530], 12 Month McAfee, Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
       <c r="D150" t="n">
-        <v>58490</v>
+        <v>61490</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Dell 15, Intel Core 3</t>
+          <t>Dell 15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Dell 15, Intel Core 3 14th Gen-100U, 16GB DDR4, 512GB SSD, FHD IPS, 15.6"/39.62cm, Windows 11, Microsoft Office Home 2024, Carbon Black, 1.63Kg, Thin &amp; Light, Laptop Model NO - Dell 15 DCU5250</t>
+          <t>Dell 15, 13th Gen Intel Core i5-1334U (16GB DDR4, 512GB SSD) Anti-Glare FHD 15.6"/39.62cm, Windows 11, Microsoft Office Home 2024, Grey, 1.66kg, [Vostro 3530], 12 Month McAfee, Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
       <c r="D151" t="n">
-        <v>51868</v>
+        <v>63490</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Dell 15, Intel Core i3/Core</t>
+          <t>Dell 15, AMD Ryzen 7-7730U,</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Dell 15, Intel Core i3/Core 3 14th Gen-100U, 16GB DDR4, 512GB SSD, FHD IPS, 15.6"/39.62cm, Windows 11, Microsoft Office Home 2024, Carbon Black, 1.63Kg, Thin &amp; Light, Laptop Model NO - Dell 15 DCU5250</t>
+          <t>Dell 15, AMD Ryzen 7-7730U, 16GB DDR4, 512GB SSD, FHD, 15.6"/39.6cm, Windows 11, Microsoft Office Home 2024, Platinum Silver, 1.63Kg, [Dell 15], 120Hz 250nits, AMD Radeon Graphics,Thin &amp; Light, Laptop</t>
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="n">
-        <v>48990</v>
+        <v>59957</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Dell 15, R5-7520U Processor, 8GB</t>
+          <t>Dell 15, AMD Ryzen 7-7730U,</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Dell 15, R5-7520U Processor, 8GB LPDDR5 RAM, 512GB SSD, FHD 15.6"/39.62 cm Display, Windows 11, MSO'24, Carbon Black, 1.63kg, Standard Keyboard, 15 Month McAfee, Thin &amp; Light Laptop</t>
+          <t>Dell 15, AMD Ryzen 7-7730U, 16GB DDR4, 512GB SSD, FHD, 15.6"/39.6cm, Windows 11, Microsoft Office Home 2024, Platinum Silver, 1.63Kg, [Dell 15], 120Hz 250nits, AMD Radeon Graphics,Thin &amp; Light, Laptop</t>
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
       <c r="D153" t="n">
-        <v>53990</v>
+        <v>58490</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>dell_g_series,_intel_core</t>
+          <t>dell_15,_intel_core_13th</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Dell G Series, Intel Core i5-13450HX, 13th Gen, NVIDIA RTX 3050-6GB, 16GB, 512GB SSD, FHD, 15.6"/39.62cm, Windows 11, MSO'24, Dark Shadow Gray, 2.65KG, [G15-5530], Backlit Keyboard, Gaming Laptop</t>
+          <t>Dell 15, Intel Core 13th Gen i5-1334U, FHD, 15.6"/39.62cm, Windows 11, MSO'24, Grey, 1.66kg, Vostro 3530, (16GB DDR4, 512GB SSD) Anti-Glare FHD 15.6"/39.62cm, 12 Month McAfee, Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C154" t="inlineStr"/>
       <c r="D154" t="n">
-        <v>89990</v>
+        <v>65490</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Dell G15, 13th Gen Intel</t>
+          <t>Dell 15, Intel Core 3</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Dell G15, 13th Gen Intel Core i5-13450HX Processor, NVIDIA RTX 3050-6GB, (16GB RAM 1TB SSD) FHD 15.6"/39.62 cm, Orange Backlit Keyboard, Win 11, MS Office'24, Dark Shadow Grey, 2.65Kg Gaming Laptop</t>
+          <t>Dell 15, Intel Core 3 14th Gen-100U, 16GB DDR4, 512GB SSD, FHD IPS, 15.6"/39.62cm, Windows 11, Microsoft Office Home 2024, Carbon Black, 1.63Kg, Thin &amp; Light, Laptop Model NO - Dell 15 DCU5250</t>
         </is>
       </c>
       <c r="C155" t="inlineStr"/>
       <c r="D155" t="n">
-        <v>79590</v>
+        <v>51868</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Dell G15, 13th Gen Intel</t>
+          <t>Dell 15, Intel Core i3/Core</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Dell G15, 13th Gen Intel Core i5-13450HX Processor, NVIDIA RTX 3050-6GB, (16GB RAM 1TB SSD) FHD 15.6"/39.62 cm, Orange Backlit Keyboard, Win 11, MS Office'24, Dark Shadow Grey, 2.65Kg Gaming Laptop</t>
+          <t>Dell 15, Intel Core i3/Core 3 14th Gen-100U, 16GB DDR4, 512GB SSD, FHD IPS, 15.6"/39.62cm, Windows 11, Microsoft Office Home 2024, Carbon Black, 1.63Kg, Thin &amp; Light, Laptop Model NO - Dell 15 DCU5250</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
       <c r="D156" t="n">
-        <v>79990</v>
+        <v>48990</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>EBook 11.6" HD Laptop |</t>
+          <t>Dell 15, R5-7520U Processor, 8GB</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EBook 11.6" HD Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB DDR4 | 128GB eMMC + M.2 SSD Expandable Slot | Win 11 Home |31Wh Battery | UHD Graphics 600 | Black</t>
+          <t>Dell 15, R5-7520U Processor, 8GB LPDDR5 RAM, 512GB SSD, FHD 15.6"/39.62 cm Display, Windows 11, MSO'24, Carbon Black, 1.63kg, Standard Keyboard, 15 Month McAfee, Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
       <c r="D157" t="n">
-        <v>11990</v>
+        <v>53990</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
@@ -3722,63 +3722,63 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>EBook 11.6" HD Laptop |</t>
+          <t>dell_g_series,_intel_core</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EBook 11.6" HD Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB DDR4 | 128GB eMMC + M.2 SSD Expandable Slot | Win 11 Home |31Wh Battery | UHD Graphics 600 | Black</t>
+          <t>Dell G Series, Intel Core i5-13450HX, 13th Gen, NVIDIA RTX 3050-6GB, 16GB, 512GB SSD, FHD, 15.6"/39.62cm, Windows 11, MSO'24, Dark Shadow Gray, 2.65KG, [G15-5530], Backlit Keyboard, Gaming Laptop</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
       <c r="D158" t="n">
-        <v>11990</v>
+        <v>89990</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>EBook 11.6" HD Laptop |</t>
+          <t>Dell G15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EBook 11.6" HD Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB DDR4 | 128GB eMMC + M.2 SSD Expandable Slot | Win 11 Home |31Wh Battery | UHD Graphics 600 | Black</t>
+          <t>Dell G15, 13th Gen Intel Core i5-13450HX Processor, NVIDIA RTX 3050-6GB, (16GB RAM 1TB SSD) FHD 15.6"/39.62 cm, Orange Backlit Keyboard, Win 11, MS Office'24, Dark Shadow Grey, 2.65Kg Gaming Laptop</t>
         </is>
       </c>
       <c r="C159" t="inlineStr"/>
       <c r="D159" t="n">
-        <v>11990</v>
+        <v>79590</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>EBook 11.6" HD Laptop |</t>
+          <t>Dell G15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EBook 11.6" HD Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB DDR4 | 128GB eMMC + M.2 SSD Expandable Slot | Win 11 Home |31Wh Battery | UHD Graphics 600 | Black</t>
+          <t>Dell G15, 13th Gen Intel Core i5-13450HX Processor, NVIDIA RTX 3050-6GB, (16GB RAM 1TB SSD) FHD 15.6"/39.62 cm, Orange Backlit Keyboard, Win 11, MS Office'24, Dark Shadow Grey, 2.65Kg Gaming Laptop</t>
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
       <c r="D160" t="n">
-        <v>11990</v>
+        <v>79990</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-08</t>
         </is>
       </c>
     </row>
@@ -3799,7 +3799,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-04-16</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -3841,7 +3841,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-19</t>
         </is>
       </c>
     </row>
@@ -3883,7 +3883,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-20</t>
         </is>
       </c>
     </row>
@@ -3904,7 +3904,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-21</t>
         </is>
       </c>
     </row>
@@ -3921,11 +3921,11 @@
       </c>
       <c r="C167" t="inlineStr"/>
       <c r="D167" t="n">
-        <v>16990</v>
+        <v>11990</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-31</t>
         </is>
       </c>
     </row>
@@ -3942,18 +3942,18 @@
       </c>
       <c r="C168" t="inlineStr"/>
       <c r="D168" t="n">
-        <v>16990</v>
+        <v>11990</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>ebook_11.6"_hd_laptop_|</t>
+          <t>EBook 11.6" HD Laptop |</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -3963,133 +3963,133 @@
       </c>
       <c r="C169" t="inlineStr"/>
       <c r="D169" t="n">
-        <v>10603</v>
+        <v>11990</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-02</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>hp_14_smartchoice,_intel_core</t>
+          <t>EBook 11.6" HD Laptop |</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>HP 14 Smartchoice, Intel Core Ultra 5 125H 12 TOPS, 24GB DDR5 (Upgradeable) 1TB SSD, Anti-Glare, FHD, 14''/35.6cm,Win11, M365*Office24, Silver, 1.4kg, ep1180tu, FHD Camera w/Shutter, Backlit AI Laptop</t>
+          <t>EBook 11.6" HD Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB DDR4 | 128GB eMMC + M.2 SSD Expandable Slot | Win 11 Home |31Wh Battery | UHD Graphics 600 | Black</t>
         </is>
       </c>
       <c r="C170" t="inlineStr"/>
       <c r="D170" t="n">
-        <v>77990</v>
+        <v>11990</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>hp_14,_amd_ryzen_7</t>
+          <t>EBook 11.6" HD Laptop |</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>HP 14, AMD Ryzen 7 7730U (16GB DDR4, 512GB SSD) FHD, Anti-Glare, Micro-Edge, 14''/35.6cm, Win11, M365 Basic(1yr), Office Home24, Silver,1.4kg, EM0104AU, FHD Camera w/Privacy Shutter, Backlit Laptop</t>
+          <t>EBook 11.6" HD Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB DDR4 | 128GB eMMC + M.2 SSD Expandable Slot | Win 11 Home |31Wh Battery | UHD Graphics 600 | Black</t>
         </is>
       </c>
       <c r="C171" t="inlineStr"/>
       <c r="D171" t="n">
-        <v>59990</v>
+        <v>16990</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>HP 14s Intel Celeron Dual</t>
+          <t>EBook 11.6" HD Laptop |</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>HP 14s Intel Celeron Dual Core N4500 Laptop (8GB/512GB SSD/Win 11) 14.0" HD Display, MSO 24, Black, 1.46kg, DQ3149TU Thin and Light Business Laptop</t>
+          <t>EBook 11.6" HD Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB DDR4 | 128GB eMMC + M.2 SSD Expandable Slot | Win 11 Home |31Wh Battery | UHD Graphics 600 | Black</t>
         </is>
       </c>
       <c r="C172" t="inlineStr"/>
       <c r="D172" t="n">
-        <v>40400</v>
+        <v>16990</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>HP 15 (2026), AMD Athlon</t>
+          <t>ebook_11.6"_hd_laptop_|</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>HP 15 (2026), AMD Athlon Dual Core 7120U - (8 GB DDR5/512 GB SSD/AMD Radeon 610M Graphics/DOS) Thin and Light Business Laptop/15.6" HD Display/Turbo Silver/Copilot Key/1.5kg</t>
+          <t>EBook 11.6" HD Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB DDR4 | 128GB eMMC + M.2 SSD Expandable Slot | Win 11 Home |31Wh Battery | UHD Graphics 600 | Black</t>
         </is>
       </c>
       <c r="C173" t="inlineStr"/>
       <c r="D173" t="n">
-        <v>39999</v>
+        <v>10603</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>HP 15 (2026), AMD Athlon</t>
+          <t>ebook_11.6"_hd_laptop_|</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>HP 15 (2026), AMD Athlon Dual Core 7120U - (8 GB DDR5/512 GB SSD/AMD Radeon 610M Graphics/Windows 11 Pro) Thin and Light Business Laptop/15.6" HD Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
+          <t>EBook 11.6" HD Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB DDR4 | 128GB eMMC + M.2 SSD Expandable Slot | Win 11 Home |31Wh Battery | UHD Graphics 600 | Black</t>
         </is>
       </c>
       <c r="C174" t="inlineStr"/>
       <c r="D174" t="n">
-        <v>39660</v>
+        <v>10990</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>hp_15_(2026),_amd_athlon</t>
+          <t>hp_14_smartchoice,_intel_core</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>HP 15 (2026), AMD Athlon Dual Core 7120U - (8 GB DDR5/512 GB SSD/AMD Radeon 610M Graphics/Windows 11 Pro) Thin and Light Business Laptop/15.6" HD Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
+          <t>HP 14 Smartchoice, Intel Core Ultra 5 125H 12 TOPS, 24GB DDR5 (Upgradeable) 1TB SSD, Anti-Glare, FHD, 14''/35.6cm,Win11, M365*Office24, Silver, 1.4kg, ep1180tu, FHD Camera w/Shutter, Backlit AI Laptop</t>
         </is>
       </c>
       <c r="C175" t="inlineStr"/>
       <c r="D175" t="n">
-        <v>41999</v>
+        <v>77990</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
@@ -4100,248 +4100,248 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>HP 15 (2026), AMD Ryzen</t>
+          <t>hp_14,_amd_ryzen_7</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>HP 15 (2026), AMD Ryzen 3 Quad Core 7335U - (8 GB DDR5/512 GB SSD/AMD Radeon 660M Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
+          <t>HP 14, AMD Ryzen 7 7730U (16GB DDR4, 512GB SSD) FHD, Anti-Glare, Micro-Edge, 14''/35.6cm, Win11, M365 Basic(1yr), Office Home24, Silver,1.4kg, EM0104AU, FHD Camera w/Privacy Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C176" t="inlineStr"/>
       <c r="D176" t="n">
-        <v>42780</v>
+        <v>59990</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>hp_15_(i5_14th_gen),</t>
+          <t>HP 14s Intel Celeron Dual</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>HP 15 (i5 14th Gen), Intel Core 5, 16GB RAM (Upgradeable), 512GB SSD, FHD, Anti-Glare, 15.6''/39.6cm, Win11, M365 Basic(1yr), Office24, Silver,1.59kg, fd0682tu, FHD Camera w/Shutter, Backlit Laptop</t>
+          <t>HP 14s Intel Celeron Dual Core N4500 Laptop (8GB/512GB SSD/Win 11) 14.0" HD Display, MSO 24, Black, 1.46kg, DQ3149TU Thin and Light Business Laptop</t>
         </is>
       </c>
       <c r="C177" t="inlineStr"/>
       <c r="D177" t="n">
-        <v>63990</v>
+        <v>40400</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-04-16</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>hp_15_laptop_|_intel</t>
+          <t>HP 15 (2026), AMD Athlon</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>HP 15 Laptop | Intel Core i5-13420H,13th Gen |16GB RAM | 512GB SSD | Win 11 |M365 Basic(1yr)* Office24|Anti-Glare, Micro-Edge, 15.6''/39.6cm|Backlit KB|FHD Camera w/Shutter|1.65kg, Silver -FR0045TU</t>
+          <t>HP 15 (2026), AMD Athlon Dual Core 7120U - (8 GB DDR5/512 GB SSD/AMD Radeon 610M Graphics/DOS) Thin and Light Business Laptop/15.6" HD Display/Turbo Silver/Copilot Key/1.5kg</t>
         </is>
       </c>
       <c r="C178" t="inlineStr"/>
       <c r="D178" t="n">
-        <v>68990</v>
+        <v>39999</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-08</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>hp_15_laptop,_(14th_gen</t>
+          <t>HP 15 (2026), AMD Athlon</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>HP 15 Laptop, (14th Gen Core i5) Intel Core 5-120U (24GB RAM, 512GB SSD, Win 11, M365 Basic(1yr)* Office24,15.6''/39.6cm FHD Anti-Glare Display, Backlit KB, FHD Camera, Dual Speakers, Silver, 1.59kg)</t>
+          <t>HP 15 (2026), AMD Athlon Dual Core 7120U - (8 GB DDR5/512 GB SSD/AMD Radeon 610M Graphics/Windows 11 Pro) Thin and Light Business Laptop/15.6" HD Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
         </is>
       </c>
       <c r="C179" t="inlineStr"/>
       <c r="D179" t="n">
-        <v>72800</v>
+        <v>39660</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>HP 15 Laptop, Intel (14th</t>
+          <t>hp_15_(2026),_amd_athlon</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>HP 15 Laptop, Intel (14th Gen) Core 5 120U (24GB DDR5, 512GB SSD), Micro-Edge, Anti-Glare, 15.6''/39.6cm, Win11, M365* Office24, Silver, 1.59kg, fd0262TU, FHD Camera, Backlit, Dual Speakers</t>
+          <t>HP 15 (2026), AMD Athlon Dual Core 7120U - (8 GB DDR5/512 GB SSD/AMD Radeon 610M Graphics/Windows 11 Pro) Thin and Light Business Laptop/15.6" HD Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
         </is>
       </c>
       <c r="C180" t="inlineStr"/>
       <c r="D180" t="n">
-        <v>67990</v>
+        <v>41999</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, 13th Gen</t>
+          <t>hp_15_(2026),_amd_athlon</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U (12GB DDR4, 512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver, 1.59kg, fd0573TU, FHD Camera w/Shutter Laptop</t>
+          <t>HP 15 (2026), AMD Athlon Dual Core 7120U - (8 GB DDR5/512 GB SSD/AMD Radeon 610M Graphics/Windows 11 Pro) Thin and Light Business Laptop/15.6" HD Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
         </is>
       </c>
       <c r="C181" t="inlineStr"/>
       <c r="D181" t="n">
-        <v>55990</v>
+        <v>42840</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, 13th Gen</t>
+          <t>HP 15 (2026), AMD Ryzen</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U(8GB DDR4,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
+          <t>HP 15 (2026), AMD Ryzen 3 Quad Core 7335U - (8 GB DDR5/512 GB SSD/AMD Radeon 660M Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
         </is>
       </c>
       <c r="C182" t="inlineStr"/>
       <c r="D182" t="n">
-        <v>51990</v>
+        <v>42780</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, 13th Gen</t>
+          <t>hp_15_(i5_14th_gen),</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U(8GB DDR4,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
+          <t>HP 15 (i5 14th Gen), Intel Core 5, 16GB RAM (Upgradeable), 512GB SSD, FHD, Anti-Glare, 15.6''/39.6cm, Win11, M365 Basic(1yr), Office24, Silver,1.59kg, fd0682tu, FHD Camera w/Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C183" t="inlineStr"/>
       <c r="D183" t="n">
-        <v>51990</v>
+        <v>63990</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, 13th Gen</t>
+          <t>hp_15_(i5_14th_gen),</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U(8GB DDR4,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
+          <t>HP 15 (i5 14th Gen), Intel Core 5, 16GB RAM (Upgradeable), 512GB SSD, FHD, Anti-Glare, 15.6''/39.6cm, Win11, M365 Basic(1yr), Office24, Silver,1.59kg, fd0682tu, FHD Camera w/Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C184" t="inlineStr"/>
       <c r="D184" t="n">
-        <v>51990</v>
+        <v>67990</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, 13th Gen</t>
+          <t>hp_15_laptop_|_amd</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U(8GB DDR4,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
+          <t>HP 15 Laptop | AMD Ryzen 7 5825U |16GB DDR4 RAM | 512GB SSD |15.6" (39.6 cm) FHD Display |AMD Radeon Graphics| Backlit KB | FHD Camera| Win 11| MS Office 2024 + M365*(1-Yr) | Silver |1.59kg |fc0533AU</t>
         </is>
       </c>
       <c r="C185" t="inlineStr"/>
       <c r="D185" t="n">
-        <v>51990</v>
+        <v>64990</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, 13th Gen</t>
+          <t>hp_15_laptop_|_intel</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U(8GB DDR4,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
+          <t>HP 15 Laptop | Intel Core i5-13420H,13th Gen |16GB RAM | 512GB SSD | Win 11 |M365 Basic(1yr)* Office24|Anti-Glare, Micro-Edge, 15.6''/39.6cm|Backlit KB|FHD Camera w/Shutter|1.65kg, Silver -FR0045TU</t>
         </is>
       </c>
       <c r="C186" t="inlineStr"/>
       <c r="D186" t="n">
-        <v>51990</v>
+        <v>68990</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>hp_15_smartchoice,_13th_gen</t>
+          <t>hp_15_laptop,_(14th_gen</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U(8GB DDR4,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
+          <t>HP 15 Laptop, (14th Gen Core i5) Intel Core 5-120U (24GB RAM, 512GB SSD, Win 11, M365 Basic(1yr)* Office24,15.6''/39.6cm FHD Anti-Glare Display, Backlit KB, FHD Camera, Dual Speakers, Silver, 1.59kg)</t>
         </is>
       </c>
       <c r="C187" t="inlineStr"/>
       <c r="D187" t="n">
-        <v>49990</v>
+        <v>72800</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
@@ -4352,231 +4352,231 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>hp_15_smartchoice,_intel_core</t>
+          <t>HP 15 Laptop, Intel (14th</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, Intel Core Ultra 5 125H, 12 Tops (16GB DDR5, 512GB SSD) FHD, IPS, 15.6''/39.6cm, Win11, M365(1yr)* Office24, Silver, 1.65kg, fd1254TU, FHD Camera w/Shutter, AI Powered Laptop</t>
+          <t>HP 15 Laptop, Intel (14th Gen) Core 5 120U (24GB DDR5, 512GB SSD), Micro-Edge, Anti-Glare, 15.6''/39.6cm, Win11, M365* Office24, Silver, 1.59kg, fd0262TU, FHD Camera, Backlit, Dual Speakers</t>
         </is>
       </c>
       <c r="C188" t="inlineStr"/>
       <c r="D188" t="n">
-        <v>69990</v>
+        <v>67990</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel</t>
+          <t>HP 15 Smartchoice, 13th Gen</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U (8GB DDR4, 512GB SSD), FHD, Micro -Edge, Anti-Glare, 15.6''/39.6cm, Win11, M365* Office24, Silver, 1.59kg, fd0624tu, FHD Camera, UHD Graphics Laptop</t>
+          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U (12GB DDR4, 512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver, 1.59kg, fd0573TU, FHD Camera w/Shutter Laptop</t>
         </is>
       </c>
       <c r="C189" t="inlineStr"/>
       <c r="D189" t="n">
-        <v>47490</v>
+        <v>55990</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-06-12</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel</t>
+          <t>HP 15 Smartchoice, 13th Gen</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
+          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U(8GB DDR4,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C190" t="inlineStr"/>
       <c r="D190" t="n">
-        <v>47990</v>
+        <v>51990</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel</t>
+          <t>HP 15 Smartchoice, 13th Gen</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
+          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U(8GB DDR4,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C191" t="inlineStr"/>
       <c r="D191" t="n">
-        <v>47990</v>
+        <v>51990</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel</t>
+          <t>HP 15 Smartchoice, 13th Gen</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
+          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U(8GB DDR4,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C192" t="inlineStr"/>
       <c r="D192" t="n">
-        <v>46990</v>
+        <v>51990</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel</t>
+          <t>HP 15 Smartchoice, 13th Gen</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
+          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U(8GB DDR4,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C193" t="inlineStr"/>
       <c r="D193" t="n">
-        <v>46990</v>
+        <v>51990</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel</t>
+          <t>HP 15 Smartchoice, 13th Gen</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
+          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U(8GB DDR4,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C194" t="inlineStr"/>
       <c r="D194" t="n">
-        <v>46990</v>
+        <v>51990</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel</t>
+          <t>hp_15_smartchoice,_13th_gen</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
+          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U(8GB DDR4,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C195" t="inlineStr"/>
       <c r="D195" t="n">
-        <v>46990</v>
+        <v>49990</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel</t>
+          <t>hp_15_smartchoice,_13th_gen</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
+          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U(8GB DDR4,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C196" t="inlineStr"/>
       <c r="D196" t="n">
-        <v>46990</v>
+        <v>49990</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel</t>
+          <t>hp_15_smartchoice,_intel_core</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
+          <t>HP 15 Smartchoice, Intel Core Ultra 5 125H, 12 Tops (16GB DDR5, 512GB SSD) FHD, IPS, 15.6''/39.6cm, Win11, M365(1yr)* Office24, Silver, 1.65kg, fd1254TU, FHD Camera w/Shutter, AI Powered Laptop</t>
         </is>
       </c>
       <c r="C197" t="inlineStr"/>
       <c r="D197" t="n">
-        <v>46990</v>
+        <v>69990</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel</t>
+          <t>hp_15_smartchoice,_intel_core</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
+          <t>HP 15 Smartchoice, Intel Core Ultra 5 125H, 12 Tops (16GB DDR5, 512GB SSD) FHD, IPS, 15.6''/39.6cm, Win11, M365(1yr)* Office24, Silver, 1.65kg, fd1254TU, FHD Camera w/Shutter, AI Powered Laptop</t>
         </is>
       </c>
       <c r="C198" t="inlineStr"/>
       <c r="D198" t="n">
-        <v>48900</v>
+        <v>69990</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -4588,37 +4588,37 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U (8GB DDR4, 512GB SSD), FHD, Micro -Edge, Anti-Glare, 15.6''/39.6cm, Win11, M365* Office24, Silver, 1.59kg, fd0624tu, FHD Camera, UHD Graphics Laptop</t>
         </is>
       </c>
       <c r="C199" t="inlineStr"/>
       <c r="D199" t="n">
-        <v>48900</v>
+        <v>47490</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-04-16</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel</t>
+          <t>hp_15,_13th_gen_intel</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U (8GB DDR4, 512GB SSD), FHD, Micro -Edge, Anti-Glare, 15.6''/39.6cm, Win11, M365* Office24, Silver, 1.59kg, fd0624tu, FHD Camera, UHD Graphics Laptop</t>
         </is>
       </c>
       <c r="C200" t="inlineStr"/>
       <c r="D200" t="n">
-        <v>50000</v>
+        <v>48990</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -4635,11 +4635,11 @@
       </c>
       <c r="C201" t="inlineStr"/>
       <c r="D201" t="n">
-        <v>49850</v>
+        <v>47990</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -4656,11 +4656,11 @@
       </c>
       <c r="C202" t="inlineStr"/>
       <c r="D202" t="n">
-        <v>49990</v>
+        <v>47990</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -4677,11 +4677,11 @@
       </c>
       <c r="C203" t="inlineStr"/>
       <c r="D203" t="n">
-        <v>49820</v>
+        <v>46990</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-08</t>
         </is>
       </c>
     </row>
@@ -4698,11 +4698,11 @@
       </c>
       <c r="C204" t="inlineStr"/>
       <c r="D204" t="n">
-        <v>49820</v>
+        <v>46990</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
@@ -4719,11 +4719,11 @@
       </c>
       <c r="C205" t="inlineStr"/>
       <c r="D205" t="n">
-        <v>50400</v>
+        <v>46990</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-10</t>
         </is>
       </c>
     </row>
@@ -4740,11 +4740,11 @@
       </c>
       <c r="C206" t="inlineStr"/>
       <c r="D206" t="n">
-        <v>50390</v>
+        <v>46990</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-14</t>
         </is>
       </c>
     </row>
@@ -4761,11 +4761,11 @@
       </c>
       <c r="C207" t="inlineStr"/>
       <c r="D207" t="n">
-        <v>50150</v>
+        <v>46990</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-15</t>
         </is>
       </c>
     </row>
@@ -4782,11 +4782,11 @@
       </c>
       <c r="C208" t="inlineStr"/>
       <c r="D208" t="n">
-        <v>50040</v>
+        <v>46990</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-17</t>
         </is>
       </c>
     </row>
@@ -4803,11 +4803,11 @@
       </c>
       <c r="C209" t="inlineStr"/>
       <c r="D209" t="n">
-        <v>50040</v>
+        <v>48900</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-05-19</t>
         </is>
       </c>
     </row>
@@ -4824,11 +4824,11 @@
       </c>
       <c r="C210" t="inlineStr"/>
       <c r="D210" t="n">
-        <v>49670</v>
+        <v>48900</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-05-20</t>
         </is>
       </c>
     </row>
@@ -4845,11 +4845,11 @@
       </c>
       <c r="C211" t="inlineStr"/>
       <c r="D211" t="n">
-        <v>49480</v>
+        <v>50000</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-21</t>
         </is>
       </c>
     </row>
@@ -4866,11 +4866,11 @@
       </c>
       <c r="C212" t="inlineStr"/>
       <c r="D212" t="n">
-        <v>49470</v>
+        <v>49850</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-22</t>
         </is>
       </c>
     </row>
@@ -4887,11 +4887,11 @@
       </c>
       <c r="C213" t="inlineStr"/>
       <c r="D213" t="n">
-        <v>49300</v>
+        <v>49990</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>
@@ -4903,348 +4903,348 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U, (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge, FHD,15.6''/39.6cm, Win11,M365 Basic(1yr),Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
         </is>
       </c>
       <c r="C214" t="inlineStr"/>
       <c r="D214" t="n">
-        <v>47990</v>
+        <v>49820</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-24</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>HP 15, AMD Ryzen 5</t>
+          <t>HP 15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>HP 15, AMD Ryzen 5 7520U,(16GB LPDDR5, 512GB SSD), Anti-Glare, Micro-Edge, FHD, 15.6''/39.6cm, Win 11, Office 24,M365 Basic(1yr)*,Silver, 1.59kg, fc0690au, FHD Camera, Backlit KB Laptop</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
         </is>
       </c>
       <c r="C215" t="inlineStr"/>
       <c r="D215" t="n">
-        <v>53990</v>
+        <v>49820</v>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>HP 15, AMD Ryzen 5</t>
+          <t>HP 15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>HP 15, AMD Ryzen 5 7520U,(16GB LPDDR5, 512GB SSD), Anti-Glare, Micro-Edge, FHD, 15.6''/39.6cm, Win 11, Office 24,M365 Basic(1yr)*,Silver, 1.59kg, fc0690au, FHD Camera, Backlit KB Laptop</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
         </is>
       </c>
       <c r="C216" t="inlineStr"/>
       <c r="D216" t="n">
-        <v>53990</v>
+        <v>50400</v>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>HP 15, AMD Ryzen 5</t>
+          <t>HP 15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>HP 15, AMD Ryzen 5 7520U,(16GB LPDDR5, 512GB SSD), Anti-Glare, Micro-Edge, FHD, 15.6''/39.6cm, Win 11, Office 24,M365 Basic(1yr)*,Silver, 1.59kg, fc0690au, FHD Camera, Backlit KB Laptop</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
         </is>
       </c>
       <c r="C217" t="inlineStr"/>
       <c r="D217" t="n">
-        <v>54990</v>
+        <v>50390</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-27</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>hp_15,_amd_ryzen_5</t>
+          <t>HP 15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>HP 15, AMD Ryzen 5 7520U,(16GB LPDDR5, 512GB SSD), Anti-Glare, Micro-Edge, FHD, 15.6''/39.6cm, Win 11, Office 24,M365 Basic(1yr)*,Silver, 1.59kg, fc0690au, FHD Camera, Backlit KB Laptop</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
         </is>
       </c>
       <c r="C218" t="inlineStr"/>
       <c r="D218" t="n">
-        <v>56830</v>
+        <v>50150</v>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-28</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>HP 15, AMD Ryzen 7</t>
+          <t>HP 15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>HP 15, AMD Ryzen 7 7735HS (16GB DDR5,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365 Basic(1yr)* Office24, Silver, 1.59kg, fc1038AU, AMD Radeon FHD Camera w/Shutter, Backlit Laptop</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
         </is>
       </c>
       <c r="C219" t="inlineStr"/>
       <c r="D219" t="n">
-        <v>59990</v>
+        <v>50040</v>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>HP 15, Intel Core 5</t>
+          <t>HP 15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>HP 15, Intel Core 5 120U (14th Gen) 16GB DDR4, 512GB SSD, FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365 Basic(1yr), Office24, Silver,1.59kg, FD0640TU/682tu, FHD Camera w/Shutter, BL Laptop</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
         </is>
       </c>
       <c r="C220" t="inlineStr"/>
       <c r="D220" t="n">
-        <v>65990</v>
+        <v>50040</v>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>HP 15, Intel Core Ultra</t>
+          <t>HP 15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>HP 15, Intel Core Ultra 5 125H (24GB DDR5, 1TB SSD), Micro-Edge, Anti-Glare, FHD, 15''/39.6cm, Win11, M365* Office24, Silver, 1.65kg, FD1458TU, FHD Camera, Backlit Laptop</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
         </is>
       </c>
       <c r="C221" t="inlineStr"/>
       <c r="D221" t="n">
-        <v>84990</v>
+        <v>49670</v>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>hp_15,_intel_core_i3-1315u-13th</t>
+          <t>HP 15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>HP 15, Intel Core i3-1315U-13th Gen Laptop (8GB DDR4 Ram,512GB SSD) Anti-Glare, Micro-Edge,15.6'" FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera Shutter, 15-fd0569TU</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
         </is>
       </c>
       <c r="C222" t="inlineStr"/>
       <c r="D222" t="n">
-        <v>49490</v>
+        <v>49480</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>HP 255R G10 Notebook (AMD</t>
+          <t>HP 15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>HP 255R G10 Notebook (AMD Athlon Silver 7120U /8GB/512GB/DOS) 15.6-inch(39.6cm), Anti-Glare, HD Laptop, Radeon Graphics, Silver,1.52kg</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
         </is>
       </c>
       <c r="C223" t="inlineStr"/>
       <c r="D223" t="n">
-        <v>41700</v>
+        <v>49470</v>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-06-12</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>HP 255R G10 Notebook (AMD</t>
+          <t>HP 15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>HP 255R G10 Notebook (AMD Athlon Silver 7120U /8GB/512GB/DOS) 15.6-inch(39.6cm), Anti-Glare, HD Laptop, Radeon Graphics, Silver,1.52kg</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
         </is>
       </c>
       <c r="C224" t="inlineStr"/>
       <c r="D224" t="n">
-        <v>39340</v>
+        <v>49300</v>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>HP 255R G10 Notebook (AMD</t>
+          <t>HP 15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>HP 255R G10 Notebook (AMD Athlon Silver 7120U /8GB/512GB/DOS) 15.6-inch(39.6cm), Anti-Glare, HD Laptop, Radeon Graphics, Silver,1.52kg</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U, (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge, FHD,15.6''/39.6cm, Win11,M365 Basic(1yr),Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C225" t="inlineStr"/>
       <c r="D225" t="n">
-        <v>40409</v>
+        <v>47990</v>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>HP 255R G10 Notebook (AMD</t>
+          <t>HP 15, AMD Ryzen 5</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>HP 255R G10 Notebook (AMD Athlon Silver 7120U /8GB/512GB/DOS) 15.6-inch(39.6cm), Anti-Glare, HD Laptop, Radeon Graphics, Silver,1.52kg</t>
+          <t>HP 15, AMD Ryzen 5 7520U,(16GB LPDDR5, 512GB SSD), Anti-Glare, Micro-Edge, FHD, 15.6''/39.6cm, Win 11, Office 24,M365 Basic(1yr)*,Silver, 1.59kg, fc0690au, FHD Camera, Backlit KB Laptop</t>
         </is>
       </c>
       <c r="C226" t="inlineStr"/>
       <c r="D226" t="n">
-        <v>39618</v>
+        <v>53990</v>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-08</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>HP 255R G10 Notebook (AMD</t>
+          <t>HP 15, AMD Ryzen 5</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>HP 255R G10 Notebook (AMD Athlon Silver 7120U /8GB/512GB/DOS) 15.6-inch(39.6cm), Anti-Glare, HD Laptop, Radeon Graphics, Silver,1.52kg</t>
+          <t>HP 15, AMD Ryzen 5 7520U,(16GB LPDDR5, 512GB SSD), Anti-Glare, Micro-Edge, FHD, 15.6''/39.6cm, Win 11, Office 24,M365 Basic(1yr)*,Silver, 1.59kg, fc0690au, FHD Camera, Backlit KB Laptop</t>
         </is>
       </c>
       <c r="C227" t="inlineStr"/>
       <c r="D227" t="n">
-        <v>39525</v>
+        <v>53990</v>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>HP Omen, Intel Core Ultra</t>
+          <t>HP 15, AMD Ryzen 5</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>HP Omen, Intel Core Ultra 7 255H, 8GB RTX 5050, 24GB DDR5(Upgradeable) 1TB SSD, 2K, 165Hz, 3ms Response time, IPS, 16''/40.6cm, Win11, M365*Office24, Shadow Black, 2.43kg, am0240tx, RGB Gaming Laptop</t>
+          <t>HP 15, AMD Ryzen 5 7520U,(16GB LPDDR5, 512GB SSD), Anti-Glare, Micro-Edge, FHD, 15.6''/39.6cm, Win 11, Office 24,M365 Basic(1yr)*,Silver, 1.59kg, fc0690au, FHD Camera, Backlit KB Laptop</t>
         </is>
       </c>
       <c r="C228" t="inlineStr"/>
       <c r="D228" t="n">
-        <v>129990</v>
+        <v>54990</v>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-24</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>HP OmniBook 3, AMD Ryzen</t>
+          <t>hp_15,_amd_ryzen_5</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>HP OmniBook 3, AMD Ryzen AI 5 330 (24GB DDR5 RAM, 1TB SSD) FHD, Anti-Glare, 15.6''/39.6cm, Win11, Office24, Glacier Silver,1.7kg, fn0074AU, FHD Camera w/Shutter, FPR, Backlit KB, Next Gen AI Laptop</t>
+          <t>HP 15, AMD Ryzen 5 7520U,(16GB LPDDR5, 512GB SSD), Anti-Glare, Micro-Edge, FHD, 15.6''/39.6cm, Win 11, Office 24,M365 Basic(1yr)*,Silver, 1.59kg, fc0690au, FHD Camera, Backlit KB Laptop</t>
         </is>
       </c>
       <c r="C229" t="inlineStr"/>
       <c r="D229" t="n">
-        <v>69990</v>
+        <v>56830</v>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>HP OmniBook 5 OLED (Previously</t>
+          <t>HP 15, AMD Ryzen 7</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>HP OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x, 1TB SSD) 2K, 14''/35.6cm, Win11, M365 Basic(1yr)* Office24, Silver, 1.35kg, he0015QU, Light-Weight, Next-Gen AI Laptop</t>
+          <t>HP 15, AMD Ryzen 7 7735HS (16GB DDR5,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365 Basic(1yr)* Office24, Silver, 1.59kg, fc1038AU, AMD Radeon FHD Camera w/Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C230" t="inlineStr"/>
       <c r="D230" t="n">
-        <v>69990</v>
+        <v>59990</v>
       </c>
       <c r="E230" t="inlineStr">
         <is>
@@ -5255,80 +5255,80 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>HP OmniBook 5 OLED (Previously</t>
+          <t>HP 15, Intel Core 5</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>HP OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x, 512GB SSD) 2K, 14''/35.6cm, Win11, M365 Basic(1yr)* Office24, Silver, 1.35kg, he0014QU, Light-Weight, Next-Gen AI Laptop</t>
+          <t>HP 15, Intel Core 5 120U (14th Gen) 16GB DDR4, 512GB SSD, FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365 Basic(1yr), Office24, Silver,1.59kg, FD0640TU/682tu, FHD Camera w/Shutter, BL Laptop</t>
         </is>
       </c>
       <c r="C231" t="inlineStr"/>
       <c r="D231" t="n">
-        <v>78990</v>
+        <v>65990</v>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>HP OmniBook 5 OLED (Previously</t>
+          <t>hp_15,_intel_core_5-120u</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>HP OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x, 512GB SSD) 2K, 14''/35.6cm, Win11, M365 Basic(1yr)* Office24, Silver, 1.35kg, he0014QU, Light-Weight, Next-Gen AI Laptop</t>
+          <t>HP 15, Intel Core 5-120U (8GB DDR4, 512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365 Basic(1yr), Office Home24, Silver,1.59kg, fd0651TU, FHD Camera w/Privacy Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C232" t="inlineStr"/>
       <c r="D232" t="n">
-        <v>66990</v>
+        <v>57500</v>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>hp_omnibook_x_flip_oled</t>
+          <t>HP 15, Intel Core Ultra</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>HP OmniBook X Flip OLED Intel Core Ultra 5 226V, 40 Tops (16GB LPDDR5x,1TB SSD) 3K, Touch, 120hz, 14''/35.6cm, Intel ARC Graphic,Win11, Office24, Meteor Silver, 1.38kg, fm0099TU,Pen, 2 in 1 AI Laptop</t>
+          <t>HP 15, Intel Core Ultra 5 125H (24GB DDR5, 1TB SSD), Micro-Edge, Anti-Glare, FHD, 15''/39.6cm, Win11, M365* Office24, Silver, 1.65kg, FD1458TU, FHD Camera, Backlit Laptop</t>
         </is>
       </c>
       <c r="C233" t="inlineStr"/>
       <c r="D233" t="n">
-        <v>115990</v>
+        <v>84990</v>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>hp_omnibook_3,_snapdragon_x</t>
+          <t>hp_15,_intel_core_i3-1315u-13th</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>HP Omnibook 3, Snapdragon X Processor 45 TOPS (16GB LPDDR5x,512GB SSD) 2K WUXGA, Anti-Glare, 14''/35.6cm, Win 11, M365*Office 24,Silver,1.42kg, hz0026QU, Lighter mini Charger, FHD IR Camera, AI Laptop</t>
+          <t>HP 15, Intel Core i3-1315U-13th Gen Laptop (8GB DDR4 Ram,512GB SSD) Anti-Glare, Micro-Edge,15.6'" FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera Shutter, 15-fd0569TU</t>
         </is>
       </c>
       <c r="C234" t="inlineStr"/>
       <c r="D234" t="n">
-        <v>79990</v>
+        <v>49490</v>
       </c>
       <c r="E234" t="inlineStr">
         <is>
@@ -5339,710 +5339,710 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>HP Omnibook 3, Snapdragon X</t>
+          <t>hp_15,_intel_core_i3-1315u-13th</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>HP Omnibook 3, Snapdragon X Processor, 45 TOPS (16GB LPDDR5x, 512GB SSD) 2K, WUXGA, IPS, 14''/35.6cm, Win 11, Office 24, Silver, 1.4kg, hz0026QU, FHD IR Camera, 42% Lighter mini GaN Charger, AI Laptop</t>
+          <t>HP 15, Intel Core i3-1315U-13th Gen Laptop (8GB DDR4 Ram,512GB SSD) Anti-Glare, Micro-Edge,15.6'" FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera Shutter, 15-fd0569TU</t>
         </is>
       </c>
       <c r="C235" t="inlineStr"/>
       <c r="D235" t="n">
-        <v>69990</v>
+        <v>50900</v>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>HP Omnibook 3, Snapdragon X</t>
+          <t>HP 255R G10 Notebook (AMD</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>HP Omnibook 3, Snapdragon X Processor, 45 TOPS (16GB LPDDR5x, 512GB SSD) 2K, WUXGA, IPS, 14''/35.6cm, Win 11, Office 24, Silver, 1.4kg, hz0026QU, FHD IR Camera, 42% Lighter mini GaN Charger, AI Laptop</t>
+          <t>HP 255R G10 Notebook (AMD Athlon Silver 7120U /8GB/512GB/DOS) 15.6-inch(39.6cm), Anti-Glare, HD Laptop, Radeon Graphics, Silver,1.52kg</t>
         </is>
       </c>
       <c r="C236" t="inlineStr"/>
       <c r="D236" t="n">
-        <v>73990</v>
+        <v>41700</v>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-04-16</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>HP Omnibook 5 OLED (Previously</t>
+          <t>HP 255R G10 Notebook (AMD</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>HP Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x,1TB SSD) 2K OLED,16''/40.6cm, Win11, M365*Office24, Glacier Silver, 1.59kg, fb0001QU, Backlit, Next-Gen AI Laptop</t>
+          <t>HP 255R G10 Notebook (AMD Athlon Silver 7120U /8GB/512GB/DOS) 15.6-inch(39.6cm), Anti-Glare, HD Laptop, Radeon Graphics, Silver,1.52kg</t>
         </is>
       </c>
       <c r="C237" t="inlineStr"/>
       <c r="D237" t="n">
-        <v>78850</v>
+        <v>39340</v>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-05-10</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>hp_omnibook_5_oled_(previously</t>
+          <t>HP 255R G10 Notebook (AMD</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>HP Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor 45 Tops (16GB LPDDR5x, 1TB SSD) 2K,16''/40.6cm, Win11, Office24, Silver, 1.59kg, fb0001QU, Multi-Day Battery AI Laptop</t>
+          <t>HP 255R G10 Notebook (AMD Athlon Silver 7120U /8GB/512GB/DOS) 15.6-inch(39.6cm), Anti-Glare, HD Laptop, Radeon Graphics, Silver,1.52kg</t>
         </is>
       </c>
       <c r="C238" t="inlineStr"/>
       <c r="D238" t="n">
-        <v>77900</v>
+        <v>40409</v>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>hp_pavilion_plus,_intel_core</t>
+          <t>HP 255R G10 Notebook (AMD</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>HP Pavilion Plus, Intel Core i5-1335U-13th Gen Laptop, (16GB LPDDR5x,512GB SSD),IPS, 300 nits, 14''(35.6cm) 2K,Win 11, M365 Basic(1yr), Office Home 24, Silver,1.38kg, 5MP Camera w/Shutter, ew0107TU</t>
+          <t>HP 255R G10 Notebook (AMD Athlon Silver 7120U /8GB/512GB/DOS) 15.6-inch(39.6cm), Anti-Glare, HD Laptop, Radeon Graphics, Silver,1.52kg</t>
         </is>
       </c>
       <c r="C239" t="inlineStr"/>
       <c r="D239" t="n">
-        <v>63990</v>
+        <v>39618</v>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>hp_professional_15_(2026),_intel</t>
+          <t>HP 255R G10 Notebook (AMD</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>HP Professional 15 (2026), Intel (i3 14th Gen) Core 3 100U - (8 GB/512 GB SSD/Intel UHD Graphics/Windows 11 Home) Thin &amp; Light Business Laptop/15.6" Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
+          <t>HP 255R G10 Notebook (AMD Athlon Silver 7120U /8GB/512GB/DOS) 15.6-inch(39.6cm), Anti-Glare, HD Laptop, Radeon Graphics, Silver,1.52kg</t>
         </is>
       </c>
       <c r="C240" t="inlineStr"/>
       <c r="D240" t="n">
-        <v>48990</v>
+        <v>39525</v>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>HP Smartchoice OmniBook 5 OLED</t>
+          <t>HP Omen, Intel Core Ultra</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>HP Smartchoice OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x, 1TB SSD) 2K, 14''/35.6cm, Win11, M365(1yr)*Office24, Silver,1.35kg, he0015QU,Light-Weight,Next-Gen AI Laptop</t>
+          <t>HP Omen, Intel Core Ultra 7 255H, 8GB RTX 5050, 24GB DDR5(Upgradeable) 1TB SSD, 2K, 165Hz, 3ms Response time, IPS, 16''/40.6cm, Win11, M365*Office24, Shadow Black, 2.43kg, am0240tx, RGB Gaming Laptop</t>
         </is>
       </c>
       <c r="C241" t="inlineStr"/>
       <c r="D241" t="n">
-        <v>82990</v>
+        <v>129990</v>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-10</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>HP Smartchoice OmniBook 5 OLED</t>
+          <t>HP OmniBook 3, AMD Ryzen</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>HP Smartchoice OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x, 1TB SSD) 2K, 14''/35.6cm, Win11, M365(1yr)*Office24, Silver,1.35kg, he0015QU,Light-Weight,Next-Gen AI Laptop</t>
+          <t>HP OmniBook 3, AMD Ryzen AI 5 330 (24GB DDR5 RAM, 1TB SSD) FHD, Anti-Glare, 15.6''/39.6cm, Win11, Office24, Glacier Silver,1.7kg, fn0074AU, FHD Camera w/Shutter, FPR, Backlit KB, Next Gen AI Laptop</t>
         </is>
       </c>
       <c r="C242" t="inlineStr"/>
       <c r="D242" t="n">
-        <v>76990</v>
+        <v>69990</v>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>HP Smartchoice OmniBook 5 OLED</t>
+          <t>HP OmniBook 5 OLED (Previously</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>HP Smartchoice OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x, 512GB SSD) 2K, 14''/35.6cm, Win11, M365(1yr)* Office24, Silver, 1.35kg, he0014QU, Next-Gen AI Laptop</t>
+          <t>HP OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x, 1TB SSD) 2K, 14''/35.6cm, Win11, M365 Basic(1yr)* Office24, Silver, 1.35kg, he0015QU, Light-Weight, Next-Gen AI Laptop</t>
         </is>
       </c>
       <c r="C243" t="inlineStr"/>
       <c r="D243" t="n">
-        <v>78990</v>
+        <v>69990</v>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-14</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>HP Smartchoice OmniBook 5 OLED</t>
+          <t>HP OmniBook 5 OLED (Previously</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>HP Smartchoice OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x, 512GB SSD) 2K, 14''/35.6cm, Win11, M365(1yr)* Office24, Silver, 1.35kg, he0014QU, Next-Gen AI Laptop</t>
+          <t>HP OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x, 512GB SSD) 2K, 14''/35.6cm, Win11, M365 Basic(1yr)* Office24, Silver, 1.35kg, he0014QU, Light-Weight, Next-Gen AI Laptop</t>
         </is>
       </c>
       <c r="C244" t="inlineStr"/>
       <c r="D244" t="n">
-        <v>79990</v>
+        <v>78990</v>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>HP Smartchoice Omnibook 5 OLED</t>
+          <t>HP OmniBook 5 OLED (Previously</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>HP Smartchoice Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x,1TB SSD) 2K OLED,16''/40.6cm, Win11, M365(1yr)*Office24, Glacier Silver, 1.59kg, fb0001QU,Next-Gen AI Laptop</t>
+          <t>HP OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x, 512GB SSD) 2K, 14''/35.6cm, Win11, M365 Basic(1yr)* Office24, Silver, 1.35kg, he0014QU, Light-Weight, Next-Gen AI Laptop</t>
         </is>
       </c>
       <c r="C245" t="inlineStr"/>
       <c r="D245" t="n">
-        <v>68739</v>
+        <v>66990</v>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>HP Smartchoice Omnibook 5 OLED</t>
+          <t>hp_omnibook_x_flip_oled</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>HP Smartchoice Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x,1TB SSD) 2K OLED,16''/40.6cm, Win11, M365(1yr)*Office24, Glacier Silver, 1.59kg, fb0001QU,Next-Gen AI Laptop</t>
+          <t>HP OmniBook X Flip OLED Intel Core Ultra 5 226V, 40 Tops (16GB LPDDR5x,1TB SSD) 3K, Touch, 120hz, 14''/35.6cm, Intel ARC Graphic,Win11, Office24, Meteor Silver, 1.38kg, fm0099TU,Pen, 2 in 1 AI Laptop</t>
         </is>
       </c>
       <c r="C246" t="inlineStr"/>
       <c r="D246" t="n">
-        <v>68739</v>
+        <v>115990</v>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>HP Smartchoice Omnibook 5 OLED</t>
+          <t>hp_omnibook_3,_snapdragon_x</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>HP Smartchoice Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x,1TB SSD) 2K OLED,16''/40.6cm, Win11, M365(1yr)*Office24, Glacier Silver, 1.59kg, fb0001QU,Next-Gen AI Laptop</t>
+          <t>HP Omnibook 3, Snapdragon X Processor 45 TOPS (16GB LPDDR5x,512GB SSD) 2K WUXGA, Anti-Glare, 14''/35.6cm, Win 11, M365*Office 24,Silver,1.42kg, hz0026QU, Lighter mini Charger, FHD IR Camera, AI Laptop</t>
         </is>
       </c>
       <c r="C247" t="inlineStr"/>
       <c r="D247" t="n">
-        <v>68739</v>
+        <v>79990</v>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>HP Smartchoice Omnibook 5 OLED</t>
+          <t>HP Omnibook 3, Snapdragon X</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>HP Smartchoice Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x,1TB SSD) 2K OLED,16''/40.6cm, Win11, M365(1yr)*Office24, Glacier Silver, 1.59kg, fb0001QU,Next-Gen AI Laptop</t>
+          <t>HP Omnibook 3, Snapdragon X Processor, 45 TOPS (16GB LPDDR5x, 512GB SSD) 2K, WUXGA, IPS, 14''/35.6cm, Win 11, Office 24, Silver, 1.4kg, hz0026QU, FHD IR Camera, 42% Lighter mini GaN Charger, AI Laptop</t>
         </is>
       </c>
       <c r="C248" t="inlineStr"/>
       <c r="D248" t="n">
-        <v>68323</v>
+        <v>69990</v>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-27</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>HP Smartchoice Omnibook 5 OLED</t>
+          <t>HP Omnibook 3, Snapdragon X</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>HP Smartchoice Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x,1TB SSD) 2K OLED,16''/40.6cm, Win11, M365(1yr)*Office24, Glacier Silver, 1.59kg, fb0001QU,Next-Gen AI Laptop</t>
+          <t>HP Omnibook 3, Snapdragon X Processor, 45 TOPS (16GB LPDDR5x, 512GB SSD) 2K, WUXGA, IPS, 14''/35.6cm, Win 11, Office 24, Silver, 1.4kg, hz0026QU, FHD IR Camera, 42% Lighter mini GaN Charger, AI Laptop</t>
         </is>
       </c>
       <c r="C249" t="inlineStr"/>
       <c r="D249" t="n">
-        <v>67940</v>
+        <v>73990</v>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>HP Smartchoice Omnibook 5 OLED</t>
+          <t>HP Omnibook 5 OLED (Previously</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>HP Smartchoice Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x,1TB SSD) 2K OLED,16''/40.6cm, Win11, M365(1yr)*Office24, Glacier Silver, 1.59kg, fb0001QU,Next-Gen AI Laptop</t>
+          <t>HP Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x,1TB SSD) 2K OLED,16''/40.6cm, Win11, M365*Office24, Glacier Silver, 1.59kg, fb0001QU, Backlit, Next-Gen AI Laptop</t>
         </is>
       </c>
       <c r="C250" t="inlineStr"/>
       <c r="D250" t="n">
-        <v>67940</v>
+        <v>78850</v>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>HP Smartchoice Victus, 13th Gen</t>
+          <t>hp_omnibook_5_oled_(previously</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>HP Smartchoice Victus, 13th Gen Intel Core i7-13620H, 8GB RTX 5050, 24GB DDR5(Upgradeable) 1TB SSD, 144Hz, FHD, 15.6''/39.6cm, Win11, M365* Office24, Mica Silver, 2.29kg, fa2309TX, RGB Gaming Laptop</t>
+          <t>HP Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor 45 Tops (16GB LPDDR5x, 1TB SSD) 2K,16''/40.6cm, Win11, Office24, Silver, 1.59kg, fb0001QU, Multi-Day Battery AI Laptop</t>
         </is>
       </c>
       <c r="C251" t="inlineStr"/>
       <c r="D251" t="n">
-        <v>112990</v>
+        <v>77900</v>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>HP Smartchoice Victus, AMD Ryzen</t>
+          <t>hp_pavilion_plus,_intel_core</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>HP Smartchoice Victus, AMD Ryzen 7 7445HS, 6GB RTX 3050, 16GB DDR5(Upgradeable) 512GB SSD, FHD, 144Hz, 300 nits, 15.6''/39.6cm, Win 11, M365* Office24, Blue, 2.29kg, fb3134AX/3120ax, Gaming Laptop</t>
+          <t>HP Pavilion Plus, Intel Core i5-1335U-13th Gen Laptop, (16GB LPDDR5x,512GB SSD),IPS, 300 nits, 14''(35.6cm) 2K,Win 11, M365 Basic(1yr), Office Home 24, Silver,1.38kg, 5MP Camera w/Shutter, ew0107TU</t>
         </is>
       </c>
       <c r="C252" t="inlineStr"/>
       <c r="D252" t="n">
-        <v>78990</v>
+        <v>63990</v>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>HP Smartchoice Victus, AMD Ryzen</t>
+          <t>hp_professional_15_(2026),_intel</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>HP Smartchoice Victus, AMD Ryzen 7 7445HS, 6GB RTX 3050, 16GB DDR5(Upgradeable) 512GB SSD, FHD, 144Hz, 300 nits, 15.6''/39.6cm, Win 11, M365* Office24, Blue, 2.29kg, fb3134AX/3120ax, Gaming Laptop</t>
+          <t>HP Professional 15 (2026), Intel (i3 14th Gen) Core 3 100U - (8 GB/512 GB SSD/Intel UHD Graphics/Windows 11 Home) Thin &amp; Light Business Laptop/15.6" Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
         </is>
       </c>
       <c r="C253" t="inlineStr"/>
       <c r="D253" t="n">
-        <v>86990</v>
+        <v>48990</v>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>HP Smartchoice Victus, AMD Ryzen</t>
+          <t>hp_professional_15_(2026),_intel</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>HP Smartchoice Victus, AMD Ryzen 7 7445HS, 6GB RTX 3050, 16GB DDR5(Upgradeable) 512GB SSD, FHD, 144Hz, 300 nits, 15.6''/39.6cm, Win 11, M365* Office24, Blue, 2.29kg, fb3134AX/3120ax, Gaming Laptop</t>
+          <t>HP Professional 15 (2026), Intel (i3 14th Gen) Core 3 100U - (8 GB/512 GB SSD/Intel UHD Graphics/Windows 11 Home) Thin &amp; Light Business Laptop/15.6" Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
         </is>
       </c>
       <c r="C254" t="inlineStr"/>
       <c r="D254" t="n">
-        <v>86990</v>
+        <v>51899</v>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>HP Victus, 14th Gen Intel</t>
+          <t>HP Smartchoice OmniBook 5 OLED</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>HP Victus, 14th Gen Intel Core i5-14450HX, 6GB RTX 3050, 24GB DDR5, 512GB SSD, FHD, 144Hz, 300 nits, IPS,15.6''/39.6cm, Win11, M365* Office24, Mica Silver, 2.3kg, fa2303tx/fa2315tx, RGB Gaming Laptop</t>
+          <t>HP Smartchoice OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x, 1TB SSD) 2K, 14''/35.6cm, Win11, M365(1yr)*Office24, Silver,1.35kg, he0015QU,Light-Weight,Next-Gen AI Laptop</t>
         </is>
       </c>
       <c r="C255" t="inlineStr"/>
       <c r="D255" t="n">
-        <v>103990</v>
+        <v>82990</v>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>HP Victus, AMD Ryzen 7</t>
+          <t>HP Smartchoice OmniBook 5 OLED</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>HP Victus, AMD Ryzen 7 7445HS, 4GB RTX 2050, 16GB DDR5(Upgradeable) 512GB SSD, FHD, 144Hz, 300 nits, IPS, 15.6'', Win11, M365* Office24, Blue, 2.29kg, fb3189ax /3122/ 23ax Backlit, Gaming Laptop</t>
+          <t>HP Smartchoice OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x, 1TB SSD) 2K, 14''/35.6cm, Win11, M365(1yr)*Office24, Silver,1.35kg, he0015QU,Light-Weight,Next-Gen AI Laptop</t>
         </is>
       </c>
       <c r="C256" t="inlineStr"/>
       <c r="D256" t="n">
-        <v>65990</v>
+        <v>76990</v>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>HP Victus, AMD Ryzen 7</t>
+          <t>HP Smartchoice OmniBook 5 OLED</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>HP Victus, AMD Ryzen 7 7445HS, 4GB RTX 2050, 16GB DDR5(Upgradeable) 512GB SSD, FHD, 144Hz, 300 nits, IPS, 15.6'', Win11, M365* Office24, Blue, 2.29kg, fb3189ax /3122/ 23ax Backlit, Gaming Laptop</t>
+          <t>HP Smartchoice OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x, 512GB SSD) 2K, 14''/35.6cm, Win11, M365(1yr)* Office24, Silver, 1.35kg, he0014QU, Next-Gen AI Laptop</t>
         </is>
       </c>
       <c r="C257" t="inlineStr"/>
       <c r="D257" t="n">
-        <v>65990</v>
+        <v>78990</v>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-24</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>HP Victus, AMD Ryzen 7</t>
+          <t>HP Smartchoice OmniBook 5 OLED</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>HP Victus, AMD Ryzen 7 7445HS, 6GB RTX 4050, 16GB DDR5(Upgradeable) 512GB SSD, 144Hz, IPS, 300nits, FHD, 15.6''/39.6cm, Win11, M365* Office24, Blue, 2.29kg, fb3130AX, Backlit, DTS Audio, Gaming Laptop</t>
+          <t>HP Smartchoice OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x, 512GB SSD) 2K, 14''/35.6cm, Win11, M365(1yr)* Office24, Silver, 1.35kg, he0014QU, Next-Gen AI Laptop</t>
         </is>
       </c>
       <c r="C258" t="inlineStr"/>
       <c r="D258" t="n">
-        <v>90990</v>
+        <v>79990</v>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>HP Victus, AMD Ryzen 7</t>
+          <t>HP Smartchoice Omnibook 5 OLED</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>HP Victus, AMD Ryzen 7 7445HS, 6GB RTX 4050, 16GB DDR5(Upgradeable) 512GB SSD, 144Hz, IPS, 300nits, FHD, 15.6''/39.6cm, Win11, M365* Office24, Blue, 2.29kg, fb3130AX, Backlit, DTS Audio, Gaming Laptop</t>
+          <t>HP Smartchoice Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x,1TB SSD) 2K OLED,16''/40.6cm, Win11, M365(1yr)*Office24, Glacier Silver, 1.59kg, fb0001QU,Next-Gen AI Laptop</t>
         </is>
       </c>
       <c r="C259" t="inlineStr"/>
       <c r="D259" t="n">
-        <v>91990</v>
+        <v>68739</v>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Lenovo Chromebook Intel Celeron N4500</t>
+          <t>HP Smartchoice Omnibook 5 OLED</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Lenovo Chromebook Intel Celeron N4500 (4GB RAM/64GB eMMC 5.1/11.6 Inch (29.46cm)/HD Display/2Wx2 Stereo Speakers/HD Camera/Chrome OS/Blue/1.21Kg), 82UY0014HA</t>
+          <t>HP Smartchoice Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x,1TB SSD) 2K OLED,16''/40.6cm, Win11, M365(1yr)*Office24, Glacier Silver, 1.59kg, fb0001QU,Next-Gen AI Laptop</t>
         </is>
       </c>
       <c r="C260" t="inlineStr"/>
       <c r="D260" t="n">
-        <v>21990</v>
+        <v>68739</v>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Lenovo Chromebook Intel Celeron N4500</t>
+          <t>HP Smartchoice Omnibook 5 OLED</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Lenovo Chromebook Intel Celeron N4500 (4GB RAM/64GB eMMC 5.1/11.6 Inch (29.46cm)/HD Display/2Wx2 Stereo Speakers/HD Camera/Chrome OS/Blue/1.21Kg), 82UY0014HA</t>
+          <t>HP Smartchoice Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x,1TB SSD) 2K OLED,16''/40.6cm, Win11, M365(1yr)*Office24, Glacier Silver, 1.59kg, fb0001QU,Next-Gen AI Laptop</t>
         </is>
       </c>
       <c r="C261" t="inlineStr"/>
       <c r="D261" t="n">
-        <v>18990</v>
+        <v>68739</v>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-27</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Lenovo IdeaPad Slim 3 13th</t>
+          <t>HP Smartchoice Omnibook 5 OLED</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Lenovo IdeaPad Slim 3 13th Gen Intel Core i5-13420H 15.3 inch (38.8cm) WUXGA IPS Laptop (16GB RAM/1TB SSD/Windows 11/MSO 365 Basic+Office 2024/Top Metal Cover/Backlit KB/Grey/1.6Kg), 83K100S0IN</t>
+          <t>HP Smartchoice Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x,1TB SSD) 2K OLED,16''/40.6cm, Win11, M365(1yr)*Office24, Glacier Silver, 1.59kg, fb0001QU,Next-Gen AI Laptop</t>
         </is>
       </c>
       <c r="C262" t="inlineStr"/>
       <c r="D262" t="n">
-        <v>70990</v>
+        <v>68323</v>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-31</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>lenovo_ideapad_slim_3_13th</t>
+          <t>HP Smartchoice Omnibook 5 OLED</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Lenovo IdeaPad Slim 3 13th Gen Intel Core i7 13620H, 16GB RAM, 512GB SSD, WUXGA IPS, 15.3"/38.8cm, Win 11, Office 2024, Top Metal Cover Grey, 1.6Kg, 83K100CJIN/S1IN, Backlit KB, Laptop</t>
+          <t>HP Smartchoice Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x,1TB SSD) 2K OLED,16''/40.6cm, Win11, M365(1yr)*Office24, Glacier Silver, 1.59kg, fb0001QU,Next-Gen AI Laptop</t>
         </is>
       </c>
       <c r="C263" t="inlineStr"/>
       <c r="D263" t="n">
-        <v>81990</v>
+        <v>67940</v>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>lenovo_ideapad_slim_3,_13th</t>
+          <t>HP Smartchoice Omnibook 5 OLED</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Lenovo IdeaPad Slim 3, 13th Gen Intel Core i5 13420H, 24GB RAM, 1TB SSD, WUXGA IPS, 15.3"/38.8cm, Windows 11, Office Home 2024, Grey, 1.6Kg, Backlit Keyboard, 1Yr ADP Free, 83K100PLIN, Laptop</t>
+          <t>HP Smartchoice Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x,1TB SSD) 2K OLED,16''/40.6cm, Win11, M365(1yr)*Office24, Glacier Silver, 1.59kg, fb0001QU,Next-Gen AI Laptop</t>
         </is>
       </c>
       <c r="C264" t="inlineStr"/>
       <c r="D264" t="n">
-        <v>79990</v>
+        <v>67940</v>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-02</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>lenovo_ideapad_slim_3,_amd</t>
+          <t>HP Smartchoice Victus, 13th Gen</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Lenovo IdeaPad Slim 3, AMD Ryzen 7 8840HS, 24GB RAM, 1TB SSD, WUXGA IPS, AI PC, 15.3"/38.8cm, Backlit Keyboard, Windows 11, Office Home 2024, Grey, 1.6Kg, 1Yr ADP Free, 83KA004TIN, AI Powered Laptop</t>
+          <t>HP Smartchoice Victus, 13th Gen Intel Core i7-13620H, 8GB RTX 5050, 24GB DDR5(Upgradeable) 1TB SSD, 144Hz, FHD, 15.6''/39.6cm, Win11, M365* Office24, Mica Silver, 2.29kg, fa2309TX, RGB Gaming Laptop</t>
         </is>
       </c>
       <c r="C265" t="inlineStr"/>
       <c r="D265" t="n">
-        <v>87990</v>
+        <v>112990</v>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-10</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>lenovo_ideapad_slim_5,_amd</t>
+          <t>HP Smartchoice Victus, AMD Ryzen</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Lenovo IdeaPad Slim 5, AMD Ryzen 5 7535HS, 16GB RAM, 512GB SSD, WUXGA IPS, 13.3"/33.7cm, Windows 11, Microsoft 365 Basic + Office 2024, Grey, 1.6Kg, Backlit KB, 1Yr ADP Free, 83J2004HIN, Laptop</t>
+          <t>HP Smartchoice Victus, AMD Ryzen 7 7445HS, 6GB RTX 3050, 16GB DDR5(Upgradeable) 512GB SSD, FHD, 144Hz, 300 nits, 15.6''/39.6cm, Win 11, M365* Office24, Blue, 2.29kg, fb3134AX/3120ax, Gaming Laptop</t>
         </is>
       </c>
       <c r="C266" t="inlineStr"/>
       <c r="D266" t="n">
-        <v>72990</v>
+        <v>78990</v>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Lenovo Ideapad Slim 3 AMD</t>
+          <t>HP Smartchoice Victus, AMD Ryzen</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Lenovo Ideapad Slim 3 AMD Ryzen 5 7520U 15.6" (39.6cm) FHD Thin and Light Laptop (16GB/512GB SSD/Windows 11/Microsoft 365 Basic + Office Home 2024/Backlit Keyboard/Grey/1.6Kg), 82XQ00XDIN</t>
+          <t>HP Smartchoice Victus, AMD Ryzen 7 7445HS, 6GB RTX 3050, 16GB DDR5(Upgradeable) 512GB SSD, FHD, 144Hz, 300 nits, 15.6''/39.6cm, Win 11, M365* Office24, Blue, 2.29kg, fb3134AX/3120ax, Gaming Laptop</t>
         </is>
       </c>
       <c r="C267" t="inlineStr"/>
       <c r="D267" t="n">
-        <v>50750</v>
+        <v>86990</v>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Lenovo LOQ 2024, Intel Core</t>
+          <t>HP Smartchoice Victus, AMD Ryzen</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Lenovo LOQ 2024, Intel Core i5-13450HX, 13th Gen, NVIDIA RTX 4050-6GB, 16GB RAM, 512GB SSD, FHD 144Hz, 15.6"/39.6cm, Windows 11, Office Home 2024, Grey, 2.4Kg, 83DV018JIN, 1Yr ADP Free Gaming Laptop</t>
+          <t>HP Smartchoice Victus, AMD Ryzen 7 7445HS, 6GB RTX 3050, 16GB DDR5(Upgradeable) 512GB SSD, FHD, 144Hz, 300 nits, 15.6''/39.6cm, Win 11, M365* Office24, Blue, 2.29kg, fb3134AX/3120ax, Gaming Laptop</t>
         </is>
       </c>
       <c r="C268" t="inlineStr"/>
       <c r="D268" t="n">
-        <v>100544</v>
+        <v>86990</v>
       </c>
       <c r="E268" t="inlineStr">
         <is>
@@ -6053,248 +6053,248 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Lenovo LOQ 2025 AMD Ryzen</t>
+          <t>HP Victus, 14th Gen Intel</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Lenovo LOQ 2025 AMD Ryzen 7 250| NVIDIA RTX 5050 8GB (16GB RAM/1TB SSD/144Hz Refresh Rate/440 AI TOPS/15.6" (39.6cm)/Windows 11/Office 2024/3 Mon. Game Pass/Grey/2.4Kg), 83JG008KIN</t>
+          <t>HP Victus, 14th Gen Intel Core i5-14450HX, 6GB RTX 3050, 24GB DDR5, 512GB SSD, FHD, 144Hz, 300 nits, IPS,15.6''/39.6cm, Win11, M365* Office24, Mica Silver, 2.3kg, fa2303tx/fa2315tx, RGB Gaming Laptop</t>
         </is>
       </c>
       <c r="C269" t="inlineStr"/>
       <c r="D269" t="n">
-        <v>134990</v>
+        <v>103990</v>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-10</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Lenovo LOQ 2025 Intel Core</t>
+          <t>HP Victus, AMD Ryzen 7</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Lenovo LOQ 2025 Intel Core i7-14700HX| NVIDIA RTX 5060 8GB (32GB RAM/1TB SSD/144Hz Refresh Rate/572 AI TOPS/15.6" (39.6cm)/Windows 11/Office 2024/3 Mon. Game Pass/Grey/2.4Kg), 83JE00T3IN</t>
+          <t>HP Victus, AMD Ryzen 7 7445HS, 4GB RTX 2050, 16GB DDR5(Upgradeable) 512GB SSD, FHD, 144Hz, 300 nits, IPS, 15.6'', Win11, M365* Office24, Blue, 2.29kg, fb3189ax /3122/ 23ax Backlit, Gaming Laptop</t>
         </is>
       </c>
       <c r="C270" t="inlineStr"/>
       <c r="D270" t="n">
-        <v>157990</v>
+        <v>65990</v>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-21</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Lenovo LOQ AMD Ryzen 5</t>
+          <t>HP Victus, AMD Ryzen 7</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Lenovo LOQ AMD Ryzen 5 7235HS | NVIDIA RTX 4050 6GB (16GB RAM/512GB SSD/144Hz Refresh Rate/15.6" (39.6cm)/Windows 11/Office Home 2024/3 Mon. Game Pass/Grey/2.4Kg), 83JC00NYIN AI Gaming Laptop</t>
+          <t>HP Victus, AMD Ryzen 7 7445HS, 4GB RTX 2050, 16GB DDR5(Upgradeable) 512GB SSD, FHD, 144Hz, 300 nits, IPS, 15.6'', Win11, M365* Office24, Blue, 2.29kg, fb3189ax /3122/ 23ax Backlit, Gaming Laptop</t>
         </is>
       </c>
       <c r="C271" t="inlineStr"/>
       <c r="D271" t="n">
-        <v>88990</v>
+        <v>65990</v>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-22</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Lenovo LOQ, 13th Gen Intel</t>
+          <t>HP Victus, AMD Ryzen 7</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Lenovo LOQ, 13th Gen Intel Core i7 13700HX, RTX 5050-8GB, 16GB RAM, 1TB SSD, FHD, 15.6"/39.6cm, 144Hz, Windows 11, Office 2024, Grey, 2.4Kg, 440 AI Tops, 3 Mon. Game Pass, 83JE00U7IN, AI Gaming Laptop</t>
+          <t>HP Victus, AMD Ryzen 7 7445HS, 6GB RTX 4050, 16GB DDR5(Upgradeable) 512GB SSD, 144Hz, IPS, 300nits, FHD, 15.6''/39.6cm, Win11, M365* Office24, Blue, 2.29kg, fb3130AX, Backlit, DTS Audio, Gaming Laptop</t>
         </is>
       </c>
       <c r="C272" t="inlineStr"/>
       <c r="D272" t="n">
-        <v>121869</v>
+        <v>90990</v>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Lenovo Legion 7 2025 Intel</t>
+          <t>HP Victus, AMD Ryzen 7</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Lenovo Legion 7 2025 Intel Core Ultra 9 275HX| NVIDIA RTX 5070 8GB (32GB RAM/1TB SSD/WQXGA OLED/240Hz/16(40.64cm)/Windows 11/Office 2024+AI Now/White/2.0Kg), 83KY001GIN AI Powered Gaming Laptop</t>
+          <t>HP Victus, AMD Ryzen 7 7445HS, 6GB RTX 4050, 16GB DDR5(Upgradeable) 512GB SSD, 144Hz, IPS, 300nits, FHD, 15.6''/39.6cm, Win11, M365* Office24, Blue, 2.29kg, fb3130AX, Backlit, DTS Audio, Gaming Laptop</t>
         </is>
       </c>
       <c r="C273" t="inlineStr"/>
       <c r="D273" t="n">
-        <v>239391</v>
+        <v>91990</v>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Lenovo Legion Pro 5 2025</t>
+          <t>Lenovo Chromebook Intel Celeron N4500</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Lenovo Legion Pro 5 2025 AMD Ryzen 9 9955HX | NVIDIA RTX 5060 8GB (32GB RAM/1TB SSD/WQXGA OLED/165Hz/16 (40.6cm)/Windows 11/Office 2024+AI Now/Black/2.3Kg), 83F2004CIN AI Powered Gaming Laptop</t>
+          <t>Lenovo Chromebook Intel Celeron N4500 (4GB RAM/64GB eMMC 5.1/11.6 Inch (29.46cm)/HD Display/2Wx2 Stereo Speakers/HD Camera/Chrome OS/Blue/1.21Kg), 82UY0014HA</t>
         </is>
       </c>
       <c r="C274" t="inlineStr"/>
       <c r="D274" t="n">
-        <v>245490</v>
+        <v>21990</v>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Lenovo Legion Pro 5 2025</t>
+          <t>Lenovo Chromebook Intel Celeron N4500</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Lenovo Legion Pro 5 2025 AMD Ryzen 9 9955HX | NVIDIA RTX 5060 8GB (32GB RAM/1TB SSD/WQXGA OLED/165Hz/16 (40.6cm)/Windows 11/Office 2024+AI Now/Black/2.3Kg), 83F2004CIN AI Powered Gaming Laptop</t>
+          <t>Lenovo Chromebook Intel Celeron N4500 (4GB RAM/64GB eMMC 5.1/11.6 Inch (29.46cm)/HD Display/2Wx2 Stereo Speakers/HD Camera/Chrome OS/Blue/1.21Kg), 82UY0014HA</t>
         </is>
       </c>
       <c r="C275" t="inlineStr"/>
       <c r="D275" t="n">
-        <v>245490</v>
+        <v>18990</v>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Lenovo Legion Pro 5 2025</t>
+          <t>Lenovo IdeaPad Slim 3 13th</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Lenovo Legion Pro 5 2025 AMD Ryzen 9 9955HX | NVIDIA RTX 5060 8GB (32GB RAM/1TB SSD/WQXGA OLED/165Hz/16 (40.6cm)/Windows 11/Office 2024+AI Now/Black/2.3Kg), 83F2004CIN AI Powered Gaming Laptop</t>
+          <t>Lenovo IdeaPad Slim 3 13th Gen Intel Core i5-13420H 15.3 inch (38.8cm) WUXGA IPS Laptop (16GB RAM/1TB SSD/Windows 11/MSO 365 Basic+Office 2024/Top Metal Cover/Backlit KB/Grey/1.6Kg), 83K100S0IN</t>
         </is>
       </c>
       <c r="C276" t="inlineStr"/>
       <c r="D276" t="n">
-        <v>245490</v>
+        <v>70990</v>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-08</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Lenovo Legion Pro 5 2025</t>
+          <t>lenovo_ideapad_slim_3_13th</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Lenovo Legion Pro 5 2025 AMD Ryzen 9 9955HX | NVIDIA RTX 5060 8GB (32GB RAM/1TB SSD/WQXGA OLED/165Hz/16 (40.6cm)/Windows 11/Office 2024+AI Now/Black/2.3Kg), 83F2004CIN AI Powered Gaming Laptop</t>
+          <t>Lenovo IdeaPad Slim 3 13th Gen Intel Core i7 13620H, 16GB RAM, 512GB SSD, WUXGA IPS, 15.3"/38.8cm, Win 11, Office 2024, Top Metal Cover Grey, 1.6Kg, 83K100CJIN/S1IN, Backlit KB, Laptop</t>
         </is>
       </c>
       <c r="C277" t="inlineStr"/>
       <c r="D277" t="n">
-        <v>245490</v>
+        <v>81990</v>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Lenovo Legion Pro 7 FIFA</t>
+          <t>lenovo_ideapad_slim_3_13th</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Lenovo Legion Pro 7 FIFA World Cup 26 Edition Intel Core Ultra 9 275HX | NVIDIA RTX 5070Ti 12GB (32GB RAM/1TB SSD/WQXGA OLED/240Hz/16(40.6cm)/Windows 11/Black/2.4Kg), 83F500HPIN AI Gaming Laptop</t>
+          <t>Lenovo IdeaPad Slim 3 13th Gen Intel Core i7 13620H, 16GB RAM, 512GB SSD, WUXGA IPS, 15.3"/38.8cm, Win 11, Office 2024, Top Metal Cover Grey, 1.6Kg, 83K100CJIN/S1IN, Backlit KB, Laptop</t>
         </is>
       </c>
       <c r="C278" t="inlineStr"/>
       <c r="D278" t="n">
-        <v>319990</v>
+        <v>79990</v>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Lenovo Smartchoice Ideapad 5 2-in-1</t>
+          <t>lenovo_ideapad_slim_3,_13th</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Lenovo Smartchoice Ideapad 5 2-in-1 13th Gen Intel Core i5-13420H (16GB RAM/512GB SSD/Windows 11/Office Home 2024/WUXGA IPS/14 (35.5cm)/Touchscreen 2-in-1/3Mon.Game Pass/Grey/1.6kg), 83KX0059IN Laptop</t>
+          <t>Lenovo IdeaPad Slim 3, 13th Gen Intel Core i5 13420H, 24GB RAM, 1TB SSD, WUXGA IPS, 15.3"/38.8cm, Windows 11, Office Home 2024, Grey, 1.6Kg, Backlit Keyboard, 1Yr ADP Free, 83K100PLIN, Laptop</t>
         </is>
       </c>
       <c r="C279" t="inlineStr"/>
       <c r="D279" t="n">
-        <v>74490</v>
+        <v>79990</v>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>lenovo_thinkbook_14,_amd_ryzen</t>
+          <t>lenovo_ideapad_slim_3,_amd</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Lenovo ThinkBook 14, AMD Ryzen 5 220, 16GB RAM, 1TB SSD, WUXGA IPS 14” (35.56cm), Windows 11 Home, Arctic Grey, 1.36Kg, 21V0A01SIG, Fingerprint, Backlit, 400 Nits, 1Y Warranty, Laptop</t>
+          <t>Lenovo IdeaPad Slim 3, AMD Ryzen 7 8840HS, 24GB RAM, 1TB SSD, WUXGA IPS, AI PC, 15.3"/38.8cm, Backlit Keyboard, Windows 11, Office Home 2024, Grey, 1.6Kg, 1Yr ADP Free, 83KA004TIN, AI Powered Laptop</t>
         </is>
       </c>
       <c r="C280" t="inlineStr"/>
       <c r="D280" t="n">
-        <v>90990</v>
+        <v>87990</v>
       </c>
       <c r="E280" t="inlineStr">
         <is>
@@ -6305,38 +6305,38 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Lenovo ThinkBook 15 G5 AMD</t>
+          <t>lenovo_ideapad_slim_3,_amd</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Lenovo ThinkBook 15 G5 AMD Ryzen 7 7730U 15.6" FHD Antiglare 250 Nits Thin and Light Laptop (8GB RAM/512GB SSD/Windows 11 Home/Fingerprint Reader/Backlit/Mineral Grey/1 Year Onsite/1.7 kg), 21JFA00BIN</t>
+          <t>Lenovo IdeaPad Slim 3, AMD Ryzen 7 8840HS, 24GB RAM, 1TB SSD, WUXGA IPS, AI PC, 15.3"/38.8cm, Backlit Keyboard, Windows 11, Office Home 2024, Grey, 1.6Kg, 1Yr ADP Free, 83KA004TIN, AI Powered Laptop</t>
         </is>
       </c>
       <c r="C281" t="inlineStr"/>
       <c r="D281" t="n">
-        <v>59999</v>
+        <v>79990</v>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>lenovo_thinkbook_16_amd_ryzen</t>
+          <t>lenovo_ideapad_slim_5,_amd</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Lenovo ThinkBook 16 AMD Ryzen 5 7535HS (8GB RAM/512GB SSD/Win 11 Home/Office 2024/Backlit Keyboard/Fingerprint) 16" WUXGA IPS 300 Nits Thin &amp; Light Laptop/1Y Warranty/Aluminium Top/1.7kg, 21MWA0BRIN</t>
+          <t>Lenovo IdeaPad Slim 5, AMD Ryzen 5 7535HS, 16GB RAM, 512GB SSD, WUXGA IPS, 13.3"/33.7cm, Windows 11, Microsoft 365 Basic + Office 2024, Grey, 1.6Kg, Backlit KB, 1Yr ADP Free, 83J2004HIN, Laptop</t>
         </is>
       </c>
       <c r="C282" t="inlineStr"/>
       <c r="D282" t="n">
-        <v>65063</v>
+        <v>72990</v>
       </c>
       <c r="E282" t="inlineStr">
         <is>
@@ -6347,227 +6347,227 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Lenovo ThinkBook 16, Intel Core</t>
+          <t>Lenovo Ideapad Slim 3 AMD</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Lenovo ThinkBook 16, Intel Core Ultra 9 185H, 16GB RAM, 512GB SSD, WUXGA IPS 16” (40.64cm), Win 11 Home, Arctic Grey, 1.7Kg, 21SKA0J5IG, Fingerprint, Backlit, 300 Nits, 1Y Warranty, AI Powered Laptop</t>
+          <t>Lenovo Ideapad Slim 3 AMD Ryzen 5 7520U 15.6" (39.6cm) FHD Thin and Light Laptop (16GB/512GB SSD/Windows 11/Microsoft 365 Basic + Office Home 2024/Backlit Keyboard/Grey/1.6Kg), 82XQ00XDIN</t>
         </is>
       </c>
       <c r="C283" t="inlineStr"/>
       <c r="D283" t="n">
-        <v>94990</v>
+        <v>50750</v>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-14</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Lenovo V14 Intel Core i3</t>
+          <t>Lenovo LOQ 2024, Intel Core</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Lenovo V14 Intel Core i3 13th Gen 14" FHD (1920x1080) Antiglare 250 Nits Thin and Light Laptop (16GB RAM/512GB SSD/Windows 11 Home/Office Home 2024/Iron Grey/1.43 kg), 83A0A0PCIN</t>
+          <t>Lenovo LOQ 2024, Intel Core i5-13450HX, 13th Gen, NVIDIA RTX 4050-6GB, 16GB RAM, 512GB SSD, FHD 144Hz, 15.6"/39.6cm, Windows 11, Office Home 2024, Grey, 2.4Kg, 83DV018JIN, 1Yr ADP Free Gaming Laptop</t>
         </is>
       </c>
       <c r="C284" t="inlineStr"/>
       <c r="D284" t="n">
-        <v>70990</v>
+        <v>100544</v>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Lenovo V14 Intel Core i3</t>
+          <t>Lenovo LOQ 2025 AMD Ryzen</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Lenovo V14 Intel Core i3 13th Gen 14" FHD (1920x1080) Antiglare 250 Nits Thin and Light Laptop (16GB RAM/512GB SSD/Windows 11 Home/Office Home 2024/Iron Grey/1.43 kg), 83A0A0PCIN</t>
+          <t>Lenovo LOQ 2025 AMD Ryzen 7 250| NVIDIA RTX 5050 8GB (16GB RAM/1TB SSD/144Hz Refresh Rate/440 AI TOPS/15.6" (39.6cm)/Windows 11/Office 2024/3 Mon. Game Pass/Grey/2.4Kg), 83JG008KIN</t>
         </is>
       </c>
       <c r="C285" t="inlineStr"/>
       <c r="D285" t="n">
-        <v>70990</v>
+        <v>134990</v>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>lenovo_v14_intel_core_i3</t>
+          <t>Lenovo LOQ 2025 Intel Core</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Lenovo V14 Intel Core i3 13th Gen 14" FHD (1920x1080) Antiglare 250 Nits Thin and Light Laptop (16GB RAM/512GB SSD/Windows 11 Home/Office Home 2024/Iron Grey/1.43 kg), 83A0A0PCIN</t>
+          <t>Lenovo LOQ 2025 Intel Core i7-14700HX| NVIDIA RTX 5060 8GB (32GB RAM/1TB SSD/144Hz Refresh Rate/572 AI TOPS/15.6" (39.6cm)/Windows 11/Office 2024/3 Mon. Game Pass/Grey/2.4Kg), 83JE00T3IN</t>
         </is>
       </c>
       <c r="C286" t="inlineStr"/>
       <c r="D286" t="n">
-        <v>70990</v>
+        <v>157990</v>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 (2024), AMD</t>
+          <t>Lenovo LOQ AMD Ryzen 5</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 (2024), AMD Ryzen 3 7320U Quad Core - (8GB/512GB SSD/AMD Radeon Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" FHD Display/Arctic Grey/1.57 kg/MS Office 2021</t>
+          <t>Lenovo LOQ AMD Ryzen 5 7235HS | NVIDIA RTX 4050 6GB (16GB RAM/512GB SSD/144Hz Refresh Rate/15.6" (39.6cm)/Windows 11/Office Home 2024/3 Mon. Game Pass/Grey/2.4Kg), 83JC00NYIN AI Gaming Laptop</t>
         </is>
       </c>
       <c r="C287" t="inlineStr"/>
       <c r="D287" t="n">
-        <v>44200</v>
+        <v>88990</v>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-19</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 (2024), AMD</t>
+          <t>Lenovo LOQ, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 (2024), AMD Ryzen 3 7320U Quad Core - (8GB/512GB SSD/AMD Radeon Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" FHD Display/Arctic Grey/1.57 kg/MS Office 2021</t>
+          <t>Lenovo LOQ, 13th Gen Intel Core i7 13700HX, RTX 5050-8GB, 16GB RAM, 1TB SSD, FHD, 15.6"/39.6cm, 144Hz, Windows 11, Office 2024, Grey, 2.4Kg, 440 AI Tops, 3 Mon. Game Pass, 83JE00U7IN, AI Gaming Laptop</t>
         </is>
       </c>
       <c r="C288" t="inlineStr"/>
       <c r="D288" t="n">
-        <v>44490</v>
+        <v>121869</v>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 (2024), AMD</t>
+          <t>Lenovo Legion 7 2025 Intel</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 (2024), AMD Ryzen 3 7320U Quad Core - (8GB/512GB SSD/AMD Radeon Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" FHD Display/Arctic Grey/1.57 kg/MS Office 2021</t>
+          <t>Lenovo Legion 7 2025 Intel Core Ultra 9 275HX| NVIDIA RTX 5070 8GB (32GB RAM/1TB SSD/WQXGA OLED/240Hz/16(40.64cm)/Windows 11/Office 2024+AI Now/White/2.0Kg), 83KY001GIN AI Powered Gaming Laptop</t>
         </is>
       </c>
       <c r="C289" t="inlineStr"/>
       <c r="D289" t="n">
-        <v>44490</v>
+        <v>239391</v>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-08</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 (2024), AMD</t>
+          <t>Lenovo Legion Pro 5 2025</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 (2024), AMD Ryzen 3 7320U Quad Core - (8GB/512GB SSD/AMD Radeon Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" FHD Display/Arctic Grey/1.57 kg/MS Office 2021</t>
+          <t>Lenovo Legion Pro 5 2025 AMD Ryzen 9 9955HX | NVIDIA RTX 5060 8GB (32GB RAM/1TB SSD/WQXGA OLED/165Hz/16 (40.6cm)/Windows 11/Office 2024+AI Now/Black/2.3Kg), 83F2004CIN AI Powered Gaming Laptop</t>
         </is>
       </c>
       <c r="C290" t="inlineStr"/>
       <c r="D290" t="n">
-        <v>44500</v>
+        <v>245490</v>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-22</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 (2024), AMD</t>
+          <t>Lenovo Legion Pro 5 2025</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 (2024), AMD Ryzen 3 7320U Quad Core - (8GB/512GB SSD/AMD Radeon Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" FHD Display/Arctic Grey/1.57 kg/MS Office 2021</t>
+          <t>Lenovo Legion Pro 5 2025 AMD Ryzen 9 9955HX | NVIDIA RTX 5060 8GB (32GB RAM/1TB SSD/WQXGA OLED/165Hz/16 (40.6cm)/Windows 11/Office 2024+AI Now/Black/2.3Kg), 83F2004CIN AI Powered Gaming Laptop</t>
         </is>
       </c>
       <c r="C291" t="inlineStr"/>
       <c r="D291" t="n">
-        <v>49999</v>
+        <v>245490</v>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-24</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 (2024), AMD</t>
+          <t>Lenovo Legion Pro 5 2025</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 (2024), AMD Ryzen 3 7320U Quad Core - (8GB/512GB SSD/AMD Radeon Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" FHD Display/Arctic Grey/1.57 kg/MS Office 2021</t>
+          <t>Lenovo Legion Pro 5 2025 AMD Ryzen 9 9955HX | NVIDIA RTX 5060 8GB (32GB RAM/1TB SSD/WQXGA OLED/165Hz/16 (40.6cm)/Windows 11/Office 2024+AI Now/Black/2.3Kg), 83F2004CIN AI Powered Gaming Laptop</t>
         </is>
       </c>
       <c r="C292" t="inlineStr"/>
       <c r="D292" t="n">
-        <v>49890</v>
+        <v>245490</v>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon</t>
+          <t>Lenovo Legion Pro 5 2025</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo Legion Pro 5 2025 AMD Ryzen 9 9955HX | NVIDIA RTX 5060 8GB (32GB RAM/1TB SSD/WQXGA OLED/165Hz/16 (40.6cm)/Windows 11/Office 2024+AI Now/Black/2.3Kg), 83F2004CIN AI Powered Gaming Laptop</t>
         </is>
       </c>
       <c r="C293" t="inlineStr"/>
       <c r="D293" t="n">
-        <v>41999</v>
+        <v>245490</v>
       </c>
       <c r="E293" t="inlineStr">
         <is>
@@ -6578,206 +6578,206 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon</t>
+          <t>Lenovo Legion Pro 7 FIFA</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo Legion Pro 7 FIFA World Cup 26 Edition Intel Core Ultra 9 275HX | NVIDIA RTX 5070Ti 12GB (32GB RAM/1TB SSD/WQXGA OLED/240Hz/16(40.6cm)/Windows 11/Black/2.4Kg), 83F500HPIN AI Gaming Laptop</t>
         </is>
       </c>
       <c r="C294" t="inlineStr"/>
       <c r="D294" t="n">
-        <v>41999</v>
+        <v>319990</v>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-15</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon</t>
+          <t>Lenovo Smartchoice Ideapad 5 2-in-1</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo Smartchoice Ideapad 5 2-in-1 13th Gen Intel Core i5-13420H (16GB RAM/512GB SSD/Windows 11/Office Home 2024/WUXGA IPS/14 (35.5cm)/Touchscreen 2-in-1/3Mon.Game Pass/Grey/1.6kg), 83KX0059IN Laptop</t>
         </is>
       </c>
       <c r="C295" t="inlineStr"/>
       <c r="D295" t="n">
-        <v>41999</v>
+        <v>74490</v>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon</t>
+          <t>lenovo_thinkbook_14,_amd_ryzen</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo ThinkBook 14, AMD Ryzen 5 220, 16GB RAM, 1TB SSD, WUXGA IPS 14” (35.56cm), Windows 11 Home, Arctic Grey, 1.36Kg, 21V0A01SIG, Fingerprint, Backlit, 400 Nits, 1Y Warranty, Laptop</t>
         </is>
       </c>
       <c r="C296" t="inlineStr"/>
       <c r="D296" t="n">
-        <v>42999</v>
+        <v>90990</v>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon</t>
+          <t>lenovo_thinkbook_14,_amd_ryzen</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo ThinkBook 14, AMD Ryzen 5 220, 16GB RAM, 1TB SSD, WUXGA IPS 14” (35.56cm), Windows 11 Home, Arctic Grey, 1.36Kg, 21V0A01SIG, Fingerprint, Backlit, 400 Nits, 1Y Warranty, Laptop</t>
         </is>
       </c>
       <c r="C297" t="inlineStr"/>
       <c r="D297" t="n">
-        <v>42999</v>
+        <v>92990</v>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon</t>
+          <t>Lenovo ThinkBook 15 G5 AMD</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo ThinkBook 15 G5 AMD Ryzen 7 7730U 15.6" FHD Antiglare 250 Nits Thin and Light Laptop (8GB RAM/512GB SSD/Windows 11 Home/Fingerprint Reader/Backlit/Mineral Grey/1 Year Onsite/1.7 kg), 21JFA00BIN</t>
         </is>
       </c>
       <c r="C298" t="inlineStr"/>
       <c r="D298" t="n">
-        <v>42999</v>
+        <v>59999</v>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-22</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon</t>
+          <t>lenovo_thinkbook_16_amd_ryzen</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo ThinkBook 16 AMD Ryzen 5 7535HS (8GB RAM/512GB SSD/Win 11 Home/Office 2024/Backlit Keyboard/Fingerprint) 16" WUXGA IPS 300 Nits Thin &amp; Light Laptop/1Y Warranty/Aluminium Top/1.7kg, 21MWA0BRIN</t>
         </is>
       </c>
       <c r="C299" t="inlineStr"/>
       <c r="D299" t="n">
-        <v>42999</v>
+        <v>65063</v>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon</t>
+          <t>lenovo_thinkbook_16,_amd_ryzen</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo ThinkBook 16, AMD Ryzen 5 7535HS, 16GB RAM, 512GB SSD, WUXGA IPS 16", Windows 11 Home, Office 2024, 1.7kg, 21MWA0BSIN, Backlit Keyboard, Fingerprint, 300 Nits, 1Y Warranty, Aluminium Top Laptop</t>
         </is>
       </c>
       <c r="C300" t="inlineStr"/>
       <c r="D300" t="n">
-        <v>42999</v>
+        <v>84500</v>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon</t>
+          <t>Lenovo ThinkBook 16, Intel Core</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo ThinkBook 16, Intel Core Ultra 9 185H, 16GB RAM, 512GB SSD, WUXGA IPS 16” (40.64cm), Win 11 Home, Arctic Grey, 1.7Kg, 21SKA0J5IG, Fingerprint, Backlit, 300 Nits, 1Y Warranty, AI Powered Laptop</t>
         </is>
       </c>
       <c r="C301" t="inlineStr"/>
       <c r="D301" t="n">
-        <v>44999</v>
+        <v>94990</v>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-20</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon</t>
+          <t>Lenovo V14 Intel Core i3</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo V14 Intel Core i3 13th Gen 14" FHD (1920x1080) Antiglare 250 Nits Thin and Light Laptop (16GB RAM/512GB SSD/Windows 11 Home/Office Home 2024/Iron Grey/1.43 kg), 83A0A0PCIN</t>
         </is>
       </c>
       <c r="C302" t="inlineStr"/>
       <c r="D302" t="n">
-        <v>43999</v>
+        <v>70990</v>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-20</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon</t>
+          <t>Lenovo V14 Intel Core i3</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo V14 Intel Core i3 13th Gen 14" FHD (1920x1080) Antiglare 250 Nits Thin and Light Laptop (16GB RAM/512GB SSD/Windows 11 Home/Office Home 2024/Iron Grey/1.43 kg), 83A0A0PCIN</t>
         </is>
       </c>
       <c r="C303" t="inlineStr"/>
       <c r="D303" t="n">
-        <v>43999</v>
+        <v>70990</v>
       </c>
       <c r="E303" t="inlineStr">
         <is>
@@ -6788,164 +6788,164 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon</t>
+          <t>lenovo_v14_intel_core_i3</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo V14 Intel Core i3 13th Gen 14" FHD (1920x1080) Antiglare 250 Nits Thin and Light Laptop (16GB RAM/512GB SSD/Windows 11 Home/Office Home 2024/Iron Grey/1.43 kg), 83A0A0PCIN</t>
         </is>
       </c>
       <c r="C304" t="inlineStr"/>
       <c r="D304" t="n">
-        <v>43999</v>
+        <v>70990</v>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon</t>
+          <t>Lenovo V15 G4 (2024), AMD</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo V15 G4 (2024), AMD Ryzen 3 7320U Quad Core - (8GB/512GB SSD/AMD Radeon Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" FHD Display/Arctic Grey/1.57 kg/MS Office 2021</t>
         </is>
       </c>
       <c r="C305" t="inlineStr"/>
       <c r="D305" t="n">
-        <v>44999</v>
+        <v>44200</v>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-22</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon</t>
+          <t>Lenovo V15 G4 (2024), AMD</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo V15 G4 (2024), AMD Ryzen 3 7320U Quad Core - (8GB/512GB SSD/AMD Radeon Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" FHD Display/Arctic Grey/1.57 kg/MS Office 2021</t>
         </is>
       </c>
       <c r="C306" t="inlineStr"/>
       <c r="D306" t="n">
-        <v>44999</v>
+        <v>44490</v>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-05-24</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>lenovo_v15_g4_amd_athlon</t>
+          <t>Lenovo V15 G4 (2024), AMD</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo V15 G4 (2024), AMD Ryzen 3 7320U Quad Core - (8GB/512GB SSD/AMD Radeon Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" FHD Display/Arctic Grey/1.57 kg/MS Office 2021</t>
         </is>
       </c>
       <c r="C307" t="inlineStr"/>
       <c r="D307" t="n">
-        <v>44999</v>
+        <v>44490</v>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen</t>
+          <t>Lenovo V15 G4 (2024), AMD</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
+          <t>Lenovo V15 G4 (2024), AMD Ryzen 3 7320U Quad Core - (8GB/512GB SSD/AMD Radeon Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" FHD Display/Arctic Grey/1.57 kg/MS Office 2021</t>
         </is>
       </c>
       <c r="C308" t="inlineStr"/>
       <c r="D308" t="n">
-        <v>49999</v>
+        <v>44500</v>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen</t>
+          <t>Lenovo V15 G4 (2024), AMD</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
+          <t>Lenovo V15 G4 (2024), AMD Ryzen 3 7320U Quad Core - (8GB/512GB SSD/AMD Radeon Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" FHD Display/Arctic Grey/1.57 kg/MS Office 2021</t>
         </is>
       </c>
       <c r="C309" t="inlineStr"/>
       <c r="D309" t="n">
-        <v>52760</v>
+        <v>49999</v>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen</t>
+          <t>Lenovo V15 G4 (2024), AMD</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
+          <t>Lenovo V15 G4 (2024), AMD Ryzen 3 7320U Quad Core - (8GB/512GB SSD/AMD Radeon Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" FHD Display/Arctic Grey/1.57 kg/MS Office 2021</t>
         </is>
       </c>
       <c r="C310" t="inlineStr"/>
       <c r="D310" t="n">
-        <v>52300</v>
+        <v>49890</v>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen</t>
+          <t>Lenovo V15 G4 AMD Athlon</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C311" t="inlineStr"/>
       <c r="D311" t="n">
-        <v>52490</v>
+        <v>41999</v>
       </c>
       <c r="E311" t="inlineStr">
         <is>
@@ -6956,38 +6956,38 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen</t>
+          <t>Lenovo V15 G4 AMD Athlon</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C312" t="inlineStr"/>
       <c r="D312" t="n">
-        <v>52300</v>
+        <v>41999</v>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen</t>
+          <t>Lenovo V15 G4 AMD Athlon</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C313" t="inlineStr"/>
       <c r="D313" t="n">
-        <v>52890</v>
+        <v>41999</v>
       </c>
       <c r="E313" t="inlineStr">
         <is>
@@ -6998,17 +6998,17 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen</t>
+          <t>Lenovo V15 G4 AMD Athlon</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C314" t="inlineStr"/>
       <c r="D314" t="n">
-        <v>53999</v>
+        <v>42999</v>
       </c>
       <c r="E314" t="inlineStr">
         <is>
@@ -7019,17 +7019,17 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen</t>
+          <t>Lenovo V15 G4 AMD Athlon</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C315" t="inlineStr"/>
       <c r="D315" t="n">
-        <v>53999</v>
+        <v>42999</v>
       </c>
       <c r="E315" t="inlineStr">
         <is>
@@ -7040,775 +7040,1216 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen</t>
+          <t>Lenovo V15 G4 AMD Athlon</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C316" t="inlineStr"/>
       <c r="D316" t="n">
-        <v>54790</v>
+        <v>42999</v>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>lenovo_v15_g6_amd_ryzen</t>
+          <t>Lenovo V15 G4 AMD Athlon</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Lenovo V15 G6 AMD Ryzen 7 170 (Coequal 7735HS) 15.6" (39.62cm) FHD Thin and Light Business Laptop (16GB RAM DDR5/ 512GB SSD/Windows 11/ MS Office 2024/ AMD Radeon Graphics/Luna Grey/ 1.6 kg)</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C317" t="inlineStr"/>
       <c r="D317" t="n">
-        <v>64999</v>
+        <v>42999</v>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Lenovo Yoga Slim 7 (Smartchoice)</t>
+          <t>Lenovo V15 G4 AMD Athlon</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Lenovo Yoga Slim 7 (Smartchoice) Aura Edition, Intel Core Ultra 5 226V, 16GB RAM, 1TB SSD, WUXGA OLED, Copilot+ AI PC, 40 TOPS, 14"/35.5cm, Windows 11, Office 2024, Grey, 1.19Kg, 83JX005FIN, AI Laptop</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C318" t="inlineStr"/>
       <c r="D318" t="n">
-        <v>99990</v>
+        <v>42999</v>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Lenovo Yoga Slim 7 (Smartchoice)</t>
+          <t>Lenovo V15 G4 AMD Athlon</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Lenovo Yoga Slim 7 (Smartchoice) Aura Edition, Intel Core Ultra 5 226V, 16GB RAM, 1TB SSD, WUXGA OLED, Copilot+ AI PC, 40 TOPS, 14"/35.5cm, Windows 11, Office 2024, Grey, 1.19Kg, 83JX005FIN, AI Laptop</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C319" t="inlineStr"/>
       <c r="D319" t="n">
-        <v>105939</v>
+        <v>44999</v>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Lenovo Yoga Slim 7, Intel</t>
+          <t>Lenovo V15 G4 AMD Athlon</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Lenovo Yoga Slim 7, Intel Core Ultra 5 125H, 16GB RAM, 512GB SSD, AI PC, WUXGA-OLED, 14"/35.5cm, Windows 11, Microsoft 365 Basic + Office 2024, Grey, 1.39Kg, 83CV00DFIN, AI Powered Laptop</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C320" t="inlineStr"/>
       <c r="D320" t="n">
-        <v>77990</v>
+        <v>43999</v>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Lenovo Yoga Slim 7, Intel</t>
+          <t>Lenovo V15 G4 AMD Athlon</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Lenovo Yoga Slim 7, Intel Core Ultra 5 125H, 16GB RAM, 512GB SSD, AI PC, WUXGA-OLED, 14"/35.5cm, Windows 11, Microsoft 365 Basic + Office 2024, Grey, 1.39Kg, 83CV00DFIN, AI Powered Laptop</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C321" t="inlineStr"/>
       <c r="D321" t="n">
-        <v>84990</v>
+        <v>43999</v>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Lenovo {SmartChoice Chromebook, Intel Celeron</t>
+          <t>Lenovo V15 G4 AMD Athlon</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Lenovo {SmartChoice Chromebook, Intel Celeron N4500, 4GB RAM, 64GB eMMC, HD, 11.6"/29.46cm, Chrome OS, Blue, 1.21Kg, 2Wx2 Stereo Speakers, HD Camera, 82UY0014HA, Laptop</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C322" t="inlineStr"/>
       <c r="D322" t="n">
-        <v>21990</v>
+        <v>43999</v>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Lenovo {SmartChoice Chromebook, Intel Celeron</t>
+          <t>Lenovo V15 G4 AMD Athlon</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Lenovo {SmartChoice Chromebook, Intel Celeron N4500, 4GB RAM, 64GB eMMC, HD, 11.6"/29.46cm, Chrome OS, Blue, 1.21Kg, 2Wx2 Stereo Speakers, HD Camera, 82UY0014HA, Laptop</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C323" t="inlineStr"/>
       <c r="D323" t="n">
-        <v>17990</v>
+        <v>44999</v>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-06-12</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>primebook_2_max_(2026)_|</t>
+          <t>Lenovo V15 G4 AMD Athlon</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Primebook 2 Max (2026) | 8GB RAM, 256GB UFS Storage | 15.6-Inch Full HD IPS Display | 12hrs Battery | MediaTek Helio G99 | Android 15 (PrimeOS 3.0) | Backlit Keyboard | in-Built AI (Gray)</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C324" t="inlineStr"/>
       <c r="D324" t="n">
-        <v>29990</v>
+        <v>44999</v>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Samsung Galaxy Book6 (Gray, 16GB</t>
+          <t>lenovo_v15_g4_amd_athlon</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Samsung Galaxy Book6 (Gray, 16GB RAM, 1TB SSD) | Intel Core Ultra 5 (Series 3) | 16" WUXGA+ Display with Touchscreen | 24Hrs Battery Life | 120 Hz Refresh Rate | Dolby Atmos Stereo Speakers | AI PC</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C325" t="inlineStr"/>
       <c r="D325" t="n">
-        <v>146990</v>
+        <v>44999</v>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Thomson NEO 14.1 Inch IN-P14C</t>
+          <t>lenovo_v15_g4_amd_athlon</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Thomson NEO 14.1 Inch IN-P14C Intel Celeron Dual Core N4020 Processor &amp; Window 11 Home Notebook (4 GB RAM DDR4/ 128 GB SSD/Numeric Touch Pad/Thin &amp; Light Weight/Silver)</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C326" t="inlineStr"/>
       <c r="D326" t="n">
-        <v>12990</v>
+        <v>44999</v>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Thomson NEO 14.1 Inch IN-P14C</t>
+          <t>Lenovo V15 G4 AMD Ryzen</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Thomson NEO 14.1 Inch IN-P14C Intel Celeron Dual Core N4020 Processor &amp; Window 11 Home Notebook (4 GB RAM DDR4/ 128 GB SSD/Numeric Touch Pad/Thin &amp; Light Weight/Silver)</t>
+          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
         </is>
       </c>
       <c r="C327" t="inlineStr"/>
       <c r="D327" t="n">
-        <v>12990</v>
+        <v>49999</v>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-05-21</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Thomson NEO 14.1 Inch IN-P14C</t>
+          <t>Lenovo V15 G4 AMD Ryzen</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Thomson NEO 14.1 Inch IN-P14C Intel Celeron Dual Core N4020 Processor &amp; Window 11 Home Notebook (4 GB RAM DDR4/ 128 GB SSD/Numeric Touch Pad/Thin &amp; Light Weight/Silver)</t>
+          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
         </is>
       </c>
       <c r="C328" t="inlineStr"/>
       <c r="D328" t="n">
-        <v>22990</v>
+        <v>52760</v>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-24</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Thomson NEO 14.1 Inch IN-P14C</t>
+          <t>Lenovo V15 G4 AMD Ryzen</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Thomson NEO 14.1 Inch IN-P14C Intel Celeron Dual Core N4020 Processor &amp; Window 11 Home Notebook (4 GB RAM DDR4/ 128 GB SSD/Numeric Touch Pad/Thin &amp; Light Weight/Silver)</t>
+          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
         </is>
       </c>
       <c r="C329" t="inlineStr"/>
       <c r="D329" t="n">
-        <v>22990</v>
+        <v>52300</v>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>acer Aspire 3, Intel Core</t>
+          <t>Lenovo V15 G4 AMD Ryzen</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>acer Aspire 3, Intel Core Celeron N4500, 12GB LPDDR4X RAM, 512GB SSD, HD, 15.6"/39.62cm, Windows 11 Home, Pure Silver, 1.5KG, A325-45, Thin and Light Laptop</t>
+          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
         </is>
       </c>
       <c r="C330" t="inlineStr"/>
       <c r="D330" t="n">
-        <v>39890</v>
+        <v>52490</v>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>acer Aspire Lite, AMD Ryzen</t>
+          <t>Lenovo V15 G4 AMD Ryzen</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>acer Aspire Lite, AMD Ryzen 3 5300U Processor, 16 GB RAM, 512GB SSD, Full HD, 15.6"/39.62cm, Windows 11 Home, Steel Gray, 1.59KG, AL15-41, Metal Body, Premium Thin and Light Laptop</t>
+          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
         </is>
       </c>
       <c r="C331" t="inlineStr"/>
       <c r="D331" t="n">
-        <v>42990</v>
+        <v>52300</v>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-27</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD</t>
+          <t>Lenovo V15 G4 AMD Ryzen</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
+          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
         </is>
       </c>
       <c r="C332" t="inlineStr"/>
       <c r="D332" t="n">
-        <v>45990</v>
+        <v>52890</v>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-31</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD</t>
+          <t>Lenovo V15 G4 AMD Ryzen</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
+          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
         </is>
       </c>
       <c r="C333" t="inlineStr"/>
       <c r="D333" t="n">
-        <v>45990</v>
+        <v>53999</v>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD</t>
+          <t>Lenovo V15 G4 AMD Ryzen</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
+          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
         </is>
       </c>
       <c r="C334" t="inlineStr"/>
       <c r="D334" t="n">
-        <v>45990</v>
+        <v>53999</v>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-06-02</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD</t>
+          <t>Lenovo V15 G4 AMD Ryzen</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
+          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
         </is>
       </c>
       <c r="C335" t="inlineStr"/>
       <c r="D335" t="n">
-        <v>43990</v>
+        <v>54790</v>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD</t>
+          <t>lenovo_v15_g4_amd_ryzen</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
+          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
         </is>
       </c>
       <c r="C336" t="inlineStr"/>
       <c r="D336" t="n">
-        <v>43990</v>
+        <v>54740</v>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD</t>
+          <t>lenovo_v15_g6_amd_ryzen</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
+          <t>Lenovo V15 G6 AMD Ryzen 7 170 (Coequal 7735HS) 15.6" (39.62cm) FHD Thin and Light Business Laptop (16GB RAM DDR5/ 512GB SSD/Windows 11/ MS Office 2024/ AMD Radeon Graphics/Luna Grey/ 1.6 kg)</t>
         </is>
       </c>
       <c r="C337" t="inlineStr"/>
       <c r="D337" t="n">
-        <v>43990</v>
+        <v>64999</v>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD</t>
+          <t>Lenovo Yoga Slim 7 (Smartchoice)</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
+          <t>Lenovo Yoga Slim 7 (Smartchoice) Aura Edition, Intel Core Ultra 5 226V, 16GB RAM, 1TB SSD, WUXGA OLED, Copilot+ AI PC, 40 TOPS, 14"/35.5cm, Windows 11, Office 2024, Grey, 1.19Kg, 83JX005FIN, AI Laptop</t>
         </is>
       </c>
       <c r="C338" t="inlineStr"/>
       <c r="D338" t="n">
-        <v>43990</v>
+        <v>99990</v>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD</t>
+          <t>Lenovo Yoga Slim 7 (Smartchoice)</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
+          <t>Lenovo Yoga Slim 7 (Smartchoice) Aura Edition, Intel Core Ultra 5 226V, 16GB RAM, 1TB SSD, WUXGA OLED, Copilot+ AI PC, 40 TOPS, 14"/35.5cm, Windows 11, Office 2024, Grey, 1.19Kg, 83JX005FIN, AI Laptop</t>
         </is>
       </c>
       <c r="C339" t="inlineStr"/>
       <c r="D339" t="n">
-        <v>43990</v>
+        <v>105939</v>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-19</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop ModeI 7410 Laptop |</t>
+          <t>Lenovo Yoga Slim 7, Intel</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop ModeI 7410 Laptop | InteI Core i5 10th Gen | 16GB DDR4 RAM | 256GB SSD | 14" Full HD Display | Win 10 Pro | InteI UHD Graphics 620 | 3 Months Seller Warranty | A+ Condition (Refab)</t>
+          <t>Lenovo Yoga Slim 7, Intel Core Ultra 5 125H, 16GB RAM, 512GB SSD, AI PC, WUXGA-OLED, 14"/35.5cm, Windows 11, Microsoft 365 Basic + Office 2024, Grey, 1.39Kg, 83CV00DFIN, AI Powered Laptop</t>
         </is>
       </c>
       <c r="C340" t="inlineStr"/>
       <c r="D340" t="n">
-        <v>27299</v>
+        <v>77990</v>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-05-15</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5</t>
+          <t>Lenovo Yoga Slim 7, Intel</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5 11th Gen Processor |8GB DDR4 RAM |256GB SSD |14" FHD Display | Win10 | A+ Condition Laptop (Refab)</t>
+          <t>Lenovo Yoga Slim 7, Intel Core Ultra 5 125H, 16GB RAM, 512GB SSD, AI PC, WUXGA-OLED, 14"/35.5cm, Windows 11, Microsoft 365 Basic + Office 2024, Grey, 1.39Kg, 83CV00DFIN, AI Powered Laptop</t>
         </is>
       </c>
       <c r="C341" t="inlineStr"/>
       <c r="D341" t="n">
-        <v>26999</v>
+        <v>84990</v>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-19</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5</t>
+          <t>Lenovo {SmartChoice Chromebook, Intel Celeron</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5 11th Gen Processor |8GB DDR4 RAM |256GB SSD |14" FHD Display | Win10 | A+ Condition Laptop (Refab)</t>
+          <t>Lenovo {SmartChoice Chromebook, Intel Celeron N4500, 4GB RAM, 64GB eMMC, HD, 11.6"/29.46cm, Chrome OS, Blue, 1.21Kg, 2Wx2 Stereo Speakers, HD Camera, 82UY0014HA, Laptop</t>
         </is>
       </c>
       <c r="C342" t="inlineStr"/>
       <c r="D342" t="n">
-        <v>26400</v>
+        <v>21990</v>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5</t>
+          <t>Lenovo {SmartChoice Chromebook, Intel Celeron</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5 11th Gen Processor |8GB DDR4 RAM |256GB SSD |14" FHD Display | Win10 | A+ Condition Laptop (Refab)</t>
+          <t>Lenovo {SmartChoice Chromebook, Intel Celeron N4500, 4GB RAM, 64GB eMMC, HD, 11.6"/29.46cm, Chrome OS, Blue, 1.21Kg, 2Wx2 Stereo Speakers, HD Camera, 82UY0014HA, Laptop</t>
         </is>
       </c>
       <c r="C343" t="inlineStr"/>
       <c r="D343" t="n">
-        <v>28599</v>
+        <v>17990</v>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-08</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5</t>
+          <t>msi_cyborg_15,_intel_12th</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5 11th Gen Processor |8GB DDR4 RAM |256GB SSD |14" FHD Display | Win10 | A+ Condition Laptop (Refab)</t>
+          <t>MSI Cyborg 15, Intel 12th Gen. i5-12450H, 40CM FHD 144Hz Gaming Laptop (16GB/512GB NVMe SSD/Windows 11 Home/MSO 2021/NVIDIA GeForce RTX 3050, GDDR6 6GB/Translucent Black/1.9Kg) A12UDX-1468IN</t>
         </is>
       </c>
       <c r="C344" t="inlineStr"/>
       <c r="D344" t="n">
-        <v>28999</v>
+        <v>72990</v>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5</t>
+          <t>primebook_2_max_(2026)_|</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5 11th Gen Processor |8GB DDR4 RAM |256GB SSD |14" FHD Display | Win10 | A+ Condition Laptop (Refab)</t>
+          <t>Primebook 2 Max (2026) | 8GB RAM, 256GB UFS Storage | 15.6-Inch Full HD IPS Display | 12hrs Battery | MediaTek Helio G99 | Android 15 (PrimeOS 3.0) | Backlit Keyboard | in-Built AI (Gray)</t>
         </is>
       </c>
       <c r="C345" t="inlineStr"/>
       <c r="D345" t="n">
-        <v>31990</v>
+        <v>29990</v>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5</t>
+          <t>Samsung Galaxy Book6 (Gray, 16GB</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5 11th Gen Processor |8GB DDR4 RAM |256GB SSD |14" FHD Display | Win10 | A+ Condition Laptop (Refab)</t>
+          <t>Samsung Galaxy Book6 (Gray, 16GB RAM, 1TB SSD) | Intel Core Ultra 5 (Series 3) | 16" WUXGA+ Display with Touchscreen | 24Hrs Battery Life | 120 Hz Refresh Rate | Dolby Atmos Stereo Speakers | AI PC</t>
         </is>
       </c>
       <c r="C346" t="inlineStr"/>
       <c r="D346" t="n">
-        <v>35490</v>
+        <v>146990</v>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5</t>
+          <t>Thomson NEO 14.1 Inch IN-P14C</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5 11th Gen Processor |8GB DDR4 RAM |256GB SSD |14" FHD Display | Win10 | A+ Condition Laptop (Refab)</t>
+          <t>Thomson NEO 14.1 Inch IN-P14C Intel Celeron Dual Core N4020 Processor &amp; Window 11 Home Notebook (4 GB RAM DDR4/ 128 GB SSD/Numeric Touch Pad/Thin &amp; Light Weight/Silver)</t>
         </is>
       </c>
       <c r="C347" t="inlineStr"/>
       <c r="D347" t="n">
-        <v>37490</v>
+        <v>12990</v>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Model E5570 Laptop | Core</t>
+          <t>Thomson NEO 14.1 Inch IN-P14C</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Model E5570 Laptop | Core i7 6th Gen | 8GB Fast RAM | 256GB SSD | 15.6" HD Display | HD Graphics | Win 10 | WiFi| (Pre-Owned &amp; Tested)</t>
+          <t>Thomson NEO 14.1 Inch IN-P14C Intel Celeron Dual Core N4020 Processor &amp; Window 11 Home Notebook (4 GB RAM DDR4/ 128 GB SSD/Numeric Touch Pad/Thin &amp; Light Weight/Silver)</t>
         </is>
       </c>
       <c r="C348" t="inlineStr"/>
       <c r="D348" t="n">
-        <v>20599</v>
+        <v>12990</v>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>𝗛𝗣𝗣𝗿𝗼𝗯𝗼𝗼𝗸Model 430 G3 Business Laptop</t>
+          <t>Thomson NEO 14.1 Inch IN-P14C</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>𝗛𝗣𝗣𝗿𝗼𝗯𝗼𝗼𝗸Model 430 G3 Business Laptop | InteI i5 6th Gen | 8GB RAM | 256GB SSD | WiFi | Webcam | Win10 Pro (Refab)</t>
+          <t>Thomson NEO 14.1 Inch IN-P14C Intel Celeron Dual Core N4020 Processor &amp; Window 11 Home Notebook (4 GB RAM DDR4/ 128 GB SSD/Numeric Touch Pad/Thin &amp; Light Weight/Silver)</t>
         </is>
       </c>
       <c r="C349" t="inlineStr"/>
       <c r="D349" t="n">
-        <v>20299</v>
+        <v>22990</v>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-08</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>𝗛𝗣𝗣𝗿𝗼𝗯𝗼𝗼𝗸Model 430 G3 Business Laptop</t>
+          <t>Thomson NEO 14.1 Inch IN-P14C</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>𝗛𝗣𝗣𝗿𝗼𝗯𝗼𝗼𝗸Model 430 G3 Business Laptop | 𝗜𝗡𝗧𝗘𝗟i5 6th Gen | 8GB RAM | 256GB SSD | WiFi | Webcam | Win10 Pro (Refab)</t>
+          <t>Thomson NEO 14.1 Inch IN-P14C Intel Celeron Dual Core N4020 Processor &amp; Window 11 Home Notebook (4 GB RAM DDR4/ 128 GB SSD/Numeric Touch Pad/Thin &amp; Light Weight/Silver)</t>
         </is>
       </c>
       <c r="C350" t="inlineStr"/>
       <c r="D350" t="n">
-        <v>20499</v>
+        <v>22990</v>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-10</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>𝗛𝗣𝗣𝗿𝗼𝗯𝗼𝗼𝗸Model 430 G3 Business Laptop</t>
+          <t>acer Aspire 3, Intel Core</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>𝗛𝗣𝗣𝗿𝗼𝗯𝗼𝗼𝗸Model 430 G3 Business Laptop | 𝗜𝗡𝗧𝗘𝗟i5 6th Gen | 8GB RAM | 256GB SSD | WiFi | Webcam | Win10 Pro (Refab)</t>
+          <t>acer Aspire 3, Intel Core Celeron N4500, 12GB LPDDR4X RAM, 512GB SSD, HD, 15.6"/39.62cm, Windows 11 Home, Pure Silver, 1.5KG, A325-45, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C351" t="inlineStr"/>
       <c r="D351" t="n">
-        <v>19999</v>
+        <v>39890</v>
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>𝗟𝗲𝗻𝗼𝘃𝗼model_l14_laptop|_core_i5</t>
+          <t>acer Aspire Lite, AMD Ryzen</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>𝗟𝗲𝗻𝗼𝘃𝗼Model L14 Laptop| Core i5 11th Gen Processor | 16GB Fast RAM/ 256GB SSD | 14″ HD Display | A+ (Pre-Owned &amp; Tested)</t>
+          <t>acer Aspire Lite, AMD Ryzen 3 5300U Processor, 16 GB RAM, 512GB SSD, Full HD, 15.6"/39.62cm, Windows 11 Home, Steel Gray, 1.59KG, AL15-41, Metal Body, Premium Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C352" t="inlineStr"/>
       <c r="D352" t="n">
+        <v>42990</v>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>acer SmartChoice Aspire Lite, AMD</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr"/>
+      <c r="D353" t="n">
+        <v>45990</v>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>acer SmartChoice Aspire Lite, AMD</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr"/>
+      <c r="D354" t="n">
+        <v>45990</v>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>acer SmartChoice Aspire Lite, AMD</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr"/>
+      <c r="D355" t="n">
+        <v>45990</v>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>acer SmartChoice Aspire Lite, AMD</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr"/>
+      <c r="D356" t="n">
+        <v>43990</v>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>acer SmartChoice Aspire Lite, AMD</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr"/>
+      <c r="D357" t="n">
+        <v>43990</v>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>acer SmartChoice Aspire Lite, AMD</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr"/>
+      <c r="D358" t="n">
+        <v>43990</v>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>acer SmartChoice Aspire Lite, AMD</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr"/>
+      <c r="D359" t="n">
+        <v>43990</v>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>acer SmartChoice Aspire Lite, AMD</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr"/>
+      <c r="D360" t="n">
+        <v>43990</v>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop ModeI 7410 Laptop |</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop ModeI 7410 Laptop | InteI Core i5 10th Gen | 16GB DDR4 RAM | 256GB SSD | 14" Full HD Display | Win 10 Pro | InteI UHD Graphics 620 | 3 Months Seller Warranty | A+ Condition (Refab)</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr"/>
+      <c r="D361" t="n">
+        <v>27299</v>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5 11th Gen Processor |8GB DDR4 RAM |256GB SSD |14" FHD Display | Win10 | A+ Condition Laptop (Refab)</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr"/>
+      <c r="D362" t="n">
+        <v>26999</v>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5 11th Gen Processor |8GB DDR4 RAM |256GB SSD |14" FHD Display | Win10 | A+ Condition Laptop (Refab)</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr"/>
+      <c r="D363" t="n">
+        <v>26400</v>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5 11th Gen Processor |8GB DDR4 RAM |256GB SSD |14" FHD Display | Win10 | A+ Condition Laptop (Refab)</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr"/>
+      <c r="D364" t="n">
+        <v>28599</v>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5 11th Gen Processor |8GB DDR4 RAM |256GB SSD |14" FHD Display | Win10 | A+ Condition Laptop (Refab)</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr"/>
+      <c r="D365" t="n">
+        <v>28999</v>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5 11th Gen Processor |8GB DDR4 RAM |256GB SSD |14" FHD Display | Win10 | A+ Condition Laptop (Refab)</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr"/>
+      <c r="D366" t="n">
+        <v>31990</v>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5 11th Gen Processor |8GB DDR4 RAM |256GB SSD |14" FHD Display | Win10 | A+ Condition Laptop (Refab)</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr"/>
+      <c r="D367" t="n">
+        <v>35490</v>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5 11th Gen Processor |8GB DDR4 RAM |256GB SSD |14" FHD Display | Win10 | A+ Condition Laptop (Refab)</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr"/>
+      <c r="D368" t="n">
+        <v>37490</v>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Model E5570 Laptop | Core</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Model E5570 Laptop | Core i7 6th Gen | 8GB Fast RAM | 256GB SSD | 15.6" HD Display | HD Graphics | Win 10 | WiFi| (Pre-Owned &amp; Tested)</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr"/>
+      <c r="D369" t="n">
+        <v>20599</v>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>𝗛𝗣𝗣𝗿𝗼𝗯𝗼𝗼𝗸Model 430 G3 Business Laptop</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>𝗛𝗣𝗣𝗿𝗼𝗯𝗼𝗼𝗸Model 430 G3 Business Laptop | InteI i5 6th Gen | 8GB RAM | 256GB SSD | WiFi | Webcam | Win10 Pro (Refab)</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr"/>
+      <c r="D370" t="n">
+        <v>20299</v>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>𝗛𝗣𝗣𝗿𝗼𝗯𝗼𝗼𝗸Model 430 G3 Business Laptop</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>𝗛𝗣𝗣𝗿𝗼𝗯𝗼𝗼𝗸Model 430 G3 Business Laptop | 𝗜𝗡𝗧𝗘𝗟i5 6th Gen | 8GB RAM | 256GB SSD | WiFi | Webcam | Win10 Pro (Refab)</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr"/>
+      <c r="D371" t="n">
+        <v>20499</v>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>𝗛𝗣𝗣𝗿𝗼𝗯𝗼𝗼𝗸Model 430 G3 Business Laptop</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>𝗛𝗣𝗣𝗿𝗼𝗯𝗼𝗼𝗸Model 430 G3 Business Laptop | 𝗜𝗡𝗧𝗘𝗟i5 6th Gen | 8GB RAM | 256GB SSD | WiFi | Webcam | Win10 Pro (Refab)</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr"/>
+      <c r="D372" t="n">
+        <v>19999</v>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>𝗟𝗲𝗻𝗼𝘃𝗼model_l14_laptop|_core_i5</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>𝗟𝗲𝗻𝗼𝘃𝗼Model L14 Laptop| Core i5 11th Gen Processor | 16GB Fast RAM/ 256GB SSD | 14″ HD Display | A+ (Pre-Owned &amp; Tested)</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr"/>
+      <c r="D373" t="n">
         <v>31599</v>
       </c>
-      <c r="E352" t="inlineStr">
+      <c r="E373" t="inlineStr">
         <is>
           <t>2026-07-21</t>
         </is>

--- a/amazon_products.xlsx
+++ b/amazon_products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E373"/>
+  <dimension ref="A1:E390"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -761,21 +761,21 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ASUS Vivobook 15, 13th Gen,</t>
+          <t>asus_tuf_a15,_amd_ryzen</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ASUS Vivobook 15, 13th Gen, Intel Core i3-1315U, 16GB RAM, 512GB SSD, FHD, Anti-Glare, 15.6", 39.6 cm, Windows 11 Home, M365 Basic(1yr)* Office24, Quiet Blue, 1.70 kg, X1504VA-BQ342WS, Laptop</t>
+          <t>ASUS TUF A15, AMD Ryzen 7 170, RTX 3050-4GB, 16GB RAM (Upgradeable), 512GB SSD, FHD, 15.6"(39.6 cm),Windows 11 Home,Graphite Black, 2.3 Kg, FA506NCQ-HN006W, Gaming Laptop</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>46900</v>
+        <v>80990</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
@@ -792,11 +792,11 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>44990</v>
+        <v>46900</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -813,11 +813,11 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>51490</v>
+        <v>44990</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-17</t>
         </is>
       </c>
     </row>
@@ -834,11 +834,11 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>53990</v>
+        <v>51490</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
     </row>
@@ -855,11 +855,11 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>46990</v>
+        <v>53990</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
     </row>
@@ -876,18 +876,18 @@
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="n">
-        <v>52990</v>
+        <v>46990</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>asus_vivobook_15,_13th_gen,</t>
+          <t>ASUS Vivobook 15, 13th Gen,</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -897,32 +897,32 @@
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="n">
-        <v>54990</v>
+        <v>52990</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ASUS Vivobook 15, Intel Core</t>
+          <t>asus_vivobook_15,_13th_gen,</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ASUS Vivobook 15, Intel Core i3 13th Gen 1315U, 12GB RAM, 512GB SSD, FHD 15.6", Windows 11, Office Home 2024, Cool Silver, 1.7Kg, X1504VA-BQ331WS, Intel UHD iGPU, Thin &amp; Light, 42Whrs Laptop</t>
+          <t>ASUS Vivobook 15, 13th Gen, Intel Core i3-1315U, 16GB RAM, 512GB SSD, FHD, Anti-Glare, 15.6", 39.6 cm, Windows 11 Home, M365 Basic(1yr)* Office24, Quiet Blue, 1.70 kg, X1504VA-BQ342WS, Laptop</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="n">
-        <v>45990</v>
+        <v>54990</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
     </row>
@@ -955,16 +955,16 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ASUS Vivobook 15, Intel Core i3 13th Gen 1315U, 12GB RAM, 512GB SSD, FHD 15.6", Windows 11, Office Home 2024, Quiet Blue, 1.7Kg, X1504VA-BQ332WS, Intel UHD iGPU, M365 Basic (1Year)*, 42Whrs Laptop</t>
+          <t>ASUS Vivobook 15, Intel Core i3 13th Gen 1315U, 12GB RAM, 512GB SSD, FHD 15.6", Windows 11, Office Home 2024, Cool Silver, 1.7Kg, X1504VA-BQ331WS, Intel UHD iGPU, Thin &amp; Light, 42Whrs Laptop</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="n">
-        <v>43990</v>
+        <v>45990</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-15</t>
         </is>
       </c>
     </row>
@@ -981,32 +981,32 @@
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="n">
-        <v>50990</v>
+        <v>43990</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-17</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ASUS Vivobook 15, Smartchoice, AMD</t>
+          <t>ASUS Vivobook 15, Intel Core</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ASUS Vivobook 15, Smartchoice, AMD Ryzen 7 5825U, 16GB RAM, 512GB SSD, FHD 15.6", Windows 11, Office Home 2024, Quiet Blue, 1.7Kg, M1502YA-BQ703WS, AMD Radeon iGPU, M365 Basic (1Year)*, 42Whr Laptop</t>
+          <t>ASUS Vivobook 15, Intel Core i3 13th Gen 1315U, 12GB RAM, 512GB SSD, FHD 15.6", Windows 11, Office Home 2024, Quiet Blue, 1.7Kg, X1504VA-BQ332WS, Intel UHD iGPU, M365 Basic (1Year)*, 42Whrs Laptop</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="n">
-        <v>49990</v>
+        <v>50990</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-19</t>
         </is>
       </c>
     </row>
@@ -1023,11 +1023,11 @@
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="n">
-        <v>53990</v>
+        <v>49990</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
@@ -1044,11 +1044,11 @@
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="n">
-        <v>54990</v>
+        <v>53990</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-17</t>
         </is>
       </c>
     </row>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-24</t>
         </is>
       </c>
     </row>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-28</t>
         </is>
       </c>
     </row>
@@ -1128,11 +1128,11 @@
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="n">
-        <v>49990</v>
+        <v>54990</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-31</t>
         </is>
       </c>
     </row>
@@ -1149,11 +1149,11 @@
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="n">
-        <v>54990</v>
+        <v>49990</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -1174,28 +1174,28 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ASUS Vivobook 15, Smartchoice,Intel Core</t>
+          <t>ASUS Vivobook 15, Smartchoice, AMD</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ASUS Vivobook 15, Smartchoice,Intel Core i3 13th Gen 1315U, 12GB RAM, 512GB SSD, FHD 15.6", Win 11, Office 2024, Quiet Blue, 1.7Kg, X1504VA-BQ332WS, Intel UHD iGPU, M365 Basic (1Year)*, 42Whrs Laptop</t>
+          <t>ASUS Vivobook 15, Smartchoice, AMD Ryzen 7 5825U, 16GB RAM, 512GB SSD, FHD 15.6", Windows 11, Office Home 2024, Quiet Blue, 1.7Kg, M1502YA-BQ703WS, AMD Radeon iGPU, M365 Basic (1Year)*, 42Whr Laptop</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="n">
-        <v>50990</v>
+        <v>54990</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-21</t>
         </is>
       </c>
     </row>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-24</t>
         </is>
       </c>
     </row>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
     </row>
@@ -1291,16 +1291,16 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ASUS Vivobook 15, Smartchoice,Intel Core i3 13th Gen 1315U, 16GB RAM, 512GB SSD, FHD 15.6", Touchscreen, Win11, Office 24, M365 Basic (1Y), Quiet Blue, 1.7Kg, X1504VA-E83959WS, Intel UHD iGPU, Laptop</t>
+          <t>ASUS Vivobook 15, Smartchoice,Intel Core i3 13th Gen 1315U, 12GB RAM, 512GB SSD, FHD 15.6", Win 11, Office 2024, Quiet Blue, 1.7Kg, X1504VA-BQ332WS, Intel UHD iGPU, M365 Basic (1Year)*, 42Whrs Laptop</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="n">
-        <v>51990</v>
+        <v>50990</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-28</t>
         </is>
       </c>
     </row>
@@ -1321,7 +1321,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-22</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -1380,11 +1380,11 @@
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="n">
-        <v>54990</v>
+        <v>51990</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-02</t>
         </is>
       </c>
     </row>
@@ -1396,16 +1396,16 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ASUS Vivobook 15, Smartchoice,Intel Core i5 13th Gen 13420H,16GB RAM, 512GB SSD, FHD 15.6",Windows 11, Office Home 2024, Quiet Blue, 1.70 kg, X1502VA-BQ836WS,Intel UHD iGPU, M365 Basic (1Year)* Laptop</t>
+          <t>ASUS Vivobook 15, Smartchoice,Intel Core i3 13th Gen 1315U, 16GB RAM, 512GB SSD, FHD 15.6", Touchscreen, Win11, Office 24, M365 Basic (1Y), Quiet Blue, 1.7Kg, X1504VA-E83959WS, Intel UHD iGPU, Laptop</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="n">
-        <v>59990</v>
+        <v>54990</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-05-31</t>
         </is>
       </c>
     </row>
@@ -1443,11 +1443,11 @@
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="n">
-        <v>60990</v>
+        <v>59990</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
@@ -1468,7 +1468,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
@@ -1489,7 +1489,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
@@ -1510,66 +1510,66 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ASUS Vivobook 16, 13th Gen,</t>
+          <t>ASUS Vivobook 15, Smartchoice,Intel Core</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ASUS Vivobook 16, 13th Gen, Intel Core i5-13420H,16GB RAM,512GB SSD,FHD (1920 x 1200) OLED,Win 11,M365 Basic (1Year)*,Backlit Keyboard,Office 2024,Silver,1.88 kg,X1605VA-SH1952WS, Thin &amp; Light Laptop</t>
+          <t>ASUS Vivobook 15, Smartchoice,Intel Core i5 13th Gen 13420H,16GB RAM, 512GB SSD, FHD 15.6",Windows 11, Office Home 2024, Quiet Blue, 1.70 kg, X1502VA-BQ836WS,Intel UHD iGPU, M365 Basic (1Year)* Laptop</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="n">
-        <v>61990</v>
+        <v>60990</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-06-12</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ASUS Vivobook Go 14, AMD</t>
+          <t>ASUS Vivobook 16, 13th Gen,</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ASUS Vivobook Go 14, AMD Ryzen 5 7520U, 16GB RAM, 512GB SSD, FHD, 14", 60Hz,42WHrs, Windows 11, M365 Basic (1Year)*,Office Home 2024, Mixed Black, 1.38 kg, E1404FA-EB774WS, Thin &amp; Light Laptop</t>
+          <t>ASUS Vivobook 16, 13th Gen, Intel Core i5-13420H,16GB RAM,512GB SSD,FHD (1920 x 1200) OLED,Win 11,M365 Basic (1Year)*,Backlit Keyboard,Office 2024,Silver,1.88 kg,X1605VA-SH1952WS, Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="n">
-        <v>52990</v>
+        <v>61990</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ASUS Vivobook S14,Smartchoice,AMD Ryzen AI</t>
+          <t>ASUS Vivobook Go 14, AMD</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ASUS Vivobook S14,Smartchoice,AMD Ryzen AI 7 350,16GB RAM,1TB SSD,OLED,14",Windows 11, Office24,M365 Basic (1Yr)*, Matte Gray,1.4Kg, M3407KA-SF049WS,50 Tops,Metallic Design,Next-Gen AI Laptop,Copilot+</t>
+          <t>ASUS Vivobook Go 14, AMD Ryzen 5 7520U, 16GB RAM, 512GB SSD, FHD, 14", 60Hz,42WHrs, Windows 11, M365 Basic (1Year)*,Office Home 2024, Mixed Black, 1.38 kg, E1404FA-EB774WS, Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="n">
-        <v>88990</v>
+        <v>52990</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -1611,53 +1611,53 @@
       </c>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="n">
-        <v>83990</v>
+        <v>88990</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-04-16</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>asus_vivobook_s16,14th_gen,_intel</t>
+          <t>ASUS Vivobook S14,Smartchoice,AMD Ryzen AI</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ASUS Vivobook S16,14th Gen, Intel Core 5-210H,Metallic Design Laptop(Intel UHD iGPU/16GB RAM/512GB SSD/FHD+/16"/144Hz/Windows 11/M365 Basic(1Year)*/Office Home 2024/Silver/1.7Kg) S3607VA-RP114WS</t>
+          <t>ASUS Vivobook S14,Smartchoice,AMD Ryzen AI 7 350,16GB RAM,1TB SSD,OLED,14",Windows 11, Office24,M365 Basic (1Yr)*, Matte Gray,1.4Kg, M3407KA-SF049WS,50 Tops,Metallic Design,Next-Gen AI Laptop,Copilot+</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="n">
-        <v>68990</v>
+        <v>83990</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-21</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ASUS Vivobook S16,Intel Core Ultra</t>
+          <t>asus_vivobook_s16,14th_gen,_intel</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ASUS Vivobook S16,Intel Core Ultra 5 225H,AI PC(Intel Arc iGPU/16GB RAM/512GB SSD/FHD/16/60Hz/Backlit Keyboard/70Whr/Windows 11/M365 Basic(1Year)*/Office Home 2024/Cool Silver/1.7 Kg) S3607CA-SH071WS</t>
+          <t>ASUS Vivobook S16,14th Gen, Intel Core 5-210H,Metallic Design Laptop(Intel UHD iGPU/16GB RAM/512GB SSD/FHD+/16"/144Hz/Windows 11/M365 Basic(1Year)*/Office Home 2024/Silver/1.7Kg) S3607VA-RP114WS</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="n">
-        <v>81990</v>
+        <v>68990</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -1674,32 +1674,32 @@
       </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="n">
-        <v>79990</v>
+        <v>81990</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ASUS Zenbook 14 (2026),Smartchoice,Intel Core</t>
+          <t>ASUS Vivobook S16,Intel Core Ultra</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>ASUS Zenbook 14 (2026),Smartchoice,Intel Core Ultra 7 255H,32GB RAM,1TB SSD,OLED,Touchscreen,14"(35.5 cm),Win 11,M365 Basic(1Y)* Office 24,Ponder Blue,1.28 Kg,UX3405CA-QL1015WS,Thin &amp; Light Laptop</t>
+          <t>ASUS Vivobook S16,Intel Core Ultra 5 225H,AI PC(Intel Arc iGPU/16GB RAM/512GB SSD/FHD/16/60Hz/Backlit Keyboard/70Whr/Windows 11/M365 Basic(1Year)*/Office Home 2024/Cool Silver/1.7 Kg) S3607CA-SH071WS</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="n">
-        <v>119990</v>
+        <v>79990</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
@@ -1720,7 +1720,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-22</t>
         </is>
       </c>
     </row>
@@ -1732,58 +1732,58 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ASUS Zenbook 14 (2026),Smartchoice,Intel Core Ultra 9 285H,32GB RAM,1TB SSD,OLED,Touchscreen,14"(35.5 cm),Win 11,M365 Basic(1Y)* Office 24,Foggy Silver,1.28 Kg,UX3405CA-QL1113WS,Thin &amp; Light Laptop</t>
+          <t>ASUS Zenbook 14 (2026),Smartchoice,Intel Core Ultra 7 255H,32GB RAM,1TB SSD,OLED,Touchscreen,14"(35.5 cm),Win 11,M365 Basic(1Y)* Office 24,Ponder Blue,1.28 Kg,UX3405CA-QL1015WS,Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="n">
-        <v>124990</v>
+        <v>119990</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ASUS Zenbook 14, Intel Core</t>
+          <t>ASUS Zenbook 14 (2026),Smartchoice,Intel Core</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>ASUS Zenbook 14, Intel Core Ultra 5 Series 2, 16GB RAM, 1TB SSD, 3K OLED 14", Touchscreen, Win 11, Office Home 2024, Ponder Blue, 1.28kg, UX3405CA-PZ162WS, Intel Arc iGPU, M365 Basic (1Year)* Laptop</t>
+          <t>ASUS Zenbook 14 (2026),Smartchoice,Intel Core Ultra 9 285H,32GB RAM,1TB SSD,OLED,Touchscreen,14"(35.5 cm),Win 11,M365 Basic(1Y)* Office 24,Foggy Silver,1.28 Kg,UX3405CA-QL1113WS,Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="n">
-        <v>106990</v>
+        <v>124990</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ASUS Zenbook 14, Smartchoice, Intel</t>
+          <t>ASUS Zenbook 14, Intel Core</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ASUS Zenbook 14, Smartchoice, Intel Core Ultra 5 Series 2,16GB RAM,1TB SSD,3K OLED 14", Touchscreen, Win 11, Office Home 2024,Blue, 1.28kg, UX3405CA-PZ162WS, Intel Arc iGPU, M365 Basic (1Year)* Laptop</t>
+          <t>ASUS Zenbook 14, Intel Core Ultra 5 Series 2, 16GB RAM, 1TB SSD, 3K OLED 14", Touchscreen, Win 11, Office Home 2024, Ponder Blue, 1.28kg, UX3405CA-PZ162WS, Intel Arc iGPU, M365 Basic (1Year)* Laptop</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="n">
-        <v>108990</v>
+        <v>106990</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-14</t>
         </is>
       </c>
     </row>
@@ -1795,37 +1795,37 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>ASUS Zenbook 14, Smartchoice, Intel Core Ultra 5 Series 2,16GB RAM,1TB SSD,3K OLED 14", Touchscreen, Win 11, Office Home 2024,Blue, 1.28kg, UX3405CA-PZ162WS, Intel iGPU, M365 Basic (1Year)* Laptop</t>
+          <t>ASUS Zenbook 14, Smartchoice, Intel Core Ultra 5 Series 2,16GB RAM,1TB SSD,3K OLED 14", Touchscreen, Win 11, Office Home 2024,Blue, 1.28kg, UX3405CA-PZ162WS, Intel Arc iGPU, M365 Basic (1Year)* Laptop</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="n">
-        <v>114990</v>
+        <v>108990</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Acer Aspire 3 Laptop Intel</t>
+          <t>ASUS Zenbook 14, Smartchoice, Intel</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Acer Aspire 3 Laptop Intel Core Celeron N4500 Processor Laptop (8 GB LPDDR4X SDRAM/256 GB SSD/Win11 Home/38 WHR/HD Webcam) A325-45 with 39.63 cm (15.6") HD Display, Pure Silver, 1.5 KG</t>
+          <t>ASUS Zenbook 14, Smartchoice, Intel Core Ultra 5 Series 2,16GB RAM,1TB SSD,3K OLED 14", Touchscreen, Win 11, Office Home 2024,Blue, 1.28kg, UX3405CA-PZ162WS, Intel iGPU, M365 Basic (1Year)* Laptop</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="n">
-        <v>36990</v>
+        <v>114990</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -1846,28 +1846,28 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Acer Aspire Lite 12th Gen,</t>
+          <t>Acer Aspire 3 Laptop Intel</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Acer Aspire Lite 12th Gen, Intel Core i5-12450H, Office 2024 + M365 Basic, 12GB RAM/512GB SSD, 39.62cm 15.6" FHD IPS Display, Win 11 Home, Pure Silver, 1.7KG,AL15-52H, Backlit KB, Thin &amp; Light Laptop</t>
+          <t>Acer Aspire 3 Laptop Intel Core Celeron N4500 Processor Laptop (8 GB LPDDR4X SDRAM/256 GB SSD/Win11 Home/38 WHR/HD Webcam) A325-45 with 39.63 cm (15.6") HD Display, Pure Silver, 1.5 KG</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="n">
-        <v>52990</v>
+        <v>36990</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
@@ -1884,11 +1884,11 @@
       </c>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="n">
-        <v>47990</v>
+        <v>52990</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-08</t>
         </is>
       </c>
     </row>
@@ -1905,11 +1905,11 @@
       </c>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="n">
-        <v>53990</v>
+        <v>47990</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-17</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
     </row>
@@ -1972,7 +1972,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
     </row>
@@ -1989,11 +1989,11 @@
       </c>
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="n">
-        <v>49990</v>
+        <v>53990</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-22</t>
         </is>
       </c>
     </row>
@@ -2010,11 +2010,11 @@
       </c>
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="n">
-        <v>53990</v>
+        <v>49990</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-27</t>
         </is>
       </c>
     </row>
@@ -2031,32 +2031,32 @@
       </c>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="n">
-        <v>50990</v>
+        <v>53990</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Acer Aspire One, Intel Core</t>
+          <t>Acer Aspire Lite 12th Gen,</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Acer Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X RAM/ 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
+          <t>Acer Aspire Lite 12th Gen, Intel Core i5-12450H, Office 2024 + M365 Basic, 12GB RAM/512GB SSD, 39.62cm 15.6" FHD IPS Display, Win 11 Home, Pure Silver, 1.7KG,AL15-52H, Backlit KB, Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="n">
-        <v>34990</v>
+        <v>50990</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-08</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
@@ -2115,11 +2115,11 @@
       </c>
       <c r="C81" t="inlineStr"/>
       <c r="D81" t="n">
-        <v>33990</v>
+        <v>34990</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-10</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-15</t>
         </is>
       </c>
     </row>
@@ -2157,11 +2157,11 @@
       </c>
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="n">
-        <v>35990</v>
+        <v>33990</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-17</t>
         </is>
       </c>
     </row>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
     </row>
@@ -2203,7 +2203,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
     </row>
@@ -2236,37 +2236,37 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Acer Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X RAM/ 512GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
+          <t>Acer Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X RAM/ 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="n">
-        <v>38990</v>
+        <v>35990</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-22</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>acer_one_14_laptop_z14-55m</t>
+          <t>Acer Aspire One, Intel Core</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Acer One 14 Laptop Z14-55M | 14" HD Display | AMD Ryzen 3 7320U | 8GB LPDDR5 RAM | 256GB NVMe SSD | Windows 11 | Thin &amp; Light Design | AMD Radeon Graphics | Silver</t>
+          <t>Acer Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X RAM/ 512GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="n">
-        <v>38750</v>
+        <v>38990</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-14</t>
         </is>
       </c>
     </row>
@@ -2283,95 +2283,95 @@
       </c>
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="n">
-        <v>38500</v>
+        <v>38750</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Acer Smartchoice Aspire One, AMD</t>
+          <t>acer_one_14_laptop_z14-55m</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Acer Smartchoice Aspire One, AMD Ryzen 3-7320U, 8GB LPDDR5 RAM/ 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.48KG, A114-43, Thin and Light Laptop</t>
+          <t>Acer One 14 Laptop Z14-55M | 14" HD Display | AMD Ryzen 3 7320U | 8GB LPDDR5 RAM | 256GB NVMe SSD | Windows 11 | Thin &amp; Light Design | AMD Radeon Graphics | Silver</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="n">
-        <v>39990</v>
+        <v>38500</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Acer Smartchoice Aspire One, AMD</t>
+          <t>acer_one_14_laptop_z14-55m</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Acer Smartchoice Aspire One, AMD Ryzen 3-7320U, 8GB LPDDR5 RAM/ 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.48KG, A114-43, Thin and Light Laptop</t>
+          <t>Acer One 14 Laptop Z14-55M | 14" HD Display | AMD Ryzen 3 7320U | 8GB LPDDR5 RAM | 256GB NVMe SSD | Windows 11 | Thin &amp; Light Design | AMD Radeon Graphics | Silver</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
       <c r="D91" t="n">
-        <v>39990</v>
+        <v>38500</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Acer Smartchoice Aspire One, Intel</t>
+          <t>Acer Smartchoice Aspire One, AMD</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Acer Smartchoice Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X / 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
+          <t>Acer Smartchoice Aspire One, AMD Ryzen 3-7320U, 8GB LPDDR5 RAM/ 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.48KG, A114-43, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="n">
-        <v>32990</v>
+        <v>39990</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Acer Smartchoice Aspire One, Intel</t>
+          <t>Acer Smartchoice Aspire One, AMD</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Acer Smartchoice Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X / 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
+          <t>Acer Smartchoice Aspire One, AMD Ryzen 3-7320U, 8GB LPDDR5 RAM/ 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.48KG, A114-43, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
       <c r="D93" t="n">
-        <v>32990</v>
+        <v>39990</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-06-12</t>
         </is>
       </c>
     </row>
@@ -2392,7 +2392,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>
@@ -2413,7 +2413,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-24</t>
         </is>
       </c>
     </row>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -2451,11 +2451,11 @@
       </c>
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="n">
-        <v>35990</v>
+        <v>32990</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-27</t>
         </is>
       </c>
     </row>
@@ -2472,11 +2472,11 @@
       </c>
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="n">
-        <v>35990</v>
+        <v>32990</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-28</t>
         </is>
       </c>
     </row>
@@ -2497,7 +2497,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
@@ -2509,75 +2509,75 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Acer Smartchoice Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X / 512GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
+          <t>Acer Smartchoice Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X / 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="n">
-        <v>34990</v>
+        <v>35990</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-06-12</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>acer_smartchoice_aspire_one,_intel</t>
+          <t>Acer Smartchoice Aspire One, Intel</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Acer Smartchoice Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X / 512GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
+          <t>Acer Smartchoice Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X / 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
       <c r="D101" t="n">
-        <v>37990</v>
+        <v>35990</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Acer Swift Go 14 AI</t>
+          <t>Acer Smartchoice Aspire One, Intel</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Acer Swift Go 14 AI PC, Qualcomm SnapdragonX Plus X1P-42-100,Office 2024 + M365 Basic,(16GB LPDDR5X/ 512GB SSD/14.5-inch WUXGA//Qualcomm Adreno/1440p IR Camera with Shutter/Win11) 1.32 kg, Steel Grey.</t>
+          <t>Acer Smartchoice Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X / 512GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="n">
-        <v>79990</v>
+        <v>34990</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-07-12</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>acer_travellite_thin_laptop_amd</t>
+          <t>acer_smartchoice_aspire_one,_intel</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Acer TravelLite Thin Laptop AMD Ryzen 5 7430U (6-Core) 16GB RAM, 512GB SSD 14" Full HD Anti-Glare Display Privacy Shutter Windows 11 MS Office Metal Body 1.34Kg Black 30M Warranty</t>
+          <t>Acer Smartchoice Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X / 512GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="n">
-        <v>53450</v>
+        <v>37990</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -2588,63 +2588,63 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Neo 13″</t>
+          <t>acer_smartchoice_aspire_one,_intel</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Citrus</t>
+          <t>Acer Smartchoice Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X / 512GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="n">
-        <v>65000</v>
+        <v>39990</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Neo 13″</t>
+          <t>Acer Swift Go 14 AI</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Indigo</t>
+          <t>Acer Swift Go 14 AI PC, Qualcomm SnapdragonX Plus X1P-42-100,Office 2024 + M365 Basic,(16GB LPDDR5X/ 512GB SSD/14.5-inch WUXGA//Qualcomm Adreno/1440p IR Camera with Shutter/Win11) 1.32 kg, Steel Grey.</t>
         </is>
       </c>
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="n">
-        <v>67900</v>
+        <v>79990</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Neo 13″</t>
+          <t>acer_travellite_thin_laptop_amd</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Indigo</t>
+          <t>Acer TravelLite Thin Laptop AMD Ryzen 5 7430U (6-Core) 16GB RAM, 512GB SSD 14" Full HD Anti-Glare Display Privacy Shutter Windows 11 MS Office Metal Body 1.34Kg Black 30M Warranty</t>
         </is>
       </c>
       <c r="C106" t="inlineStr"/>
       <c r="D106" t="n">
-        <v>65000</v>
+        <v>53450</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -2656,16 +2656,16 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Indigo</t>
+          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Citrus</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
       <c r="D107" t="n">
-        <v>65700</v>
+        <v>65000</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
@@ -2682,11 +2682,11 @@
       </c>
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="n">
-        <v>65000</v>
+        <v>67900</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -2707,7 +2707,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
@@ -2724,11 +2724,11 @@
       </c>
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="n">
-        <v>65000</v>
+        <v>65700</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-28</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Silver</t>
+          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Indigo</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
@@ -2749,7 +2749,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -2761,7 +2761,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Silver</t>
+          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Indigo</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
@@ -2782,16 +2782,16 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Silver</t>
+          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Indigo</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
       <c r="D113" t="n">
-        <v>65700</v>
+        <v>65000</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -2808,11 +2808,11 @@
       </c>
       <c r="C114" t="inlineStr"/>
       <c r="D114" t="n">
-        <v>67900</v>
+        <v>65000</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-24</t>
         </is>
       </c>
     </row>
@@ -2833,7 +2833,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -2850,11 +2850,11 @@
       </c>
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="n">
-        <v>64990</v>
+        <v>65700</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-27</t>
         </is>
       </c>
     </row>
@@ -2871,11 +2871,11 @@
       </c>
       <c r="C117" t="inlineStr"/>
       <c r="D117" t="n">
-        <v>63990</v>
+        <v>67900</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-05-31</t>
         </is>
       </c>
     </row>
@@ -2892,11 +2892,11 @@
       </c>
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="n">
-        <v>63990</v>
+        <v>65000</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-02</t>
         </is>
       </c>
     </row>
@@ -2913,74 +2913,74 @@
       </c>
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="n">
-        <v>63990</v>
+        <v>64990</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Pro Laptop</t>
+          <t>Apple 2026 MacBook Neo 13″</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Pro Laptop with M5 Max chip with 18‑core CPU and 40‑core GPU: Built for AI, 41.05 cm (16.2″) Liquid Retina XDR Display, 48GB Unified Memory, 2TB SSD Storage; Space Black</t>
+          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Silver</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
       <c r="D120" t="n">
-        <v>499900</v>
+        <v>63990</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Pro Laptop</t>
+          <t>Apple 2026 MacBook Neo 13″</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Pro Laptop with M5 Max chip with 18‑core CPU and 40‑core GPU: Built for AI, 41.05 cm (16.2″) Liquid Retina XDR Display, 48GB Unified Memory, 2TB SSD Storage; Space Black</t>
+          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Silver</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
       <c r="D121" t="n">
-        <v>499900</v>
+        <v>63990</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Pro Laptop</t>
+          <t>Apple 2026 MacBook Neo 13″</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Pro Laptop with M5 Max chip with 18‑core CPU and 40‑core GPU: Built for AI, 41.05 cm (16.2″) Liquid Retina XDR Display, 48GB Unified Memory, 2TB SSD Storage; Space Black</t>
+          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Silver</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
       <c r="D122" t="n">
-        <v>499900</v>
+        <v>63990</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-12</t>
         </is>
       </c>
     </row>
@@ -2992,16 +2992,16 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Pro Laptop with M5 Pro chip with 15‑core CPU and 16‑core GPU: Built for AI, 35.97 cm (14.2″) Liquid Retina XDR Display, 24GB Unified Memory, 1TB SSD Storage; Silver</t>
+          <t>Apple 2026 MacBook Pro Laptop with M5 Max chip with 18‑core CPU and 40‑core GPU: Built for AI, 41.05 cm (16.2″) Liquid Retina XDR Display, 48GB Unified Memory, 2TB SSD Storage; Space Black</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
       <c r="D123" t="n">
-        <v>234900</v>
+        <v>499900</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
@@ -3013,79 +3013,79 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Pro Laptop with M5 Pro chip with 15‑core CPU and 16‑core GPU: Built for AI, 35.97 cm (14.2″) Liquid Retina XDR Display, 24GB Unified Memory, 1TB SSD Storage; Silver</t>
+          <t>Apple 2026 MacBook Pro Laptop with M5 Max chip with 18‑core CPU and 40‑core GPU: Built for AI, 41.05 cm (16.2″) Liquid Retina XDR Display, 48GB Unified Memory, 2TB SSD Storage; Space Black</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="n">
-        <v>227400</v>
+        <v>499900</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-05-28</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>BrowseBook 14.1" FHD IPS Laptop</t>
+          <t>Apple 2026 MacBook Pro Laptop</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>BrowseBook 14.1" FHD IPS Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB RAM | 128GB SSD | Windows 11 | 38Wh | 1.3kg | Grey</t>
+          <t>Apple 2026 MacBook Pro Laptop with M5 Max chip with 18‑core CPU and 40‑core GPU: Built for AI, 41.05 cm (16.2″) Liquid Retina XDR Display, 48GB Unified Memory, 2TB SSD Storage; Space Black</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
       <c r="D125" t="n">
-        <v>13990</v>
+        <v>499900</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-06-02</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>BrowseBook 14.1" FHD IPS Laptop</t>
+          <t>Apple 2026 MacBook Pro Laptop</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>BrowseBook 14.1" FHD IPS Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB RAM | 128GB SSD | Windows 11 | 38Wh | 1.3kg | Grey</t>
+          <t>Apple 2026 MacBook Pro Laptop with M5 Pro chip with 15‑core CPU and 16‑core GPU: Built for AI, 35.97 cm (14.2″) Liquid Retina XDR Display, 24GB Unified Memory, 1TB SSD Storage; Silver</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
       <c r="D126" t="n">
-        <v>13990</v>
+        <v>234900</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-06-12</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>BrowseBook 14.1" FHD IPS Laptop</t>
+          <t>Apple 2026 MacBook Pro Laptop</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>BrowseBook 14.1" FHD IPS Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB RAM | 128GB SSD | Windows 11 | 38Wh | 1.3kg | Grey</t>
+          <t>Apple 2026 MacBook Pro Laptop with M5 Pro chip with 15‑core CPU and 16‑core GPU: Built for AI, 35.97 cm (14.2″) Liquid Retina XDR Display, 24GB Unified Memory, 1TB SSD Storage; Silver</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
       <c r="D127" t="n">
-        <v>13990</v>
+        <v>227400</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
@@ -3102,11 +3102,11 @@
       </c>
       <c r="C128" t="inlineStr"/>
       <c r="D128" t="n">
-        <v>20990</v>
+        <v>13990</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -3118,79 +3118,79 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>BrowseBook 14.1" FHD IPS Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 8GB RAM | 256GB SSD | Windows 11 | 38Wh | 1.3kg | Grey</t>
+          <t>BrowseBook 14.1" FHD IPS Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB RAM | 128GB SSD | Windows 11 | 38Wh | 1.3kg | Grey</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
       <c r="D129" t="n">
-        <v>18990</v>
+        <v>13990</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron) Laptop,</t>
+          <t>BrowseBook 14.1" FHD IPS Laptop</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core 3 100U Processor, 8GB DDR4, 512 SSD, 15.6" NT FHD 120Hz IPS AG 250 nit Display, Win 11 + Office H&amp;S 2024, Carbon Black, Thin &amp; Light- 1.63Kg</t>
+          <t>BrowseBook 14.1" FHD IPS Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB RAM | 128GB SSD | Windows 11 | 38Wh | 1.3kg | Grey</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
       <c r="D130" t="n">
-        <v>46490</v>
+        <v>13990</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>dell_15_(previously_inspiron)_laptop,</t>
+          <t>BrowseBook 14.1" FHD IPS Laptop</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 16GB DDR4, 512 SSD, Intel UHD Graphics, 15.6" FHD 120Hz IPS AG 250 nit Display, Win 11 + Office 2024, Black, 1.63Kg</t>
+          <t>BrowseBook 14.1" FHD IPS Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB RAM | 128GB SSD | Windows 11 | 38Wh | 1.3kg | Grey</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
       <c r="D131" t="n">
-        <v>58990</v>
+        <v>20990</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron) Laptop,</t>
+          <t>BrowseBook 14.1" FHD IPS Laptop</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 8GB DDR4, 512 SSD, 15.6" FHD 120Hz IPS 250 nit Display, Win 11 + Office H&amp;S 2024, Carbon Black, Thin &amp; Light 1.63Kg</t>
+          <t>BrowseBook 14.1" FHD IPS Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 8GB RAM | 256GB SSD | Windows 11 | 38Wh | 1.3kg | Grey</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
       <c r="D132" t="n">
-        <v>45490</v>
+        <v>18990</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-15</t>
         </is>
       </c>
     </row>
@@ -3202,37 +3202,37 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 8GB DDR4, 512 SSD, 15.6" FHD 120Hz IPS 250 nit Display, Win 11 + Office H&amp;S 2024, Carbon Black, Thin &amp; Light 1.63Kg</t>
+          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core 3 100U Processor, 8GB DDR4, 512 SSD, 15.6" NT FHD 120Hz IPS AG 250 nit Display, Win 11 + Office H&amp;S 2024, Carbon Black, Thin &amp; Light- 1.63Kg</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="n">
-        <v>44990</v>
+        <v>46490</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron) Laptop,</t>
+          <t>dell_15_(previously_inspiron)_laptop,</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 8GB DDR4, 512 SSD, 15.6" FHD 120Hz IPS 250 nit Display, Win 11 + Office H&amp;S 2024, Carbon Black, Thin &amp; Light 1.63Kg</t>
+          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 16GB DDR4, 512 SSD, Intel UHD Graphics, 15.6" FHD 120Hz IPS AG 250 nit Display, Win 11 + Office 2024, Black, 1.63Kg</t>
         </is>
       </c>
       <c r="C134" t="inlineStr"/>
       <c r="D134" t="n">
-        <v>44990</v>
+        <v>58990</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -3253,7 +3253,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-17</t>
         </is>
       </c>
     </row>
@@ -3270,11 +3270,11 @@
       </c>
       <c r="C136" t="inlineStr"/>
       <c r="D136" t="n">
-        <v>45490</v>
+        <v>44990</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
@@ -3291,11 +3291,11 @@
       </c>
       <c r="C137" t="inlineStr"/>
       <c r="D137" t="n">
-        <v>45490</v>
+        <v>44990</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
@@ -3312,11 +3312,11 @@
       </c>
       <c r="C138" t="inlineStr"/>
       <c r="D138" t="n">
-        <v>46490</v>
+        <v>45490</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -3333,200 +3333,200 @@
       </c>
       <c r="C139" t="inlineStr"/>
       <c r="D139" t="n">
-        <v>46990</v>
+        <v>45490</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>dell_15_(previously_inspiron)_laptop,</t>
+          <t>Dell 15 (Previously Inspiron) Laptop,</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 8GB, 512GB, Intel UHD Graphics, 15.6" FHD IPS 250nit Display, 12m Mcafee, Win 11 + MSO'24, Platinum Silver, 1.63kg</t>
+          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 8GB DDR4, 512 SSD, 15.6" FHD 120Hz IPS 250 nit Display, Win 11 + Office H&amp;S 2024, Carbon Black, Thin &amp; Light 1.63Kg</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
       <c r="D140" t="n">
-        <v>47499</v>
+        <v>45490</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron), 13th</t>
+          <t>Dell 15 (Previously Inspiron) Laptop,</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron), 13th Gen Intel Core i5-1334U (16GB RAM, 1TB SSD) FHD, Anti-Glare 15.6"/39.62cm, Windows 11 MSO'24, Silver, 1.62kg, 12 Month McAfee, Thin &amp; Light, Backlit Keyboard Laptop</t>
+          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 8GB DDR4, 512 SSD, 15.6" FHD 120Hz IPS 250 nit Display, Win 11 + Office H&amp;S 2024, Carbon Black, Thin &amp; Light 1.63Kg</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
       <c r="D141" t="n">
-        <v>63990</v>
+        <v>46490</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-06-12</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>dell_15_(previously_inspiron),_amd</t>
+          <t>Dell 15 (Previously Inspiron) Laptop,</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron), AMD Ryzen 5-7530U, 16GB RAM, 512GB SSD, FHD IPS, 15.6"/39.62cm, Win 11, MSO 2024, Platinum Silver, 1.67kg,Standard Keyboard, 12 Month McAfee, Thin &amp; Light, Laptop</t>
+          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 8GB DDR4, 512 SSD, 15.6" FHD 120Hz IPS 250 nit Display, Win 11 + Office H&amp;S 2024, Carbon Black, Thin &amp; Light 1.63Kg</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
       <c r="D142" t="n">
-        <v>56086</v>
+        <v>46990</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Dell 15 AI Powered Laptop,</t>
+          <t>dell_15_(previously_inspiron)_laptop,</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Dell 15 AI Powered Laptop, Intel Core Ultra 5 225H, 8GB DDR5 RAM, 512GB SSD, 15.6" FHD Anti-Glare Display, Intel Arc Graphics, Standard Keyboard, Dedicated Copilot Key, Black, Win11 Home + MSO H&amp;S'24</t>
+          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 8GB, 512GB, Intel UHD Graphics, 15.6" FHD IPS 250nit Display, 12m Mcafee, Win 11 + MSO'24, Platinum Silver, 1.63kg</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
       <c r="D143" t="n">
-        <v>68990</v>
+        <v>47499</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>dell_15_ai_powered_laptop,</t>
+          <t>dell_15_(previously_inspiron)_laptop,</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Dell 15 Ai Powered Laptop, Intel Core Ultra 7 255H, 16GB DDR5 RAM, 512GB SSD, 15.6" FHD Anti-Glare Display, Intel Arc Graphics, Backlit Keyboard, Dedicated Copilot Key, Silver, Win11 Home + MSO H&amp;S'24</t>
+          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 8GB, 512GB, Intel UHD Graphics, 15.6" FHD IPS 250nit Display, 12m Mcafee, Win 11 + MSO'24, Platinum Silver, 1.63kg</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
       <c r="D144" t="n">
-        <v>103990</v>
+        <v>47499</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Dell 15 Smart Choice (Previously</t>
+          <t>Dell 15 (Previously Inspiron), 13th</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Dell 15 Smart Choice (Previously Inspiron), 13th Gen Intel Core i5-1334U (16GB RAM, 1TB SSD) FHD, 15.6"/39.62cm, Windows 11 MSO'24, Silver, 1.62kg, 12 Month McAfee, Backlit KB, Thin &amp; Light Laptop</t>
+          <t>Dell 15 (Previously Inspiron), 13th Gen Intel Core i5-1334U (16GB RAM, 1TB SSD) FHD, Anti-Glare 15.6"/39.62cm, Windows 11 MSO'24, Silver, 1.62kg, 12 Month McAfee, Thin &amp; Light, Backlit Keyboard Laptop</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
       <c r="D145" t="n">
-        <v>66990</v>
+        <v>63990</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-17</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Dell 15 Smart Choice (Previously</t>
+          <t>dell_15_(previously_inspiron),_amd</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Dell 15 Smart Choice (Previously Inspiron), 13th Gen Intel Core i5-1334U (16GB RAM, 1TB SSD) FHD, 15.6"/39.62cm, Windows 11 MSO'24, Silver, 1.62kg, 12 Month McAfee, Backlit KB, Thin &amp; Light Laptop</t>
+          <t>Dell 15 (Previously Inspiron), AMD Ryzen 5-7530U, 16GB RAM, 512GB SSD, FHD IPS, 15.6"/39.62cm, Win 11, MSO 2024, Platinum Silver, 1.67kg,Standard Keyboard, 12 Month McAfee, Thin &amp; Light, Laptop</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
       <c r="D146" t="n">
-        <v>67990</v>
+        <v>56086</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Dell 15 Smart Choice (Previously</t>
+          <t>Dell 15 AI Powered Laptop,</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Dell 15 Smart Choice (Previously Inspiron), 13th Gen Intel Core i5-1334U (16GB RAM, 1TB SSD) FHD, 15.6"/39.62cm, Windows 11 MSO'24, Silver, 1.62kg, 12 Month McAfee, Backlit KB, Thin &amp; Light Laptop</t>
+          <t>Dell 15 AI Powered Laptop, Intel Core Ultra 5 225H, 8GB DDR5 RAM, 512GB SSD, 15.6" FHD Anti-Glare Display, Intel Arc Graphics, Standard Keyboard, Dedicated Copilot Key, Black, Win11 Home + MSO H&amp;S'24</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
       <c r="D147" t="n">
-        <v>67990</v>
+        <v>68990</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-15</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Dell 15 Smart Choice (Previously</t>
+          <t>dell_15_ai_powered_laptop,</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Dell 15 Smart Choice (Previously Inspiron), 13th Gen Intel Core i5-1334U (16GB RAM, 1TB SSD) FHD, 15.6"/39.62cm, Windows 11 MSO'24, Silver, 1.62kg, 12 Month McAfee, Backlit KB, Thin &amp; Light Laptop</t>
+          <t>Dell 15 Ai Powered Laptop, Intel Core Ultra 7 255H, 16GB DDR5 RAM, 512GB SSD, 15.6" FHD Anti-Glare Display, Intel Arc Graphics, Backlit Keyboard, Dedicated Copilot Key, Silver, Win11 Home + MSO H&amp;S'24</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
       <c r="D148" t="n">
-        <v>69990</v>
+        <v>103990</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -3543,347 +3543,347 @@
       </c>
       <c r="C149" t="inlineStr"/>
       <c r="D149" t="n">
-        <v>67990</v>
+        <v>66990</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-05-28</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Dell 15, 13th Gen Intel</t>
+          <t>Dell 15 Smart Choice (Previously</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Dell 15, 13th Gen Intel Core i5-1334U (16GB DDR4, 512GB SSD) Anti-Glare FHD 15.6"/39.62cm, Windows 11, Microsoft Office Home 2024, Grey, 1.66kg, [Vostro 3530], 12 Month McAfee, Thin &amp; Light Laptop</t>
+          <t>Dell 15 Smart Choice (Previously Inspiron), 13th Gen Intel Core i5-1334U (16GB RAM, 1TB SSD) FHD, 15.6"/39.62cm, Windows 11 MSO'24, Silver, 1.62kg, 12 Month McAfee, Backlit KB, Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
       <c r="D150" t="n">
-        <v>61490</v>
+        <v>67990</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-31</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Dell 15, 13th Gen Intel</t>
+          <t>Dell 15 Smart Choice (Previously</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Dell 15, 13th Gen Intel Core i5-1334U (16GB DDR4, 512GB SSD) Anti-Glare FHD 15.6"/39.62cm, Windows 11, Microsoft Office Home 2024, Grey, 1.66kg, [Vostro 3530], 12 Month McAfee, Thin &amp; Light Laptop</t>
+          <t>Dell 15 Smart Choice (Previously Inspiron), 13th Gen Intel Core i5-1334U (16GB RAM, 1TB SSD) FHD, 15.6"/39.62cm, Windows 11 MSO'24, Silver, 1.62kg, 12 Month McAfee, Backlit KB, Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
       <c r="D151" t="n">
-        <v>63490</v>
+        <v>67990</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Dell 15, AMD Ryzen 7-7730U,</t>
+          <t>Dell 15 Smart Choice (Previously</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Dell 15, AMD Ryzen 7-7730U, 16GB DDR4, 512GB SSD, FHD, 15.6"/39.6cm, Windows 11, Microsoft Office Home 2024, Platinum Silver, 1.63Kg, [Dell 15], 120Hz 250nits, AMD Radeon Graphics,Thin &amp; Light, Laptop</t>
+          <t>Dell 15 Smart Choice (Previously Inspiron), 13th Gen Intel Core i5-1334U (16GB RAM, 1TB SSD) FHD, 15.6"/39.62cm, Windows 11 MSO'24, Silver, 1.62kg, 12 Month McAfee, Backlit KB, Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="n">
-        <v>59957</v>
+        <v>69990</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-06-02</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Dell 15, AMD Ryzen 7-7730U,</t>
+          <t>Dell 15 Smart Choice (Previously</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Dell 15, AMD Ryzen 7-7730U, 16GB DDR4, 512GB SSD, FHD, 15.6"/39.6cm, Windows 11, Microsoft Office Home 2024, Platinum Silver, 1.63Kg, [Dell 15], 120Hz 250nits, AMD Radeon Graphics,Thin &amp; Light, Laptop</t>
+          <t>Dell 15 Smart Choice (Previously Inspiron), 13th Gen Intel Core i5-1334U (16GB RAM, 1TB SSD) FHD, 15.6"/39.62cm, Windows 11 MSO'24, Silver, 1.62kg, 12 Month McAfee, Backlit KB, Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
       <c r="D153" t="n">
-        <v>58490</v>
+        <v>67990</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-06-14</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>dell_15,_intel_core_13th</t>
+          <t>dell_15_smartchoice_(previously_inspiron),</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Dell 15, Intel Core 13th Gen i5-1334U, FHD, 15.6"/39.62cm, Windows 11, MSO'24, Grey, 1.66kg, Vostro 3530, (16GB DDR4, 512GB SSD) Anti-Glare FHD 15.6"/39.62cm, 12 Month McAfee, Thin &amp; Light Laptop</t>
+          <t>Dell 15 SmartChoice (Previously Inspiron), Intel 13th Gen Core i5-1334U, 16GB, 1TB SSD, FHD,15.6"/39.62cm, Win 11, MSO'24, Silver, 1.62kg, [Dell 15], 12 Month McAfee, Backlit KB, Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C154" t="inlineStr"/>
       <c r="D154" t="n">
-        <v>65490</v>
+        <v>68990</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Dell 15, Intel Core 3</t>
+          <t>Dell 15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Dell 15, Intel Core 3 14th Gen-100U, 16GB DDR4, 512GB SSD, FHD IPS, 15.6"/39.62cm, Windows 11, Microsoft Office Home 2024, Carbon Black, 1.63Kg, Thin &amp; Light, Laptop Model NO - Dell 15 DCU5250</t>
+          <t>Dell 15, 13th Gen Intel Core i5-1334U (16GB DDR4, 512GB SSD) Anti-Glare FHD 15.6"/39.62cm, Windows 11, Microsoft Office Home 2024, Grey, 1.66kg, [Vostro 3530], 12 Month McAfee, Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C155" t="inlineStr"/>
       <c r="D155" t="n">
-        <v>51868</v>
+        <v>61490</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Dell 15, Intel Core i3/Core</t>
+          <t>Dell 15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Dell 15, Intel Core i3/Core 3 14th Gen-100U, 16GB DDR4, 512GB SSD, FHD IPS, 15.6"/39.62cm, Windows 11, Microsoft Office Home 2024, Carbon Black, 1.63Kg, Thin &amp; Light, Laptop Model NO - Dell 15 DCU5250</t>
+          <t>Dell 15, 13th Gen Intel Core i5-1334U (16GB DDR4, 512GB SSD) Anti-Glare FHD 15.6"/39.62cm, Windows 11, Microsoft Office Home 2024, Grey, 1.66kg, [Vostro 3530], 12 Month McAfee, Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
       <c r="D156" t="n">
-        <v>48990</v>
+        <v>63490</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Dell 15, R5-7520U Processor, 8GB</t>
+          <t>Dell 15, AMD Ryzen 7-7730U,</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Dell 15, R5-7520U Processor, 8GB LPDDR5 RAM, 512GB SSD, FHD 15.6"/39.62 cm Display, Windows 11, MSO'24, Carbon Black, 1.63kg, Standard Keyboard, 15 Month McAfee, Thin &amp; Light Laptop</t>
+          <t>Dell 15, AMD Ryzen 7-7730U, 16GB DDR4, 512GB SSD, FHD, 15.6"/39.6cm, Windows 11, Microsoft Office Home 2024, Platinum Silver, 1.63Kg, [Dell 15], 120Hz 250nits, AMD Radeon Graphics,Thin &amp; Light, Laptop</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
       <c r="D157" t="n">
-        <v>53990</v>
+        <v>59957</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>dell_g_series,_intel_core</t>
+          <t>Dell 15, AMD Ryzen 7-7730U,</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Dell G Series, Intel Core i5-13450HX, 13th Gen, NVIDIA RTX 3050-6GB, 16GB, 512GB SSD, FHD, 15.6"/39.62cm, Windows 11, MSO'24, Dark Shadow Gray, 2.65KG, [G15-5530], Backlit Keyboard, Gaming Laptop</t>
+          <t>Dell 15, AMD Ryzen 7-7730U, 16GB DDR4, 512GB SSD, FHD, 15.6"/39.6cm, Windows 11, Microsoft Office Home 2024, Platinum Silver, 1.63Kg, [Dell 15], 120Hz 250nits, AMD Radeon Graphics,Thin &amp; Light, Laptop</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
       <c r="D158" t="n">
-        <v>89990</v>
+        <v>58490</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-17</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Dell G15, 13th Gen Intel</t>
+          <t>dell_15,_intel_core_13th</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Dell G15, 13th Gen Intel Core i5-13450HX Processor, NVIDIA RTX 3050-6GB, (16GB RAM 1TB SSD) FHD 15.6"/39.62 cm, Orange Backlit Keyboard, Win 11, MS Office'24, Dark Shadow Grey, 2.65Kg Gaming Laptop</t>
+          <t>Dell 15, Intel Core 13th Gen i5-1334U, FHD, 15.6"/39.62cm, Windows 11, MSO'24, Grey, 1.66kg, Vostro 3530, (16GB DDR4, 512GB SSD) Anti-Glare FHD 15.6"/39.62cm, 12 Month McAfee, Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C159" t="inlineStr"/>
       <c r="D159" t="n">
-        <v>79590</v>
+        <v>65490</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Dell G15, 13th Gen Intel</t>
+          <t>Dell 15, Intel Core 3</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Dell G15, 13th Gen Intel Core i5-13450HX Processor, NVIDIA RTX 3050-6GB, (16GB RAM 1TB SSD) FHD 15.6"/39.62 cm, Orange Backlit Keyboard, Win 11, MS Office'24, Dark Shadow Grey, 2.65Kg Gaming Laptop</t>
+          <t>Dell 15, Intel Core 3 14th Gen-100U, 16GB DDR4, 512GB SSD, FHD IPS, 15.6"/39.62cm, Windows 11, Microsoft Office Home 2024, Carbon Black, 1.63Kg, Thin &amp; Light, Laptop Model NO - Dell 15 DCU5250</t>
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
       <c r="D160" t="n">
-        <v>79990</v>
+        <v>51868</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>EBook 11.6" HD Laptop |</t>
+          <t>Dell 15, Intel Core i3/Core</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EBook 11.6" HD Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB DDR4 | 128GB eMMC + M.2 SSD Expandable Slot | Win 11 Home |31Wh Battery | UHD Graphics 600 | Black</t>
+          <t>Dell 15, Intel Core i3/Core 3 14th Gen-100U, 16GB DDR4, 512GB SSD, FHD IPS, 15.6"/39.62cm, Windows 11, Microsoft Office Home 2024, Carbon Black, 1.63Kg, Thin &amp; Light, Laptop Model NO - Dell 15 DCU5250</t>
         </is>
       </c>
       <c r="C161" t="inlineStr"/>
       <c r="D161" t="n">
-        <v>11990</v>
+        <v>48990</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>EBook 11.6" HD Laptop |</t>
+          <t>Dell 15, R5-7520U Processor, 8GB</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EBook 11.6" HD Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB DDR4 | 128GB eMMC + M.2 SSD Expandable Slot | Win 11 Home |31Wh Battery | UHD Graphics 600 | Black</t>
+          <t>Dell 15, R5-7520U Processor, 8GB LPDDR5 RAM, 512GB SSD, FHD 15.6"/39.62 cm Display, Windows 11, MSO'24, Carbon Black, 1.63kg, Standard Keyboard, 15 Month McAfee, Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C162" t="inlineStr"/>
       <c r="D162" t="n">
-        <v>11990</v>
+        <v>53990</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-16</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>EBook 11.6" HD Laptop |</t>
+          <t>dell_g_series,_intel_core</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EBook 11.6" HD Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB DDR4 | 128GB eMMC + M.2 SSD Expandable Slot | Win 11 Home |31Wh Battery | UHD Graphics 600 | Black</t>
+          <t>Dell G Series, Intel Core i5-13450HX, 13th Gen, NVIDIA RTX 3050-6GB, 16GB, 512GB SSD, FHD, 15.6"/39.62cm, Windows 11, MSO'24, Dark Shadow Gray, 2.65KG, [G15-5530], Backlit Keyboard, Gaming Laptop</t>
         </is>
       </c>
       <c r="C163" t="inlineStr"/>
       <c r="D163" t="n">
-        <v>11990</v>
+        <v>89990</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>EBook 11.6" HD Laptop |</t>
+          <t>Dell G15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EBook 11.6" HD Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB DDR4 | 128GB eMMC + M.2 SSD Expandable Slot | Win 11 Home |31Wh Battery | UHD Graphics 600 | Black</t>
+          <t>Dell G15, 13th Gen Intel Core i5-13450HX Processor, NVIDIA RTX 3050-6GB, (16GB RAM 1TB SSD) FHD 15.6"/39.62 cm, Orange Backlit Keyboard, Win 11, MS Office'24, Dark Shadow Grey, 2.65Kg Gaming Laptop</t>
         </is>
       </c>
       <c r="C164" t="inlineStr"/>
       <c r="D164" t="n">
-        <v>11990</v>
+        <v>79590</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>EBook 11.6" HD Laptop |</t>
+          <t>Dell G15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>EBook 11.6" HD Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB DDR4 | 128GB eMMC + M.2 SSD Expandable Slot | Win 11 Home |31Wh Battery | UHD Graphics 600 | Black</t>
+          <t>Dell G15, 13th Gen Intel Core i5-13450HX Processor, NVIDIA RTX 3050-6GB, (16GB RAM 1TB SSD) FHD 15.6"/39.62 cm, Orange Backlit Keyboard, Win 11, MS Office'24, Dark Shadow Grey, 2.65Kg Gaming Laptop</t>
         </is>
       </c>
       <c r="C165" t="inlineStr"/>
       <c r="D165" t="n">
-        <v>11990</v>
+        <v>79990</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-08</t>
         </is>
       </c>
     </row>
@@ -3904,7 +3904,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-04-16</t>
         </is>
       </c>
     </row>
@@ -3925,7 +3925,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -3946,7 +3946,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -3967,7 +3967,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-19</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-20</t>
         </is>
       </c>
     </row>
@@ -4005,11 +4005,11 @@
       </c>
       <c r="C171" t="inlineStr"/>
       <c r="D171" t="n">
-        <v>16990</v>
+        <v>11990</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-21</t>
         </is>
       </c>
     </row>
@@ -4026,18 +4026,18 @@
       </c>
       <c r="C172" t="inlineStr"/>
       <c r="D172" t="n">
-        <v>16990</v>
+        <v>11990</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-05-31</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>ebook_11.6"_hd_laptop_|</t>
+          <t>EBook 11.6" HD Laptop |</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -4047,18 +4047,18 @@
       </c>
       <c r="C173" t="inlineStr"/>
       <c r="D173" t="n">
-        <v>10603</v>
+        <v>11990</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>ebook_11.6"_hd_laptop_|</t>
+          <t>EBook 11.6" HD Laptop |</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -4068,196 +4068,196 @@
       </c>
       <c r="C174" t="inlineStr"/>
       <c r="D174" t="n">
-        <v>10990</v>
+        <v>11990</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-06-02</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>hp_14_smartchoice,_intel_core</t>
+          <t>EBook 11.6" HD Laptop |</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>HP 14 Smartchoice, Intel Core Ultra 5 125H 12 TOPS, 24GB DDR5 (Upgradeable) 1TB SSD, Anti-Glare, FHD, 14''/35.6cm,Win11, M365*Office24, Silver, 1.4kg, ep1180tu, FHD Camera w/Shutter, Backlit AI Laptop</t>
+          <t>EBook 11.6" HD Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB DDR4 | 128GB eMMC + M.2 SSD Expandable Slot | Win 11 Home |31Wh Battery | UHD Graphics 600 | Black</t>
         </is>
       </c>
       <c r="C175" t="inlineStr"/>
       <c r="D175" t="n">
-        <v>77990</v>
+        <v>11990</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>hp_14,_amd_ryzen_7</t>
+          <t>EBook 11.6" HD Laptop |</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>HP 14, AMD Ryzen 7 7730U (16GB DDR4, 512GB SSD) FHD, Anti-Glare, Micro-Edge, 14''/35.6cm, Win11, M365 Basic(1yr), Office Home24, Silver,1.4kg, EM0104AU, FHD Camera w/Privacy Shutter, Backlit Laptop</t>
+          <t>EBook 11.6" HD Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB DDR4 | 128GB eMMC + M.2 SSD Expandable Slot | Win 11 Home |31Wh Battery | UHD Graphics 600 | Black</t>
         </is>
       </c>
       <c r="C176" t="inlineStr"/>
       <c r="D176" t="n">
-        <v>59990</v>
+        <v>16990</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>HP 14s Intel Celeron Dual</t>
+          <t>EBook 11.6" HD Laptop |</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>HP 14s Intel Celeron Dual Core N4500 Laptop (8GB/512GB SSD/Win 11) 14.0" HD Display, MSO 24, Black, 1.46kg, DQ3149TU Thin and Light Business Laptop</t>
+          <t>EBook 11.6" HD Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB DDR4 | 128GB eMMC + M.2 SSD Expandable Slot | Win 11 Home |31Wh Battery | UHD Graphics 600 | Black</t>
         </is>
       </c>
       <c r="C177" t="inlineStr"/>
       <c r="D177" t="n">
-        <v>40400</v>
+        <v>16990</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>HP 15 (2026), AMD Athlon</t>
+          <t>ebook_11.6"_hd_laptop_|</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>HP 15 (2026), AMD Athlon Dual Core 7120U - (8 GB DDR5/512 GB SSD/AMD Radeon 610M Graphics/DOS) Thin and Light Business Laptop/15.6" HD Display/Turbo Silver/Copilot Key/1.5kg</t>
+          <t>EBook 11.6" HD Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB DDR4 | 128GB eMMC + M.2 SSD Expandable Slot | Win 11 Home |31Wh Battery | UHD Graphics 600 | Black</t>
         </is>
       </c>
       <c r="C178" t="inlineStr"/>
       <c r="D178" t="n">
-        <v>39999</v>
+        <v>10603</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>HP 15 (2026), AMD Athlon</t>
+          <t>ebook_11.6"_hd_laptop_|</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>HP 15 (2026), AMD Athlon Dual Core 7120U - (8 GB DDR5/512 GB SSD/AMD Radeon 610M Graphics/Windows 11 Pro) Thin and Light Business Laptop/15.6" HD Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
+          <t>EBook 11.6" HD Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB DDR4 | 128GB eMMC + M.2 SSD Expandable Slot | Win 11 Home |31Wh Battery | UHD Graphics 600 | Black</t>
         </is>
       </c>
       <c r="C179" t="inlineStr"/>
       <c r="D179" t="n">
-        <v>39660</v>
+        <v>10990</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>hp_15_(2026),_amd_athlon</t>
+          <t>ebook_11.6"_hd_laptop_|</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>HP 15 (2026), AMD Athlon Dual Core 7120U - (8 GB DDR5/512 GB SSD/AMD Radeon 610M Graphics/Windows 11 Pro) Thin and Light Business Laptop/15.6" HD Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
+          <t>EBook 11.6" HD Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB DDR4 | 128GB eMMC + M.2 SSD Expandable Slot | Win 11 Home |31Wh Battery | UHD Graphics 600 | Black</t>
         </is>
       </c>
       <c r="C180" t="inlineStr"/>
       <c r="D180" t="n">
-        <v>41999</v>
+        <v>10990</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>hp_15_(2026),_amd_athlon</t>
+          <t>hp_14_smartchoice,_intel_core</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>HP 15 (2026), AMD Athlon Dual Core 7120U - (8 GB DDR5/512 GB SSD/AMD Radeon 610M Graphics/Windows 11 Pro) Thin and Light Business Laptop/15.6" HD Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
+          <t>HP 14 Smartchoice, Intel Core Ultra 5 125H 12 TOPS, 24GB DDR5 (Upgradeable) 1TB SSD, Anti-Glare, FHD, 14''/35.6cm,Win11, M365*Office24, Silver, 1.4kg, ep1180tu, FHD Camera w/Shutter, Backlit AI Laptop</t>
         </is>
       </c>
       <c r="C181" t="inlineStr"/>
       <c r="D181" t="n">
-        <v>42840</v>
+        <v>77990</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>HP 15 (2026), AMD Ryzen</t>
+          <t>hp_14_smartchoice,_intel_core</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>HP 15 (2026), AMD Ryzen 3 Quad Core 7335U - (8 GB DDR5/512 GB SSD/AMD Radeon 660M Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
+          <t>HP 14 Smartchoice, Intel Core Ultra 5 125H 12 TOPS, 24GB DDR5 (Upgradeable) 1TB SSD, Anti-Glare, FHD, 14''/35.6cm,Win11, M365*Office24, Silver, 1.4kg, ep1180tu, FHD Camera w/Shutter, Backlit AI Laptop</t>
         </is>
       </c>
       <c r="C182" t="inlineStr"/>
       <c r="D182" t="n">
-        <v>42780</v>
+        <v>77990</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>hp_15_(i5_14th_gen),</t>
+          <t>hp_14,_amd_ryzen_7</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>HP 15 (i5 14th Gen), Intel Core 5, 16GB RAM (Upgradeable), 512GB SSD, FHD, Anti-Glare, 15.6''/39.6cm, Win11, M365 Basic(1yr), Office24, Silver,1.59kg, fd0682tu, FHD Camera w/Shutter, Backlit Laptop</t>
+          <t>HP 14, AMD Ryzen 7 7730U (16GB DDR4, 512GB SSD) FHD, Anti-Glare, Micro-Edge, 14''/35.6cm, Win11, M365 Basic(1yr), Office Home24, Silver,1.4kg, EM0104AU, FHD Camera w/Privacy Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C183" t="inlineStr"/>
       <c r="D183" t="n">
-        <v>63990</v>
+        <v>59990</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
@@ -4268,248 +4268,248 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>hp_15_(i5_14th_gen),</t>
+          <t>hp_14,_amd_ryzen_7</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>HP 15 (i5 14th Gen), Intel Core 5, 16GB RAM (Upgradeable), 512GB SSD, FHD, Anti-Glare, 15.6''/39.6cm, Win11, M365 Basic(1yr), Office24, Silver,1.59kg, fd0682tu, FHD Camera w/Shutter, Backlit Laptop</t>
+          <t>HP 14, AMD Ryzen 7 7730U (16GB DDR4, 512GB SSD) FHD, Anti-Glare, Micro-Edge, 14''/35.6cm, Win11, M365 Basic(1yr), Office Home24, Silver,1.4kg, EM0104AU, FHD Camera w/Privacy Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C184" t="inlineStr"/>
       <c r="D184" t="n">
-        <v>67990</v>
+        <v>64990</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>hp_15_laptop_|_amd</t>
+          <t>HP 14s Intel Celeron Dual</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>HP 15 Laptop | AMD Ryzen 7 5825U |16GB DDR4 RAM | 512GB SSD |15.6" (39.6 cm) FHD Display |AMD Radeon Graphics| Backlit KB | FHD Camera| Win 11| MS Office 2024 + M365*(1-Yr) | Silver |1.59kg |fc0533AU</t>
+          <t>HP 14s Intel Celeron Dual Core N4500 Laptop (8GB/512GB SSD/Win 11) 14.0" HD Display, MSO 24, Black, 1.46kg, DQ3149TU Thin and Light Business Laptop</t>
         </is>
       </c>
       <c r="C185" t="inlineStr"/>
       <c r="D185" t="n">
-        <v>64990</v>
+        <v>40400</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-04-16</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>hp_15_laptop_|_intel</t>
+          <t>HP 15 (2026), AMD Athlon</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>HP 15 Laptop | Intel Core i5-13420H,13th Gen |16GB RAM | 512GB SSD | Win 11 |M365 Basic(1yr)* Office24|Anti-Glare, Micro-Edge, 15.6''/39.6cm|Backlit KB|FHD Camera w/Shutter|1.65kg, Silver -FR0045TU</t>
+          <t>HP 15 (2026), AMD Athlon Dual Core 7120U - (8 GB DDR5/512 GB SSD/AMD Radeon 610M Graphics/DOS) Thin and Light Business Laptop/15.6" HD Display/Turbo Silver/Copilot Key/1.5kg</t>
         </is>
       </c>
       <c r="C186" t="inlineStr"/>
       <c r="D186" t="n">
-        <v>68990</v>
+        <v>39999</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-08</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>hp_15_laptop,_(14th_gen</t>
+          <t>HP 15 (2026), AMD Athlon</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>HP 15 Laptop, (14th Gen Core i5) Intel Core 5-120U (24GB RAM, 512GB SSD, Win 11, M365 Basic(1yr)* Office24,15.6''/39.6cm FHD Anti-Glare Display, Backlit KB, FHD Camera, Dual Speakers, Silver, 1.59kg)</t>
+          <t>HP 15 (2026), AMD Athlon Dual Core 7120U - (8 GB DDR5/512 GB SSD/AMD Radeon 610M Graphics/Windows 11 Pro) Thin and Light Business Laptop/15.6" HD Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
         </is>
       </c>
       <c r="C187" t="inlineStr"/>
       <c r="D187" t="n">
-        <v>72800</v>
+        <v>39660</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>HP 15 Laptop, Intel (14th</t>
+          <t>hp_15_(2026),_amd_athlon</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>HP 15 Laptop, Intel (14th Gen) Core 5 120U (24GB DDR5, 512GB SSD), Micro-Edge, Anti-Glare, 15.6''/39.6cm, Win11, M365* Office24, Silver, 1.59kg, fd0262TU, FHD Camera, Backlit, Dual Speakers</t>
+          <t>HP 15 (2026), AMD Athlon Dual Core 7120U - (8 GB DDR5/512 GB SSD/AMD Radeon 610M Graphics/Windows 11 Pro) Thin and Light Business Laptop/15.6" HD Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
         </is>
       </c>
       <c r="C188" t="inlineStr"/>
       <c r="D188" t="n">
-        <v>67990</v>
+        <v>41999</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, 13th Gen</t>
+          <t>hp_15_(2026),_amd_athlon</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U (12GB DDR4, 512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver, 1.59kg, fd0573TU, FHD Camera w/Shutter Laptop</t>
+          <t>HP 15 (2026), AMD Athlon Dual Core 7120U - (8 GB DDR5/512 GB SSD/AMD Radeon 610M Graphics/Windows 11 Pro) Thin and Light Business Laptop/15.6" HD Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
         </is>
       </c>
       <c r="C189" t="inlineStr"/>
       <c r="D189" t="n">
-        <v>55990</v>
+        <v>42840</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, 13th Gen</t>
+          <t>hp_15_(2026),_amd_athlon</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U(8GB DDR4,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
+          <t>HP 15 (2026), AMD Athlon Dual Core 7120U - (8 GB DDR5/512 GB SSD/AMD Radeon 610M Graphics/Windows 11 Pro) Thin and Light Business Laptop/15.6" HD Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
         </is>
       </c>
       <c r="C190" t="inlineStr"/>
       <c r="D190" t="n">
-        <v>51990</v>
+        <v>42840</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, 13th Gen</t>
+          <t>HP 15 (2026), AMD Ryzen</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U(8GB DDR4,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
+          <t>HP 15 (2026), AMD Ryzen 3 Quad Core 7335U - (8 GB DDR5/512 GB SSD/AMD Radeon 660M Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
         </is>
       </c>
       <c r="C191" t="inlineStr"/>
       <c r="D191" t="n">
-        <v>51990</v>
+        <v>42780</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, 13th Gen</t>
+          <t>hp_15_(i5_14th_gen),</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U(8GB DDR4,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
+          <t>HP 15 (i5 14th Gen), Intel Core 5, 16GB RAM (Upgradeable), 512GB SSD, FHD, Anti-Glare, 15.6''/39.6cm, Win11, M365 Basic(1yr), Office24, Silver,1.59kg, fd0682tu, FHD Camera w/Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C192" t="inlineStr"/>
       <c r="D192" t="n">
-        <v>51990</v>
+        <v>63990</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, 13th Gen</t>
+          <t>hp_15_(i5_14th_gen),</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U(8GB DDR4,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
+          <t>HP 15 (i5 14th Gen), Intel Core 5, 16GB RAM (Upgradeable), 512GB SSD, FHD, Anti-Glare, 15.6''/39.6cm, Win11, M365 Basic(1yr), Office24, Silver,1.59kg, fd0682tu, FHD Camera w/Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C193" t="inlineStr"/>
       <c r="D193" t="n">
-        <v>51990</v>
+        <v>67990</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, 13th Gen</t>
+          <t>hp_15_laptop_|_amd</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U(8GB DDR4,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
+          <t>HP 15 Laptop | AMD Ryzen 7 5825U |16GB DDR4 RAM | 512GB SSD |15.6" (39.6 cm) FHD Display |AMD Radeon Graphics| Backlit KB | FHD Camera| Win 11| MS Office 2024 + M365*(1-Yr) | Silver |1.59kg |fc0533AU</t>
         </is>
       </c>
       <c r="C194" t="inlineStr"/>
       <c r="D194" t="n">
-        <v>51990</v>
+        <v>64990</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>hp_15_smartchoice,_13th_gen</t>
+          <t>hp_15_laptop_|_intel</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U(8GB DDR4,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
+          <t>HP 15 Laptop | Intel Core i5-13420H,13th Gen |16GB RAM | 512GB SSD | Win 11 |M365 Basic(1yr)* Office24|Anti-Glare, Micro-Edge, 15.6''/39.6cm|Backlit KB|FHD Camera w/Shutter|1.65kg, Silver -FR0045TU</t>
         </is>
       </c>
       <c r="C195" t="inlineStr"/>
       <c r="D195" t="n">
-        <v>49990</v>
+        <v>68990</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
@@ -4520,273 +4520,273 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>hp_15_smartchoice,_13th_gen</t>
+          <t>hp_15_laptop,_(14th_gen</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U(8GB DDR4,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
+          <t>HP 15 Laptop, (14th Gen Core i5) Intel Core 5-120U (24GB RAM, 512GB SSD, Win 11, M365 Basic(1yr)* Office24,15.6''/39.6cm FHD Anti-Glare Display, Backlit KB, FHD Camera, Dual Speakers, Silver, 1.59kg)</t>
         </is>
       </c>
       <c r="C196" t="inlineStr"/>
       <c r="D196" t="n">
-        <v>49990</v>
+        <v>72800</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>hp_15_smartchoice,_intel_core</t>
+          <t>HP 15 Laptop, Intel (14th</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, Intel Core Ultra 5 125H, 12 Tops (16GB DDR5, 512GB SSD) FHD, IPS, 15.6''/39.6cm, Win11, M365(1yr)* Office24, Silver, 1.65kg, fd1254TU, FHD Camera w/Shutter, AI Powered Laptop</t>
+          <t>HP 15 Laptop, Intel (14th Gen) Core 5 120U (24GB DDR5, 512GB SSD), Micro-Edge, Anti-Glare, 15.6''/39.6cm, Win11, M365* Office24, Silver, 1.59kg, fd0262TU, FHD Camera, Backlit, Dual Speakers</t>
         </is>
       </c>
       <c r="C197" t="inlineStr"/>
       <c r="D197" t="n">
-        <v>69990</v>
+        <v>67990</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>hp_15_smartchoice,_intel_core</t>
+          <t>HP 15 Smartchoice, 13th Gen</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, Intel Core Ultra 5 125H, 12 Tops (16GB DDR5, 512GB SSD) FHD, IPS, 15.6''/39.6cm, Win11, M365(1yr)* Office24, Silver, 1.65kg, fd1254TU, FHD Camera w/Shutter, AI Powered Laptop</t>
+          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U (12GB DDR4, 512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver, 1.59kg, fd0573TU, FHD Camera w/Shutter Laptop</t>
         </is>
       </c>
       <c r="C198" t="inlineStr"/>
       <c r="D198" t="n">
-        <v>69990</v>
+        <v>55990</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-06-12</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel</t>
+          <t>HP 15 Smartchoice, 13th Gen</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U (8GB DDR4, 512GB SSD), FHD, Micro -Edge, Anti-Glare, 15.6''/39.6cm, Win11, M365* Office24, Silver, 1.59kg, fd0624tu, FHD Camera, UHD Graphics Laptop</t>
+          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U(8GB DDR4,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C199" t="inlineStr"/>
       <c r="D199" t="n">
-        <v>47490</v>
+        <v>51990</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>hp_15,_13th_gen_intel</t>
+          <t>HP 15 Smartchoice, 13th Gen</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U (8GB DDR4, 512GB SSD), FHD, Micro -Edge, Anti-Glare, 15.6''/39.6cm, Win11, M365* Office24, Silver, 1.59kg, fd0624tu, FHD Camera, UHD Graphics Laptop</t>
+          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U(8GB DDR4,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C200" t="inlineStr"/>
       <c r="D200" t="n">
-        <v>48990</v>
+        <v>51990</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel</t>
+          <t>HP 15 Smartchoice, 13th Gen</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
+          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U(8GB DDR4,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C201" t="inlineStr"/>
       <c r="D201" t="n">
-        <v>47990</v>
+        <v>51990</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel</t>
+          <t>HP 15 Smartchoice, 13th Gen</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
+          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U(8GB DDR4,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C202" t="inlineStr"/>
       <c r="D202" t="n">
-        <v>47990</v>
+        <v>51990</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel</t>
+          <t>HP 15 Smartchoice, 13th Gen</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
+          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U(8GB DDR4,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C203" t="inlineStr"/>
       <c r="D203" t="n">
-        <v>46990</v>
+        <v>51990</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel</t>
+          <t>hp_15_smartchoice,_13th_gen</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
+          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U(8GB DDR4,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C204" t="inlineStr"/>
       <c r="D204" t="n">
-        <v>46990</v>
+        <v>49990</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel</t>
+          <t>hp_15_smartchoice,_13th_gen</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
+          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U(8GB DDR4,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C205" t="inlineStr"/>
       <c r="D205" t="n">
-        <v>46990</v>
+        <v>49990</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel</t>
+          <t>hp_15_smartchoice,_13th_gen</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
+          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U(8GB DDR4,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C206" t="inlineStr"/>
       <c r="D206" t="n">
-        <v>46990</v>
+        <v>49990</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel</t>
+          <t>hp_15_smartchoice,_intel_core</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
+          <t>HP 15 Smartchoice, Intel Core Ultra 5 125H, 12 Tops (16GB DDR5, 512GB SSD) FHD, IPS, 15.6''/39.6cm, Win11, M365(1yr)* Office24, Silver, 1.65kg, fd1254TU, FHD Camera w/Shutter, AI Powered Laptop</t>
         </is>
       </c>
       <c r="C207" t="inlineStr"/>
       <c r="D207" t="n">
-        <v>46990</v>
+        <v>69990</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel</t>
+          <t>hp_15_smartchoice,_intel_core</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
+          <t>HP 15 Smartchoice, Intel Core Ultra 5 125H, 12 Tops (16GB DDR5, 512GB SSD) FHD, IPS, 15.6''/39.6cm, Win11, M365(1yr)* Office24, Silver, 1.65kg, fd1254TU, FHD Camera w/Shutter, AI Powered Laptop</t>
         </is>
       </c>
       <c r="C208" t="inlineStr"/>
       <c r="D208" t="n">
-        <v>46990</v>
+        <v>69990</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -4798,58 +4798,58 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U (8GB DDR4, 512GB SSD), FHD, Micro -Edge, Anti-Glare, 15.6''/39.6cm, Win11, M365* Office24, Silver, 1.59kg, fd0624tu, FHD Camera, UHD Graphics Laptop</t>
         </is>
       </c>
       <c r="C209" t="inlineStr"/>
       <c r="D209" t="n">
-        <v>48900</v>
+        <v>47490</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-04-16</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel</t>
+          <t>hp_15,_13th_gen_intel</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U (8GB DDR4, 512GB SSD), FHD, Micro -Edge, Anti-Glare, 15.6''/39.6cm, Win11, M365* Office24, Silver, 1.59kg, fd0624tu, FHD Camera, UHD Graphics Laptop</t>
         </is>
       </c>
       <c r="C210" t="inlineStr"/>
       <c r="D210" t="n">
-        <v>48900</v>
+        <v>48990</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel</t>
+          <t>hp_15,_13th_gen_intel</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U (8GB DDR4, 512GB SSD), FHD, Micro -Edge, Anti-Glare, 15.6''/39.6cm, Win11, M365* Office24, Silver, 1.59kg, fd0624tu, FHD Camera, UHD Graphics Laptop</t>
         </is>
       </c>
       <c r="C211" t="inlineStr"/>
       <c r="D211" t="n">
-        <v>50000</v>
+        <v>48990</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
@@ -4866,11 +4866,11 @@
       </c>
       <c r="C212" t="inlineStr"/>
       <c r="D212" t="n">
-        <v>49850</v>
+        <v>47990</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -4887,11 +4887,11 @@
       </c>
       <c r="C213" t="inlineStr"/>
       <c r="D213" t="n">
-        <v>49990</v>
+        <v>47990</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -4908,11 +4908,11 @@
       </c>
       <c r="C214" t="inlineStr"/>
       <c r="D214" t="n">
-        <v>49820</v>
+        <v>46990</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-08</t>
         </is>
       </c>
     </row>
@@ -4929,11 +4929,11 @@
       </c>
       <c r="C215" t="inlineStr"/>
       <c r="D215" t="n">
-        <v>49820</v>
+        <v>46990</v>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
@@ -4950,11 +4950,11 @@
       </c>
       <c r="C216" t="inlineStr"/>
       <c r="D216" t="n">
-        <v>50400</v>
+        <v>46990</v>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-10</t>
         </is>
       </c>
     </row>
@@ -4971,11 +4971,11 @@
       </c>
       <c r="C217" t="inlineStr"/>
       <c r="D217" t="n">
-        <v>50390</v>
+        <v>46990</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-14</t>
         </is>
       </c>
     </row>
@@ -4992,11 +4992,11 @@
       </c>
       <c r="C218" t="inlineStr"/>
       <c r="D218" t="n">
-        <v>50150</v>
+        <v>46990</v>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-15</t>
         </is>
       </c>
     </row>
@@ -5013,11 +5013,11 @@
       </c>
       <c r="C219" t="inlineStr"/>
       <c r="D219" t="n">
-        <v>50040</v>
+        <v>46990</v>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-17</t>
         </is>
       </c>
     </row>
@@ -5034,11 +5034,11 @@
       </c>
       <c r="C220" t="inlineStr"/>
       <c r="D220" t="n">
-        <v>50040</v>
+        <v>48900</v>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-05-19</t>
         </is>
       </c>
     </row>
@@ -5055,11 +5055,11 @@
       </c>
       <c r="C221" t="inlineStr"/>
       <c r="D221" t="n">
-        <v>49670</v>
+        <v>48900</v>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-05-20</t>
         </is>
       </c>
     </row>
@@ -5076,11 +5076,11 @@
       </c>
       <c r="C222" t="inlineStr"/>
       <c r="D222" t="n">
-        <v>49480</v>
+        <v>50000</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-21</t>
         </is>
       </c>
     </row>
@@ -5097,11 +5097,11 @@
       </c>
       <c r="C223" t="inlineStr"/>
       <c r="D223" t="n">
-        <v>49470</v>
+        <v>49850</v>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-22</t>
         </is>
       </c>
     </row>
@@ -5118,11 +5118,11 @@
       </c>
       <c r="C224" t="inlineStr"/>
       <c r="D224" t="n">
-        <v>49300</v>
+        <v>49990</v>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>
@@ -5134,1356 +5134,1356 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U, (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge, FHD,15.6''/39.6cm, Win11,M365 Basic(1yr),Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
         </is>
       </c>
       <c r="C225" t="inlineStr"/>
       <c r="D225" t="n">
-        <v>47990</v>
+        <v>49820</v>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-24</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>HP 15, AMD Ryzen 5</t>
+          <t>HP 15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>HP 15, AMD Ryzen 5 7520U,(16GB LPDDR5, 512GB SSD), Anti-Glare, Micro-Edge, FHD, 15.6''/39.6cm, Win 11, Office 24,M365 Basic(1yr)*,Silver, 1.59kg, fc0690au, FHD Camera, Backlit KB Laptop</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
         </is>
       </c>
       <c r="C226" t="inlineStr"/>
       <c r="D226" t="n">
-        <v>53990</v>
+        <v>49820</v>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>HP 15, AMD Ryzen 5</t>
+          <t>HP 15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>HP 15, AMD Ryzen 5 7520U,(16GB LPDDR5, 512GB SSD), Anti-Glare, Micro-Edge, FHD, 15.6''/39.6cm, Win 11, Office 24,M365 Basic(1yr)*,Silver, 1.59kg, fc0690au, FHD Camera, Backlit KB Laptop</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
         </is>
       </c>
       <c r="C227" t="inlineStr"/>
       <c r="D227" t="n">
-        <v>53990</v>
+        <v>50400</v>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>HP 15, AMD Ryzen 5</t>
+          <t>HP 15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>HP 15, AMD Ryzen 5 7520U,(16GB LPDDR5, 512GB SSD), Anti-Glare, Micro-Edge, FHD, 15.6''/39.6cm, Win 11, Office 24,M365 Basic(1yr)*,Silver, 1.59kg, fc0690au, FHD Camera, Backlit KB Laptop</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
         </is>
       </c>
       <c r="C228" t="inlineStr"/>
       <c r="D228" t="n">
-        <v>54990</v>
+        <v>50390</v>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-27</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>hp_15,_amd_ryzen_5</t>
+          <t>HP 15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>HP 15, AMD Ryzen 5 7520U,(16GB LPDDR5, 512GB SSD), Anti-Glare, Micro-Edge, FHD, 15.6''/39.6cm, Win 11, Office 24,M365 Basic(1yr)*,Silver, 1.59kg, fc0690au, FHD Camera, Backlit KB Laptop</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
         </is>
       </c>
       <c r="C229" t="inlineStr"/>
       <c r="D229" t="n">
-        <v>56830</v>
+        <v>50150</v>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-28</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>HP 15, AMD Ryzen 7</t>
+          <t>HP 15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>HP 15, AMD Ryzen 7 7735HS (16GB DDR5,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365 Basic(1yr)* Office24, Silver, 1.59kg, fc1038AU, AMD Radeon FHD Camera w/Shutter, Backlit Laptop</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
         </is>
       </c>
       <c r="C230" t="inlineStr"/>
       <c r="D230" t="n">
-        <v>59990</v>
+        <v>50040</v>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>HP 15, Intel Core 5</t>
+          <t>HP 15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>HP 15, Intel Core 5 120U (14th Gen) 16GB DDR4, 512GB SSD, FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365 Basic(1yr), Office24, Silver,1.59kg, FD0640TU/682tu, FHD Camera w/Shutter, BL Laptop</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
         </is>
       </c>
       <c r="C231" t="inlineStr"/>
       <c r="D231" t="n">
-        <v>65990</v>
+        <v>50040</v>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>hp_15,_intel_core_5-120u</t>
+          <t>HP 15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>HP 15, Intel Core 5-120U (8GB DDR4, 512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365 Basic(1yr), Office Home24, Silver,1.59kg, fd0651TU, FHD Camera w/Privacy Shutter, Backlit Laptop</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
         </is>
       </c>
       <c r="C232" t="inlineStr"/>
       <c r="D232" t="n">
-        <v>57500</v>
+        <v>49670</v>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>HP 15, Intel Core Ultra</t>
+          <t>HP 15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>HP 15, Intel Core Ultra 5 125H (24GB DDR5, 1TB SSD), Micro-Edge, Anti-Glare, FHD, 15''/39.6cm, Win11, M365* Office24, Silver, 1.65kg, FD1458TU, FHD Camera, Backlit Laptop</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
         </is>
       </c>
       <c r="C233" t="inlineStr"/>
       <c r="D233" t="n">
-        <v>84990</v>
+        <v>49480</v>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>hp_15,_intel_core_i3-1315u-13th</t>
+          <t>HP 15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>HP 15, Intel Core i3-1315U-13th Gen Laptop (8GB DDR4 Ram,512GB SSD) Anti-Glare, Micro-Edge,15.6'" FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera Shutter, 15-fd0569TU</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
         </is>
       </c>
       <c r="C234" t="inlineStr"/>
       <c r="D234" t="n">
-        <v>49490</v>
+        <v>49470</v>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-12</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>hp_15,_intel_core_i3-1315u-13th</t>
+          <t>HP 15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>HP 15, Intel Core i3-1315U-13th Gen Laptop (8GB DDR4 Ram,512GB SSD) Anti-Glare, Micro-Edge,15.6'" FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera Shutter, 15-fd0569TU</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
         </is>
       </c>
       <c r="C235" t="inlineStr"/>
       <c r="D235" t="n">
-        <v>50900</v>
+        <v>49300</v>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>HP 255R G10 Notebook (AMD</t>
+          <t>HP 15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>HP 255R G10 Notebook (AMD Athlon Silver 7120U /8GB/512GB/DOS) 15.6-inch(39.6cm), Anti-Glare, HD Laptop, Radeon Graphics, Silver,1.52kg</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U, (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge, FHD,15.6''/39.6cm, Win11,M365 Basic(1yr),Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C236" t="inlineStr"/>
       <c r="D236" t="n">
-        <v>41700</v>
+        <v>47990</v>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>HP 255R G10 Notebook (AMD</t>
+          <t>HP 15, AMD Ryzen 5</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>HP 255R G10 Notebook (AMD Athlon Silver 7120U /8GB/512GB/DOS) 15.6-inch(39.6cm), Anti-Glare, HD Laptop, Radeon Graphics, Silver,1.52kg</t>
+          <t>HP 15, AMD Ryzen 5 7520U,(16GB LPDDR5, 512GB SSD), Anti-Glare, Micro-Edge, FHD, 15.6''/39.6cm, Win 11, Office 24,M365 Basic(1yr)*,Silver, 1.59kg, fc0690au, FHD Camera, Backlit KB Laptop</t>
         </is>
       </c>
       <c r="C237" t="inlineStr"/>
       <c r="D237" t="n">
-        <v>39340</v>
+        <v>53990</v>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-08</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>HP 255R G10 Notebook (AMD</t>
+          <t>HP 15, AMD Ryzen 5</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>HP 255R G10 Notebook (AMD Athlon Silver 7120U /8GB/512GB/DOS) 15.6-inch(39.6cm), Anti-Glare, HD Laptop, Radeon Graphics, Silver,1.52kg</t>
+          <t>HP 15, AMD Ryzen 5 7520U,(16GB LPDDR5, 512GB SSD), Anti-Glare, Micro-Edge, FHD, 15.6''/39.6cm, Win 11, Office 24,M365 Basic(1yr)*,Silver, 1.59kg, fc0690au, FHD Camera, Backlit KB Laptop</t>
         </is>
       </c>
       <c r="C238" t="inlineStr"/>
       <c r="D238" t="n">
-        <v>40409</v>
+        <v>53990</v>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>HP 255R G10 Notebook (AMD</t>
+          <t>HP 15, AMD Ryzen 5</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>HP 255R G10 Notebook (AMD Athlon Silver 7120U /8GB/512GB/DOS) 15.6-inch(39.6cm), Anti-Glare, HD Laptop, Radeon Graphics, Silver,1.52kg</t>
+          <t>HP 15, AMD Ryzen 5 7520U,(16GB LPDDR5, 512GB SSD), Anti-Glare, Micro-Edge, FHD, 15.6''/39.6cm, Win 11, Office 24,M365 Basic(1yr)*,Silver, 1.59kg, fc0690au, FHD Camera, Backlit KB Laptop</t>
         </is>
       </c>
       <c r="C239" t="inlineStr"/>
       <c r="D239" t="n">
-        <v>39618</v>
+        <v>54990</v>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>HP 255R G10 Notebook (AMD</t>
+          <t>hp_15,_amd_ryzen_5</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>HP 255R G10 Notebook (AMD Athlon Silver 7120U /8GB/512GB/DOS) 15.6-inch(39.6cm), Anti-Glare, HD Laptop, Radeon Graphics, Silver,1.52kg</t>
+          <t>HP 15, AMD Ryzen 5 7520U,(16GB LPDDR5, 512GB SSD), Anti-Glare, Micro-Edge, FHD, 15.6''/39.6cm, Win 11, Office 24,M365 Basic(1yr)*,Silver, 1.59kg, fc0690au, FHD Camera, Backlit KB Laptop</t>
         </is>
       </c>
       <c r="C240" t="inlineStr"/>
       <c r="D240" t="n">
-        <v>39525</v>
+        <v>56830</v>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>HP Omen, Intel Core Ultra</t>
+          <t>HP 15, AMD Ryzen 7</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>HP Omen, Intel Core Ultra 7 255H, 8GB RTX 5050, 24GB DDR5(Upgradeable) 1TB SSD, 2K, 165Hz, 3ms Response time, IPS, 16''/40.6cm, Win11, M365*Office24, Shadow Black, 2.43kg, am0240tx, RGB Gaming Laptop</t>
+          <t>HP 15, AMD Ryzen 7 7735HS (16GB DDR5,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365 Basic(1yr)* Office24, Silver, 1.59kg, fc1038AU, AMD Radeon FHD Camera w/Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C241" t="inlineStr"/>
       <c r="D241" t="n">
-        <v>129990</v>
+        <v>59990</v>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-14</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>HP OmniBook 3, AMD Ryzen</t>
+          <t>HP 15, Intel Core 5</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>HP OmniBook 3, AMD Ryzen AI 5 330 (24GB DDR5 RAM, 1TB SSD) FHD, Anti-Glare, 15.6''/39.6cm, Win11, Office24, Glacier Silver,1.7kg, fn0074AU, FHD Camera w/Shutter, FPR, Backlit KB, Next Gen AI Laptop</t>
+          <t>HP 15, Intel Core 5 120U (14th Gen) 16GB DDR4, 512GB SSD, FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365 Basic(1yr), Office24, Silver,1.59kg, FD0640TU/682tu, FHD Camera w/Shutter, BL Laptop</t>
         </is>
       </c>
       <c r="C242" t="inlineStr"/>
       <c r="D242" t="n">
-        <v>69990</v>
+        <v>65990</v>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>HP OmniBook 5 OLED (Previously</t>
+          <t>hp_15,_intel_core_5-120u</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>HP OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x, 1TB SSD) 2K, 14''/35.6cm, Win11, M365 Basic(1yr)* Office24, Silver, 1.35kg, he0015QU, Light-Weight, Next-Gen AI Laptop</t>
+          <t>HP 15, Intel Core 5-120U (8GB DDR4, 512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365 Basic(1yr), Office Home24, Silver,1.59kg, fd0651TU, FHD Camera w/Privacy Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C243" t="inlineStr"/>
       <c r="D243" t="n">
-        <v>69990</v>
+        <v>57500</v>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>HP OmniBook 5 OLED (Previously</t>
+          <t>HP 15, Intel Core Ultra</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>HP OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x, 512GB SSD) 2K, 14''/35.6cm, Win11, M365 Basic(1yr)* Office24, Silver, 1.35kg, he0014QU, Light-Weight, Next-Gen AI Laptop</t>
+          <t>HP 15, Intel Core Ultra 5 125H (24GB DDR5, 1TB SSD), Micro-Edge, Anti-Glare, FHD, 15''/39.6cm, Win11, M365* Office24, Silver, 1.65kg, FD1458TU, FHD Camera, Backlit Laptop</t>
         </is>
       </c>
       <c r="C244" t="inlineStr"/>
       <c r="D244" t="n">
-        <v>78990</v>
+        <v>84990</v>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>HP OmniBook 5 OLED (Previously</t>
+          <t>hp_15,_intel_core_i3-1315u-13th</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>HP OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x, 512GB SSD) 2K, 14''/35.6cm, Win11, M365 Basic(1yr)* Office24, Silver, 1.35kg, he0014QU, Light-Weight, Next-Gen AI Laptop</t>
+          <t>HP 15, Intel Core i3-1315U-13th Gen Laptop (8GB DDR4 Ram,512GB SSD) Anti-Glare, Micro-Edge,15.6'" FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera Shutter, 15-fd0569TU</t>
         </is>
       </c>
       <c r="C245" t="inlineStr"/>
       <c r="D245" t="n">
-        <v>66990</v>
+        <v>49490</v>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>hp_omnibook_x_flip_oled</t>
+          <t>hp_15,_intel_core_i3-1315u-13th</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>HP OmniBook X Flip OLED Intel Core Ultra 5 226V, 40 Tops (16GB LPDDR5x,1TB SSD) 3K, Touch, 120hz, 14''/35.6cm, Intel ARC Graphic,Win11, Office24, Meteor Silver, 1.38kg, fm0099TU,Pen, 2 in 1 AI Laptop</t>
+          <t>HP 15, Intel Core i3-1315U-13th Gen Laptop (8GB DDR4 Ram,512GB SSD) Anti-Glare, Micro-Edge,15.6'" FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera Shutter, 15-fd0569TU</t>
         </is>
       </c>
       <c r="C246" t="inlineStr"/>
       <c r="D246" t="n">
-        <v>115990</v>
+        <v>50900</v>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>hp_omnibook_3,_snapdragon_x</t>
+          <t>HP 255R G10 Notebook (AMD</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>HP Omnibook 3, Snapdragon X Processor 45 TOPS (16GB LPDDR5x,512GB SSD) 2K WUXGA, Anti-Glare, 14''/35.6cm, Win 11, M365*Office 24,Silver,1.42kg, hz0026QU, Lighter mini Charger, FHD IR Camera, AI Laptop</t>
+          <t>HP 255R G10 Notebook (AMD Athlon Silver 7120U /8GB/512GB/DOS) 15.6-inch(39.6cm), Anti-Glare, HD Laptop, Radeon Graphics, Silver,1.52kg</t>
         </is>
       </c>
       <c r="C247" t="inlineStr"/>
       <c r="D247" t="n">
-        <v>79990</v>
+        <v>41700</v>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-04-16</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>HP Omnibook 3, Snapdragon X</t>
+          <t>HP 255R G10 Notebook (AMD</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>HP Omnibook 3, Snapdragon X Processor, 45 TOPS (16GB LPDDR5x, 512GB SSD) 2K, WUXGA, IPS, 14''/35.6cm, Win 11, Office 24, Silver, 1.4kg, hz0026QU, FHD IR Camera, 42% Lighter mini GaN Charger, AI Laptop</t>
+          <t>HP 255R G10 Notebook (AMD Athlon Silver 7120U /8GB/512GB/DOS) 15.6-inch(39.6cm), Anti-Glare, HD Laptop, Radeon Graphics, Silver,1.52kg</t>
         </is>
       </c>
       <c r="C248" t="inlineStr"/>
       <c r="D248" t="n">
-        <v>69990</v>
+        <v>39340</v>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-10</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>HP Omnibook 3, Snapdragon X</t>
+          <t>HP 255R G10 Notebook (AMD</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>HP Omnibook 3, Snapdragon X Processor, 45 TOPS (16GB LPDDR5x, 512GB SSD) 2K, WUXGA, IPS, 14''/35.6cm, Win 11, Office 24, Silver, 1.4kg, hz0026QU, FHD IR Camera, 42% Lighter mini GaN Charger, AI Laptop</t>
+          <t>HP 255R G10 Notebook (AMD Athlon Silver 7120U /8GB/512GB/DOS) 15.6-inch(39.6cm), Anti-Glare, HD Laptop, Radeon Graphics, Silver,1.52kg</t>
         </is>
       </c>
       <c r="C249" t="inlineStr"/>
       <c r="D249" t="n">
-        <v>73990</v>
+        <v>40409</v>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-20</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>HP Omnibook 5 OLED (Previously</t>
+          <t>HP 255R G10 Notebook (AMD</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>HP Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x,1TB SSD) 2K OLED,16''/40.6cm, Win11, M365*Office24, Glacier Silver, 1.59kg, fb0001QU, Backlit, Next-Gen AI Laptop</t>
+          <t>HP 255R G10 Notebook (AMD Athlon Silver 7120U /8GB/512GB/DOS) 15.6-inch(39.6cm), Anti-Glare, HD Laptop, Radeon Graphics, Silver,1.52kg</t>
         </is>
       </c>
       <c r="C250" t="inlineStr"/>
       <c r="D250" t="n">
-        <v>78850</v>
+        <v>39618</v>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>hp_omnibook_5_oled_(previously</t>
+          <t>HP 255R G10 Notebook (AMD</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>HP Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor 45 Tops (16GB LPDDR5x, 1TB SSD) 2K,16''/40.6cm, Win11, Office24, Silver, 1.59kg, fb0001QU, Multi-Day Battery AI Laptop</t>
+          <t>HP 255R G10 Notebook (AMD Athlon Silver 7120U /8GB/512GB/DOS) 15.6-inch(39.6cm), Anti-Glare, HD Laptop, Radeon Graphics, Silver,1.52kg</t>
         </is>
       </c>
       <c r="C251" t="inlineStr"/>
       <c r="D251" t="n">
-        <v>77900</v>
+        <v>39525</v>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>hp_pavilion_plus,_intel_core</t>
+          <t>HP Omen, Intel Core Ultra</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>HP Pavilion Plus, Intel Core i5-1335U-13th Gen Laptop, (16GB LPDDR5x,512GB SSD),IPS, 300 nits, 14''(35.6cm) 2K,Win 11, M365 Basic(1yr), Office Home 24, Silver,1.38kg, 5MP Camera w/Shutter, ew0107TU</t>
+          <t>HP Omen, Intel Core Ultra 7 255H, 8GB RTX 5050, 24GB DDR5(Upgradeable) 1TB SSD, 2K, 165Hz, 3ms Response time, IPS, 16''/40.6cm, Win11, M365*Office24, Shadow Black, 2.43kg, am0240tx, RGB Gaming Laptop</t>
         </is>
       </c>
       <c r="C252" t="inlineStr"/>
       <c r="D252" t="n">
-        <v>63990</v>
+        <v>129990</v>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-10</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>hp_professional_15_(2026),_intel</t>
+          <t>HP OmniBook 3, AMD Ryzen</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>HP Professional 15 (2026), Intel (i3 14th Gen) Core 3 100U - (8 GB/512 GB SSD/Intel UHD Graphics/Windows 11 Home) Thin &amp; Light Business Laptop/15.6" Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
+          <t>HP OmniBook 3, AMD Ryzen AI 5 330 (24GB DDR5 RAM, 1TB SSD) FHD, Anti-Glare, 15.6''/39.6cm, Win11, Office24, Glacier Silver,1.7kg, fn0074AU, FHD Camera w/Shutter, FPR, Backlit KB, Next Gen AI Laptop</t>
         </is>
       </c>
       <c r="C253" t="inlineStr"/>
       <c r="D253" t="n">
-        <v>48990</v>
+        <v>69990</v>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>hp_professional_15_(2026),_intel</t>
+          <t>HP OmniBook 5 OLED (Previously</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>HP Professional 15 (2026), Intel (i3 14th Gen) Core 3 100U - (8 GB/512 GB SSD/Intel UHD Graphics/Windows 11 Home) Thin &amp; Light Business Laptop/15.6" Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
+          <t>HP OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x, 1TB SSD) 2K, 14''/35.6cm, Win11, M365 Basic(1yr)* Office24, Silver, 1.35kg, he0015QU, Light-Weight, Next-Gen AI Laptop</t>
         </is>
       </c>
       <c r="C254" t="inlineStr"/>
       <c r="D254" t="n">
-        <v>51899</v>
+        <v>69990</v>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-05-14</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>HP Smartchoice OmniBook 5 OLED</t>
+          <t>HP OmniBook 5 OLED (Previously</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>HP Smartchoice OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x, 1TB SSD) 2K, 14''/35.6cm, Win11, M365(1yr)*Office24, Silver,1.35kg, he0015QU,Light-Weight,Next-Gen AI Laptop</t>
+          <t>HP OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x, 512GB SSD) 2K, 14''/35.6cm, Win11, M365 Basic(1yr)* Office24, Silver, 1.35kg, he0014QU, Light-Weight, Next-Gen AI Laptop</t>
         </is>
       </c>
       <c r="C255" t="inlineStr"/>
       <c r="D255" t="n">
-        <v>82990</v>
+        <v>78990</v>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>HP Smartchoice OmniBook 5 OLED</t>
+          <t>HP OmniBook 5 OLED (Previously</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>HP Smartchoice OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x, 1TB SSD) 2K, 14''/35.6cm, Win11, M365(1yr)*Office24, Silver,1.35kg, he0015QU,Light-Weight,Next-Gen AI Laptop</t>
+          <t>HP OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x, 512GB SSD) 2K, 14''/35.6cm, Win11, M365 Basic(1yr)* Office24, Silver, 1.35kg, he0014QU, Light-Weight, Next-Gen AI Laptop</t>
         </is>
       </c>
       <c r="C256" t="inlineStr"/>
       <c r="D256" t="n">
-        <v>76990</v>
+        <v>66990</v>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>HP Smartchoice OmniBook 5 OLED</t>
+          <t>hp_omnibook_5_oled_(previously</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>HP Smartchoice OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x, 512GB SSD) 2K, 14''/35.6cm, Win11, M365(1yr)* Office24, Silver, 1.35kg, he0014QU, Next-Gen AI Laptop</t>
+          <t>HP OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor 45 Tops (16GB LPDDR5x, 512GB SSD), 2K 14''/35.6cm, Win11, Office24, Silver, 1.29kg, he0014QU, Multi-Day Battery, AI Laptop</t>
         </is>
       </c>
       <c r="C257" t="inlineStr"/>
       <c r="D257" t="n">
-        <v>78990</v>
+        <v>79990</v>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>HP Smartchoice OmniBook 5 OLED</t>
+          <t>hp_omnibook_x_flip_oled</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>HP Smartchoice OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x, 512GB SSD) 2K, 14''/35.6cm, Win11, M365(1yr)* Office24, Silver, 1.35kg, he0014QU, Next-Gen AI Laptop</t>
+          <t>HP OmniBook X Flip OLED Intel Core Ultra 5 226V, 40 Tops (16GB LPDDR5x,1TB SSD) 3K, Touch, 120hz, 14''/35.6cm, Intel ARC Graphic,Win11, Office24, Meteor Silver, 1.38kg, fm0099TU,Pen, 2 in 1 AI Laptop</t>
         </is>
       </c>
       <c r="C258" t="inlineStr"/>
       <c r="D258" t="n">
-        <v>79990</v>
+        <v>115990</v>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>HP Smartchoice Omnibook 5 OLED</t>
+          <t>hp_omnibook_3,_snapdragon_x</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>HP Smartchoice Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x,1TB SSD) 2K OLED,16''/40.6cm, Win11, M365(1yr)*Office24, Glacier Silver, 1.59kg, fb0001QU,Next-Gen AI Laptop</t>
+          <t>HP Omnibook 3, Snapdragon X Processor 45 TOPS (16GB LPDDR5x,512GB SSD) 2K WUXGA, Anti-Glare, 14''/35.6cm, Win 11, M365*Office 24,Silver,1.42kg, hz0026QU, Lighter mini Charger, FHD IR Camera, AI Laptop</t>
         </is>
       </c>
       <c r="C259" t="inlineStr"/>
       <c r="D259" t="n">
-        <v>68739</v>
+        <v>79990</v>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>HP Smartchoice Omnibook 5 OLED</t>
+          <t>HP Omnibook 3, Snapdragon X</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>HP Smartchoice Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x,1TB SSD) 2K OLED,16''/40.6cm, Win11, M365(1yr)*Office24, Glacier Silver, 1.59kg, fb0001QU,Next-Gen AI Laptop</t>
+          <t>HP Omnibook 3, Snapdragon X Processor, 45 TOPS (16GB LPDDR5x, 512GB SSD) 2K, WUXGA, IPS, 14''/35.6cm, Win 11, Office 24, Silver, 1.4kg, hz0026QU, FHD IR Camera, 42% Lighter mini GaN Charger, AI Laptop</t>
         </is>
       </c>
       <c r="C260" t="inlineStr"/>
       <c r="D260" t="n">
-        <v>68739</v>
+        <v>69990</v>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>HP Smartchoice Omnibook 5 OLED</t>
+          <t>HP Omnibook 3, Snapdragon X</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>HP Smartchoice Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x,1TB SSD) 2K OLED,16''/40.6cm, Win11, M365(1yr)*Office24, Glacier Silver, 1.59kg, fb0001QU,Next-Gen AI Laptop</t>
+          <t>HP Omnibook 3, Snapdragon X Processor, 45 TOPS (16GB LPDDR5x, 512GB SSD) 2K, WUXGA, IPS, 14''/35.6cm, Win 11, Office 24, Silver, 1.4kg, hz0026QU, FHD IR Camera, 42% Lighter mini GaN Charger, AI Laptop</t>
         </is>
       </c>
       <c r="C261" t="inlineStr"/>
       <c r="D261" t="n">
-        <v>68739</v>
+        <v>73990</v>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>HP Smartchoice Omnibook 5 OLED</t>
+          <t>HP Omnibook 5 OLED (Previously</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>HP Smartchoice Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x,1TB SSD) 2K OLED,16''/40.6cm, Win11, M365(1yr)*Office24, Glacier Silver, 1.59kg, fb0001QU,Next-Gen AI Laptop</t>
+          <t>HP Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x,1TB SSD) 2K OLED,16''/40.6cm, Win11, M365*Office24, Glacier Silver, 1.59kg, fb0001QU, Backlit, Next-Gen AI Laptop</t>
         </is>
       </c>
       <c r="C262" t="inlineStr"/>
       <c r="D262" t="n">
-        <v>68323</v>
+        <v>78850</v>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>HP Smartchoice Omnibook 5 OLED</t>
+          <t>hp_omnibook_5_oled_(previously</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>HP Smartchoice Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x,1TB SSD) 2K OLED,16''/40.6cm, Win11, M365(1yr)*Office24, Glacier Silver, 1.59kg, fb0001QU,Next-Gen AI Laptop</t>
+          <t>HP Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor 45 Tops (16GB LPDDR5x, 1TB SSD) 2K,16''/40.6cm, Win11, Office24, Silver, 1.59kg, fb0001QU, Multi-Day Battery AI Laptop</t>
         </is>
       </c>
       <c r="C263" t="inlineStr"/>
       <c r="D263" t="n">
-        <v>67940</v>
+        <v>77900</v>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>HP Smartchoice Omnibook 5 OLED</t>
+          <t>hp_pavilion_plus,_intel_core</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>HP Smartchoice Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x,1TB SSD) 2K OLED,16''/40.6cm, Win11, M365(1yr)*Office24, Glacier Silver, 1.59kg, fb0001QU,Next-Gen AI Laptop</t>
+          <t>HP Pavilion Plus, Intel Core i5-1335U-13th Gen Laptop, (16GB LPDDR5x,512GB SSD),IPS, 300 nits, 14''(35.6cm) 2K,Win 11, M365 Basic(1yr), Office Home 24, Silver,1.38kg, 5MP Camera w/Shutter, ew0107TU</t>
         </is>
       </c>
       <c r="C264" t="inlineStr"/>
       <c r="D264" t="n">
-        <v>67940</v>
+        <v>63990</v>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>HP Smartchoice Victus, 13th Gen</t>
+          <t>hp_professional_15_(2026),_intel</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>HP Smartchoice Victus, 13th Gen Intel Core i7-13620H, 8GB RTX 5050, 24GB DDR5(Upgradeable) 1TB SSD, 144Hz, FHD, 15.6''/39.6cm, Win11, M365* Office24, Mica Silver, 2.29kg, fa2309TX, RGB Gaming Laptop</t>
+          <t>HP Professional 15 (2026), Intel (i3 14th Gen) Core 3 100U - (8 GB/512 GB SSD/Intel UHD Graphics/Windows 11 Home) Thin &amp; Light Business Laptop/15.6" Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
         </is>
       </c>
       <c r="C265" t="inlineStr"/>
       <c r="D265" t="n">
-        <v>112990</v>
+        <v>48990</v>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>HP Smartchoice Victus, AMD Ryzen</t>
+          <t>hp_professional_15_(2026),_intel</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>HP Smartchoice Victus, AMD Ryzen 7 7445HS, 6GB RTX 3050, 16GB DDR5(Upgradeable) 512GB SSD, FHD, 144Hz, 300 nits, 15.6''/39.6cm, Win 11, M365* Office24, Blue, 2.29kg, fb3134AX/3120ax, Gaming Laptop</t>
+          <t>HP Professional 15 (2026), Intel (i3 14th Gen) Core 3 100U - (8 GB/512 GB SSD/Intel UHD Graphics/Windows 11 Home) Thin &amp; Light Business Laptop/15.6" Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
         </is>
       </c>
       <c r="C266" t="inlineStr"/>
       <c r="D266" t="n">
-        <v>78990</v>
+        <v>51899</v>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>HP Smartchoice Victus, AMD Ryzen</t>
+          <t>hp_professional_15_(2026),_intel</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>HP Smartchoice Victus, AMD Ryzen 7 7445HS, 6GB RTX 3050, 16GB DDR5(Upgradeable) 512GB SSD, FHD, 144Hz, 300 nits, 15.6''/39.6cm, Win 11, M365* Office24, Blue, 2.29kg, fb3134AX/3120ax, Gaming Laptop</t>
+          <t>HP Professional 15 (2026), Intel (i3 14th Gen) Core 3 100U - (8 GB/512 GB SSD/Intel UHD Graphics/Windows 11 Home) Thin &amp; Light Business Laptop/15.6" Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
         </is>
       </c>
       <c r="C267" t="inlineStr"/>
       <c r="D267" t="n">
-        <v>86990</v>
+        <v>51840</v>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>HP Smartchoice Victus, AMD Ryzen</t>
+          <t>HP Smartchoice OmniBook 5 OLED</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>HP Smartchoice Victus, AMD Ryzen 7 7445HS, 6GB RTX 3050, 16GB DDR5(Upgradeable) 512GB SSD, FHD, 144Hz, 300 nits, 15.6''/39.6cm, Win 11, M365* Office24, Blue, 2.29kg, fb3134AX/3120ax, Gaming Laptop</t>
+          <t>HP Smartchoice OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x, 1TB SSD) 2K, 14''/35.6cm, Win11, M365(1yr)*Office24, Silver,1.35kg, he0015QU,Light-Weight,Next-Gen AI Laptop</t>
         </is>
       </c>
       <c r="C268" t="inlineStr"/>
       <c r="D268" t="n">
-        <v>86990</v>
+        <v>82990</v>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>HP Victus, 14th Gen Intel</t>
+          <t>HP Smartchoice OmniBook 5 OLED</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>HP Victus, 14th Gen Intel Core i5-14450HX, 6GB RTX 3050, 24GB DDR5, 512GB SSD, FHD, 144Hz, 300 nits, IPS,15.6''/39.6cm, Win11, M365* Office24, Mica Silver, 2.3kg, fa2303tx/fa2315tx, RGB Gaming Laptop</t>
+          <t>HP Smartchoice OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x, 1TB SSD) 2K, 14''/35.6cm, Win11, M365(1yr)*Office24, Silver,1.35kg, he0015QU,Light-Weight,Next-Gen AI Laptop</t>
         </is>
       </c>
       <c r="C269" t="inlineStr"/>
       <c r="D269" t="n">
-        <v>103990</v>
+        <v>76990</v>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>HP Victus, AMD Ryzen 7</t>
+          <t>HP Smartchoice OmniBook 5 OLED</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>HP Victus, AMD Ryzen 7 7445HS, 4GB RTX 2050, 16GB DDR5(Upgradeable) 512GB SSD, FHD, 144Hz, 300 nits, IPS, 15.6'', Win11, M365* Office24, Blue, 2.29kg, fb3189ax /3122/ 23ax Backlit, Gaming Laptop</t>
+          <t>HP Smartchoice OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x, 512GB SSD) 2K, 14''/35.6cm, Win11, M365(1yr)* Office24, Silver, 1.35kg, he0014QU, Next-Gen AI Laptop</t>
         </is>
       </c>
       <c r="C270" t="inlineStr"/>
       <c r="D270" t="n">
-        <v>65990</v>
+        <v>78990</v>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-24</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>HP Victus, AMD Ryzen 7</t>
+          <t>HP Smartchoice OmniBook 5 OLED</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>HP Victus, AMD Ryzen 7 7445HS, 4GB RTX 2050, 16GB DDR5(Upgradeable) 512GB SSD, FHD, 144Hz, 300 nits, IPS, 15.6'', Win11, M365* Office24, Blue, 2.29kg, fb3189ax /3122/ 23ax Backlit, Gaming Laptop</t>
+          <t>HP Smartchoice OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x, 512GB SSD) 2K, 14''/35.6cm, Win11, M365(1yr)* Office24, Silver, 1.35kg, he0014QU, Next-Gen AI Laptop</t>
         </is>
       </c>
       <c r="C271" t="inlineStr"/>
       <c r="D271" t="n">
-        <v>65990</v>
+        <v>79990</v>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>HP Victus, AMD Ryzen 7</t>
+          <t>HP Smartchoice Omnibook 5 OLED</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>HP Victus, AMD Ryzen 7 7445HS, 6GB RTX 4050, 16GB DDR5(Upgradeable) 512GB SSD, 144Hz, IPS, 300nits, FHD, 15.6''/39.6cm, Win11, M365* Office24, Blue, 2.29kg, fb3130AX, Backlit, DTS Audio, Gaming Laptop</t>
+          <t>HP Smartchoice Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x,1TB SSD) 2K OLED,16''/40.6cm, Win11, M365(1yr)*Office24, Glacier Silver, 1.59kg, fb0001QU,Next-Gen AI Laptop</t>
         </is>
       </c>
       <c r="C272" t="inlineStr"/>
       <c r="D272" t="n">
-        <v>90990</v>
+        <v>68739</v>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>HP Victus, AMD Ryzen 7</t>
+          <t>HP Smartchoice Omnibook 5 OLED</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>HP Victus, AMD Ryzen 7 7445HS, 6GB RTX 4050, 16GB DDR5(Upgradeable) 512GB SSD, 144Hz, IPS, 300nits, FHD, 15.6''/39.6cm, Win11, M365* Office24, Blue, 2.29kg, fb3130AX, Backlit, DTS Audio, Gaming Laptop</t>
+          <t>HP Smartchoice Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x,1TB SSD) 2K OLED,16''/40.6cm, Win11, M365(1yr)*Office24, Glacier Silver, 1.59kg, fb0001QU,Next-Gen AI Laptop</t>
         </is>
       </c>
       <c r="C273" t="inlineStr"/>
       <c r="D273" t="n">
-        <v>91990</v>
+        <v>68739</v>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Lenovo Chromebook Intel Celeron N4500</t>
+          <t>HP Smartchoice Omnibook 5 OLED</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Lenovo Chromebook Intel Celeron N4500 (4GB RAM/64GB eMMC 5.1/11.6 Inch (29.46cm)/HD Display/2Wx2 Stereo Speakers/HD Camera/Chrome OS/Blue/1.21Kg), 82UY0014HA</t>
+          <t>HP Smartchoice Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x,1TB SSD) 2K OLED,16''/40.6cm, Win11, M365(1yr)*Office24, Glacier Silver, 1.59kg, fb0001QU,Next-Gen AI Laptop</t>
         </is>
       </c>
       <c r="C274" t="inlineStr"/>
       <c r="D274" t="n">
-        <v>21990</v>
+        <v>68739</v>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-27</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Lenovo Chromebook Intel Celeron N4500</t>
+          <t>HP Smartchoice Omnibook 5 OLED</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Lenovo Chromebook Intel Celeron N4500 (4GB RAM/64GB eMMC 5.1/11.6 Inch (29.46cm)/HD Display/2Wx2 Stereo Speakers/HD Camera/Chrome OS/Blue/1.21Kg), 82UY0014HA</t>
+          <t>HP Smartchoice Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x,1TB SSD) 2K OLED,16''/40.6cm, Win11, M365(1yr)*Office24, Glacier Silver, 1.59kg, fb0001QU,Next-Gen AI Laptop</t>
         </is>
       </c>
       <c r="C275" t="inlineStr"/>
       <c r="D275" t="n">
-        <v>18990</v>
+        <v>68323</v>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-31</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Lenovo IdeaPad Slim 3 13th</t>
+          <t>HP Smartchoice Omnibook 5 OLED</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Lenovo IdeaPad Slim 3 13th Gen Intel Core i5-13420H 15.3 inch (38.8cm) WUXGA IPS Laptop (16GB RAM/1TB SSD/Windows 11/MSO 365 Basic+Office 2024/Top Metal Cover/Backlit KB/Grey/1.6Kg), 83K100S0IN</t>
+          <t>HP Smartchoice Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x,1TB SSD) 2K OLED,16''/40.6cm, Win11, M365(1yr)*Office24, Glacier Silver, 1.59kg, fb0001QU,Next-Gen AI Laptop</t>
         </is>
       </c>
       <c r="C276" t="inlineStr"/>
       <c r="D276" t="n">
-        <v>70990</v>
+        <v>67940</v>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>lenovo_ideapad_slim_3_13th</t>
+          <t>HP Smartchoice Omnibook 5 OLED</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Lenovo IdeaPad Slim 3 13th Gen Intel Core i7 13620H, 16GB RAM, 512GB SSD, WUXGA IPS, 15.3"/38.8cm, Win 11, Office 2024, Top Metal Cover Grey, 1.6Kg, 83K100CJIN/S1IN, Backlit KB, Laptop</t>
+          <t>HP Smartchoice Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x,1TB SSD) 2K OLED,16''/40.6cm, Win11, M365(1yr)*Office24, Glacier Silver, 1.59kg, fb0001QU,Next-Gen AI Laptop</t>
         </is>
       </c>
       <c r="C277" t="inlineStr"/>
       <c r="D277" t="n">
-        <v>81990</v>
+        <v>67940</v>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-02</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>lenovo_ideapad_slim_3_13th</t>
+          <t>HP Smartchoice Victus, 13th Gen</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Lenovo IdeaPad Slim 3 13th Gen Intel Core i7 13620H, 16GB RAM, 512GB SSD, WUXGA IPS, 15.3"/38.8cm, Win 11, Office 2024, Top Metal Cover Grey, 1.6Kg, 83K100CJIN/S1IN, Backlit KB, Laptop</t>
+          <t>HP Smartchoice Victus, 13th Gen Intel Core i7-13620H, 8GB RTX 5050, 24GB DDR5(Upgradeable) 1TB SSD, 144Hz, FHD, 15.6''/39.6cm, Win11, M365* Office24, Mica Silver, 2.29kg, fa2309TX, RGB Gaming Laptop</t>
         </is>
       </c>
       <c r="C278" t="inlineStr"/>
       <c r="D278" t="n">
-        <v>79990</v>
+        <v>112990</v>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-05-10</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>lenovo_ideapad_slim_3,_13th</t>
+          <t>HP Smartchoice Victus, AMD Ryzen</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Lenovo IdeaPad Slim 3, 13th Gen Intel Core i5 13420H, 24GB RAM, 1TB SSD, WUXGA IPS, 15.3"/38.8cm, Windows 11, Office Home 2024, Grey, 1.6Kg, Backlit Keyboard, 1Yr ADP Free, 83K100PLIN, Laptop</t>
+          <t>HP Smartchoice Victus, AMD Ryzen 7 7445HS, 6GB RTX 3050, 16GB DDR5(Upgradeable) 512GB SSD, FHD, 144Hz, 300 nits, 15.6''/39.6cm, Win 11, M365* Office24, Blue, 2.29kg, fb3134AX/3120ax, Gaming Laptop</t>
         </is>
       </c>
       <c r="C279" t="inlineStr"/>
       <c r="D279" t="n">
-        <v>79990</v>
+        <v>78990</v>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>lenovo_ideapad_slim_3,_amd</t>
+          <t>HP Smartchoice Victus, AMD Ryzen</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Lenovo IdeaPad Slim 3, AMD Ryzen 7 8840HS, 24GB RAM, 1TB SSD, WUXGA IPS, AI PC, 15.3"/38.8cm, Backlit Keyboard, Windows 11, Office Home 2024, Grey, 1.6Kg, 1Yr ADP Free, 83KA004TIN, AI Powered Laptop</t>
+          <t>HP Smartchoice Victus, AMD Ryzen 7 7445HS, 6GB RTX 3050, 16GB DDR5(Upgradeable) 512GB SSD, FHD, 144Hz, 300 nits, 15.6''/39.6cm, Win 11, M365* Office24, Blue, 2.29kg, fb3134AX/3120ax, Gaming Laptop</t>
         </is>
       </c>
       <c r="C280" t="inlineStr"/>
       <c r="D280" t="n">
-        <v>87990</v>
+        <v>86990</v>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>lenovo_ideapad_slim_3,_amd</t>
+          <t>HP Smartchoice Victus, AMD Ryzen</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Lenovo IdeaPad Slim 3, AMD Ryzen 7 8840HS, 24GB RAM, 1TB SSD, WUXGA IPS, AI PC, 15.3"/38.8cm, Backlit Keyboard, Windows 11, Office Home 2024, Grey, 1.6Kg, 1Yr ADP Free, 83KA004TIN, AI Powered Laptop</t>
+          <t>HP Smartchoice Victus, AMD Ryzen 7 7445HS, 6GB RTX 3050, 16GB DDR5(Upgradeable) 512GB SSD, FHD, 144Hz, 300 nits, 15.6''/39.6cm, Win 11, M365* Office24, Blue, 2.29kg, fb3134AX/3120ax, Gaming Laptop</t>
         </is>
       </c>
       <c r="C281" t="inlineStr"/>
       <c r="D281" t="n">
-        <v>79990</v>
+        <v>86990</v>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>lenovo_ideapad_slim_5,_amd</t>
+          <t>HP Victus, 14th Gen Intel</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Lenovo IdeaPad Slim 5, AMD Ryzen 5 7535HS, 16GB RAM, 512GB SSD, WUXGA IPS, 13.3"/33.7cm, Windows 11, Microsoft 365 Basic + Office 2024, Grey, 1.6Kg, Backlit KB, 1Yr ADP Free, 83J2004HIN, Laptop</t>
+          <t>HP Victus, 14th Gen Intel Core i5-14450HX, 6GB RTX 3050, 24GB DDR5, 512GB SSD, FHD, 144Hz, 300 nits, IPS,15.6''/39.6cm, Win11, M365* Office24, Mica Silver, 2.3kg, fa2303tx/fa2315tx, RGB Gaming Laptop</t>
         </is>
       </c>
       <c r="C282" t="inlineStr"/>
       <c r="D282" t="n">
-        <v>72990</v>
+        <v>103990</v>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-10</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Lenovo Ideapad Slim 3 AMD</t>
+          <t>HP Victus, AMD Ryzen 7</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Lenovo Ideapad Slim 3 AMD Ryzen 5 7520U 15.6" (39.6cm) FHD Thin and Light Laptop (16GB/512GB SSD/Windows 11/Microsoft 365 Basic + Office Home 2024/Backlit Keyboard/Grey/1.6Kg), 82XQ00XDIN</t>
+          <t>HP Victus, AMD Ryzen 7 7445HS, 4GB RTX 2050, 16GB DDR5(Upgradeable) 512GB SSD, FHD, 144Hz, 300 nits, IPS, 15.6'', Win11, M365* Office24, Blue, 2.29kg, fb3189ax /3122/ 23ax Backlit, Gaming Laptop</t>
         </is>
       </c>
       <c r="C283" t="inlineStr"/>
       <c r="D283" t="n">
-        <v>50750</v>
+        <v>65990</v>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-21</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Lenovo LOQ 2024, Intel Core</t>
+          <t>HP Victus, AMD Ryzen 7</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Lenovo LOQ 2024, Intel Core i5-13450HX, 13th Gen, NVIDIA RTX 4050-6GB, 16GB RAM, 512GB SSD, FHD 144Hz, 15.6"/39.6cm, Windows 11, Office Home 2024, Grey, 2.4Kg, 83DV018JIN, 1Yr ADP Free Gaming Laptop</t>
+          <t>HP Victus, AMD Ryzen 7 7445HS, 4GB RTX 2050, 16GB DDR5(Upgradeable) 512GB SSD, FHD, 144Hz, 300 nits, IPS, 15.6'', Win11, M365* Office24, Blue, 2.29kg, fb3189ax /3122/ 23ax Backlit, Gaming Laptop</t>
         </is>
       </c>
       <c r="C284" t="inlineStr"/>
       <c r="D284" t="n">
-        <v>100544</v>
+        <v>65990</v>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-22</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Lenovo LOQ 2025 AMD Ryzen</t>
+          <t>HP Victus, AMD Ryzen 7</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Lenovo LOQ 2025 AMD Ryzen 7 250| NVIDIA RTX 5050 8GB (16GB RAM/1TB SSD/144Hz Refresh Rate/440 AI TOPS/15.6" (39.6cm)/Windows 11/Office 2024/3 Mon. Game Pass/Grey/2.4Kg), 83JG008KIN</t>
+          <t>HP Victus, AMD Ryzen 7 7445HS, 6GB RTX 4050, 16GB DDR5(Upgradeable) 512GB SSD, 144Hz, IPS, 300nits, FHD, 15.6''/39.6cm, Win11, M365* Office24, Blue, 2.29kg, fb3130AX, Backlit, DTS Audio, Gaming Laptop</t>
         </is>
       </c>
       <c r="C285" t="inlineStr"/>
       <c r="D285" t="n">
-        <v>134990</v>
+        <v>90990</v>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Lenovo LOQ 2025 Intel Core</t>
+          <t>HP Victus, AMD Ryzen 7</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Lenovo LOQ 2025 Intel Core i7-14700HX| NVIDIA RTX 5060 8GB (32GB RAM/1TB SSD/144Hz Refresh Rate/572 AI TOPS/15.6" (39.6cm)/Windows 11/Office 2024/3 Mon. Game Pass/Grey/2.4Kg), 83JE00T3IN</t>
+          <t>HP Victus, AMD Ryzen 7 7445HS, 6GB RTX 4050, 16GB DDR5(Upgradeable) 512GB SSD, 144Hz, IPS, 300nits, FHD, 15.6''/39.6cm, Win11, M365* Office24, Blue, 2.29kg, fb3130AX, Backlit, DTS Audio, Gaming Laptop</t>
         </is>
       </c>
       <c r="C286" t="inlineStr"/>
       <c r="D286" t="n">
-        <v>157990</v>
+        <v>91990</v>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Lenovo LOQ AMD Ryzen 5</t>
+          <t>Lenovo Chromebook Intel Celeron N4500</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Lenovo LOQ AMD Ryzen 5 7235HS | NVIDIA RTX 4050 6GB (16GB RAM/512GB SSD/144Hz Refresh Rate/15.6" (39.6cm)/Windows 11/Office Home 2024/3 Mon. Game Pass/Grey/2.4Kg), 83JC00NYIN AI Gaming Laptop</t>
+          <t>Lenovo Chromebook Intel Celeron N4500 (4GB RAM/64GB eMMC 5.1/11.6 Inch (29.46cm)/HD Display/2Wx2 Stereo Speakers/HD Camera/Chrome OS/Blue/1.21Kg), 82UY0014HA</t>
         </is>
       </c>
       <c r="C287" t="inlineStr"/>
       <c r="D287" t="n">
-        <v>88990</v>
+        <v>21990</v>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Lenovo LOQ, 13th Gen Intel</t>
+          <t>Lenovo Chromebook Intel Celeron N4500</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Lenovo LOQ, 13th Gen Intel Core i7 13700HX, RTX 5050-8GB, 16GB RAM, 1TB SSD, FHD, 15.6"/39.6cm, 144Hz, Windows 11, Office 2024, Grey, 2.4Kg, 440 AI Tops, 3 Mon. Game Pass, 83JE00U7IN, AI Gaming Laptop</t>
+          <t>Lenovo Chromebook Intel Celeron N4500 (4GB RAM/64GB eMMC 5.1/11.6 Inch (29.46cm)/HD Display/2Wx2 Stereo Speakers/HD Camera/Chrome OS/Blue/1.21Kg), 82UY0014HA</t>
         </is>
       </c>
       <c r="C288" t="inlineStr"/>
       <c r="D288" t="n">
-        <v>121869</v>
+        <v>18990</v>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Lenovo Legion 7 2025 Intel</t>
+          <t>Lenovo IdeaPad Slim 3 13th</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Lenovo Legion 7 2025 Intel Core Ultra 9 275HX| NVIDIA RTX 5070 8GB (32GB RAM/1TB SSD/WQXGA OLED/240Hz/16(40.64cm)/Windows 11/Office 2024+AI Now/White/2.0Kg), 83KY001GIN AI Powered Gaming Laptop</t>
+          <t>Lenovo IdeaPad Slim 3 13th Gen Intel Core i5-13420H 15.3 inch (38.8cm) WUXGA IPS Laptop (16GB RAM/1TB SSD/Windows 11/MSO 365 Basic+Office 2024/Top Metal Cover/Backlit KB/Grey/1.6Kg), 83K100S0IN</t>
         </is>
       </c>
       <c r="C289" t="inlineStr"/>
       <c r="D289" t="n">
-        <v>239391</v>
+        <v>70990</v>
       </c>
       <c r="E289" t="inlineStr">
         <is>
@@ -6494,143 +6494,143 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Lenovo Legion Pro 5 2025</t>
+          <t>lenovo_ideapad_slim_3_13th</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Lenovo Legion Pro 5 2025 AMD Ryzen 9 9955HX | NVIDIA RTX 5060 8GB (32GB RAM/1TB SSD/WQXGA OLED/165Hz/16 (40.6cm)/Windows 11/Office 2024+AI Now/Black/2.3Kg), 83F2004CIN AI Powered Gaming Laptop</t>
+          <t>Lenovo IdeaPad Slim 3 13th Gen Intel Core i7 13620H, 16GB RAM, 512GB SSD, WUXGA IPS, 15.3"/38.8cm, Win 11, Office 2024, Top Metal Cover Grey, 1.6Kg, 83K100CJIN/S1IN, Backlit KB, Laptop</t>
         </is>
       </c>
       <c r="C290" t="inlineStr"/>
       <c r="D290" t="n">
-        <v>245490</v>
+        <v>81990</v>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Lenovo Legion Pro 5 2025</t>
+          <t>lenovo_ideapad_slim_3_13th</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Lenovo Legion Pro 5 2025 AMD Ryzen 9 9955HX | NVIDIA RTX 5060 8GB (32GB RAM/1TB SSD/WQXGA OLED/165Hz/16 (40.6cm)/Windows 11/Office 2024+AI Now/Black/2.3Kg), 83F2004CIN AI Powered Gaming Laptop</t>
+          <t>Lenovo IdeaPad Slim 3 13th Gen Intel Core i7 13620H, 16GB RAM, 512GB SSD, WUXGA IPS, 15.3"/38.8cm, Win 11, Office 2024, Top Metal Cover Grey, 1.6Kg, 83K100CJIN/S1IN, Backlit KB, Laptop</t>
         </is>
       </c>
       <c r="C291" t="inlineStr"/>
       <c r="D291" t="n">
-        <v>245490</v>
+        <v>79990</v>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Lenovo Legion Pro 5 2025</t>
+          <t>lenovo_ideapad_slim_3,_13th</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Lenovo Legion Pro 5 2025 AMD Ryzen 9 9955HX | NVIDIA RTX 5060 8GB (32GB RAM/1TB SSD/WQXGA OLED/165Hz/16 (40.6cm)/Windows 11/Office 2024+AI Now/Black/2.3Kg), 83F2004CIN AI Powered Gaming Laptop</t>
+          <t>Lenovo IdeaPad Slim 3, 13th Gen Intel Core i5 13420H, 24GB RAM, 1TB SSD, WUXGA IPS, 15.3"/38.8cm, Windows 11, Office Home 2024, Grey, 1.6Kg, Backlit Keyboard, 1Yr ADP Free, 83K100PLIN, Laptop</t>
         </is>
       </c>
       <c r="C292" t="inlineStr"/>
       <c r="D292" t="n">
-        <v>245490</v>
+        <v>79990</v>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Lenovo Legion Pro 5 2025</t>
+          <t>lenovo_ideapad_slim_3,_amd</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Lenovo Legion Pro 5 2025 AMD Ryzen 9 9955HX | NVIDIA RTX 5060 8GB (32GB RAM/1TB SSD/WQXGA OLED/165Hz/16 (40.6cm)/Windows 11/Office 2024+AI Now/Black/2.3Kg), 83F2004CIN AI Powered Gaming Laptop</t>
+          <t>Lenovo IdeaPad Slim 3, AMD Ryzen 7 8840HS, 24GB RAM, 1TB SSD, WUXGA IPS, AI PC, 15.3"/38.8cm, Backlit Keyboard, Windows 11, Office Home 2024, Grey, 1.6Kg, 1Yr ADP Free, 83KA004TIN, AI Powered Laptop</t>
         </is>
       </c>
       <c r="C293" t="inlineStr"/>
       <c r="D293" t="n">
-        <v>245490</v>
+        <v>87990</v>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Lenovo Legion Pro 7 FIFA</t>
+          <t>lenovo_ideapad_slim_3,_amd</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Lenovo Legion Pro 7 FIFA World Cup 26 Edition Intel Core Ultra 9 275HX | NVIDIA RTX 5070Ti 12GB (32GB RAM/1TB SSD/WQXGA OLED/240Hz/16(40.6cm)/Windows 11/Black/2.4Kg), 83F500HPIN AI Gaming Laptop</t>
+          <t>Lenovo IdeaPad Slim 3, AMD Ryzen 7 8840HS, 24GB RAM, 1TB SSD, WUXGA IPS, AI PC, 15.3"/38.8cm, Backlit Keyboard, Windows 11, Office Home 2024, Grey, 1.6Kg, 1Yr ADP Free, 83KA004TIN, AI Powered Laptop</t>
         </is>
       </c>
       <c r="C294" t="inlineStr"/>
       <c r="D294" t="n">
-        <v>319990</v>
+        <v>79990</v>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Lenovo Smartchoice Ideapad 5 2-in-1</t>
+          <t>lenovo_ideapad_slim_3,_amd</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Lenovo Smartchoice Ideapad 5 2-in-1 13th Gen Intel Core i5-13420H (16GB RAM/512GB SSD/Windows 11/Office Home 2024/WUXGA IPS/14 (35.5cm)/Touchscreen 2-in-1/3Mon.Game Pass/Grey/1.6kg), 83KX0059IN Laptop</t>
+          <t>Lenovo IdeaPad Slim 3, AMD Ryzen 7 8840HS, 24GB RAM, 1TB SSD, WUXGA IPS, AI PC, 15.3"/38.8cm, Backlit Keyboard, Windows 11, Office Home 2024, Grey, 1.6Kg, 1Yr ADP Free, 83KA004TIN, AI Powered Laptop</t>
         </is>
       </c>
       <c r="C295" t="inlineStr"/>
       <c r="D295" t="n">
-        <v>74490</v>
+        <v>79990</v>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>lenovo_thinkbook_14,_amd_ryzen</t>
+          <t>lenovo_ideapad_slim_5,_amd</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Lenovo ThinkBook 14, AMD Ryzen 5 220, 16GB RAM, 1TB SSD, WUXGA IPS 14” (35.56cm), Windows 11 Home, Arctic Grey, 1.36Kg, 21V0A01SIG, Fingerprint, Backlit, 400 Nits, 1Y Warranty, Laptop</t>
+          <t>Lenovo IdeaPad Slim 5, AMD Ryzen 5 7535HS, 16GB RAM, 512GB SSD, WUXGA IPS, 13.3"/33.7cm, Windows 11, Microsoft 365 Basic + Office 2024, Grey, 1.6Kg, Backlit KB, 1Yr ADP Free, 83J2004HIN, Laptop</t>
         </is>
       </c>
       <c r="C296" t="inlineStr"/>
       <c r="D296" t="n">
-        <v>90990</v>
+        <v>72990</v>
       </c>
       <c r="E296" t="inlineStr">
         <is>
@@ -6641,1615 +6641,1972 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>lenovo_thinkbook_14,_amd_ryzen</t>
+          <t>Lenovo Ideapad Slim 3 AMD</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Lenovo ThinkBook 14, AMD Ryzen 5 220, 16GB RAM, 1TB SSD, WUXGA IPS 14” (35.56cm), Windows 11 Home, Arctic Grey, 1.36Kg, 21V0A01SIG, Fingerprint, Backlit, 400 Nits, 1Y Warranty, Laptop</t>
+          <t>Lenovo Ideapad Slim 3 AMD Ryzen 5 7520U 15.6" (39.6cm) FHD Thin and Light Laptop (16GB/512GB SSD/Windows 11/Microsoft 365 Basic + Office Home 2024/Backlit Keyboard/Grey/1.6Kg), 82XQ00XDIN</t>
         </is>
       </c>
       <c r="C297" t="inlineStr"/>
       <c r="D297" t="n">
-        <v>92990</v>
+        <v>50750</v>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-05-14</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Lenovo ThinkBook 15 G5 AMD</t>
+          <t>Lenovo LOQ 2024, Intel Core</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Lenovo ThinkBook 15 G5 AMD Ryzen 7 7730U 15.6" FHD Antiglare 250 Nits Thin and Light Laptop (8GB RAM/512GB SSD/Windows 11 Home/Fingerprint Reader/Backlit/Mineral Grey/1 Year Onsite/1.7 kg), 21JFA00BIN</t>
+          <t>Lenovo LOQ 2024, Intel Core i5-13450HX, 13th Gen, NVIDIA RTX 4050-6GB, 16GB RAM, 512GB SSD, FHD 144Hz, 15.6"/39.6cm, Windows 11, Office Home 2024, Grey, 2.4Kg, 83DV018JIN, 1Yr ADP Free Gaming Laptop</t>
         </is>
       </c>
       <c r="C298" t="inlineStr"/>
       <c r="D298" t="n">
-        <v>59999</v>
+        <v>100544</v>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>lenovo_thinkbook_16_amd_ryzen</t>
+          <t>Lenovo LOQ 2025 AMD Ryzen</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Lenovo ThinkBook 16 AMD Ryzen 5 7535HS (8GB RAM/512GB SSD/Win 11 Home/Office 2024/Backlit Keyboard/Fingerprint) 16" WUXGA IPS 300 Nits Thin &amp; Light Laptop/1Y Warranty/Aluminium Top/1.7kg, 21MWA0BRIN</t>
+          <t>Lenovo LOQ 2025 AMD Ryzen 7 250| NVIDIA RTX 5050 8GB (16GB RAM/1TB SSD/144Hz Refresh Rate/440 AI TOPS/15.6" (39.6cm)/Windows 11/Office 2024/3 Mon. Game Pass/Grey/2.4Kg), 83JG008KIN</t>
         </is>
       </c>
       <c r="C299" t="inlineStr"/>
       <c r="D299" t="n">
-        <v>65063</v>
+        <v>134990</v>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>lenovo_thinkbook_16,_amd_ryzen</t>
+          <t>Lenovo LOQ 2025 Intel Core</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Lenovo ThinkBook 16, AMD Ryzen 5 7535HS, 16GB RAM, 512GB SSD, WUXGA IPS 16", Windows 11 Home, Office 2024, 1.7kg, 21MWA0BSIN, Backlit Keyboard, Fingerprint, 300 Nits, 1Y Warranty, Aluminium Top Laptop</t>
+          <t>Lenovo LOQ 2025 Intel Core i7-14700HX| NVIDIA RTX 5060 8GB (32GB RAM/1TB SSD/144Hz Refresh Rate/572 AI TOPS/15.6" (39.6cm)/Windows 11/Office 2024/3 Mon. Game Pass/Grey/2.4Kg), 83JE00T3IN</t>
         </is>
       </c>
       <c r="C300" t="inlineStr"/>
       <c r="D300" t="n">
-        <v>84500</v>
+        <v>157990</v>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Lenovo ThinkBook 16, Intel Core</t>
+          <t>Lenovo LOQ AMD Ryzen 5</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Lenovo ThinkBook 16, Intel Core Ultra 9 185H, 16GB RAM, 512GB SSD, WUXGA IPS 16” (40.64cm), Win 11 Home, Arctic Grey, 1.7Kg, 21SKA0J5IG, Fingerprint, Backlit, 300 Nits, 1Y Warranty, AI Powered Laptop</t>
+          <t>Lenovo LOQ AMD Ryzen 5 7235HS | NVIDIA RTX 4050 6GB (16GB RAM/512GB SSD/144Hz Refresh Rate/15.6" (39.6cm)/Windows 11/Office Home 2024/3 Mon. Game Pass/Grey/2.4Kg), 83JC00NYIN AI Gaming Laptop</t>
         </is>
       </c>
       <c r="C301" t="inlineStr"/>
       <c r="D301" t="n">
-        <v>94990</v>
+        <v>88990</v>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Lenovo V14 Intel Core i3</t>
+          <t>Lenovo LOQ, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Lenovo V14 Intel Core i3 13th Gen 14" FHD (1920x1080) Antiglare 250 Nits Thin and Light Laptop (16GB RAM/512GB SSD/Windows 11 Home/Office Home 2024/Iron Grey/1.43 kg), 83A0A0PCIN</t>
+          <t>Lenovo LOQ, 13th Gen Intel Core i7 13700HX, RTX 5050-8GB, 16GB RAM, 1TB SSD, FHD, 15.6"/39.6cm, 144Hz, Windows 11, Office 2024, Grey, 2.4Kg, 440 AI Tops, 3 Mon. Game Pass, 83JE00U7IN, AI Gaming Laptop</t>
         </is>
       </c>
       <c r="C302" t="inlineStr"/>
       <c r="D302" t="n">
-        <v>70990</v>
+        <v>121869</v>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Lenovo V14 Intel Core i3</t>
+          <t>Lenovo Legion 7 2025 Intel</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Lenovo V14 Intel Core i3 13th Gen 14" FHD (1920x1080) Antiglare 250 Nits Thin and Light Laptop (16GB RAM/512GB SSD/Windows 11 Home/Office Home 2024/Iron Grey/1.43 kg), 83A0A0PCIN</t>
+          <t>Lenovo Legion 7 2025 Intel Core Ultra 9 275HX| NVIDIA RTX 5070 8GB (32GB RAM/1TB SSD/WQXGA OLED/240Hz/16(40.64cm)/Windows 11/Office 2024+AI Now/White/2.0Kg), 83KY001GIN AI Powered Gaming Laptop</t>
         </is>
       </c>
       <c r="C303" t="inlineStr"/>
       <c r="D303" t="n">
-        <v>70990</v>
+        <v>239391</v>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-05-08</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>lenovo_v14_intel_core_i3</t>
+          <t>Lenovo Legion Pro 5 2025</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Lenovo V14 Intel Core i3 13th Gen 14" FHD (1920x1080) Antiglare 250 Nits Thin and Light Laptop (16GB RAM/512GB SSD/Windows 11 Home/Office Home 2024/Iron Grey/1.43 kg), 83A0A0PCIN</t>
+          <t>Lenovo Legion Pro 5 2025 AMD Ryzen 9 9955HX | NVIDIA RTX 5060 8GB (32GB RAM/1TB SSD/WQXGA OLED/165Hz/16 (40.6cm)/Windows 11/Office 2024+AI Now/Black/2.3Kg), 83F2004CIN AI Powered Gaming Laptop</t>
         </is>
       </c>
       <c r="C304" t="inlineStr"/>
       <c r="D304" t="n">
-        <v>70990</v>
+        <v>245490</v>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 (2024), AMD</t>
+          <t>Lenovo Legion Pro 5 2025</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 (2024), AMD Ryzen 3 7320U Quad Core - (8GB/512GB SSD/AMD Radeon Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" FHD Display/Arctic Grey/1.57 kg/MS Office 2021</t>
+          <t>Lenovo Legion Pro 5 2025 AMD Ryzen 9 9955HX | NVIDIA RTX 5060 8GB (32GB RAM/1TB SSD/WQXGA OLED/165Hz/16 (40.6cm)/Windows 11/Office 2024+AI Now/Black/2.3Kg), 83F2004CIN AI Powered Gaming Laptop</t>
         </is>
       </c>
       <c r="C305" t="inlineStr"/>
       <c r="D305" t="n">
-        <v>44200</v>
+        <v>245490</v>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-24</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 (2024), AMD</t>
+          <t>Lenovo Legion Pro 5 2025</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 (2024), AMD Ryzen 3 7320U Quad Core - (8GB/512GB SSD/AMD Radeon Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" FHD Display/Arctic Grey/1.57 kg/MS Office 2021</t>
+          <t>Lenovo Legion Pro 5 2025 AMD Ryzen 9 9955HX | NVIDIA RTX 5060 8GB (32GB RAM/1TB SSD/WQXGA OLED/165Hz/16 (40.6cm)/Windows 11/Office 2024+AI Now/Black/2.3Kg), 83F2004CIN AI Powered Gaming Laptop</t>
         </is>
       </c>
       <c r="C306" t="inlineStr"/>
       <c r="D306" t="n">
-        <v>44490</v>
+        <v>245490</v>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 (2024), AMD</t>
+          <t>Lenovo Legion Pro 5 2025</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 (2024), AMD Ryzen 3 7320U Quad Core - (8GB/512GB SSD/AMD Radeon Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" FHD Display/Arctic Grey/1.57 kg/MS Office 2021</t>
+          <t>Lenovo Legion Pro 5 2025 AMD Ryzen 9 9955HX | NVIDIA RTX 5060 8GB (32GB RAM/1TB SSD/WQXGA OLED/165Hz/16 (40.6cm)/Windows 11/Office 2024+AI Now/Black/2.3Kg), 83F2004CIN AI Powered Gaming Laptop</t>
         </is>
       </c>
       <c r="C307" t="inlineStr"/>
       <c r="D307" t="n">
-        <v>44490</v>
+        <v>245490</v>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 (2024), AMD</t>
+          <t>Lenovo Legion Pro 7 FIFA</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 (2024), AMD Ryzen 3 7320U Quad Core - (8GB/512GB SSD/AMD Radeon Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" FHD Display/Arctic Grey/1.57 kg/MS Office 2021</t>
+          <t>Lenovo Legion Pro 7 FIFA World Cup 26 Edition Intel Core Ultra 9 275HX | NVIDIA RTX 5070Ti 12GB (32GB RAM/1TB SSD/WQXGA OLED/240Hz/16(40.6cm)/Windows 11/Black/2.4Kg), 83F500HPIN AI Gaming Laptop</t>
         </is>
       </c>
       <c r="C308" t="inlineStr"/>
       <c r="D308" t="n">
-        <v>44500</v>
+        <v>319990</v>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-15</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 (2024), AMD</t>
+          <t>Lenovo Smartchoice Ideapad 5 2-in-1</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 (2024), AMD Ryzen 3 7320U Quad Core - (8GB/512GB SSD/AMD Radeon Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" FHD Display/Arctic Grey/1.57 kg/MS Office 2021</t>
+          <t>Lenovo Smartchoice Ideapad 5 2-in-1 13th Gen Intel Core i5-13420H (16GB RAM/512GB SSD/Windows 11/Office Home 2024/WUXGA IPS/14 (35.5cm)/Touchscreen 2-in-1/3Mon.Game Pass/Grey/1.6kg), 83KX0059IN Laptop</t>
         </is>
       </c>
       <c r="C309" t="inlineStr"/>
       <c r="D309" t="n">
-        <v>49999</v>
+        <v>74490</v>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 (2024), AMD</t>
+          <t>lenovo_thinkbook_14,_amd_ryzen</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 (2024), AMD Ryzen 3 7320U Quad Core - (8GB/512GB SSD/AMD Radeon Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" FHD Display/Arctic Grey/1.57 kg/MS Office 2021</t>
+          <t>Lenovo ThinkBook 14, AMD Ryzen 5 220, 16GB RAM, 1TB SSD, WUXGA IPS 14” (35.56cm), Windows 11 Home, Arctic Grey, 1.36Kg, 21V0A01SIG, Fingerprint, Backlit, 400 Nits, 1Y Warranty, Laptop</t>
         </is>
       </c>
       <c r="C310" t="inlineStr"/>
       <c r="D310" t="n">
-        <v>49890</v>
+        <v>90990</v>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon</t>
+          <t>lenovo_thinkbook_14,_amd_ryzen</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo ThinkBook 14, AMD Ryzen 5 220, 16GB RAM, 1TB SSD, WUXGA IPS 14” (35.56cm), Windows 11 Home, Arctic Grey, 1.36Kg, 21V0A01SIG, Fingerprint, Backlit, 400 Nits, 1Y Warranty, Laptop</t>
         </is>
       </c>
       <c r="C311" t="inlineStr"/>
       <c r="D311" t="n">
-        <v>41999</v>
+        <v>92990</v>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon</t>
+          <t>lenovo_thinkbook_14,_amd_ryzen</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo ThinkBook 14, AMD Ryzen 5 220, 16GB RAM, 1TB SSD, WUXGA IPS 14” (35.56cm), Windows 11 Home, Arctic Grey, 1.36Kg, 21V0A01SIG, Fingerprint, Backlit, 400 Nits, 1Y Warranty, Laptop</t>
         </is>
       </c>
       <c r="C312" t="inlineStr"/>
       <c r="D312" t="n">
-        <v>41999</v>
+        <v>92990</v>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon</t>
+          <t>Lenovo ThinkBook 15 G5 AMD</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo ThinkBook 15 G5 AMD Ryzen 7 7730U 15.6" FHD Antiglare 250 Nits Thin and Light Laptop (8GB RAM/512GB SSD/Windows 11 Home/Fingerprint Reader/Backlit/Mineral Grey/1 Year Onsite/1.7 kg), 21JFA00BIN</t>
         </is>
       </c>
       <c r="C313" t="inlineStr"/>
       <c r="D313" t="n">
-        <v>41999</v>
+        <v>59999</v>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-22</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon</t>
+          <t>lenovo_thinkbook_16_amd_ryzen</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo ThinkBook 16 AMD Ryzen 5 7535HS (8GB RAM/512GB SSD/Win 11 Home/Office 2024/Backlit Keyboard/Fingerprint) 16" WUXGA IPS 300 Nits Thin &amp; Light Laptop/1Y Warranty/Aluminium Top/1.7kg, 21MWA0BRIN</t>
         </is>
       </c>
       <c r="C314" t="inlineStr"/>
       <c r="D314" t="n">
-        <v>42999</v>
+        <v>65063</v>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon</t>
+          <t>lenovo_thinkbook_16_amd_ryzen</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo ThinkBook 16 AMD Ryzen 5 7535HS (8GB RAM/512GB SSD/Win 11 Home/Office 2024/Backlit Keyboard/Fingerprint) 16" WUXGA IPS 300 Nits Thin &amp; Light Laptop/1Y Warranty/Aluminium Top/1.7kg, 21MWA0BRIN</t>
         </is>
       </c>
       <c r="C315" t="inlineStr"/>
       <c r="D315" t="n">
-        <v>42999</v>
+        <v>65063</v>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon</t>
+          <t>lenovo_thinkbook_16,_amd_ryzen</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo ThinkBook 16, AMD Ryzen 5 7535HS, 16GB RAM, 512GB SSD, WUXGA IPS 16", Windows 11 Home, Office 2024, 1.7kg, 21MWA0BSIN, Backlit Keyboard, Fingerprint, 300 Nits, 1Y Warranty, Aluminium Top Laptop</t>
         </is>
       </c>
       <c r="C316" t="inlineStr"/>
       <c r="D316" t="n">
-        <v>42999</v>
+        <v>84500</v>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon</t>
+          <t>Lenovo ThinkBook 16, Intel Core</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo ThinkBook 16, Intel Core Ultra 9 185H, 16GB RAM, 512GB SSD, WUXGA IPS 16” (40.64cm), Win 11 Home, Arctic Grey, 1.7Kg, 21SKA0J5IG, Fingerprint, Backlit, 300 Nits, 1Y Warranty, AI Powered Laptop</t>
         </is>
       </c>
       <c r="C317" t="inlineStr"/>
       <c r="D317" t="n">
-        <v>42999</v>
+        <v>94990</v>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-20</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon</t>
+          <t>Lenovo V14 Intel Core i3</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo V14 Intel Core i3 13th Gen 14" FHD (1920x1080) Antiglare 250 Nits Thin and Light Laptop (16GB RAM/512GB SSD/Windows 11 Home/Office Home 2024/Iron Grey/1.43 kg), 83A0A0PCIN</t>
         </is>
       </c>
       <c r="C318" t="inlineStr"/>
       <c r="D318" t="n">
-        <v>42999</v>
+        <v>70990</v>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-05-20</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon</t>
+          <t>Lenovo V14 Intel Core i3</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo V14 Intel Core i3 13th Gen 14" FHD (1920x1080) Antiglare 250 Nits Thin and Light Laptop (16GB RAM/512GB SSD/Windows 11 Home/Office Home 2024/Iron Grey/1.43 kg), 83A0A0PCIN</t>
         </is>
       </c>
       <c r="C319" t="inlineStr"/>
       <c r="D319" t="n">
-        <v>44999</v>
+        <v>70990</v>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon</t>
+          <t>lenovo_v14_intel_core_i3</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo V14 Intel Core i3 13th Gen 14" FHD (1920x1080) Antiglare 250 Nits Thin and Light Laptop (16GB RAM/512GB SSD/Windows 11 Home/Office Home 2024/Iron Grey/1.43 kg), 83A0A0PCIN</t>
         </is>
       </c>
       <c r="C320" t="inlineStr"/>
       <c r="D320" t="n">
-        <v>43999</v>
+        <v>70990</v>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon</t>
+          <t>Lenovo V15 G4 (2024), AMD</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo V15 G4 (2024), AMD Ryzen 3 7320U Quad Core - (8GB/512GB SSD/AMD Radeon Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" FHD Display/Arctic Grey/1.57 kg/MS Office 2021</t>
         </is>
       </c>
       <c r="C321" t="inlineStr"/>
       <c r="D321" t="n">
-        <v>43999</v>
+        <v>44200</v>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-05-22</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon</t>
+          <t>Lenovo V15 G4 (2024), AMD</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo V15 G4 (2024), AMD Ryzen 3 7320U Quad Core - (8GB/512GB SSD/AMD Radeon Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" FHD Display/Arctic Grey/1.57 kg/MS Office 2021</t>
         </is>
       </c>
       <c r="C322" t="inlineStr"/>
       <c r="D322" t="n">
-        <v>43999</v>
+        <v>44490</v>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-24</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon</t>
+          <t>Lenovo V15 G4 (2024), AMD</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo V15 G4 (2024), AMD Ryzen 3 7320U Quad Core - (8GB/512GB SSD/AMD Radeon Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" FHD Display/Arctic Grey/1.57 kg/MS Office 2021</t>
         </is>
       </c>
       <c r="C323" t="inlineStr"/>
       <c r="D323" t="n">
-        <v>44999</v>
+        <v>44490</v>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon</t>
+          <t>Lenovo V15 G4 (2024), AMD</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo V15 G4 (2024), AMD Ryzen 3 7320U Quad Core - (8GB/512GB SSD/AMD Radeon Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" FHD Display/Arctic Grey/1.57 kg/MS Office 2021</t>
         </is>
       </c>
       <c r="C324" t="inlineStr"/>
       <c r="D324" t="n">
-        <v>44999</v>
+        <v>44500</v>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>lenovo_v15_g4_amd_athlon</t>
+          <t>Lenovo V15 G4 (2024), AMD</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo V15 G4 (2024), AMD Ryzen 3 7320U Quad Core - (8GB/512GB SSD/AMD Radeon Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" FHD Display/Arctic Grey/1.57 kg/MS Office 2021</t>
         </is>
       </c>
       <c r="C325" t="inlineStr"/>
       <c r="D325" t="n">
-        <v>44999</v>
+        <v>49999</v>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>lenovo_v15_g4_amd_athlon</t>
+          <t>Lenovo V15 G4 (2024), AMD</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo V15 G4 (2024), AMD Ryzen 3 7320U Quad Core - (8GB/512GB SSD/AMD Radeon Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" FHD Display/Arctic Grey/1.57 kg/MS Office 2021</t>
         </is>
       </c>
       <c r="C326" t="inlineStr"/>
       <c r="D326" t="n">
-        <v>44999</v>
+        <v>49890</v>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen</t>
+          <t>Lenovo V15 G4 AMD Athlon</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C327" t="inlineStr"/>
       <c r="D327" t="n">
-        <v>49999</v>
+        <v>41999</v>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen</t>
+          <t>Lenovo V15 G4 AMD Athlon</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C328" t="inlineStr"/>
       <c r="D328" t="n">
-        <v>52760</v>
+        <v>41999</v>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-28</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen</t>
+          <t>Lenovo V15 G4 AMD Athlon</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C329" t="inlineStr"/>
       <c r="D329" t="n">
-        <v>52300</v>
+        <v>41999</v>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-31</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen</t>
+          <t>Lenovo V15 G4 AMD Athlon</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C330" t="inlineStr"/>
       <c r="D330" t="n">
-        <v>52490</v>
+        <v>42999</v>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen</t>
+          <t>Lenovo V15 G4 AMD Athlon</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C331" t="inlineStr"/>
       <c r="D331" t="n">
-        <v>52300</v>
+        <v>42999</v>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-02</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen</t>
+          <t>Lenovo V15 G4 AMD Athlon</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C332" t="inlineStr"/>
       <c r="D332" t="n">
-        <v>52890</v>
+        <v>42999</v>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen</t>
+          <t>Lenovo V15 G4 AMD Athlon</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C333" t="inlineStr"/>
       <c r="D333" t="n">
-        <v>53999</v>
+        <v>42999</v>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen</t>
+          <t>Lenovo V15 G4 AMD Athlon</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C334" t="inlineStr"/>
       <c r="D334" t="n">
-        <v>53999</v>
+        <v>42999</v>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen</t>
+          <t>Lenovo V15 G4 AMD Athlon</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C335" t="inlineStr"/>
       <c r="D335" t="n">
-        <v>54790</v>
+        <v>44999</v>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>lenovo_v15_g4_amd_ryzen</t>
+          <t>Lenovo V15 G4 AMD Athlon</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C336" t="inlineStr"/>
       <c r="D336" t="n">
-        <v>54740</v>
+        <v>43999</v>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>lenovo_v15_g6_amd_ryzen</t>
+          <t>Lenovo V15 G4 AMD Athlon</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Lenovo V15 G6 AMD Ryzen 7 170 (Coequal 7735HS) 15.6" (39.62cm) FHD Thin and Light Business Laptop (16GB RAM DDR5/ 512GB SSD/Windows 11/ MS Office 2024/ AMD Radeon Graphics/Luna Grey/ 1.6 kg)</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C337" t="inlineStr"/>
       <c r="D337" t="n">
-        <v>64999</v>
+        <v>43999</v>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Lenovo Yoga Slim 7 (Smartchoice)</t>
+          <t>Lenovo V15 G4 AMD Athlon</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Lenovo Yoga Slim 7 (Smartchoice) Aura Edition, Intel Core Ultra 5 226V, 16GB RAM, 1TB SSD, WUXGA OLED, Copilot+ AI PC, 40 TOPS, 14"/35.5cm, Windows 11, Office 2024, Grey, 1.19Kg, 83JX005FIN, AI Laptop</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C338" t="inlineStr"/>
       <c r="D338" t="n">
-        <v>99990</v>
+        <v>43999</v>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Lenovo Yoga Slim 7 (Smartchoice)</t>
+          <t>Lenovo V15 G4 AMD Athlon</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Lenovo Yoga Slim 7 (Smartchoice) Aura Edition, Intel Core Ultra 5 226V, 16GB RAM, 1TB SSD, WUXGA OLED, Copilot+ AI PC, 40 TOPS, 14"/35.5cm, Windows 11, Office 2024, Grey, 1.19Kg, 83JX005FIN, AI Laptop</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C339" t="inlineStr"/>
       <c r="D339" t="n">
-        <v>105939</v>
+        <v>44999</v>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-12</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Lenovo Yoga Slim 7, Intel</t>
+          <t>Lenovo V15 G4 AMD Athlon</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Lenovo Yoga Slim 7, Intel Core Ultra 5 125H, 16GB RAM, 512GB SSD, AI PC, WUXGA-OLED, 14"/35.5cm, Windows 11, Microsoft 365 Basic + Office 2024, Grey, 1.39Kg, 83CV00DFIN, AI Powered Laptop</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C340" t="inlineStr"/>
       <c r="D340" t="n">
-        <v>77990</v>
+        <v>44999</v>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Lenovo Yoga Slim 7, Intel</t>
+          <t>lenovo_v15_g4_amd_athlon</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Lenovo Yoga Slim 7, Intel Core Ultra 5 125H, 16GB RAM, 512GB SSD, AI PC, WUXGA-OLED, 14"/35.5cm, Windows 11, Microsoft 365 Basic + Office 2024, Grey, 1.39Kg, 83CV00DFIN, AI Powered Laptop</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C341" t="inlineStr"/>
       <c r="D341" t="n">
-        <v>84990</v>
+        <v>44999</v>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Lenovo {SmartChoice Chromebook, Intel Celeron</t>
+          <t>lenovo_v15_g4_amd_athlon</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Lenovo {SmartChoice Chromebook, Intel Celeron N4500, 4GB RAM, 64GB eMMC, HD, 11.6"/29.46cm, Chrome OS, Blue, 1.21Kg, 2Wx2 Stereo Speakers, HD Camera, 82UY0014HA, Laptop</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C342" t="inlineStr"/>
       <c r="D342" t="n">
-        <v>21990</v>
+        <v>44999</v>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Lenovo {SmartChoice Chromebook, Intel Celeron</t>
+          <t>lenovo_v15_g4_amd_athlon</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Lenovo {SmartChoice Chromebook, Intel Celeron N4500, 4GB RAM, 64GB eMMC, HD, 11.6"/29.46cm, Chrome OS, Blue, 1.21Kg, 2Wx2 Stereo Speakers, HD Camera, 82UY0014HA, Laptop</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C343" t="inlineStr"/>
       <c r="D343" t="n">
-        <v>17990</v>
+        <v>44999</v>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>msi_cyborg_15,_intel_12th</t>
+          <t>Lenovo V15 G4 AMD Ryzen</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>MSI Cyborg 15, Intel 12th Gen. i5-12450H, 40CM FHD 144Hz Gaming Laptop (16GB/512GB NVMe SSD/Windows 11 Home/MSO 2021/NVIDIA GeForce RTX 3050, GDDR6 6GB/Translucent Black/1.9Kg) A12UDX-1468IN</t>
+          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
         </is>
       </c>
       <c r="C344" t="inlineStr"/>
       <c r="D344" t="n">
-        <v>72990</v>
+        <v>49999</v>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-05-21</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>primebook_2_max_(2026)_|</t>
+          <t>Lenovo V15 G4 AMD Ryzen</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Primebook 2 Max (2026) | 8GB RAM, 256GB UFS Storage | 15.6-Inch Full HD IPS Display | 12hrs Battery | MediaTek Helio G99 | Android 15 (PrimeOS 3.0) | Backlit Keyboard | in-Built AI (Gray)</t>
+          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
         </is>
       </c>
       <c r="C345" t="inlineStr"/>
       <c r="D345" t="n">
-        <v>29990</v>
+        <v>52760</v>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-24</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Samsung Galaxy Book6 (Gray, 16GB</t>
+          <t>Lenovo V15 G4 AMD Ryzen</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Samsung Galaxy Book6 (Gray, 16GB RAM, 1TB SSD) | Intel Core Ultra 5 (Series 3) | 16" WUXGA+ Display with Touchscreen | 24Hrs Battery Life | 120 Hz Refresh Rate | Dolby Atmos Stereo Speakers | AI PC</t>
+          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
         </is>
       </c>
       <c r="C346" t="inlineStr"/>
       <c r="D346" t="n">
-        <v>146990</v>
+        <v>52300</v>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Thomson NEO 14.1 Inch IN-P14C</t>
+          <t>Lenovo V15 G4 AMD Ryzen</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Thomson NEO 14.1 Inch IN-P14C Intel Celeron Dual Core N4020 Processor &amp; Window 11 Home Notebook (4 GB RAM DDR4/ 128 GB SSD/Numeric Touch Pad/Thin &amp; Light Weight/Silver)</t>
+          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
         </is>
       </c>
       <c r="C347" t="inlineStr"/>
       <c r="D347" t="n">
-        <v>12990</v>
+        <v>52490</v>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Thomson NEO 14.1 Inch IN-P14C</t>
+          <t>Lenovo V15 G4 AMD Ryzen</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Thomson NEO 14.1 Inch IN-P14C Intel Celeron Dual Core N4020 Processor &amp; Window 11 Home Notebook (4 GB RAM DDR4/ 128 GB SSD/Numeric Touch Pad/Thin &amp; Light Weight/Silver)</t>
+          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
         </is>
       </c>
       <c r="C348" t="inlineStr"/>
       <c r="D348" t="n">
-        <v>12990</v>
+        <v>52300</v>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-05-27</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Thomson NEO 14.1 Inch IN-P14C</t>
+          <t>Lenovo V15 G4 AMD Ryzen</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Thomson NEO 14.1 Inch IN-P14C Intel Celeron Dual Core N4020 Processor &amp; Window 11 Home Notebook (4 GB RAM DDR4/ 128 GB SSD/Numeric Touch Pad/Thin &amp; Light Weight/Silver)</t>
+          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
         </is>
       </c>
       <c r="C349" t="inlineStr"/>
       <c r="D349" t="n">
-        <v>22990</v>
+        <v>52890</v>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-31</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Thomson NEO 14.1 Inch IN-P14C</t>
+          <t>Lenovo V15 G4 AMD Ryzen</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Thomson NEO 14.1 Inch IN-P14C Intel Celeron Dual Core N4020 Processor &amp; Window 11 Home Notebook (4 GB RAM DDR4/ 128 GB SSD/Numeric Touch Pad/Thin &amp; Light Weight/Silver)</t>
+          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
         </is>
       </c>
       <c r="C350" t="inlineStr"/>
       <c r="D350" t="n">
-        <v>22990</v>
+        <v>53999</v>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>acer Aspire 3, Intel Core</t>
+          <t>Lenovo V15 G4 AMD Ryzen</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>acer Aspire 3, Intel Core Celeron N4500, 12GB LPDDR4X RAM, 512GB SSD, HD, 15.6"/39.62cm, Windows 11 Home, Pure Silver, 1.5KG, A325-45, Thin and Light Laptop</t>
+          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
         </is>
       </c>
       <c r="C351" t="inlineStr"/>
       <c r="D351" t="n">
-        <v>39890</v>
+        <v>53999</v>
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-06-02</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>acer Aspire Lite, AMD Ryzen</t>
+          <t>Lenovo V15 G4 AMD Ryzen</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>acer Aspire Lite, AMD Ryzen 3 5300U Processor, 16 GB RAM, 512GB SSD, Full HD, 15.6"/39.62cm, Windows 11 Home, Steel Gray, 1.59KG, AL15-41, Metal Body, Premium Thin and Light Laptop</t>
+          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
         </is>
       </c>
       <c r="C352" t="inlineStr"/>
       <c r="D352" t="n">
-        <v>42990</v>
+        <v>54790</v>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD</t>
+          <t>lenovo_v15_g4_amd_ryzen</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
+          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
         </is>
       </c>
       <c r="C353" t="inlineStr"/>
       <c r="D353" t="n">
-        <v>45990</v>
+        <v>54740</v>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD</t>
+          <t>lenovo_v15_g6_amd_ryzen</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
+          <t>Lenovo V15 G6 AMD Ryzen 7 170 (Coequal 7735HS) 15.6" (39.62cm) FHD Thin and Light Business Laptop (16GB RAM DDR5/ 512GB SSD/Windows 11/ MS Office 2024/ AMD Radeon Graphics/Luna Grey/ 1.6 kg)</t>
         </is>
       </c>
       <c r="C354" t="inlineStr"/>
       <c r="D354" t="n">
-        <v>45990</v>
+        <v>64999</v>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD</t>
+          <t>Lenovo Yoga Slim 7 (Smartchoice)</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
+          <t>Lenovo Yoga Slim 7 (Smartchoice) Aura Edition, Intel Core Ultra 5 226V, 16GB RAM, 1TB SSD, WUXGA OLED, Copilot+ AI PC, 40 TOPS, 14"/35.5cm, Windows 11, Office 2024, Grey, 1.19Kg, 83JX005FIN, AI Laptop</t>
         </is>
       </c>
       <c r="C355" t="inlineStr"/>
       <c r="D355" t="n">
-        <v>45990</v>
+        <v>99990</v>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-05-15</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD</t>
+          <t>Lenovo Yoga Slim 7 (Smartchoice)</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
+          <t>Lenovo Yoga Slim 7 (Smartchoice) Aura Edition, Intel Core Ultra 5 226V, 16GB RAM, 1TB SSD, WUXGA OLED, Copilot+ AI PC, 40 TOPS, 14"/35.5cm, Windows 11, Office 2024, Grey, 1.19Kg, 83JX005FIN, AI Laptop</t>
         </is>
       </c>
       <c r="C356" t="inlineStr"/>
       <c r="D356" t="n">
-        <v>43990</v>
+        <v>105939</v>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-19</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD</t>
+          <t>Lenovo Yoga Slim 7, Intel</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
+          <t>Lenovo Yoga Slim 7, Intel Core Ultra 5 125H, 16GB RAM, 512GB SSD, AI PC, WUXGA-OLED, 14"/35.5cm, Windows 11, Microsoft 365 Basic + Office 2024, Grey, 1.39Kg, 83CV00DFIN, AI Powered Laptop</t>
         </is>
       </c>
       <c r="C357" t="inlineStr"/>
       <c r="D357" t="n">
-        <v>43990</v>
+        <v>77990</v>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-15</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD</t>
+          <t>Lenovo Yoga Slim 7, Intel</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
+          <t>Lenovo Yoga Slim 7, Intel Core Ultra 5 125H, 16GB RAM, 512GB SSD, AI PC, WUXGA-OLED, 14"/35.5cm, Windows 11, Microsoft 365 Basic + Office 2024, Grey, 1.39Kg, 83CV00DFIN, AI Powered Laptop</t>
         </is>
       </c>
       <c r="C358" t="inlineStr"/>
       <c r="D358" t="n">
-        <v>43990</v>
+        <v>84990</v>
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-19</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD</t>
+          <t>Lenovo {SmartChoice Chromebook, Intel Celeron</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
+          <t>Lenovo {SmartChoice Chromebook, Intel Celeron N4500, 4GB RAM, 64GB eMMC, HD, 11.6"/29.46cm, Chrome OS, Blue, 1.21Kg, 2Wx2 Stereo Speakers, HD Camera, 82UY0014HA, Laptop</t>
         </is>
       </c>
       <c r="C359" t="inlineStr"/>
       <c r="D359" t="n">
-        <v>43990</v>
+        <v>21990</v>
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD</t>
+          <t>Lenovo {SmartChoice Chromebook, Intel Celeron</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
+          <t>Lenovo {SmartChoice Chromebook, Intel Celeron N4500, 4GB RAM, 64GB eMMC, HD, 11.6"/29.46cm, Chrome OS, Blue, 1.21Kg, 2Wx2 Stereo Speakers, HD Camera, 82UY0014HA, Laptop</t>
         </is>
       </c>
       <c r="C360" t="inlineStr"/>
       <c r="D360" t="n">
-        <v>43990</v>
+        <v>17990</v>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-08</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop ModeI 7410 Laptop |</t>
+          <t>msi_cyborg_15,_intel_12th</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop ModeI 7410 Laptop | InteI Core i5 10th Gen | 16GB DDR4 RAM | 256GB SSD | 14" Full HD Display | Win 10 Pro | InteI UHD Graphics 620 | 3 Months Seller Warranty | A+ Condition (Refab)</t>
+          <t>MSI Cyborg 15, Intel 12th Gen. i5-12450H, 40CM FHD 144Hz Gaming Laptop (16GB/512GB NVMe SSD/Windows 11 Home/MSO 2021/NVIDIA GeForce RTX 3050, GDDR6 6GB/Translucent Black/1.9Kg) A12UDX-1468IN</t>
         </is>
       </c>
       <c r="C361" t="inlineStr"/>
       <c r="D361" t="n">
-        <v>27299</v>
+        <v>72990</v>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5</t>
+          <t>primebook_2_max_(2026)_|</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5 11th Gen Processor |8GB DDR4 RAM |256GB SSD |14" FHD Display | Win10 | A+ Condition Laptop (Refab)</t>
+          <t>Primebook 2 Max (2026) | 8GB RAM, 256GB UFS Storage | 15.6-Inch Full HD IPS Display | 12hrs Battery | MediaTek Helio G99 | Android 15 (PrimeOS 3.0) | Backlit Keyboard | in-Built AI (Gray)</t>
         </is>
       </c>
       <c r="C362" t="inlineStr"/>
       <c r="D362" t="n">
-        <v>26999</v>
+        <v>29990</v>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5</t>
+          <t>Samsung Galaxy Book6 (Gray, 16GB</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5 11th Gen Processor |8GB DDR4 RAM |256GB SSD |14" FHD Display | Win10 | A+ Condition Laptop (Refab)</t>
+          <t>Samsung Galaxy Book6 (Gray, 16GB RAM, 1TB SSD) | Intel Core Ultra 5 (Series 3) | 16" WUXGA+ Display with Touchscreen | 24Hrs Battery Life | 120 Hz Refresh Rate | Dolby Atmos Stereo Speakers | AI PC</t>
         </is>
       </c>
       <c r="C363" t="inlineStr"/>
       <c r="D363" t="n">
-        <v>26400</v>
+        <v>146990</v>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5</t>
+          <t>Thomson NEO 14.1 Inch IN-P14C</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5 11th Gen Processor |8GB DDR4 RAM |256GB SSD |14" FHD Display | Win10 | A+ Condition Laptop (Refab)</t>
+          <t>Thomson NEO 14.1 Inch IN-P14C Intel Celeron Dual Core N4020 Processor &amp; Window 11 Home Notebook (4 GB RAM DDR4/ 128 GB SSD/Numeric Touch Pad/Thin &amp; Light Weight/Silver)</t>
         </is>
       </c>
       <c r="C364" t="inlineStr"/>
       <c r="D364" t="n">
-        <v>28599</v>
+        <v>12990</v>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5</t>
+          <t>Thomson NEO 14.1 Inch IN-P14C</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5 11th Gen Processor |8GB DDR4 RAM |256GB SSD |14" FHD Display | Win10 | A+ Condition Laptop (Refab)</t>
+          <t>Thomson NEO 14.1 Inch IN-P14C Intel Celeron Dual Core N4020 Processor &amp; Window 11 Home Notebook (4 GB RAM DDR4/ 128 GB SSD/Numeric Touch Pad/Thin &amp; Light Weight/Silver)</t>
         </is>
       </c>
       <c r="C365" t="inlineStr"/>
       <c r="D365" t="n">
-        <v>28999</v>
+        <v>12990</v>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5</t>
+          <t>Thomson NEO 14.1 Inch IN-P14C</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5 11th Gen Processor |8GB DDR4 RAM |256GB SSD |14" FHD Display | Win10 | A+ Condition Laptop (Refab)</t>
+          <t>Thomson NEO 14.1 Inch IN-P14C Intel Celeron Dual Core N4020 Processor &amp; Window 11 Home Notebook (4 GB RAM DDR4/ 128 GB SSD/Numeric Touch Pad/Thin &amp; Light Weight/Silver)</t>
         </is>
       </c>
       <c r="C366" t="inlineStr"/>
       <c r="D366" t="n">
-        <v>31990</v>
+        <v>22990</v>
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-08</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5</t>
+          <t>Thomson NEO 14.1 Inch IN-P14C</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5 11th Gen Processor |8GB DDR4 RAM |256GB SSD |14" FHD Display | Win10 | A+ Condition Laptop (Refab)</t>
+          <t>Thomson NEO 14.1 Inch IN-P14C Intel Celeron Dual Core N4020 Processor &amp; Window 11 Home Notebook (4 GB RAM DDR4/ 128 GB SSD/Numeric Touch Pad/Thin &amp; Light Weight/Silver)</t>
         </is>
       </c>
       <c r="C367" t="inlineStr"/>
       <c r="D367" t="n">
-        <v>35490</v>
+        <v>22990</v>
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-10</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5</t>
+          <t>acer Aspire 3, Intel Core</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5 11th Gen Processor |8GB DDR4 RAM |256GB SSD |14" FHD Display | Win10 | A+ Condition Laptop (Refab)</t>
+          <t>acer Aspire 3, Intel Core Celeron N4500, 12GB LPDDR4X RAM, 512GB SSD, HD, 15.6"/39.62cm, Windows 11 Home, Pure Silver, 1.5KG, A325-45, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C368" t="inlineStr"/>
       <c r="D368" t="n">
-        <v>37490</v>
+        <v>39890</v>
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Model E5570 Laptop | Core</t>
+          <t>acer Aspire Lite, AMD Ryzen</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Model E5570 Laptop | Core i7 6th Gen | 8GB Fast RAM | 256GB SSD | 15.6" HD Display | HD Graphics | Win 10 | WiFi| (Pre-Owned &amp; Tested)</t>
+          <t>acer Aspire Lite, AMD Ryzen 3 5300U Processor, 16 GB RAM, 512GB SSD, Full HD, 15.6"/39.62cm, Windows 11 Home, Steel Gray, 1.59KG, AL15-41, Metal Body, Premium Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C369" t="inlineStr"/>
       <c r="D369" t="n">
-        <v>20599</v>
+        <v>42990</v>
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-04-16</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>𝗛𝗣𝗣𝗿𝗼𝗯𝗼𝗼𝗸Model 430 G3 Business Laptop</t>
+          <t>acer SmartChoice Aspire Lite, AMD</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>𝗛𝗣𝗣𝗿𝗼𝗯𝗼𝗼𝗸Model 430 G3 Business Laptop | InteI i5 6th Gen | 8GB RAM | 256GB SSD | WiFi | Webcam | Win10 Pro (Refab)</t>
+          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C370" t="inlineStr"/>
       <c r="D370" t="n">
-        <v>20299</v>
+        <v>45990</v>
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>𝗛𝗣𝗣𝗿𝗼𝗯𝗼𝗼𝗸Model 430 G3 Business Laptop</t>
+          <t>acer SmartChoice Aspire Lite, AMD</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>𝗛𝗣𝗣𝗿𝗼𝗯𝗼𝗼𝗸Model 430 G3 Business Laptop | 𝗜𝗡𝗧𝗘𝗟i5 6th Gen | 8GB RAM | 256GB SSD | WiFi | Webcam | Win10 Pro (Refab)</t>
+          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C371" t="inlineStr"/>
       <c r="D371" t="n">
-        <v>20499</v>
+        <v>45990</v>
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-04-16</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>𝗛𝗣𝗣𝗿𝗼𝗯𝗼𝗼𝗸Model 430 G3 Business Laptop</t>
+          <t>acer SmartChoice Aspire Lite, AMD</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>𝗛𝗣𝗣𝗿𝗼𝗯𝗼𝗼𝗸Model 430 G3 Business Laptop | 𝗜𝗡𝗧𝗘𝗟i5 6th Gen | 8GB RAM | 256GB SSD | WiFi | Webcam | Win10 Pro (Refab)</t>
+          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C372" t="inlineStr"/>
       <c r="D372" t="n">
-        <v>19999</v>
+        <v>45990</v>
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>𝗟𝗲𝗻𝗼𝘃𝗼model_l14_laptop|_core_i5</t>
+          <t>acer SmartChoice Aspire Lite, AMD</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>𝗟𝗲𝗻𝗼𝘃𝗼Model L14 Laptop| Core i5 11th Gen Processor | 16GB Fast RAM/ 256GB SSD | 14″ HD Display | A+ (Pre-Owned &amp; Tested)</t>
+          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C373" t="inlineStr"/>
       <c r="D373" t="n">
+        <v>43990</v>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>acer SmartChoice Aspire Lite, AMD</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr"/>
+      <c r="D374" t="n">
+        <v>43990</v>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>acer SmartChoice Aspire Lite, AMD</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr"/>
+      <c r="D375" t="n">
+        <v>43990</v>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>acer SmartChoice Aspire Lite, AMD</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr"/>
+      <c r="D376" t="n">
+        <v>43990</v>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>acer SmartChoice Aspire Lite, AMD</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr"/>
+      <c r="D377" t="n">
+        <v>43990</v>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop ModeI 7410 Laptop |</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop ModeI 7410 Laptop | InteI Core i5 10th Gen | 16GB DDR4 RAM | 256GB SSD | 14" Full HD Display | Win 10 Pro | InteI UHD Graphics 620 | 3 Months Seller Warranty | A+ Condition (Refab)</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr"/>
+      <c r="D378" t="n">
+        <v>27299</v>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5 11th Gen Processor |8GB DDR4 RAM |256GB SSD |14" FHD Display | Win10 | A+ Condition Laptop (Refab)</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr"/>
+      <c r="D379" t="n">
+        <v>26999</v>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5 11th Gen Processor |8GB DDR4 RAM |256GB SSD |14" FHD Display | Win10 | A+ Condition Laptop (Refab)</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr"/>
+      <c r="D380" t="n">
+        <v>26400</v>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5 11th Gen Processor |8GB DDR4 RAM |256GB SSD |14" FHD Display | Win10 | A+ Condition Laptop (Refab)</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr"/>
+      <c r="D381" t="n">
+        <v>28599</v>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5 11th Gen Processor |8GB DDR4 RAM |256GB SSD |14" FHD Display | Win10 | A+ Condition Laptop (Refab)</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr"/>
+      <c r="D382" t="n">
+        <v>28999</v>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5 11th Gen Processor |8GB DDR4 RAM |256GB SSD |14" FHD Display | Win10 | A+ Condition Laptop (Refab)</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr"/>
+      <c r="D383" t="n">
+        <v>31990</v>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5 11th Gen Processor |8GB DDR4 RAM |256GB SSD |14" FHD Display | Win10 | A+ Condition Laptop (Refab)</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr"/>
+      <c r="D384" t="n">
+        <v>35490</v>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5 11th Gen Processor |8GB DDR4 RAM |256GB SSD |14" FHD Display | Win10 | A+ Condition Laptop (Refab)</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr"/>
+      <c r="D385" t="n">
+        <v>37490</v>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Model E5570 Laptop | Core</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Model E5570 Laptop | Core i7 6th Gen | 8GB Fast RAM | 256GB SSD | 15.6" HD Display | HD Graphics | Win 10 | WiFi| (Pre-Owned &amp; Tested)</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr"/>
+      <c r="D386" t="n">
+        <v>20599</v>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>𝗛𝗣𝗣𝗿𝗼𝗯𝗼𝗼𝗸Model 430 G3 Business Laptop</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>𝗛𝗣𝗣𝗿𝗼𝗯𝗼𝗼𝗸Model 430 G3 Business Laptop | InteI i5 6th Gen | 8GB RAM | 256GB SSD | WiFi | Webcam | Win10 Pro (Refab)</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr"/>
+      <c r="D387" t="n">
+        <v>20299</v>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>𝗛𝗣𝗣𝗿𝗼𝗯𝗼𝗼𝗸Model 430 G3 Business Laptop</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>𝗛𝗣𝗣𝗿𝗼𝗯𝗼𝗼𝗸Model 430 G3 Business Laptop | 𝗜𝗡𝗧𝗘𝗟i5 6th Gen | 8GB RAM | 256GB SSD | WiFi | Webcam | Win10 Pro (Refab)</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr"/>
+      <c r="D388" t="n">
+        <v>20499</v>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>𝗛𝗣𝗣𝗿𝗼𝗯𝗼𝗼𝗸Model 430 G3 Business Laptop</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>𝗛𝗣𝗣𝗿𝗼𝗯𝗼𝗼𝗸Model 430 G3 Business Laptop | 𝗜𝗡𝗧𝗘𝗟i5 6th Gen | 8GB RAM | 256GB SSD | WiFi | Webcam | Win10 Pro (Refab)</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr"/>
+      <c r="D389" t="n">
+        <v>19999</v>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>𝗟𝗲𝗻𝗼𝘃𝗼model_l14_laptop|_core_i5</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>𝗟𝗲𝗻𝗼𝘃𝗼Model L14 Laptop| Core i5 11th Gen Processor | 16GB Fast RAM/ 256GB SSD | 14″ HD Display | A+ (Pre-Owned &amp; Tested)</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr"/>
+      <c r="D390" t="n">
         <v>31599</v>
       </c>
-      <c r="E373" t="inlineStr">
+      <c r="E390" t="inlineStr">
         <is>
           <t>2026-07-21</t>
         </is>

--- a/amazon_products.xlsx
+++ b/amazon_products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E390"/>
+  <dimension ref="A1:E410"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -782,21 +782,21 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ASUS Vivobook 15, 13th Gen,</t>
+          <t>asus_tuf_a15,_amd_ryzen</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ASUS Vivobook 15, 13th Gen, Intel Core i3-1315U, 16GB RAM, 512GB SSD, FHD, Anti-Glare, 15.6", 39.6 cm, Windows 11 Home, M365 Basic(1yr)* Office24, Quiet Blue, 1.70 kg, X1504VA-BQ342WS, Laptop</t>
+          <t>ASUS TUF A15, AMD Ryzen 7 170, RTX 3050-4GB, 16GB RAM (Upgradeable), 512GB SSD, FHD, 15.6"(39.6 cm),Windows 11 Home,Graphite Black, 2.3 Kg, FA506NCQ-HN006W, Gaming Laptop</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>46900</v>
+        <v>70990</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -813,11 +813,11 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>44990</v>
+        <v>46900</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -834,11 +834,11 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>51490</v>
+        <v>44990</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-17</t>
         </is>
       </c>
     </row>
@@ -855,11 +855,11 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>53990</v>
+        <v>51490</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
     </row>
@@ -876,11 +876,11 @@
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="n">
-        <v>46990</v>
+        <v>53990</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
     </row>
@@ -897,18 +897,18 @@
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="n">
-        <v>52990</v>
+        <v>46990</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>asus_vivobook_15,_13th_gen,</t>
+          <t>ASUS Vivobook 15, 13th Gen,</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -918,32 +918,32 @@
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="n">
-        <v>54990</v>
+        <v>52990</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ASUS Vivobook 15, Intel Core</t>
+          <t>asus_vivobook_15,_13th_gen,</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ASUS Vivobook 15, Intel Core i3 13th Gen 1315U, 12GB RAM, 512GB SSD, FHD 15.6", Windows 11, Office Home 2024, Cool Silver, 1.7Kg, X1504VA-BQ331WS, Intel UHD iGPU, Thin &amp; Light, 42Whrs Laptop</t>
+          <t>ASUS Vivobook 15, 13th Gen, Intel Core i3-1315U, 16GB RAM, 512GB SSD, FHD, Anti-Glare, 15.6", 39.6 cm, Windows 11 Home, M365 Basic(1yr)* Office24, Quiet Blue, 1.70 kg, X1504VA-BQ342WS, Laptop</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="n">
-        <v>45990</v>
+        <v>54990</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
     </row>
@@ -976,16 +976,16 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ASUS Vivobook 15, Intel Core i3 13th Gen 1315U, 12GB RAM, 512GB SSD, FHD 15.6", Windows 11, Office Home 2024, Quiet Blue, 1.7Kg, X1504VA-BQ332WS, Intel UHD iGPU, M365 Basic (1Year)*, 42Whrs Laptop</t>
+          <t>ASUS Vivobook 15, Intel Core i3 13th Gen 1315U, 12GB RAM, 512GB SSD, FHD 15.6", Windows 11, Office Home 2024, Cool Silver, 1.7Kg, X1504VA-BQ331WS, Intel UHD iGPU, Thin &amp; Light, 42Whrs Laptop</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="n">
-        <v>43990</v>
+        <v>45990</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-15</t>
         </is>
       </c>
     </row>
@@ -1002,32 +1002,32 @@
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="n">
-        <v>50990</v>
+        <v>43990</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-17</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ASUS Vivobook 15, Smartchoice, AMD</t>
+          <t>ASUS Vivobook 15, Intel Core</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ASUS Vivobook 15, Smartchoice, AMD Ryzen 7 5825U, 16GB RAM, 512GB SSD, FHD 15.6", Windows 11, Office Home 2024, Quiet Blue, 1.7Kg, M1502YA-BQ703WS, AMD Radeon iGPU, M365 Basic (1Year)*, 42Whr Laptop</t>
+          <t>ASUS Vivobook 15, Intel Core i3 13th Gen 1315U, 12GB RAM, 512GB SSD, FHD 15.6", Windows 11, Office Home 2024, Quiet Blue, 1.7Kg, X1504VA-BQ332WS, Intel UHD iGPU, M365 Basic (1Year)*, 42Whrs Laptop</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="n">
-        <v>49990</v>
+        <v>50990</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-19</t>
         </is>
       </c>
     </row>
@@ -1044,11 +1044,11 @@
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="n">
-        <v>53990</v>
+        <v>49990</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
@@ -1065,11 +1065,11 @@
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="n">
-        <v>54990</v>
+        <v>53990</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-17</t>
         </is>
       </c>
     </row>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-24</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-28</t>
         </is>
       </c>
     </row>
@@ -1149,11 +1149,11 @@
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="n">
-        <v>49990</v>
+        <v>54990</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-31</t>
         </is>
       </c>
     </row>
@@ -1170,11 +1170,11 @@
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="n">
-        <v>54990</v>
+        <v>49990</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -1195,28 +1195,28 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ASUS Vivobook 15, Smartchoice,Intel Core</t>
+          <t>ASUS Vivobook 15, Smartchoice, AMD</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ASUS Vivobook 15, Smartchoice,Intel Core i3 13th Gen 1315U, 12GB RAM, 512GB SSD, FHD 15.6", Win 11, Office 2024, Quiet Blue, 1.7Kg, X1504VA-BQ332WS, Intel UHD iGPU, M365 Basic (1Year)*, 42Whrs Laptop</t>
+          <t>ASUS Vivobook 15, Smartchoice, AMD Ryzen 7 5825U, 16GB RAM, 512GB SSD, FHD 15.6", Windows 11, Office Home 2024, Quiet Blue, 1.7Kg, M1502YA-BQ703WS, AMD Radeon iGPU, M365 Basic (1Year)*, 42Whr Laptop</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="n">
-        <v>50990</v>
+        <v>54990</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-21</t>
         </is>
       </c>
     </row>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-24</t>
         </is>
       </c>
     </row>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
     </row>
@@ -1312,16 +1312,16 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ASUS Vivobook 15, Smartchoice,Intel Core i3 13th Gen 1315U, 16GB RAM, 512GB SSD, FHD 15.6", Touchscreen, Win11, Office 24, M365 Basic (1Y), Quiet Blue, 1.7Kg, X1504VA-E83959WS, Intel UHD iGPU, Laptop</t>
+          <t>ASUS Vivobook 15, Smartchoice,Intel Core i3 13th Gen 1315U, 12GB RAM, 512GB SSD, FHD 15.6", Win 11, Office 2024, Quiet Blue, 1.7Kg, X1504VA-BQ332WS, Intel UHD iGPU, M365 Basic (1Year)*, 42Whrs Laptop</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="n">
-        <v>51990</v>
+        <v>50990</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-28</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-22</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -1401,11 +1401,11 @@
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="n">
-        <v>54990</v>
+        <v>51990</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-02</t>
         </is>
       </c>
     </row>
@@ -1417,16 +1417,16 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ASUS Vivobook 15, Smartchoice,Intel Core i5 13th Gen 13420H,16GB RAM, 512GB SSD, FHD 15.6",Windows 11, Office Home 2024, Quiet Blue, 1.70 kg, X1502VA-BQ836WS,Intel UHD iGPU, M365 Basic (1Year)* Laptop</t>
+          <t>ASUS Vivobook 15, Smartchoice,Intel Core i3 13th Gen 1315U, 16GB RAM, 512GB SSD, FHD 15.6", Touchscreen, Win11, Office 24, M365 Basic (1Y), Quiet Blue, 1.7Kg, X1504VA-E83959WS, Intel UHD iGPU, Laptop</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="n">
-        <v>59990</v>
+        <v>54990</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
@@ -1447,7 +1447,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-05-31</t>
         </is>
       </c>
     </row>
@@ -1464,11 +1464,11 @@
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="n">
-        <v>60990</v>
+        <v>59990</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
@@ -1489,7 +1489,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
@@ -1531,490 +1531,490 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ASUS Vivobook 16, 13th Gen,</t>
+          <t>ASUS Vivobook 15, Smartchoice,Intel Core</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ASUS Vivobook 16, 13th Gen, Intel Core i5-13420H,16GB RAM,512GB SSD,FHD (1920 x 1200) OLED,Win 11,M365 Basic (1Year)*,Backlit Keyboard,Office 2024,Silver,1.88 kg,X1605VA-SH1952WS, Thin &amp; Light Laptop</t>
+          <t>ASUS Vivobook 15, Smartchoice,Intel Core i5 13th Gen 13420H,16GB RAM, 512GB SSD, FHD 15.6",Windows 11, Office Home 2024, Quiet Blue, 1.70 kg, X1502VA-BQ836WS,Intel UHD iGPU, M365 Basic (1Year)* Laptop</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="n">
-        <v>61990</v>
+        <v>60990</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-06-12</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ASUS Vivobook Go 14, AMD</t>
+          <t>asus_vivobook_15,_smartchoice,intel_core</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ASUS Vivobook Go 14, AMD Ryzen 5 7520U, 16GB RAM, 512GB SSD, FHD, 14", 60Hz,42WHrs, Windows 11, M365 Basic (1Year)*,Office Home 2024, Mixed Black, 1.38 kg, E1404FA-EB774WS, Thin &amp; Light Laptop</t>
+          <t>ASUS Vivobook 15, Smartchoice,Intel Core i5 13th Gen 13420H,16GB RAM, 512GB SSD, FHD 15.6",Windows 11, Office Home 2024, Quiet Blue, 1.70 kg, X1502VA-BQ836WS,Intel UHD iGPU, M365 Basic (1Year)* Laptop</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="n">
-        <v>52990</v>
+        <v>63990</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ASUS Vivobook S14,Smartchoice,AMD Ryzen AI</t>
+          <t>asus_vivobook_16_(2026),smartchoice,intel_core</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ASUS Vivobook S14,Smartchoice,AMD Ryzen AI 7 350,16GB RAM,1TB SSD,OLED,14",Windows 11, Office24,M365 Basic (1Yr)*, Matte Gray,1.4Kg, M3407KA-SF049WS,50 Tops,Metallic Design,Next-Gen AI Laptop,Copilot+</t>
+          <t>ASUS Vivobook 16 (2026),Smartchoice,Intel Core Ultra 5 325 (Series 3), Intel iGPU,16GB RAM,512GB SSD,FHD+, 16"(40 cm),Win11,M365 Basic(1Y),Office 24,Quiet Blue,1.88 kg,X1607AA-MB037WS, Copilot+ AI PC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="n">
-        <v>88990</v>
+        <v>94990</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ASUS Vivobook S14,Smartchoice,AMD Ryzen AI</t>
+          <t>ASUS Vivobook 16, 13th Gen,</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ASUS Vivobook S14,Smartchoice,AMD Ryzen AI 7 350,16GB RAM,1TB SSD,OLED,14",Windows 11, Office24,M365 Basic (1Yr)*, Matte Gray,1.4Kg, M3407KA-SF049WS,50 Tops,Metallic Design,Next-Gen AI Laptop,Copilot+</t>
+          <t>ASUS Vivobook 16, 13th Gen, Intel Core i5-13420H,16GB RAM,512GB SSD,FHD (1920 x 1200) OLED,Win 11,M365 Basic (1Year)*,Backlit Keyboard,Office 2024,Silver,1.88 kg,X1605VA-SH1952WS, Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="n">
-        <v>88990</v>
+        <v>61990</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-14</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ASUS Vivobook S14,Smartchoice,AMD Ryzen AI</t>
+          <t>asus_vivobook_16,_smartchoice,_intel</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ASUS Vivobook S14,Smartchoice,AMD Ryzen AI 7 350,16GB RAM,1TB SSD,OLED,14",Windows 11, Office24,M365 Basic (1Yr)*, Matte Gray,1.4Kg, M3407KA-SF049WS,50 Tops,Metallic Design,Next-Gen AI Laptop,Copilot+</t>
+          <t>ASUS Vivobook 16, Smartchoice, Intel Core Ultra 5 Series 2, 16GB RAM, 512GB SSD, FHD+ 16", Windows 11, Office Home 2024, Silver, 1.88kg, X1607CA-MB142WS, Intel iGPU, M365 Basic (1Year), AI Laptop</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="n">
-        <v>83990</v>
+        <v>77990</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>asus_vivobook_s16,14th_gen,_intel</t>
+          <t>ASUS Vivobook Go 14, AMD</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ASUS Vivobook S16,14th Gen, Intel Core 5-210H,Metallic Design Laptop(Intel UHD iGPU/16GB RAM/512GB SSD/FHD+/16"/144Hz/Windows 11/M365 Basic(1Year)*/Office Home 2024/Silver/1.7Kg) S3607VA-RP114WS</t>
+          <t>ASUS Vivobook Go 14, AMD Ryzen 5 7520U, 16GB RAM, 512GB SSD, FHD, 14", 60Hz,42WHrs, Windows 11, M365 Basic (1Year)*,Office Home 2024, Mixed Black, 1.38 kg, E1404FA-EB774WS, Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="n">
-        <v>68990</v>
+        <v>52990</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ASUS Vivobook S16,Intel Core Ultra</t>
+          <t>ASUS Vivobook S14,Smartchoice,AMD Ryzen AI</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ASUS Vivobook S16,Intel Core Ultra 5 225H,AI PC(Intel Arc iGPU/16GB RAM/512GB SSD/FHD/16/60Hz/Backlit Keyboard/70Whr/Windows 11/M365 Basic(1Year)*/Office Home 2024/Cool Silver/1.7 Kg) S3607CA-SH071WS</t>
+          <t>ASUS Vivobook S14,Smartchoice,AMD Ryzen AI 7 350,16GB RAM,1TB SSD,OLED,14",Windows 11, Office24,M365 Basic (1Yr)*, Matte Gray,1.4Kg, M3407KA-SF049WS,50 Tops,Metallic Design,Next-Gen AI Laptop,Copilot+</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="n">
-        <v>81990</v>
+        <v>88990</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ASUS Vivobook S16,Intel Core Ultra</t>
+          <t>ASUS Vivobook S14,Smartchoice,AMD Ryzen AI</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>ASUS Vivobook S16,Intel Core Ultra 5 225H,AI PC(Intel Arc iGPU/16GB RAM/512GB SSD/FHD/16/60Hz/Backlit Keyboard/70Whr/Windows 11/M365 Basic(1Year)*/Office Home 2024/Cool Silver/1.7 Kg) S3607CA-SH071WS</t>
+          <t>ASUS Vivobook S14,Smartchoice,AMD Ryzen AI 7 350,16GB RAM,1TB SSD,OLED,14",Windows 11, Office24,M365 Basic (1Yr)*, Matte Gray,1.4Kg, M3407KA-SF049WS,50 Tops,Metallic Design,Next-Gen AI Laptop,Copilot+</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="n">
-        <v>79990</v>
+        <v>88990</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-04-16</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ASUS Zenbook 14 (2026),Smartchoice,Intel Core</t>
+          <t>ASUS Vivobook S14,Smartchoice,AMD Ryzen AI</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>ASUS Zenbook 14 (2026),Smartchoice,Intel Core Ultra 7 255H,32GB RAM,1TB SSD,OLED,Touchscreen,14"(35.5 cm),Win 11,M365 Basic(1Y)* Office 24,Ponder Blue,1.28 Kg,UX3405CA-QL1015WS,Thin &amp; Light Laptop</t>
+          <t>ASUS Vivobook S14,Smartchoice,AMD Ryzen AI 7 350,16GB RAM,1TB SSD,OLED,14",Windows 11, Office24,M365 Basic (1Yr)*, Matte Gray,1.4Kg, M3407KA-SF049WS,50 Tops,Metallic Design,Next-Gen AI Laptop,Copilot+</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="n">
-        <v>119990</v>
+        <v>83990</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ASUS Zenbook 14 (2026),Smartchoice,Intel Core</t>
+          <t>asus_vivobook_s16_oled,_intel</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ASUS Zenbook 14 (2026),Smartchoice,Intel Core Ultra 7 255H,32GB RAM,1TB SSD,OLED,Touchscreen,14"(35.5 cm),Win 11,M365 Basic(1Y)* Office 24,Ponder Blue,1.28 Kg,UX3405CA-QL1015WS,Thin &amp; Light Laptop</t>
+          <t>ASUS Vivobook S16 OLED, Intel Core Ultra 5 225H, 16GB RAM, 512GB SSD, FHD 16", Win 11, Office 2024, Cool Silver, 1.7Kg, S3607CA-SH071WS,Intel iGPU, 70Whr, M365 Basic(1Year) Metallic Design Laptop</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="n">
-        <v>119990</v>
+        <v>92990</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ASUS Zenbook 14 (2026),Smartchoice,Intel Core</t>
+          <t>asus_vivobook_s16,14th_gen,_intel</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>ASUS Zenbook 14 (2026),Smartchoice,Intel Core Ultra 9 285H,32GB RAM,1TB SSD,OLED,Touchscreen,14"(35.5 cm),Win 11,M365 Basic(1Y)* Office 24,Foggy Silver,1.28 Kg,UX3405CA-QL1113WS,Thin &amp; Light Laptop</t>
+          <t>ASUS Vivobook S16,14th Gen, Intel Core 5-210H,Metallic Design Laptop(Intel UHD iGPU/16GB RAM/512GB SSD/FHD+/16"/144Hz/Windows 11/M365 Basic(1Year)*/Office Home 2024/Silver/1.7Kg) S3607VA-RP114WS</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="n">
-        <v>124990</v>
+        <v>68990</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ASUS Zenbook 14, Intel Core</t>
+          <t>ASUS Vivobook S16,Intel Core Ultra</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ASUS Zenbook 14, Intel Core Ultra 5 Series 2, 16GB RAM, 1TB SSD, 3K OLED 14", Touchscreen, Win 11, Office Home 2024, Ponder Blue, 1.28kg, UX3405CA-PZ162WS, Intel Arc iGPU, M365 Basic (1Year)* Laptop</t>
+          <t>ASUS Vivobook S16,Intel Core Ultra 5 225H,AI PC(Intel Arc iGPU/16GB RAM/512GB SSD/FHD/16/60Hz/Backlit Keyboard/70Whr/Windows 11/M365 Basic(1Year)*/Office Home 2024/Cool Silver/1.7 Kg) S3607CA-SH071WS</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="n">
-        <v>106990</v>
+        <v>81990</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ASUS Zenbook 14, Smartchoice, Intel</t>
+          <t>ASUS Vivobook S16,Intel Core Ultra</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>ASUS Zenbook 14, Smartchoice, Intel Core Ultra 5 Series 2,16GB RAM,1TB SSD,3K OLED 14", Touchscreen, Win 11, Office Home 2024,Blue, 1.28kg, UX3405CA-PZ162WS, Intel Arc iGPU, M365 Basic (1Year)* Laptop</t>
+          <t>ASUS Vivobook S16,Intel Core Ultra 5 225H,AI PC(Intel Arc iGPU/16GB RAM/512GB SSD/FHD/16/60Hz/Backlit Keyboard/70Whr/Windows 11/M365 Basic(1Year)*/Office Home 2024/Cool Silver/1.7 Kg) S3607CA-SH071WS</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="n">
-        <v>108990</v>
+        <v>79990</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ASUS Zenbook 14, Smartchoice, Intel</t>
+          <t>ASUS Zenbook 14 (2026),Smartchoice,Intel Core</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ASUS Zenbook 14, Smartchoice, Intel Core Ultra 5 Series 2,16GB RAM,1TB SSD,3K OLED 14", Touchscreen, Win 11, Office Home 2024,Blue, 1.28kg, UX3405CA-PZ162WS, Intel iGPU, M365 Basic (1Year)* Laptop</t>
+          <t>ASUS Zenbook 14 (2026),Smartchoice,Intel Core Ultra 7 255H,32GB RAM,1TB SSD,OLED,Touchscreen,14"(35.5 cm),Win 11,M365 Basic(1Y)* Office 24,Ponder Blue,1.28 Kg,UX3405CA-QL1015WS,Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="n">
-        <v>114990</v>
+        <v>119990</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-22</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Acer Aspire 3 Laptop Intel</t>
+          <t>ASUS Zenbook 14 (2026),Smartchoice,Intel Core</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Acer Aspire 3 Laptop Intel Core Celeron N4500 Processor Laptop (8 GB LPDDR4X SDRAM/256 GB SSD/Win11 Home/38 WHR/HD Webcam) A325-45 with 39.63 cm (15.6") HD Display, Pure Silver, 1.5 KG</t>
+          <t>ASUS Zenbook 14 (2026),Smartchoice,Intel Core Ultra 7 255H,32GB RAM,1TB SSD,OLED,Touchscreen,14"(35.5 cm),Win 11,M365 Basic(1Y)* Office 24,Ponder Blue,1.28 Kg,UX3405CA-QL1015WS,Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="n">
-        <v>36990</v>
+        <v>119990</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Acer Aspire 3 Laptop Intel</t>
+          <t>ASUS Zenbook 14 (2026),Smartchoice,Intel Core</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Acer Aspire 3 Laptop Intel Core Celeron N4500 Processor Laptop (8 GB LPDDR4X SDRAM/256 GB SSD/Win11 Home/38 WHR/HD Webcam) A325-45 with 39.63 cm (15.6") HD Display, Pure Silver, 1.5 KG</t>
+          <t>ASUS Zenbook 14 (2026),Smartchoice,Intel Core Ultra 9 285H,32GB RAM,1TB SSD,OLED,Touchscreen,14"(35.5 cm),Win 11,M365 Basic(1Y)* Office 24,Foggy Silver,1.28 Kg,UX3405CA-QL1113WS,Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="n">
-        <v>36990</v>
+        <v>124990</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Acer Aspire Lite 12th Gen,</t>
+          <t>ASUS Zenbook 14, Intel Core</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Acer Aspire Lite 12th Gen, Intel Core i5-12450H, Office 2024 + M365 Basic, 12GB RAM/512GB SSD, 39.62cm 15.6" FHD IPS Display, Win 11 Home, Pure Silver, 1.7KG,AL15-52H, Backlit KB, Thin &amp; Light Laptop</t>
+          <t>ASUS Zenbook 14, Intel Core Ultra 5 Series 2, 16GB RAM, 1TB SSD, 3K OLED 14", Touchscreen, Win 11, Office Home 2024, Ponder Blue, 1.28kg, UX3405CA-PZ162WS, Intel Arc iGPU, M365 Basic (1Year)* Laptop</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="n">
-        <v>52990</v>
+        <v>106990</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-14</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Acer Aspire Lite 12th Gen,</t>
+          <t>ASUS Zenbook 14, Smartchoice, Intel</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Acer Aspire Lite 12th Gen, Intel Core i5-12450H, Office 2024 + M365 Basic, 12GB RAM/512GB SSD, 39.62cm 15.6" FHD IPS Display, Win 11 Home, Pure Silver, 1.7KG,AL15-52H, Backlit KB, Thin &amp; Light Laptop</t>
+          <t>ASUS Zenbook 14, Smartchoice, Intel Core Ultra 5 Series 2,16GB RAM,1TB SSD,3K OLED 14", Touchscreen, Win 11, Office Home 2024,Blue, 1.28kg, UX3405CA-PZ162WS, Intel Arc iGPU, M365 Basic (1Year)* Laptop</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="n">
-        <v>47990</v>
+        <v>108990</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Acer Aspire Lite 12th Gen,</t>
+          <t>ASUS Zenbook 14, Smartchoice, Intel</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Acer Aspire Lite 12th Gen, Intel Core i5-12450H, Office 2024 + M365 Basic, 12GB RAM/512GB SSD, 39.62cm 15.6" FHD IPS Display, Win 11 Home, Pure Silver, 1.7KG,AL15-52H, Backlit KB, Thin &amp; Light Laptop</t>
+          <t>ASUS Zenbook 14, Smartchoice, Intel Core Ultra 5 Series 2,16GB RAM,1TB SSD,3K OLED 14", Touchscreen, Win 11, Office Home 2024,Blue, 1.28kg, UX3405CA-PZ162WS, Intel iGPU, M365 Basic (1Year)* Laptop</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="n">
-        <v>53990</v>
+        <v>114990</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Acer Aspire Lite 12th Gen,</t>
+          <t>asus_zenbook_14,smartchoice,intel_core_ultra</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Acer Aspire Lite 12th Gen, Intel Core i5-12450H, Office 2024 + M365 Basic, 12GB RAM/512GB SSD, 39.62cm 15.6" FHD IPS Display, Win 11 Home, Pure Silver, 1.7KG,AL15-52H, Backlit KB, Thin &amp; Light Laptop</t>
+          <t>ASUS Zenbook 14,Smartchoice,Intel Core Ultra 5 (Series 2),16GB,1TB,3K OLED Touch Screen,14",120Hz,Win 11,M365 Basic (1Y)*,Office 2024, Silver,1.28 kg,UX3405CA-PZ345WS,Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="n">
-        <v>53990</v>
+        <v>117990</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Acer Aspire Lite 12th Gen,</t>
+          <t>asus_zenbook_s14_(2026),smartchoice,intel_core</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Acer Aspire Lite 12th Gen, Intel Core i5-12450H, Office 2024 + M365 Basic, 12GB RAM/512GB SSD, 39.62cm 15.6" FHD IPS Display, Win 11 Home, Pure Silver, 1.7KG,AL15-52H, Backlit KB, Thin &amp; Light Laptop</t>
+          <t>ASUS Zenbook S14 (2026),Smartchoice,Intel Core Ultra 5 226V,Intel Arc iGPU,16GB/512GB,3K OLED,Touchscreen,14"(35.5 cm),Windows 11,M365 Basic(1Y),Office 2024,Gray,1.2 Kg,UX5406SA-PZ658WS,Copilot+ PC</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="n">
-        <v>53990</v>
+        <v>134990</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Acer Aspire Lite 12th Gen,</t>
+          <t>Acer Aspire 3 Laptop Intel</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Acer Aspire Lite 12th Gen, Intel Core i5-12450H, Office 2024 + M365 Basic, 12GB RAM/512GB SSD, 39.62cm 15.6" FHD IPS Display, Win 11 Home, Pure Silver, 1.7KG,AL15-52H, Backlit KB, Thin &amp; Light Laptop</t>
+          <t>Acer Aspire 3 Laptop Intel Core Celeron N4500 Processor Laptop (8 GB LPDDR4X SDRAM/256 GB SSD/Win11 Home/38 WHR/HD Webcam) A325-45 with 39.63 cm (15.6") HD Display, Pure Silver, 1.5 KG</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="n">
-        <v>53990</v>
+        <v>36990</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Acer Aspire Lite 12th Gen,</t>
+          <t>Acer Aspire 3 Laptop Intel</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Acer Aspire Lite 12th Gen, Intel Core i5-12450H, Office 2024 + M365 Basic, 12GB RAM/512GB SSD, 39.62cm 15.6" FHD IPS Display, Win 11 Home, Pure Silver, 1.7KG,AL15-52H, Backlit KB, Thin &amp; Light Laptop</t>
+          <t>Acer Aspire 3 Laptop Intel Core Celeron N4500 Processor Laptop (8 GB LPDDR4X SDRAM/256 GB SSD/Win11 Home/38 WHR/HD Webcam) A325-45 with 39.63 cm (15.6") HD Display, Pure Silver, 1.5 KG</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="n">
-        <v>49990</v>
+        <v>36990</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
@@ -2031,11 +2031,11 @@
       </c>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="n">
-        <v>53990</v>
+        <v>52990</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-08</t>
         </is>
       </c>
     </row>
@@ -2052,158 +2052,158 @@
       </c>
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="n">
-        <v>50990</v>
+        <v>47990</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-17</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Acer Aspire One, Intel Core</t>
+          <t>Acer Aspire Lite 12th Gen,</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Acer Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X RAM/ 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
+          <t>Acer Aspire Lite 12th Gen, Intel Core i5-12450H, Office 2024 + M365 Basic, 12GB RAM/512GB SSD, 39.62cm 15.6" FHD IPS Display, Win 11 Home, Pure Silver, 1.7KG,AL15-52H, Backlit KB, Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="n">
-        <v>34990</v>
+        <v>53990</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-19</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Acer Aspire One, Intel Core</t>
+          <t>Acer Aspire Lite 12th Gen,</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Acer Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X RAM/ 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
+          <t>Acer Aspire Lite 12th Gen, Intel Core i5-12450H, Office 2024 + M365 Basic, 12GB RAM/512GB SSD, 39.62cm 15.6" FHD IPS Display, Win 11 Home, Pure Silver, 1.7KG,AL15-52H, Backlit KB, Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="n">
-        <v>34990</v>
+        <v>53990</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-20</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Acer Aspire One, Intel Core</t>
+          <t>Acer Aspire Lite 12th Gen,</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Acer Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X RAM/ 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
+          <t>Acer Aspire Lite 12th Gen, Intel Core i5-12450H, Office 2024 + M365 Basic, 12GB RAM/512GB SSD, 39.62cm 15.6" FHD IPS Display, Win 11 Home, Pure Silver, 1.7KG,AL15-52H, Backlit KB, Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
       <c r="D81" t="n">
-        <v>34990</v>
+        <v>53990</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-21</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Acer Aspire One, Intel Core</t>
+          <t>Acer Aspire Lite 12th Gen,</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Acer Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X RAM/ 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
+          <t>Acer Aspire Lite 12th Gen, Intel Core i5-12450H, Office 2024 + M365 Basic, 12GB RAM/512GB SSD, 39.62cm 15.6" FHD IPS Display, Win 11 Home, Pure Silver, 1.7KG,AL15-52H, Backlit KB, Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="n">
-        <v>33990</v>
+        <v>53990</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-22</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Acer Aspire One, Intel Core</t>
+          <t>Acer Aspire Lite 12th Gen,</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Acer Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X RAM/ 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
+          <t>Acer Aspire Lite 12th Gen, Intel Core i5-12450H, Office 2024 + M365 Basic, 12GB RAM/512GB SSD, 39.62cm 15.6" FHD IPS Display, Win 11 Home, Pure Silver, 1.7KG,AL15-52H, Backlit KB, Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="n">
-        <v>33990</v>
+        <v>49990</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-27</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Acer Aspire One, Intel Core</t>
+          <t>Acer Aspire Lite 12th Gen,</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Acer Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X RAM/ 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
+          <t>Acer Aspire Lite 12th Gen, Intel Core i5-12450H, Office 2024 + M365 Basic, 12GB RAM/512GB SSD, 39.62cm 15.6" FHD IPS Display, Win 11 Home, Pure Silver, 1.7KG,AL15-52H, Backlit KB, Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="n">
-        <v>35990</v>
+        <v>53990</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Acer Aspire One, Intel Core</t>
+          <t>Acer Aspire Lite 12th Gen,</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Acer Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X RAM/ 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
+          <t>Acer Aspire Lite 12th Gen, Intel Core i5-12450H, Office 2024 + M365 Basic, 12GB RAM/512GB SSD, 39.62cm 15.6" FHD IPS Display, Win 11 Home, Pure Silver, 1.7KG,AL15-52H, Backlit KB, Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="n">
-        <v>35990</v>
+        <v>50990</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
@@ -2220,11 +2220,11 @@
       </c>
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="n">
-        <v>35990</v>
+        <v>34990</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-08</t>
         </is>
       </c>
     </row>
@@ -2241,11 +2241,11 @@
       </c>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="n">
-        <v>35990</v>
+        <v>34990</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
@@ -2257,583 +2257,583 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Acer Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X RAM/ 512GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
+          <t>Acer Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X RAM/ 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="n">
-        <v>38990</v>
+        <v>34990</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-10</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>acer_one_14_laptop_z14-55m</t>
+          <t>Acer Aspire One, Intel Core</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Acer One 14 Laptop Z14-55M | 14" HD Display | AMD Ryzen 3 7320U | 8GB LPDDR5 RAM | 256GB NVMe SSD | Windows 11 | Thin &amp; Light Design | AMD Radeon Graphics | Silver</t>
+          <t>Acer Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X RAM/ 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="n">
-        <v>38750</v>
+        <v>33990</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-15</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>acer_one_14_laptop_z14-55m</t>
+          <t>Acer Aspire One, Intel Core</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Acer One 14 Laptop Z14-55M | 14" HD Display | AMD Ryzen 3 7320U | 8GB LPDDR5 RAM | 256GB NVMe SSD | Windows 11 | Thin &amp; Light Design | AMD Radeon Graphics | Silver</t>
+          <t>Acer Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X RAM/ 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="n">
-        <v>38500</v>
+        <v>33990</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-05-17</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>acer_one_14_laptop_z14-55m</t>
+          <t>Acer Aspire One, Intel Core</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Acer One 14 Laptop Z14-55M | 14" HD Display | AMD Ryzen 3 7320U | 8GB LPDDR5 RAM | 256GB NVMe SSD | Windows 11 | Thin &amp; Light Design | AMD Radeon Graphics | Silver</t>
+          <t>Acer Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X RAM/ 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
       <c r="D91" t="n">
-        <v>38500</v>
+        <v>35990</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-05-19</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Acer Smartchoice Aspire One, AMD</t>
+          <t>Acer Aspire One, Intel Core</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Acer Smartchoice Aspire One, AMD Ryzen 3-7320U, 8GB LPDDR5 RAM/ 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.48KG, A114-43, Thin and Light Laptop</t>
+          <t>Acer Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X RAM/ 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="n">
-        <v>39990</v>
+        <v>35990</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-20</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Acer Smartchoice Aspire One, AMD</t>
+          <t>Acer Aspire One, Intel Core</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Acer Smartchoice Aspire One, AMD Ryzen 3-7320U, 8GB LPDDR5 RAM/ 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.48KG, A114-43, Thin and Light Laptop</t>
+          <t>Acer Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X RAM/ 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
       <c r="D93" t="n">
-        <v>39990</v>
+        <v>35990</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-21</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Acer Smartchoice Aspire One, Intel</t>
+          <t>Acer Aspire One, Intel Core</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Acer Smartchoice Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X / 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
+          <t>Acer Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X RAM/ 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="n">
-        <v>32990</v>
+        <v>35990</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-22</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Acer Smartchoice Aspire One, Intel</t>
+          <t>Acer Aspire One, Intel Core</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Acer Smartchoice Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X / 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
+          <t>Acer Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X RAM/ 512GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="n">
-        <v>32990</v>
+        <v>38990</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-14</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Acer Smartchoice Aspire One, Intel</t>
+          <t>acer_one_14_laptop_z14-55m</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Acer Smartchoice Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X / 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
+          <t>Acer One 14 Laptop Z14-55M | 14" HD Display | AMD Ryzen 3 7320U | 8GB LPDDR5 RAM | 256GB NVMe SSD | Windows 11 | Thin &amp; Light Design | AMD Radeon Graphics | Silver</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="n">
-        <v>32990</v>
+        <v>38750</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Acer Smartchoice Aspire One, Intel</t>
+          <t>acer_one_14_laptop_z14-55m</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Acer Smartchoice Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X / 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
+          <t>Acer One 14 Laptop Z14-55M | 14" HD Display | AMD Ryzen 3 7320U | 8GB LPDDR5 RAM | 256GB NVMe SSD | Windows 11 | Thin &amp; Light Design | AMD Radeon Graphics | Silver</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="n">
-        <v>32990</v>
+        <v>38500</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Acer Smartchoice Aspire One, Intel</t>
+          <t>acer_one_14_laptop_z14-55m</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Acer Smartchoice Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X / 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
+          <t>Acer One 14 Laptop Z14-55M | 14" HD Display | AMD Ryzen 3 7320U | 8GB LPDDR5 RAM | 256GB NVMe SSD | Windows 11 | Thin &amp; Light Design | AMD Radeon Graphics | Silver</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="n">
-        <v>32990</v>
+        <v>38500</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Acer Smartchoice Aspire One, Intel</t>
+          <t>acer_one_14_laptop_z14-55m</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Acer Smartchoice Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X / 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
+          <t>Acer One 14 Laptop Z14-55M | 14" HD Display | AMD Ryzen 3 7320U | 8GB LPDDR5 RAM | 256GB NVMe SSD | Windows 11 | Thin &amp; Light Design | AMD Radeon Graphics | Silver</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
       <c r="D99" t="n">
-        <v>35990</v>
+        <v>38500</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Acer Smartchoice Aspire One, Intel</t>
+          <t>Acer Smartchoice Aspire One, AMD</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Acer Smartchoice Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X / 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
+          <t>Acer Smartchoice Aspire One, AMD Ryzen 3-7320U, 8GB LPDDR5 RAM/ 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.48KG, A114-43, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="n">
-        <v>35990</v>
+        <v>39990</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Acer Smartchoice Aspire One, Intel</t>
+          <t>Acer Smartchoice Aspire One, AMD</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Acer Smartchoice Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X / 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
+          <t>Acer Smartchoice Aspire One, AMD Ryzen 3-7320U, 8GB LPDDR5 RAM/ 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.48KG, A114-43, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
       <c r="D101" t="n">
-        <v>35990</v>
+        <v>39990</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Acer Smartchoice Aspire One, Intel</t>
+          <t>acer_smartchoice_aspire_one,_amd</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Acer Smartchoice Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X / 512GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
+          <t>Acer Smartchoice Aspire One, AMD Ryzen 3-7320U, 8GB LPDDR5 RAM/ 512GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.48KG, A114-43, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="n">
-        <v>34990</v>
+        <v>41990</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>acer_smartchoice_aspire_one,_intel</t>
+          <t>Acer Smartchoice Aspire One, Intel</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Acer Smartchoice Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X / 512GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
+          <t>Acer Smartchoice Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X / 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="n">
-        <v>37990</v>
+        <v>32990</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>acer_smartchoice_aspire_one,_intel</t>
+          <t>Acer Smartchoice Aspire One, Intel</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Acer Smartchoice Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X / 512GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
+          <t>Acer Smartchoice Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X / 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="n">
-        <v>39990</v>
+        <v>32990</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-05-24</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Acer Swift Go 14 AI</t>
+          <t>Acer Smartchoice Aspire One, Intel</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Acer Swift Go 14 AI PC, Qualcomm SnapdragonX Plus X1P-42-100,Office 2024 + M365 Basic,(16GB LPDDR5X/ 512GB SSD/14.5-inch WUXGA//Qualcomm Adreno/1440p IR Camera with Shutter/Win11) 1.32 kg, Steel Grey.</t>
+          <t>Acer Smartchoice Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X / 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="n">
-        <v>79990</v>
+        <v>32990</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>acer_travellite_thin_laptop_amd</t>
+          <t>Acer Smartchoice Aspire One, Intel</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Acer TravelLite Thin Laptop AMD Ryzen 5 7430U (6-Core) 16GB RAM, 512GB SSD 14" Full HD Anti-Glare Display Privacy Shutter Windows 11 MS Office Metal Body 1.34Kg Black 30M Warranty</t>
+          <t>Acer Smartchoice Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X / 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C106" t="inlineStr"/>
       <c r="D106" t="n">
-        <v>53450</v>
+        <v>32990</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-27</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Neo 13″</t>
+          <t>Acer Smartchoice Aspire One, Intel</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Citrus</t>
+          <t>Acer Smartchoice Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X / 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
       <c r="D107" t="n">
-        <v>65000</v>
+        <v>32990</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-05-28</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Neo 13″</t>
+          <t>Acer Smartchoice Aspire One, Intel</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Indigo</t>
+          <t>Acer Smartchoice Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X / 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="n">
-        <v>67900</v>
+        <v>35990</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Neo 13″</t>
+          <t>Acer Smartchoice Aspire One, Intel</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Indigo</t>
+          <t>Acer Smartchoice Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X / 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
       <c r="D109" t="n">
-        <v>65000</v>
+        <v>35990</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-12</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Neo 13″</t>
+          <t>Acer Smartchoice Aspire One, Intel</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Indigo</t>
+          <t>Acer Smartchoice Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X / 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="n">
-        <v>65700</v>
+        <v>35990</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Neo 13″</t>
+          <t>Acer Smartchoice Aspire One, Intel</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Indigo</t>
+          <t>Acer Smartchoice Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X / 512GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
       <c r="D111" t="n">
-        <v>65000</v>
+        <v>34990</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-07-12</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Neo 13″</t>
+          <t>acer_smartchoice_aspire_one,_intel</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Indigo</t>
+          <t>Acer Smartchoice Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X / 512GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="n">
-        <v>65000</v>
+        <v>37990</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Neo 13″</t>
+          <t>acer_smartchoice_aspire_one,_intel</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Indigo</t>
+          <t>Acer Smartchoice Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X / 512GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
       <c r="D113" t="n">
-        <v>65000</v>
+        <v>39990</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Neo 13″</t>
+          <t>Acer Swift Go 14 AI</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Silver</t>
+          <t>Acer Swift Go 14 AI PC, Qualcomm SnapdragonX Plus X1P-42-100,Office 2024 + M365 Basic,(16GB LPDDR5X/ 512GB SSD/14.5-inch WUXGA//Qualcomm Adreno/1440p IR Camera with Shutter/Win11) 1.32 kg, Steel Grey.</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
       <c r="D114" t="n">
-        <v>65000</v>
+        <v>79990</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Neo 13″</t>
+          <t>acer_travellite_thin_laptop_amd</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Silver</t>
+          <t>Acer TravelLite Thin Laptop AMD Ryzen 5 7430U (6-Core) 16GB RAM, 512GB SSD 14" Full HD Anti-Glare Display Privacy Shutter Windows 11 MS Office Metal Body 1.34Kg Black 30M Warranty</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
       <c r="D115" t="n">
-        <v>65000</v>
+        <v>53450</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -2845,16 +2845,16 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Silver</t>
+          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Citrus</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="n">
-        <v>65700</v>
+        <v>65000</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Silver</t>
+          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Indigo</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
@@ -2875,7 +2875,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -2887,7 +2887,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Silver</t>
+          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Indigo</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
@@ -2908,16 +2908,16 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Silver</t>
+          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Indigo</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="n">
-        <v>64990</v>
+        <v>65700</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-28</t>
         </is>
       </c>
     </row>
@@ -2929,16 +2929,16 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Silver</t>
+          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Indigo</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
       <c r="D120" t="n">
-        <v>63990</v>
+        <v>65000</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -2950,16 +2950,16 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Silver</t>
+          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Indigo</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
       <c r="D121" t="n">
-        <v>63990</v>
+        <v>65000</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
@@ -2971,415 +2971,415 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Silver</t>
+          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Indigo</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
       <c r="D122" t="n">
-        <v>63990</v>
+        <v>65000</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Pro Laptop</t>
+          <t>Apple 2026 MacBook Neo 13″</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Pro Laptop with M5 Max chip with 18‑core CPU and 40‑core GPU: Built for AI, 41.05 cm (16.2″) Liquid Retina XDR Display, 48GB Unified Memory, 2TB SSD Storage; Space Black</t>
+          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Silver</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
       <c r="D123" t="n">
-        <v>499900</v>
+        <v>65000</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-24</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Pro Laptop</t>
+          <t>Apple 2026 MacBook Neo 13″</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Pro Laptop with M5 Max chip with 18‑core CPU and 40‑core GPU: Built for AI, 41.05 cm (16.2″) Liquid Retina XDR Display, 48GB Unified Memory, 2TB SSD Storage; Space Black</t>
+          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Silver</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="n">
-        <v>499900</v>
+        <v>65000</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Pro Laptop</t>
+          <t>Apple 2026 MacBook Neo 13″</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Pro Laptop with M5 Max chip with 18‑core CPU and 40‑core GPU: Built for AI, 41.05 cm (16.2″) Liquid Retina XDR Display, 48GB Unified Memory, 2TB SSD Storage; Space Black</t>
+          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Silver</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
       <c r="D125" t="n">
-        <v>499900</v>
+        <v>65700</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-27</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Pro Laptop</t>
+          <t>Apple 2026 MacBook Neo 13″</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Pro Laptop with M5 Pro chip with 15‑core CPU and 16‑core GPU: Built for AI, 35.97 cm (14.2″) Liquid Retina XDR Display, 24GB Unified Memory, 1TB SSD Storage; Silver</t>
+          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Silver</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
       <c r="D126" t="n">
-        <v>234900</v>
+        <v>67900</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-31</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Pro Laptop</t>
+          <t>Apple 2026 MacBook Neo 13″</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Pro Laptop with M5 Pro chip with 15‑core CPU and 16‑core GPU: Built for AI, 35.97 cm (14.2″) Liquid Retina XDR Display, 24GB Unified Memory, 1TB SSD Storage; Silver</t>
+          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Silver</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
       <c r="D127" t="n">
-        <v>227400</v>
+        <v>65000</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-02</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>BrowseBook 14.1" FHD IPS Laptop</t>
+          <t>Apple 2026 MacBook Neo 13″</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>BrowseBook 14.1" FHD IPS Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB RAM | 128GB SSD | Windows 11 | 38Wh | 1.3kg | Grey</t>
+          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Silver</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
       <c r="D128" t="n">
-        <v>13990</v>
+        <v>64990</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>BrowseBook 14.1" FHD IPS Laptop</t>
+          <t>Apple 2026 MacBook Neo 13″</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>BrowseBook 14.1" FHD IPS Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB RAM | 128GB SSD | Windows 11 | 38Wh | 1.3kg | Grey</t>
+          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Silver</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
       <c r="D129" t="n">
-        <v>13990</v>
+        <v>63990</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>BrowseBook 14.1" FHD IPS Laptop</t>
+          <t>Apple 2026 MacBook Neo 13″</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>BrowseBook 14.1" FHD IPS Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB RAM | 128GB SSD | Windows 11 | 38Wh | 1.3kg | Grey</t>
+          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Silver</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
       <c r="D130" t="n">
-        <v>13990</v>
+        <v>63990</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>BrowseBook 14.1" FHD IPS Laptop</t>
+          <t>Apple 2026 MacBook Neo 13″</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>BrowseBook 14.1" FHD IPS Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB RAM | 128GB SSD | Windows 11 | 38Wh | 1.3kg | Grey</t>
+          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Silver</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
       <c r="D131" t="n">
-        <v>20990</v>
+        <v>63990</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-06-12</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>BrowseBook 14.1" FHD IPS Laptop</t>
+          <t>Apple 2026 MacBook Pro Laptop</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>BrowseBook 14.1" FHD IPS Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 8GB RAM | 256GB SSD | Windows 11 | 38Wh | 1.3kg | Grey</t>
+          <t>Apple 2026 MacBook Pro Laptop with M5 Max chip with 18‑core CPU and 40‑core GPU: Built for AI, 41.05 cm (16.2″) Liquid Retina XDR Display, 48GB Unified Memory, 2TB SSD Storage; Space Black</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
       <c r="D132" t="n">
-        <v>18990</v>
+        <v>499900</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron) Laptop,</t>
+          <t>Apple 2026 MacBook Pro Laptop</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core 3 100U Processor, 8GB DDR4, 512 SSD, 15.6" NT FHD 120Hz IPS AG 250 nit Display, Win 11 + Office H&amp;S 2024, Carbon Black, Thin &amp; Light- 1.63Kg</t>
+          <t>Apple 2026 MacBook Pro Laptop with M5 Max chip with 18‑core CPU and 40‑core GPU: Built for AI, 41.05 cm (16.2″) Liquid Retina XDR Display, 48GB Unified Memory, 2TB SSD Storage; Space Black</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="n">
-        <v>46490</v>
+        <v>499900</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-28</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>dell_15_(previously_inspiron)_laptop,</t>
+          <t>Apple 2026 MacBook Pro Laptop</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 16GB DDR4, 512 SSD, Intel UHD Graphics, 15.6" FHD 120Hz IPS AG 250 nit Display, Win 11 + Office 2024, Black, 1.63Kg</t>
+          <t>Apple 2026 MacBook Pro Laptop with M5 Max chip with 18‑core CPU and 40‑core GPU: Built for AI, 41.05 cm (16.2″) Liquid Retina XDR Display, 48GB Unified Memory, 2TB SSD Storage; Space Black</t>
         </is>
       </c>
       <c r="C134" t="inlineStr"/>
       <c r="D134" t="n">
-        <v>58990</v>
+        <v>499900</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-02</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron) Laptop,</t>
+          <t>Apple 2026 MacBook Pro Laptop</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 8GB DDR4, 512 SSD, 15.6" FHD 120Hz IPS 250 nit Display, Win 11 + Office H&amp;S 2024, Carbon Black, Thin &amp; Light 1.63Kg</t>
+          <t>Apple 2026 MacBook Pro Laptop with M5 Pro chip with 15‑core CPU and 16‑core GPU: Built for AI, 35.97 cm (14.2″) Liquid Retina XDR Display, 24GB Unified Memory, 1TB SSD Storage; Silver</t>
         </is>
       </c>
       <c r="C135" t="inlineStr"/>
       <c r="D135" t="n">
-        <v>45490</v>
+        <v>234900</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-06-12</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron) Laptop,</t>
+          <t>Apple 2026 MacBook Pro Laptop</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 8GB DDR4, 512 SSD, 15.6" FHD 120Hz IPS 250 nit Display, Win 11 + Office H&amp;S 2024, Carbon Black, Thin &amp; Light 1.63Kg</t>
+          <t>Apple 2026 MacBook Pro Laptop with M5 Pro chip with 15‑core CPU and 16‑core GPU: Built for AI, 35.97 cm (14.2″) Liquid Retina XDR Display, 24GB Unified Memory, 1TB SSD Storage; Silver</t>
         </is>
       </c>
       <c r="C136" t="inlineStr"/>
       <c r="D136" t="n">
-        <v>44990</v>
+        <v>227400</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron) Laptop,</t>
+          <t>BrowseBook 14.1" FHD IPS Laptop</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 8GB DDR4, 512 SSD, 15.6" FHD 120Hz IPS 250 nit Display, Win 11 + Office H&amp;S 2024, Carbon Black, Thin &amp; Light 1.63Kg</t>
+          <t>BrowseBook 14.1" FHD IPS Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB RAM | 128GB SSD | Windows 11 | 38Wh | 1.3kg | Grey</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
       <c r="D137" t="n">
-        <v>44990</v>
+        <v>13990</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron) Laptop,</t>
+          <t>BrowseBook 14.1" FHD IPS Laptop</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 8GB DDR4, 512 SSD, 15.6" FHD 120Hz IPS 250 nit Display, Win 11 + Office H&amp;S 2024, Carbon Black, Thin &amp; Light 1.63Kg</t>
+          <t>BrowseBook 14.1" FHD IPS Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB RAM | 128GB SSD | Windows 11 | 38Wh | 1.3kg | Grey</t>
         </is>
       </c>
       <c r="C138" t="inlineStr"/>
       <c r="D138" t="n">
-        <v>45490</v>
+        <v>13990</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-04-16</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron) Laptop,</t>
+          <t>BrowseBook 14.1" FHD IPS Laptop</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 8GB DDR4, 512 SSD, 15.6" FHD 120Hz IPS 250 nit Display, Win 11 + Office H&amp;S 2024, Carbon Black, Thin &amp; Light 1.63Kg</t>
+          <t>BrowseBook 14.1" FHD IPS Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB RAM | 128GB SSD | Windows 11 | 38Wh | 1.3kg | Grey</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
       <c r="D139" t="n">
-        <v>45490</v>
+        <v>13990</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron) Laptop,</t>
+          <t>BrowseBook 14.1" FHD IPS Laptop</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 8GB DDR4, 512 SSD, 15.6" FHD 120Hz IPS 250 nit Display, Win 11 + Office H&amp;S 2024, Carbon Black, Thin &amp; Light 1.63Kg</t>
+          <t>BrowseBook 14.1" FHD IPS Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB RAM | 128GB SSD | Windows 11 | 38Wh | 1.3kg | Grey</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
       <c r="D140" t="n">
-        <v>45490</v>
+        <v>20990</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron) Laptop,</t>
+          <t>BrowseBook 14.1" FHD IPS Laptop</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 8GB DDR4, 512 SSD, 15.6" FHD 120Hz IPS 250 nit Display, Win 11 + Office H&amp;S 2024, Carbon Black, Thin &amp; Light 1.63Kg</t>
+          <t>BrowseBook 14.1" FHD IPS Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 8GB RAM | 256GB SSD | Windows 11 | 38Wh | 1.3kg | Grey</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
       <c r="D141" t="n">
-        <v>46490</v>
+        <v>18990</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-15</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3391,16 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 8GB DDR4, 512 SSD, 15.6" FHD 120Hz IPS 250 nit Display, Win 11 + Office H&amp;S 2024, Carbon Black, Thin &amp; Light 1.63Kg</t>
+          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core 3 100U Processor, 8GB DDR4, 512 SSD, 15.6" NT FHD 120Hz IPS AG 250 nit Display, Win 11 + Office H&amp;S 2024, Carbon Black, Thin &amp; Light- 1.63Kg</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
       <c r="D142" t="n">
-        <v>46990</v>
+        <v>46490</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
@@ -3412,16 +3412,16 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 8GB, 512GB, Intel UHD Graphics, 15.6" FHD IPS 250nit Display, 12m Mcafee, Win 11 + MSO'24, Platinum Silver, 1.63kg</t>
+          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 16GB DDR4, 512 SSD, Intel UHD Graphics, 15.6" FHD 120Hz IPS AG 250 nit Display, Win 11 + Office 2024, Black, 1.63Kg</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
       <c r="D143" t="n">
-        <v>47499</v>
+        <v>58990</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -3433,33 +3433,33 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 8GB, 512GB, Intel UHD Graphics, 15.6" FHD IPS 250nit Display, 12m Mcafee, Win 11 + MSO'24, Platinum Silver, 1.63kg</t>
+          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 16GB DDR4, 512 SSD, Intel UHD Graphics, 15.6" FHD 120Hz IPS AG 250 nit Display, Win 11 + Office 2024, Black, 1.63Kg</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
       <c r="D144" t="n">
-        <v>47499</v>
+        <v>59490</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron), 13th</t>
+          <t>Dell 15 (Previously Inspiron) Laptop,</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron), 13th Gen Intel Core i5-1334U (16GB RAM, 1TB SSD) FHD, Anti-Glare 15.6"/39.62cm, Windows 11 MSO'24, Silver, 1.62kg, 12 Month McAfee, Thin &amp; Light, Backlit Keyboard Laptop</t>
+          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 8GB DDR4, 512 SSD, 15.6" FHD 120Hz IPS 250 nit Display, Win 11 + Office H&amp;S 2024, Carbon Black, Thin &amp; Light 1.63Kg</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
       <c r="D145" t="n">
-        <v>63990</v>
+        <v>45490</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
@@ -3470,185 +3470,185 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>dell_15_(previously_inspiron),_amd</t>
+          <t>Dell 15 (Previously Inspiron) Laptop,</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron), AMD Ryzen 5-7530U, 16GB RAM, 512GB SSD, FHD IPS, 15.6"/39.62cm, Win 11, MSO 2024, Platinum Silver, 1.67kg,Standard Keyboard, 12 Month McAfee, Thin &amp; Light, Laptop</t>
+          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 8GB DDR4, 512 SSD, 15.6" FHD 120Hz IPS 250 nit Display, Win 11 + Office H&amp;S 2024, Carbon Black, Thin &amp; Light 1.63Kg</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
       <c r="D146" t="n">
-        <v>56086</v>
+        <v>44990</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Dell 15 AI Powered Laptop,</t>
+          <t>Dell 15 (Previously Inspiron) Laptop,</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Dell 15 AI Powered Laptop, Intel Core Ultra 5 225H, 8GB DDR5 RAM, 512GB SSD, 15.6" FHD Anti-Glare Display, Intel Arc Graphics, Standard Keyboard, Dedicated Copilot Key, Black, Win11 Home + MSO H&amp;S'24</t>
+          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 8GB DDR4, 512 SSD, 15.6" FHD 120Hz IPS 250 nit Display, Win 11 + Office H&amp;S 2024, Carbon Black, Thin &amp; Light 1.63Kg</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
       <c r="D147" t="n">
-        <v>68990</v>
+        <v>44990</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>dell_15_ai_powered_laptop,</t>
+          <t>Dell 15 (Previously Inspiron) Laptop,</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Dell 15 Ai Powered Laptop, Intel Core Ultra 7 255H, 16GB DDR5 RAM, 512GB SSD, 15.6" FHD Anti-Glare Display, Intel Arc Graphics, Backlit Keyboard, Dedicated Copilot Key, Silver, Win11 Home + MSO H&amp;S'24</t>
+          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 8GB DDR4, 512 SSD, 15.6" FHD 120Hz IPS 250 nit Display, Win 11 + Office H&amp;S 2024, Carbon Black, Thin &amp; Light 1.63Kg</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
       <c r="D148" t="n">
-        <v>103990</v>
+        <v>45490</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Dell 15 Smart Choice (Previously</t>
+          <t>Dell 15 (Previously Inspiron) Laptop,</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Dell 15 Smart Choice (Previously Inspiron), 13th Gen Intel Core i5-1334U (16GB RAM, 1TB SSD) FHD, 15.6"/39.62cm, Windows 11 MSO'24, Silver, 1.62kg, 12 Month McAfee, Backlit KB, Thin &amp; Light Laptop</t>
+          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 8GB DDR4, 512 SSD, 15.6" FHD 120Hz IPS 250 nit Display, Win 11 + Office H&amp;S 2024, Carbon Black, Thin &amp; Light 1.63Kg</t>
         </is>
       </c>
       <c r="C149" t="inlineStr"/>
       <c r="D149" t="n">
-        <v>66990</v>
+        <v>45490</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Dell 15 Smart Choice (Previously</t>
+          <t>Dell 15 (Previously Inspiron) Laptop,</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Dell 15 Smart Choice (Previously Inspiron), 13th Gen Intel Core i5-1334U (16GB RAM, 1TB SSD) FHD, 15.6"/39.62cm, Windows 11 MSO'24, Silver, 1.62kg, 12 Month McAfee, Backlit KB, Thin &amp; Light Laptop</t>
+          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 8GB DDR4, 512 SSD, 15.6" FHD 120Hz IPS 250 nit Display, Win 11 + Office H&amp;S 2024, Carbon Black, Thin &amp; Light 1.63Kg</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
       <c r="D150" t="n">
-        <v>67990</v>
+        <v>45490</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Dell 15 Smart Choice (Previously</t>
+          <t>Dell 15 (Previously Inspiron) Laptop,</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Dell 15 Smart Choice (Previously Inspiron), 13th Gen Intel Core i5-1334U (16GB RAM, 1TB SSD) FHD, 15.6"/39.62cm, Windows 11 MSO'24, Silver, 1.62kg, 12 Month McAfee, Backlit KB, Thin &amp; Light Laptop</t>
+          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 8GB DDR4, 512 SSD, 15.6" FHD 120Hz IPS 250 nit Display, Win 11 + Office H&amp;S 2024, Carbon Black, Thin &amp; Light 1.63Kg</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
       <c r="D151" t="n">
-        <v>67990</v>
+        <v>46490</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-12</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Dell 15 Smart Choice (Previously</t>
+          <t>Dell 15 (Previously Inspiron) Laptop,</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Dell 15 Smart Choice (Previously Inspiron), 13th Gen Intel Core i5-1334U (16GB RAM, 1TB SSD) FHD, 15.6"/39.62cm, Windows 11 MSO'24, Silver, 1.62kg, 12 Month McAfee, Backlit KB, Thin &amp; Light Laptop</t>
+          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 8GB DDR4, 512 SSD, 15.6" FHD 120Hz IPS 250 nit Display, Win 11 + Office H&amp;S 2024, Carbon Black, Thin &amp; Light 1.63Kg</t>
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="n">
-        <v>69990</v>
+        <v>46990</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Dell 15 Smart Choice (Previously</t>
+          <t>dell_15_(previously_inspiron)_laptop,</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Dell 15 Smart Choice (Previously Inspiron), 13th Gen Intel Core i5-1334U (16GB RAM, 1TB SSD) FHD, 15.6"/39.62cm, Windows 11 MSO'24, Silver, 1.62kg, 12 Month McAfee, Backlit KB, Thin &amp; Light Laptop</t>
+          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 8GB, 512GB, Intel UHD Graphics, 15.6" FHD IPS 250nit Display, 12m Mcafee, Win 11 + MSO'24, Platinum Silver, 1.63kg</t>
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
       <c r="D153" t="n">
-        <v>67990</v>
+        <v>47499</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>dell_15_smartchoice_(previously_inspiron),</t>
+          <t>dell_15_(previously_inspiron)_laptop,</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Dell 15 SmartChoice (Previously Inspiron), Intel 13th Gen Core i5-1334U, 16GB, 1TB SSD, FHD,15.6"/39.62cm, Win 11, MSO'24, Silver, 1.62kg, [Dell 15], 12 Month McAfee, Backlit KB, Thin &amp; Light Laptop</t>
+          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 8GB, 512GB, Intel UHD Graphics, 15.6" FHD IPS 250nit Display, 12m Mcafee, Win 11 + MSO'24, Platinum Silver, 1.63kg</t>
         </is>
       </c>
       <c r="C154" t="inlineStr"/>
       <c r="D154" t="n">
-        <v>68990</v>
+        <v>47499</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
@@ -3659,290 +3659,290 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Dell 15, 13th Gen Intel</t>
+          <t>Dell 15 (Previously Inspiron), 13th</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Dell 15, 13th Gen Intel Core i5-1334U (16GB DDR4, 512GB SSD) Anti-Glare FHD 15.6"/39.62cm, Windows 11, Microsoft Office Home 2024, Grey, 1.66kg, [Vostro 3530], 12 Month McAfee, Thin &amp; Light Laptop</t>
+          <t>Dell 15 (Previously Inspiron), 13th Gen Intel Core i5-1334U (16GB RAM, 1TB SSD) FHD, Anti-Glare 15.6"/39.62cm, Windows 11 MSO'24, Silver, 1.62kg, 12 Month McAfee, Thin &amp; Light, Backlit Keyboard Laptop</t>
         </is>
       </c>
       <c r="C155" t="inlineStr"/>
       <c r="D155" t="n">
-        <v>61490</v>
+        <v>63990</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-17</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Dell 15, 13th Gen Intel</t>
+          <t>dell_15_(previously_inspiron),_amd</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Dell 15, 13th Gen Intel Core i5-1334U (16GB DDR4, 512GB SSD) Anti-Glare FHD 15.6"/39.62cm, Windows 11, Microsoft Office Home 2024, Grey, 1.66kg, [Vostro 3530], 12 Month McAfee, Thin &amp; Light Laptop</t>
+          <t>Dell 15 (Previously Inspiron), AMD Ryzen 5-7530U, 16GB RAM, 512GB SSD, FHD IPS, 15.6"/39.62cm, Win 11, MSO 2024, Platinum Silver, 1.67kg,Standard Keyboard, 12 Month McAfee, Thin &amp; Light, Laptop</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
       <c r="D156" t="n">
-        <v>63490</v>
+        <v>56086</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Dell 15, AMD Ryzen 7-7730U,</t>
+          <t>Dell 15 AI Powered Laptop,</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Dell 15, AMD Ryzen 7-7730U, 16GB DDR4, 512GB SSD, FHD, 15.6"/39.6cm, Windows 11, Microsoft Office Home 2024, Platinum Silver, 1.63Kg, [Dell 15], 120Hz 250nits, AMD Radeon Graphics,Thin &amp; Light, Laptop</t>
+          <t>Dell 15 AI Powered Laptop, Intel Core Ultra 5 225H, 8GB DDR5 RAM, 512GB SSD, 15.6" FHD Anti-Glare Display, Intel Arc Graphics, Standard Keyboard, Dedicated Copilot Key, Black, Win11 Home + MSO H&amp;S'24</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
       <c r="D157" t="n">
-        <v>59957</v>
+        <v>68990</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-05-15</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Dell 15, AMD Ryzen 7-7730U,</t>
+          <t>dell_15_ai_powered_laptop,</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Dell 15, AMD Ryzen 7-7730U, 16GB DDR4, 512GB SSD, FHD, 15.6"/39.6cm, Windows 11, Microsoft Office Home 2024, Platinum Silver, 1.63Kg, [Dell 15], 120Hz 250nits, AMD Radeon Graphics,Thin &amp; Light, Laptop</t>
+          <t>Dell 15 Ai Powered Laptop, Intel Core Ultra 7 255H, 16GB DDR5 RAM, 512GB SSD, 15.6" FHD Anti-Glare Display, Intel Arc Graphics, Backlit Keyboard, Dedicated Copilot Key, Silver, Win11 Home + MSO H&amp;S'24</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
       <c r="D158" t="n">
-        <v>58490</v>
+        <v>103990</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>dell_15,_intel_core_13th</t>
+          <t>Dell 15 Smart Choice (Previously</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Dell 15, Intel Core 13th Gen i5-1334U, FHD, 15.6"/39.62cm, Windows 11, MSO'24, Grey, 1.66kg, Vostro 3530, (16GB DDR4, 512GB SSD) Anti-Glare FHD 15.6"/39.62cm, 12 Month McAfee, Thin &amp; Light Laptop</t>
+          <t>Dell 15 Smart Choice (Previously Inspiron), 13th Gen Intel Core i5-1334U (16GB RAM, 1TB SSD) FHD, 15.6"/39.62cm, Windows 11 MSO'24, Silver, 1.62kg, 12 Month McAfee, Backlit KB, Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C159" t="inlineStr"/>
       <c r="D159" t="n">
-        <v>65490</v>
+        <v>66990</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-05-28</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Dell 15, Intel Core 3</t>
+          <t>Dell 15 Smart Choice (Previously</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Dell 15, Intel Core 3 14th Gen-100U, 16GB DDR4, 512GB SSD, FHD IPS, 15.6"/39.62cm, Windows 11, Microsoft Office Home 2024, Carbon Black, 1.63Kg, Thin &amp; Light, Laptop Model NO - Dell 15 DCU5250</t>
+          <t>Dell 15 Smart Choice (Previously Inspiron), 13th Gen Intel Core i5-1334U (16GB RAM, 1TB SSD) FHD, 15.6"/39.62cm, Windows 11 MSO'24, Silver, 1.62kg, 12 Month McAfee, Backlit KB, Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
       <c r="D160" t="n">
-        <v>51868</v>
+        <v>67990</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-05-31</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Dell 15, Intel Core i3/Core</t>
+          <t>Dell 15 Smart Choice (Previously</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Dell 15, Intel Core i3/Core 3 14th Gen-100U, 16GB DDR4, 512GB SSD, FHD IPS, 15.6"/39.62cm, Windows 11, Microsoft Office Home 2024, Carbon Black, 1.63Kg, Thin &amp; Light, Laptop Model NO - Dell 15 DCU5250</t>
+          <t>Dell 15 Smart Choice (Previously Inspiron), 13th Gen Intel Core i5-1334U (16GB RAM, 1TB SSD) FHD, 15.6"/39.62cm, Windows 11 MSO'24, Silver, 1.62kg, 12 Month McAfee, Backlit KB, Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C161" t="inlineStr"/>
       <c r="D161" t="n">
-        <v>48990</v>
+        <v>67990</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Dell 15, R5-7520U Processor, 8GB</t>
+          <t>Dell 15 Smart Choice (Previously</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Dell 15, R5-7520U Processor, 8GB LPDDR5 RAM, 512GB SSD, FHD 15.6"/39.62 cm Display, Windows 11, MSO'24, Carbon Black, 1.63kg, Standard Keyboard, 15 Month McAfee, Thin &amp; Light Laptop</t>
+          <t>Dell 15 Smart Choice (Previously Inspiron), 13th Gen Intel Core i5-1334U (16GB RAM, 1TB SSD) FHD, 15.6"/39.62cm, Windows 11 MSO'24, Silver, 1.62kg, 12 Month McAfee, Backlit KB, Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C162" t="inlineStr"/>
       <c r="D162" t="n">
-        <v>53990</v>
+        <v>69990</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-06-02</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>dell_g_series,_intel_core</t>
+          <t>Dell 15 Smart Choice (Previously</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Dell G Series, Intel Core i5-13450HX, 13th Gen, NVIDIA RTX 3050-6GB, 16GB, 512GB SSD, FHD, 15.6"/39.62cm, Windows 11, MSO'24, Dark Shadow Gray, 2.65KG, [G15-5530], Backlit Keyboard, Gaming Laptop</t>
+          <t>Dell 15 Smart Choice (Previously Inspiron), 13th Gen Intel Core i5-1334U (16GB RAM, 1TB SSD) FHD, 15.6"/39.62cm, Windows 11 MSO'24, Silver, 1.62kg, 12 Month McAfee, Backlit KB, Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C163" t="inlineStr"/>
       <c r="D163" t="n">
-        <v>89990</v>
+        <v>67990</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-14</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Dell G15, 13th Gen Intel</t>
+          <t>dell_15_smartchoice_(previously_inspiron),</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Dell G15, 13th Gen Intel Core i5-13450HX Processor, NVIDIA RTX 3050-6GB, (16GB RAM 1TB SSD) FHD 15.6"/39.62 cm, Orange Backlit Keyboard, Win 11, MS Office'24, Dark Shadow Grey, 2.65Kg Gaming Laptop</t>
+          <t>Dell 15 SmartChoice (Previously Inspiron), Intel 13th Gen Core i5-1334U, 16GB, 1TB SSD, FHD,15.6"/39.62cm, Win 11, MSO'24, Silver, 1.62kg, [Dell 15], 12 Month McAfee, Backlit KB, Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C164" t="inlineStr"/>
       <c r="D164" t="n">
-        <v>79590</v>
+        <v>68990</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Dell G15, 13th Gen Intel</t>
+          <t>dell_15_smartchoice_(previously_inspiron),</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Dell G15, 13th Gen Intel Core i5-13450HX Processor, NVIDIA RTX 3050-6GB, (16GB RAM 1TB SSD) FHD 15.6"/39.62 cm, Orange Backlit Keyboard, Win 11, MS Office'24, Dark Shadow Grey, 2.65Kg Gaming Laptop</t>
+          <t>Dell 15 SmartChoice (Previously Inspiron), Intel 13th Gen Core i5-1334U, 16GB, 1TB SSD, FHD,15.6"/39.62cm, Win 11, MSO'24, Silver, 1.62kg, [Dell 15], 12 Month McAfee, Backlit KB, Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C165" t="inlineStr"/>
       <c r="D165" t="n">
-        <v>79990</v>
+        <v>68990</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>EBook 11.6" HD Laptop |</t>
+          <t>Dell 15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>EBook 11.6" HD Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB DDR4 | 128GB eMMC + M.2 SSD Expandable Slot | Win 11 Home |31Wh Battery | UHD Graphics 600 | Black</t>
+          <t>Dell 15, 13th Gen Intel Core i5-1334U (16GB DDR4, 512GB SSD) Anti-Glare FHD 15.6"/39.62cm, Windows 11, Microsoft Office Home 2024, Grey, 1.66kg, [Vostro 3530], 12 Month McAfee, Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C166" t="inlineStr"/>
       <c r="D166" t="n">
-        <v>11990</v>
+        <v>61490</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>EBook 11.6" HD Laptop |</t>
+          <t>Dell 15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>EBook 11.6" HD Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB DDR4 | 128GB eMMC + M.2 SSD Expandable Slot | Win 11 Home |31Wh Battery | UHD Graphics 600 | Black</t>
+          <t>Dell 15, 13th Gen Intel Core i5-1334U (16GB DDR4, 512GB SSD) Anti-Glare FHD 15.6"/39.62cm, Windows 11, Microsoft Office Home 2024, Grey, 1.66kg, [Vostro 3530], 12 Month McAfee, Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C167" t="inlineStr"/>
       <c r="D167" t="n">
-        <v>11990</v>
+        <v>63490</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>EBook 11.6" HD Laptop |</t>
+          <t>Dell 15, AMD Ryzen 7-7730U,</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>EBook 11.6" HD Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB DDR4 | 128GB eMMC + M.2 SSD Expandable Slot | Win 11 Home |31Wh Battery | UHD Graphics 600 | Black</t>
+          <t>Dell 15, AMD Ryzen 7-7730U, 16GB DDR4, 512GB SSD, FHD, 15.6"/39.6cm, Windows 11, Microsoft Office Home 2024, Platinum Silver, 1.63Kg, [Dell 15], 120Hz 250nits, AMD Radeon Graphics,Thin &amp; Light, Laptop</t>
         </is>
       </c>
       <c r="C168" t="inlineStr"/>
       <c r="D168" t="n">
-        <v>11990</v>
+        <v>59957</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
@@ -3953,168 +3953,168 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>EBook 11.6" HD Laptop |</t>
+          <t>Dell 15, AMD Ryzen 7-7730U,</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>EBook 11.6" HD Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB DDR4 | 128GB eMMC + M.2 SSD Expandable Slot | Win 11 Home |31Wh Battery | UHD Graphics 600 | Black</t>
+          <t>Dell 15, AMD Ryzen 7-7730U, 16GB DDR4, 512GB SSD, FHD, 15.6"/39.6cm, Windows 11, Microsoft Office Home 2024, Platinum Silver, 1.63Kg, [Dell 15], 120Hz 250nits, AMD Radeon Graphics,Thin &amp; Light, Laptop</t>
         </is>
       </c>
       <c r="C169" t="inlineStr"/>
       <c r="D169" t="n">
-        <v>11990</v>
+        <v>58490</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-17</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>EBook 11.6" HD Laptop |</t>
+          <t>dell_15,_intel_core_13th</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>EBook 11.6" HD Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB DDR4 | 128GB eMMC + M.2 SSD Expandable Slot | Win 11 Home |31Wh Battery | UHD Graphics 600 | Black</t>
+          <t>Dell 15, Intel Core 13th Gen i5-1334U, FHD, 15.6"/39.62cm, Windows 11, MSO'24, Grey, 1.66kg, Vostro 3530, (16GB DDR4, 512GB SSD) Anti-Glare FHD 15.6"/39.62cm, 12 Month McAfee, Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C170" t="inlineStr"/>
       <c r="D170" t="n">
-        <v>11990</v>
+        <v>65490</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>EBook 11.6" HD Laptop |</t>
+          <t>Dell 15, Intel Core 3</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>EBook 11.6" HD Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB DDR4 | 128GB eMMC + M.2 SSD Expandable Slot | Win 11 Home |31Wh Battery | UHD Graphics 600 | Black</t>
+          <t>Dell 15, Intel Core 3 14th Gen-100U, 16GB DDR4, 512GB SSD, FHD IPS, 15.6"/39.62cm, Windows 11, Microsoft Office Home 2024, Carbon Black, 1.63Kg, Thin &amp; Light, Laptop Model NO - Dell 15 DCU5250</t>
         </is>
       </c>
       <c r="C171" t="inlineStr"/>
       <c r="D171" t="n">
-        <v>11990</v>
+        <v>51868</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>EBook 11.6" HD Laptop |</t>
+          <t>Dell 15, Intel Core i3/Core</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>EBook 11.6" HD Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB DDR4 | 128GB eMMC + M.2 SSD Expandable Slot | Win 11 Home |31Wh Battery | UHD Graphics 600 | Black</t>
+          <t>Dell 15, Intel Core i3/Core 3 14th Gen-100U, 16GB DDR4, 512GB SSD, FHD IPS, 15.6"/39.62cm, Windows 11, Microsoft Office Home 2024, Carbon Black, 1.63Kg, Thin &amp; Light, Laptop Model NO - Dell 15 DCU5250</t>
         </is>
       </c>
       <c r="C172" t="inlineStr"/>
       <c r="D172" t="n">
-        <v>11990</v>
+        <v>48990</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>EBook 11.6" HD Laptop |</t>
+          <t>Dell 15, R5-7520U Processor, 8GB</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>EBook 11.6" HD Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB DDR4 | 128GB eMMC + M.2 SSD Expandable Slot | Win 11 Home |31Wh Battery | UHD Graphics 600 | Black</t>
+          <t>Dell 15, R5-7520U Processor, 8GB LPDDR5 RAM, 512GB SSD, FHD 15.6"/39.62 cm Display, Windows 11, MSO'24, Carbon Black, 1.63kg, Standard Keyboard, 15 Month McAfee, Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C173" t="inlineStr"/>
       <c r="D173" t="n">
-        <v>11990</v>
+        <v>53990</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-04-16</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>EBook 11.6" HD Laptop |</t>
+          <t>dell_g_series,_intel_core</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>EBook 11.6" HD Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB DDR4 | 128GB eMMC + M.2 SSD Expandable Slot | Win 11 Home |31Wh Battery | UHD Graphics 600 | Black</t>
+          <t>Dell G Series, Intel Core i5-13450HX, 13th Gen, NVIDIA RTX 3050-6GB, 16GB, 512GB SSD, FHD, 15.6"/39.62cm, Windows 11, MSO'24, Dark Shadow Gray, 2.65KG, [G15-5530], Backlit Keyboard, Gaming Laptop</t>
         </is>
       </c>
       <c r="C174" t="inlineStr"/>
       <c r="D174" t="n">
-        <v>11990</v>
+        <v>89990</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>EBook 11.6" HD Laptop |</t>
+          <t>Dell G15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>EBook 11.6" HD Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB DDR4 | 128GB eMMC + M.2 SSD Expandable Slot | Win 11 Home |31Wh Battery | UHD Graphics 600 | Black</t>
+          <t>Dell G15, 13th Gen Intel Core i5-13450HX Processor, NVIDIA RTX 3050-6GB, (16GB RAM 1TB SSD) FHD 15.6"/39.62 cm, Orange Backlit Keyboard, Win 11, MS Office'24, Dark Shadow Grey, 2.65Kg Gaming Laptop</t>
         </is>
       </c>
       <c r="C175" t="inlineStr"/>
       <c r="D175" t="n">
-        <v>11990</v>
+        <v>79590</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>EBook 11.6" HD Laptop |</t>
+          <t>Dell G15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>EBook 11.6" HD Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB DDR4 | 128GB eMMC + M.2 SSD Expandable Slot | Win 11 Home |31Wh Battery | UHD Graphics 600 | Black</t>
+          <t>Dell G15, 13th Gen Intel Core i5-13450HX Processor, NVIDIA RTX 3050-6GB, (16GB RAM 1TB SSD) FHD 15.6"/39.62 cm, Orange Backlit Keyboard, Win 11, MS Office'24, Dark Shadow Grey, 2.65Kg Gaming Laptop</t>
         </is>
       </c>
       <c r="C176" t="inlineStr"/>
       <c r="D176" t="n">
-        <v>16990</v>
+        <v>79990</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-08</t>
         </is>
       </c>
     </row>
@@ -4131,18 +4131,18 @@
       </c>
       <c r="C177" t="inlineStr"/>
       <c r="D177" t="n">
-        <v>16990</v>
+        <v>11990</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-04-16</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>ebook_11.6"_hd_laptop_|</t>
+          <t>EBook 11.6" HD Laptop |</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -4152,18 +4152,18 @@
       </c>
       <c r="C178" t="inlineStr"/>
       <c r="D178" t="n">
-        <v>10603</v>
+        <v>11990</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>ebook_11.6"_hd_laptop_|</t>
+          <t>EBook 11.6" HD Laptop |</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -4173,18 +4173,18 @@
       </c>
       <c r="C179" t="inlineStr"/>
       <c r="D179" t="n">
-        <v>10990</v>
+        <v>11990</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>ebook_11.6"_hd_laptop_|</t>
+          <t>EBook 11.6" HD Laptop |</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -4194,343 +4194,343 @@
       </c>
       <c r="C180" t="inlineStr"/>
       <c r="D180" t="n">
-        <v>10990</v>
+        <v>11990</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-05-19</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>hp_14_smartchoice,_intel_core</t>
+          <t>EBook 11.6" HD Laptop |</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>HP 14 Smartchoice, Intel Core Ultra 5 125H 12 TOPS, 24GB DDR5 (Upgradeable) 1TB SSD, Anti-Glare, FHD, 14''/35.6cm,Win11, M365*Office24, Silver, 1.4kg, ep1180tu, FHD Camera w/Shutter, Backlit AI Laptop</t>
+          <t>EBook 11.6" HD Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB DDR4 | 128GB eMMC + M.2 SSD Expandable Slot | Win 11 Home |31Wh Battery | UHD Graphics 600 | Black</t>
         </is>
       </c>
       <c r="C181" t="inlineStr"/>
       <c r="D181" t="n">
-        <v>77990</v>
+        <v>11990</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>hp_14_smartchoice,_intel_core</t>
+          <t>EBook 11.6" HD Laptop |</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>HP 14 Smartchoice, Intel Core Ultra 5 125H 12 TOPS, 24GB DDR5 (Upgradeable) 1TB SSD, Anti-Glare, FHD, 14''/35.6cm,Win11, M365*Office24, Silver, 1.4kg, ep1180tu, FHD Camera w/Shutter, Backlit AI Laptop</t>
+          <t>EBook 11.6" HD Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB DDR4 | 128GB eMMC + M.2 SSD Expandable Slot | Win 11 Home |31Wh Battery | UHD Graphics 600 | Black</t>
         </is>
       </c>
       <c r="C182" t="inlineStr"/>
       <c r="D182" t="n">
-        <v>77990</v>
+        <v>11990</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-05-21</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>hp_14,_amd_ryzen_7</t>
+          <t>EBook 11.6" HD Laptop |</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>HP 14, AMD Ryzen 7 7730U (16GB DDR4, 512GB SSD) FHD, Anti-Glare, Micro-Edge, 14''/35.6cm, Win11, M365 Basic(1yr), Office Home24, Silver,1.4kg, EM0104AU, FHD Camera w/Privacy Shutter, Backlit Laptop</t>
+          <t>EBook 11.6" HD Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB DDR4 | 128GB eMMC + M.2 SSD Expandable Slot | Win 11 Home |31Wh Battery | UHD Graphics 600 | Black</t>
         </is>
       </c>
       <c r="C183" t="inlineStr"/>
       <c r="D183" t="n">
-        <v>59990</v>
+        <v>11990</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-31</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>hp_14,_amd_ryzen_7</t>
+          <t>EBook 11.6" HD Laptop |</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>HP 14, AMD Ryzen 7 7730U (16GB DDR4, 512GB SSD) FHD, Anti-Glare, Micro-Edge, 14''/35.6cm, Win11, M365 Basic(1yr), Office Home24, Silver,1.4kg, EM0104AU, FHD Camera w/Privacy Shutter, Backlit Laptop</t>
+          <t>EBook 11.6" HD Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB DDR4 | 128GB eMMC + M.2 SSD Expandable Slot | Win 11 Home |31Wh Battery | UHD Graphics 600 | Black</t>
         </is>
       </c>
       <c r="C184" t="inlineStr"/>
       <c r="D184" t="n">
-        <v>64990</v>
+        <v>11990</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>HP 14s Intel Celeron Dual</t>
+          <t>EBook 11.6" HD Laptop |</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>HP 14s Intel Celeron Dual Core N4500 Laptop (8GB/512GB SSD/Win 11) 14.0" HD Display, MSO 24, Black, 1.46kg, DQ3149TU Thin and Light Business Laptop</t>
+          <t>EBook 11.6" HD Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB DDR4 | 128GB eMMC + M.2 SSD Expandable Slot | Win 11 Home |31Wh Battery | UHD Graphics 600 | Black</t>
         </is>
       </c>
       <c r="C185" t="inlineStr"/>
       <c r="D185" t="n">
-        <v>40400</v>
+        <v>11990</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-06-02</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>HP 15 (2026), AMD Athlon</t>
+          <t>EBook 11.6" HD Laptop |</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>HP 15 (2026), AMD Athlon Dual Core 7120U - (8 GB DDR5/512 GB SSD/AMD Radeon 610M Graphics/DOS) Thin and Light Business Laptop/15.6" HD Display/Turbo Silver/Copilot Key/1.5kg</t>
+          <t>EBook 11.6" HD Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB DDR4 | 128GB eMMC + M.2 SSD Expandable Slot | Win 11 Home |31Wh Battery | UHD Graphics 600 | Black</t>
         </is>
       </c>
       <c r="C186" t="inlineStr"/>
       <c r="D186" t="n">
-        <v>39999</v>
+        <v>11990</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>HP 15 (2026), AMD Athlon</t>
+          <t>EBook 11.6" HD Laptop |</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>HP 15 (2026), AMD Athlon Dual Core 7120U - (8 GB DDR5/512 GB SSD/AMD Radeon 610M Graphics/Windows 11 Pro) Thin and Light Business Laptop/15.6" HD Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
+          <t>EBook 11.6" HD Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB DDR4 | 128GB eMMC + M.2 SSD Expandable Slot | Win 11 Home |31Wh Battery | UHD Graphics 600 | Black</t>
         </is>
       </c>
       <c r="C187" t="inlineStr"/>
       <c r="D187" t="n">
-        <v>39660</v>
+        <v>16990</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>hp_15_(2026),_amd_athlon</t>
+          <t>EBook 11.6" HD Laptop |</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>HP 15 (2026), AMD Athlon Dual Core 7120U - (8 GB DDR5/512 GB SSD/AMD Radeon 610M Graphics/Windows 11 Pro) Thin and Light Business Laptop/15.6" HD Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
+          <t>EBook 11.6" HD Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB DDR4 | 128GB eMMC + M.2 SSD Expandable Slot | Win 11 Home |31Wh Battery | UHD Graphics 600 | Black</t>
         </is>
       </c>
       <c r="C188" t="inlineStr"/>
       <c r="D188" t="n">
-        <v>41999</v>
+        <v>16990</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>hp_15_(2026),_amd_athlon</t>
+          <t>ebook_11.6"_hd_laptop_|</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>HP 15 (2026), AMD Athlon Dual Core 7120U - (8 GB DDR5/512 GB SSD/AMD Radeon 610M Graphics/Windows 11 Pro) Thin and Light Business Laptop/15.6" HD Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
+          <t>EBook 11.6" HD Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB DDR4 | 128GB eMMC + M.2 SSD Expandable Slot | Win 11 Home |31Wh Battery | UHD Graphics 600 | Black</t>
         </is>
       </c>
       <c r="C189" t="inlineStr"/>
       <c r="D189" t="n">
-        <v>42840</v>
+        <v>10603</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>hp_15_(2026),_amd_athlon</t>
+          <t>ebook_11.6"_hd_laptop_|</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>HP 15 (2026), AMD Athlon Dual Core 7120U - (8 GB DDR5/512 GB SSD/AMD Radeon 610M Graphics/Windows 11 Pro) Thin and Light Business Laptop/15.6" HD Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
+          <t>EBook 11.6" HD Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB DDR4 | 128GB eMMC + M.2 SSD Expandable Slot | Win 11 Home |31Wh Battery | UHD Graphics 600 | Black</t>
         </is>
       </c>
       <c r="C190" t="inlineStr"/>
       <c r="D190" t="n">
-        <v>42840</v>
+        <v>10990</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>HP 15 (2026), AMD Ryzen</t>
+          <t>ebook_11.6"_hd_laptop_|</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>HP 15 (2026), AMD Ryzen 3 Quad Core 7335U - (8 GB DDR5/512 GB SSD/AMD Radeon 660M Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
+          <t>EBook 11.6" HD Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB DDR4 | 128GB eMMC + M.2 SSD Expandable Slot | Win 11 Home |31Wh Battery | UHD Graphics 600 | Black</t>
         </is>
       </c>
       <c r="C191" t="inlineStr"/>
       <c r="D191" t="n">
-        <v>42780</v>
+        <v>10990</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>hp_15_(i5_14th_gen),</t>
+          <t>ebook_11.6"_hd_laptop_|</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>HP 15 (i5 14th Gen), Intel Core 5, 16GB RAM (Upgradeable), 512GB SSD, FHD, Anti-Glare, 15.6''/39.6cm, Win11, M365 Basic(1yr), Office24, Silver,1.59kg, fd0682tu, FHD Camera w/Shutter, Backlit Laptop</t>
+          <t>EBook 11.6" HD Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB DDR4 | 128GB eMMC + M.2 SSD Expandable Slot | Win 11 Home |31Wh Battery | UHD Graphics 600 | Black</t>
         </is>
       </c>
       <c r="C192" t="inlineStr"/>
       <c r="D192" t="n">
-        <v>63990</v>
+        <v>10990</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>hp_15_(i5_14th_gen),</t>
+          <t>hp_14_smartchoice,_intel_core</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>HP 15 (i5 14th Gen), Intel Core 5, 16GB RAM (Upgradeable), 512GB SSD, FHD, Anti-Glare, 15.6''/39.6cm, Win11, M365 Basic(1yr), Office24, Silver,1.59kg, fd0682tu, FHD Camera w/Shutter, Backlit Laptop</t>
+          <t>HP 14 Smartchoice, Intel Core Ultra 5 125H 12 TOPS, 24GB DDR5 (Upgradeable) 1TB SSD, Anti-Glare, FHD, 14''/35.6cm,Win11, M365*Office24, Silver, 1.4kg, ep1180tu, FHD Camera w/Shutter, Backlit AI Laptop</t>
         </is>
       </c>
       <c r="C193" t="inlineStr"/>
       <c r="D193" t="n">
-        <v>67990</v>
+        <v>77990</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>hp_15_laptop_|_amd</t>
+          <t>hp_14_smartchoice,_intel_core</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>HP 15 Laptop | AMD Ryzen 7 5825U |16GB DDR4 RAM | 512GB SSD |15.6" (39.6 cm) FHD Display |AMD Radeon Graphics| Backlit KB | FHD Camera| Win 11| MS Office 2024 + M365*(1-Yr) | Silver |1.59kg |fc0533AU</t>
+          <t>HP 14 Smartchoice, Intel Core Ultra 5 125H 12 TOPS, 24GB DDR5 (Upgradeable) 1TB SSD, Anti-Glare, FHD, 14''/35.6cm,Win11, M365*Office24, Silver, 1.4kg, ep1180tu, FHD Camera w/Shutter, Backlit AI Laptop</t>
         </is>
       </c>
       <c r="C194" t="inlineStr"/>
       <c r="D194" t="n">
-        <v>64990</v>
+        <v>77990</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>hp_15_laptop_|_intel</t>
+          <t>hp_14_smartchoice,_intel_core</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>HP 15 Laptop | Intel Core i5-13420H,13th Gen |16GB RAM | 512GB SSD | Win 11 |M365 Basic(1yr)* Office24|Anti-Glare, Micro-Edge, 15.6''/39.6cm|Backlit KB|FHD Camera w/Shutter|1.65kg, Silver -FR0045TU</t>
+          <t>HP 14 Smartchoice, Intel Core Ultra 5 125H 12 TOPS, 24GB DDR5 (Upgradeable) 1TB SSD, Anti-Glare, FHD, 14''/35.6cm,Win11, M365*Office24, Silver, 1.4kg, ep1180tu, FHD Camera w/Shutter, Backlit AI Laptop</t>
         </is>
       </c>
       <c r="C195" t="inlineStr"/>
       <c r="D195" t="n">
-        <v>68990</v>
+        <v>79990</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>hp_15_laptop,_(14th_gen</t>
+          <t>hp_14,_amd_ryzen_7</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>HP 15 Laptop, (14th Gen Core i5) Intel Core 5-120U (24GB RAM, 512GB SSD, Win 11, M365 Basic(1yr)* Office24,15.6''/39.6cm FHD Anti-Glare Display, Backlit KB, FHD Camera, Dual Speakers, Silver, 1.59kg)</t>
+          <t>HP 14, AMD Ryzen 7 7730U (16GB DDR4, 512GB SSD) FHD, Anti-Glare, Micro-Edge, 14''/35.6cm, Win11, M365 Basic(1yr), Office Home24, Silver,1.4kg, EM0104AU, FHD Camera w/Privacy Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C196" t="inlineStr"/>
       <c r="D196" t="n">
-        <v>72800</v>
+        <v>59990</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
@@ -4541,227 +4541,227 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>HP 15 Laptop, Intel (14th</t>
+          <t>hp_14,_amd_ryzen_7</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>HP 15 Laptop, Intel (14th Gen) Core 5 120U (24GB DDR5, 512GB SSD), Micro-Edge, Anti-Glare, 15.6''/39.6cm, Win11, M365* Office24, Silver, 1.59kg, fd0262TU, FHD Camera, Backlit, Dual Speakers</t>
+          <t>HP 14, AMD Ryzen 7 7730U (16GB DDR4, 512GB SSD) FHD, Anti-Glare, Micro-Edge, 14''/35.6cm, Win11, M365 Basic(1yr), Office Home24, Silver,1.4kg, EM0104AU, FHD Camera w/Privacy Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C197" t="inlineStr"/>
       <c r="D197" t="n">
-        <v>67990</v>
+        <v>64990</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, 13th Gen</t>
+          <t>HP 14s Intel Celeron Dual</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U (12GB DDR4, 512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver, 1.59kg, fd0573TU, FHD Camera w/Shutter Laptop</t>
+          <t>HP 14s Intel Celeron Dual Core N4500 Laptop (8GB/512GB SSD/Win 11) 14.0" HD Display, MSO 24, Black, 1.46kg, DQ3149TU Thin and Light Business Laptop</t>
         </is>
       </c>
       <c r="C198" t="inlineStr"/>
       <c r="D198" t="n">
-        <v>55990</v>
+        <v>40400</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-04-16</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, 13th Gen</t>
+          <t>hp_15_(2025),_amd_athlon</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U(8GB DDR4,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
+          <t>HP 15 (2025), AMD Athlon 7120U Dual Core - (8 GB/256 GB SSD/AMD Radeon Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" HD Display/Black/1.5 kg/MS Office 2021</t>
         </is>
       </c>
       <c r="C199" t="inlineStr"/>
       <c r="D199" t="n">
-        <v>51990</v>
+        <v>41999</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, 13th Gen</t>
+          <t>HP 15 (2026), AMD Athlon</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U(8GB DDR4,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
+          <t>HP 15 (2026), AMD Athlon Dual Core 7120U - (8 GB DDR5/512 GB SSD/AMD Radeon 610M Graphics/DOS) Thin and Light Business Laptop/15.6" HD Display/Turbo Silver/Copilot Key/1.5kg</t>
         </is>
       </c>
       <c r="C200" t="inlineStr"/>
       <c r="D200" t="n">
-        <v>51990</v>
+        <v>39999</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-08</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, 13th Gen</t>
+          <t>HP 15 (2026), AMD Athlon</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U(8GB DDR4,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
+          <t>HP 15 (2026), AMD Athlon Dual Core 7120U - (8 GB DDR5/512 GB SSD/AMD Radeon 610M Graphics/Windows 11 Pro) Thin and Light Business Laptop/15.6" HD Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
         </is>
       </c>
       <c r="C201" t="inlineStr"/>
       <c r="D201" t="n">
-        <v>51990</v>
+        <v>39660</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, 13th Gen</t>
+          <t>hp_15_(2026),_amd_athlon</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U(8GB DDR4,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
+          <t>HP 15 (2026), AMD Athlon Dual Core 7120U - (8 GB DDR5/512 GB SSD/AMD Radeon 610M Graphics/Windows 11 Pro) Thin and Light Business Laptop/15.6" HD Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
         </is>
       </c>
       <c r="C202" t="inlineStr"/>
       <c r="D202" t="n">
-        <v>51990</v>
+        <v>41999</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, 13th Gen</t>
+          <t>hp_15_(2026),_amd_athlon</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U(8GB DDR4,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
+          <t>HP 15 (2026), AMD Athlon Dual Core 7120U - (8 GB DDR5/512 GB SSD/AMD Radeon 610M Graphics/Windows 11 Pro) Thin and Light Business Laptop/15.6" HD Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
         </is>
       </c>
       <c r="C203" t="inlineStr"/>
       <c r="D203" t="n">
-        <v>51990</v>
+        <v>42840</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>hp_15_smartchoice,_13th_gen</t>
+          <t>hp_15_(2026),_amd_athlon</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U(8GB DDR4,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
+          <t>HP 15 (2026), AMD Athlon Dual Core 7120U - (8 GB DDR5/512 GB SSD/AMD Radeon 610M Graphics/Windows 11 Pro) Thin and Light Business Laptop/15.6" HD Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
         </is>
       </c>
       <c r="C204" t="inlineStr"/>
       <c r="D204" t="n">
-        <v>49990</v>
+        <v>42840</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>hp_15_smartchoice,_13th_gen</t>
+          <t>hp_15_(2026),_amd_athlon</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U(8GB DDR4,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
+          <t>HP 15 (2026), AMD Athlon Dual Core 7120U - (8 GB DDR5/512 GB SSD/AMD Radeon 610M Graphics/Windows 11 Pro) Thin and Light Business Laptop/15.6" HD Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
         </is>
       </c>
       <c r="C205" t="inlineStr"/>
       <c r="D205" t="n">
-        <v>49990</v>
+        <v>42840</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>hp_15_smartchoice,_13th_gen</t>
+          <t>HP 15 (2026), AMD Ryzen</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U(8GB DDR4,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
+          <t>HP 15 (2026), AMD Ryzen 3 Quad Core 7335U - (8 GB DDR5/512 GB SSD/AMD Radeon 660M Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
         </is>
       </c>
       <c r="C206" t="inlineStr"/>
       <c r="D206" t="n">
-        <v>49990</v>
+        <v>42780</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>hp_15_smartchoice,_intel_core</t>
+          <t>hp_15_(i5_14th_gen),</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, Intel Core Ultra 5 125H, 12 Tops (16GB DDR5, 512GB SSD) FHD, IPS, 15.6''/39.6cm, Win11, M365(1yr)* Office24, Silver, 1.65kg, fd1254TU, FHD Camera w/Shutter, AI Powered Laptop</t>
+          <t>HP 15 (i5 14th Gen), Intel Core 5, 16GB RAM (Upgradeable), 512GB SSD, FHD, Anti-Glare, 15.6''/39.6cm, Win11, M365 Basic(1yr), Office24, Silver,1.59kg, fd0682tu, FHD Camera w/Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C207" t="inlineStr"/>
       <c r="D207" t="n">
-        <v>69990</v>
+        <v>63990</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
@@ -4772,17 +4772,17 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>hp_15_smartchoice,_intel_core</t>
+          <t>hp_15_(i5_14th_gen),</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, Intel Core Ultra 5 125H, 12 Tops (16GB DDR5, 512GB SSD) FHD, IPS, 15.6''/39.6cm, Win11, M365(1yr)* Office24, Silver, 1.65kg, fd1254TU, FHD Camera w/Shutter, AI Powered Laptop</t>
+          <t>HP 15 (i5 14th Gen), Intel Core 5, 16GB RAM (Upgradeable), 512GB SSD, FHD, Anti-Glare, 15.6''/39.6cm, Win11, M365 Basic(1yr), Office24, Silver,1.59kg, fd0682tu, FHD Camera w/Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C208" t="inlineStr"/>
       <c r="D208" t="n">
-        <v>69990</v>
+        <v>67990</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
@@ -4793,336 +4793,336 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel</t>
+          <t>hp_15_laptop_|_amd</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U (8GB DDR4, 512GB SSD), FHD, Micro -Edge, Anti-Glare, 15.6''/39.6cm, Win11, M365* Office24, Silver, 1.59kg, fd0624tu, FHD Camera, UHD Graphics Laptop</t>
+          <t>HP 15 Laptop | AMD Ryzen 7 5825U |16GB DDR4 RAM | 512GB SSD |15.6" (39.6 cm) FHD Display |AMD Radeon Graphics| Backlit KB | FHD Camera| Win 11| MS Office 2024 + M365*(1-Yr) | Silver |1.59kg |fc0533AU</t>
         </is>
       </c>
       <c r="C209" t="inlineStr"/>
       <c r="D209" t="n">
-        <v>47490</v>
+        <v>64990</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>hp_15,_13th_gen_intel</t>
+          <t>hp_15_laptop_|_intel</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U (8GB DDR4, 512GB SSD), FHD, Micro -Edge, Anti-Glare, 15.6''/39.6cm, Win11, M365* Office24, Silver, 1.59kg, fd0624tu, FHD Camera, UHD Graphics Laptop</t>
+          <t>HP 15 Laptop | Intel Core i5-13420H,13th Gen |16GB RAM | 512GB SSD | Win 11 |M365 Basic(1yr)* Office24|Anti-Glare, Micro-Edge, 15.6''/39.6cm|Backlit KB|FHD Camera w/Shutter|1.65kg, Silver -FR0045TU</t>
         </is>
       </c>
       <c r="C210" t="inlineStr"/>
       <c r="D210" t="n">
-        <v>48990</v>
+        <v>68990</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>hp_15,_13th_gen_intel</t>
+          <t>hp_15_laptop,_(14th_gen</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U (8GB DDR4, 512GB SSD), FHD, Micro -Edge, Anti-Glare, 15.6''/39.6cm, Win11, M365* Office24, Silver, 1.59kg, fd0624tu, FHD Camera, UHD Graphics Laptop</t>
+          <t>HP 15 Laptop, (14th Gen Core i5) Intel Core 5-120U (24GB RAM, 512GB SSD, Win 11, M365 Basic(1yr)* Office24,15.6''/39.6cm FHD Anti-Glare Display, Backlit KB, FHD Camera, Dual Speakers, Silver, 1.59kg)</t>
         </is>
       </c>
       <c r="C211" t="inlineStr"/>
       <c r="D211" t="n">
-        <v>48990</v>
+        <v>72800</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel</t>
+          <t>HP 15 Laptop, Intel (14th</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
+          <t>HP 15 Laptop, Intel (14th Gen) Core 5 120U (24GB DDR5, 512GB SSD), Micro-Edge, Anti-Glare, 15.6''/39.6cm, Win11, M365* Office24, Silver, 1.59kg, fd0262TU, FHD Camera, Backlit, Dual Speakers</t>
         </is>
       </c>
       <c r="C212" t="inlineStr"/>
       <c r="D212" t="n">
-        <v>47990</v>
+        <v>67990</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel</t>
+          <t>HP 15 Smartchoice, 13th Gen</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
+          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U (12GB DDR4, 512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver, 1.59kg, fd0573TU, FHD Camera w/Shutter Laptop</t>
         </is>
       </c>
       <c r="C213" t="inlineStr"/>
       <c r="D213" t="n">
-        <v>47990</v>
+        <v>55990</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-06-12</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel</t>
+          <t>HP 15 Smartchoice, 13th Gen</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
+          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U(8GB DDR4,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C214" t="inlineStr"/>
       <c r="D214" t="n">
-        <v>46990</v>
+        <v>51990</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel</t>
+          <t>HP 15 Smartchoice, 13th Gen</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
+          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U(8GB DDR4,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C215" t="inlineStr"/>
       <c r="D215" t="n">
-        <v>46990</v>
+        <v>51990</v>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel</t>
+          <t>HP 15 Smartchoice, 13th Gen</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
+          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U(8GB DDR4,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C216" t="inlineStr"/>
       <c r="D216" t="n">
-        <v>46990</v>
+        <v>51990</v>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel</t>
+          <t>HP 15 Smartchoice, 13th Gen</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
+          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U(8GB DDR4,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C217" t="inlineStr"/>
       <c r="D217" t="n">
-        <v>46990</v>
+        <v>51990</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel</t>
+          <t>HP 15 Smartchoice, 13th Gen</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
+          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U(8GB DDR4,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C218" t="inlineStr"/>
       <c r="D218" t="n">
-        <v>46990</v>
+        <v>51990</v>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel</t>
+          <t>hp_15_smartchoice,_13th_gen</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
+          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U(8GB DDR4,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C219" t="inlineStr"/>
       <c r="D219" t="n">
-        <v>46990</v>
+        <v>49990</v>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel</t>
+          <t>hp_15_smartchoice,_13th_gen</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
+          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U(8GB DDR4,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C220" t="inlineStr"/>
       <c r="D220" t="n">
-        <v>48900</v>
+        <v>49990</v>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel</t>
+          <t>hp_15_smartchoice,_13th_gen</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
+          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U(8GB DDR4,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C221" t="inlineStr"/>
       <c r="D221" t="n">
-        <v>48900</v>
+        <v>49990</v>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel</t>
+          <t>hp_15_smartchoice,_13th_gen</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
+          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U(8GB DDR4,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C222" t="inlineStr"/>
       <c r="D222" t="n">
-        <v>50000</v>
+        <v>49990</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel</t>
+          <t>hp_15_smartchoice,_intel_core</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
+          <t>HP 15 Smartchoice, Intel Core Ultra 5 125H, 12 Tops (16GB DDR5, 512GB SSD) FHD, IPS, 15.6''/39.6cm, Win11, M365(1yr)* Office24, Silver, 1.65kg, fd1254TU, FHD Camera w/Shutter, AI Powered Laptop</t>
         </is>
       </c>
       <c r="C223" t="inlineStr"/>
       <c r="D223" t="n">
-        <v>49850</v>
+        <v>69990</v>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel</t>
+          <t>hp_15_smartchoice,_intel_core</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
+          <t>HP 15 Smartchoice, Intel Core Ultra 5 125H, 12 Tops (16GB DDR5, 512GB SSD) FHD, IPS, 15.6''/39.6cm, Win11, M365(1yr)* Office24, Silver, 1.65kg, fd1254TU, FHD Camera w/Shutter, AI Powered Laptop</t>
         </is>
       </c>
       <c r="C224" t="inlineStr"/>
       <c r="D224" t="n">
-        <v>49990</v>
+        <v>69990</v>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -5134,79 +5134,79 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U (8GB DDR4, 512GB SSD), FHD, Micro -Edge, Anti-Glare, 15.6''/39.6cm, Win11, M365* Office24, Silver, 1.59kg, fd0624tu, FHD Camera, UHD Graphics Laptop</t>
         </is>
       </c>
       <c r="C225" t="inlineStr"/>
       <c r="D225" t="n">
-        <v>49820</v>
+        <v>47490</v>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-04-16</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel</t>
+          <t>hp_15,_13th_gen_intel</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U (8GB DDR4, 512GB SSD), FHD, Micro -Edge, Anti-Glare, 15.6''/39.6cm, Win11, M365* Office24, Silver, 1.59kg, fd0624tu, FHD Camera, UHD Graphics Laptop</t>
         </is>
       </c>
       <c r="C226" t="inlineStr"/>
       <c r="D226" t="n">
-        <v>49820</v>
+        <v>48990</v>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel</t>
+          <t>hp_15,_13th_gen_intel</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U (8GB DDR4, 512GB SSD), FHD, Micro -Edge, Anti-Glare, 15.6''/39.6cm, Win11, M365* Office24, Silver, 1.59kg, fd0624tu, FHD Camera, UHD Graphics Laptop</t>
         </is>
       </c>
       <c r="C227" t="inlineStr"/>
       <c r="D227" t="n">
-        <v>50400</v>
+        <v>48990</v>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel</t>
+          <t>hp_15,_13th_gen_intel</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U (8GB DDR4, 512GB SSD), FHD, Micro -Edge, Anti-Glare, 15.6''/39.6cm, Win11, M365* Office24, Silver, 1.59kg, fd0624tu, FHD Camera, UHD Graphics Laptop</t>
         </is>
       </c>
       <c r="C228" t="inlineStr"/>
       <c r="D228" t="n">
-        <v>50390</v>
+        <v>48990</v>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -5223,11 +5223,11 @@
       </c>
       <c r="C229" t="inlineStr"/>
       <c r="D229" t="n">
-        <v>50150</v>
+        <v>47990</v>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -5244,11 +5244,11 @@
       </c>
       <c r="C230" t="inlineStr"/>
       <c r="D230" t="n">
-        <v>50040</v>
+        <v>47990</v>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -5265,11 +5265,11 @@
       </c>
       <c r="C231" t="inlineStr"/>
       <c r="D231" t="n">
-        <v>50040</v>
+        <v>46990</v>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-05-08</t>
         </is>
       </c>
     </row>
@@ -5286,11 +5286,11 @@
       </c>
       <c r="C232" t="inlineStr"/>
       <c r="D232" t="n">
-        <v>49670</v>
+        <v>46990</v>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
@@ -5307,11 +5307,11 @@
       </c>
       <c r="C233" t="inlineStr"/>
       <c r="D233" t="n">
-        <v>49480</v>
+        <v>46990</v>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-10</t>
         </is>
       </c>
     </row>
@@ -5328,11 +5328,11 @@
       </c>
       <c r="C234" t="inlineStr"/>
       <c r="D234" t="n">
-        <v>49470</v>
+        <v>46990</v>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-14</t>
         </is>
       </c>
     </row>
@@ -5349,11 +5349,11 @@
       </c>
       <c r="C235" t="inlineStr"/>
       <c r="D235" t="n">
-        <v>49300</v>
+        <v>46990</v>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-05-15</t>
         </is>
       </c>
     </row>
@@ -5365,1566 +5365,1566 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U, (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge, FHD,15.6''/39.6cm, Win11,M365 Basic(1yr),Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
         </is>
       </c>
       <c r="C236" t="inlineStr"/>
       <c r="D236" t="n">
-        <v>47990</v>
+        <v>46990</v>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-17</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>HP 15, AMD Ryzen 5</t>
+          <t>HP 15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>HP 15, AMD Ryzen 5 7520U,(16GB LPDDR5, 512GB SSD), Anti-Glare, Micro-Edge, FHD, 15.6''/39.6cm, Win 11, Office 24,M365 Basic(1yr)*,Silver, 1.59kg, fc0690au, FHD Camera, Backlit KB Laptop</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
         </is>
       </c>
       <c r="C237" t="inlineStr"/>
       <c r="D237" t="n">
-        <v>53990</v>
+        <v>48900</v>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-19</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>HP 15, AMD Ryzen 5</t>
+          <t>HP 15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>HP 15, AMD Ryzen 5 7520U,(16GB LPDDR5, 512GB SSD), Anti-Glare, Micro-Edge, FHD, 15.6''/39.6cm, Win 11, Office 24,M365 Basic(1yr)*,Silver, 1.59kg, fc0690au, FHD Camera, Backlit KB Laptop</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
         </is>
       </c>
       <c r="C238" t="inlineStr"/>
       <c r="D238" t="n">
-        <v>53990</v>
+        <v>48900</v>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-20</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>HP 15, AMD Ryzen 5</t>
+          <t>HP 15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>HP 15, AMD Ryzen 5 7520U,(16GB LPDDR5, 512GB SSD), Anti-Glare, Micro-Edge, FHD, 15.6''/39.6cm, Win 11, Office 24,M365 Basic(1yr)*,Silver, 1.59kg, fc0690au, FHD Camera, Backlit KB Laptop</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
         </is>
       </c>
       <c r="C239" t="inlineStr"/>
       <c r="D239" t="n">
-        <v>54990</v>
+        <v>50000</v>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-21</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>hp_15,_amd_ryzen_5</t>
+          <t>HP 15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>HP 15, AMD Ryzen 5 7520U,(16GB LPDDR5, 512GB SSD), Anti-Glare, Micro-Edge, FHD, 15.6''/39.6cm, Win 11, Office 24,M365 Basic(1yr)*,Silver, 1.59kg, fc0690au, FHD Camera, Backlit KB Laptop</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
         </is>
       </c>
       <c r="C240" t="inlineStr"/>
       <c r="D240" t="n">
-        <v>56830</v>
+        <v>49850</v>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>HP 15, AMD Ryzen 7</t>
+          <t>HP 15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>HP 15, AMD Ryzen 7 7735HS (16GB DDR5,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365 Basic(1yr)* Office24, Silver, 1.59kg, fc1038AU, AMD Radeon FHD Camera w/Shutter, Backlit Laptop</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
         </is>
       </c>
       <c r="C241" t="inlineStr"/>
       <c r="D241" t="n">
-        <v>59990</v>
+        <v>49990</v>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>HP 15, Intel Core 5</t>
+          <t>HP 15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>HP 15, Intel Core 5 120U (14th Gen) 16GB DDR4, 512GB SSD, FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365 Basic(1yr), Office24, Silver,1.59kg, FD0640TU/682tu, FHD Camera w/Shutter, BL Laptop</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
         </is>
       </c>
       <c r="C242" t="inlineStr"/>
       <c r="D242" t="n">
-        <v>65990</v>
+        <v>49820</v>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-24</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>hp_15,_intel_core_5-120u</t>
+          <t>HP 15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>HP 15, Intel Core 5-120U (8GB DDR4, 512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365 Basic(1yr), Office Home24, Silver,1.59kg, fd0651TU, FHD Camera w/Privacy Shutter, Backlit Laptop</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
         </is>
       </c>
       <c r="C243" t="inlineStr"/>
       <c r="D243" t="n">
-        <v>57500</v>
+        <v>49820</v>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>HP 15, Intel Core Ultra</t>
+          <t>HP 15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>HP 15, Intel Core Ultra 5 125H (24GB DDR5, 1TB SSD), Micro-Edge, Anti-Glare, FHD, 15''/39.6cm, Win11, M365* Office24, Silver, 1.65kg, FD1458TU, FHD Camera, Backlit Laptop</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
         </is>
       </c>
       <c r="C244" t="inlineStr"/>
       <c r="D244" t="n">
-        <v>84990</v>
+        <v>50400</v>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>hp_15,_intel_core_i3-1315u-13th</t>
+          <t>HP 15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>HP 15, Intel Core i3-1315U-13th Gen Laptop (8GB DDR4 Ram,512GB SSD) Anti-Glare, Micro-Edge,15.6'" FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera Shutter, 15-fd0569TU</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
         </is>
       </c>
       <c r="C245" t="inlineStr"/>
       <c r="D245" t="n">
-        <v>49490</v>
+        <v>50390</v>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-27</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>hp_15,_intel_core_i3-1315u-13th</t>
+          <t>HP 15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>HP 15, Intel Core i3-1315U-13th Gen Laptop (8GB DDR4 Ram,512GB SSD) Anti-Glare, Micro-Edge,15.6'" FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera Shutter, 15-fd0569TU</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
         </is>
       </c>
       <c r="C246" t="inlineStr"/>
       <c r="D246" t="n">
-        <v>50900</v>
+        <v>50150</v>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-05-28</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>HP 255R G10 Notebook (AMD</t>
+          <t>HP 15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>HP 255R G10 Notebook (AMD Athlon Silver 7120U /8GB/512GB/DOS) 15.6-inch(39.6cm), Anti-Glare, HD Laptop, Radeon Graphics, Silver,1.52kg</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
         </is>
       </c>
       <c r="C247" t="inlineStr"/>
       <c r="D247" t="n">
-        <v>41700</v>
+        <v>50040</v>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>HP 255R G10 Notebook (AMD</t>
+          <t>HP 15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>HP 255R G10 Notebook (AMD Athlon Silver 7120U /8GB/512GB/DOS) 15.6-inch(39.6cm), Anti-Glare, HD Laptop, Radeon Graphics, Silver,1.52kg</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
         </is>
       </c>
       <c r="C248" t="inlineStr"/>
       <c r="D248" t="n">
-        <v>39340</v>
+        <v>50040</v>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>HP 255R G10 Notebook (AMD</t>
+          <t>HP 15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>HP 255R G10 Notebook (AMD Athlon Silver 7120U /8GB/512GB/DOS) 15.6-inch(39.6cm), Anti-Glare, HD Laptop, Radeon Graphics, Silver,1.52kg</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
         </is>
       </c>
       <c r="C249" t="inlineStr"/>
       <c r="D249" t="n">
-        <v>40409</v>
+        <v>49670</v>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>HP 255R G10 Notebook (AMD</t>
+          <t>HP 15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>HP 255R G10 Notebook (AMD Athlon Silver 7120U /8GB/512GB/DOS) 15.6-inch(39.6cm), Anti-Glare, HD Laptop, Radeon Graphics, Silver,1.52kg</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
         </is>
       </c>
       <c r="C250" t="inlineStr"/>
       <c r="D250" t="n">
-        <v>39618</v>
+        <v>49480</v>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>HP 255R G10 Notebook (AMD</t>
+          <t>HP 15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>HP 255R G10 Notebook (AMD Athlon Silver 7120U /8GB/512GB/DOS) 15.6-inch(39.6cm), Anti-Glare, HD Laptop, Radeon Graphics, Silver,1.52kg</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
         </is>
       </c>
       <c r="C251" t="inlineStr"/>
       <c r="D251" t="n">
-        <v>39525</v>
+        <v>49470</v>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-12</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>HP Omen, Intel Core Ultra</t>
+          <t>HP 15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>HP Omen, Intel Core Ultra 7 255H, 8GB RTX 5050, 24GB DDR5(Upgradeable) 1TB SSD, 2K, 165Hz, 3ms Response time, IPS, 16''/40.6cm, Win11, M365*Office24, Shadow Black, 2.43kg, am0240tx, RGB Gaming Laptop</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
         </is>
       </c>
       <c r="C252" t="inlineStr"/>
       <c r="D252" t="n">
-        <v>129990</v>
+        <v>49300</v>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>HP OmniBook 3, AMD Ryzen</t>
+          <t>HP 15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>HP OmniBook 3, AMD Ryzen AI 5 330 (24GB DDR5 RAM, 1TB SSD) FHD, Anti-Glare, 15.6''/39.6cm, Win11, Office24, Glacier Silver,1.7kg, fn0074AU, FHD Camera w/Shutter, FPR, Backlit KB, Next Gen AI Laptop</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U, (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge, FHD,15.6''/39.6cm, Win11,M365 Basic(1yr),Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C253" t="inlineStr"/>
       <c r="D253" t="n">
-        <v>69990</v>
+        <v>47990</v>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>HP OmniBook 5 OLED (Previously</t>
+          <t>HP 15, AMD Ryzen 5</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>HP OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x, 1TB SSD) 2K, 14''/35.6cm, Win11, M365 Basic(1yr)* Office24, Silver, 1.35kg, he0015QU, Light-Weight, Next-Gen AI Laptop</t>
+          <t>HP 15, AMD Ryzen 5 7520U,(16GB LPDDR5, 512GB SSD), Anti-Glare, Micro-Edge, FHD, 15.6''/39.6cm, Win 11, Office 24,M365 Basic(1yr)*,Silver, 1.59kg, fc0690au, FHD Camera, Backlit KB Laptop</t>
         </is>
       </c>
       <c r="C254" t="inlineStr"/>
       <c r="D254" t="n">
-        <v>69990</v>
+        <v>53990</v>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-08</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>HP OmniBook 5 OLED (Previously</t>
+          <t>HP 15, AMD Ryzen 5</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>HP OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x, 512GB SSD) 2K, 14''/35.6cm, Win11, M365 Basic(1yr)* Office24, Silver, 1.35kg, he0014QU, Light-Weight, Next-Gen AI Laptop</t>
+          <t>HP 15, AMD Ryzen 5 7520U,(16GB LPDDR5, 512GB SSD), Anti-Glare, Micro-Edge, FHD, 15.6''/39.6cm, Win 11, Office 24,M365 Basic(1yr)*,Silver, 1.59kg, fc0690au, FHD Camera, Backlit KB Laptop</t>
         </is>
       </c>
       <c r="C255" t="inlineStr"/>
       <c r="D255" t="n">
-        <v>78990</v>
+        <v>53990</v>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>HP OmniBook 5 OLED (Previously</t>
+          <t>HP 15, AMD Ryzen 5</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>HP OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x, 512GB SSD) 2K, 14''/35.6cm, Win11, M365 Basic(1yr)* Office24, Silver, 1.35kg, he0014QU, Light-Weight, Next-Gen AI Laptop</t>
+          <t>HP 15, AMD Ryzen 5 7520U,(16GB LPDDR5, 512GB SSD), Anti-Glare, Micro-Edge, FHD, 15.6''/39.6cm, Win 11, Office 24,M365 Basic(1yr)*,Silver, 1.59kg, fc0690au, FHD Camera, Backlit KB Laptop</t>
         </is>
       </c>
       <c r="C256" t="inlineStr"/>
       <c r="D256" t="n">
-        <v>66990</v>
+        <v>54990</v>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-24</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>hp_omnibook_5_oled_(previously</t>
+          <t>hp_15,_amd_ryzen_5</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>HP OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor 45 Tops (16GB LPDDR5x, 512GB SSD), 2K 14''/35.6cm, Win11, Office24, Silver, 1.29kg, he0014QU, Multi-Day Battery, AI Laptop</t>
+          <t>HP 15, AMD Ryzen 5 7520U,(16GB LPDDR5, 512GB SSD), Anti-Glare, Micro-Edge, FHD, 15.6''/39.6cm, Win 11, Office 24,M365 Basic(1yr)*,Silver, 1.59kg, fc0690au, FHD Camera, Backlit KB Laptop</t>
         </is>
       </c>
       <c r="C257" t="inlineStr"/>
       <c r="D257" t="n">
-        <v>79990</v>
+        <v>56830</v>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>hp_omnibook_x_flip_oled</t>
+          <t>HP 15, AMD Ryzen 7</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>HP OmniBook X Flip OLED Intel Core Ultra 5 226V, 40 Tops (16GB LPDDR5x,1TB SSD) 3K, Touch, 120hz, 14''/35.6cm, Intel ARC Graphic,Win11, Office24, Meteor Silver, 1.38kg, fm0099TU,Pen, 2 in 1 AI Laptop</t>
+          <t>HP 15, AMD Ryzen 7 7735HS (16GB DDR5,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365 Basic(1yr)* Office24, Silver, 1.59kg, fc1038AU, AMD Radeon FHD Camera w/Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C258" t="inlineStr"/>
       <c r="D258" t="n">
-        <v>115990</v>
+        <v>59990</v>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-14</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>hp_omnibook_3,_snapdragon_x</t>
+          <t>HP 15, Intel Core 5</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>HP Omnibook 3, Snapdragon X Processor 45 TOPS (16GB LPDDR5x,512GB SSD) 2K WUXGA, Anti-Glare, 14''/35.6cm, Win 11, M365*Office 24,Silver,1.42kg, hz0026QU, Lighter mini Charger, FHD IR Camera, AI Laptop</t>
+          <t>HP 15, Intel Core 5 120U (14th Gen) 16GB DDR4, 512GB SSD, FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365 Basic(1yr), Office24, Silver,1.59kg, FD0640TU/682tu, FHD Camera w/Shutter, BL Laptop</t>
         </is>
       </c>
       <c r="C259" t="inlineStr"/>
       <c r="D259" t="n">
-        <v>79990</v>
+        <v>65990</v>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>HP Omnibook 3, Snapdragon X</t>
+          <t>hp_15,_intel_core_5-120u</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>HP Omnibook 3, Snapdragon X Processor, 45 TOPS (16GB LPDDR5x, 512GB SSD) 2K, WUXGA, IPS, 14''/35.6cm, Win 11, Office 24, Silver, 1.4kg, hz0026QU, FHD IR Camera, 42% Lighter mini GaN Charger, AI Laptop</t>
+          <t>HP 15, Intel Core 5-120U (8GB DDR4, 512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365 Basic(1yr), Office Home24, Silver,1.59kg, fd0651TU, FHD Camera w/Privacy Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C260" t="inlineStr"/>
       <c r="D260" t="n">
-        <v>69990</v>
+        <v>57500</v>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>HP Omnibook 3, Snapdragon X</t>
+          <t>HP 15, Intel Core Ultra</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>HP Omnibook 3, Snapdragon X Processor, 45 TOPS (16GB LPDDR5x, 512GB SSD) 2K, WUXGA, IPS, 14''/35.6cm, Win 11, Office 24, Silver, 1.4kg, hz0026QU, FHD IR Camera, 42% Lighter mini GaN Charger, AI Laptop</t>
+          <t>HP 15, Intel Core Ultra 5 125H (24GB DDR5, 1TB SSD), Micro-Edge, Anti-Glare, FHD, 15''/39.6cm, Win11, M365* Office24, Silver, 1.65kg, FD1458TU, FHD Camera, Backlit Laptop</t>
         </is>
       </c>
       <c r="C261" t="inlineStr"/>
       <c r="D261" t="n">
-        <v>73990</v>
+        <v>84990</v>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>HP Omnibook 5 OLED (Previously</t>
+          <t>hp_15,_intel_core_i3-1315u-13th</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>HP Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x,1TB SSD) 2K OLED,16''/40.6cm, Win11, M365*Office24, Glacier Silver, 1.59kg, fb0001QU, Backlit, Next-Gen AI Laptop</t>
+          <t>HP 15, Intel Core i3-1315U-13th Gen Laptop (8GB DDR4 Ram,512GB SSD) Anti-Glare, Micro-Edge,15.6'" FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera Shutter, 15-fd0569TU</t>
         </is>
       </c>
       <c r="C262" t="inlineStr"/>
       <c r="D262" t="n">
-        <v>78850</v>
+        <v>49490</v>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>hp_omnibook_5_oled_(previously</t>
+          <t>hp_15,_intel_core_i3-1315u-13th</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>HP Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor 45 Tops (16GB LPDDR5x, 1TB SSD) 2K,16''/40.6cm, Win11, Office24, Silver, 1.59kg, fb0001QU, Multi-Day Battery AI Laptop</t>
+          <t>HP 15, Intel Core i3-1315U-13th Gen Laptop (8GB DDR4 Ram,512GB SSD) Anti-Glare, Micro-Edge,15.6'" FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera Shutter, 15-fd0569TU</t>
         </is>
       </c>
       <c r="C263" t="inlineStr"/>
       <c r="D263" t="n">
-        <v>77900</v>
+        <v>50900</v>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>hp_pavilion_plus,_intel_core</t>
+          <t>HP 255R G10 Notebook (AMD</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>HP Pavilion Plus, Intel Core i5-1335U-13th Gen Laptop, (16GB LPDDR5x,512GB SSD),IPS, 300 nits, 14''(35.6cm) 2K,Win 11, M365 Basic(1yr), Office Home 24, Silver,1.38kg, 5MP Camera w/Shutter, ew0107TU</t>
+          <t>HP 255R G10 Notebook (AMD Athlon Silver 7120U /8GB/512GB/DOS) 15.6-inch(39.6cm), Anti-Glare, HD Laptop, Radeon Graphics, Silver,1.52kg</t>
         </is>
       </c>
       <c r="C264" t="inlineStr"/>
       <c r="D264" t="n">
-        <v>63990</v>
+        <v>41700</v>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-04-16</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>hp_professional_15_(2026),_intel</t>
+          <t>HP 255R G10 Notebook (AMD</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>HP Professional 15 (2026), Intel (i3 14th Gen) Core 3 100U - (8 GB/512 GB SSD/Intel UHD Graphics/Windows 11 Home) Thin &amp; Light Business Laptop/15.6" Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
+          <t>HP 255R G10 Notebook (AMD Athlon Silver 7120U /8GB/512GB/DOS) 15.6-inch(39.6cm), Anti-Glare, HD Laptop, Radeon Graphics, Silver,1.52kg</t>
         </is>
       </c>
       <c r="C265" t="inlineStr"/>
       <c r="D265" t="n">
-        <v>48990</v>
+        <v>39340</v>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-10</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>hp_professional_15_(2026),_intel</t>
+          <t>HP 255R G10 Notebook (AMD</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>HP Professional 15 (2026), Intel (i3 14th Gen) Core 3 100U - (8 GB/512 GB SSD/Intel UHD Graphics/Windows 11 Home) Thin &amp; Light Business Laptop/15.6" Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
+          <t>HP 255R G10 Notebook (AMD Athlon Silver 7120U /8GB/512GB/DOS) 15.6-inch(39.6cm), Anti-Glare, HD Laptop, Radeon Graphics, Silver,1.52kg</t>
         </is>
       </c>
       <c r="C266" t="inlineStr"/>
       <c r="D266" t="n">
-        <v>51899</v>
+        <v>40409</v>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-05-20</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>hp_professional_15_(2026),_intel</t>
+          <t>HP 255R G10 Notebook (AMD</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>HP Professional 15 (2026), Intel (i3 14th Gen) Core 3 100U - (8 GB/512 GB SSD/Intel UHD Graphics/Windows 11 Home) Thin &amp; Light Business Laptop/15.6" Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
+          <t>HP 255R G10 Notebook (AMD Athlon Silver 7120U /8GB/512GB/DOS) 15.6-inch(39.6cm), Anti-Glare, HD Laptop, Radeon Graphics, Silver,1.52kg</t>
         </is>
       </c>
       <c r="C267" t="inlineStr"/>
       <c r="D267" t="n">
-        <v>51840</v>
+        <v>39618</v>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>HP Smartchoice OmniBook 5 OLED</t>
+          <t>HP 255R G10 Notebook (AMD</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>HP Smartchoice OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x, 1TB SSD) 2K, 14''/35.6cm, Win11, M365(1yr)*Office24, Silver,1.35kg, he0015QU,Light-Weight,Next-Gen AI Laptop</t>
+          <t>HP 255R G10 Notebook (AMD Athlon Silver 7120U /8GB/512GB/DOS) 15.6-inch(39.6cm), Anti-Glare, HD Laptop, Radeon Graphics, Silver,1.52kg</t>
         </is>
       </c>
       <c r="C268" t="inlineStr"/>
       <c r="D268" t="n">
-        <v>82990</v>
+        <v>39525</v>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>HP Smartchoice OmniBook 5 OLED</t>
+          <t>HP Omen, Intel Core Ultra</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>HP Smartchoice OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x, 1TB SSD) 2K, 14''/35.6cm, Win11, M365(1yr)*Office24, Silver,1.35kg, he0015QU,Light-Weight,Next-Gen AI Laptop</t>
+          <t>HP Omen, Intel Core Ultra 7 255H, 8GB RTX 5050, 24GB DDR5(Upgradeable) 1TB SSD, 2K, 165Hz, 3ms Response time, IPS, 16''/40.6cm, Win11, M365*Office24, Shadow Black, 2.43kg, am0240tx, RGB Gaming Laptop</t>
         </is>
       </c>
       <c r="C269" t="inlineStr"/>
       <c r="D269" t="n">
-        <v>76990</v>
+        <v>129990</v>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-05-10</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>HP Smartchoice OmniBook 5 OLED</t>
+          <t>HP OmniBook 3, AMD Ryzen</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>HP Smartchoice OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x, 512GB SSD) 2K, 14''/35.6cm, Win11, M365(1yr)* Office24, Silver, 1.35kg, he0014QU, Next-Gen AI Laptop</t>
+          <t>HP OmniBook 3, AMD Ryzen AI 5 330 (24GB DDR5 RAM, 1TB SSD) FHD, Anti-Glare, 15.6''/39.6cm, Win11, Office24, Glacier Silver,1.7kg, fn0074AU, FHD Camera w/Shutter, FPR, Backlit KB, Next Gen AI Laptop</t>
         </is>
       </c>
       <c r="C270" t="inlineStr"/>
       <c r="D270" t="n">
-        <v>78990</v>
+        <v>69990</v>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>HP Smartchoice OmniBook 5 OLED</t>
+          <t>HP OmniBook 5 OLED (Previously</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>HP Smartchoice OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x, 512GB SSD) 2K, 14''/35.6cm, Win11, M365(1yr)* Office24, Silver, 1.35kg, he0014QU, Next-Gen AI Laptop</t>
+          <t>HP OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x, 1TB SSD) 2K, 14''/35.6cm, Win11, M365 Basic(1yr)* Office24, Silver, 1.35kg, he0015QU, Light-Weight, Next-Gen AI Laptop</t>
         </is>
       </c>
       <c r="C271" t="inlineStr"/>
       <c r="D271" t="n">
-        <v>79990</v>
+        <v>69990</v>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-14</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>HP Smartchoice Omnibook 5 OLED</t>
+          <t>HP OmniBook 5 OLED (Previously</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>HP Smartchoice Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x,1TB SSD) 2K OLED,16''/40.6cm, Win11, M365(1yr)*Office24, Glacier Silver, 1.59kg, fb0001QU,Next-Gen AI Laptop</t>
+          <t>HP OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x, 512GB SSD) 2K, 14''/35.6cm, Win11, M365 Basic(1yr)* Office24, Silver, 1.35kg, he0014QU, Light-Weight, Next-Gen AI Laptop</t>
         </is>
       </c>
       <c r="C272" t="inlineStr"/>
       <c r="D272" t="n">
-        <v>68739</v>
+        <v>78990</v>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>HP Smartchoice Omnibook 5 OLED</t>
+          <t>HP OmniBook 5 OLED (Previously</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>HP Smartchoice Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x,1TB SSD) 2K OLED,16''/40.6cm, Win11, M365(1yr)*Office24, Glacier Silver, 1.59kg, fb0001QU,Next-Gen AI Laptop</t>
+          <t>HP OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x, 512GB SSD) 2K, 14''/35.6cm, Win11, M365 Basic(1yr)* Office24, Silver, 1.35kg, he0014QU, Light-Weight, Next-Gen AI Laptop</t>
         </is>
       </c>
       <c r="C273" t="inlineStr"/>
       <c r="D273" t="n">
-        <v>68739</v>
+        <v>66990</v>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>HP Smartchoice Omnibook 5 OLED</t>
+          <t>hp_omnibook_5_oled_(previously</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>HP Smartchoice Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x,1TB SSD) 2K OLED,16''/40.6cm, Win11, M365(1yr)*Office24, Glacier Silver, 1.59kg, fb0001QU,Next-Gen AI Laptop</t>
+          <t>HP OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor 45 Tops (16GB LPDDR5x, 512GB SSD), 2K 14''/35.6cm, Win11, Office24, Silver, 1.29kg, he0014QU, Multi-Day Battery, AI Laptop</t>
         </is>
       </c>
       <c r="C274" t="inlineStr"/>
       <c r="D274" t="n">
-        <v>68739</v>
+        <v>79990</v>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>HP Smartchoice Omnibook 5 OLED</t>
+          <t>hp_omnibook_x_flip_oled</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>HP Smartchoice Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x,1TB SSD) 2K OLED,16''/40.6cm, Win11, M365(1yr)*Office24, Glacier Silver, 1.59kg, fb0001QU,Next-Gen AI Laptop</t>
+          <t>HP OmniBook X Flip OLED Intel Core Ultra 5 226V, 40 Tops (16GB LPDDR5x,1TB SSD) 3K, Touch, 120hz, 14''/35.6cm, Intel ARC Graphic,Win11, Office24, Meteor Silver, 1.38kg, fm0099TU,Pen, 2 in 1 AI Laptop</t>
         </is>
       </c>
       <c r="C275" t="inlineStr"/>
       <c r="D275" t="n">
-        <v>68323</v>
+        <v>115990</v>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>HP Smartchoice Omnibook 5 OLED</t>
+          <t>hp_omnibook_3,_snapdragon_x</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>HP Smartchoice Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x,1TB SSD) 2K OLED,16''/40.6cm, Win11, M365(1yr)*Office24, Glacier Silver, 1.59kg, fb0001QU,Next-Gen AI Laptop</t>
+          <t>HP Omnibook 3, Snapdragon X Processor 45 TOPS (16GB LPDDR5x,512GB SSD) 2K WUXGA, Anti-Glare, 14''/35.6cm, Win 11, M365*Office 24,Silver,1.42kg, hz0026QU, Lighter mini Charger, FHD IR Camera, AI Laptop</t>
         </is>
       </c>
       <c r="C276" t="inlineStr"/>
       <c r="D276" t="n">
-        <v>67940</v>
+        <v>79990</v>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>HP Smartchoice Omnibook 5 OLED</t>
+          <t>HP Omnibook 3, Snapdragon X</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>HP Smartchoice Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x,1TB SSD) 2K OLED,16''/40.6cm, Win11, M365(1yr)*Office24, Glacier Silver, 1.59kg, fb0001QU,Next-Gen AI Laptop</t>
+          <t>HP Omnibook 3, Snapdragon X Processor, 45 TOPS (16GB LPDDR5x, 512GB SSD) 2K, WUXGA, IPS, 14''/35.6cm, Win 11, Office 24, Silver, 1.4kg, hz0026QU, FHD IR Camera, 42% Lighter mini GaN Charger, AI Laptop</t>
         </is>
       </c>
       <c r="C277" t="inlineStr"/>
       <c r="D277" t="n">
-        <v>67940</v>
+        <v>69990</v>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-27</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>HP Smartchoice Victus, 13th Gen</t>
+          <t>HP Omnibook 3, Snapdragon X</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>HP Smartchoice Victus, 13th Gen Intel Core i7-13620H, 8GB RTX 5050, 24GB DDR5(Upgradeable) 1TB SSD, 144Hz, FHD, 15.6''/39.6cm, Win11, M365* Office24, Mica Silver, 2.29kg, fa2309TX, RGB Gaming Laptop</t>
+          <t>HP Omnibook 3, Snapdragon X Processor, 45 TOPS (16GB LPDDR5x, 512GB SSD) 2K, WUXGA, IPS, 14''/35.6cm, Win 11, Office 24, Silver, 1.4kg, hz0026QU, FHD IR Camera, 42% Lighter mini GaN Charger, AI Laptop</t>
         </is>
       </c>
       <c r="C278" t="inlineStr"/>
       <c r="D278" t="n">
-        <v>112990</v>
+        <v>73990</v>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>HP Smartchoice Victus, AMD Ryzen</t>
+          <t>HP Omnibook 5 OLED (Previously</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>HP Smartchoice Victus, AMD Ryzen 7 7445HS, 6GB RTX 3050, 16GB DDR5(Upgradeable) 512GB SSD, FHD, 144Hz, 300 nits, 15.6''/39.6cm, Win 11, M365* Office24, Blue, 2.29kg, fb3134AX/3120ax, Gaming Laptop</t>
+          <t>HP Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x,1TB SSD) 2K OLED,16''/40.6cm, Win11, M365*Office24, Glacier Silver, 1.59kg, fb0001QU, Backlit, Next-Gen AI Laptop</t>
         </is>
       </c>
       <c r="C279" t="inlineStr"/>
       <c r="D279" t="n">
-        <v>78990</v>
+        <v>78850</v>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>HP Smartchoice Victus, AMD Ryzen</t>
+          <t>hp_omnibook_5_oled_(previously</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>HP Smartchoice Victus, AMD Ryzen 7 7445HS, 6GB RTX 3050, 16GB DDR5(Upgradeable) 512GB SSD, FHD, 144Hz, 300 nits, 15.6''/39.6cm, Win 11, M365* Office24, Blue, 2.29kg, fb3134AX/3120ax, Gaming Laptop</t>
+          <t>HP Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor 45 Tops (16GB LPDDR5x, 1TB SSD) 2K,16''/40.6cm, Win11, Office24, Silver, 1.59kg, fb0001QU, Multi-Day Battery AI Laptop</t>
         </is>
       </c>
       <c r="C280" t="inlineStr"/>
       <c r="D280" t="n">
-        <v>86990</v>
+        <v>77900</v>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>HP Smartchoice Victus, AMD Ryzen</t>
+          <t>hp_pavilion_plus,_intel_core</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>HP Smartchoice Victus, AMD Ryzen 7 7445HS, 6GB RTX 3050, 16GB DDR5(Upgradeable) 512GB SSD, FHD, 144Hz, 300 nits, 15.6''/39.6cm, Win 11, M365* Office24, Blue, 2.29kg, fb3134AX/3120ax, Gaming Laptop</t>
+          <t>HP Pavilion Plus, Intel Core i5-1335U-13th Gen Laptop, (16GB LPDDR5x,512GB SSD),IPS, 300 nits, 14''(35.6cm) 2K,Win 11, M365 Basic(1yr), Office Home 24, Silver,1.38kg, 5MP Camera w/Shutter, ew0107TU</t>
         </is>
       </c>
       <c r="C281" t="inlineStr"/>
       <c r="D281" t="n">
-        <v>86990</v>
+        <v>63990</v>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>HP Victus, 14th Gen Intel</t>
+          <t>hp_professional_15_(2026),_intel</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>HP Victus, 14th Gen Intel Core i5-14450HX, 6GB RTX 3050, 24GB DDR5, 512GB SSD, FHD, 144Hz, 300 nits, IPS,15.6''/39.6cm, Win11, M365* Office24, Mica Silver, 2.3kg, fa2303tx/fa2315tx, RGB Gaming Laptop</t>
+          <t>HP Professional 15 (2026), Intel (i3 14th Gen) Core 3 100U - (8 GB/512 GB SSD/Intel UHD Graphics/Windows 11 Home) Thin &amp; Light Business Laptop/15.6" Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
         </is>
       </c>
       <c r="C282" t="inlineStr"/>
       <c r="D282" t="n">
-        <v>103990</v>
+        <v>48990</v>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>HP Victus, AMD Ryzen 7</t>
+          <t>hp_professional_15_(2026),_intel</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>HP Victus, AMD Ryzen 7 7445HS, 4GB RTX 2050, 16GB DDR5(Upgradeable) 512GB SSD, FHD, 144Hz, 300 nits, IPS, 15.6'', Win11, M365* Office24, Blue, 2.29kg, fb3189ax /3122/ 23ax Backlit, Gaming Laptop</t>
+          <t>HP Professional 15 (2026), Intel (i3 14th Gen) Core 3 100U - (8 GB/512 GB SSD/Intel UHD Graphics/Windows 11 Home) Thin &amp; Light Business Laptop/15.6" Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
         </is>
       </c>
       <c r="C283" t="inlineStr"/>
       <c r="D283" t="n">
-        <v>65990</v>
+        <v>51899</v>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>HP Victus, AMD Ryzen 7</t>
+          <t>hp_professional_15_(2026),_intel</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>HP Victus, AMD Ryzen 7 7445HS, 4GB RTX 2050, 16GB DDR5(Upgradeable) 512GB SSD, FHD, 144Hz, 300 nits, IPS, 15.6'', Win11, M365* Office24, Blue, 2.29kg, fb3189ax /3122/ 23ax Backlit, Gaming Laptop</t>
+          <t>HP Professional 15 (2026), Intel (i3 14th Gen) Core 3 100U - (8 GB/512 GB SSD/Intel UHD Graphics/Windows 11 Home) Thin &amp; Light Business Laptop/15.6" Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
         </is>
       </c>
       <c r="C284" t="inlineStr"/>
       <c r="D284" t="n">
-        <v>65990</v>
+        <v>51840</v>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>HP Victus, AMD Ryzen 7</t>
+          <t>hp_professional_15_(2026),_intel</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>HP Victus, AMD Ryzen 7 7445HS, 6GB RTX 4050, 16GB DDR5(Upgradeable) 512GB SSD, 144Hz, IPS, 300nits, FHD, 15.6''/39.6cm, Win11, M365* Office24, Blue, 2.29kg, fb3130AX, Backlit, DTS Audio, Gaming Laptop</t>
+          <t>HP Professional 15 (2026), Intel (i3 14th Gen) Core 3 100U - (8 GB/512 GB SSD/Intel UHD Graphics/Windows 11 Home) Thin &amp; Light Business Laptop/15.6" Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
         </is>
       </c>
       <c r="C285" t="inlineStr"/>
       <c r="D285" t="n">
-        <v>90990</v>
+        <v>51840</v>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>HP Victus, AMD Ryzen 7</t>
+          <t>HP Smartchoice OmniBook 5 OLED</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>HP Victus, AMD Ryzen 7 7445HS, 6GB RTX 4050, 16GB DDR5(Upgradeable) 512GB SSD, 144Hz, IPS, 300nits, FHD, 15.6''/39.6cm, Win11, M365* Office24, Blue, 2.29kg, fb3130AX, Backlit, DTS Audio, Gaming Laptop</t>
+          <t>HP Smartchoice OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x, 1TB SSD) 2K, 14''/35.6cm, Win11, M365(1yr)*Office24, Silver,1.35kg, he0015QU,Light-Weight,Next-Gen AI Laptop</t>
         </is>
       </c>
       <c r="C286" t="inlineStr"/>
       <c r="D286" t="n">
-        <v>91990</v>
+        <v>82990</v>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Lenovo Chromebook Intel Celeron N4500</t>
+          <t>HP Smartchoice OmniBook 5 OLED</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Lenovo Chromebook Intel Celeron N4500 (4GB RAM/64GB eMMC 5.1/11.6 Inch (29.46cm)/HD Display/2Wx2 Stereo Speakers/HD Camera/Chrome OS/Blue/1.21Kg), 82UY0014HA</t>
+          <t>HP Smartchoice OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x, 1TB SSD) 2K, 14''/35.6cm, Win11, M365(1yr)*Office24, Silver,1.35kg, he0015QU,Light-Weight,Next-Gen AI Laptop</t>
         </is>
       </c>
       <c r="C287" t="inlineStr"/>
       <c r="D287" t="n">
-        <v>21990</v>
+        <v>76990</v>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Lenovo Chromebook Intel Celeron N4500</t>
+          <t>HP Smartchoice OmniBook 5 OLED</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Lenovo Chromebook Intel Celeron N4500 (4GB RAM/64GB eMMC 5.1/11.6 Inch (29.46cm)/HD Display/2Wx2 Stereo Speakers/HD Camera/Chrome OS/Blue/1.21Kg), 82UY0014HA</t>
+          <t>HP Smartchoice OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x, 512GB SSD) 2K, 14''/35.6cm, Win11, M365(1yr)* Office24, Silver, 1.35kg, he0014QU, Next-Gen AI Laptop</t>
         </is>
       </c>
       <c r="C288" t="inlineStr"/>
       <c r="D288" t="n">
-        <v>18990</v>
+        <v>78990</v>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-24</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Lenovo IdeaPad Slim 3 13th</t>
+          <t>HP Smartchoice OmniBook 5 OLED</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Lenovo IdeaPad Slim 3 13th Gen Intel Core i5-13420H 15.3 inch (38.8cm) WUXGA IPS Laptop (16GB RAM/1TB SSD/Windows 11/MSO 365 Basic+Office 2024/Top Metal Cover/Backlit KB/Grey/1.6Kg), 83K100S0IN</t>
+          <t>HP Smartchoice OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x, 512GB SSD) 2K, 14''/35.6cm, Win11, M365(1yr)* Office24, Silver, 1.35kg, he0014QU, Next-Gen AI Laptop</t>
         </is>
       </c>
       <c r="C289" t="inlineStr"/>
       <c r="D289" t="n">
-        <v>70990</v>
+        <v>79990</v>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>lenovo_ideapad_slim_3_13th</t>
+          <t>HP Smartchoice Omnibook 5 OLED</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Lenovo IdeaPad Slim 3 13th Gen Intel Core i7 13620H, 16GB RAM, 512GB SSD, WUXGA IPS, 15.3"/38.8cm, Win 11, Office 2024, Top Metal Cover Grey, 1.6Kg, 83K100CJIN/S1IN, Backlit KB, Laptop</t>
+          <t>HP Smartchoice Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x,1TB SSD) 2K OLED,16''/40.6cm, Win11, M365(1yr)*Office24, Glacier Silver, 1.59kg, fb0001QU,Next-Gen AI Laptop</t>
         </is>
       </c>
       <c r="C290" t="inlineStr"/>
       <c r="D290" t="n">
-        <v>81990</v>
+        <v>68739</v>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>lenovo_ideapad_slim_3_13th</t>
+          <t>HP Smartchoice Omnibook 5 OLED</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Lenovo IdeaPad Slim 3 13th Gen Intel Core i7 13620H, 16GB RAM, 512GB SSD, WUXGA IPS, 15.3"/38.8cm, Win 11, Office 2024, Top Metal Cover Grey, 1.6Kg, 83K100CJIN/S1IN, Backlit KB, Laptop</t>
+          <t>HP Smartchoice Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x,1TB SSD) 2K OLED,16''/40.6cm, Win11, M365(1yr)*Office24, Glacier Silver, 1.59kg, fb0001QU,Next-Gen AI Laptop</t>
         </is>
       </c>
       <c r="C291" t="inlineStr"/>
       <c r="D291" t="n">
-        <v>79990</v>
+        <v>68739</v>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>lenovo_ideapad_slim_3,_13th</t>
+          <t>HP Smartchoice Omnibook 5 OLED</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Lenovo IdeaPad Slim 3, 13th Gen Intel Core i5 13420H, 24GB RAM, 1TB SSD, WUXGA IPS, 15.3"/38.8cm, Windows 11, Office Home 2024, Grey, 1.6Kg, Backlit Keyboard, 1Yr ADP Free, 83K100PLIN, Laptop</t>
+          <t>HP Smartchoice Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x,1TB SSD) 2K OLED,16''/40.6cm, Win11, M365(1yr)*Office24, Glacier Silver, 1.59kg, fb0001QU,Next-Gen AI Laptop</t>
         </is>
       </c>
       <c r="C292" t="inlineStr"/>
       <c r="D292" t="n">
-        <v>79990</v>
+        <v>68739</v>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-27</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>lenovo_ideapad_slim_3,_amd</t>
+          <t>HP Smartchoice Omnibook 5 OLED</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Lenovo IdeaPad Slim 3, AMD Ryzen 7 8840HS, 24GB RAM, 1TB SSD, WUXGA IPS, AI PC, 15.3"/38.8cm, Backlit Keyboard, Windows 11, Office Home 2024, Grey, 1.6Kg, 1Yr ADP Free, 83KA004TIN, AI Powered Laptop</t>
+          <t>HP Smartchoice Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x,1TB SSD) 2K OLED,16''/40.6cm, Win11, M365(1yr)*Office24, Glacier Silver, 1.59kg, fb0001QU,Next-Gen AI Laptop</t>
         </is>
       </c>
       <c r="C293" t="inlineStr"/>
       <c r="D293" t="n">
-        <v>87990</v>
+        <v>68323</v>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-31</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>lenovo_ideapad_slim_3,_amd</t>
+          <t>HP Smartchoice Omnibook 5 OLED</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Lenovo IdeaPad Slim 3, AMD Ryzen 7 8840HS, 24GB RAM, 1TB SSD, WUXGA IPS, AI PC, 15.3"/38.8cm, Backlit Keyboard, Windows 11, Office Home 2024, Grey, 1.6Kg, 1Yr ADP Free, 83KA004TIN, AI Powered Laptop</t>
+          <t>HP Smartchoice Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x,1TB SSD) 2K OLED,16''/40.6cm, Win11, M365(1yr)*Office24, Glacier Silver, 1.59kg, fb0001QU,Next-Gen AI Laptop</t>
         </is>
       </c>
       <c r="C294" t="inlineStr"/>
       <c r="D294" t="n">
-        <v>79990</v>
+        <v>67940</v>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>lenovo_ideapad_slim_3,_amd</t>
+          <t>HP Smartchoice Omnibook 5 OLED</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Lenovo IdeaPad Slim 3, AMD Ryzen 7 8840HS, 24GB RAM, 1TB SSD, WUXGA IPS, AI PC, 15.3"/38.8cm, Backlit Keyboard, Windows 11, Office Home 2024, Grey, 1.6Kg, 1Yr ADP Free, 83KA004TIN, AI Powered Laptop</t>
+          <t>HP Smartchoice Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x,1TB SSD) 2K OLED,16''/40.6cm, Win11, M365(1yr)*Office24, Glacier Silver, 1.59kg, fb0001QU,Next-Gen AI Laptop</t>
         </is>
       </c>
       <c r="C295" t="inlineStr"/>
       <c r="D295" t="n">
-        <v>79990</v>
+        <v>67940</v>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-06-02</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>lenovo_ideapad_slim_5,_amd</t>
+          <t>HP Smartchoice Victus, 13th Gen</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Lenovo IdeaPad Slim 5, AMD Ryzen 5 7535HS, 16GB RAM, 512GB SSD, WUXGA IPS, 13.3"/33.7cm, Windows 11, Microsoft 365 Basic + Office 2024, Grey, 1.6Kg, Backlit KB, 1Yr ADP Free, 83J2004HIN, Laptop</t>
+          <t>HP Smartchoice Victus, 13th Gen Intel Core i7-13620H, 8GB RTX 5050, 24GB DDR5(Upgradeable) 1TB SSD, 144Hz, FHD, 15.6''/39.6cm, Win11, M365* Office24, Mica Silver, 2.29kg, fa2309TX, RGB Gaming Laptop</t>
         </is>
       </c>
       <c r="C296" t="inlineStr"/>
       <c r="D296" t="n">
-        <v>72990</v>
+        <v>112990</v>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-10</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Lenovo Ideapad Slim 3 AMD</t>
+          <t>HP Smartchoice Victus, AMD Ryzen</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Lenovo Ideapad Slim 3 AMD Ryzen 5 7520U 15.6" (39.6cm) FHD Thin and Light Laptop (16GB/512GB SSD/Windows 11/Microsoft 365 Basic + Office Home 2024/Backlit Keyboard/Grey/1.6Kg), 82XQ00XDIN</t>
+          <t>HP Smartchoice Victus, AMD Ryzen 7 7445HS, 6GB RTX 3050, 16GB DDR5(Upgradeable) 512GB SSD, FHD, 144Hz, 300 nits, 15.6''/39.6cm, Win 11, M365* Office24, Blue, 2.29kg, fb3134AX/3120ax, Gaming Laptop</t>
         </is>
       </c>
       <c r="C297" t="inlineStr"/>
       <c r="D297" t="n">
-        <v>50750</v>
+        <v>78990</v>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Lenovo LOQ 2024, Intel Core</t>
+          <t>HP Smartchoice Victus, AMD Ryzen</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Lenovo LOQ 2024, Intel Core i5-13450HX, 13th Gen, NVIDIA RTX 4050-6GB, 16GB RAM, 512GB SSD, FHD 144Hz, 15.6"/39.6cm, Windows 11, Office Home 2024, Grey, 2.4Kg, 83DV018JIN, 1Yr ADP Free Gaming Laptop</t>
+          <t>HP Smartchoice Victus, AMD Ryzen 7 7445HS, 6GB RTX 3050, 16GB DDR5(Upgradeable) 512GB SSD, FHD, 144Hz, 300 nits, 15.6''/39.6cm, Win 11, M365* Office24, Blue, 2.29kg, fb3134AX/3120ax, Gaming Laptop</t>
         </is>
       </c>
       <c r="C298" t="inlineStr"/>
       <c r="D298" t="n">
-        <v>100544</v>
+        <v>86990</v>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Lenovo LOQ 2025 AMD Ryzen</t>
+          <t>HP Smartchoice Victus, AMD Ryzen</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Lenovo LOQ 2025 AMD Ryzen 7 250| NVIDIA RTX 5050 8GB (16GB RAM/1TB SSD/144Hz Refresh Rate/440 AI TOPS/15.6" (39.6cm)/Windows 11/Office 2024/3 Mon. Game Pass/Grey/2.4Kg), 83JG008KIN</t>
+          <t>HP Smartchoice Victus, AMD Ryzen 7 7445HS, 6GB RTX 3050, 16GB DDR5(Upgradeable) 512GB SSD, FHD, 144Hz, 300 nits, 15.6''/39.6cm, Win 11, M365* Office24, Blue, 2.29kg, fb3134AX/3120ax, Gaming Laptop</t>
         </is>
       </c>
       <c r="C299" t="inlineStr"/>
       <c r="D299" t="n">
-        <v>134990</v>
+        <v>86990</v>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Lenovo LOQ 2025 Intel Core</t>
+          <t>HP Victus, 14th Gen Intel</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Lenovo LOQ 2025 Intel Core i7-14700HX| NVIDIA RTX 5060 8GB (32GB RAM/1TB SSD/144Hz Refresh Rate/572 AI TOPS/15.6" (39.6cm)/Windows 11/Office 2024/3 Mon. Game Pass/Grey/2.4Kg), 83JE00T3IN</t>
+          <t>HP Victus, 14th Gen Intel Core i5-14450HX, 6GB RTX 3050, 24GB DDR5, 512GB SSD, FHD, 144Hz, 300 nits, IPS,15.6''/39.6cm, Win11, M365* Office24, Mica Silver, 2.3kg, fa2303tx/fa2315tx, RGB Gaming Laptop</t>
         </is>
       </c>
       <c r="C300" t="inlineStr"/>
       <c r="D300" t="n">
-        <v>157990</v>
+        <v>103990</v>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Lenovo LOQ AMD Ryzen 5</t>
+          <t>HP Victus, AMD Ryzen 7</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Lenovo LOQ AMD Ryzen 5 7235HS | NVIDIA RTX 4050 6GB (16GB RAM/512GB SSD/144Hz Refresh Rate/15.6" (39.6cm)/Windows 11/Office Home 2024/3 Mon. Game Pass/Grey/2.4Kg), 83JC00NYIN AI Gaming Laptop</t>
+          <t>HP Victus, AMD Ryzen 7 7445HS, 4GB RTX 2050, 16GB DDR5(Upgradeable) 512GB SSD, FHD, 144Hz, 300 nits, IPS, 15.6'', Win11, M365* Office24, Blue, 2.29kg, fb3189ax /3122/ 23ax Backlit, Gaming Laptop</t>
         </is>
       </c>
       <c r="C301" t="inlineStr"/>
       <c r="D301" t="n">
-        <v>88990</v>
+        <v>65990</v>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-21</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Lenovo LOQ, 13th Gen Intel</t>
+          <t>HP Victus, AMD Ryzen 7</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Lenovo LOQ, 13th Gen Intel Core i7 13700HX, RTX 5050-8GB, 16GB RAM, 1TB SSD, FHD, 15.6"/39.6cm, 144Hz, Windows 11, Office 2024, Grey, 2.4Kg, 440 AI Tops, 3 Mon. Game Pass, 83JE00U7IN, AI Gaming Laptop</t>
+          <t>HP Victus, AMD Ryzen 7 7445HS, 4GB RTX 2050, 16GB DDR5(Upgradeable) 512GB SSD, FHD, 144Hz, 300 nits, IPS, 15.6'', Win11, M365* Office24, Blue, 2.29kg, fb3189ax /3122/ 23ax Backlit, Gaming Laptop</t>
         </is>
       </c>
       <c r="C302" t="inlineStr"/>
       <c r="D302" t="n">
-        <v>121869</v>
+        <v>65990</v>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-22</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Lenovo Legion 7 2025 Intel</t>
+          <t>HP Victus, AMD Ryzen 7</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Lenovo Legion 7 2025 Intel Core Ultra 9 275HX| NVIDIA RTX 5070 8GB (32GB RAM/1TB SSD/WQXGA OLED/240Hz/16(40.64cm)/Windows 11/Office 2024+AI Now/White/2.0Kg), 83KY001GIN AI Powered Gaming Laptop</t>
+          <t>HP Victus, AMD Ryzen 7 7445HS, 6GB RTX 4050, 16GB DDR5(Upgradeable) 512GB SSD, 144Hz, IPS, 300nits, FHD, 15.6''/39.6cm, Win11, M365* Office24, Blue, 2.29kg, fb3130AX, Backlit, DTS Audio, Gaming Laptop</t>
         </is>
       </c>
       <c r="C303" t="inlineStr"/>
       <c r="D303" t="n">
-        <v>239391</v>
+        <v>90990</v>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Lenovo Legion Pro 5 2025</t>
+          <t>HP Victus, AMD Ryzen 7</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Lenovo Legion Pro 5 2025 AMD Ryzen 9 9955HX | NVIDIA RTX 5060 8GB (32GB RAM/1TB SSD/WQXGA OLED/165Hz/16 (40.6cm)/Windows 11/Office 2024+AI Now/Black/2.3Kg), 83F2004CIN AI Powered Gaming Laptop</t>
+          <t>HP Victus, AMD Ryzen 7 7445HS, 6GB RTX 4050, 16GB DDR5(Upgradeable) 512GB SSD, 144Hz, IPS, 300nits, FHD, 15.6''/39.6cm, Win11, M365* Office24, Blue, 2.29kg, fb3130AX, Backlit, DTS Audio, Gaming Laptop</t>
         </is>
       </c>
       <c r="C304" t="inlineStr"/>
       <c r="D304" t="n">
-        <v>245490</v>
+        <v>91990</v>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Lenovo Legion Pro 5 2025</t>
+          <t>Lenovo Chromebook Intel Celeron N4500</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Lenovo Legion Pro 5 2025 AMD Ryzen 9 9955HX | NVIDIA RTX 5060 8GB (32GB RAM/1TB SSD/WQXGA OLED/165Hz/16 (40.6cm)/Windows 11/Office 2024+AI Now/Black/2.3Kg), 83F2004CIN AI Powered Gaming Laptop</t>
+          <t>Lenovo Chromebook Intel Celeron N4500 (4GB RAM/64GB eMMC 5.1/11.6 Inch (29.46cm)/HD Display/2Wx2 Stereo Speakers/HD Camera/Chrome OS/Blue/1.21Kg), 82UY0014HA</t>
         </is>
       </c>
       <c r="C305" t="inlineStr"/>
       <c r="D305" t="n">
-        <v>245490</v>
+        <v>21990</v>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Lenovo Legion Pro 5 2025</t>
+          <t>Lenovo Chromebook Intel Celeron N4500</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Lenovo Legion Pro 5 2025 AMD Ryzen 9 9955HX | NVIDIA RTX 5060 8GB (32GB RAM/1TB SSD/WQXGA OLED/165Hz/16 (40.6cm)/Windows 11/Office 2024+AI Now/Black/2.3Kg), 83F2004CIN AI Powered Gaming Laptop</t>
+          <t>Lenovo Chromebook Intel Celeron N4500 (4GB RAM/64GB eMMC 5.1/11.6 Inch (29.46cm)/HD Display/2Wx2 Stereo Speakers/HD Camera/Chrome OS/Blue/1.21Kg), 82UY0014HA</t>
         </is>
       </c>
       <c r="C306" t="inlineStr"/>
       <c r="D306" t="n">
-        <v>245490</v>
+        <v>18990</v>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Lenovo Legion Pro 5 2025</t>
+          <t>Lenovo IdeaPad Slim 3 13th</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Lenovo Legion Pro 5 2025 AMD Ryzen 9 9955HX | NVIDIA RTX 5060 8GB (32GB RAM/1TB SSD/WQXGA OLED/165Hz/16 (40.6cm)/Windows 11/Office 2024+AI Now/Black/2.3Kg), 83F2004CIN AI Powered Gaming Laptop</t>
+          <t>Lenovo IdeaPad Slim 3 13th Gen Intel Core i5-13420H 15.3 inch (38.8cm) WUXGA IPS Laptop (16GB RAM/1TB SSD/Windows 11/MSO 365 Basic+Office 2024/Top Metal Cover/Backlit KB/Grey/1.6Kg), 83K100S0IN</t>
         </is>
       </c>
       <c r="C307" t="inlineStr"/>
       <c r="D307" t="n">
-        <v>245490</v>
+        <v>70990</v>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-08</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Lenovo Legion Pro 7 FIFA</t>
+          <t>lenovo_ideapad_slim_3_13th</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Lenovo Legion Pro 7 FIFA World Cup 26 Edition Intel Core Ultra 9 275HX | NVIDIA RTX 5070Ti 12GB (32GB RAM/1TB SSD/WQXGA OLED/240Hz/16(40.6cm)/Windows 11/Black/2.4Kg), 83F500HPIN AI Gaming Laptop</t>
+          <t>Lenovo IdeaPad Slim 3 13th Gen Intel Core i7 13620H, 16GB RAM, 512GB SSD, WUXGA IPS, 15.3"/38.8cm, Win 11, Office 2024, Top Metal Cover Grey, 1.6Kg, 83K100CJIN/S1IN, Backlit KB, Laptop</t>
         </is>
       </c>
       <c r="C308" t="inlineStr"/>
       <c r="D308" t="n">
-        <v>319990</v>
+        <v>81990</v>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Lenovo Smartchoice Ideapad 5 2-in-1</t>
+          <t>lenovo_ideapad_slim_3_13th</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Lenovo Smartchoice Ideapad 5 2-in-1 13th Gen Intel Core i5-13420H (16GB RAM/512GB SSD/Windows 11/Office Home 2024/WUXGA IPS/14 (35.5cm)/Touchscreen 2-in-1/3Mon.Game Pass/Grey/1.6kg), 83KX0059IN Laptop</t>
+          <t>Lenovo IdeaPad Slim 3 13th Gen Intel Core i7 13620H, 16GB RAM, 512GB SSD, WUXGA IPS, 15.3"/38.8cm, Win 11, Office 2024, Top Metal Cover Grey, 1.6Kg, 83K100CJIN/S1IN, Backlit KB, Laptop</t>
         </is>
       </c>
       <c r="C309" t="inlineStr"/>
       <c r="D309" t="n">
-        <v>74490</v>
+        <v>79990</v>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>lenovo_thinkbook_14,_amd_ryzen</t>
+          <t>lenovo_ideapad_slim_3,_13th</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Lenovo ThinkBook 14, AMD Ryzen 5 220, 16GB RAM, 1TB SSD, WUXGA IPS 14” (35.56cm), Windows 11 Home, Arctic Grey, 1.36Kg, 21V0A01SIG, Fingerprint, Backlit, 400 Nits, 1Y Warranty, Laptop</t>
+          <t>Lenovo IdeaPad Slim 3, 13th Gen Intel Core i5 13420H, 24GB RAM, 1TB SSD, WUXGA IPS, 15.3"/38.8cm, Windows 11, Office Home 2024, Grey, 1.6Kg, Backlit Keyboard, 1Yr ADP Free, 83K100PLIN, Laptop</t>
         </is>
       </c>
       <c r="C310" t="inlineStr"/>
       <c r="D310" t="n">
-        <v>90990</v>
+        <v>79990</v>
       </c>
       <c r="E310" t="inlineStr">
         <is>
@@ -6935,705 +6935,705 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>lenovo_thinkbook_14,_amd_ryzen</t>
+          <t>lenovo_ideapad_slim_3,_amd</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Lenovo ThinkBook 14, AMD Ryzen 5 220, 16GB RAM, 1TB SSD, WUXGA IPS 14” (35.56cm), Windows 11 Home, Arctic Grey, 1.36Kg, 21V0A01SIG, Fingerprint, Backlit, 400 Nits, 1Y Warranty, Laptop</t>
+          <t>Lenovo IdeaPad Slim 3, AMD Ryzen 7 8840HS, 24GB RAM, 1TB SSD, WUXGA IPS, AI PC, 15.3"/38.8cm, Backlit Keyboard, Windows 11, Office Home 2024, Grey, 1.6Kg, 1Yr ADP Free, 83KA004TIN, AI Powered Laptop</t>
         </is>
       </c>
       <c r="C311" t="inlineStr"/>
       <c r="D311" t="n">
-        <v>92990</v>
+        <v>87990</v>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>lenovo_thinkbook_14,_amd_ryzen</t>
+          <t>lenovo_ideapad_slim_3,_amd</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Lenovo ThinkBook 14, AMD Ryzen 5 220, 16GB RAM, 1TB SSD, WUXGA IPS 14” (35.56cm), Windows 11 Home, Arctic Grey, 1.36Kg, 21V0A01SIG, Fingerprint, Backlit, 400 Nits, 1Y Warranty, Laptop</t>
+          <t>Lenovo IdeaPad Slim 3, AMD Ryzen 7 8840HS, 24GB RAM, 1TB SSD, WUXGA IPS, AI PC, 15.3"/38.8cm, Backlit Keyboard, Windows 11, Office Home 2024, Grey, 1.6Kg, 1Yr ADP Free, 83KA004TIN, AI Powered Laptop</t>
         </is>
       </c>
       <c r="C312" t="inlineStr"/>
       <c r="D312" t="n">
-        <v>92990</v>
+        <v>79990</v>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Lenovo ThinkBook 15 G5 AMD</t>
+          <t>lenovo_ideapad_slim_3,_amd</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Lenovo ThinkBook 15 G5 AMD Ryzen 7 7730U 15.6" FHD Antiglare 250 Nits Thin and Light Laptop (8GB RAM/512GB SSD/Windows 11 Home/Fingerprint Reader/Backlit/Mineral Grey/1 Year Onsite/1.7 kg), 21JFA00BIN</t>
+          <t>Lenovo IdeaPad Slim 3, AMD Ryzen 7 8840HS, 24GB RAM, 1TB SSD, WUXGA IPS, AI PC, 15.3"/38.8cm, Backlit Keyboard, Windows 11, Office Home 2024, Grey, 1.6Kg, 1Yr ADP Free, 83KA004TIN, AI Powered Laptop</t>
         </is>
       </c>
       <c r="C313" t="inlineStr"/>
       <c r="D313" t="n">
-        <v>59999</v>
+        <v>79990</v>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>lenovo_thinkbook_16_amd_ryzen</t>
+          <t>lenovo_ideapad_slim_3,_amd</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Lenovo ThinkBook 16 AMD Ryzen 5 7535HS (8GB RAM/512GB SSD/Win 11 Home/Office 2024/Backlit Keyboard/Fingerprint) 16" WUXGA IPS 300 Nits Thin &amp; Light Laptop/1Y Warranty/Aluminium Top/1.7kg, 21MWA0BRIN</t>
+          <t>Lenovo IdeaPad Slim 3, AMD Ryzen 7 8840HS, 24GB RAM, 1TB SSD, WUXGA IPS, AI PC, 15.3"/38.8cm, Backlit Keyboard, Windows 11, Office Home 2024, Grey, 1.6Kg, 1Yr ADP Free, 83KA004TIN, AI Powered Laptop</t>
         </is>
       </c>
       <c r="C314" t="inlineStr"/>
       <c r="D314" t="n">
-        <v>65063</v>
+        <v>84990</v>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>lenovo_thinkbook_16_amd_ryzen</t>
+          <t>lenovo_ideapad_slim_5,_amd</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Lenovo ThinkBook 16 AMD Ryzen 5 7535HS (8GB RAM/512GB SSD/Win 11 Home/Office 2024/Backlit Keyboard/Fingerprint) 16" WUXGA IPS 300 Nits Thin &amp; Light Laptop/1Y Warranty/Aluminium Top/1.7kg, 21MWA0BRIN</t>
+          <t>Lenovo IdeaPad Slim 5, AMD Ryzen 5 7535HS, 16GB RAM, 512GB SSD, WUXGA IPS, 13.3"/33.7cm, Windows 11, Microsoft 365 Basic + Office 2024, Grey, 1.6Kg, Backlit KB, 1Yr ADP Free, 83J2004HIN, Laptop</t>
         </is>
       </c>
       <c r="C315" t="inlineStr"/>
       <c r="D315" t="n">
-        <v>65063</v>
+        <v>72990</v>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>lenovo_thinkbook_16,_amd_ryzen</t>
+          <t>Lenovo Ideapad Slim 3 AMD</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Lenovo ThinkBook 16, AMD Ryzen 5 7535HS, 16GB RAM, 512GB SSD, WUXGA IPS 16", Windows 11 Home, Office 2024, 1.7kg, 21MWA0BSIN, Backlit Keyboard, Fingerprint, 300 Nits, 1Y Warranty, Aluminium Top Laptop</t>
+          <t>Lenovo Ideapad Slim 3 AMD Ryzen 5 7520U 15.6" (39.6cm) FHD Thin and Light Laptop (16GB/512GB SSD/Windows 11/Microsoft 365 Basic + Office Home 2024/Backlit Keyboard/Grey/1.6Kg), 82XQ00XDIN</t>
         </is>
       </c>
       <c r="C316" t="inlineStr"/>
       <c r="D316" t="n">
-        <v>84500</v>
+        <v>50750</v>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-05-14</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Lenovo ThinkBook 16, Intel Core</t>
+          <t>Lenovo LOQ 2024, Intel Core</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Lenovo ThinkBook 16, Intel Core Ultra 9 185H, 16GB RAM, 512GB SSD, WUXGA IPS 16” (40.64cm), Win 11 Home, Arctic Grey, 1.7Kg, 21SKA0J5IG, Fingerprint, Backlit, 300 Nits, 1Y Warranty, AI Powered Laptop</t>
+          <t>Lenovo LOQ 2024, Intel Core i5-13450HX, 13th Gen, NVIDIA RTX 4050-6GB, 16GB RAM, 512GB SSD, FHD 144Hz, 15.6"/39.6cm, Windows 11, Office Home 2024, Grey, 2.4Kg, 83DV018JIN, 1Yr ADP Free Gaming Laptop</t>
         </is>
       </c>
       <c r="C317" t="inlineStr"/>
       <c r="D317" t="n">
-        <v>94990</v>
+        <v>100544</v>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Lenovo V14 Intel Core i3</t>
+          <t>Lenovo LOQ 2025 AMD Ryzen</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Lenovo V14 Intel Core i3 13th Gen 14" FHD (1920x1080) Antiglare 250 Nits Thin and Light Laptop (16GB RAM/512GB SSD/Windows 11 Home/Office Home 2024/Iron Grey/1.43 kg), 83A0A0PCIN</t>
+          <t>Lenovo LOQ 2025 AMD Ryzen 7 250| NVIDIA RTX 5050 8GB (16GB RAM/1TB SSD/144Hz Refresh Rate/440 AI TOPS/15.6" (39.6cm)/Windows 11/Office 2024/3 Mon. Game Pass/Grey/2.4Kg), 83JG008KIN</t>
         </is>
       </c>
       <c r="C318" t="inlineStr"/>
       <c r="D318" t="n">
-        <v>70990</v>
+        <v>134990</v>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Lenovo V14 Intel Core i3</t>
+          <t>Lenovo LOQ 2025 Intel Core</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Lenovo V14 Intel Core i3 13th Gen 14" FHD (1920x1080) Antiglare 250 Nits Thin and Light Laptop (16GB RAM/512GB SSD/Windows 11 Home/Office Home 2024/Iron Grey/1.43 kg), 83A0A0PCIN</t>
+          <t>Lenovo LOQ 2025 Intel Core i7-14700HX| NVIDIA RTX 5060 8GB (32GB RAM/1TB SSD/144Hz Refresh Rate/572 AI TOPS/15.6" (39.6cm)/Windows 11/Office 2024/3 Mon. Game Pass/Grey/2.4Kg), 83JE00T3IN</t>
         </is>
       </c>
       <c r="C319" t="inlineStr"/>
       <c r="D319" t="n">
-        <v>70990</v>
+        <v>157990</v>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>lenovo_v14_intel_core_i3</t>
+          <t>Lenovo LOQ AMD Ryzen 5</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Lenovo V14 Intel Core i3 13th Gen 14" FHD (1920x1080) Antiglare 250 Nits Thin and Light Laptop (16GB RAM/512GB SSD/Windows 11 Home/Office Home 2024/Iron Grey/1.43 kg), 83A0A0PCIN</t>
+          <t>Lenovo LOQ AMD Ryzen 5 7235HS | NVIDIA RTX 4050 6GB (16GB RAM/512GB SSD/144Hz Refresh Rate/15.6" (39.6cm)/Windows 11/Office Home 2024/3 Mon. Game Pass/Grey/2.4Kg), 83JC00NYIN AI Gaming Laptop</t>
         </is>
       </c>
       <c r="C320" t="inlineStr"/>
       <c r="D320" t="n">
-        <v>70990</v>
+        <v>88990</v>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-19</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 (2024), AMD</t>
+          <t>Lenovo LOQ, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 (2024), AMD Ryzen 3 7320U Quad Core - (8GB/512GB SSD/AMD Radeon Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" FHD Display/Arctic Grey/1.57 kg/MS Office 2021</t>
+          <t>Lenovo LOQ, 13th Gen Intel Core i7 13700HX, RTX 5050-8GB, 16GB RAM, 1TB SSD, FHD, 15.6"/39.6cm, 144Hz, Windows 11, Office 2024, Grey, 2.4Kg, 440 AI Tops, 3 Mon. Game Pass, 83JE00U7IN, AI Gaming Laptop</t>
         </is>
       </c>
       <c r="C321" t="inlineStr"/>
       <c r="D321" t="n">
-        <v>44200</v>
+        <v>121869</v>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 (2024), AMD</t>
+          <t>Lenovo Legion 7 2025 Intel</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 (2024), AMD Ryzen 3 7320U Quad Core - (8GB/512GB SSD/AMD Radeon Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" FHD Display/Arctic Grey/1.57 kg/MS Office 2021</t>
+          <t>Lenovo Legion 7 2025 Intel Core Ultra 9 275HX| NVIDIA RTX 5070 8GB (32GB RAM/1TB SSD/WQXGA OLED/240Hz/16(40.64cm)/Windows 11/Office 2024+AI Now/White/2.0Kg), 83KY001GIN AI Powered Gaming Laptop</t>
         </is>
       </c>
       <c r="C322" t="inlineStr"/>
       <c r="D322" t="n">
-        <v>44490</v>
+        <v>239391</v>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-08</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 (2024), AMD</t>
+          <t>Lenovo Legion Pro 5 2025</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 (2024), AMD Ryzen 3 7320U Quad Core - (8GB/512GB SSD/AMD Radeon Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" FHD Display/Arctic Grey/1.57 kg/MS Office 2021</t>
+          <t>Lenovo Legion Pro 5 2025 AMD Ryzen 9 9955HX | NVIDIA RTX 5060 8GB (32GB RAM/1TB SSD/WQXGA OLED/165Hz/16 (40.6cm)/Windows 11/Office 2024+AI Now/Black/2.3Kg), 83F2004CIN AI Powered Gaming Laptop</t>
         </is>
       </c>
       <c r="C323" t="inlineStr"/>
       <c r="D323" t="n">
-        <v>44490</v>
+        <v>245490</v>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-22</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 (2024), AMD</t>
+          <t>Lenovo Legion Pro 5 2025</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 (2024), AMD Ryzen 3 7320U Quad Core - (8GB/512GB SSD/AMD Radeon Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" FHD Display/Arctic Grey/1.57 kg/MS Office 2021</t>
+          <t>Lenovo Legion Pro 5 2025 AMD Ryzen 9 9955HX | NVIDIA RTX 5060 8GB (32GB RAM/1TB SSD/WQXGA OLED/165Hz/16 (40.6cm)/Windows 11/Office 2024+AI Now/Black/2.3Kg), 83F2004CIN AI Powered Gaming Laptop</t>
         </is>
       </c>
       <c r="C324" t="inlineStr"/>
       <c r="D324" t="n">
-        <v>44500</v>
+        <v>245490</v>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-24</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 (2024), AMD</t>
+          <t>Lenovo Legion Pro 5 2025</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 (2024), AMD Ryzen 3 7320U Quad Core - (8GB/512GB SSD/AMD Radeon Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" FHD Display/Arctic Grey/1.57 kg/MS Office 2021</t>
+          <t>Lenovo Legion Pro 5 2025 AMD Ryzen 9 9955HX | NVIDIA RTX 5060 8GB (32GB RAM/1TB SSD/WQXGA OLED/165Hz/16 (40.6cm)/Windows 11/Office 2024+AI Now/Black/2.3Kg), 83F2004CIN AI Powered Gaming Laptop</t>
         </is>
       </c>
       <c r="C325" t="inlineStr"/>
       <c r="D325" t="n">
-        <v>49999</v>
+        <v>245490</v>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 (2024), AMD</t>
+          <t>Lenovo Legion Pro 5 2025</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 (2024), AMD Ryzen 3 7320U Quad Core - (8GB/512GB SSD/AMD Radeon Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" FHD Display/Arctic Grey/1.57 kg/MS Office 2021</t>
+          <t>Lenovo Legion Pro 5 2025 AMD Ryzen 9 9955HX | NVIDIA RTX 5060 8GB (32GB RAM/1TB SSD/WQXGA OLED/165Hz/16 (40.6cm)/Windows 11/Office 2024+AI Now/Black/2.3Kg), 83F2004CIN AI Powered Gaming Laptop</t>
         </is>
       </c>
       <c r="C326" t="inlineStr"/>
       <c r="D326" t="n">
-        <v>49890</v>
+        <v>245490</v>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon</t>
+          <t>Lenovo Legion Pro 7 FIFA</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo Legion Pro 7 FIFA World Cup 26 Edition Intel Core Ultra 9 275HX | NVIDIA RTX 5070Ti 12GB (32GB RAM/1TB SSD/WQXGA OLED/240Hz/16(40.6cm)/Windows 11/Black/2.4Kg), 83F500HPIN AI Gaming Laptop</t>
         </is>
       </c>
       <c r="C327" t="inlineStr"/>
       <c r="D327" t="n">
-        <v>41999</v>
+        <v>319990</v>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-15</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon</t>
+          <t>Lenovo Smartchoice Ideapad 5 2-in-1</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo Smartchoice Ideapad 5 2-in-1 13th Gen Intel Core i5-13420H (16GB RAM/512GB SSD/Windows 11/Office Home 2024/WUXGA IPS/14 (35.5cm)/Touchscreen 2-in-1/3Mon.Game Pass/Grey/1.6kg), 83KX0059IN Laptop</t>
         </is>
       </c>
       <c r="C328" t="inlineStr"/>
       <c r="D328" t="n">
-        <v>41999</v>
+        <v>74490</v>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon</t>
+          <t>lenovo_thinkbook_14,_amd_ryzen</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo ThinkBook 14, AMD Ryzen 5 220, 16GB RAM, 1TB SSD, WUXGA IPS 14” (35.56cm), Windows 11 Home, Arctic Grey, 1.36Kg, 21V0A01SIG, Fingerprint, Backlit, 400 Nits, 1Y Warranty, Laptop</t>
         </is>
       </c>
       <c r="C329" t="inlineStr"/>
       <c r="D329" t="n">
-        <v>41999</v>
+        <v>90990</v>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon</t>
+          <t>lenovo_thinkbook_14,_amd_ryzen</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo ThinkBook 14, AMD Ryzen 5 220, 16GB RAM, 1TB SSD, WUXGA IPS 14” (35.56cm), Windows 11 Home, Arctic Grey, 1.36Kg, 21V0A01SIG, Fingerprint, Backlit, 400 Nits, 1Y Warranty, Laptop</t>
         </is>
       </c>
       <c r="C330" t="inlineStr"/>
       <c r="D330" t="n">
-        <v>42999</v>
+        <v>92990</v>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon</t>
+          <t>lenovo_thinkbook_14,_amd_ryzen</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo ThinkBook 14, AMD Ryzen 5 220, 16GB RAM, 1TB SSD, WUXGA IPS 14” (35.56cm), Windows 11 Home, Arctic Grey, 1.36Kg, 21V0A01SIG, Fingerprint, Backlit, 400 Nits, 1Y Warranty, Laptop</t>
         </is>
       </c>
       <c r="C331" t="inlineStr"/>
       <c r="D331" t="n">
-        <v>42999</v>
+        <v>92990</v>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon</t>
+          <t>Lenovo ThinkBook 15 G5 AMD</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo ThinkBook 15 G5 AMD Ryzen 7 7730U 15.6" FHD Antiglare 250 Nits Thin and Light Laptop (8GB RAM/512GB SSD/Windows 11 Home/Fingerprint Reader/Backlit/Mineral Grey/1 Year Onsite/1.7 kg), 21JFA00BIN</t>
         </is>
       </c>
       <c r="C332" t="inlineStr"/>
       <c r="D332" t="n">
-        <v>42999</v>
+        <v>59999</v>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-22</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon</t>
+          <t>lenovo_thinkbook_16_amd_ryzen</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo ThinkBook 16 AMD Ryzen 5 7535HS (8GB RAM/512GB SSD/Win 11 Home/Office 2024/Backlit Keyboard/Fingerprint) 16" WUXGA IPS 300 Nits Thin &amp; Light Laptop/1Y Warranty/Aluminium Top/1.7kg, 21MWA0BRIN</t>
         </is>
       </c>
       <c r="C333" t="inlineStr"/>
       <c r="D333" t="n">
-        <v>42999</v>
+        <v>65063</v>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon</t>
+          <t>lenovo_thinkbook_16_amd_ryzen</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo ThinkBook 16 AMD Ryzen 5 7535HS (8GB RAM/512GB SSD/Win 11 Home/Office 2024/Backlit Keyboard/Fingerprint) 16" WUXGA IPS 300 Nits Thin &amp; Light Laptop/1Y Warranty/Aluminium Top/1.7kg, 21MWA0BRIN</t>
         </is>
       </c>
       <c r="C334" t="inlineStr"/>
       <c r="D334" t="n">
-        <v>42999</v>
+        <v>65063</v>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon</t>
+          <t>lenovo_thinkbook_16,_amd_ryzen</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo ThinkBook 16, AMD Ryzen 5 7535HS, 16GB RAM, 512GB SSD, WUXGA IPS 16", Windows 11 Home, Office 2024, 1.7kg, 21MWA0BSIN, Backlit Keyboard, Fingerprint, 300 Nits, 1Y Warranty, Aluminium Top Laptop</t>
         </is>
       </c>
       <c r="C335" t="inlineStr"/>
       <c r="D335" t="n">
-        <v>44999</v>
+        <v>84500</v>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon</t>
+          <t>Lenovo ThinkBook 16, Intel Core</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo ThinkBook 16, Intel Core Ultra 9 185H, 16GB RAM, 512GB SSD, WUXGA IPS 16” (40.64cm), Win 11 Home, Arctic Grey, 1.7Kg, 21SKA0J5IG, Fingerprint, Backlit, 300 Nits, 1Y Warranty, AI Powered Laptop</t>
         </is>
       </c>
       <c r="C336" t="inlineStr"/>
       <c r="D336" t="n">
-        <v>43999</v>
+        <v>94990</v>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-20</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon</t>
+          <t>Lenovo V14 Intel Core i3</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo V14 Intel Core i3 13th Gen 14" FHD (1920x1080) Antiglare 250 Nits Thin and Light Laptop (16GB RAM/512GB SSD/Windows 11 Home/Office Home 2024/Iron Grey/1.43 kg), 83A0A0PCIN</t>
         </is>
       </c>
       <c r="C337" t="inlineStr"/>
       <c r="D337" t="n">
-        <v>43999</v>
+        <v>70990</v>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-05-20</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon</t>
+          <t>Lenovo V14 Intel Core i3</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo V14 Intel Core i3 13th Gen 14" FHD (1920x1080) Antiglare 250 Nits Thin and Light Laptop (16GB RAM/512GB SSD/Windows 11 Home/Office Home 2024/Iron Grey/1.43 kg), 83A0A0PCIN</t>
         </is>
       </c>
       <c r="C338" t="inlineStr"/>
       <c r="D338" t="n">
-        <v>43999</v>
+        <v>70990</v>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon</t>
+          <t>lenovo_v14_intel_core_i3</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo V14 Intel Core i3 13th Gen 14" FHD (1920x1080) Antiglare 250 Nits Thin and Light Laptop (16GB RAM/512GB SSD/Windows 11 Home/Office Home 2024/Iron Grey/1.43 kg), 83A0A0PCIN</t>
         </is>
       </c>
       <c r="C339" t="inlineStr"/>
       <c r="D339" t="n">
-        <v>44999</v>
+        <v>70990</v>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon</t>
+          <t>Lenovo V15 G4 (2024), AMD</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo V15 G4 (2024), AMD Ryzen 3 7320U Quad Core - (8GB/512GB SSD/AMD Radeon Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" FHD Display/Arctic Grey/1.57 kg/MS Office 2021</t>
         </is>
       </c>
       <c r="C340" t="inlineStr"/>
       <c r="D340" t="n">
-        <v>44999</v>
+        <v>44200</v>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-05-22</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>lenovo_v15_g4_amd_athlon</t>
+          <t>Lenovo V15 G4 (2024), AMD</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo V15 G4 (2024), AMD Ryzen 3 7320U Quad Core - (8GB/512GB SSD/AMD Radeon Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" FHD Display/Arctic Grey/1.57 kg/MS Office 2021</t>
         </is>
       </c>
       <c r="C341" t="inlineStr"/>
       <c r="D341" t="n">
-        <v>44999</v>
+        <v>44490</v>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-24</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>lenovo_v15_g4_amd_athlon</t>
+          <t>Lenovo V15 G4 (2024), AMD</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo V15 G4 (2024), AMD Ryzen 3 7320U Quad Core - (8GB/512GB SSD/AMD Radeon Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" FHD Display/Arctic Grey/1.57 kg/MS Office 2021</t>
         </is>
       </c>
       <c r="C342" t="inlineStr"/>
       <c r="D342" t="n">
-        <v>44999</v>
+        <v>44490</v>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>lenovo_v15_g4_amd_athlon</t>
+          <t>Lenovo V15 G4 (2024), AMD</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo V15 G4 (2024), AMD Ryzen 3 7320U Quad Core - (8GB/512GB SSD/AMD Radeon Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" FHD Display/Arctic Grey/1.57 kg/MS Office 2021</t>
         </is>
       </c>
       <c r="C343" t="inlineStr"/>
       <c r="D343" t="n">
-        <v>44999</v>
+        <v>44500</v>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen</t>
+          <t>Lenovo V15 G4 (2024), AMD</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
+          <t>Lenovo V15 G4 (2024), AMD Ryzen 3 7320U Quad Core - (8GB/512GB SSD/AMD Radeon Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" FHD Display/Arctic Grey/1.57 kg/MS Office 2021</t>
         </is>
       </c>
       <c r="C344" t="inlineStr"/>
@@ -7642,171 +7642,171 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen</t>
+          <t>Lenovo V15 G4 (2024), AMD</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
+          <t>Lenovo V15 G4 (2024), AMD Ryzen 3 7320U Quad Core - (8GB/512GB SSD/AMD Radeon Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" FHD Display/Arctic Grey/1.57 kg/MS Office 2021</t>
         </is>
       </c>
       <c r="C345" t="inlineStr"/>
       <c r="D345" t="n">
-        <v>52760</v>
+        <v>49890</v>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen</t>
+          <t>Lenovo V15 G4 AMD Athlon</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C346" t="inlineStr"/>
       <c r="D346" t="n">
-        <v>52300</v>
+        <v>41999</v>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen</t>
+          <t>Lenovo V15 G4 AMD Athlon</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C347" t="inlineStr"/>
       <c r="D347" t="n">
-        <v>52490</v>
+        <v>41999</v>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-28</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen</t>
+          <t>Lenovo V15 G4 AMD Athlon</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C348" t="inlineStr"/>
       <c r="D348" t="n">
-        <v>52300</v>
+        <v>41999</v>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-31</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen</t>
+          <t>Lenovo V15 G4 AMD Athlon</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C349" t="inlineStr"/>
       <c r="D349" t="n">
-        <v>52890</v>
+        <v>42999</v>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen</t>
+          <t>Lenovo V15 G4 AMD Athlon</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C350" t="inlineStr"/>
       <c r="D350" t="n">
-        <v>53999</v>
+        <v>42999</v>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen</t>
+          <t>Lenovo V15 G4 AMD Athlon</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C351" t="inlineStr"/>
       <c r="D351" t="n">
-        <v>53999</v>
+        <v>42999</v>
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen</t>
+          <t>Lenovo V15 G4 AMD Athlon</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C352" t="inlineStr"/>
       <c r="D352" t="n">
-        <v>54790</v>
+        <v>42999</v>
       </c>
       <c r="E352" t="inlineStr">
         <is>
@@ -7817,185 +7817,185 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>lenovo_v15_g4_amd_ryzen</t>
+          <t>Lenovo V15 G4 AMD Athlon</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C353" t="inlineStr"/>
       <c r="D353" t="n">
-        <v>54740</v>
+        <v>42999</v>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>lenovo_v15_g6_amd_ryzen</t>
+          <t>Lenovo V15 G4 AMD Athlon</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Lenovo V15 G6 AMD Ryzen 7 170 (Coequal 7735HS) 15.6" (39.62cm) FHD Thin and Light Business Laptop (16GB RAM DDR5/ 512GB SSD/Windows 11/ MS Office 2024/ AMD Radeon Graphics/Luna Grey/ 1.6 kg)</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C354" t="inlineStr"/>
       <c r="D354" t="n">
-        <v>64999</v>
+        <v>44999</v>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Lenovo Yoga Slim 7 (Smartchoice)</t>
+          <t>Lenovo V15 G4 AMD Athlon</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Lenovo Yoga Slim 7 (Smartchoice) Aura Edition, Intel Core Ultra 5 226V, 16GB RAM, 1TB SSD, WUXGA OLED, Copilot+ AI PC, 40 TOPS, 14"/35.5cm, Windows 11, Office 2024, Grey, 1.19Kg, 83JX005FIN, AI Laptop</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C355" t="inlineStr"/>
       <c r="D355" t="n">
-        <v>99990</v>
+        <v>43999</v>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Lenovo Yoga Slim 7 (Smartchoice)</t>
+          <t>Lenovo V15 G4 AMD Athlon</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Lenovo Yoga Slim 7 (Smartchoice) Aura Edition, Intel Core Ultra 5 226V, 16GB RAM, 1TB SSD, WUXGA OLED, Copilot+ AI PC, 40 TOPS, 14"/35.5cm, Windows 11, Office 2024, Grey, 1.19Kg, 83JX005FIN, AI Laptop</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C356" t="inlineStr"/>
       <c r="D356" t="n">
-        <v>105939</v>
+        <v>43999</v>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Lenovo Yoga Slim 7, Intel</t>
+          <t>Lenovo V15 G4 AMD Athlon</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Lenovo Yoga Slim 7, Intel Core Ultra 5 125H, 16GB RAM, 512GB SSD, AI PC, WUXGA-OLED, 14"/35.5cm, Windows 11, Microsoft 365 Basic + Office 2024, Grey, 1.39Kg, 83CV00DFIN, AI Powered Laptop</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C357" t="inlineStr"/>
       <c r="D357" t="n">
-        <v>77990</v>
+        <v>43999</v>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Lenovo Yoga Slim 7, Intel</t>
+          <t>Lenovo V15 G4 AMD Athlon</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Lenovo Yoga Slim 7, Intel Core Ultra 5 125H, 16GB RAM, 512GB SSD, AI PC, WUXGA-OLED, 14"/35.5cm, Windows 11, Microsoft 365 Basic + Office 2024, Grey, 1.39Kg, 83CV00DFIN, AI Powered Laptop</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C358" t="inlineStr"/>
       <c r="D358" t="n">
-        <v>84990</v>
+        <v>44999</v>
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-12</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Lenovo {SmartChoice Chromebook, Intel Celeron</t>
+          <t>Lenovo V15 G4 AMD Athlon</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Lenovo {SmartChoice Chromebook, Intel Celeron N4500, 4GB RAM, 64GB eMMC, HD, 11.6"/29.46cm, Chrome OS, Blue, 1.21Kg, 2Wx2 Stereo Speakers, HD Camera, 82UY0014HA, Laptop</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C359" t="inlineStr"/>
       <c r="D359" t="n">
-        <v>21990</v>
+        <v>44999</v>
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Lenovo {SmartChoice Chromebook, Intel Celeron</t>
+          <t>lenovo_v15_g4_amd_athlon</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Lenovo {SmartChoice Chromebook, Intel Celeron N4500, 4GB RAM, 64GB eMMC, HD, 11.6"/29.46cm, Chrome OS, Blue, 1.21Kg, 2Wx2 Stereo Speakers, HD Camera, 82UY0014HA, Laptop</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C360" t="inlineStr"/>
       <c r="D360" t="n">
-        <v>17990</v>
+        <v>44999</v>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>msi_cyborg_15,_intel_12th</t>
+          <t>lenovo_v15_g4_amd_athlon</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>MSI Cyborg 15, Intel 12th Gen. i5-12450H, 40CM FHD 144Hz Gaming Laptop (16GB/512GB NVMe SSD/Windows 11 Home/MSO 2021/NVIDIA GeForce RTX 3050, GDDR6 6GB/Translucent Black/1.9Kg) A12UDX-1468IN</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C361" t="inlineStr"/>
       <c r="D361" t="n">
-        <v>72990</v>
+        <v>44999</v>
       </c>
       <c r="E361" t="inlineStr">
         <is>
@@ -8006,332 +8006,332 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>primebook_2_max_(2026)_|</t>
+          <t>lenovo_v15_g4_amd_athlon</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Primebook 2 Max (2026) | 8GB RAM, 256GB UFS Storage | 15.6-Inch Full HD IPS Display | 12hrs Battery | MediaTek Helio G99 | Android 15 (PrimeOS 3.0) | Backlit Keyboard | in-Built AI (Gray)</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C362" t="inlineStr"/>
       <c r="D362" t="n">
-        <v>29990</v>
+        <v>44999</v>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Samsung Galaxy Book6 (Gray, 16GB</t>
+          <t>lenovo_v15_g4_amd_athlon</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Samsung Galaxy Book6 (Gray, 16GB RAM, 1TB SSD) | Intel Core Ultra 5 (Series 3) | 16" WUXGA+ Display with Touchscreen | 24Hrs Battery Life | 120 Hz Refresh Rate | Dolby Atmos Stereo Speakers | AI PC</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C363" t="inlineStr"/>
       <c r="D363" t="n">
-        <v>146990</v>
+        <v>44999</v>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Thomson NEO 14.1 Inch IN-P14C</t>
+          <t>Lenovo V15 G4 AMD Ryzen</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Thomson NEO 14.1 Inch IN-P14C Intel Celeron Dual Core N4020 Processor &amp; Window 11 Home Notebook (4 GB RAM DDR4/ 128 GB SSD/Numeric Touch Pad/Thin &amp; Light Weight/Silver)</t>
+          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
         </is>
       </c>
       <c r="C364" t="inlineStr"/>
       <c r="D364" t="n">
-        <v>12990</v>
+        <v>49999</v>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-21</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Thomson NEO 14.1 Inch IN-P14C</t>
+          <t>Lenovo V15 G4 AMD Ryzen</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Thomson NEO 14.1 Inch IN-P14C Intel Celeron Dual Core N4020 Processor &amp; Window 11 Home Notebook (4 GB RAM DDR4/ 128 GB SSD/Numeric Touch Pad/Thin &amp; Light Weight/Silver)</t>
+          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
         </is>
       </c>
       <c r="C365" t="inlineStr"/>
       <c r="D365" t="n">
-        <v>12990</v>
+        <v>52760</v>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Thomson NEO 14.1 Inch IN-P14C</t>
+          <t>Lenovo V15 G4 AMD Ryzen</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Thomson NEO 14.1 Inch IN-P14C Intel Celeron Dual Core N4020 Processor &amp; Window 11 Home Notebook (4 GB RAM DDR4/ 128 GB SSD/Numeric Touch Pad/Thin &amp; Light Weight/Silver)</t>
+          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
         </is>
       </c>
       <c r="C366" t="inlineStr"/>
       <c r="D366" t="n">
-        <v>22990</v>
+        <v>52300</v>
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>Thomson NEO 14.1 Inch IN-P14C</t>
+          <t>Lenovo V15 G4 AMD Ryzen</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Thomson NEO 14.1 Inch IN-P14C Intel Celeron Dual Core N4020 Processor &amp; Window 11 Home Notebook (4 GB RAM DDR4/ 128 GB SSD/Numeric Touch Pad/Thin &amp; Light Weight/Silver)</t>
+          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
         </is>
       </c>
       <c r="C367" t="inlineStr"/>
       <c r="D367" t="n">
-        <v>22990</v>
+        <v>52490</v>
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>acer Aspire 3, Intel Core</t>
+          <t>Lenovo V15 G4 AMD Ryzen</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>acer Aspire 3, Intel Core Celeron N4500, 12GB LPDDR4X RAM, 512GB SSD, HD, 15.6"/39.62cm, Windows 11 Home, Pure Silver, 1.5KG, A325-45, Thin and Light Laptop</t>
+          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
         </is>
       </c>
       <c r="C368" t="inlineStr"/>
       <c r="D368" t="n">
-        <v>39890</v>
+        <v>52300</v>
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-05-27</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>acer Aspire Lite, AMD Ryzen</t>
+          <t>Lenovo V15 G4 AMD Ryzen</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>acer Aspire Lite, AMD Ryzen 3 5300U Processor, 16 GB RAM, 512GB SSD, Full HD, 15.6"/39.62cm, Windows 11 Home, Steel Gray, 1.59KG, AL15-41, Metal Body, Premium Thin and Light Laptop</t>
+          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
         </is>
       </c>
       <c r="C369" t="inlineStr"/>
       <c r="D369" t="n">
-        <v>42990</v>
+        <v>52890</v>
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-31</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD</t>
+          <t>Lenovo V15 G4 AMD Ryzen</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
+          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
         </is>
       </c>
       <c r="C370" t="inlineStr"/>
       <c r="D370" t="n">
-        <v>45990</v>
+        <v>53999</v>
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD</t>
+          <t>Lenovo V15 G4 AMD Ryzen</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
+          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
         </is>
       </c>
       <c r="C371" t="inlineStr"/>
       <c r="D371" t="n">
-        <v>45990</v>
+        <v>53999</v>
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-06-02</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD</t>
+          <t>Lenovo V15 G4 AMD Ryzen</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
+          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
         </is>
       </c>
       <c r="C372" t="inlineStr"/>
       <c r="D372" t="n">
-        <v>45990</v>
+        <v>54790</v>
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD</t>
+          <t>lenovo_v15_g4_amd_ryzen</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
+          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
         </is>
       </c>
       <c r="C373" t="inlineStr"/>
       <c r="D373" t="n">
-        <v>43990</v>
+        <v>54740</v>
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD</t>
+          <t>lenovo_v15_g6_amd_ryzen</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
+          <t>Lenovo V15 G6 AMD Ryzen 7 170 (Coequal 7735HS) 15.6" (39.62cm) FHD Thin and Light Business Laptop (16GB RAM DDR5/ 512GB SSD/Windows 11/ MS Office 2024/ AMD Radeon Graphics/Luna Grey/ 1.6 kg)</t>
         </is>
       </c>
       <c r="C374" t="inlineStr"/>
       <c r="D374" t="n">
-        <v>43990</v>
+        <v>64999</v>
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD</t>
+          <t>Lenovo Yoga Slim 7 (Smartchoice)</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
+          <t>Lenovo Yoga Slim 7 (Smartchoice) Aura Edition, Intel Core Ultra 5 226V, 16GB RAM, 1TB SSD, WUXGA OLED, Copilot+ AI PC, 40 TOPS, 14"/35.5cm, Windows 11, Office 2024, Grey, 1.19Kg, 83JX005FIN, AI Laptop</t>
         </is>
       </c>
       <c r="C375" t="inlineStr"/>
       <c r="D375" t="n">
-        <v>43990</v>
+        <v>99990</v>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-15</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD</t>
+          <t>Lenovo Yoga Slim 7 (Smartchoice)</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
+          <t>Lenovo Yoga Slim 7 (Smartchoice) Aura Edition, Intel Core Ultra 5 226V, 16GB RAM, 1TB SSD, WUXGA OLED, Copilot+ AI PC, 40 TOPS, 14"/35.5cm, Windows 11, Office 2024, Grey, 1.19Kg, 83JX005FIN, AI Laptop</t>
         </is>
       </c>
       <c r="C376" t="inlineStr"/>
       <c r="D376" t="n">
-        <v>43990</v>
+        <v>105939</v>
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-19</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD</t>
+          <t>Lenovo Yoga Slim 7, Intel</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
+          <t>Lenovo Yoga Slim 7, Intel Core Ultra 5 125H, 16GB RAM, 512GB SSD, AI PC, WUXGA-OLED, 14"/35.5cm, Windows 11, Microsoft 365 Basic + Office 2024, Grey, 1.39Kg, 83CV00DFIN, AI Powered Laptop</t>
         </is>
       </c>
       <c r="C377" t="inlineStr"/>
       <c r="D377" t="n">
-        <v>43990</v>
+        <v>77990</v>
       </c>
       <c r="E377" t="inlineStr">
         <is>
@@ -8342,206 +8342,206 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop ModeI 7410 Laptop |</t>
+          <t>Lenovo Yoga Slim 7, Intel</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop ModeI 7410 Laptop | InteI Core i5 10th Gen | 16GB DDR4 RAM | 256GB SSD | 14" Full HD Display | Win 10 Pro | InteI UHD Graphics 620 | 3 Months Seller Warranty | A+ Condition (Refab)</t>
+          <t>Lenovo Yoga Slim 7, Intel Core Ultra 5 125H, 16GB RAM, 512GB SSD, AI PC, WUXGA-OLED, 14"/35.5cm, Windows 11, Microsoft 365 Basic + Office 2024, Grey, 1.39Kg, 83CV00DFIN, AI Powered Laptop</t>
         </is>
       </c>
       <c r="C378" t="inlineStr"/>
       <c r="D378" t="n">
-        <v>27299</v>
+        <v>84990</v>
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-05-19</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5</t>
+          <t>Lenovo {SmartChoice Chromebook, Intel Celeron</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5 11th Gen Processor |8GB DDR4 RAM |256GB SSD |14" FHD Display | Win10 | A+ Condition Laptop (Refab)</t>
+          <t>Lenovo {SmartChoice Chromebook, Intel Celeron N4500, 4GB RAM, 64GB eMMC, HD, 11.6"/29.46cm, Chrome OS, Blue, 1.21Kg, 2Wx2 Stereo Speakers, HD Camera, 82UY0014HA, Laptop</t>
         </is>
       </c>
       <c r="C379" t="inlineStr"/>
       <c r="D379" t="n">
-        <v>26999</v>
+        <v>21990</v>
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5</t>
+          <t>Lenovo {SmartChoice Chromebook, Intel Celeron</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5 11th Gen Processor |8GB DDR4 RAM |256GB SSD |14" FHD Display | Win10 | A+ Condition Laptop (Refab)</t>
+          <t>Lenovo {SmartChoice Chromebook, Intel Celeron N4500, 4GB RAM, 64GB eMMC, HD, 11.6"/29.46cm, Chrome OS, Blue, 1.21Kg, 2Wx2 Stereo Speakers, HD Camera, 82UY0014HA, Laptop</t>
         </is>
       </c>
       <c r="C380" t="inlineStr"/>
       <c r="D380" t="n">
-        <v>26400</v>
+        <v>17990</v>
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-08</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5</t>
+          <t>msi_cyborg_15,_intel_12th</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5 11th Gen Processor |8GB DDR4 RAM |256GB SSD |14" FHD Display | Win10 | A+ Condition Laptop (Refab)</t>
+          <t>MSI Cyborg 15, Intel 12th Gen. i5-12450H, 40CM FHD 144Hz Gaming Laptop (16GB/512GB NVMe SSD/Windows 11 Home/MSO 2021/NVIDIA GeForce RTX 3050, GDDR6 6GB/Translucent Black/1.9Kg) A12UDX-1468IN</t>
         </is>
       </c>
       <c r="C381" t="inlineStr"/>
       <c r="D381" t="n">
-        <v>28599</v>
+        <v>72990</v>
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5</t>
+          <t>primebook_2_max_(2026)_|</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5 11th Gen Processor |8GB DDR4 RAM |256GB SSD |14" FHD Display | Win10 | A+ Condition Laptop (Refab)</t>
+          <t>Primebook 2 Max (2026) | 8GB RAM, 256GB UFS Storage | 15.6-Inch Full HD IPS Display | 12hrs Battery | MediaTek Helio G99 | Android 15 (PrimeOS 3.0) | Backlit Keyboard | in-Built AI (Gray)</t>
         </is>
       </c>
       <c r="C382" t="inlineStr"/>
       <c r="D382" t="n">
-        <v>28999</v>
+        <v>29990</v>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5</t>
+          <t>Samsung Galaxy Book6 (Gray, 16GB</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5 11th Gen Processor |8GB DDR4 RAM |256GB SSD |14" FHD Display | Win10 | A+ Condition Laptop (Refab)</t>
+          <t>Samsung Galaxy Book6 (Gray, 16GB RAM, 1TB SSD) | Intel Core Ultra 5 (Series 3) | 16" WUXGA+ Display with Touchscreen | 24Hrs Battery Life | 120 Hz Refresh Rate | Dolby Atmos Stereo Speakers | AI PC</t>
         </is>
       </c>
       <c r="C383" t="inlineStr"/>
       <c r="D383" t="n">
-        <v>31990</v>
+        <v>146990</v>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5</t>
+          <t>Thomson NEO 14.1 Inch IN-P14C</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5 11th Gen Processor |8GB DDR4 RAM |256GB SSD |14" FHD Display | Win10 | A+ Condition Laptop (Refab)</t>
+          <t>Thomson NEO 14.1 Inch IN-P14C Intel Celeron Dual Core N4020 Processor &amp; Window 11 Home Notebook (4 GB RAM DDR4/ 128 GB SSD/Numeric Touch Pad/Thin &amp; Light Weight/Silver)</t>
         </is>
       </c>
       <c r="C384" t="inlineStr"/>
       <c r="D384" t="n">
-        <v>35490</v>
+        <v>12990</v>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5</t>
+          <t>Thomson NEO 14.1 Inch IN-P14C</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5 11th Gen Processor |8GB DDR4 RAM |256GB SSD |14" FHD Display | Win10 | A+ Condition Laptop (Refab)</t>
+          <t>Thomson NEO 14.1 Inch IN-P14C Intel Celeron Dual Core N4020 Processor &amp; Window 11 Home Notebook (4 GB RAM DDR4/ 128 GB SSD/Numeric Touch Pad/Thin &amp; Light Weight/Silver)</t>
         </is>
       </c>
       <c r="C385" t="inlineStr"/>
       <c r="D385" t="n">
-        <v>37490</v>
+        <v>12990</v>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Model E5570 Laptop | Core</t>
+          <t>Thomson NEO 14.1 Inch IN-P14C</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Model E5570 Laptop | Core i7 6th Gen | 8GB Fast RAM | 256GB SSD | 15.6" HD Display | HD Graphics | Win 10 | WiFi| (Pre-Owned &amp; Tested)</t>
+          <t>Thomson NEO 14.1 Inch IN-P14C Intel Celeron Dual Core N4020 Processor &amp; Window 11 Home Notebook (4 GB RAM DDR4/ 128 GB SSD/Numeric Touch Pad/Thin &amp; Light Weight/Silver)</t>
         </is>
       </c>
       <c r="C386" t="inlineStr"/>
       <c r="D386" t="n">
-        <v>20599</v>
+        <v>22990</v>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-08</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>𝗛𝗣𝗣𝗿𝗼𝗯𝗼𝗼𝗸Model 430 G3 Business Laptop</t>
+          <t>Thomson NEO 14.1 Inch IN-P14C</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>𝗛𝗣𝗣𝗿𝗼𝗯𝗼𝗼𝗸Model 430 G3 Business Laptop | InteI i5 6th Gen | 8GB RAM | 256GB SSD | WiFi | Webcam | Win10 Pro (Refab)</t>
+          <t>Thomson NEO 14.1 Inch IN-P14C Intel Celeron Dual Core N4020 Processor &amp; Window 11 Home Notebook (4 GB RAM DDR4/ 128 GB SSD/Numeric Touch Pad/Thin &amp; Light Weight/Silver)</t>
         </is>
       </c>
       <c r="C387" t="inlineStr"/>
       <c r="D387" t="n">
-        <v>20299</v>
+        <v>22990</v>
       </c>
       <c r="E387" t="inlineStr">
         <is>
@@ -8552,61 +8552,481 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>𝗛𝗣𝗣𝗿𝗼𝗯𝗼𝗼𝗸Model 430 G3 Business Laptop</t>
+          <t>acer Aspire 3, Intel Core</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>𝗛𝗣𝗣𝗿𝗼𝗯𝗼𝗼𝗸Model 430 G3 Business Laptop | 𝗜𝗡𝗧𝗘𝗟i5 6th Gen | 8GB RAM | 256GB SSD | WiFi | Webcam | Win10 Pro (Refab)</t>
+          <t>acer Aspire 3, Intel Core Celeron N4500, 12GB LPDDR4X RAM, 512GB SSD, HD, 15.6"/39.62cm, Windows 11 Home, Pure Silver, 1.5KG, A325-45, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C388" t="inlineStr"/>
       <c r="D388" t="n">
-        <v>20499</v>
+        <v>39890</v>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>𝗛𝗣𝗣𝗿𝗼𝗯𝗼𝗼𝗸Model 430 G3 Business Laptop</t>
+          <t>acer Aspire Lite, AMD Ryzen</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>𝗛𝗣𝗣𝗿𝗼𝗯𝗼𝗼𝗸Model 430 G3 Business Laptop | 𝗜𝗡𝗧𝗘𝗟i5 6th Gen | 8GB RAM | 256GB SSD | WiFi | Webcam | Win10 Pro (Refab)</t>
+          <t>acer Aspire Lite, AMD Ryzen 3 5300U Processor, 16 GB RAM, 512GB SSD, Full HD, 15.6"/39.62cm, Windows 11 Home, Steel Gray, 1.59KG, AL15-41, Metal Body, Premium Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C389" t="inlineStr"/>
       <c r="D389" t="n">
-        <v>19999</v>
+        <v>42990</v>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-04-16</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>𝗟𝗲𝗻𝗼𝘃𝗼model_l14_laptop|_core_i5</t>
+          <t>acer SmartChoice Aspire Lite, AMD</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>𝗟𝗲𝗻𝗼𝘃𝗼Model L14 Laptop| Core i5 11th Gen Processor | 16GB Fast RAM/ 256GB SSD | 14″ HD Display | A+ (Pre-Owned &amp; Tested)</t>
+          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C390" t="inlineStr"/>
       <c r="D390" t="n">
+        <v>45990</v>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>acer SmartChoice Aspire Lite, AMD</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr"/>
+      <c r="D391" t="n">
+        <v>45990</v>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>acer SmartChoice Aspire Lite, AMD</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr"/>
+      <c r="D392" t="n">
+        <v>45990</v>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>acer SmartChoice Aspire Lite, AMD</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr"/>
+      <c r="D393" t="n">
+        <v>43990</v>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>acer SmartChoice Aspire Lite, AMD</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr"/>
+      <c r="D394" t="n">
+        <v>43990</v>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>acer SmartChoice Aspire Lite, AMD</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr"/>
+      <c r="D395" t="n">
+        <v>43990</v>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>acer SmartChoice Aspire Lite, AMD</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr"/>
+      <c r="D396" t="n">
+        <v>43990</v>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>acer SmartChoice Aspire Lite, AMD</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr"/>
+      <c r="D397" t="n">
+        <v>43990</v>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop ModeI 7410 Laptop |</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop ModeI 7410 Laptop | InteI Core i5 10th Gen | 16GB DDR4 RAM | 256GB SSD | 14" Full HD Display | Win 10 Pro | InteI UHD Graphics 620 | 3 Months Seller Warranty | A+ Condition (Refab)</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr"/>
+      <c r="D398" t="n">
+        <v>27299</v>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5 11th Gen Processor |8GB DDR4 RAM |256GB SSD |14" FHD Display | Win10 | A+ Condition Laptop (Refab)</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr"/>
+      <c r="D399" t="n">
+        <v>26999</v>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5 11th Gen Processor |8GB DDR4 RAM |256GB SSD |14" FHD Display | Win10 | A+ Condition Laptop (Refab)</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr"/>
+      <c r="D400" t="n">
+        <v>26400</v>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5 11th Gen Processor |8GB DDR4 RAM |256GB SSD |14" FHD Display | Win10 | A+ Condition Laptop (Refab)</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr"/>
+      <c r="D401" t="n">
+        <v>28599</v>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5 11th Gen Processor |8GB DDR4 RAM |256GB SSD |14" FHD Display | Win10 | A+ Condition Laptop (Refab)</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr"/>
+      <c r="D402" t="n">
+        <v>28999</v>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5 11th Gen Processor |8GB DDR4 RAM |256GB SSD |14" FHD Display | Win10 | A+ Condition Laptop (Refab)</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr"/>
+      <c r="D403" t="n">
+        <v>31990</v>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5 11th Gen Processor |8GB DDR4 RAM |256GB SSD |14" FHD Display | Win10 | A+ Condition Laptop (Refab)</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr"/>
+      <c r="D404" t="n">
+        <v>35490</v>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5 11th Gen Processor |8GB DDR4 RAM |256GB SSD |14" FHD Display | Win10 | A+ Condition Laptop (Refab)</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr"/>
+      <c r="D405" t="n">
+        <v>37490</v>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Model E5570 Laptop | Core</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Model E5570 Laptop | Core i7 6th Gen | 8GB Fast RAM | 256GB SSD | 15.6" HD Display | HD Graphics | Win 10 | WiFi| (Pre-Owned &amp; Tested)</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr"/>
+      <c r="D406" t="n">
+        <v>20599</v>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>𝗛𝗣𝗣𝗿𝗼𝗯𝗼𝗼𝗸Model 430 G3 Business Laptop</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>𝗛𝗣𝗣𝗿𝗼𝗯𝗼𝗼𝗸Model 430 G3 Business Laptop | InteI i5 6th Gen | 8GB RAM | 256GB SSD | WiFi | Webcam | Win10 Pro (Refab)</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr"/>
+      <c r="D407" t="n">
+        <v>20299</v>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>𝗛𝗣𝗣𝗿𝗼𝗯𝗼𝗼𝗸Model 430 G3 Business Laptop</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>𝗛𝗣𝗣𝗿𝗼𝗯𝗼𝗼𝗸Model 430 G3 Business Laptop | 𝗜𝗡𝗧𝗘𝗟i5 6th Gen | 8GB RAM | 256GB SSD | WiFi | Webcam | Win10 Pro (Refab)</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr"/>
+      <c r="D408" t="n">
+        <v>20499</v>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>𝗛𝗣𝗣𝗿𝗼𝗯𝗼𝗼𝗸Model 430 G3 Business Laptop</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>𝗛𝗣𝗣𝗿𝗼𝗯𝗼𝗼𝗸Model 430 G3 Business Laptop | 𝗜𝗡𝗧𝗘𝗟i5 6th Gen | 8GB RAM | 256GB SSD | WiFi | Webcam | Win10 Pro (Refab)</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr"/>
+      <c r="D409" t="n">
+        <v>19999</v>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>𝗟𝗲𝗻𝗼𝘃𝗼model_l14_laptop|_core_i5</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>𝗟𝗲𝗻𝗼𝘃𝗼Model L14 Laptop| Core i5 11th Gen Processor | 16GB Fast RAM/ 256GB SSD | 14″ HD Display | A+ (Pre-Owned &amp; Tested)</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr"/>
+      <c r="D410" t="n">
         <v>31599</v>
       </c>
-      <c r="E390" t="inlineStr">
+      <c r="E410" t="inlineStr">
         <is>
           <t>2026-07-21</t>
         </is>

--- a/amazon_products.xlsx
+++ b/amazon_products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E410"/>
+  <dimension ref="A1:E427"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1643,38 +1643,38 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ASUS Vivobook Go 14, AMD</t>
+          <t>asus_vivobook_go_14_(2026),amd</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ASUS Vivobook Go 14, AMD Ryzen 5 7520U, 16GB RAM, 512GB SSD, FHD, 14", 60Hz,42WHrs, Windows 11, M365 Basic (1Year)*,Office Home 2024, Mixed Black, 1.38 kg, E1404FA-EB774WS, Thin &amp; Light Laptop</t>
+          <t>ASUS Vivobook Go 14 (2026),AMD Ryzen 3 30 Processor,AMD Radeon iGPU,8GB RAM,512GB SSD,FHD,14" (35.5 cm),Windows 11,M365 Basic(1Y)* Office 2024,Cool Silver,1.38 Kg,E1404FA-EB1224WS,Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="n">
-        <v>52990</v>
+        <v>44990</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-08-04</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ASUS Vivobook S14,Smartchoice,AMD Ryzen AI</t>
+          <t>ASUS Vivobook Go 14, AMD</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ASUS Vivobook S14,Smartchoice,AMD Ryzen AI 7 350,16GB RAM,1TB SSD,OLED,14",Windows 11, Office24,M365 Basic (1Yr)*, Matte Gray,1.4Kg, M3407KA-SF049WS,50 Tops,Metallic Design,Next-Gen AI Laptop,Copilot+</t>
+          <t>ASUS Vivobook Go 14, AMD Ryzen 5 7520U, 16GB RAM, 512GB SSD, FHD, 14", 60Hz,42WHrs, Windows 11, M365 Basic (1Year)*,Office Home 2024, Mixed Black, 1.38 kg, E1404FA-EB774WS, Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="n">
-        <v>88990</v>
+        <v>52990</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -1716,74 +1716,74 @@
       </c>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="n">
-        <v>83990</v>
+        <v>88990</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-04-16</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>asus_vivobook_s16_oled,_intel</t>
+          <t>ASUS Vivobook S14,Smartchoice,AMD Ryzen AI</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ASUS Vivobook S16 OLED, Intel Core Ultra 5 225H, 16GB RAM, 512GB SSD, FHD 16", Win 11, Office 2024, Cool Silver, 1.7Kg, S3607CA-SH071WS,Intel iGPU, 70Whr, M365 Basic(1Year) Metallic Design Laptop</t>
+          <t>ASUS Vivobook S14,Smartchoice,AMD Ryzen AI 7 350,16GB RAM,1TB SSD,OLED,14",Windows 11, Office24,M365 Basic (1Yr)*, Matte Gray,1.4Kg, M3407KA-SF049WS,50 Tops,Metallic Design,Next-Gen AI Laptop,Copilot+</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="n">
-        <v>92990</v>
+        <v>83990</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-05-21</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>asus_vivobook_s16,14th_gen,_intel</t>
+          <t>asus_vivobook_s16_oled,_intel</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>ASUS Vivobook S16,14th Gen, Intel Core 5-210H,Metallic Design Laptop(Intel UHD iGPU/16GB RAM/512GB SSD/FHD+/16"/144Hz/Windows 11/M365 Basic(1Year)*/Office Home 2024/Silver/1.7Kg) S3607VA-RP114WS</t>
+          <t>ASUS Vivobook S16 OLED, Intel Core Ultra 5 225H, 16GB RAM, 512GB SSD, FHD 16", Win 11, Office 2024, Cool Silver, 1.7Kg, S3607CA-SH071WS,Intel iGPU, 70Whr, M365 Basic(1Year) Metallic Design Laptop</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="n">
-        <v>68990</v>
+        <v>92990</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ASUS Vivobook S16,Intel Core Ultra</t>
+          <t>asus_vivobook_s16,14th_gen,_intel</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ASUS Vivobook S16,Intel Core Ultra 5 225H,AI PC(Intel Arc iGPU/16GB RAM/512GB SSD/FHD/16/60Hz/Backlit Keyboard/70Whr/Windows 11/M365 Basic(1Year)*/Office Home 2024/Cool Silver/1.7 Kg) S3607CA-SH071WS</t>
+          <t>ASUS Vivobook S16,14th Gen, Intel Core 5-210H,Metallic Design Laptop(Intel UHD iGPU/16GB RAM/512GB SSD/FHD+/16"/144Hz/Windows 11/M365 Basic(1Year)*/Office Home 2024/Silver/1.7Kg) S3607VA-RP114WS</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="n">
-        <v>81990</v>
+        <v>68990</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -1800,32 +1800,32 @@
       </c>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="n">
-        <v>79990</v>
+        <v>81990</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ASUS Zenbook 14 (2026),Smartchoice,Intel Core</t>
+          <t>ASUS Vivobook S16,Intel Core Ultra</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ASUS Zenbook 14 (2026),Smartchoice,Intel Core Ultra 7 255H,32GB RAM,1TB SSD,OLED,Touchscreen,14"(35.5 cm),Win 11,M365 Basic(1Y)* Office 24,Ponder Blue,1.28 Kg,UX3405CA-QL1015WS,Thin &amp; Light Laptop</t>
+          <t>ASUS Vivobook S16,Intel Core Ultra 5 225H,AI PC(Intel Arc iGPU/16GB RAM/512GB SSD/FHD/16/60Hz/Backlit Keyboard/70Whr/Windows 11/M365 Basic(1Year)*/Office Home 2024/Cool Silver/1.7 Kg) S3607CA-SH071WS</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="n">
-        <v>119990</v>
+        <v>79990</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
@@ -1846,7 +1846,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-22</t>
         </is>
       </c>
     </row>
@@ -1858,58 +1858,58 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>ASUS Zenbook 14 (2026),Smartchoice,Intel Core Ultra 9 285H,32GB RAM,1TB SSD,OLED,Touchscreen,14"(35.5 cm),Win 11,M365 Basic(1Y)* Office 24,Foggy Silver,1.28 Kg,UX3405CA-QL1113WS,Thin &amp; Light Laptop</t>
+          <t>ASUS Zenbook 14 (2026),Smartchoice,Intel Core Ultra 7 255H,32GB RAM,1TB SSD,OLED,Touchscreen,14"(35.5 cm),Win 11,M365 Basic(1Y)* Office 24,Ponder Blue,1.28 Kg,UX3405CA-QL1015WS,Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="n">
-        <v>124990</v>
+        <v>119990</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ASUS Zenbook 14, Intel Core</t>
+          <t>ASUS Zenbook 14 (2026),Smartchoice,Intel Core</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ASUS Zenbook 14, Intel Core Ultra 5 Series 2, 16GB RAM, 1TB SSD, 3K OLED 14", Touchscreen, Win 11, Office Home 2024, Ponder Blue, 1.28kg, UX3405CA-PZ162WS, Intel Arc iGPU, M365 Basic (1Year)* Laptop</t>
+          <t>ASUS Zenbook 14 (2026),Smartchoice,Intel Core Ultra 9 285H,32GB RAM,1TB SSD,OLED,Touchscreen,14"(35.5 cm),Win 11,M365 Basic(1Y)* Office 24,Foggy Silver,1.28 Kg,UX3405CA-QL1113WS,Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="n">
-        <v>106990</v>
+        <v>124990</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ASUS Zenbook 14, Smartchoice, Intel</t>
+          <t>ASUS Zenbook 14, Intel Core</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ASUS Zenbook 14, Smartchoice, Intel Core Ultra 5 Series 2,16GB RAM,1TB SSD,3K OLED 14", Touchscreen, Win 11, Office Home 2024,Blue, 1.28kg, UX3405CA-PZ162WS, Intel Arc iGPU, M365 Basic (1Year)* Laptop</t>
+          <t>ASUS Zenbook 14, Intel Core Ultra 5 Series 2, 16GB RAM, 1TB SSD, 3K OLED 14", Touchscreen, Win 11, Office Home 2024, Ponder Blue, 1.28kg, UX3405CA-PZ162WS, Intel Arc iGPU, M365 Basic (1Year)* Laptop</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="n">
-        <v>108990</v>
+        <v>106990</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-14</t>
         </is>
       </c>
     </row>
@@ -1921,54 +1921,54 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ASUS Zenbook 14, Smartchoice, Intel Core Ultra 5 Series 2,16GB RAM,1TB SSD,3K OLED 14", Touchscreen, Win 11, Office Home 2024,Blue, 1.28kg, UX3405CA-PZ162WS, Intel iGPU, M365 Basic (1Year)* Laptop</t>
+          <t>ASUS Zenbook 14, Smartchoice, Intel Core Ultra 5 Series 2,16GB RAM,1TB SSD,3K OLED 14", Touchscreen, Win 11, Office Home 2024,Blue, 1.28kg, UX3405CA-PZ162WS, Intel Arc iGPU, M365 Basic (1Year)* Laptop</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="n">
-        <v>114990</v>
+        <v>108990</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>asus_zenbook_14,smartchoice,intel_core_ultra</t>
+          <t>ASUS Zenbook 14, Smartchoice, Intel</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>ASUS Zenbook 14,Smartchoice,Intel Core Ultra 5 (Series 2),16GB,1TB,3K OLED Touch Screen,14",120Hz,Win 11,M365 Basic (1Y)*,Office 2024, Silver,1.28 kg,UX3405CA-PZ345WS,Thin &amp; Light Laptop</t>
+          <t>ASUS Zenbook 14, Smartchoice, Intel Core Ultra 5 Series 2,16GB RAM,1TB SSD,3K OLED 14", Touchscreen, Win 11, Office Home 2024,Blue, 1.28kg, UX3405CA-PZ162WS, Intel iGPU, M365 Basic (1Year)* Laptop</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="n">
-        <v>117990</v>
+        <v>114990</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>asus_zenbook_s14_(2026),smartchoice,intel_core</t>
+          <t>asus_zenbook_14,smartchoice,intel_core_ultra</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>ASUS Zenbook S14 (2026),Smartchoice,Intel Core Ultra 5 226V,Intel Arc iGPU,16GB/512GB,3K OLED,Touchscreen,14"(35.5 cm),Windows 11,M365 Basic(1Y),Office 2024,Gray,1.2 Kg,UX5406SA-PZ658WS,Copilot+ PC</t>
+          <t>ASUS Zenbook 14,Smartchoice,Intel Core Ultra 5 (Series 2),16GB,1TB,3K OLED Touch Screen,14",120Hz,Win 11,M365 Basic (1Y)*,Office 2024, Silver,1.28 kg,UX3405CA-PZ345WS,Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="n">
-        <v>134990</v>
+        <v>117990</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -1979,21 +1979,21 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Acer Aspire 3 Laptop Intel</t>
+          <t>asus_zenbook_s14_(2026),smartchoice,intel_core</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Acer Aspire 3 Laptop Intel Core Celeron N4500 Processor Laptop (8 GB LPDDR4X SDRAM/256 GB SSD/Win11 Home/38 WHR/HD Webcam) A325-45 with 39.63 cm (15.6") HD Display, Pure Silver, 1.5 KG</t>
+          <t>ASUS Zenbook S14 (2026),Smartchoice,Intel Core Ultra 5 226V,Intel Arc iGPU,16GB/512GB,3K OLED,Touchscreen,14"(35.5 cm),Windows 11,M365 Basic(1Y),Office 2024,Gray,1.2 Kg,UX5406SA-PZ658WS,Copilot+ PC</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="n">
-        <v>36990</v>
+        <v>134990</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -2014,28 +2014,28 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Acer Aspire Lite 12th Gen,</t>
+          <t>Acer Aspire 3 Laptop Intel</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Acer Aspire Lite 12th Gen, Intel Core i5-12450H, Office 2024 + M365 Basic, 12GB RAM/512GB SSD, 39.62cm 15.6" FHD IPS Display, Win 11 Home, Pure Silver, 1.7KG,AL15-52H, Backlit KB, Thin &amp; Light Laptop</t>
+          <t>Acer Aspire 3 Laptop Intel Core Celeron N4500 Processor Laptop (8 GB LPDDR4X SDRAM/256 GB SSD/Win11 Home/38 WHR/HD Webcam) A325-45 with 39.63 cm (15.6") HD Display, Pure Silver, 1.5 KG</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="n">
-        <v>52990</v>
+        <v>36990</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
@@ -2052,11 +2052,11 @@
       </c>
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="n">
-        <v>47990</v>
+        <v>52990</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-08</t>
         </is>
       </c>
     </row>
@@ -2073,11 +2073,11 @@
       </c>
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="n">
-        <v>53990</v>
+        <v>47990</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-17</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
     </row>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
     </row>
@@ -2157,11 +2157,11 @@
       </c>
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="n">
-        <v>49990</v>
+        <v>53990</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-22</t>
         </is>
       </c>
     </row>
@@ -2178,11 +2178,11 @@
       </c>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="n">
-        <v>53990</v>
+        <v>49990</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-27</t>
         </is>
       </c>
     </row>
@@ -2199,32 +2199,32 @@
       </c>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="n">
-        <v>50990</v>
+        <v>53990</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Acer Aspire One, Intel Core</t>
+          <t>Acer Aspire Lite 12th Gen,</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Acer Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X RAM/ 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
+          <t>Acer Aspire Lite 12th Gen, Intel Core i5-12450H, Office 2024 + M365 Basic, 12GB RAM/512GB SSD, 39.62cm 15.6" FHD IPS Display, Win 11 Home, Pure Silver, 1.7KG,AL15-52H, Backlit KB, Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="n">
-        <v>34990</v>
+        <v>50990</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-08</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
@@ -2283,11 +2283,11 @@
       </c>
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="n">
-        <v>33990</v>
+        <v>34990</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-10</t>
         </is>
       </c>
     </row>
@@ -2308,7 +2308,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-15</t>
         </is>
       </c>
     </row>
@@ -2325,11 +2325,11 @@
       </c>
       <c r="C91" t="inlineStr"/>
       <c r="D91" t="n">
-        <v>35990</v>
+        <v>33990</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-17</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
     </row>
@@ -2371,7 +2371,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
     </row>
@@ -2392,7 +2392,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
     </row>
@@ -2404,37 +2404,37 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Acer Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X RAM/ 512GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
+          <t>Acer Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X RAM/ 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="n">
-        <v>38990</v>
+        <v>35990</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-22</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>acer_one_14_laptop_z14-55m</t>
+          <t>Acer Aspire One, Intel Core</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Acer One 14 Laptop Z14-55M | 14" HD Display | AMD Ryzen 3 7320U | 8GB LPDDR5 RAM | 256GB NVMe SSD | Windows 11 | Thin &amp; Light Design | AMD Radeon Graphics | Silver</t>
+          <t>Acer Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X RAM/ 512GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="n">
-        <v>38750</v>
+        <v>38990</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-14</t>
         </is>
       </c>
     </row>
@@ -2451,11 +2451,11 @@
       </c>
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="n">
-        <v>38500</v>
+        <v>38750</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -2497,133 +2497,133 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Acer Smartchoice Aspire One, AMD</t>
+          <t>acer_one_14_laptop_z14-55m</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Acer Smartchoice Aspire One, AMD Ryzen 3-7320U, 8GB LPDDR5 RAM/ 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.48KG, A114-43, Thin and Light Laptop</t>
+          <t>Acer One 14 Laptop Z14-55M | 14" HD Display | AMD Ryzen 3 7320U | 8GB LPDDR5 RAM | 256GB NVMe SSD | Windows 11 | Thin &amp; Light Design | AMD Radeon Graphics | Silver</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="n">
-        <v>39990</v>
+        <v>38500</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Acer Smartchoice Aspire One, AMD</t>
+          <t>acer_one_14_laptop_z14-55m</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Acer Smartchoice Aspire One, AMD Ryzen 3-7320U, 8GB LPDDR5 RAM/ 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.48KG, A114-43, Thin and Light Laptop</t>
+          <t>Acer One 14 Laptop Z14-55M | 14" HD Display | AMD Ryzen 3 7320U | 8GB LPDDR5 RAM | 256GB NVMe SSD | Windows 11 | Thin &amp; Light Design | AMD Radeon Graphics | Silver</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
       <c r="D101" t="n">
-        <v>39990</v>
+        <v>38500</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-08-04</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>acer_smartchoice_aspire_one,_amd</t>
+          <t>Acer Smartchoice Aspire One, AMD</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Acer Smartchoice Aspire One, AMD Ryzen 3-7320U, 8GB LPDDR5 RAM/ 512GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.48KG, A114-43, Thin and Light Laptop</t>
+          <t>Acer Smartchoice Aspire One, AMD Ryzen 3-7320U, 8GB LPDDR5 RAM/ 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.48KG, A114-43, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="n">
-        <v>41990</v>
+        <v>39990</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Acer Smartchoice Aspire One, Intel</t>
+          <t>Acer Smartchoice Aspire One, AMD</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Acer Smartchoice Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X / 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
+          <t>Acer Smartchoice Aspire One, AMD Ryzen 3-7320U, 8GB LPDDR5 RAM/ 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.48KG, A114-43, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="n">
-        <v>32990</v>
+        <v>39990</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-06-12</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Acer Smartchoice Aspire One, Intel</t>
+          <t>acer_smartchoice_aspire_one,_amd</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Acer Smartchoice Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X / 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
+          <t>Acer Smartchoice Aspire One, AMD Ryzen 3-7320U, 8GB LPDDR5 RAM/ 512GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.48KG, A114-43, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="n">
-        <v>32990</v>
+        <v>41990</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Acer Smartchoice Aspire One, Intel</t>
+          <t>acer_smartchoice_aspire_one,_amd</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Acer Smartchoice Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X / 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
+          <t>Acer Smartchoice Aspire One, AMD Ryzen 5-40, 8GB LPDDR5 RAM/ 512GB SSD, 14.0"/35.56cm WXGA Display, Win 11 Home, Pure Silver, 1.48KG, A114-43, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="n">
-        <v>32990</v>
+        <v>42990</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-08-04</t>
         </is>
       </c>
     </row>
@@ -2644,7 +2644,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>
@@ -2665,7 +2665,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-24</t>
         </is>
       </c>
     </row>
@@ -2682,11 +2682,11 @@
       </c>
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="n">
-        <v>35990</v>
+        <v>32990</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -2703,11 +2703,11 @@
       </c>
       <c r="C109" t="inlineStr"/>
       <c r="D109" t="n">
-        <v>35990</v>
+        <v>32990</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-27</t>
         </is>
       </c>
     </row>
@@ -2724,11 +2724,11 @@
       </c>
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="n">
-        <v>35990</v>
+        <v>32990</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-05-28</t>
         </is>
       </c>
     </row>
@@ -2740,184 +2740,184 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Acer Smartchoice Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X / 512GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
+          <t>Acer Smartchoice Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X / 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
       <c r="D111" t="n">
-        <v>34990</v>
+        <v>35990</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>acer_smartchoice_aspire_one,_intel</t>
+          <t>Acer Smartchoice Aspire One, Intel</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Acer Smartchoice Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X / 512GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
+          <t>Acer Smartchoice Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X / 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="n">
-        <v>37990</v>
+        <v>35990</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-12</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>acer_smartchoice_aspire_one,_intel</t>
+          <t>Acer Smartchoice Aspire One, Intel</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Acer Smartchoice Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X / 512GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
+          <t>Acer Smartchoice Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X / 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
       <c r="D113" t="n">
-        <v>39990</v>
+        <v>35990</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Acer Swift Go 14 AI</t>
+          <t>acer_smartchoice_aspire_one,_intel</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Acer Swift Go 14 AI PC, Qualcomm SnapdragonX Plus X1P-42-100,Office 2024 + M365 Basic,(16GB LPDDR5X/ 512GB SSD/14.5-inch WUXGA//Qualcomm Adreno/1440p IR Camera with Shutter/Win11) 1.32 kg, Steel Grey.</t>
+          <t>Acer Smartchoice Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X / 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
       <c r="D114" t="n">
-        <v>79990</v>
+        <v>33990</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-08-04</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>acer_travellite_thin_laptop_amd</t>
+          <t>Acer Smartchoice Aspire One, Intel</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Acer TravelLite Thin Laptop AMD Ryzen 5 7430U (6-Core) 16GB RAM, 512GB SSD 14" Full HD Anti-Glare Display Privacy Shutter Windows 11 MS Office Metal Body 1.34Kg Black 30M Warranty</t>
+          <t>Acer Smartchoice Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X / 512GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
       <c r="D115" t="n">
-        <v>53450</v>
+        <v>34990</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-12</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Neo 13″</t>
+          <t>acer_smartchoice_aspire_one,_intel</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Citrus</t>
+          <t>Acer Smartchoice Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X / 512GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="n">
-        <v>65000</v>
+        <v>37990</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Neo 13″</t>
+          <t>acer_smartchoice_aspire_one,_intel</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Indigo</t>
+          <t>Acer Smartchoice Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X / 512GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
       <c r="D117" t="n">
-        <v>67900</v>
+        <v>39990</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Neo 13″</t>
+          <t>Acer Swift Go 14 AI</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Indigo</t>
+          <t>Acer Swift Go 14 AI PC, Qualcomm SnapdragonX Plus X1P-42-100,Office 2024 + M365 Basic,(16GB LPDDR5X/ 512GB SSD/14.5-inch WUXGA//Qualcomm Adreno/1440p IR Camera with Shutter/Win11) 1.32 kg, Steel Grey.</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="n">
-        <v>65000</v>
+        <v>79990</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Neo 13″</t>
+          <t>acer_travellite_thin_laptop_amd</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Indigo</t>
+          <t>Acer TravelLite Thin Laptop AMD Ryzen 5 7430U (6-Core) 16GB RAM, 512GB SSD 14" Full HD Anti-Glare Display Privacy Shutter Windows 11 MS Office Metal Body 1.34Kg Black 30M Warranty</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="n">
-        <v>65700</v>
+        <v>53450</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Indigo</t>
+          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Citrus</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
@@ -2938,7 +2938,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
@@ -2955,11 +2955,11 @@
       </c>
       <c r="C121" t="inlineStr"/>
       <c r="D121" t="n">
-        <v>65000</v>
+        <v>67900</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -2980,7 +2980,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
@@ -2992,16 +2992,16 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Silver</t>
+          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Indigo</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
       <c r="D123" t="n">
-        <v>65000</v>
+        <v>65700</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-28</t>
         </is>
       </c>
     </row>
@@ -3013,7 +3013,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Silver</t>
+          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Indigo</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
@@ -3022,7 +3022,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -3034,16 +3034,16 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Silver</t>
+          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Indigo</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
       <c r="D125" t="n">
-        <v>65700</v>
+        <v>65000</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
@@ -3055,16 +3055,16 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Silver</t>
+          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Indigo</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
       <c r="D126" t="n">
-        <v>67900</v>
+        <v>65000</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -3085,7 +3085,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-24</t>
         </is>
       </c>
     </row>
@@ -3102,11 +3102,11 @@
       </c>
       <c r="C128" t="inlineStr"/>
       <c r="D128" t="n">
-        <v>64990</v>
+        <v>65000</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -3123,11 +3123,11 @@
       </c>
       <c r="C129" t="inlineStr"/>
       <c r="D129" t="n">
-        <v>63990</v>
+        <v>65700</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-05-27</t>
         </is>
       </c>
     </row>
@@ -3144,11 +3144,11 @@
       </c>
       <c r="C130" t="inlineStr"/>
       <c r="D130" t="n">
-        <v>63990</v>
+        <v>67900</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-31</t>
         </is>
       </c>
     </row>
@@ -3165,91 +3165,91 @@
       </c>
       <c r="C131" t="inlineStr"/>
       <c r="D131" t="n">
-        <v>63990</v>
+        <v>65000</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-02</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Pro Laptop</t>
+          <t>Apple 2026 MacBook Neo 13″</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Pro Laptop with M5 Max chip with 18‑core CPU and 40‑core GPU: Built for AI, 41.05 cm (16.2″) Liquid Retina XDR Display, 48GB Unified Memory, 2TB SSD Storage; Space Black</t>
+          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Silver</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
       <c r="D132" t="n">
-        <v>499900</v>
+        <v>64990</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Pro Laptop</t>
+          <t>Apple 2026 MacBook Neo 13″</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Pro Laptop with M5 Max chip with 18‑core CPU and 40‑core GPU: Built for AI, 41.05 cm (16.2″) Liquid Retina XDR Display, 48GB Unified Memory, 2TB SSD Storage; Space Black</t>
+          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Silver</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="n">
-        <v>499900</v>
+        <v>63990</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Pro Laptop</t>
+          <t>Apple 2026 MacBook Neo 13″</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Pro Laptop with M5 Max chip with 18‑core CPU and 40‑core GPU: Built for AI, 41.05 cm (16.2″) Liquid Retina XDR Display, 48GB Unified Memory, 2TB SSD Storage; Space Black</t>
+          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Silver</t>
         </is>
       </c>
       <c r="C134" t="inlineStr"/>
       <c r="D134" t="n">
-        <v>499900</v>
+        <v>63990</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Pro Laptop</t>
+          <t>Apple 2026 MacBook Neo 13″</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Pro Laptop with M5 Pro chip with 15‑core CPU and 16‑core GPU: Built for AI, 35.97 cm (14.2″) Liquid Retina XDR Display, 24GB Unified Memory, 1TB SSD Storage; Silver</t>
+          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Silver</t>
         </is>
       </c>
       <c r="C135" t="inlineStr"/>
       <c r="D135" t="n">
-        <v>234900</v>
+        <v>63990</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -3265,100 +3265,100 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Pro Laptop with M5 Pro chip with 15‑core CPU and 16‑core GPU: Built for AI, 35.97 cm (14.2″) Liquid Retina XDR Display, 24GB Unified Memory, 1TB SSD Storage; Silver</t>
+          <t>Apple 2026 MacBook Pro Laptop with M5 Max chip with 18‑core CPU and 40‑core GPU: Built for AI, 41.05 cm (16.2″) Liquid Retina XDR Display, 48GB Unified Memory, 2TB SSD Storage; Space Black</t>
         </is>
       </c>
       <c r="C136" t="inlineStr"/>
       <c r="D136" t="n">
-        <v>227400</v>
+        <v>499900</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>BrowseBook 14.1" FHD IPS Laptop</t>
+          <t>Apple 2026 MacBook Pro Laptop</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>BrowseBook 14.1" FHD IPS Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB RAM | 128GB SSD | Windows 11 | 38Wh | 1.3kg | Grey</t>
+          <t>Apple 2026 MacBook Pro Laptop with M5 Max chip with 18‑core CPU and 40‑core GPU: Built for AI, 41.05 cm (16.2″) Liquid Retina XDR Display, 48GB Unified Memory, 2TB SSD Storage; Space Black</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
       <c r="D137" t="n">
-        <v>13990</v>
+        <v>499900</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-28</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>BrowseBook 14.1" FHD IPS Laptop</t>
+          <t>Apple 2026 MacBook Pro Laptop</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>BrowseBook 14.1" FHD IPS Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB RAM | 128GB SSD | Windows 11 | 38Wh | 1.3kg | Grey</t>
+          <t>Apple 2026 MacBook Pro Laptop with M5 Max chip with 18‑core CPU and 40‑core GPU: Built for AI, 41.05 cm (16.2″) Liquid Retina XDR Display, 48GB Unified Memory, 2TB SSD Storage; Space Black</t>
         </is>
       </c>
       <c r="C138" t="inlineStr"/>
       <c r="D138" t="n">
-        <v>13990</v>
+        <v>499900</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-06-02</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>BrowseBook 14.1" FHD IPS Laptop</t>
+          <t>Apple 2026 MacBook Pro Laptop</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>BrowseBook 14.1" FHD IPS Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB RAM | 128GB SSD | Windows 11 | 38Wh | 1.3kg | Grey</t>
+          <t>Apple 2026 MacBook Pro Laptop with M5 Pro chip with 15‑core CPU and 16‑core GPU: Built for AI, 35.97 cm (14.2″) Liquid Retina XDR Display, 24GB Unified Memory, 1TB SSD Storage; Silver</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
       <c r="D139" t="n">
-        <v>13990</v>
+        <v>234900</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-06-12</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>BrowseBook 14.1" FHD IPS Laptop</t>
+          <t>Apple 2026 MacBook Pro Laptop</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>BrowseBook 14.1" FHD IPS Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB RAM | 128GB SSD | Windows 11 | 38Wh | 1.3kg | Grey</t>
+          <t>Apple 2026 MacBook Pro Laptop with M5 Pro chip with 15‑core CPU and 16‑core GPU: Built for AI, 35.97 cm (14.2″) Liquid Retina XDR Display, 24GB Unified Memory, 1TB SSD Storage; Silver</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
       <c r="D140" t="n">
-        <v>20990</v>
+        <v>227400</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
@@ -3370,100 +3370,100 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>BrowseBook 14.1" FHD IPS Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 8GB RAM | 256GB SSD | Windows 11 | 38Wh | 1.3kg | Grey</t>
+          <t>BrowseBook 14.1" FHD IPS Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB RAM | 128GB SSD | Windows 11 | 38Wh | 1.3kg | Grey</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
       <c r="D141" t="n">
-        <v>18990</v>
+        <v>13990</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron) Laptop,</t>
+          <t>BrowseBook 14.1" FHD IPS Laptop</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core 3 100U Processor, 8GB DDR4, 512 SSD, 15.6" NT FHD 120Hz IPS AG 250 nit Display, Win 11 + Office H&amp;S 2024, Carbon Black, Thin &amp; Light- 1.63Kg</t>
+          <t>BrowseBook 14.1" FHD IPS Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB RAM | 128GB SSD | Windows 11 | 38Wh | 1.3kg | Grey</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
       <c r="D142" t="n">
-        <v>46490</v>
+        <v>13990</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-04-16</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>dell_15_(previously_inspiron)_laptop,</t>
+          <t>BrowseBook 14.1" FHD IPS Laptop</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 16GB DDR4, 512 SSD, Intel UHD Graphics, 15.6" FHD 120Hz IPS AG 250 nit Display, Win 11 + Office 2024, Black, 1.63Kg</t>
+          <t>BrowseBook 14.1" FHD IPS Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB RAM | 128GB SSD | Windows 11 | 38Wh | 1.3kg | Grey</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
       <c r="D143" t="n">
-        <v>58990</v>
+        <v>13990</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>dell_15_(previously_inspiron)_laptop,</t>
+          <t>BrowseBook 14.1" FHD IPS Laptop</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 16GB DDR4, 512 SSD, Intel UHD Graphics, 15.6" FHD 120Hz IPS AG 250 nit Display, Win 11 + Office 2024, Black, 1.63Kg</t>
+          <t>BrowseBook 14.1" FHD IPS Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB RAM | 128GB SSD | Windows 11 | 38Wh | 1.3kg | Grey</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
       <c r="D144" t="n">
-        <v>59490</v>
+        <v>20990</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron) Laptop,</t>
+          <t>BrowseBook 14.1" FHD IPS Laptop</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 8GB DDR4, 512 SSD, 15.6" FHD 120Hz IPS 250 nit Display, Win 11 + Office H&amp;S 2024, Carbon Black, Thin &amp; Light 1.63Kg</t>
+          <t>BrowseBook 14.1" FHD IPS Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 8GB RAM | 256GB SSD | Windows 11 | 38Wh | 1.3kg | Grey</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
       <c r="D145" t="n">
-        <v>45490</v>
+        <v>18990</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-15</t>
         </is>
       </c>
     </row>
@@ -3475,58 +3475,58 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 8GB DDR4, 512 SSD, 15.6" FHD 120Hz IPS 250 nit Display, Win 11 + Office H&amp;S 2024, Carbon Black, Thin &amp; Light 1.63Kg</t>
+          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core 3 100U Processor, 8GB DDR4, 512 SSD, 15.6" NT FHD 120Hz IPS AG 250 nit Display, Win 11 + Office H&amp;S 2024, Carbon Black, Thin &amp; Light- 1.63Kg</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
       <c r="D146" t="n">
-        <v>44990</v>
+        <v>46490</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron) Laptop,</t>
+          <t>dell_15_(previously_inspiron)_laptop,</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 8GB DDR4, 512 SSD, 15.6" FHD 120Hz IPS 250 nit Display, Win 11 + Office H&amp;S 2024, Carbon Black, Thin &amp; Light 1.63Kg</t>
+          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 16GB DDR4, 512 SSD, Intel UHD Graphics, 15.6" FHD 120Hz IPS AG 250 nit Display, Win 11 + Office 2024, Black, 1.63Kg</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
       <c r="D147" t="n">
-        <v>44990</v>
+        <v>58990</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron) Laptop,</t>
+          <t>dell_15_(previously_inspiron)_laptop,</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 8GB DDR4, 512 SSD, 15.6" FHD 120Hz IPS 250 nit Display, Win 11 + Office H&amp;S 2024, Carbon Black, Thin &amp; Light 1.63Kg</t>
+          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 16GB DDR4, 512 SSD, Intel UHD Graphics, 15.6" FHD 120Hz IPS AG 250 nit Display, Win 11 + Office 2024, Black, 1.63Kg</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
       <c r="D148" t="n">
-        <v>45490</v>
+        <v>59490</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -3547,7 +3547,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-17</t>
         </is>
       </c>
     </row>
@@ -3564,11 +3564,11 @@
       </c>
       <c r="C150" t="inlineStr"/>
       <c r="D150" t="n">
-        <v>45490</v>
+        <v>44990</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
@@ -3585,11 +3585,11 @@
       </c>
       <c r="C151" t="inlineStr"/>
       <c r="D151" t="n">
-        <v>46490</v>
+        <v>44990</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
@@ -3606,620 +3606,620 @@
       </c>
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="n">
-        <v>46990</v>
+        <v>45490</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>dell_15_(previously_inspiron)_laptop,</t>
+          <t>Dell 15 (Previously Inspiron) Laptop,</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 8GB, 512GB, Intel UHD Graphics, 15.6" FHD IPS 250nit Display, 12m Mcafee, Win 11 + MSO'24, Platinum Silver, 1.63kg</t>
+          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 8GB DDR4, 512 SSD, 15.6" FHD 120Hz IPS 250 nit Display, Win 11 + Office H&amp;S 2024, Carbon Black, Thin &amp; Light 1.63Kg</t>
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
       <c r="D153" t="n">
-        <v>47499</v>
+        <v>45490</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>dell_15_(previously_inspiron)_laptop,</t>
+          <t>Dell 15 (Previously Inspiron) Laptop,</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 8GB, 512GB, Intel UHD Graphics, 15.6" FHD IPS 250nit Display, 12m Mcafee, Win 11 + MSO'24, Platinum Silver, 1.63kg</t>
+          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 8GB DDR4, 512 SSD, 15.6" FHD 120Hz IPS 250 nit Display, Win 11 + Office H&amp;S 2024, Carbon Black, Thin &amp; Light 1.63Kg</t>
         </is>
       </c>
       <c r="C154" t="inlineStr"/>
       <c r="D154" t="n">
-        <v>47499</v>
+        <v>45490</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron), 13th</t>
+          <t>Dell 15 (Previously Inspiron) Laptop,</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron), 13th Gen Intel Core i5-1334U (16GB RAM, 1TB SSD) FHD, Anti-Glare 15.6"/39.62cm, Windows 11 MSO'24, Silver, 1.62kg, 12 Month McAfee, Thin &amp; Light, Backlit Keyboard Laptop</t>
+          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 8GB DDR4, 512 SSD, 15.6" FHD 120Hz IPS 250 nit Display, Win 11 + Office H&amp;S 2024, Carbon Black, Thin &amp; Light 1.63Kg</t>
         </is>
       </c>
       <c r="C155" t="inlineStr"/>
       <c r="D155" t="n">
-        <v>63990</v>
+        <v>46490</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-06-12</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>dell_15_(previously_inspiron),_amd</t>
+          <t>Dell 15 (Previously Inspiron) Laptop,</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron), AMD Ryzen 5-7530U, 16GB RAM, 512GB SSD, FHD IPS, 15.6"/39.62cm, Win 11, MSO 2024, Platinum Silver, 1.67kg,Standard Keyboard, 12 Month McAfee, Thin &amp; Light, Laptop</t>
+          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 8GB DDR4, 512 SSD, 15.6" FHD 120Hz IPS 250 nit Display, Win 11 + Office H&amp;S 2024, Carbon Black, Thin &amp; Light 1.63Kg</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
       <c r="D156" t="n">
-        <v>56086</v>
+        <v>46990</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Dell 15 AI Powered Laptop,</t>
+          <t>dell_15_(previously_inspiron)_laptop,</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Dell 15 AI Powered Laptop, Intel Core Ultra 5 225H, 8GB DDR5 RAM, 512GB SSD, 15.6" FHD Anti-Glare Display, Intel Arc Graphics, Standard Keyboard, Dedicated Copilot Key, Black, Win11 Home + MSO H&amp;S'24</t>
+          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 8GB, 512GB, Intel UHD Graphics, 15.6" FHD IPS 250nit Display, 12m Mcafee, Win 11 + MSO'24, Platinum Silver, 1.63kg</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
       <c r="D157" t="n">
-        <v>68990</v>
+        <v>47499</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>dell_15_ai_powered_laptop,</t>
+          <t>dell_15_(previously_inspiron)_laptop,</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Dell 15 Ai Powered Laptop, Intel Core Ultra 7 255H, 16GB DDR5 RAM, 512GB SSD, 15.6" FHD Anti-Glare Display, Intel Arc Graphics, Backlit Keyboard, Dedicated Copilot Key, Silver, Win11 Home + MSO H&amp;S'24</t>
+          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 8GB, 512GB, Intel UHD Graphics, 15.6" FHD IPS 250nit Display, 12m Mcafee, Win 11 + MSO'24, Platinum Silver, 1.63kg</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
       <c r="D158" t="n">
-        <v>103990</v>
+        <v>47499</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Dell 15 Smart Choice (Previously</t>
+          <t>dell_15_(previously_inspiron)_laptop,</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Dell 15 Smart Choice (Previously Inspiron), 13th Gen Intel Core i5-1334U (16GB RAM, 1TB SSD) FHD, 15.6"/39.62cm, Windows 11 MSO'24, Silver, 1.62kg, 12 Month McAfee, Backlit KB, Thin &amp; Light Laptop</t>
+          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 8GB, 512GB, Intel UHD Graphics, 15.6" FHD IPS 250nit Display, 12m Mcafee, Win 11 + MSO'24, Platinum Silver, 1.63kg</t>
         </is>
       </c>
       <c r="C159" t="inlineStr"/>
       <c r="D159" t="n">
-        <v>66990</v>
+        <v>55700</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-08-04</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Dell 15 Smart Choice (Previously</t>
+          <t>Dell 15 (Previously Inspiron), 13th</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Dell 15 Smart Choice (Previously Inspiron), 13th Gen Intel Core i5-1334U (16GB RAM, 1TB SSD) FHD, 15.6"/39.62cm, Windows 11 MSO'24, Silver, 1.62kg, 12 Month McAfee, Backlit KB, Thin &amp; Light Laptop</t>
+          <t>Dell 15 (Previously Inspiron), 13th Gen Intel Core i5-1334U (16GB RAM, 1TB SSD) FHD, Anti-Glare 15.6"/39.62cm, Windows 11 MSO'24, Silver, 1.62kg, 12 Month McAfee, Thin &amp; Light, Backlit Keyboard Laptop</t>
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
       <c r="D160" t="n">
-        <v>67990</v>
+        <v>63990</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-17</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Dell 15 Smart Choice (Previously</t>
+          <t>dell_15_(previously_inspiron),_amd</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Dell 15 Smart Choice (Previously Inspiron), 13th Gen Intel Core i5-1334U (16GB RAM, 1TB SSD) FHD, 15.6"/39.62cm, Windows 11 MSO'24, Silver, 1.62kg, 12 Month McAfee, Backlit KB, Thin &amp; Light Laptop</t>
+          <t>Dell 15 (Previously Inspiron), AMD Ryzen 5-7530U, 16GB RAM, 512GB SSD, FHD IPS, 15.6"/39.62cm, Win 11, MSO 2024, Platinum Silver, 1.67kg,Standard Keyboard, 12 Month McAfee, Thin &amp; Light, Laptop</t>
         </is>
       </c>
       <c r="C161" t="inlineStr"/>
       <c r="D161" t="n">
-        <v>67990</v>
+        <v>56086</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Dell 15 Smart Choice (Previously</t>
+          <t>Dell 15 AI Powered Laptop,</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Dell 15 Smart Choice (Previously Inspiron), 13th Gen Intel Core i5-1334U (16GB RAM, 1TB SSD) FHD, 15.6"/39.62cm, Windows 11 MSO'24, Silver, 1.62kg, 12 Month McAfee, Backlit KB, Thin &amp; Light Laptop</t>
+          <t>Dell 15 AI Powered Laptop, Intel Core Ultra 5 225H, 8GB DDR5 RAM, 512GB SSD, 15.6" FHD Anti-Glare Display, Intel Arc Graphics, Standard Keyboard, Dedicated Copilot Key, Black, Win11 Home + MSO H&amp;S'24</t>
         </is>
       </c>
       <c r="C162" t="inlineStr"/>
       <c r="D162" t="n">
-        <v>69990</v>
+        <v>68990</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-15</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Dell 15 Smart Choice (Previously</t>
+          <t>dell_15_ai_powered_laptop,</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Dell 15 Smart Choice (Previously Inspiron), 13th Gen Intel Core i5-1334U (16GB RAM, 1TB SSD) FHD, 15.6"/39.62cm, Windows 11 MSO'24, Silver, 1.62kg, 12 Month McAfee, Backlit KB, Thin &amp; Light Laptop</t>
+          <t>Dell 15 Ai Powered Laptop, Intel Core Ultra 7 255H, 16GB DDR5 RAM, 512GB SSD, 15.6" FHD Anti-Glare Display, Intel Arc Graphics, Backlit Keyboard, Dedicated Copilot Key, Silver, Win11 Home + MSO H&amp;S'24</t>
         </is>
       </c>
       <c r="C163" t="inlineStr"/>
       <c r="D163" t="n">
-        <v>67990</v>
+        <v>103990</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>dell_15_smartchoice_(previously_inspiron),</t>
+          <t>Dell 15 Smart Choice (Previously</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Dell 15 SmartChoice (Previously Inspiron), Intel 13th Gen Core i5-1334U, 16GB, 1TB SSD, FHD,15.6"/39.62cm, Win 11, MSO'24, Silver, 1.62kg, [Dell 15], 12 Month McAfee, Backlit KB, Thin &amp; Light Laptop</t>
+          <t>Dell 15 Smart Choice (Previously Inspiron), 13th Gen Intel Core i5-1334U (16GB RAM, 1TB SSD) FHD, 15.6"/39.62cm, Windows 11 MSO'24, Silver, 1.62kg, 12 Month McAfee, Backlit KB, Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C164" t="inlineStr"/>
       <c r="D164" t="n">
-        <v>68990</v>
+        <v>66990</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-05-28</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>dell_15_smartchoice_(previously_inspiron),</t>
+          <t>Dell 15 Smart Choice (Previously</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Dell 15 SmartChoice (Previously Inspiron), Intel 13th Gen Core i5-1334U, 16GB, 1TB SSD, FHD,15.6"/39.62cm, Win 11, MSO'24, Silver, 1.62kg, [Dell 15], 12 Month McAfee, Backlit KB, Thin &amp; Light Laptop</t>
+          <t>Dell 15 Smart Choice (Previously Inspiron), 13th Gen Intel Core i5-1334U (16GB RAM, 1TB SSD) FHD, 15.6"/39.62cm, Windows 11 MSO'24, Silver, 1.62kg, 12 Month McAfee, Backlit KB, Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C165" t="inlineStr"/>
       <c r="D165" t="n">
-        <v>68990</v>
+        <v>67990</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-05-31</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Dell 15, 13th Gen Intel</t>
+          <t>Dell 15 Smart Choice (Previously</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Dell 15, 13th Gen Intel Core i5-1334U (16GB DDR4, 512GB SSD) Anti-Glare FHD 15.6"/39.62cm, Windows 11, Microsoft Office Home 2024, Grey, 1.66kg, [Vostro 3530], 12 Month McAfee, Thin &amp; Light Laptop</t>
+          <t>Dell 15 Smart Choice (Previously Inspiron), 13th Gen Intel Core i5-1334U (16GB RAM, 1TB SSD) FHD, 15.6"/39.62cm, Windows 11 MSO'24, Silver, 1.62kg, 12 Month McAfee, Backlit KB, Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C166" t="inlineStr"/>
       <c r="D166" t="n">
-        <v>61490</v>
+        <v>67990</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Dell 15, 13th Gen Intel</t>
+          <t>Dell 15 Smart Choice (Previously</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Dell 15, 13th Gen Intel Core i5-1334U (16GB DDR4, 512GB SSD) Anti-Glare FHD 15.6"/39.62cm, Windows 11, Microsoft Office Home 2024, Grey, 1.66kg, [Vostro 3530], 12 Month McAfee, Thin &amp; Light Laptop</t>
+          <t>Dell 15 Smart Choice (Previously Inspiron), 13th Gen Intel Core i5-1334U (16GB RAM, 1TB SSD) FHD, 15.6"/39.62cm, Windows 11 MSO'24, Silver, 1.62kg, 12 Month McAfee, Backlit KB, Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C167" t="inlineStr"/>
       <c r="D167" t="n">
-        <v>63490</v>
+        <v>69990</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-02</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Dell 15, AMD Ryzen 7-7730U,</t>
+          <t>Dell 15 Smart Choice (Previously</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Dell 15, AMD Ryzen 7-7730U, 16GB DDR4, 512GB SSD, FHD, 15.6"/39.6cm, Windows 11, Microsoft Office Home 2024, Platinum Silver, 1.63Kg, [Dell 15], 120Hz 250nits, AMD Radeon Graphics,Thin &amp; Light, Laptop</t>
+          <t>Dell 15 Smart Choice (Previously Inspiron), 13th Gen Intel Core i5-1334U (16GB RAM, 1TB SSD) FHD, 15.6"/39.62cm, Windows 11 MSO'24, Silver, 1.62kg, 12 Month McAfee, Backlit KB, Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C168" t="inlineStr"/>
       <c r="D168" t="n">
-        <v>59957</v>
+        <v>67990</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-06-14</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Dell 15, AMD Ryzen 7-7730U,</t>
+          <t>dell_15_smartchoice_(previously_inspiron),</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Dell 15, AMD Ryzen 7-7730U, 16GB DDR4, 512GB SSD, FHD, 15.6"/39.6cm, Windows 11, Microsoft Office Home 2024, Platinum Silver, 1.63Kg, [Dell 15], 120Hz 250nits, AMD Radeon Graphics,Thin &amp; Light, Laptop</t>
+          <t>Dell 15 SmartChoice (Previously Inspiron), Intel 13th Gen Core i5-1334U, 16GB, 1TB SSD, FHD,15.6"/39.62cm, Win 11, MSO'24, Silver, 1.62kg, [Dell 15], 12 Month McAfee, Backlit KB, Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C169" t="inlineStr"/>
       <c r="D169" t="n">
-        <v>58490</v>
+        <v>68990</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>dell_15,_intel_core_13th</t>
+          <t>dell_15_smartchoice_(previously_inspiron),</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Dell 15, Intel Core 13th Gen i5-1334U, FHD, 15.6"/39.62cm, Windows 11, MSO'24, Grey, 1.66kg, Vostro 3530, (16GB DDR4, 512GB SSD) Anti-Glare FHD 15.6"/39.62cm, 12 Month McAfee, Thin &amp; Light Laptop</t>
+          <t>Dell 15 SmartChoice (Previously Inspiron), Intel 13th Gen Core i5-1334U, 16GB, 1TB SSD, FHD,15.6"/39.62cm, Win 11, MSO'24, Silver, 1.62kg, [Dell 15], 12 Month McAfee, Backlit KB, Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C170" t="inlineStr"/>
       <c r="D170" t="n">
-        <v>65490</v>
+        <v>68990</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Dell 15, Intel Core 3</t>
+          <t>Dell 15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Dell 15, Intel Core 3 14th Gen-100U, 16GB DDR4, 512GB SSD, FHD IPS, 15.6"/39.62cm, Windows 11, Microsoft Office Home 2024, Carbon Black, 1.63Kg, Thin &amp; Light, Laptop Model NO - Dell 15 DCU5250</t>
+          <t>Dell 15, 13th Gen Intel Core i5-1334U (16GB DDR4, 512GB SSD) Anti-Glare FHD 15.6"/39.62cm, Windows 11, Microsoft Office Home 2024, Grey, 1.66kg, [Vostro 3530], 12 Month McAfee, Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C171" t="inlineStr"/>
       <c r="D171" t="n">
-        <v>51868</v>
+        <v>61490</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Dell 15, Intel Core i3/Core</t>
+          <t>Dell 15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Dell 15, Intel Core i3/Core 3 14th Gen-100U, 16GB DDR4, 512GB SSD, FHD IPS, 15.6"/39.62cm, Windows 11, Microsoft Office Home 2024, Carbon Black, 1.63Kg, Thin &amp; Light, Laptop Model NO - Dell 15 DCU5250</t>
+          <t>Dell 15, 13th Gen Intel Core i5-1334U (16GB DDR4, 512GB SSD) Anti-Glare FHD 15.6"/39.62cm, Windows 11, Microsoft Office Home 2024, Grey, 1.66kg, [Vostro 3530], 12 Month McAfee, Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C172" t="inlineStr"/>
       <c r="D172" t="n">
-        <v>48990</v>
+        <v>63490</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Dell 15, R5-7520U Processor, 8GB</t>
+          <t>Dell 15, AMD Ryzen 7-7730U,</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Dell 15, R5-7520U Processor, 8GB LPDDR5 RAM, 512GB SSD, FHD 15.6"/39.62 cm Display, Windows 11, MSO'24, Carbon Black, 1.63kg, Standard Keyboard, 15 Month McAfee, Thin &amp; Light Laptop</t>
+          <t>Dell 15, AMD Ryzen 7-7730U, 16GB DDR4, 512GB SSD, FHD, 15.6"/39.6cm, Windows 11, Microsoft Office Home 2024, Platinum Silver, 1.63Kg, [Dell 15], 120Hz 250nits, AMD Radeon Graphics,Thin &amp; Light, Laptop</t>
         </is>
       </c>
       <c r="C173" t="inlineStr"/>
       <c r="D173" t="n">
-        <v>53990</v>
+        <v>59957</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>dell_g_series,_intel_core</t>
+          <t>Dell 15, AMD Ryzen 7-7730U,</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Dell G Series, Intel Core i5-13450HX, 13th Gen, NVIDIA RTX 3050-6GB, 16GB, 512GB SSD, FHD, 15.6"/39.62cm, Windows 11, MSO'24, Dark Shadow Gray, 2.65KG, [G15-5530], Backlit Keyboard, Gaming Laptop</t>
+          <t>Dell 15, AMD Ryzen 7-7730U, 16GB DDR4, 512GB SSD, FHD, 15.6"/39.6cm, Windows 11, Microsoft Office Home 2024, Platinum Silver, 1.63Kg, [Dell 15], 120Hz 250nits, AMD Radeon Graphics,Thin &amp; Light, Laptop</t>
         </is>
       </c>
       <c r="C174" t="inlineStr"/>
       <c r="D174" t="n">
-        <v>89990</v>
+        <v>58490</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-17</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Dell G15, 13th Gen Intel</t>
+          <t>dell_15,_intel_core_13th</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Dell G15, 13th Gen Intel Core i5-13450HX Processor, NVIDIA RTX 3050-6GB, (16GB RAM 1TB SSD) FHD 15.6"/39.62 cm, Orange Backlit Keyboard, Win 11, MS Office'24, Dark Shadow Grey, 2.65Kg Gaming Laptop</t>
+          <t>Dell 15, Intel Core 13th Gen i5-1334U, FHD, 15.6"/39.62cm, Windows 11, MSO'24, Grey, 1.66kg, Vostro 3530, (16GB DDR4, 512GB SSD) Anti-Glare FHD 15.6"/39.62cm, 12 Month McAfee, Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C175" t="inlineStr"/>
       <c r="D175" t="n">
-        <v>79590</v>
+        <v>65490</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Dell G15, 13th Gen Intel</t>
+          <t>Dell 15, Intel Core 3</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Dell G15, 13th Gen Intel Core i5-13450HX Processor, NVIDIA RTX 3050-6GB, (16GB RAM 1TB SSD) FHD 15.6"/39.62 cm, Orange Backlit Keyboard, Win 11, MS Office'24, Dark Shadow Grey, 2.65Kg Gaming Laptop</t>
+          <t>Dell 15, Intel Core 3 14th Gen-100U, 16GB DDR4, 512GB SSD, FHD IPS, 15.6"/39.62cm, Windows 11, Microsoft Office Home 2024, Carbon Black, 1.63Kg, Thin &amp; Light, Laptop Model NO - Dell 15 DCU5250</t>
         </is>
       </c>
       <c r="C176" t="inlineStr"/>
       <c r="D176" t="n">
-        <v>79990</v>
+        <v>51868</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>EBook 11.6" HD Laptop |</t>
+          <t>Dell 15, Intel Core i3/Core</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>EBook 11.6" HD Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB DDR4 | 128GB eMMC + M.2 SSD Expandable Slot | Win 11 Home |31Wh Battery | UHD Graphics 600 | Black</t>
+          <t>Dell 15, Intel Core i3/Core 3 14th Gen-100U, 16GB DDR4, 512GB SSD, FHD IPS, 15.6"/39.62cm, Windows 11, Microsoft Office Home 2024, Carbon Black, 1.63Kg, Thin &amp; Light, Laptop Model NO - Dell 15 DCU5250</t>
         </is>
       </c>
       <c r="C177" t="inlineStr"/>
       <c r="D177" t="n">
-        <v>11990</v>
+        <v>48990</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>EBook 11.6" HD Laptop |</t>
+          <t>Dell 15, R5-7520U Processor, 8GB</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>EBook 11.6" HD Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB DDR4 | 128GB eMMC + M.2 SSD Expandable Slot | Win 11 Home |31Wh Battery | UHD Graphics 600 | Black</t>
+          <t>Dell 15, R5-7520U Processor, 8GB LPDDR5 RAM, 512GB SSD, FHD 15.6"/39.62 cm Display, Windows 11, MSO'24, Carbon Black, 1.63kg, Standard Keyboard, 15 Month McAfee, Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C178" t="inlineStr"/>
       <c r="D178" t="n">
-        <v>11990</v>
+        <v>53990</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-16</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>EBook 11.6" HD Laptop |</t>
+          <t>dell_g_series,_intel_core</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>EBook 11.6" HD Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB DDR4 | 128GB eMMC + M.2 SSD Expandable Slot | Win 11 Home |31Wh Battery | UHD Graphics 600 | Black</t>
+          <t>Dell G Series, Intel Core i5-13450HX, 13th Gen, NVIDIA RTX 3050-6GB, 16GB, 512GB SSD, FHD, 15.6"/39.62cm, Windows 11, MSO'24, Dark Shadow Gray, 2.65KG, [G15-5530], Backlit Keyboard, Gaming Laptop</t>
         </is>
       </c>
       <c r="C179" t="inlineStr"/>
       <c r="D179" t="n">
-        <v>11990</v>
+        <v>89990</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>EBook 11.6" HD Laptop |</t>
+          <t>Dell G15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>EBook 11.6" HD Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB DDR4 | 128GB eMMC + M.2 SSD Expandable Slot | Win 11 Home |31Wh Battery | UHD Graphics 600 | Black</t>
+          <t>Dell G15, 13th Gen Intel Core i5-13450HX Processor, NVIDIA RTX 3050-6GB, (16GB RAM 1TB SSD) FHD 15.6"/39.62 cm, Orange Backlit Keyboard, Win 11, MS Office'24, Dark Shadow Grey, 2.65Kg Gaming Laptop</t>
         </is>
       </c>
       <c r="C180" t="inlineStr"/>
       <c r="D180" t="n">
-        <v>11990</v>
+        <v>79590</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>EBook 11.6" HD Laptop |</t>
+          <t>Dell G15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>EBook 11.6" HD Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB DDR4 | 128GB eMMC + M.2 SSD Expandable Slot | Win 11 Home |31Wh Battery | UHD Graphics 600 | Black</t>
+          <t>Dell G15, 13th Gen Intel Core i5-13450HX Processor, NVIDIA RTX 3050-6GB, (16GB RAM 1TB SSD) FHD 15.6"/39.62 cm, Orange Backlit Keyboard, Win 11, MS Office'24, Dark Shadow Grey, 2.65Kg Gaming Laptop</t>
         </is>
       </c>
       <c r="C181" t="inlineStr"/>
       <c r="D181" t="n">
-        <v>11990</v>
+        <v>79990</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-08</t>
         </is>
       </c>
     </row>
@@ -4240,7 +4240,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-04-16</t>
         </is>
       </c>
     </row>
@@ -4261,7 +4261,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -4282,7 +4282,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -4303,7 +4303,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-19</t>
         </is>
       </c>
     </row>
@@ -4324,7 +4324,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-20</t>
         </is>
       </c>
     </row>
@@ -4341,11 +4341,11 @@
       </c>
       <c r="C187" t="inlineStr"/>
       <c r="D187" t="n">
-        <v>16990</v>
+        <v>11990</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-21</t>
         </is>
       </c>
     </row>
@@ -4362,18 +4362,18 @@
       </c>
       <c r="C188" t="inlineStr"/>
       <c r="D188" t="n">
-        <v>16990</v>
+        <v>11990</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-05-31</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>ebook_11.6"_hd_laptop_|</t>
+          <t>EBook 11.6" HD Laptop |</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -4383,18 +4383,18 @@
       </c>
       <c r="C189" t="inlineStr"/>
       <c r="D189" t="n">
-        <v>10603</v>
+        <v>11990</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>ebook_11.6"_hd_laptop_|</t>
+          <t>EBook 11.6" HD Laptop |</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -4404,18 +4404,18 @@
       </c>
       <c r="C190" t="inlineStr"/>
       <c r="D190" t="n">
-        <v>10990</v>
+        <v>11990</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-06-02</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>ebook_11.6"_hd_laptop_|</t>
+          <t>EBook 11.6" HD Laptop |</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -4425,18 +4425,18 @@
       </c>
       <c r="C191" t="inlineStr"/>
       <c r="D191" t="n">
-        <v>10990</v>
+        <v>11990</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>ebook_11.6"_hd_laptop_|</t>
+          <t>EBook 11.6" HD Laptop |</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -4446,217 +4446,217 @@
       </c>
       <c r="C192" t="inlineStr"/>
       <c r="D192" t="n">
-        <v>10990</v>
+        <v>16990</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>hp_14_smartchoice,_intel_core</t>
+          <t>EBook 11.6" HD Laptop |</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>HP 14 Smartchoice, Intel Core Ultra 5 125H 12 TOPS, 24GB DDR5 (Upgradeable) 1TB SSD, Anti-Glare, FHD, 14''/35.6cm,Win11, M365*Office24, Silver, 1.4kg, ep1180tu, FHD Camera w/Shutter, Backlit AI Laptop</t>
+          <t>EBook 11.6" HD Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB DDR4 | 128GB eMMC + M.2 SSD Expandable Slot | Win 11 Home |31Wh Battery | UHD Graphics 600 | Black</t>
         </is>
       </c>
       <c r="C193" t="inlineStr"/>
       <c r="D193" t="n">
-        <v>77990</v>
+        <v>16990</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>hp_14_smartchoice,_intel_core</t>
+          <t>ebook_11.6"_hd_laptop_|</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>HP 14 Smartchoice, Intel Core Ultra 5 125H 12 TOPS, 24GB DDR5 (Upgradeable) 1TB SSD, Anti-Glare, FHD, 14''/35.6cm,Win11, M365*Office24, Silver, 1.4kg, ep1180tu, FHD Camera w/Shutter, Backlit AI Laptop</t>
+          <t>EBook 11.6" HD Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB DDR4 | 128GB eMMC + M.2 SSD Expandable Slot | Win 11 Home |31Wh Battery | UHD Graphics 600 | Black</t>
         </is>
       </c>
       <c r="C194" t="inlineStr"/>
       <c r="D194" t="n">
-        <v>77990</v>
+        <v>10603</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>hp_14_smartchoice,_intel_core</t>
+          <t>ebook_11.6"_hd_laptop_|</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>HP 14 Smartchoice, Intel Core Ultra 5 125H 12 TOPS, 24GB DDR5 (Upgradeable) 1TB SSD, Anti-Glare, FHD, 14''/35.6cm,Win11, M365*Office24, Silver, 1.4kg, ep1180tu, FHD Camera w/Shutter, Backlit AI Laptop</t>
+          <t>EBook 11.6" HD Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB DDR4 | 128GB eMMC + M.2 SSD Expandable Slot | Win 11 Home |31Wh Battery | UHD Graphics 600 | Black</t>
         </is>
       </c>
       <c r="C195" t="inlineStr"/>
       <c r="D195" t="n">
-        <v>79990</v>
+        <v>10990</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>hp_14,_amd_ryzen_7</t>
+          <t>ebook_11.6"_hd_laptop_|</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>HP 14, AMD Ryzen 7 7730U (16GB DDR4, 512GB SSD) FHD, Anti-Glare, Micro-Edge, 14''/35.6cm, Win11, M365 Basic(1yr), Office Home24, Silver,1.4kg, EM0104AU, FHD Camera w/Privacy Shutter, Backlit Laptop</t>
+          <t>EBook 11.6" HD Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB DDR4 | 128GB eMMC + M.2 SSD Expandable Slot | Win 11 Home |31Wh Battery | UHD Graphics 600 | Black</t>
         </is>
       </c>
       <c r="C196" t="inlineStr"/>
       <c r="D196" t="n">
-        <v>59990</v>
+        <v>10990</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>hp_14,_amd_ryzen_7</t>
+          <t>ebook_11.6"_hd_laptop_|</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>HP 14, AMD Ryzen 7 7730U (16GB DDR4, 512GB SSD) FHD, Anti-Glare, Micro-Edge, 14''/35.6cm, Win11, M365 Basic(1yr), Office Home24, Silver,1.4kg, EM0104AU, FHD Camera w/Privacy Shutter, Backlit Laptop</t>
+          <t>EBook 11.6" HD Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB DDR4 | 128GB eMMC + M.2 SSD Expandable Slot | Win 11 Home |31Wh Battery | UHD Graphics 600 | Black</t>
         </is>
       </c>
       <c r="C197" t="inlineStr"/>
       <c r="D197" t="n">
-        <v>64990</v>
+        <v>10990</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>HP 14s Intel Celeron Dual</t>
+          <t>ebook_11.6"_hd_laptop_|</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>HP 14s Intel Celeron Dual Core N4500 Laptop (8GB/512GB SSD/Win 11) 14.0" HD Display, MSO 24, Black, 1.46kg, DQ3149TU Thin and Light Business Laptop</t>
+          <t>EBook 11.6" HD Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB DDR4 | 128GB eMMC + M.2 SSD Expandable Slot | Win 11 Home |31Wh Battery | UHD Graphics 600 | Black</t>
         </is>
       </c>
       <c r="C198" t="inlineStr"/>
       <c r="D198" t="n">
-        <v>40400</v>
+        <v>10990</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-08-04</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>hp_15_(2025),_amd_athlon</t>
+          <t>hp_14_smartchoice,_intel_core</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>HP 15 (2025), AMD Athlon 7120U Dual Core - (8 GB/256 GB SSD/AMD Radeon Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" HD Display/Black/1.5 kg/MS Office 2021</t>
+          <t>HP 14 Smartchoice, Intel Core Ultra 5 125H 12 TOPS, 24GB DDR5 (Upgradeable) 1TB SSD, Anti-Glare, FHD, 14''/35.6cm,Win11, M365*Office24, Silver, 1.4kg, ep1180tu, FHD Camera w/Shutter, Backlit AI Laptop</t>
         </is>
       </c>
       <c r="C199" t="inlineStr"/>
       <c r="D199" t="n">
-        <v>41999</v>
+        <v>77990</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>HP 15 (2026), AMD Athlon</t>
+          <t>hp_14_smartchoice,_intel_core</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>HP 15 (2026), AMD Athlon Dual Core 7120U - (8 GB DDR5/512 GB SSD/AMD Radeon 610M Graphics/DOS) Thin and Light Business Laptop/15.6" HD Display/Turbo Silver/Copilot Key/1.5kg</t>
+          <t>HP 14 Smartchoice, Intel Core Ultra 5 125H 12 TOPS, 24GB DDR5 (Upgradeable) 1TB SSD, Anti-Glare, FHD, 14''/35.6cm,Win11, M365*Office24, Silver, 1.4kg, ep1180tu, FHD Camera w/Shutter, Backlit AI Laptop</t>
         </is>
       </c>
       <c r="C200" t="inlineStr"/>
       <c r="D200" t="n">
-        <v>39999</v>
+        <v>77990</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>HP 15 (2026), AMD Athlon</t>
+          <t>hp_14_smartchoice,_intel_core</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>HP 15 (2026), AMD Athlon Dual Core 7120U - (8 GB DDR5/512 GB SSD/AMD Radeon 610M Graphics/Windows 11 Pro) Thin and Light Business Laptop/15.6" HD Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
+          <t>HP 14 Smartchoice, Intel Core Ultra 5 125H 12 TOPS, 24GB DDR5 (Upgradeable) 1TB SSD, Anti-Glare, FHD, 14''/35.6cm,Win11, M365*Office24, Silver, 1.4kg, ep1180tu, FHD Camera w/Shutter, Backlit AI Laptop</t>
         </is>
       </c>
       <c r="C201" t="inlineStr"/>
       <c r="D201" t="n">
-        <v>39660</v>
+        <v>79990</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>hp_15_(2026),_amd_athlon</t>
+          <t>hp_14,_amd_ryzen_7</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>HP 15 (2026), AMD Athlon Dual Core 7120U - (8 GB DDR5/512 GB SSD/AMD Radeon 610M Graphics/Windows 11 Pro) Thin and Light Business Laptop/15.6" HD Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
+          <t>HP 14, AMD Ryzen 7 7730U (16GB DDR4, 512GB SSD) FHD, Anti-Glare, Micro-Edge, 14''/35.6cm, Win11, M365 Basic(1yr), Office Home24, Silver,1.4kg, EM0104AU, FHD Camera w/Privacy Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C202" t="inlineStr"/>
       <c r="D202" t="n">
-        <v>41999</v>
+        <v>59990</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
@@ -4667,59 +4667,59 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>hp_15_(2026),_amd_athlon</t>
+          <t>hp_14,_amd_ryzen_7</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>HP 15 (2026), AMD Athlon Dual Core 7120U - (8 GB DDR5/512 GB SSD/AMD Radeon 610M Graphics/Windows 11 Pro) Thin and Light Business Laptop/15.6" HD Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
+          <t>HP 14, AMD Ryzen 7 7730U (16GB DDR4, 512GB SSD) FHD, Anti-Glare, Micro-Edge, 14''/35.6cm, Win11, M365 Basic(1yr), Office Home24, Silver,1.4kg, EM0104AU, FHD Camera w/Privacy Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C203" t="inlineStr"/>
       <c r="D203" t="n">
-        <v>42840</v>
+        <v>64990</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>hp_15_(2026),_amd_athlon</t>
+          <t>HP 14s Intel Celeron Dual</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>HP 15 (2026), AMD Athlon Dual Core 7120U - (8 GB DDR5/512 GB SSD/AMD Radeon 610M Graphics/Windows 11 Pro) Thin and Light Business Laptop/15.6" HD Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
+          <t>HP 14s Intel Celeron Dual Core N4500 Laptop (8GB/512GB SSD/Win 11) 14.0" HD Display, MSO 24, Black, 1.46kg, DQ3149TU Thin and Light Business Laptop</t>
         </is>
       </c>
       <c r="C204" t="inlineStr"/>
       <c r="D204" t="n">
-        <v>42840</v>
+        <v>40400</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-04-16</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>hp_15_(2026),_amd_athlon</t>
+          <t>hp_15_(2025),_amd_athlon</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>HP 15 (2026), AMD Athlon Dual Core 7120U - (8 GB DDR5/512 GB SSD/AMD Radeon 610M Graphics/Windows 11 Pro) Thin and Light Business Laptop/15.6" HD Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
+          <t>HP 15 (2025), AMD Athlon 7120U Dual Core - (8 GB/256 GB SSD/AMD Radeon Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" HD Display/Black/1.5 kg/MS Office 2021</t>
         </is>
       </c>
       <c r="C205" t="inlineStr"/>
       <c r="D205" t="n">
-        <v>42840</v>
+        <v>41999</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
@@ -4730,290 +4730,290 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>HP 15 (2026), AMD Ryzen</t>
+          <t>hp_15_(2025),_amd_athlon</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>HP 15 (2026), AMD Ryzen 3 Quad Core 7335U - (8 GB DDR5/512 GB SSD/AMD Radeon 660M Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
+          <t>HP 15 (2025), AMD Athlon 7120U Dual Core - (8 GB/256 GB SSD/AMD Radeon Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" HD Display/Black/1.5 kg/MS Office 2021</t>
         </is>
       </c>
       <c r="C206" t="inlineStr"/>
       <c r="D206" t="n">
-        <v>42780</v>
+        <v>41999</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-08-04</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>hp_15_(i5_14th_gen),</t>
+          <t>HP 15 (2026), AMD Athlon</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>HP 15 (i5 14th Gen), Intel Core 5, 16GB RAM (Upgradeable), 512GB SSD, FHD, Anti-Glare, 15.6''/39.6cm, Win11, M365 Basic(1yr), Office24, Silver,1.59kg, fd0682tu, FHD Camera w/Shutter, Backlit Laptop</t>
+          <t>HP 15 (2026), AMD Athlon Dual Core 7120U - (8 GB DDR5/512 GB SSD/AMD Radeon 610M Graphics/DOS) Thin and Light Business Laptop/15.6" HD Display/Turbo Silver/Copilot Key/1.5kg</t>
         </is>
       </c>
       <c r="C207" t="inlineStr"/>
       <c r="D207" t="n">
-        <v>63990</v>
+        <v>39999</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-08</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>hp_15_(i5_14th_gen),</t>
+          <t>HP 15 (2026), AMD Athlon</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>HP 15 (i5 14th Gen), Intel Core 5, 16GB RAM (Upgradeable), 512GB SSD, FHD, Anti-Glare, 15.6''/39.6cm, Win11, M365 Basic(1yr), Office24, Silver,1.59kg, fd0682tu, FHD Camera w/Shutter, Backlit Laptop</t>
+          <t>HP 15 (2026), AMD Athlon Dual Core 7120U - (8 GB DDR5/512 GB SSD/AMD Radeon 610M Graphics/Windows 11 Pro) Thin and Light Business Laptop/15.6" HD Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
         </is>
       </c>
       <c r="C208" t="inlineStr"/>
       <c r="D208" t="n">
-        <v>67990</v>
+        <v>39660</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>hp_15_laptop_|_amd</t>
+          <t>hp_15_(2026),_amd_athlon</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>HP 15 Laptop | AMD Ryzen 7 5825U |16GB DDR4 RAM | 512GB SSD |15.6" (39.6 cm) FHD Display |AMD Radeon Graphics| Backlit KB | FHD Camera| Win 11| MS Office 2024 + M365*(1-Yr) | Silver |1.59kg |fc0533AU</t>
+          <t>HP 15 (2026), AMD Athlon Dual Core 7120U - (8 GB DDR5/512 GB SSD/AMD Radeon 610M Graphics/Windows 11 Pro) Thin and Light Business Laptop/15.6" HD Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
         </is>
       </c>
       <c r="C209" t="inlineStr"/>
       <c r="D209" t="n">
-        <v>64990</v>
+        <v>41999</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>hp_15_laptop_|_intel</t>
+          <t>hp_15_(2026),_amd_athlon</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>HP 15 Laptop | Intel Core i5-13420H,13th Gen |16GB RAM | 512GB SSD | Win 11 |M365 Basic(1yr)* Office24|Anti-Glare, Micro-Edge, 15.6''/39.6cm|Backlit KB|FHD Camera w/Shutter|1.65kg, Silver -FR0045TU</t>
+          <t>HP 15 (2026), AMD Athlon Dual Core 7120U - (8 GB DDR5/512 GB SSD/AMD Radeon 610M Graphics/Windows 11 Pro) Thin and Light Business Laptop/15.6" HD Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
         </is>
       </c>
       <c r="C210" t="inlineStr"/>
       <c r="D210" t="n">
-        <v>68990</v>
+        <v>42840</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>hp_15_laptop,_(14th_gen</t>
+          <t>hp_15_(2026),_amd_athlon</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>HP 15 Laptop, (14th Gen Core i5) Intel Core 5-120U (24GB RAM, 512GB SSD, Win 11, M365 Basic(1yr)* Office24,15.6''/39.6cm FHD Anti-Glare Display, Backlit KB, FHD Camera, Dual Speakers, Silver, 1.59kg)</t>
+          <t>HP 15 (2026), AMD Athlon Dual Core 7120U - (8 GB DDR5/512 GB SSD/AMD Radeon 610M Graphics/Windows 11 Pro) Thin and Light Business Laptop/15.6" HD Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
         </is>
       </c>
       <c r="C211" t="inlineStr"/>
       <c r="D211" t="n">
-        <v>72800</v>
+        <v>42840</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>HP 15 Laptop, Intel (14th</t>
+          <t>hp_15_(2026),_amd_athlon</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>HP 15 Laptop, Intel (14th Gen) Core 5 120U (24GB DDR5, 512GB SSD), Micro-Edge, Anti-Glare, 15.6''/39.6cm, Win11, M365* Office24, Silver, 1.59kg, fd0262TU, FHD Camera, Backlit, Dual Speakers</t>
+          <t>HP 15 (2026), AMD Athlon Dual Core 7120U - (8 GB DDR5/512 GB SSD/AMD Radeon 610M Graphics/Windows 11 Pro) Thin and Light Business Laptop/15.6" HD Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
         </is>
       </c>
       <c r="C212" t="inlineStr"/>
       <c r="D212" t="n">
-        <v>67990</v>
+        <v>42840</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, 13th Gen</t>
+          <t>hp_15_(2026),_amd_athlon</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U (12GB DDR4, 512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver, 1.59kg, fd0573TU, FHD Camera w/Shutter Laptop</t>
+          <t>HP 15 (2026), AMD Athlon Dual Core 7120U - (8 GB DDR5/512 GB SSD/AMD Radeon 610M Graphics/Windows 11 Pro) Thin and Light Business Laptop/15.6" HD Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
         </is>
       </c>
       <c r="C213" t="inlineStr"/>
       <c r="D213" t="n">
-        <v>55990</v>
+        <v>42840</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-08-04</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, 13th Gen</t>
+          <t>HP 15 (2026), AMD Ryzen</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U(8GB DDR4,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
+          <t>HP 15 (2026), AMD Ryzen 3 Quad Core 7335U - (8 GB DDR5/512 GB SSD/AMD Radeon 660M Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
         </is>
       </c>
       <c r="C214" t="inlineStr"/>
       <c r="D214" t="n">
-        <v>51990</v>
+        <v>42780</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, 13th Gen</t>
+          <t>hp_15_(i5_14th_gen),</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U(8GB DDR4,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
+          <t>HP 15 (i5 14th Gen), Intel Core 5, 16GB RAM (Upgradeable), 512GB SSD, FHD, Anti-Glare, 15.6''/39.6cm, Win11, M365 Basic(1yr), Office24, Silver,1.59kg, fd0682tu, FHD Camera w/Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C215" t="inlineStr"/>
       <c r="D215" t="n">
-        <v>51990</v>
+        <v>63990</v>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, 13th Gen</t>
+          <t>hp_15_(i5_14th_gen),</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U(8GB DDR4,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
+          <t>HP 15 (i5 14th Gen), Intel Core 5, 16GB RAM (Upgradeable), 512GB SSD, FHD, Anti-Glare, 15.6''/39.6cm, Win11, M365 Basic(1yr), Office24, Silver,1.59kg, fd0682tu, FHD Camera w/Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C216" t="inlineStr"/>
       <c r="D216" t="n">
-        <v>51990</v>
+        <v>67990</v>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, 13th Gen</t>
+          <t>hp_15_laptop_|_amd</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U(8GB DDR4,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
+          <t>HP 15 Laptop | AMD Ryzen 7 5825U |16GB DDR4 RAM | 512GB SSD |15.6" (39.6 cm) FHD Display |AMD Radeon Graphics| Backlit KB | FHD Camera| Win 11| MS Office 2024 + M365*(1-Yr) | Silver |1.59kg |fc0533AU</t>
         </is>
       </c>
       <c r="C217" t="inlineStr"/>
       <c r="D217" t="n">
-        <v>51990</v>
+        <v>64990</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, 13th Gen</t>
+          <t>hp_15_laptop_|_intel</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U(8GB DDR4,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
+          <t>HP 15 Laptop | Intel Core i5-13420H,13th Gen |16GB RAM | 512GB SSD | Win 11 |M365 Basic(1yr)* Office24|Anti-Glare, Micro-Edge, 15.6''/39.6cm|Backlit KB|FHD Camera w/Shutter|1.65kg, Silver -FR0045TU</t>
         </is>
       </c>
       <c r="C218" t="inlineStr"/>
       <c r="D218" t="n">
-        <v>51990</v>
+        <v>68990</v>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>hp_15_smartchoice,_13th_gen</t>
+          <t>hp_15_laptop,_(14th_gen</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U(8GB DDR4,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
+          <t>HP 15 Laptop, (14th Gen Core i5) Intel Core 5-120U (24GB RAM, 512GB SSD, Win 11, M365 Basic(1yr)* Office24,15.6''/39.6cm FHD Anti-Glare Display, Backlit KB, FHD Camera, Dual Speakers, Silver, 1.59kg)</t>
         </is>
       </c>
       <c r="C219" t="inlineStr"/>
       <c r="D219" t="n">
-        <v>49990</v>
+        <v>72800</v>
       </c>
       <c r="E219" t="inlineStr">
         <is>
@@ -5024,294 +5024,294 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>hp_15_smartchoice,_13th_gen</t>
+          <t>hp_15_laptop,_(14th_gen</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U(8GB DDR4,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
+          <t>HP 15 Laptop, (14th Gen Core i5) Intel Core 5-120U (24GB RAM, 512GB SSD, Win 11, M365 Basic(1yr)* Office24,15.6''/39.6cm FHD Anti-Glare Display, Backlit KB, FHD Camera, Dual Speakers, Silver, 1.59kg)</t>
         </is>
       </c>
       <c r="C220" t="inlineStr"/>
       <c r="D220" t="n">
-        <v>49990</v>
+        <v>72900</v>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-04</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>hp_15_smartchoice,_13th_gen</t>
+          <t>HP 15 Laptop, Intel (14th</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U(8GB DDR4,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
+          <t>HP 15 Laptop, Intel (14th Gen) Core 5 120U (24GB DDR5, 512GB SSD), Micro-Edge, Anti-Glare, 15.6''/39.6cm, Win11, M365* Office24, Silver, 1.59kg, fd0262TU, FHD Camera, Backlit, Dual Speakers</t>
         </is>
       </c>
       <c r="C221" t="inlineStr"/>
       <c r="D221" t="n">
-        <v>49990</v>
+        <v>67990</v>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>hp_15_smartchoice,_13th_gen</t>
+          <t>HP 15 Smartchoice, 13th Gen</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U(8GB DDR4,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
+          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U (12GB DDR4, 512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver, 1.59kg, fd0573TU, FHD Camera w/Shutter Laptop</t>
         </is>
       </c>
       <c r="C222" t="inlineStr"/>
       <c r="D222" t="n">
-        <v>49990</v>
+        <v>55990</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-06-12</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>hp_15_smartchoice,_intel_core</t>
+          <t>HP 15 Smartchoice, 13th Gen</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, Intel Core Ultra 5 125H, 12 Tops (16GB DDR5, 512GB SSD) FHD, IPS, 15.6''/39.6cm, Win11, M365(1yr)* Office24, Silver, 1.65kg, fd1254TU, FHD Camera w/Shutter, AI Powered Laptop</t>
+          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U(8GB DDR4,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C223" t="inlineStr"/>
       <c r="D223" t="n">
-        <v>69990</v>
+        <v>51990</v>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>hp_15_smartchoice,_intel_core</t>
+          <t>HP 15 Smartchoice, 13th Gen</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, Intel Core Ultra 5 125H, 12 Tops (16GB DDR5, 512GB SSD) FHD, IPS, 15.6''/39.6cm, Win11, M365(1yr)* Office24, Silver, 1.65kg, fd1254TU, FHD Camera w/Shutter, AI Powered Laptop</t>
+          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U(8GB DDR4,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C224" t="inlineStr"/>
       <c r="D224" t="n">
-        <v>69990</v>
+        <v>51990</v>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel</t>
+          <t>HP 15 Smartchoice, 13th Gen</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U (8GB DDR4, 512GB SSD), FHD, Micro -Edge, Anti-Glare, 15.6''/39.6cm, Win11, M365* Office24, Silver, 1.59kg, fd0624tu, FHD Camera, UHD Graphics Laptop</t>
+          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U(8GB DDR4,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C225" t="inlineStr"/>
       <c r="D225" t="n">
-        <v>47490</v>
+        <v>51990</v>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>hp_15,_13th_gen_intel</t>
+          <t>HP 15 Smartchoice, 13th Gen</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U (8GB DDR4, 512GB SSD), FHD, Micro -Edge, Anti-Glare, 15.6''/39.6cm, Win11, M365* Office24, Silver, 1.59kg, fd0624tu, FHD Camera, UHD Graphics Laptop</t>
+          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U(8GB DDR4,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C226" t="inlineStr"/>
       <c r="D226" t="n">
-        <v>48990</v>
+        <v>51990</v>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>hp_15,_13th_gen_intel</t>
+          <t>HP 15 Smartchoice, 13th Gen</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U (8GB DDR4, 512GB SSD), FHD, Micro -Edge, Anti-Glare, 15.6''/39.6cm, Win11, M365* Office24, Silver, 1.59kg, fd0624tu, FHD Camera, UHD Graphics Laptop</t>
+          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U(8GB DDR4,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C227" t="inlineStr"/>
       <c r="D227" t="n">
-        <v>48990</v>
+        <v>51990</v>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>hp_15,_13th_gen_intel</t>
+          <t>hp_15_smartchoice,_13th_gen</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U (8GB DDR4, 512GB SSD), FHD, Micro -Edge, Anti-Glare, 15.6''/39.6cm, Win11, M365* Office24, Silver, 1.59kg, fd0624tu, FHD Camera, UHD Graphics Laptop</t>
+          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U(8GB DDR4,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C228" t="inlineStr"/>
       <c r="D228" t="n">
-        <v>48990</v>
+        <v>49990</v>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel</t>
+          <t>hp_15_smartchoice,_13th_gen</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
+          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U(8GB DDR4,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C229" t="inlineStr"/>
       <c r="D229" t="n">
-        <v>47990</v>
+        <v>49990</v>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel</t>
+          <t>hp_15_smartchoice,_13th_gen</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
+          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U(8GB DDR4,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C230" t="inlineStr"/>
       <c r="D230" t="n">
-        <v>47990</v>
+        <v>49990</v>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel</t>
+          <t>hp_15_smartchoice,_13th_gen</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
+          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U(8GB DDR4,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C231" t="inlineStr"/>
       <c r="D231" t="n">
-        <v>46990</v>
+        <v>49990</v>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel</t>
+          <t>hp_15_smartchoice,_intel_core</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
+          <t>HP 15 Smartchoice, Intel Core Ultra 5 125H, 12 Tops (16GB DDR5, 512GB SSD) FHD, IPS, 15.6''/39.6cm, Win11, M365(1yr)* Office24, Silver, 1.65kg, fd1254TU, FHD Camera w/Shutter, AI Powered Laptop</t>
         </is>
       </c>
       <c r="C232" t="inlineStr"/>
       <c r="D232" t="n">
-        <v>46990</v>
+        <v>69990</v>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel</t>
+          <t>hp_15_smartchoice,_intel_core</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
+          <t>HP 15 Smartchoice, Intel Core Ultra 5 125H, 12 Tops (16GB DDR5, 512GB SSD) FHD, IPS, 15.6''/39.6cm, Win11, M365(1yr)* Office24, Silver, 1.65kg, fd1254TU, FHD Camera w/Shutter, AI Powered Laptop</t>
         </is>
       </c>
       <c r="C233" t="inlineStr"/>
       <c r="D233" t="n">
-        <v>46990</v>
+        <v>69990</v>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -5323,100 +5323,100 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U (8GB DDR4, 512GB SSD), FHD, Micro -Edge, Anti-Glare, 15.6''/39.6cm, Win11, M365* Office24, Silver, 1.59kg, fd0624tu, FHD Camera, UHD Graphics Laptop</t>
         </is>
       </c>
       <c r="C234" t="inlineStr"/>
       <c r="D234" t="n">
-        <v>46990</v>
+        <v>47490</v>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-04-16</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel</t>
+          <t>hp_15,_13th_gen_intel</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U (8GB DDR4, 512GB SSD), FHD, Micro -Edge, Anti-Glare, 15.6''/39.6cm, Win11, M365* Office24, Silver, 1.59kg, fd0624tu, FHD Camera, UHD Graphics Laptop</t>
         </is>
       </c>
       <c r="C235" t="inlineStr"/>
       <c r="D235" t="n">
-        <v>46990</v>
+        <v>48990</v>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel</t>
+          <t>hp_15,_13th_gen_intel</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U (8GB DDR4, 512GB SSD), FHD, Micro -Edge, Anti-Glare, 15.6''/39.6cm, Win11, M365* Office24, Silver, 1.59kg, fd0624tu, FHD Camera, UHD Graphics Laptop</t>
         </is>
       </c>
       <c r="C236" t="inlineStr"/>
       <c r="D236" t="n">
-        <v>46990</v>
+        <v>48990</v>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel</t>
+          <t>hp_15,_13th_gen_intel</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U (8GB DDR4, 512GB SSD), FHD, Micro -Edge, Anti-Glare, 15.6''/39.6cm, Win11, M365* Office24, Silver, 1.59kg, fd0624tu, FHD Camera, UHD Graphics Laptop</t>
         </is>
       </c>
       <c r="C237" t="inlineStr"/>
       <c r="D237" t="n">
-        <v>48900</v>
+        <v>48990</v>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel</t>
+          <t>hp_15,_13th_gen_intel</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U (8GB DDR4, 512GB SSD), FHD, Micro -Edge, Anti-Glare, 15.6''/39.6cm, Win11, M365* Office24, Silver, 1.59kg, fd0624tu, FHD Camera, UHD Graphics Laptop</t>
         </is>
       </c>
       <c r="C238" t="inlineStr"/>
       <c r="D238" t="n">
-        <v>48900</v>
+        <v>48990</v>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-08-04</t>
         </is>
       </c>
     </row>
@@ -5433,11 +5433,11 @@
       </c>
       <c r="C239" t="inlineStr"/>
       <c r="D239" t="n">
-        <v>50000</v>
+        <v>47990</v>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -5454,11 +5454,11 @@
       </c>
       <c r="C240" t="inlineStr"/>
       <c r="D240" t="n">
-        <v>49850</v>
+        <v>47990</v>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -5475,11 +5475,11 @@
       </c>
       <c r="C241" t="inlineStr"/>
       <c r="D241" t="n">
-        <v>49990</v>
+        <v>46990</v>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-08</t>
         </is>
       </c>
     </row>
@@ -5496,11 +5496,11 @@
       </c>
       <c r="C242" t="inlineStr"/>
       <c r="D242" t="n">
-        <v>49820</v>
+        <v>46990</v>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
@@ -5517,11 +5517,11 @@
       </c>
       <c r="C243" t="inlineStr"/>
       <c r="D243" t="n">
-        <v>49820</v>
+        <v>46990</v>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-10</t>
         </is>
       </c>
     </row>
@@ -5538,11 +5538,11 @@
       </c>
       <c r="C244" t="inlineStr"/>
       <c r="D244" t="n">
-        <v>50400</v>
+        <v>46990</v>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-14</t>
         </is>
       </c>
     </row>
@@ -5559,11 +5559,11 @@
       </c>
       <c r="C245" t="inlineStr"/>
       <c r="D245" t="n">
-        <v>50390</v>
+        <v>46990</v>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-15</t>
         </is>
       </c>
     </row>
@@ -5580,11 +5580,11 @@
       </c>
       <c r="C246" t="inlineStr"/>
       <c r="D246" t="n">
-        <v>50150</v>
+        <v>46990</v>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-17</t>
         </is>
       </c>
     </row>
@@ -5601,11 +5601,11 @@
       </c>
       <c r="C247" t="inlineStr"/>
       <c r="D247" t="n">
-        <v>50040</v>
+        <v>48900</v>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-19</t>
         </is>
       </c>
     </row>
@@ -5622,11 +5622,11 @@
       </c>
       <c r="C248" t="inlineStr"/>
       <c r="D248" t="n">
-        <v>50040</v>
+        <v>48900</v>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-05-20</t>
         </is>
       </c>
     </row>
@@ -5643,11 +5643,11 @@
       </c>
       <c r="C249" t="inlineStr"/>
       <c r="D249" t="n">
-        <v>49670</v>
+        <v>50000</v>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-05-21</t>
         </is>
       </c>
     </row>
@@ -5664,11 +5664,11 @@
       </c>
       <c r="C250" t="inlineStr"/>
       <c r="D250" t="n">
-        <v>49480</v>
+        <v>49850</v>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-22</t>
         </is>
       </c>
     </row>
@@ -5685,11 +5685,11 @@
       </c>
       <c r="C251" t="inlineStr"/>
       <c r="D251" t="n">
-        <v>49470</v>
+        <v>49990</v>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>
@@ -5706,11 +5706,11 @@
       </c>
       <c r="C252" t="inlineStr"/>
       <c r="D252" t="n">
-        <v>49300</v>
+        <v>49820</v>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-05-24</t>
         </is>
       </c>
     </row>
@@ -5722,1062 +5722,1062 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U, (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge, FHD,15.6''/39.6cm, Win11,M365 Basic(1yr),Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
         </is>
       </c>
       <c r="C253" t="inlineStr"/>
       <c r="D253" t="n">
-        <v>47990</v>
+        <v>49820</v>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>HP 15, AMD Ryzen 5</t>
+          <t>HP 15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>HP 15, AMD Ryzen 5 7520U,(16GB LPDDR5, 512GB SSD), Anti-Glare, Micro-Edge, FHD, 15.6''/39.6cm, Win 11, Office 24,M365 Basic(1yr)*,Silver, 1.59kg, fc0690au, FHD Camera, Backlit KB Laptop</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
         </is>
       </c>
       <c r="C254" t="inlineStr"/>
       <c r="D254" t="n">
-        <v>53990</v>
+        <v>50400</v>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>HP 15, AMD Ryzen 5</t>
+          <t>HP 15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>HP 15, AMD Ryzen 5 7520U,(16GB LPDDR5, 512GB SSD), Anti-Glare, Micro-Edge, FHD, 15.6''/39.6cm, Win 11, Office 24,M365 Basic(1yr)*,Silver, 1.59kg, fc0690au, FHD Camera, Backlit KB Laptop</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
         </is>
       </c>
       <c r="C255" t="inlineStr"/>
       <c r="D255" t="n">
-        <v>53990</v>
+        <v>50390</v>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-27</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>HP 15, AMD Ryzen 5</t>
+          <t>HP 15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>HP 15, AMD Ryzen 5 7520U,(16GB LPDDR5, 512GB SSD), Anti-Glare, Micro-Edge, FHD, 15.6''/39.6cm, Win 11, Office 24,M365 Basic(1yr)*,Silver, 1.59kg, fc0690au, FHD Camera, Backlit KB Laptop</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
         </is>
       </c>
       <c r="C256" t="inlineStr"/>
       <c r="D256" t="n">
-        <v>54990</v>
+        <v>50150</v>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-28</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>hp_15,_amd_ryzen_5</t>
+          <t>HP 15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>HP 15, AMD Ryzen 5 7520U,(16GB LPDDR5, 512GB SSD), Anti-Glare, Micro-Edge, FHD, 15.6''/39.6cm, Win 11, Office 24,M365 Basic(1yr)*,Silver, 1.59kg, fc0690au, FHD Camera, Backlit KB Laptop</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
         </is>
       </c>
       <c r="C257" t="inlineStr"/>
       <c r="D257" t="n">
-        <v>56830</v>
+        <v>50040</v>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>HP 15, AMD Ryzen 7</t>
+          <t>HP 15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>HP 15, AMD Ryzen 7 7735HS (16GB DDR5,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365 Basic(1yr)* Office24, Silver, 1.59kg, fc1038AU, AMD Radeon FHD Camera w/Shutter, Backlit Laptop</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
         </is>
       </c>
       <c r="C258" t="inlineStr"/>
       <c r="D258" t="n">
-        <v>59990</v>
+        <v>50040</v>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>HP 15, Intel Core 5</t>
+          <t>HP 15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>HP 15, Intel Core 5 120U (14th Gen) 16GB DDR4, 512GB SSD, FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365 Basic(1yr), Office24, Silver,1.59kg, FD0640TU/682tu, FHD Camera w/Shutter, BL Laptop</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
         </is>
       </c>
       <c r="C259" t="inlineStr"/>
       <c r="D259" t="n">
-        <v>65990</v>
+        <v>49670</v>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>hp_15,_intel_core_5-120u</t>
+          <t>HP 15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>HP 15, Intel Core 5-120U (8GB DDR4, 512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365 Basic(1yr), Office Home24, Silver,1.59kg, fd0651TU, FHD Camera w/Privacy Shutter, Backlit Laptop</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
         </is>
       </c>
       <c r="C260" t="inlineStr"/>
       <c r="D260" t="n">
-        <v>57500</v>
+        <v>49480</v>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>HP 15, Intel Core Ultra</t>
+          <t>HP 15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>HP 15, Intel Core Ultra 5 125H (24GB DDR5, 1TB SSD), Micro-Edge, Anti-Glare, FHD, 15''/39.6cm, Win11, M365* Office24, Silver, 1.65kg, FD1458TU, FHD Camera, Backlit Laptop</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
         </is>
       </c>
       <c r="C261" t="inlineStr"/>
       <c r="D261" t="n">
-        <v>84990</v>
+        <v>49470</v>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-06-12</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>hp_15,_intel_core_i3-1315u-13th</t>
+          <t>HP 15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>HP 15, Intel Core i3-1315U-13th Gen Laptop (8GB DDR4 Ram,512GB SSD) Anti-Glare, Micro-Edge,15.6'" FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera Shutter, 15-fd0569TU</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
         </is>
       </c>
       <c r="C262" t="inlineStr"/>
       <c r="D262" t="n">
-        <v>49490</v>
+        <v>49300</v>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>hp_15,_intel_core_i3-1315u-13th</t>
+          <t>HP 15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>HP 15, Intel Core i3-1315U-13th Gen Laptop (8GB DDR4 Ram,512GB SSD) Anti-Glare, Micro-Edge,15.6'" FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera Shutter, 15-fd0569TU</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U, (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge, FHD,15.6''/39.6cm, Win11,M365 Basic(1yr),Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C263" t="inlineStr"/>
       <c r="D263" t="n">
-        <v>50900</v>
+        <v>47990</v>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>HP 255R G10 Notebook (AMD</t>
+          <t>HP 15, AMD Ryzen 5</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>HP 255R G10 Notebook (AMD Athlon Silver 7120U /8GB/512GB/DOS) 15.6-inch(39.6cm), Anti-Glare, HD Laptop, Radeon Graphics, Silver,1.52kg</t>
+          <t>HP 15, AMD Ryzen 5 7520U,(16GB LPDDR5, 512GB SSD), Anti-Glare, Micro-Edge, FHD, 15.6''/39.6cm, Win 11, Office 24,M365 Basic(1yr)*,Silver, 1.59kg, fc0690au, FHD Camera, Backlit KB Laptop</t>
         </is>
       </c>
       <c r="C264" t="inlineStr"/>
       <c r="D264" t="n">
-        <v>41700</v>
+        <v>53990</v>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-08</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>HP 255R G10 Notebook (AMD</t>
+          <t>HP 15, AMD Ryzen 5</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>HP 255R G10 Notebook (AMD Athlon Silver 7120U /8GB/512GB/DOS) 15.6-inch(39.6cm), Anti-Glare, HD Laptop, Radeon Graphics, Silver,1.52kg</t>
+          <t>HP 15, AMD Ryzen 5 7520U,(16GB LPDDR5, 512GB SSD), Anti-Glare, Micro-Edge, FHD, 15.6''/39.6cm, Win 11, Office 24,M365 Basic(1yr)*,Silver, 1.59kg, fc0690au, FHD Camera, Backlit KB Laptop</t>
         </is>
       </c>
       <c r="C265" t="inlineStr"/>
       <c r="D265" t="n">
-        <v>39340</v>
+        <v>53990</v>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>HP 255R G10 Notebook (AMD</t>
+          <t>HP 15, AMD Ryzen 5</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>HP 255R G10 Notebook (AMD Athlon Silver 7120U /8GB/512GB/DOS) 15.6-inch(39.6cm), Anti-Glare, HD Laptop, Radeon Graphics, Silver,1.52kg</t>
+          <t>HP 15, AMD Ryzen 5 7520U,(16GB LPDDR5, 512GB SSD), Anti-Glare, Micro-Edge, FHD, 15.6''/39.6cm, Win 11, Office 24,M365 Basic(1yr)*,Silver, 1.59kg, fc0690au, FHD Camera, Backlit KB Laptop</t>
         </is>
       </c>
       <c r="C266" t="inlineStr"/>
       <c r="D266" t="n">
-        <v>40409</v>
+        <v>54990</v>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-24</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>HP 255R G10 Notebook (AMD</t>
+          <t>hp_15,_amd_ryzen_5</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>HP 255R G10 Notebook (AMD Athlon Silver 7120U /8GB/512GB/DOS) 15.6-inch(39.6cm), Anti-Glare, HD Laptop, Radeon Graphics, Silver,1.52kg</t>
+          <t>HP 15, AMD Ryzen 5 7520U,(16GB LPDDR5, 512GB SSD), Anti-Glare, Micro-Edge, FHD, 15.6''/39.6cm, Win 11, Office 24,M365 Basic(1yr)*,Silver, 1.59kg, fc0690au, FHD Camera, Backlit KB Laptop</t>
         </is>
       </c>
       <c r="C267" t="inlineStr"/>
       <c r="D267" t="n">
-        <v>39618</v>
+        <v>56830</v>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>HP 255R G10 Notebook (AMD</t>
+          <t>HP 15, AMD Ryzen 7</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>HP 255R G10 Notebook (AMD Athlon Silver 7120U /8GB/512GB/DOS) 15.6-inch(39.6cm), Anti-Glare, HD Laptop, Radeon Graphics, Silver,1.52kg</t>
+          <t>HP 15, AMD Ryzen 7 7735HS (16GB DDR5,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365 Basic(1yr)* Office24, Silver, 1.59kg, fc1038AU, AMD Radeon FHD Camera w/Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C268" t="inlineStr"/>
       <c r="D268" t="n">
-        <v>39525</v>
+        <v>59990</v>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-14</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>HP Omen, Intel Core Ultra</t>
+          <t>HP 15, Intel Core 5</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>HP Omen, Intel Core Ultra 7 255H, 8GB RTX 5050, 24GB DDR5(Upgradeable) 1TB SSD, 2K, 165Hz, 3ms Response time, IPS, 16''/40.6cm, Win11, M365*Office24, Shadow Black, 2.43kg, am0240tx, RGB Gaming Laptop</t>
+          <t>HP 15, Intel Core 5 120U (14th Gen) 16GB DDR4, 512GB SSD, FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365 Basic(1yr), Office24, Silver,1.59kg, FD0640TU/682tu, FHD Camera w/Shutter, BL Laptop</t>
         </is>
       </c>
       <c r="C269" t="inlineStr"/>
       <c r="D269" t="n">
-        <v>129990</v>
+        <v>65990</v>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>HP OmniBook 3, AMD Ryzen</t>
+          <t>hp_15,_intel_core_5-120u</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>HP OmniBook 3, AMD Ryzen AI 5 330 (24GB DDR5 RAM, 1TB SSD) FHD, Anti-Glare, 15.6''/39.6cm, Win11, Office24, Glacier Silver,1.7kg, fn0074AU, FHD Camera w/Shutter, FPR, Backlit KB, Next Gen AI Laptop</t>
+          <t>HP 15, Intel Core 5-120U (8GB DDR4, 512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365 Basic(1yr), Office Home24, Silver,1.59kg, fd0651TU, FHD Camera w/Privacy Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C270" t="inlineStr"/>
       <c r="D270" t="n">
-        <v>69990</v>
+        <v>57500</v>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>HP OmniBook 5 OLED (Previously</t>
+          <t>hp_15,_intel_core_5-120u</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>HP OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x, 1TB SSD) 2K, 14''/35.6cm, Win11, M365 Basic(1yr)* Office24, Silver, 1.35kg, he0015QU, Light-Weight, Next-Gen AI Laptop</t>
+          <t>HP 15, Intel Core 5-120U (8GB DDR4, 512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365 Basic(1yr), Office Home24, Silver,1.59kg, fd0651TU, FHD Camera w/Privacy Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C271" t="inlineStr"/>
       <c r="D271" t="n">
-        <v>69990</v>
+        <v>57700</v>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-08-04</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>HP OmniBook 5 OLED (Previously</t>
+          <t>hp_15,_intel_core_ultra</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>HP OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x, 512GB SSD) 2K, 14''/35.6cm, Win11, M365 Basic(1yr)* Office24, Silver, 1.35kg, he0014QU, Light-Weight, Next-Gen AI Laptop</t>
+          <t>HP 15, Intel Core Ultra 5 125H (16GB DDR5, 1TB SSD) FHD, IPS, 15.6''/39.6cm, Win11, M365 Basic(1yr)*Office24, Silver, 1.65kg, fd1354TU, Intel Arc Graphics, FHD Camera w/Shutter, AI Powered Laptop</t>
         </is>
       </c>
       <c r="C272" t="inlineStr"/>
       <c r="D272" t="n">
-        <v>78990</v>
+        <v>74990</v>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-08-04</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>HP OmniBook 5 OLED (Previously</t>
+          <t>HP 15, Intel Core Ultra</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>HP OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x, 512GB SSD) 2K, 14''/35.6cm, Win11, M365 Basic(1yr)* Office24, Silver, 1.35kg, he0014QU, Light-Weight, Next-Gen AI Laptop</t>
+          <t>HP 15, Intel Core Ultra 5 125H (24GB DDR5, 1TB SSD), Micro-Edge, Anti-Glare, FHD, 15''/39.6cm, Win11, M365* Office24, Silver, 1.65kg, FD1458TU, FHD Camera, Backlit Laptop</t>
         </is>
       </c>
       <c r="C273" t="inlineStr"/>
       <c r="D273" t="n">
-        <v>66990</v>
+        <v>84990</v>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>hp_omnibook_5_oled_(previously</t>
+          <t>hp_15,_intel_core_i3-1315u-13th</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>HP OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor 45 Tops (16GB LPDDR5x, 512GB SSD), 2K 14''/35.6cm, Win11, Office24, Silver, 1.29kg, he0014QU, Multi-Day Battery, AI Laptop</t>
+          <t>HP 15, Intel Core i3-1315U-13th Gen Laptop (8GB DDR4 Ram,512GB SSD) Anti-Glare, Micro-Edge,15.6'" FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera Shutter, 15-fd0569TU</t>
         </is>
       </c>
       <c r="C274" t="inlineStr"/>
       <c r="D274" t="n">
-        <v>79990</v>
+        <v>49490</v>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>hp_omnibook_x_flip_oled</t>
+          <t>hp_15,_intel_core_i3-1315u-13th</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>HP OmniBook X Flip OLED Intel Core Ultra 5 226V, 40 Tops (16GB LPDDR5x,1TB SSD) 3K, Touch, 120hz, 14''/35.6cm, Intel ARC Graphic,Win11, Office24, Meteor Silver, 1.38kg, fm0099TU,Pen, 2 in 1 AI Laptop</t>
+          <t>HP 15, Intel Core i3-1315U-13th Gen Laptop (8GB DDR4 Ram,512GB SSD) Anti-Glare, Micro-Edge,15.6'" FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera Shutter, 15-fd0569TU</t>
         </is>
       </c>
       <c r="C275" t="inlineStr"/>
       <c r="D275" t="n">
-        <v>115990</v>
+        <v>50900</v>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>hp_omnibook_3,_snapdragon_x</t>
+          <t>HP 255R G10 Notebook (AMD</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>HP Omnibook 3, Snapdragon X Processor 45 TOPS (16GB LPDDR5x,512GB SSD) 2K WUXGA, Anti-Glare, 14''/35.6cm, Win 11, M365*Office 24,Silver,1.42kg, hz0026QU, Lighter mini Charger, FHD IR Camera, AI Laptop</t>
+          <t>HP 255R G10 Notebook (AMD Athlon Silver 7120U /8GB/512GB/DOS) 15.6-inch(39.6cm), Anti-Glare, HD Laptop, Radeon Graphics, Silver,1.52kg</t>
         </is>
       </c>
       <c r="C276" t="inlineStr"/>
       <c r="D276" t="n">
-        <v>79990</v>
+        <v>41700</v>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-04-16</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>HP Omnibook 3, Snapdragon X</t>
+          <t>HP 255R G10 Notebook (AMD</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>HP Omnibook 3, Snapdragon X Processor, 45 TOPS (16GB LPDDR5x, 512GB SSD) 2K, WUXGA, IPS, 14''/35.6cm, Win 11, Office 24, Silver, 1.4kg, hz0026QU, FHD IR Camera, 42% Lighter mini GaN Charger, AI Laptop</t>
+          <t>HP 255R G10 Notebook (AMD Athlon Silver 7120U /8GB/512GB/DOS) 15.6-inch(39.6cm), Anti-Glare, HD Laptop, Radeon Graphics, Silver,1.52kg</t>
         </is>
       </c>
       <c r="C277" t="inlineStr"/>
       <c r="D277" t="n">
-        <v>69990</v>
+        <v>39340</v>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-10</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>HP Omnibook 3, Snapdragon X</t>
+          <t>HP 255R G10 Notebook (AMD</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>HP Omnibook 3, Snapdragon X Processor, 45 TOPS (16GB LPDDR5x, 512GB SSD) 2K, WUXGA, IPS, 14''/35.6cm, Win 11, Office 24, Silver, 1.4kg, hz0026QU, FHD IR Camera, 42% Lighter mini GaN Charger, AI Laptop</t>
+          <t>HP 255R G10 Notebook (AMD Athlon Silver 7120U /8GB/512GB/DOS) 15.6-inch(39.6cm), Anti-Glare, HD Laptop, Radeon Graphics, Silver,1.52kg</t>
         </is>
       </c>
       <c r="C278" t="inlineStr"/>
       <c r="D278" t="n">
-        <v>73990</v>
+        <v>40409</v>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-20</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>HP Omnibook 5 OLED (Previously</t>
+          <t>HP 255R G10 Notebook (AMD</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>HP Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x,1TB SSD) 2K OLED,16''/40.6cm, Win11, M365*Office24, Glacier Silver, 1.59kg, fb0001QU, Backlit, Next-Gen AI Laptop</t>
+          <t>HP 255R G10 Notebook (AMD Athlon Silver 7120U /8GB/512GB/DOS) 15.6-inch(39.6cm), Anti-Glare, HD Laptop, Radeon Graphics, Silver,1.52kg</t>
         </is>
       </c>
       <c r="C279" t="inlineStr"/>
       <c r="D279" t="n">
-        <v>78850</v>
+        <v>39618</v>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>hp_omnibook_5_oled_(previously</t>
+          <t>HP 255R G10 Notebook (AMD</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>HP Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor 45 Tops (16GB LPDDR5x, 1TB SSD) 2K,16''/40.6cm, Win11, Office24, Silver, 1.59kg, fb0001QU, Multi-Day Battery AI Laptop</t>
+          <t>HP 255R G10 Notebook (AMD Athlon Silver 7120U /8GB/512GB/DOS) 15.6-inch(39.6cm), Anti-Glare, HD Laptop, Radeon Graphics, Silver,1.52kg</t>
         </is>
       </c>
       <c r="C280" t="inlineStr"/>
       <c r="D280" t="n">
-        <v>77900</v>
+        <v>39525</v>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>hp_pavilion_plus,_intel_core</t>
+          <t>HP Omen, Intel Core Ultra</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>HP Pavilion Plus, Intel Core i5-1335U-13th Gen Laptop, (16GB LPDDR5x,512GB SSD),IPS, 300 nits, 14''(35.6cm) 2K,Win 11, M365 Basic(1yr), Office Home 24, Silver,1.38kg, 5MP Camera w/Shutter, ew0107TU</t>
+          <t>HP Omen, Intel Core Ultra 7 255H, 8GB RTX 5050, 24GB DDR5(Upgradeable) 1TB SSD, 2K, 165Hz, 3ms Response time, IPS, 16''/40.6cm, Win11, M365*Office24, Shadow Black, 2.43kg, am0240tx, RGB Gaming Laptop</t>
         </is>
       </c>
       <c r="C281" t="inlineStr"/>
       <c r="D281" t="n">
-        <v>63990</v>
+        <v>129990</v>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-10</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>hp_professional_15_(2026),_intel</t>
+          <t>HP OmniBook 3, AMD Ryzen</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>HP Professional 15 (2026), Intel (i3 14th Gen) Core 3 100U - (8 GB/512 GB SSD/Intel UHD Graphics/Windows 11 Home) Thin &amp; Light Business Laptop/15.6" Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
+          <t>HP OmniBook 3, AMD Ryzen AI 5 330 (24GB DDR5 RAM, 1TB SSD) FHD, Anti-Glare, 15.6''/39.6cm, Win11, Office24, Glacier Silver,1.7kg, fn0074AU, FHD Camera w/Shutter, FPR, Backlit KB, Next Gen AI Laptop</t>
         </is>
       </c>
       <c r="C282" t="inlineStr"/>
       <c r="D282" t="n">
-        <v>48990</v>
+        <v>69990</v>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>hp_professional_15_(2026),_intel</t>
+          <t>HP OmniBook 5 OLED (Previously</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>HP Professional 15 (2026), Intel (i3 14th Gen) Core 3 100U - (8 GB/512 GB SSD/Intel UHD Graphics/Windows 11 Home) Thin &amp; Light Business Laptop/15.6" Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
+          <t>HP OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x, 1TB SSD) 2K, 14''/35.6cm, Win11, M365 Basic(1yr)* Office24, Silver, 1.35kg, he0015QU, Light-Weight, Next-Gen AI Laptop</t>
         </is>
       </c>
       <c r="C283" t="inlineStr"/>
       <c r="D283" t="n">
-        <v>51899</v>
+        <v>69990</v>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-05-14</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>hp_professional_15_(2026),_intel</t>
+          <t>HP OmniBook 5 OLED (Previously</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>HP Professional 15 (2026), Intel (i3 14th Gen) Core 3 100U - (8 GB/512 GB SSD/Intel UHD Graphics/Windows 11 Home) Thin &amp; Light Business Laptop/15.6" Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
+          <t>HP OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x, 512GB SSD) 2K, 14''/35.6cm, Win11, M365 Basic(1yr)* Office24, Silver, 1.35kg, he0014QU, Light-Weight, Next-Gen AI Laptop</t>
         </is>
       </c>
       <c r="C284" t="inlineStr"/>
       <c r="D284" t="n">
-        <v>51840</v>
+        <v>78990</v>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>hp_professional_15_(2026),_intel</t>
+          <t>HP OmniBook 5 OLED (Previously</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>HP Professional 15 (2026), Intel (i3 14th Gen) Core 3 100U - (8 GB/512 GB SSD/Intel UHD Graphics/Windows 11 Home) Thin &amp; Light Business Laptop/15.6" Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
+          <t>HP OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x, 512GB SSD) 2K, 14''/35.6cm, Win11, M365 Basic(1yr)* Office24, Silver, 1.35kg, he0014QU, Light-Weight, Next-Gen AI Laptop</t>
         </is>
       </c>
       <c r="C285" t="inlineStr"/>
       <c r="D285" t="n">
-        <v>51840</v>
+        <v>66990</v>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>HP Smartchoice OmniBook 5 OLED</t>
+          <t>hp_omnibook_5_oled_(previously</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>HP Smartchoice OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x, 1TB SSD) 2K, 14''/35.6cm, Win11, M365(1yr)*Office24, Silver,1.35kg, he0015QU,Light-Weight,Next-Gen AI Laptop</t>
+          <t>HP OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor 45 Tops (16GB LPDDR5x, 512GB SSD), 2K 14''/35.6cm, Win11, Office24, Silver, 1.29kg, he0014QU, Multi-Day Battery, AI Laptop</t>
         </is>
       </c>
       <c r="C286" t="inlineStr"/>
       <c r="D286" t="n">
-        <v>82990</v>
+        <v>79990</v>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>HP Smartchoice OmniBook 5 OLED</t>
+          <t>hp_omnibook_x_flip_oled</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>HP Smartchoice OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x, 1TB SSD) 2K, 14''/35.6cm, Win11, M365(1yr)*Office24, Silver,1.35kg, he0015QU,Light-Weight,Next-Gen AI Laptop</t>
+          <t>HP OmniBook X Flip OLED Intel Core Ultra 5 226V, 40 Tops (16GB LPDDR5x,1TB SSD) 3K, Touch, 120hz, 14''/35.6cm, Intel ARC Graphic,Win11, Office24, Meteor Silver, 1.38kg, fm0099TU,Pen, 2 in 1 AI Laptop</t>
         </is>
       </c>
       <c r="C287" t="inlineStr"/>
       <c r="D287" t="n">
-        <v>76990</v>
+        <v>115990</v>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>HP Smartchoice OmniBook 5 OLED</t>
+          <t>hp_omnibook_3,_snapdragon_x</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>HP Smartchoice OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x, 512GB SSD) 2K, 14''/35.6cm, Win11, M365(1yr)* Office24, Silver, 1.35kg, he0014QU, Next-Gen AI Laptop</t>
+          <t>HP Omnibook 3, Snapdragon X Processor 45 TOPS (16GB LPDDR5x,512GB SSD) 2K WUXGA, Anti-Glare, 14''/35.6cm, Win 11, M365*Office 24,Silver,1.42kg, hz0026QU, Lighter mini Charger, FHD IR Camera, AI Laptop</t>
         </is>
       </c>
       <c r="C288" t="inlineStr"/>
       <c r="D288" t="n">
-        <v>78990</v>
+        <v>79990</v>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>HP Smartchoice OmniBook 5 OLED</t>
+          <t>HP Omnibook 3, Snapdragon X</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>HP Smartchoice OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x, 512GB SSD) 2K, 14''/35.6cm, Win11, M365(1yr)* Office24, Silver, 1.35kg, he0014QU, Next-Gen AI Laptop</t>
+          <t>HP Omnibook 3, Snapdragon X Processor, 45 TOPS (16GB LPDDR5x, 512GB SSD) 2K, WUXGA, IPS, 14''/35.6cm, Win 11, Office 24, Silver, 1.4kg, hz0026QU, FHD IR Camera, 42% Lighter mini GaN Charger, AI Laptop</t>
         </is>
       </c>
       <c r="C289" t="inlineStr"/>
       <c r="D289" t="n">
-        <v>79990</v>
+        <v>69990</v>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-27</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>HP Smartchoice Omnibook 5 OLED</t>
+          <t>HP Omnibook 3, Snapdragon X</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>HP Smartchoice Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x,1TB SSD) 2K OLED,16''/40.6cm, Win11, M365(1yr)*Office24, Glacier Silver, 1.59kg, fb0001QU,Next-Gen AI Laptop</t>
+          <t>HP Omnibook 3, Snapdragon X Processor, 45 TOPS (16GB LPDDR5x, 512GB SSD) 2K, WUXGA, IPS, 14''/35.6cm, Win 11, Office 24, Silver, 1.4kg, hz0026QU, FHD IR Camera, 42% Lighter mini GaN Charger, AI Laptop</t>
         </is>
       </c>
       <c r="C290" t="inlineStr"/>
       <c r="D290" t="n">
-        <v>68739</v>
+        <v>73990</v>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>HP Smartchoice Omnibook 5 OLED</t>
+          <t>HP Omnibook 5 OLED (Previously</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>HP Smartchoice Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x,1TB SSD) 2K OLED,16''/40.6cm, Win11, M365(1yr)*Office24, Glacier Silver, 1.59kg, fb0001QU,Next-Gen AI Laptop</t>
+          <t>HP Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x,1TB SSD) 2K OLED,16''/40.6cm, Win11, M365*Office24, Glacier Silver, 1.59kg, fb0001QU, Backlit, Next-Gen AI Laptop</t>
         </is>
       </c>
       <c r="C291" t="inlineStr"/>
       <c r="D291" t="n">
-        <v>68739</v>
+        <v>78850</v>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>HP Smartchoice Omnibook 5 OLED</t>
+          <t>hp_omnibook_5_oled_(previously</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>HP Smartchoice Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x,1TB SSD) 2K OLED,16''/40.6cm, Win11, M365(1yr)*Office24, Glacier Silver, 1.59kg, fb0001QU,Next-Gen AI Laptop</t>
+          <t>HP Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor 45 Tops (16GB LPDDR5x, 1TB SSD) 2K,16''/40.6cm, Win11, Office24, Silver, 1.59kg, fb0001QU, Multi-Day Battery AI Laptop</t>
         </is>
       </c>
       <c r="C292" t="inlineStr"/>
       <c r="D292" t="n">
-        <v>68739</v>
+        <v>77900</v>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>HP Smartchoice Omnibook 5 OLED</t>
+          <t>hp_pavilion_plus,_intel_core</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>HP Smartchoice Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x,1TB SSD) 2K OLED,16''/40.6cm, Win11, M365(1yr)*Office24, Glacier Silver, 1.59kg, fb0001QU,Next-Gen AI Laptop</t>
+          <t>HP Pavilion Plus, Intel Core i5-1335U-13th Gen Laptop, (16GB LPDDR5x,512GB SSD),IPS, 300 nits, 14''(35.6cm) 2K,Win 11, M365 Basic(1yr), Office Home 24, Silver,1.38kg, 5MP Camera w/Shutter, ew0107TU</t>
         </is>
       </c>
       <c r="C293" t="inlineStr"/>
       <c r="D293" t="n">
-        <v>68323</v>
+        <v>63990</v>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>HP Smartchoice Omnibook 5 OLED</t>
+          <t>hp_professional_15_(2026),_intel</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>HP Smartchoice Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x,1TB SSD) 2K OLED,16''/40.6cm, Win11, M365(1yr)*Office24, Glacier Silver, 1.59kg, fb0001QU,Next-Gen AI Laptop</t>
+          <t>HP Professional 15 (2026), Intel (i3 14th Gen) Core 3 100U - (8 GB/512 GB SSD/Intel UHD Graphics/Windows 11 Home) Thin &amp; Light Business Laptop/15.6" Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
         </is>
       </c>
       <c r="C294" t="inlineStr"/>
       <c r="D294" t="n">
-        <v>67940</v>
+        <v>48990</v>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>HP Smartchoice Omnibook 5 OLED</t>
+          <t>hp_professional_15_(2026),_intel</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>HP Smartchoice Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x,1TB SSD) 2K OLED,16''/40.6cm, Win11, M365(1yr)*Office24, Glacier Silver, 1.59kg, fb0001QU,Next-Gen AI Laptop</t>
+          <t>HP Professional 15 (2026), Intel (i3 14th Gen) Core 3 100U - (8 GB/512 GB SSD/Intel UHD Graphics/Windows 11 Home) Thin &amp; Light Business Laptop/15.6" Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
         </is>
       </c>
       <c r="C295" t="inlineStr"/>
       <c r="D295" t="n">
-        <v>67940</v>
+        <v>51899</v>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>HP Smartchoice Victus, 13th Gen</t>
+          <t>hp_professional_15_(2026),_intel</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>HP Smartchoice Victus, 13th Gen Intel Core i7-13620H, 8GB RTX 5050, 24GB DDR5(Upgradeable) 1TB SSD, 144Hz, FHD, 15.6''/39.6cm, Win11, M365* Office24, Mica Silver, 2.29kg, fa2309TX, RGB Gaming Laptop</t>
+          <t>HP Professional 15 (2026), Intel (i3 14th Gen) Core 3 100U - (8 GB/512 GB SSD/Intel UHD Graphics/Windows 11 Home) Thin &amp; Light Business Laptop/15.6" Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
         </is>
       </c>
       <c r="C296" t="inlineStr"/>
       <c r="D296" t="n">
-        <v>112990</v>
+        <v>51840</v>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>HP Smartchoice Victus, AMD Ryzen</t>
+          <t>hp_professional_15_(2026),_intel</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>HP Smartchoice Victus, AMD Ryzen 7 7445HS, 6GB RTX 3050, 16GB DDR5(Upgradeable) 512GB SSD, FHD, 144Hz, 300 nits, 15.6''/39.6cm, Win 11, M365* Office24, Blue, 2.29kg, fb3134AX/3120ax, Gaming Laptop</t>
+          <t>HP Professional 15 (2026), Intel (i3 14th Gen) Core 3 100U - (8 GB/512 GB SSD/Intel UHD Graphics/Windows 11 Home) Thin &amp; Light Business Laptop/15.6" Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
         </is>
       </c>
       <c r="C297" t="inlineStr"/>
       <c r="D297" t="n">
-        <v>78990</v>
+        <v>51840</v>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>HP Smartchoice Victus, AMD Ryzen</t>
+          <t>HP Smartchoice OmniBook 5 OLED</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>HP Smartchoice Victus, AMD Ryzen 7 7445HS, 6GB RTX 3050, 16GB DDR5(Upgradeable) 512GB SSD, FHD, 144Hz, 300 nits, 15.6''/39.6cm, Win 11, M365* Office24, Blue, 2.29kg, fb3134AX/3120ax, Gaming Laptop</t>
+          <t>HP Smartchoice OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x, 1TB SSD) 2K, 14''/35.6cm, Win11, M365(1yr)*Office24, Silver,1.35kg, he0015QU,Light-Weight,Next-Gen AI Laptop</t>
         </is>
       </c>
       <c r="C298" t="inlineStr"/>
       <c r="D298" t="n">
-        <v>86990</v>
+        <v>82990</v>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>HP Smartchoice Victus, AMD Ryzen</t>
+          <t>HP Smartchoice OmniBook 5 OLED</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>HP Smartchoice Victus, AMD Ryzen 7 7445HS, 6GB RTX 3050, 16GB DDR5(Upgradeable) 512GB SSD, FHD, 144Hz, 300 nits, 15.6''/39.6cm, Win 11, M365* Office24, Blue, 2.29kg, fb3134AX/3120ax, Gaming Laptop</t>
+          <t>HP Smartchoice OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x, 1TB SSD) 2K, 14''/35.6cm, Win11, M365(1yr)*Office24, Silver,1.35kg, he0015QU,Light-Weight,Next-Gen AI Laptop</t>
         </is>
       </c>
       <c r="C299" t="inlineStr"/>
       <c r="D299" t="n">
-        <v>86990</v>
+        <v>76990</v>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>HP Victus, 14th Gen Intel</t>
+          <t>HP Smartchoice OmniBook 5 OLED</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>HP Victus, 14th Gen Intel Core i5-14450HX, 6GB RTX 3050, 24GB DDR5, 512GB SSD, FHD, 144Hz, 300 nits, IPS,15.6''/39.6cm, Win11, M365* Office24, Mica Silver, 2.3kg, fa2303tx/fa2315tx, RGB Gaming Laptop</t>
+          <t>HP Smartchoice OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x, 512GB SSD) 2K, 14''/35.6cm, Win11, M365(1yr)* Office24, Silver, 1.35kg, he0014QU, Next-Gen AI Laptop</t>
         </is>
       </c>
       <c r="C300" t="inlineStr"/>
       <c r="D300" t="n">
-        <v>103990</v>
+        <v>78990</v>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-24</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>HP Victus, AMD Ryzen 7</t>
+          <t>HP Smartchoice OmniBook 5 OLED</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>HP Victus, AMD Ryzen 7 7445HS, 4GB RTX 2050, 16GB DDR5(Upgradeable) 512GB SSD, FHD, 144Hz, 300 nits, IPS, 15.6'', Win11, M365* Office24, Blue, 2.29kg, fb3189ax /3122/ 23ax Backlit, Gaming Laptop</t>
+          <t>HP Smartchoice OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x, 512GB SSD) 2K, 14''/35.6cm, Win11, M365(1yr)* Office24, Silver, 1.35kg, he0014QU, Next-Gen AI Laptop</t>
         </is>
       </c>
       <c r="C301" t="inlineStr"/>
       <c r="D301" t="n">
-        <v>65990</v>
+        <v>79990</v>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>HP Victus, AMD Ryzen 7</t>
+          <t>HP Smartchoice Omnibook 5 OLED</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>HP Victus, AMD Ryzen 7 7445HS, 4GB RTX 2050, 16GB DDR5(Upgradeable) 512GB SSD, FHD, 144Hz, 300 nits, IPS, 15.6'', Win11, M365* Office24, Blue, 2.29kg, fb3189ax /3122/ 23ax Backlit, Gaming Laptop</t>
+          <t>HP Smartchoice Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x,1TB SSD) 2K OLED,16''/40.6cm, Win11, M365(1yr)*Office24, Glacier Silver, 1.59kg, fb0001QU,Next-Gen AI Laptop</t>
         </is>
       </c>
       <c r="C302" t="inlineStr"/>
       <c r="D302" t="n">
-        <v>65990</v>
+        <v>68739</v>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>HP Victus, AMD Ryzen 7</t>
+          <t>HP Smartchoice Omnibook 5 OLED</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>HP Victus, AMD Ryzen 7 7445HS, 6GB RTX 4050, 16GB DDR5(Upgradeable) 512GB SSD, 144Hz, IPS, 300nits, FHD, 15.6''/39.6cm, Win11, M365* Office24, Blue, 2.29kg, fb3130AX, Backlit, DTS Audio, Gaming Laptop</t>
+          <t>HP Smartchoice Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x,1TB SSD) 2K OLED,16''/40.6cm, Win11, M365(1yr)*Office24, Glacier Silver, 1.59kg, fb0001QU,Next-Gen AI Laptop</t>
         </is>
       </c>
       <c r="C303" t="inlineStr"/>
       <c r="D303" t="n">
-        <v>90990</v>
+        <v>68739</v>
       </c>
       <c r="E303" t="inlineStr">
         <is>
@@ -6788,1155 +6788,1155 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>HP Victus, AMD Ryzen 7</t>
+          <t>HP Smartchoice Omnibook 5 OLED</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>HP Victus, AMD Ryzen 7 7445HS, 6GB RTX 4050, 16GB DDR5(Upgradeable) 512GB SSD, 144Hz, IPS, 300nits, FHD, 15.6''/39.6cm, Win11, M365* Office24, Blue, 2.29kg, fb3130AX, Backlit, DTS Audio, Gaming Laptop</t>
+          <t>HP Smartchoice Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x,1TB SSD) 2K OLED,16''/40.6cm, Win11, M365(1yr)*Office24, Glacier Silver, 1.59kg, fb0001QU,Next-Gen AI Laptop</t>
         </is>
       </c>
       <c r="C304" t="inlineStr"/>
       <c r="D304" t="n">
-        <v>91990</v>
+        <v>68739</v>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-05-27</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Lenovo Chromebook Intel Celeron N4500</t>
+          <t>HP Smartchoice Omnibook 5 OLED</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Lenovo Chromebook Intel Celeron N4500 (4GB RAM/64GB eMMC 5.1/11.6 Inch (29.46cm)/HD Display/2Wx2 Stereo Speakers/HD Camera/Chrome OS/Blue/1.21Kg), 82UY0014HA</t>
+          <t>HP Smartchoice Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x,1TB SSD) 2K OLED,16''/40.6cm, Win11, M365(1yr)*Office24, Glacier Silver, 1.59kg, fb0001QU,Next-Gen AI Laptop</t>
         </is>
       </c>
       <c r="C305" t="inlineStr"/>
       <c r="D305" t="n">
-        <v>21990</v>
+        <v>68323</v>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-31</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Lenovo Chromebook Intel Celeron N4500</t>
+          <t>HP Smartchoice Omnibook 5 OLED</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Lenovo Chromebook Intel Celeron N4500 (4GB RAM/64GB eMMC 5.1/11.6 Inch (29.46cm)/HD Display/2Wx2 Stereo Speakers/HD Camera/Chrome OS/Blue/1.21Kg), 82UY0014HA</t>
+          <t>HP Smartchoice Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x,1TB SSD) 2K OLED,16''/40.6cm, Win11, M365(1yr)*Office24, Glacier Silver, 1.59kg, fb0001QU,Next-Gen AI Laptop</t>
         </is>
       </c>
       <c r="C306" t="inlineStr"/>
       <c r="D306" t="n">
-        <v>18990</v>
+        <v>67940</v>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Lenovo IdeaPad Slim 3 13th</t>
+          <t>HP Smartchoice Omnibook 5 OLED</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Lenovo IdeaPad Slim 3 13th Gen Intel Core i5-13420H 15.3 inch (38.8cm) WUXGA IPS Laptop (16GB RAM/1TB SSD/Windows 11/MSO 365 Basic+Office 2024/Top Metal Cover/Backlit KB/Grey/1.6Kg), 83K100S0IN</t>
+          <t>HP Smartchoice Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x,1TB SSD) 2K OLED,16''/40.6cm, Win11, M365(1yr)*Office24, Glacier Silver, 1.59kg, fb0001QU,Next-Gen AI Laptop</t>
         </is>
       </c>
       <c r="C307" t="inlineStr"/>
       <c r="D307" t="n">
-        <v>70990</v>
+        <v>67940</v>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-06-02</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>lenovo_ideapad_slim_3_13th</t>
+          <t>HP Smartchoice Victus, 13th Gen</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Lenovo IdeaPad Slim 3 13th Gen Intel Core i7 13620H, 16GB RAM, 512GB SSD, WUXGA IPS, 15.3"/38.8cm, Win 11, Office 2024, Top Metal Cover Grey, 1.6Kg, 83K100CJIN/S1IN, Backlit KB, Laptop</t>
+          <t>HP Smartchoice Victus, 13th Gen Intel Core i7-13620H, 8GB RTX 5050, 24GB DDR5(Upgradeable) 1TB SSD, 144Hz, FHD, 15.6''/39.6cm, Win11, M365* Office24, Mica Silver, 2.29kg, fa2309TX, RGB Gaming Laptop</t>
         </is>
       </c>
       <c r="C308" t="inlineStr"/>
       <c r="D308" t="n">
-        <v>81990</v>
+        <v>112990</v>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-10</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>lenovo_ideapad_slim_3_13th</t>
+          <t>HP Smartchoice Victus, AMD Ryzen</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Lenovo IdeaPad Slim 3 13th Gen Intel Core i7 13620H, 16GB RAM, 512GB SSD, WUXGA IPS, 15.3"/38.8cm, Win 11, Office 2024, Top Metal Cover Grey, 1.6Kg, 83K100CJIN/S1IN, Backlit KB, Laptop</t>
+          <t>HP Smartchoice Victus, AMD Ryzen 7 7445HS, 6GB RTX 3050, 16GB DDR5(Upgradeable) 512GB SSD, FHD, 144Hz, 300 nits, 15.6''/39.6cm, Win 11, M365* Office24, Blue, 2.29kg, fb3134AX/3120ax, Gaming Laptop</t>
         </is>
       </c>
       <c r="C309" t="inlineStr"/>
       <c r="D309" t="n">
-        <v>79990</v>
+        <v>78990</v>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>lenovo_ideapad_slim_3,_13th</t>
+          <t>HP Smartchoice Victus, AMD Ryzen</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Lenovo IdeaPad Slim 3, 13th Gen Intel Core i5 13420H, 24GB RAM, 1TB SSD, WUXGA IPS, 15.3"/38.8cm, Windows 11, Office Home 2024, Grey, 1.6Kg, Backlit Keyboard, 1Yr ADP Free, 83K100PLIN, Laptop</t>
+          <t>HP Smartchoice Victus, AMD Ryzen 7 7445HS, 6GB RTX 3050, 16GB DDR5(Upgradeable) 512GB SSD, FHD, 144Hz, 300 nits, 15.6''/39.6cm, Win 11, M365* Office24, Blue, 2.29kg, fb3134AX/3120ax, Gaming Laptop</t>
         </is>
       </c>
       <c r="C310" t="inlineStr"/>
       <c r="D310" t="n">
-        <v>79990</v>
+        <v>86990</v>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>lenovo_ideapad_slim_3,_amd</t>
+          <t>HP Smartchoice Victus, AMD Ryzen</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Lenovo IdeaPad Slim 3, AMD Ryzen 7 8840HS, 24GB RAM, 1TB SSD, WUXGA IPS, AI PC, 15.3"/38.8cm, Backlit Keyboard, Windows 11, Office Home 2024, Grey, 1.6Kg, 1Yr ADP Free, 83KA004TIN, AI Powered Laptop</t>
+          <t>HP Smartchoice Victus, AMD Ryzen 7 7445HS, 6GB RTX 3050, 16GB DDR5(Upgradeable) 512GB SSD, FHD, 144Hz, 300 nits, 15.6''/39.6cm, Win 11, M365* Office24, Blue, 2.29kg, fb3134AX/3120ax, Gaming Laptop</t>
         </is>
       </c>
       <c r="C311" t="inlineStr"/>
       <c r="D311" t="n">
-        <v>87990</v>
+        <v>86990</v>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>lenovo_ideapad_slim_3,_amd</t>
+          <t>HP Victus, 14th Gen Intel</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Lenovo IdeaPad Slim 3, AMD Ryzen 7 8840HS, 24GB RAM, 1TB SSD, WUXGA IPS, AI PC, 15.3"/38.8cm, Backlit Keyboard, Windows 11, Office Home 2024, Grey, 1.6Kg, 1Yr ADP Free, 83KA004TIN, AI Powered Laptop</t>
+          <t>HP Victus, 14th Gen Intel Core i5-14450HX, 6GB RTX 3050, 24GB DDR5, 512GB SSD, FHD, 144Hz, 300 nits, IPS,15.6''/39.6cm, Win11, M365* Office24, Mica Silver, 2.3kg, fa2303tx/fa2315tx, RGB Gaming Laptop</t>
         </is>
       </c>
       <c r="C312" t="inlineStr"/>
       <c r="D312" t="n">
-        <v>79990</v>
+        <v>103990</v>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-05-10</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>lenovo_ideapad_slim_3,_amd</t>
+          <t>HP Victus, AMD Ryzen 7</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Lenovo IdeaPad Slim 3, AMD Ryzen 7 8840HS, 24GB RAM, 1TB SSD, WUXGA IPS, AI PC, 15.3"/38.8cm, Backlit Keyboard, Windows 11, Office Home 2024, Grey, 1.6Kg, 1Yr ADP Free, 83KA004TIN, AI Powered Laptop</t>
+          <t>HP Victus, AMD Ryzen 7 7445HS, 4GB RTX 2050, 16GB DDR5(Upgradeable) 512GB SSD, FHD, 144Hz, 300 nits, IPS, 15.6'', Win11, M365* Office24, Blue, 2.29kg, fb3189ax /3122/ 23ax Backlit, Gaming Laptop</t>
         </is>
       </c>
       <c r="C313" t="inlineStr"/>
       <c r="D313" t="n">
-        <v>79990</v>
+        <v>65990</v>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-05-21</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>lenovo_ideapad_slim_3,_amd</t>
+          <t>HP Victus, AMD Ryzen 7</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Lenovo IdeaPad Slim 3, AMD Ryzen 7 8840HS, 24GB RAM, 1TB SSD, WUXGA IPS, AI PC, 15.3"/38.8cm, Backlit Keyboard, Windows 11, Office Home 2024, Grey, 1.6Kg, 1Yr ADP Free, 83KA004TIN, AI Powered Laptop</t>
+          <t>HP Victus, AMD Ryzen 7 7445HS, 4GB RTX 2050, 16GB DDR5(Upgradeable) 512GB SSD, FHD, 144Hz, 300 nits, IPS, 15.6'', Win11, M365* Office24, Blue, 2.29kg, fb3189ax /3122/ 23ax Backlit, Gaming Laptop</t>
         </is>
       </c>
       <c r="C314" t="inlineStr"/>
       <c r="D314" t="n">
-        <v>84990</v>
+        <v>65990</v>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-05-22</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>lenovo_ideapad_slim_5,_amd</t>
+          <t>HP Victus, AMD Ryzen 7</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Lenovo IdeaPad Slim 5, AMD Ryzen 5 7535HS, 16GB RAM, 512GB SSD, WUXGA IPS, 13.3"/33.7cm, Windows 11, Microsoft 365 Basic + Office 2024, Grey, 1.6Kg, Backlit KB, 1Yr ADP Free, 83J2004HIN, Laptop</t>
+          <t>HP Victus, AMD Ryzen 7 7445HS, 6GB RTX 4050, 16GB DDR5(Upgradeable) 512GB SSD, 144Hz, IPS, 300nits, FHD, 15.6''/39.6cm, Win11, M365* Office24, Blue, 2.29kg, fb3130AX, Backlit, DTS Audio, Gaming Laptop</t>
         </is>
       </c>
       <c r="C315" t="inlineStr"/>
       <c r="D315" t="n">
-        <v>72990</v>
+        <v>90990</v>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Lenovo Ideapad Slim 3 AMD</t>
+          <t>HP Victus, AMD Ryzen 7</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Lenovo Ideapad Slim 3 AMD Ryzen 5 7520U 15.6" (39.6cm) FHD Thin and Light Laptop (16GB/512GB SSD/Windows 11/Microsoft 365 Basic + Office Home 2024/Backlit Keyboard/Grey/1.6Kg), 82XQ00XDIN</t>
+          <t>HP Victus, AMD Ryzen 7 7445HS, 6GB RTX 4050, 16GB DDR5(Upgradeable) 512GB SSD, 144Hz, IPS, 300nits, FHD, 15.6''/39.6cm, Win11, M365* Office24, Blue, 2.29kg, fb3130AX, Backlit, DTS Audio, Gaming Laptop</t>
         </is>
       </c>
       <c r="C316" t="inlineStr"/>
       <c r="D316" t="n">
-        <v>50750</v>
+        <v>91990</v>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Lenovo LOQ 2024, Intel Core</t>
+          <t>Lenovo Chromebook Intel Celeron N4500</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Lenovo LOQ 2024, Intel Core i5-13450HX, 13th Gen, NVIDIA RTX 4050-6GB, 16GB RAM, 512GB SSD, FHD 144Hz, 15.6"/39.6cm, Windows 11, Office Home 2024, Grey, 2.4Kg, 83DV018JIN, 1Yr ADP Free Gaming Laptop</t>
+          <t>Lenovo Chromebook Intel Celeron N4500 (4GB RAM/64GB eMMC 5.1/11.6 Inch (29.46cm)/HD Display/2Wx2 Stereo Speakers/HD Camera/Chrome OS/Blue/1.21Kg), 82UY0014HA</t>
         </is>
       </c>
       <c r="C317" t="inlineStr"/>
       <c r="D317" t="n">
-        <v>100544</v>
+        <v>21990</v>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Lenovo LOQ 2025 AMD Ryzen</t>
+          <t>Lenovo Chromebook Intel Celeron N4500</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Lenovo LOQ 2025 AMD Ryzen 7 250| NVIDIA RTX 5050 8GB (16GB RAM/1TB SSD/144Hz Refresh Rate/440 AI TOPS/15.6" (39.6cm)/Windows 11/Office 2024/3 Mon. Game Pass/Grey/2.4Kg), 83JG008KIN</t>
+          <t>Lenovo Chromebook Intel Celeron N4500 (4GB RAM/64GB eMMC 5.1/11.6 Inch (29.46cm)/HD Display/2Wx2 Stereo Speakers/HD Camera/Chrome OS/Blue/1.21Kg), 82UY0014HA</t>
         </is>
       </c>
       <c r="C318" t="inlineStr"/>
       <c r="D318" t="n">
-        <v>134990</v>
+        <v>18990</v>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Lenovo LOQ 2025 Intel Core</t>
+          <t>Lenovo IdeaPad Slim 3 13th</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Lenovo LOQ 2025 Intel Core i7-14700HX| NVIDIA RTX 5060 8GB (32GB RAM/1TB SSD/144Hz Refresh Rate/572 AI TOPS/15.6" (39.6cm)/Windows 11/Office 2024/3 Mon. Game Pass/Grey/2.4Kg), 83JE00T3IN</t>
+          <t>Lenovo IdeaPad Slim 3 13th Gen Intel Core i5-13420H 15.3 inch (38.8cm) WUXGA IPS Laptop (16GB RAM/1TB SSD/Windows 11/MSO 365 Basic+Office 2024/Top Metal Cover/Backlit KB/Grey/1.6Kg), 83K100S0IN</t>
         </is>
       </c>
       <c r="C319" t="inlineStr"/>
       <c r="D319" t="n">
-        <v>157990</v>
+        <v>70990</v>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-08</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Lenovo LOQ AMD Ryzen 5</t>
+          <t>lenovo_ideapad_slim_3_13th</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Lenovo LOQ AMD Ryzen 5 7235HS | NVIDIA RTX 4050 6GB (16GB RAM/512GB SSD/144Hz Refresh Rate/15.6" (39.6cm)/Windows 11/Office Home 2024/3 Mon. Game Pass/Grey/2.4Kg), 83JC00NYIN AI Gaming Laptop</t>
+          <t>Lenovo IdeaPad Slim 3 13th Gen Intel Core i7 13620H, 16GB RAM, 512GB SSD, WUXGA IPS, 15.3"/38.8cm, Win 11, Office 2024, Top Metal Cover Grey, 1.6Kg, 83K100CJIN/S1IN, Backlit KB, Laptop</t>
         </is>
       </c>
       <c r="C320" t="inlineStr"/>
       <c r="D320" t="n">
-        <v>88990</v>
+        <v>81990</v>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Lenovo LOQ, 13th Gen Intel</t>
+          <t>lenovo_ideapad_slim_3_13th</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Lenovo LOQ, 13th Gen Intel Core i7 13700HX, RTX 5050-8GB, 16GB RAM, 1TB SSD, FHD, 15.6"/39.6cm, 144Hz, Windows 11, Office 2024, Grey, 2.4Kg, 440 AI Tops, 3 Mon. Game Pass, 83JE00U7IN, AI Gaming Laptop</t>
+          <t>Lenovo IdeaPad Slim 3 13th Gen Intel Core i7 13620H, 16GB RAM, 512GB SSD, WUXGA IPS, 15.3"/38.8cm, Win 11, Office 2024, Top Metal Cover Grey, 1.6Kg, 83K100CJIN/S1IN, Backlit KB, Laptop</t>
         </is>
       </c>
       <c r="C321" t="inlineStr"/>
       <c r="D321" t="n">
-        <v>121869</v>
+        <v>79990</v>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Lenovo Legion 7 2025 Intel</t>
+          <t>lenovo_ideapad_slim_3,_13th</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Lenovo Legion 7 2025 Intel Core Ultra 9 275HX| NVIDIA RTX 5070 8GB (32GB RAM/1TB SSD/WQXGA OLED/240Hz/16(40.64cm)/Windows 11/Office 2024+AI Now/White/2.0Kg), 83KY001GIN AI Powered Gaming Laptop</t>
+          <t>Lenovo IdeaPad Slim 3, 13th Gen Intel Core i5 13420H, 24GB RAM, 1TB SSD, WUXGA IPS, 15.3"/38.8cm, Windows 11, Office Home 2024, Grey, 1.6Kg, Backlit Keyboard, 1Yr ADP Free, 83K100PLIN, Laptop</t>
         </is>
       </c>
       <c r="C322" t="inlineStr"/>
       <c r="D322" t="n">
-        <v>239391</v>
+        <v>79990</v>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Lenovo Legion Pro 5 2025</t>
+          <t>lenovo_ideapad_slim_3,_amd</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Lenovo Legion Pro 5 2025 AMD Ryzen 9 9955HX | NVIDIA RTX 5060 8GB (32GB RAM/1TB SSD/WQXGA OLED/165Hz/16 (40.6cm)/Windows 11/Office 2024+AI Now/Black/2.3Kg), 83F2004CIN AI Powered Gaming Laptop</t>
+          <t>Lenovo IdeaPad Slim 3, AMD Ryzen 7 8840HS, 24GB RAM, 1TB SSD, WUXGA IPS, AI PC, 15.3"/38.8cm, Backlit Keyboard, Windows 11, Office Home 2024, Grey, 1.6Kg, 1Yr ADP Free, 83KA004TIN, AI Powered Laptop</t>
         </is>
       </c>
       <c r="C323" t="inlineStr"/>
       <c r="D323" t="n">
-        <v>245490</v>
+        <v>87990</v>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Lenovo Legion Pro 5 2025</t>
+          <t>lenovo_ideapad_slim_3,_amd</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Lenovo Legion Pro 5 2025 AMD Ryzen 9 9955HX | NVIDIA RTX 5060 8GB (32GB RAM/1TB SSD/WQXGA OLED/165Hz/16 (40.6cm)/Windows 11/Office 2024+AI Now/Black/2.3Kg), 83F2004CIN AI Powered Gaming Laptop</t>
+          <t>Lenovo IdeaPad Slim 3, AMD Ryzen 7 8840HS, 24GB RAM, 1TB SSD, WUXGA IPS, AI PC, 15.3"/38.8cm, Backlit Keyboard, Windows 11, Office Home 2024, Grey, 1.6Kg, 1Yr ADP Free, 83KA004TIN, AI Powered Laptop</t>
         </is>
       </c>
       <c r="C324" t="inlineStr"/>
       <c r="D324" t="n">
-        <v>245490</v>
+        <v>79990</v>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Lenovo Legion Pro 5 2025</t>
+          <t>lenovo_ideapad_slim_3,_amd</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Lenovo Legion Pro 5 2025 AMD Ryzen 9 9955HX | NVIDIA RTX 5060 8GB (32GB RAM/1TB SSD/WQXGA OLED/165Hz/16 (40.6cm)/Windows 11/Office 2024+AI Now/Black/2.3Kg), 83F2004CIN AI Powered Gaming Laptop</t>
+          <t>Lenovo IdeaPad Slim 3, AMD Ryzen 7 8840HS, 24GB RAM, 1TB SSD, WUXGA IPS, AI PC, 15.3"/38.8cm, Backlit Keyboard, Windows 11, Office Home 2024, Grey, 1.6Kg, 1Yr ADP Free, 83KA004TIN, AI Powered Laptop</t>
         </is>
       </c>
       <c r="C325" t="inlineStr"/>
       <c r="D325" t="n">
-        <v>245490</v>
+        <v>79990</v>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Lenovo Legion Pro 5 2025</t>
+          <t>lenovo_ideapad_slim_3,_amd</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Lenovo Legion Pro 5 2025 AMD Ryzen 9 9955HX | NVIDIA RTX 5060 8GB (32GB RAM/1TB SSD/WQXGA OLED/165Hz/16 (40.6cm)/Windows 11/Office 2024+AI Now/Black/2.3Kg), 83F2004CIN AI Powered Gaming Laptop</t>
+          <t>Lenovo IdeaPad Slim 3, AMD Ryzen 7 8840HS, 24GB RAM, 1TB SSD, WUXGA IPS, AI PC, 15.3"/38.8cm, Backlit Keyboard, Windows 11, Office Home 2024, Grey, 1.6Kg, 1Yr ADP Free, 83KA004TIN, AI Powered Laptop</t>
         </is>
       </c>
       <c r="C326" t="inlineStr"/>
       <c r="D326" t="n">
-        <v>245490</v>
+        <v>84990</v>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Lenovo Legion Pro 7 FIFA</t>
+          <t>lenovo_ideapad_slim_5,_amd</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Lenovo Legion Pro 7 FIFA World Cup 26 Edition Intel Core Ultra 9 275HX | NVIDIA RTX 5070Ti 12GB (32GB RAM/1TB SSD/WQXGA OLED/240Hz/16(40.6cm)/Windows 11/Black/2.4Kg), 83F500HPIN AI Gaming Laptop</t>
+          <t>Lenovo IdeaPad Slim 5, AMD Ryzen 5 7535HS, 16GB RAM, 512GB SSD, WUXGA IPS, 13.3"/33.7cm, Windows 11, Microsoft 365 Basic + Office 2024, Grey, 1.6Kg, Backlit KB, 1Yr ADP Free, 83J2004HIN, Laptop</t>
         </is>
       </c>
       <c r="C327" t="inlineStr"/>
       <c r="D327" t="n">
-        <v>319990</v>
+        <v>72990</v>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Lenovo Smartchoice Ideapad 5 2-in-1</t>
+          <t>Lenovo Ideapad Slim 3 AMD</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Lenovo Smartchoice Ideapad 5 2-in-1 13th Gen Intel Core i5-13420H (16GB RAM/512GB SSD/Windows 11/Office Home 2024/WUXGA IPS/14 (35.5cm)/Touchscreen 2-in-1/3Mon.Game Pass/Grey/1.6kg), 83KX0059IN Laptop</t>
+          <t>Lenovo Ideapad Slim 3 AMD Ryzen 5 7520U 15.6" (39.6cm) FHD Thin and Light Laptop (16GB/512GB SSD/Windows 11/Microsoft 365 Basic + Office Home 2024/Backlit Keyboard/Grey/1.6Kg), 82XQ00XDIN</t>
         </is>
       </c>
       <c r="C328" t="inlineStr"/>
       <c r="D328" t="n">
-        <v>74490</v>
+        <v>50750</v>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>lenovo_thinkbook_14,_amd_ryzen</t>
+          <t>Lenovo LOQ 2024, Intel Core</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Lenovo ThinkBook 14, AMD Ryzen 5 220, 16GB RAM, 1TB SSD, WUXGA IPS 14” (35.56cm), Windows 11 Home, Arctic Grey, 1.36Kg, 21V0A01SIG, Fingerprint, Backlit, 400 Nits, 1Y Warranty, Laptop</t>
+          <t>Lenovo LOQ 2024, Intel Core i5-13450HX, 13th Gen, NVIDIA RTX 4050-6GB, 16GB RAM, 512GB SSD, FHD 144Hz, 15.6"/39.6cm, Windows 11, Office Home 2024, Grey, 2.4Kg, 83DV018JIN, 1Yr ADP Free Gaming Laptop</t>
         </is>
       </c>
       <c r="C329" t="inlineStr"/>
       <c r="D329" t="n">
-        <v>90990</v>
+        <v>100544</v>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>lenovo_thinkbook_14,_amd_ryzen</t>
+          <t>Lenovo LOQ 2025 AMD Ryzen</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Lenovo ThinkBook 14, AMD Ryzen 5 220, 16GB RAM, 1TB SSD, WUXGA IPS 14” (35.56cm), Windows 11 Home, Arctic Grey, 1.36Kg, 21V0A01SIG, Fingerprint, Backlit, 400 Nits, 1Y Warranty, Laptop</t>
+          <t>Lenovo LOQ 2025 AMD Ryzen 7 250| NVIDIA RTX 5050 8GB (16GB RAM/1TB SSD/144Hz Refresh Rate/440 AI TOPS/15.6" (39.6cm)/Windows 11/Office 2024/3 Mon. Game Pass/Grey/2.4Kg), 83JG008KIN</t>
         </is>
       </c>
       <c r="C330" t="inlineStr"/>
       <c r="D330" t="n">
-        <v>92990</v>
+        <v>134990</v>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>lenovo_thinkbook_14,_amd_ryzen</t>
+          <t>Lenovo LOQ 2025 Intel Core</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Lenovo ThinkBook 14, AMD Ryzen 5 220, 16GB RAM, 1TB SSD, WUXGA IPS 14” (35.56cm), Windows 11 Home, Arctic Grey, 1.36Kg, 21V0A01SIG, Fingerprint, Backlit, 400 Nits, 1Y Warranty, Laptop</t>
+          <t>Lenovo LOQ 2025 Intel Core i7-14700HX| NVIDIA RTX 5060 8GB (32GB RAM/1TB SSD/144Hz Refresh Rate/572 AI TOPS/15.6" (39.6cm)/Windows 11/Office 2024/3 Mon. Game Pass/Grey/2.4Kg), 83JE00T3IN</t>
         </is>
       </c>
       <c r="C331" t="inlineStr"/>
       <c r="D331" t="n">
-        <v>92990</v>
+        <v>157990</v>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Lenovo ThinkBook 15 G5 AMD</t>
+          <t>Lenovo LOQ AMD Ryzen 5</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Lenovo ThinkBook 15 G5 AMD Ryzen 7 7730U 15.6" FHD Antiglare 250 Nits Thin and Light Laptop (8GB RAM/512GB SSD/Windows 11 Home/Fingerprint Reader/Backlit/Mineral Grey/1 Year Onsite/1.7 kg), 21JFA00BIN</t>
+          <t>Lenovo LOQ AMD Ryzen 5 7235HS | NVIDIA RTX 4050 6GB (16GB RAM/512GB SSD/144Hz Refresh Rate/15.6" (39.6cm)/Windows 11/Office Home 2024/3 Mon. Game Pass/Grey/2.4Kg), 83JC00NYIN AI Gaming Laptop</t>
         </is>
       </c>
       <c r="C332" t="inlineStr"/>
       <c r="D332" t="n">
-        <v>59999</v>
+        <v>88990</v>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-19</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>lenovo_thinkbook_16_amd_ryzen</t>
+          <t>Lenovo LOQ, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Lenovo ThinkBook 16 AMD Ryzen 5 7535HS (8GB RAM/512GB SSD/Win 11 Home/Office 2024/Backlit Keyboard/Fingerprint) 16" WUXGA IPS 300 Nits Thin &amp; Light Laptop/1Y Warranty/Aluminium Top/1.7kg, 21MWA0BRIN</t>
+          <t>Lenovo LOQ, 13th Gen Intel Core i7 13700HX, RTX 5050-8GB, 16GB RAM, 1TB SSD, FHD, 15.6"/39.6cm, 144Hz, Windows 11, Office 2024, Grey, 2.4Kg, 440 AI Tops, 3 Mon. Game Pass, 83JE00U7IN, AI Gaming Laptop</t>
         </is>
       </c>
       <c r="C333" t="inlineStr"/>
       <c r="D333" t="n">
-        <v>65063</v>
+        <v>121869</v>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>lenovo_thinkbook_16_amd_ryzen</t>
+          <t>Lenovo Legion 7 2025 Intel</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Lenovo ThinkBook 16 AMD Ryzen 5 7535HS (8GB RAM/512GB SSD/Win 11 Home/Office 2024/Backlit Keyboard/Fingerprint) 16" WUXGA IPS 300 Nits Thin &amp; Light Laptop/1Y Warranty/Aluminium Top/1.7kg, 21MWA0BRIN</t>
+          <t>Lenovo Legion 7 2025 Intel Core Ultra 9 275HX| NVIDIA RTX 5070 8GB (32GB RAM/1TB SSD/WQXGA OLED/240Hz/16(40.64cm)/Windows 11/Office 2024+AI Now/White/2.0Kg), 83KY001GIN AI Powered Gaming Laptop</t>
         </is>
       </c>
       <c r="C334" t="inlineStr"/>
       <c r="D334" t="n">
-        <v>65063</v>
+        <v>239391</v>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-05-08</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>lenovo_thinkbook_16,_amd_ryzen</t>
+          <t>Lenovo Legion Pro 5 2025</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Lenovo ThinkBook 16, AMD Ryzen 5 7535HS, 16GB RAM, 512GB SSD, WUXGA IPS 16", Windows 11 Home, Office 2024, 1.7kg, 21MWA0BSIN, Backlit Keyboard, Fingerprint, 300 Nits, 1Y Warranty, Aluminium Top Laptop</t>
+          <t>Lenovo Legion Pro 5 2025 AMD Ryzen 9 9955HX | NVIDIA RTX 5060 8GB (32GB RAM/1TB SSD/WQXGA OLED/165Hz/16 (40.6cm)/Windows 11/Office 2024+AI Now/Black/2.3Kg), 83F2004CIN AI Powered Gaming Laptop</t>
         </is>
       </c>
       <c r="C335" t="inlineStr"/>
       <c r="D335" t="n">
-        <v>84500</v>
+        <v>245490</v>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-05-22</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Lenovo ThinkBook 16, Intel Core</t>
+          <t>Lenovo Legion Pro 5 2025</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Lenovo ThinkBook 16, Intel Core Ultra 9 185H, 16GB RAM, 512GB SSD, WUXGA IPS 16” (40.64cm), Win 11 Home, Arctic Grey, 1.7Kg, 21SKA0J5IG, Fingerprint, Backlit, 300 Nits, 1Y Warranty, AI Powered Laptop</t>
+          <t>Lenovo Legion Pro 5 2025 AMD Ryzen 9 9955HX | NVIDIA RTX 5060 8GB (32GB RAM/1TB SSD/WQXGA OLED/165Hz/16 (40.6cm)/Windows 11/Office 2024+AI Now/Black/2.3Kg), 83F2004CIN AI Powered Gaming Laptop</t>
         </is>
       </c>
       <c r="C336" t="inlineStr"/>
       <c r="D336" t="n">
-        <v>94990</v>
+        <v>245490</v>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-24</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Lenovo V14 Intel Core i3</t>
+          <t>Lenovo Legion Pro 5 2025</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Lenovo V14 Intel Core i3 13th Gen 14" FHD (1920x1080) Antiglare 250 Nits Thin and Light Laptop (16GB RAM/512GB SSD/Windows 11 Home/Office Home 2024/Iron Grey/1.43 kg), 83A0A0PCIN</t>
+          <t>Lenovo Legion Pro 5 2025 AMD Ryzen 9 9955HX | NVIDIA RTX 5060 8GB (32GB RAM/1TB SSD/WQXGA OLED/165Hz/16 (40.6cm)/Windows 11/Office 2024+AI Now/Black/2.3Kg), 83F2004CIN AI Powered Gaming Laptop</t>
         </is>
       </c>
       <c r="C337" t="inlineStr"/>
       <c r="D337" t="n">
-        <v>70990</v>
+        <v>245490</v>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Lenovo V14 Intel Core i3</t>
+          <t>Lenovo Legion Pro 5 2025</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Lenovo V14 Intel Core i3 13th Gen 14" FHD (1920x1080) Antiglare 250 Nits Thin and Light Laptop (16GB RAM/512GB SSD/Windows 11 Home/Office Home 2024/Iron Grey/1.43 kg), 83A0A0PCIN</t>
+          <t>Lenovo Legion Pro 5 2025 AMD Ryzen 9 9955HX | NVIDIA RTX 5060 8GB (32GB RAM/1TB SSD/WQXGA OLED/165Hz/16 (40.6cm)/Windows 11/Office 2024+AI Now/Black/2.3Kg), 83F2004CIN AI Powered Gaming Laptop</t>
         </is>
       </c>
       <c r="C338" t="inlineStr"/>
       <c r="D338" t="n">
-        <v>70990</v>
+        <v>245490</v>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>lenovo_v14_intel_core_i3</t>
+          <t>Lenovo Legion Pro 7 FIFA</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Lenovo V14 Intel Core i3 13th Gen 14" FHD (1920x1080) Antiglare 250 Nits Thin and Light Laptop (16GB RAM/512GB SSD/Windows 11 Home/Office Home 2024/Iron Grey/1.43 kg), 83A0A0PCIN</t>
+          <t>Lenovo Legion Pro 7 FIFA World Cup 26 Edition Intel Core Ultra 9 275HX | NVIDIA RTX 5070Ti 12GB (32GB RAM/1TB SSD/WQXGA OLED/240Hz/16(40.6cm)/Windows 11/Black/2.4Kg), 83F500HPIN AI Gaming Laptop</t>
         </is>
       </c>
       <c r="C339" t="inlineStr"/>
       <c r="D339" t="n">
-        <v>70990</v>
+        <v>319990</v>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-15</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 (2024), AMD</t>
+          <t>Lenovo Smartchoice Ideapad 5 2-in-1</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 (2024), AMD Ryzen 3 7320U Quad Core - (8GB/512GB SSD/AMD Radeon Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" FHD Display/Arctic Grey/1.57 kg/MS Office 2021</t>
+          <t>Lenovo Smartchoice Ideapad 5 2-in-1 13th Gen Intel Core i5-13420H (16GB RAM/512GB SSD/Windows 11/Office Home 2024/WUXGA IPS/14 (35.5cm)/Touchscreen 2-in-1/3Mon.Game Pass/Grey/1.6kg), 83KX0059IN Laptop</t>
         </is>
       </c>
       <c r="C340" t="inlineStr"/>
       <c r="D340" t="n">
-        <v>44200</v>
+        <v>74490</v>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 (2024), AMD</t>
+          <t>lenovo_thinkbook_14,_amd_ryzen</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 (2024), AMD Ryzen 3 7320U Quad Core - (8GB/512GB SSD/AMD Radeon Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" FHD Display/Arctic Grey/1.57 kg/MS Office 2021</t>
+          <t>Lenovo ThinkBook 14, AMD Ryzen 5 220, 16GB RAM, 1TB SSD, WUXGA IPS 14” (35.56cm), Windows 11 Home, Arctic Grey, 1.36Kg, 21V0A01SIG, Fingerprint, Backlit, 400 Nits, 1Y Warranty, Laptop</t>
         </is>
       </c>
       <c r="C341" t="inlineStr"/>
       <c r="D341" t="n">
-        <v>44490</v>
+        <v>90990</v>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 (2024), AMD</t>
+          <t>lenovo_thinkbook_14,_amd_ryzen</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 (2024), AMD Ryzen 3 7320U Quad Core - (8GB/512GB SSD/AMD Radeon Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" FHD Display/Arctic Grey/1.57 kg/MS Office 2021</t>
+          <t>Lenovo ThinkBook 14, AMD Ryzen 5 220, 16GB RAM, 1TB SSD, WUXGA IPS 14” (35.56cm), Windows 11 Home, Arctic Grey, 1.36Kg, 21V0A01SIG, Fingerprint, Backlit, 400 Nits, 1Y Warranty, Laptop</t>
         </is>
       </c>
       <c r="C342" t="inlineStr"/>
       <c r="D342" t="n">
-        <v>44490</v>
+        <v>92990</v>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 (2024), AMD</t>
+          <t>lenovo_thinkbook_14,_amd_ryzen</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 (2024), AMD Ryzen 3 7320U Quad Core - (8GB/512GB SSD/AMD Radeon Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" FHD Display/Arctic Grey/1.57 kg/MS Office 2021</t>
+          <t>Lenovo ThinkBook 14, AMD Ryzen 5 220, 16GB RAM, 1TB SSD, WUXGA IPS 14” (35.56cm), Windows 11 Home, Arctic Grey, 1.36Kg, 21V0A01SIG, Fingerprint, Backlit, 400 Nits, 1Y Warranty, Laptop</t>
         </is>
       </c>
       <c r="C343" t="inlineStr"/>
       <c r="D343" t="n">
-        <v>44500</v>
+        <v>92990</v>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 (2024), AMD</t>
+          <t>Lenovo ThinkBook 15 G5 AMD</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 (2024), AMD Ryzen 3 7320U Quad Core - (8GB/512GB SSD/AMD Radeon Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" FHD Display/Arctic Grey/1.57 kg/MS Office 2021</t>
+          <t>Lenovo ThinkBook 15 G5 AMD Ryzen 7 7730U 15.6" FHD Antiglare 250 Nits Thin and Light Laptop (8GB RAM/512GB SSD/Windows 11 Home/Fingerprint Reader/Backlit/Mineral Grey/1 Year Onsite/1.7 kg), 21JFA00BIN</t>
         </is>
       </c>
       <c r="C344" t="inlineStr"/>
       <c r="D344" t="n">
-        <v>49999</v>
+        <v>59999</v>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-22</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 (2024), AMD</t>
+          <t>lenovo_thinkbook_16_amd_ryzen</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 (2024), AMD Ryzen 3 7320U Quad Core - (8GB/512GB SSD/AMD Radeon Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" FHD Display/Arctic Grey/1.57 kg/MS Office 2021</t>
+          <t>Lenovo ThinkBook 16 AMD Ryzen 5 7535HS (8GB RAM/512GB SSD/Win 11 Home/Office 2024/Backlit Keyboard/Fingerprint) 16" WUXGA IPS 300 Nits Thin &amp; Light Laptop/1Y Warranty/Aluminium Top/1.7kg, 21MWA0BRIN</t>
         </is>
       </c>
       <c r="C345" t="inlineStr"/>
       <c r="D345" t="n">
-        <v>49890</v>
+        <v>65063</v>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon</t>
+          <t>lenovo_thinkbook_16_amd_ryzen</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo ThinkBook 16 AMD Ryzen 5 7535HS (8GB RAM/512GB SSD/Win 11 Home/Office 2024/Backlit Keyboard/Fingerprint) 16" WUXGA IPS 300 Nits Thin &amp; Light Laptop/1Y Warranty/Aluminium Top/1.7kg, 21MWA0BRIN</t>
         </is>
       </c>
       <c r="C346" t="inlineStr"/>
       <c r="D346" t="n">
-        <v>41999</v>
+        <v>65063</v>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon</t>
+          <t>lenovo_thinkbook_16,_amd_ryzen</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo ThinkBook 16, AMD Ryzen 5 7535HS, 16GB RAM, 512GB SSD, WUXGA IPS 16", Windows 11 Home, Office 2024, 1.7kg, 21MWA0BSIN, Backlit Keyboard, Fingerprint, 300 Nits, 1Y Warranty, Aluminium Top Laptop</t>
         </is>
       </c>
       <c r="C347" t="inlineStr"/>
       <c r="D347" t="n">
-        <v>41999</v>
+        <v>84500</v>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon</t>
+          <t>Lenovo ThinkBook 16, Intel Core</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo ThinkBook 16, Intel Core Ultra 9 185H, 16GB RAM, 512GB SSD, WUXGA IPS 16” (40.64cm), Win 11 Home, Arctic Grey, 1.7Kg, 21SKA0J5IG, Fingerprint, Backlit, 300 Nits, 1Y Warranty, AI Powered Laptop</t>
         </is>
       </c>
       <c r="C348" t="inlineStr"/>
       <c r="D348" t="n">
-        <v>41999</v>
+        <v>94990</v>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-20</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon</t>
+          <t>Lenovo V14 Intel Core i3</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo V14 Intel Core i3 13th Gen 14" FHD (1920x1080) Antiglare 250 Nits Thin and Light Laptop (16GB RAM/512GB SSD/Windows 11 Home/Office Home 2024/Iron Grey/1.43 kg), 83A0A0PCIN</t>
         </is>
       </c>
       <c r="C349" t="inlineStr"/>
       <c r="D349" t="n">
-        <v>42999</v>
+        <v>70990</v>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-20</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon</t>
+          <t>Lenovo V14 Intel Core i3</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo V14 Intel Core i3 13th Gen 14" FHD (1920x1080) Antiglare 250 Nits Thin and Light Laptop (16GB RAM/512GB SSD/Windows 11 Home/Office Home 2024/Iron Grey/1.43 kg), 83A0A0PCIN</t>
         </is>
       </c>
       <c r="C350" t="inlineStr"/>
       <c r="D350" t="n">
-        <v>42999</v>
+        <v>70990</v>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon</t>
+          <t>lenovo_v14_intel_core_i3</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo V14 Intel Core i3 13th Gen 14" FHD (1920x1080) Antiglare 250 Nits Thin and Light Laptop (16GB RAM/512GB SSD/Windows 11 Home/Office Home 2024/Iron Grey/1.43 kg), 83A0A0PCIN</t>
         </is>
       </c>
       <c r="C351" t="inlineStr"/>
       <c r="D351" t="n">
-        <v>42999</v>
+        <v>70990</v>
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon</t>
+          <t>lenovo_v15_amd_ryzen_7</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo V15 AMD Ryzen 7 7730U 15.6" (39.62cm) FHD 250 Nits Antiglare Thin and Light Laptop (16GB/512GB SSD/Windows 11/Iron Grey/1.65 Kg) Grey</t>
         </is>
       </c>
       <c r="C352" t="inlineStr"/>
       <c r="D352" t="n">
-        <v>42999</v>
+        <v>64999</v>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon</t>
+          <t>Lenovo V15 G4 (2024), AMD</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo V15 G4 (2024), AMD Ryzen 3 7320U Quad Core - (8GB/512GB SSD/AMD Radeon Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" FHD Display/Arctic Grey/1.57 kg/MS Office 2021</t>
         </is>
       </c>
       <c r="C353" t="inlineStr"/>
       <c r="D353" t="n">
-        <v>42999</v>
+        <v>44200</v>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-05-22</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon</t>
+          <t>Lenovo V15 G4 (2024), AMD</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo V15 G4 (2024), AMD Ryzen 3 7320U Quad Core - (8GB/512GB SSD/AMD Radeon Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" FHD Display/Arctic Grey/1.57 kg/MS Office 2021</t>
         </is>
       </c>
       <c r="C354" t="inlineStr"/>
       <c r="D354" t="n">
-        <v>44999</v>
+        <v>44490</v>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-24</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon</t>
+          <t>Lenovo V15 G4 (2024), AMD</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo V15 G4 (2024), AMD Ryzen 3 7320U Quad Core - (8GB/512GB SSD/AMD Radeon Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" FHD Display/Arctic Grey/1.57 kg/MS Office 2021</t>
         </is>
       </c>
       <c r="C355" t="inlineStr"/>
       <c r="D355" t="n">
-        <v>43999</v>
+        <v>44490</v>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon</t>
+          <t>Lenovo V15 G4 (2024), AMD</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo V15 G4 (2024), AMD Ryzen 3 7320U Quad Core - (8GB/512GB SSD/AMD Radeon Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" FHD Display/Arctic Grey/1.57 kg/MS Office 2021</t>
         </is>
       </c>
       <c r="C356" t="inlineStr"/>
       <c r="D356" t="n">
-        <v>43999</v>
+        <v>44500</v>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon</t>
+          <t>Lenovo V15 G4 (2024), AMD</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo V15 G4 (2024), AMD Ryzen 3 7320U Quad Core - (8GB/512GB SSD/AMD Radeon Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" FHD Display/Arctic Grey/1.57 kg/MS Office 2021</t>
         </is>
       </c>
       <c r="C357" t="inlineStr"/>
       <c r="D357" t="n">
-        <v>43999</v>
+        <v>49999</v>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon</t>
+          <t>Lenovo V15 G4 (2024), AMD</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo V15 G4 (2024), AMD Ryzen 3 7320U Quad Core - (8GB/512GB SSD/AMD Radeon Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" FHD Display/Arctic Grey/1.57 kg/MS Office 2021</t>
         </is>
       </c>
       <c r="C358" t="inlineStr"/>
       <c r="D358" t="n">
-        <v>44999</v>
+        <v>49890</v>
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
@@ -7953,18 +7953,18 @@
       </c>
       <c r="C359" t="inlineStr"/>
       <c r="D359" t="n">
-        <v>44999</v>
+        <v>41999</v>
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>lenovo_v15_g4_amd_athlon</t>
+          <t>Lenovo V15 G4 AMD Athlon</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -7974,18 +7974,18 @@
       </c>
       <c r="C360" t="inlineStr"/>
       <c r="D360" t="n">
-        <v>44999</v>
+        <v>41999</v>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-28</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>lenovo_v15_g4_amd_athlon</t>
+          <t>Lenovo V15 G4 AMD Athlon</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -7995,18 +7995,18 @@
       </c>
       <c r="C361" t="inlineStr"/>
       <c r="D361" t="n">
-        <v>44999</v>
+        <v>41999</v>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>lenovo_v15_g4_amd_athlon</t>
+          <t>Lenovo V15 G4 AMD Athlon</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -8016,18 +8016,18 @@
       </c>
       <c r="C362" t="inlineStr"/>
       <c r="D362" t="n">
-        <v>44999</v>
+        <v>42999</v>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>lenovo_v15_g4_amd_athlon</t>
+          <t>Lenovo V15 G4 AMD Athlon</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -8037,996 +8037,1353 @@
       </c>
       <c r="C363" t="inlineStr"/>
       <c r="D363" t="n">
-        <v>44999</v>
+        <v>42999</v>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen</t>
+          <t>Lenovo V15 G4 AMD Athlon</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C364" t="inlineStr"/>
       <c r="D364" t="n">
-        <v>49999</v>
+        <v>42999</v>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen</t>
+          <t>Lenovo V15 G4 AMD Athlon</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C365" t="inlineStr"/>
       <c r="D365" t="n">
-        <v>52760</v>
+        <v>42999</v>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen</t>
+          <t>Lenovo V15 G4 AMD Athlon</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C366" t="inlineStr"/>
       <c r="D366" t="n">
-        <v>52300</v>
+        <v>42999</v>
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen</t>
+          <t>Lenovo V15 G4 AMD Athlon</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C367" t="inlineStr"/>
       <c r="D367" t="n">
-        <v>52490</v>
+        <v>44999</v>
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen</t>
+          <t>Lenovo V15 G4 AMD Athlon</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C368" t="inlineStr"/>
       <c r="D368" t="n">
-        <v>52300</v>
+        <v>43999</v>
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen</t>
+          <t>Lenovo V15 G4 AMD Athlon</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C369" t="inlineStr"/>
       <c r="D369" t="n">
-        <v>52890</v>
+        <v>43999</v>
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen</t>
+          <t>Lenovo V15 G4 AMD Athlon</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C370" t="inlineStr"/>
       <c r="D370" t="n">
-        <v>53999</v>
+        <v>43999</v>
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen</t>
+          <t>Lenovo V15 G4 AMD Athlon</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C371" t="inlineStr"/>
       <c r="D371" t="n">
-        <v>53999</v>
+        <v>44999</v>
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-12</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen</t>
+          <t>Lenovo V15 G4 AMD Athlon</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C372" t="inlineStr"/>
       <c r="D372" t="n">
-        <v>54790</v>
+        <v>44999</v>
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>lenovo_v15_g4_amd_ryzen</t>
+          <t>lenovo_v15_g4_amd_athlon</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C373" t="inlineStr"/>
       <c r="D373" t="n">
-        <v>54740</v>
+        <v>44999</v>
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>lenovo_v15_g6_amd_ryzen</t>
+          <t>lenovo_v15_g4_amd_athlon</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Lenovo V15 G6 AMD Ryzen 7 170 (Coequal 7735HS) 15.6" (39.62cm) FHD Thin and Light Business Laptop (16GB RAM DDR5/ 512GB SSD/Windows 11/ MS Office 2024/ AMD Radeon Graphics/Luna Grey/ 1.6 kg)</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C374" t="inlineStr"/>
       <c r="D374" t="n">
-        <v>64999</v>
+        <v>44999</v>
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Lenovo Yoga Slim 7 (Smartchoice)</t>
+          <t>lenovo_v15_g4_amd_athlon</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Lenovo Yoga Slim 7 (Smartchoice) Aura Edition, Intel Core Ultra 5 226V, 16GB RAM, 1TB SSD, WUXGA OLED, Copilot+ AI PC, 40 TOPS, 14"/35.5cm, Windows 11, Office 2024, Grey, 1.19Kg, 83JX005FIN, AI Laptop</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C375" t="inlineStr"/>
       <c r="D375" t="n">
-        <v>99990</v>
+        <v>44999</v>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>Lenovo Yoga Slim 7 (Smartchoice)</t>
+          <t>lenovo_v15_g4_amd_athlon</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Lenovo Yoga Slim 7 (Smartchoice) Aura Edition, Intel Core Ultra 5 226V, 16GB RAM, 1TB SSD, WUXGA OLED, Copilot+ AI PC, 40 TOPS, 14"/35.5cm, Windows 11, Office 2024, Grey, 1.19Kg, 83JX005FIN, AI Laptop</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C376" t="inlineStr"/>
       <c r="D376" t="n">
-        <v>105939</v>
+        <v>44999</v>
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>Lenovo Yoga Slim 7, Intel</t>
+          <t>lenovo_v15_g4_amd_athlon</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Lenovo Yoga Slim 7, Intel Core Ultra 5 125H, 16GB RAM, 512GB SSD, AI PC, WUXGA-OLED, 14"/35.5cm, Windows 11, Microsoft 365 Basic + Office 2024, Grey, 1.39Kg, 83CV00DFIN, AI Powered Laptop</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C377" t="inlineStr"/>
       <c r="D377" t="n">
-        <v>77990</v>
+        <v>44999</v>
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-08-04</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Lenovo Yoga Slim 7, Intel</t>
+          <t>Lenovo V15 G4 AMD Ryzen</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Lenovo Yoga Slim 7, Intel Core Ultra 5 125H, 16GB RAM, 512GB SSD, AI PC, WUXGA-OLED, 14"/35.5cm, Windows 11, Microsoft 365 Basic + Office 2024, Grey, 1.39Kg, 83CV00DFIN, AI Powered Laptop</t>
+          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
         </is>
       </c>
       <c r="C378" t="inlineStr"/>
       <c r="D378" t="n">
-        <v>84990</v>
+        <v>49999</v>
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-21</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Lenovo {SmartChoice Chromebook, Intel Celeron</t>
+          <t>Lenovo V15 G4 AMD Ryzen</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Lenovo {SmartChoice Chromebook, Intel Celeron N4500, 4GB RAM, 64GB eMMC, HD, 11.6"/29.46cm, Chrome OS, Blue, 1.21Kg, 2Wx2 Stereo Speakers, HD Camera, 82UY0014HA, Laptop</t>
+          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
         </is>
       </c>
       <c r="C379" t="inlineStr"/>
       <c r="D379" t="n">
-        <v>21990</v>
+        <v>52760</v>
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-24</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>Lenovo {SmartChoice Chromebook, Intel Celeron</t>
+          <t>Lenovo V15 G4 AMD Ryzen</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Lenovo {SmartChoice Chromebook, Intel Celeron N4500, 4GB RAM, 64GB eMMC, HD, 11.6"/29.46cm, Chrome OS, Blue, 1.21Kg, 2Wx2 Stereo Speakers, HD Camera, 82UY0014HA, Laptop</t>
+          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
         </is>
       </c>
       <c r="C380" t="inlineStr"/>
       <c r="D380" t="n">
-        <v>17990</v>
+        <v>52300</v>
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>msi_cyborg_15,_intel_12th</t>
+          <t>Lenovo V15 G4 AMD Ryzen</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>MSI Cyborg 15, Intel 12th Gen. i5-12450H, 40CM FHD 144Hz Gaming Laptop (16GB/512GB NVMe SSD/Windows 11 Home/MSO 2021/NVIDIA GeForce RTX 3050, GDDR6 6GB/Translucent Black/1.9Kg) A12UDX-1468IN</t>
+          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
         </is>
       </c>
       <c r="C381" t="inlineStr"/>
       <c r="D381" t="n">
-        <v>72990</v>
+        <v>52490</v>
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>primebook_2_max_(2026)_|</t>
+          <t>Lenovo V15 G4 AMD Ryzen</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Primebook 2 Max (2026) | 8GB RAM, 256GB UFS Storage | 15.6-Inch Full HD IPS Display | 12hrs Battery | MediaTek Helio G99 | Android 15 (PrimeOS 3.0) | Backlit Keyboard | in-Built AI (Gray)</t>
+          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
         </is>
       </c>
       <c r="C382" t="inlineStr"/>
       <c r="D382" t="n">
-        <v>29990</v>
+        <v>52300</v>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-27</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Samsung Galaxy Book6 (Gray, 16GB</t>
+          <t>Lenovo V15 G4 AMD Ryzen</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Samsung Galaxy Book6 (Gray, 16GB RAM, 1TB SSD) | Intel Core Ultra 5 (Series 3) | 16" WUXGA+ Display with Touchscreen | 24Hrs Battery Life | 120 Hz Refresh Rate | Dolby Atmos Stereo Speakers | AI PC</t>
+          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
         </is>
       </c>
       <c r="C383" t="inlineStr"/>
       <c r="D383" t="n">
-        <v>146990</v>
+        <v>52890</v>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-31</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>Thomson NEO 14.1 Inch IN-P14C</t>
+          <t>Lenovo V15 G4 AMD Ryzen</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Thomson NEO 14.1 Inch IN-P14C Intel Celeron Dual Core N4020 Processor &amp; Window 11 Home Notebook (4 GB RAM DDR4/ 128 GB SSD/Numeric Touch Pad/Thin &amp; Light Weight/Silver)</t>
+          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
         </is>
       </c>
       <c r="C384" t="inlineStr"/>
       <c r="D384" t="n">
-        <v>12990</v>
+        <v>53999</v>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>Thomson NEO 14.1 Inch IN-P14C</t>
+          <t>Lenovo V15 G4 AMD Ryzen</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Thomson NEO 14.1 Inch IN-P14C Intel Celeron Dual Core N4020 Processor &amp; Window 11 Home Notebook (4 GB RAM DDR4/ 128 GB SSD/Numeric Touch Pad/Thin &amp; Light Weight/Silver)</t>
+          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
         </is>
       </c>
       <c r="C385" t="inlineStr"/>
       <c r="D385" t="n">
-        <v>12990</v>
+        <v>53999</v>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-06-02</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>Thomson NEO 14.1 Inch IN-P14C</t>
+          <t>Lenovo V15 G4 AMD Ryzen</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Thomson NEO 14.1 Inch IN-P14C Intel Celeron Dual Core N4020 Processor &amp; Window 11 Home Notebook (4 GB RAM DDR4/ 128 GB SSD/Numeric Touch Pad/Thin &amp; Light Weight/Silver)</t>
+          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
         </is>
       </c>
       <c r="C386" t="inlineStr"/>
       <c r="D386" t="n">
-        <v>22990</v>
+        <v>54790</v>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>Thomson NEO 14.1 Inch IN-P14C</t>
+          <t>lenovo_v15_g4_amd_ryzen</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Thomson NEO 14.1 Inch IN-P14C Intel Celeron Dual Core N4020 Processor &amp; Window 11 Home Notebook (4 GB RAM DDR4/ 128 GB SSD/Numeric Touch Pad/Thin &amp; Light Weight/Silver)</t>
+          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
         </is>
       </c>
       <c r="C387" t="inlineStr"/>
       <c r="D387" t="n">
-        <v>22990</v>
+        <v>54740</v>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>acer Aspire 3, Intel Core</t>
+          <t>lenovo_v15_g6_amd_ryzen</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>acer Aspire 3, Intel Core Celeron N4500, 12GB LPDDR4X RAM, 512GB SSD, HD, 15.6"/39.62cm, Windows 11 Home, Pure Silver, 1.5KG, A325-45, Thin and Light Laptop</t>
+          <t>Lenovo V15 G6 AMD Ryzen 7 170 (Coequal 7735HS) 15.6" (39.62cm) FHD Thin and Light Business Laptop (16GB RAM DDR5/ 512GB SSD/Windows 11/ MS Office 2024/ AMD Radeon Graphics/Luna Grey/ 1.6 kg)</t>
         </is>
       </c>
       <c r="C388" t="inlineStr"/>
       <c r="D388" t="n">
-        <v>39890</v>
+        <v>64999</v>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>acer Aspire Lite, AMD Ryzen</t>
+          <t>lenovo_v15_g6_amd_ryzen</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>acer Aspire Lite, AMD Ryzen 3 5300U Processor, 16 GB RAM, 512GB SSD, Full HD, 15.6"/39.62cm, Windows 11 Home, Steel Gray, 1.59KG, AL15-41, Metal Body, Premium Thin and Light Laptop</t>
+          <t>Lenovo V15 G6 AMD Ryzen 7 170 (Coequal 7735HS) 15.6" (39.62cm) FHD Thin and Light Business Laptop (16GB RAM DDR5/ 512GB SSD/Windows 11/ MS Office 2024/ AMD Radeon Graphics/Luna Grey/ 1.6 kg)</t>
         </is>
       </c>
       <c r="C389" t="inlineStr"/>
       <c r="D389" t="n">
-        <v>42990</v>
+        <v>66999</v>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-08-04</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD</t>
+          <t>Lenovo Yoga Slim 7 (Smartchoice)</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
+          <t>Lenovo Yoga Slim 7 (Smartchoice) Aura Edition, Intel Core Ultra 5 226V, 16GB RAM, 1TB SSD, WUXGA OLED, Copilot+ AI PC, 40 TOPS, 14"/35.5cm, Windows 11, Office 2024, Grey, 1.19Kg, 83JX005FIN, AI Laptop</t>
         </is>
       </c>
       <c r="C390" t="inlineStr"/>
       <c r="D390" t="n">
-        <v>45990</v>
+        <v>99990</v>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-15</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD</t>
+          <t>Lenovo Yoga Slim 7 (Smartchoice)</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
+          <t>Lenovo Yoga Slim 7 (Smartchoice) Aura Edition, Intel Core Ultra 5 226V, 16GB RAM, 1TB SSD, WUXGA OLED, Copilot+ AI PC, 40 TOPS, 14"/35.5cm, Windows 11, Office 2024, Grey, 1.19Kg, 83JX005FIN, AI Laptop</t>
         </is>
       </c>
       <c r="C391" t="inlineStr"/>
       <c r="D391" t="n">
-        <v>45990</v>
+        <v>105939</v>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-19</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD</t>
+          <t>Lenovo Yoga Slim 7, Intel</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
+          <t>Lenovo Yoga Slim 7, Intel Core Ultra 5 125H, 16GB RAM, 512GB SSD, AI PC, WUXGA-OLED, 14"/35.5cm, Windows 11, Microsoft 365 Basic + Office 2024, Grey, 1.39Kg, 83CV00DFIN, AI Powered Laptop</t>
         </is>
       </c>
       <c r="C392" t="inlineStr"/>
       <c r="D392" t="n">
-        <v>45990</v>
+        <v>77990</v>
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-05-15</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD</t>
+          <t>Lenovo Yoga Slim 7, Intel</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
+          <t>Lenovo Yoga Slim 7, Intel Core Ultra 5 125H, 16GB RAM, 512GB SSD, AI PC, WUXGA-OLED, 14"/35.5cm, Windows 11, Microsoft 365 Basic + Office 2024, Grey, 1.39Kg, 83CV00DFIN, AI Powered Laptop</t>
         </is>
       </c>
       <c r="C393" t="inlineStr"/>
       <c r="D393" t="n">
-        <v>43990</v>
+        <v>84990</v>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-19</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD</t>
+          <t>Lenovo {SmartChoice Chromebook, Intel Celeron</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
+          <t>Lenovo {SmartChoice Chromebook, Intel Celeron N4500, 4GB RAM, 64GB eMMC, HD, 11.6"/29.46cm, Chrome OS, Blue, 1.21Kg, 2Wx2 Stereo Speakers, HD Camera, 82UY0014HA, Laptop</t>
         </is>
       </c>
       <c r="C394" t="inlineStr"/>
       <c r="D394" t="n">
-        <v>43990</v>
+        <v>21990</v>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD</t>
+          <t>Lenovo {SmartChoice Chromebook, Intel Celeron</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
+          <t>Lenovo {SmartChoice Chromebook, Intel Celeron N4500, 4GB RAM, 64GB eMMC, HD, 11.6"/29.46cm, Chrome OS, Blue, 1.21Kg, 2Wx2 Stereo Speakers, HD Camera, 82UY0014HA, Laptop</t>
         </is>
       </c>
       <c r="C395" t="inlineStr"/>
       <c r="D395" t="n">
-        <v>43990</v>
+        <v>17990</v>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-08</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD</t>
+          <t>msi_cyborg_15,_intel_12th</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
+          <t>MSI Cyborg 15, Intel 12th Gen. i5-12450H, 40CM FHD 144Hz Gaming Laptop (16GB/512GB NVMe SSD/Windows 11 Home/MSO 2021/NVIDIA GeForce RTX 3050, GDDR6 6GB/Translucent Black/1.9Kg) A12UDX-1468IN</t>
         </is>
       </c>
       <c r="C396" t="inlineStr"/>
       <c r="D396" t="n">
-        <v>43990</v>
+        <v>72990</v>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD</t>
+          <t>primebook_2_max_(2026)_|</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
+          <t>Primebook 2 Max (2026) | 8GB RAM, 256GB UFS Storage | 15.6-Inch Full HD IPS Display | 12hrs Battery | MediaTek Helio G99 | Android 15 (PrimeOS 3.0) | Backlit Keyboard | in-Built AI (Gray)</t>
         </is>
       </c>
       <c r="C397" t="inlineStr"/>
       <c r="D397" t="n">
-        <v>43990</v>
+        <v>29990</v>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop ModeI 7410 Laptop |</t>
+          <t>primebook_2_max_(2026)_|</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop ModeI 7410 Laptop | InteI Core i5 10th Gen | 16GB DDR4 RAM | 256GB SSD | 14" Full HD Display | Win 10 Pro | InteI UHD Graphics 620 | 3 Months Seller Warranty | A+ Condition (Refab)</t>
+          <t>Primebook 2 Max (2026) | 8GB RAM, 256GB UFS Storage | 15.6-Inch Full HD IPS Display | 12hrs Battery | MediaTek Helio G99 | Android 15 (PrimeOS 3.0) | Backlit Keyboard | in-Built AI (Gray)</t>
         </is>
       </c>
       <c r="C398" t="inlineStr"/>
       <c r="D398" t="n">
-        <v>27299</v>
+        <v>31990</v>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-08-04</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5</t>
+          <t>primebook_2_pro_(2026)_|</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5 11th Gen Processor |8GB DDR4 RAM |256GB SSD |14" FHD Display | Win10 | A+ Condition Laptop (Refab)</t>
+          <t>Primebook 2 Pro (2026) | 8GB RAM, 128GB UFS Storage | 14.1-Inch FHD IPS Display | 14 Hours Battery | MediaTek Helio G99 | Android 15 (PrimeOS 3.0) | Backlit Keyboard | in-Built AI (Gray)</t>
         </is>
       </c>
       <c r="C399" t="inlineStr"/>
       <c r="D399" t="n">
-        <v>26999</v>
+        <v>26990</v>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-08-04</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5</t>
+          <t>Samsung Galaxy Book6 (Gray, 16GB</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5 11th Gen Processor |8GB DDR4 RAM |256GB SSD |14" FHD Display | Win10 | A+ Condition Laptop (Refab)</t>
+          <t>Samsung Galaxy Book6 (Gray, 16GB RAM, 1TB SSD) | Intel Core Ultra 5 (Series 3) | 16" WUXGA+ Display with Touchscreen | 24Hrs Battery Life | 120 Hz Refresh Rate | Dolby Atmos Stereo Speakers | AI PC</t>
         </is>
       </c>
       <c r="C400" t="inlineStr"/>
       <c r="D400" t="n">
-        <v>26400</v>
+        <v>146990</v>
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5</t>
+          <t>Thomson NEO 14.1 Inch IN-P14C</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5 11th Gen Processor |8GB DDR4 RAM |256GB SSD |14" FHD Display | Win10 | A+ Condition Laptop (Refab)</t>
+          <t>Thomson NEO 14.1 Inch IN-P14C Intel Celeron Dual Core N4020 Processor &amp; Window 11 Home Notebook (4 GB RAM DDR4/ 128 GB SSD/Numeric Touch Pad/Thin &amp; Light Weight/Silver)</t>
         </is>
       </c>
       <c r="C401" t="inlineStr"/>
       <c r="D401" t="n">
-        <v>28599</v>
+        <v>12990</v>
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5</t>
+          <t>Thomson NEO 14.1 Inch IN-P14C</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5 11th Gen Processor |8GB DDR4 RAM |256GB SSD |14" FHD Display | Win10 | A+ Condition Laptop (Refab)</t>
+          <t>Thomson NEO 14.1 Inch IN-P14C Intel Celeron Dual Core N4020 Processor &amp; Window 11 Home Notebook (4 GB RAM DDR4/ 128 GB SSD/Numeric Touch Pad/Thin &amp; Light Weight/Silver)</t>
         </is>
       </c>
       <c r="C402" t="inlineStr"/>
       <c r="D402" t="n">
-        <v>28999</v>
+        <v>12990</v>
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5</t>
+          <t>Thomson NEO 14.1 Inch IN-P14C</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5 11th Gen Processor |8GB DDR4 RAM |256GB SSD |14" FHD Display | Win10 | A+ Condition Laptop (Refab)</t>
+          <t>Thomson NEO 14.1 Inch IN-P14C Intel Celeron Dual Core N4020 Processor &amp; Window 11 Home Notebook (4 GB RAM DDR4/ 128 GB SSD/Numeric Touch Pad/Thin &amp; Light Weight/Silver)</t>
         </is>
       </c>
       <c r="C403" t="inlineStr"/>
       <c r="D403" t="n">
-        <v>31990</v>
+        <v>22990</v>
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-08</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5</t>
+          <t>Thomson NEO 14.1 Inch IN-P14C</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5 11th Gen Processor |8GB DDR4 RAM |256GB SSD |14" FHD Display | Win10 | A+ Condition Laptop (Refab)</t>
+          <t>Thomson NEO 14.1 Inch IN-P14C Intel Celeron Dual Core N4020 Processor &amp; Window 11 Home Notebook (4 GB RAM DDR4/ 128 GB SSD/Numeric Touch Pad/Thin &amp; Light Weight/Silver)</t>
         </is>
       </c>
       <c r="C404" t="inlineStr"/>
       <c r="D404" t="n">
-        <v>35490</v>
+        <v>22990</v>
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-10</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5</t>
+          <t>acer Aspire 3, Intel Core</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5 11th Gen Processor |8GB DDR4 RAM |256GB SSD |14" FHD Display | Win10 | A+ Condition Laptop (Refab)</t>
+          <t>acer Aspire 3, Intel Core Celeron N4500, 12GB LPDDR4X RAM, 512GB SSD, HD, 15.6"/39.62cm, Windows 11 Home, Pure Silver, 1.5KG, A325-45, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C405" t="inlineStr"/>
       <c r="D405" t="n">
-        <v>37490</v>
+        <v>39890</v>
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Model E5570 Laptop | Core</t>
+          <t>acer Aspire Lite, AMD Ryzen</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Model E5570 Laptop | Core i7 6th Gen | 8GB Fast RAM | 256GB SSD | 15.6" HD Display | HD Graphics | Win 10 | WiFi| (Pre-Owned &amp; Tested)</t>
+          <t>acer Aspire Lite, AMD Ryzen 3 5300U Processor, 16 GB RAM, 512GB SSD, Full HD, 15.6"/39.62cm, Windows 11 Home, Steel Gray, 1.59KG, AL15-41, Metal Body, Premium Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C406" t="inlineStr"/>
       <c r="D406" t="n">
-        <v>20599</v>
+        <v>42990</v>
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-04-16</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>𝗛𝗣𝗣𝗿𝗼𝗯𝗼𝗼𝗸Model 430 G3 Business Laptop</t>
+          <t>acer SmartChoice Aspire Lite, AMD</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>𝗛𝗣𝗣𝗿𝗼𝗯𝗼𝗼𝗸Model 430 G3 Business Laptop | InteI i5 6th Gen | 8GB RAM | 256GB SSD | WiFi | Webcam | Win10 Pro (Refab)</t>
+          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C407" t="inlineStr"/>
       <c r="D407" t="n">
-        <v>20299</v>
+        <v>45990</v>
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>𝗛𝗣𝗣𝗿𝗼𝗯𝗼𝗼𝗸Model 430 G3 Business Laptop</t>
+          <t>acer SmartChoice Aspire Lite, AMD</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>𝗛𝗣𝗣𝗿𝗼𝗯𝗼𝗼𝗸Model 430 G3 Business Laptop | 𝗜𝗡𝗧𝗘𝗟i5 6th Gen | 8GB RAM | 256GB SSD | WiFi | Webcam | Win10 Pro (Refab)</t>
+          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C408" t="inlineStr"/>
       <c r="D408" t="n">
-        <v>20499</v>
+        <v>45990</v>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-04-16</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>𝗛𝗣𝗣𝗿𝗼𝗯𝗼𝗼𝗸Model 430 G3 Business Laptop</t>
+          <t>acer SmartChoice Aspire Lite, AMD</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>𝗛𝗣𝗣𝗿𝗼𝗯𝗼𝗼𝗸Model 430 G3 Business Laptop | 𝗜𝗡𝗧𝗘𝗟i5 6th Gen | 8GB RAM | 256GB SSD | WiFi | Webcam | Win10 Pro (Refab)</t>
+          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C409" t="inlineStr"/>
       <c r="D409" t="n">
-        <v>19999</v>
+        <v>45990</v>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>𝗟𝗲𝗻𝗼𝘃𝗼model_l14_laptop|_core_i5</t>
+          <t>acer SmartChoice Aspire Lite, AMD</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>𝗟𝗲𝗻𝗼𝘃𝗼Model L14 Laptop| Core i5 11th Gen Processor | 16GB Fast RAM/ 256GB SSD | 14″ HD Display | A+ (Pre-Owned &amp; Tested)</t>
+          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C410" t="inlineStr"/>
       <c r="D410" t="n">
+        <v>43990</v>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>acer SmartChoice Aspire Lite, AMD</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr"/>
+      <c r="D411" t="n">
+        <v>43990</v>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>acer SmartChoice Aspire Lite, AMD</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr"/>
+      <c r="D412" t="n">
+        <v>43990</v>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>acer SmartChoice Aspire Lite, AMD</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr"/>
+      <c r="D413" t="n">
+        <v>43990</v>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>acer SmartChoice Aspire Lite, AMD</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr"/>
+      <c r="D414" t="n">
+        <v>43990</v>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop ModeI 7410 Laptop |</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop ModeI 7410 Laptop | InteI Core i5 10th Gen | 16GB DDR4 RAM | 256GB SSD | 14" Full HD Display | Win 10 Pro | InteI UHD Graphics 620 | 3 Months Seller Warranty | A+ Condition (Refab)</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr"/>
+      <c r="D415" t="n">
+        <v>27299</v>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5 11th Gen Processor |8GB DDR4 RAM |256GB SSD |14" FHD Display | Win10 | A+ Condition Laptop (Refab)</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr"/>
+      <c r="D416" t="n">
+        <v>26999</v>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5 11th Gen Processor |8GB DDR4 RAM |256GB SSD |14" FHD Display | Win10 | A+ Condition Laptop (Refab)</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr"/>
+      <c r="D417" t="n">
+        <v>26400</v>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5 11th Gen Processor |8GB DDR4 RAM |256GB SSD |14" FHD Display | Win10 | A+ Condition Laptop (Refab)</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr"/>
+      <c r="D418" t="n">
+        <v>28599</v>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5 11th Gen Processor |8GB DDR4 RAM |256GB SSD |14" FHD Display | Win10 | A+ Condition Laptop (Refab)</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr"/>
+      <c r="D419" t="n">
+        <v>28999</v>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5 11th Gen Processor |8GB DDR4 RAM |256GB SSD |14" FHD Display | Win10 | A+ Condition Laptop (Refab)</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr"/>
+      <c r="D420" t="n">
+        <v>31990</v>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5 11th Gen Processor |8GB DDR4 RAM |256GB SSD |14" FHD Display | Win10 | A+ Condition Laptop (Refab)</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr"/>
+      <c r="D421" t="n">
+        <v>35490</v>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5 11th Gen Processor |8GB DDR4 RAM |256GB SSD |14" FHD Display | Win10 | A+ Condition Laptop (Refab)</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr"/>
+      <c r="D422" t="n">
+        <v>37490</v>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Model E5570 Laptop | Core</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Model E5570 Laptop | Core i7 6th Gen | 8GB Fast RAM | 256GB SSD | 15.6" HD Display | HD Graphics | Win 10 | WiFi| (Pre-Owned &amp; Tested)</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr"/>
+      <c r="D423" t="n">
+        <v>20599</v>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>𝗛𝗣𝗣𝗿𝗼𝗯𝗼𝗼𝗸Model 430 G3 Business Laptop</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>𝗛𝗣𝗣𝗿𝗼𝗯𝗼𝗼𝗸Model 430 G3 Business Laptop | InteI i5 6th Gen | 8GB RAM | 256GB SSD | WiFi | Webcam | Win10 Pro (Refab)</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr"/>
+      <c r="D424" t="n">
+        <v>20299</v>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>𝗛𝗣𝗣𝗿𝗼𝗯𝗼𝗼𝗸Model 430 G3 Business Laptop</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>𝗛𝗣𝗣𝗿𝗼𝗯𝗼𝗼𝗸Model 430 G3 Business Laptop | 𝗜𝗡𝗧𝗘𝗟i5 6th Gen | 8GB RAM | 256GB SSD | WiFi | Webcam | Win10 Pro (Refab)</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr"/>
+      <c r="D425" t="n">
+        <v>20499</v>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>𝗛𝗣𝗣𝗿𝗼𝗯𝗼𝗼𝗸Model 430 G3 Business Laptop</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>𝗛𝗣𝗣𝗿𝗼𝗯𝗼𝗼𝗸Model 430 G3 Business Laptop | 𝗜𝗡𝗧𝗘𝗟i5 6th Gen | 8GB RAM | 256GB SSD | WiFi | Webcam | Win10 Pro (Refab)</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr"/>
+      <c r="D426" t="n">
+        <v>19999</v>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>𝗟𝗲𝗻𝗼𝘃𝗼model_l14_laptop|_core_i5</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>𝗟𝗲𝗻𝗼𝘃𝗼Model L14 Laptop| Core i5 11th Gen Processor | 16GB Fast RAM/ 256GB SSD | 14″ HD Display | A+ (Pre-Owned &amp; Tested)</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr"/>
+      <c r="D427" t="n">
         <v>31599</v>
       </c>
-      <c r="E410" t="inlineStr">
+      <c r="E427" t="inlineStr">
         <is>
           <t>2026-07-21</t>
         </is>

--- a/amazon_products.xlsx
+++ b/amazon_products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E445"/>
+  <dimension ref="A1:E466"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1622,21 +1622,21 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>asus_vivobook_16_(2026),smartchoice,intel_core</t>
+          <t>asus_vivobook_15,_smartchoice,intel_core</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ASUS Vivobook 16 (2026),Smartchoice,Intel Core Ultra 5 325 (Series 3), Intel iGPU,16GB RAM,512GB SSD,FHD+, 16"(40 cm),Win11,M365 Basic(1Y),Office 24,Quiet Blue,1.88 kg,X1607AA-MB037WS, Copilot+ AI PC</t>
+          <t>ASUS Vivobook 15, Smartchoice,Intel Core i5 13th Gen 13420H,16GB RAM, 512GB SSD, FHD 15.6",Windows 11, Office Home 2024, Quiet Blue, 1.70 kg, X1502VA-BQ836WS,Intel UHD iGPU, M365 Basic (1Year)* Laptop</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="n">
-        <v>94990</v>
+        <v>63990</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -1657,49 +1657,49 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ASUS Vivobook 16, 13th Gen,</t>
+          <t>asus_vivobook_16_(2026),smartchoice,intel_core</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ASUS Vivobook 16, 13th Gen, Intel Core i5-13420H,16GB RAM,512GB SSD,FHD (1920 x 1200) OLED,Win 11,M365 Basic (1Year)*,Backlit Keyboard,Office 2024,Silver,1.88 kg,X1605VA-SH1952WS, Thin &amp; Light Laptop</t>
+          <t>ASUS Vivobook 16 (2026),Smartchoice,Intel Core Ultra 5 325 (Series 3), Intel iGPU,16GB RAM,512GB SSD,FHD+, 16"(40 cm),Win11,M365 Basic(1Y),Office 24,Quiet Blue,1.88 kg,X1607AA-MB037WS, Copilot+ AI PC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="n">
-        <v>61990</v>
+        <v>94990</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-08-05</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>asus_vivobook_16,_smartchoice,_intel</t>
+          <t>ASUS Vivobook 16, 13th Gen,</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>ASUS Vivobook 16, Smartchoice, Intel Core Ultra 5 Series 2, 16GB RAM, 512GB SSD, FHD+ 16", Windows 11, Office Home 2024, Silver, 1.88kg, X1607CA-MB142WS, Intel iGPU, M365 Basic (1Year), AI Laptop</t>
+          <t>ASUS Vivobook 16, 13th Gen, Intel Core i5-13420H,16GB RAM,512GB SSD,FHD (1920 x 1200) OLED,Win 11,M365 Basic (1Year)*,Backlit Keyboard,Office 2024,Silver,1.88 kg,X1605VA-SH1952WS, Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="n">
-        <v>77990</v>
+        <v>61990</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-05-14</t>
         </is>
       </c>
     </row>
@@ -1720,24 +1720,24 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>asus_vivobook_16,smartchoice,_13th_gen,</t>
+          <t>asus_vivobook_16,_smartchoice,_intel</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ASUS Vivobook 16,Smartchoice, 13th Gen, Intel Core i5-13420H,16GB RAM,512GB SSD,FHD, OLED,Win 11,M365 Basic (1Y),Backlit Keyboard,Office 2024,Silver,1.88 kg,X1605VA-SH1952WS, Thin &amp; Light Laptop</t>
+          <t>ASUS Vivobook 16, Smartchoice, Intel Core Ultra 5 Series 2, 16GB RAM, 512GB SSD, FHD+ 16", Windows 11, Office Home 2024, Silver, 1.88kg, X1607CA-MB142WS, Intel iGPU, M365 Basic (1Year), AI Laptop</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="n">
-        <v>67990</v>
+        <v>77990</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -1748,546 +1748,546 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>asus_vivobook_go_14_(2026),amd</t>
+          <t>asus_vivobook_16,_snapdragon_x,</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>ASUS Vivobook Go 14 (2026),AMD Ryzen 3 30 Processor,AMD Radeon iGPU,8GB RAM,512GB SSD,FHD,14" (35.5 cm),Windows 11,M365 Basic(1Y)* Office 2024,Cool Silver,1.38 Kg,E1404FA-EB1224WS,Thin &amp; Light Laptop</t>
+          <t>ASUS Vivobook 16, Snapdragon X, 16GB RAM, 512GB SSD, FHD+ 16", Windows 11, Office Home 2024, Quiet Blue, 1.88kg, X1607QA-MB049WS, Qualcomm Adreno iGPU, 45TOPS, M365 Basic (1Year)* Laptop</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="n">
-        <v>44990</v>
+        <v>61990</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ASUS Vivobook Go 14, AMD</t>
+          <t>asus_vivobook_16,smartchoice,_13th_gen,</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ASUS Vivobook Go 14, AMD Ryzen 5 7520U, 16GB RAM, 512GB SSD, FHD, 14", 60Hz,42WHrs, Windows 11, M365 Basic (1Year)*,Office Home 2024, Mixed Black, 1.38 kg, E1404FA-EB774WS, Thin &amp; Light Laptop</t>
+          <t>ASUS Vivobook 16,Smartchoice, 13th Gen, Intel Core i5-13420H,16GB RAM,512GB SSD,FHD, OLED,Win 11,M365 Basic (1Y),Backlit Keyboard,Office 2024,Silver,1.88 kg,X1605VA-SH1952WS, Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="n">
-        <v>52990</v>
+        <v>67990</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-08-05</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>asus_vivobook_s14,smartchoice,amd_ryzen_ai</t>
+          <t>asus_vivobook_16,smartchoice,_13th_gen,</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>ASUS Vivobook S14,Smartchoice,AMD Ryzen AI 5 330,16GB RAM,512GB SSD,OLED,14",Win11,Office24,M365 Basic (1Yr),Matte Gray,1.4Kg,M3407KA-SF044WS,50 Tops,Metallic Design Laptop,Next-Gen AI Laptop,Copilot+</t>
+          <t>ASUS Vivobook 16,Smartchoice, 13th Gen, Intel Core i5-13420H,16GB RAM,512GB SSD,FHD, OLED,Win 11,M365 Basic (1Y),Backlit Keyboard,Office 2024,Silver,1.88 kg,X1605VA-SH1952WS, Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="n">
-        <v>71990</v>
+        <v>67990</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ASUS Vivobook S14,Smartchoice,AMD Ryzen AI</t>
+          <t>asus_vivobook_go_14_(2026),amd</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ASUS Vivobook S14,Smartchoice,AMD Ryzen AI 7 350,16GB RAM,1TB SSD,OLED,14",Windows 11, Office24,M365 Basic (1Yr)*, Matte Gray,1.4Kg, M3407KA-SF049WS,50 Tops,Metallic Design,Next-Gen AI Laptop,Copilot+</t>
+          <t>ASUS Vivobook Go 14 (2026),AMD Ryzen 3 30 Processor,AMD Radeon iGPU,8GB RAM,512GB SSD,FHD,14" (35.5 cm),Windows 11,M365 Basic(1Y)* Office 2024,Cool Silver,1.38 Kg,E1404FA-EB1224WS,Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="n">
-        <v>88990</v>
+        <v>44990</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-08-04</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ASUS Vivobook S14,Smartchoice,AMD Ryzen AI</t>
+          <t>ASUS Vivobook Go 14, AMD</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>ASUS Vivobook S14,Smartchoice,AMD Ryzen AI 7 350,16GB RAM,1TB SSD,OLED,14",Windows 11, Office24,M365 Basic (1Yr)*, Matte Gray,1.4Kg, M3407KA-SF049WS,50 Tops,Metallic Design,Next-Gen AI Laptop,Copilot+</t>
+          <t>ASUS Vivobook Go 14, AMD Ryzen 5 7520U, 16GB RAM, 512GB SSD, FHD, 14", 60Hz,42WHrs, Windows 11, M365 Basic (1Year)*,Office Home 2024, Mixed Black, 1.38 kg, E1404FA-EB774WS, Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="n">
-        <v>88990</v>
+        <v>52990</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ASUS Vivobook S14,Smartchoice,AMD Ryzen AI</t>
+          <t>asus_vivobook_s14,smartchoice,amd_ryzen_ai</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>ASUS Vivobook S14,Smartchoice,AMD Ryzen AI 7 350,16GB RAM,1TB SSD,OLED,14",Windows 11, Office24,M365 Basic (1Yr)*, Matte Gray,1.4Kg, M3407KA-SF049WS,50 Tops,Metallic Design,Next-Gen AI Laptop,Copilot+</t>
+          <t>ASUS Vivobook S14,Smartchoice,AMD Ryzen AI 5 330,16GB RAM,512GB SSD,OLED,14",Win11,Office24,M365 Basic (1Yr),Matte Gray,1.4Kg,M3407KA-SF044WS,50 Tops,Metallic Design Laptop,Next-Gen AI Laptop,Copilot+</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="n">
-        <v>83990</v>
+        <v>71990</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-08-05</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>asus_vivobook_s16_oled,_intel</t>
+          <t>asus_vivobook_s14,smartchoice,amd_ryzen_ai</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ASUS Vivobook S16 OLED, Intel Core Ultra 5 225H, 16GB RAM, 512GB SSD, FHD 16", Win 11, Office 2024, Cool Silver, 1.7Kg, S3607CA-SH071WS,Intel iGPU, 70Whr, M365 Basic(1Year) Metallic Design Laptop</t>
+          <t>ASUS Vivobook S14,Smartchoice,AMD Ryzen AI 5 330,16GB RAM,512GB SSD,OLED,14",Win11,Office24,M365 Basic (1Yr),Matte Gray,1.4Kg,M3407KA-SF044WS,50 Tops,Metallic Design Laptop,Next-Gen AI Laptop,Copilot+</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="n">
-        <v>92990</v>
+        <v>71990</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>asus_vivobook_s16_oled,_intel</t>
+          <t>ASUS Vivobook S14,Smartchoice,AMD Ryzen AI</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ASUS Vivobook S16 OLED, Intel Core Ultra 5 225H, 16GB RAM, 512GB SSD, FHD 16", Win 11, Office 2024, Cool Silver, 1.7Kg, S3607CA-SH071WS,Intel iGPU, 70Whr, M365 Basic(1Year) Metallic Design Laptop</t>
+          <t>ASUS Vivobook S14,Smartchoice,AMD Ryzen AI 7 350,16GB RAM,1TB SSD,OLED,14",Windows 11, Office24,M365 Basic (1Yr)*, Matte Gray,1.4Kg, M3407KA-SF049WS,50 Tops,Metallic Design,Next-Gen AI Laptop,Copilot+</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="n">
-        <v>92990</v>
+        <v>88990</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>asus_vivobook_s16,14th_gen,_intel</t>
+          <t>ASUS Vivobook S14,Smartchoice,AMD Ryzen AI</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ASUS Vivobook S16,14th Gen, Intel Core 5-210H,Metallic Design Laptop(Intel UHD iGPU/16GB RAM/512GB SSD/FHD+/16"/144Hz/Windows 11/M365 Basic(1Year)*/Office Home 2024/Silver/1.7Kg) S3607VA-RP114WS</t>
+          <t>ASUS Vivobook S14,Smartchoice,AMD Ryzen AI 7 350,16GB RAM,1TB SSD,OLED,14",Windows 11, Office24,M365 Basic (1Yr)*, Matte Gray,1.4Kg, M3407KA-SF049WS,50 Tops,Metallic Design,Next-Gen AI Laptop,Copilot+</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="n">
-        <v>68990</v>
+        <v>88990</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-04-16</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ASUS Vivobook S16,Intel Core Ultra</t>
+          <t>ASUS Vivobook S14,Smartchoice,AMD Ryzen AI</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>ASUS Vivobook S16,Intel Core Ultra 5 225H,AI PC(Intel Arc iGPU/16GB RAM/512GB SSD/FHD/16/60Hz/Backlit Keyboard/70Whr/Windows 11/M365 Basic(1Year)*/Office Home 2024/Cool Silver/1.7 Kg) S3607CA-SH071WS</t>
+          <t>ASUS Vivobook S14,Smartchoice,AMD Ryzen AI 7 350,16GB RAM,1TB SSD,OLED,14",Windows 11, Office24,M365 Basic (1Yr)*, Matte Gray,1.4Kg, M3407KA-SF049WS,50 Tops,Metallic Design,Next-Gen AI Laptop,Copilot+</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="n">
-        <v>81990</v>
+        <v>83990</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-21</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ASUS Vivobook S16,Intel Core Ultra</t>
+          <t>asus_vivobook_s16_oled,_intel</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>ASUS Vivobook S16,Intel Core Ultra 5 225H,AI PC(Intel Arc iGPU/16GB RAM/512GB SSD/FHD/16/60Hz/Backlit Keyboard/70Whr/Windows 11/M365 Basic(1Year)*/Office Home 2024/Cool Silver/1.7 Kg) S3607CA-SH071WS</t>
+          <t>ASUS Vivobook S16 OLED, Intel Core Ultra 5 225H, 16GB RAM, 512GB SSD, FHD 16", Win 11, Office 2024, Cool Silver, 1.7Kg, S3607CA-SH071WS,Intel iGPU, 70Whr, M365 Basic(1Year) Metallic Design Laptop</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="n">
-        <v>79990</v>
+        <v>92990</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ASUS Zenbook 14 (2026),Smartchoice,Intel Core</t>
+          <t>asus_vivobook_s16_oled,_intel</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ASUS Zenbook 14 (2026),Smartchoice,Intel Core Ultra 7 255H,32GB RAM,1TB SSD,OLED,Touchscreen,14"(35.5 cm),Win 11,M365 Basic(1Y)* Office 24,Ponder Blue,1.28 Kg,UX3405CA-QL1015WS,Thin &amp; Light Laptop</t>
+          <t>ASUS Vivobook S16 OLED, Intel Core Ultra 5 225H, 16GB RAM, 512GB SSD, FHD 16", Win 11, Office 2024, Cool Silver, 1.7Kg, S3607CA-SH071WS,Intel iGPU, 70Whr, M365 Basic(1Year) Metallic Design Laptop</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="n">
-        <v>119990</v>
+        <v>92990</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-08-05</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ASUS Zenbook 14 (2026),Smartchoice,Intel Core</t>
+          <t>asus_vivobook_s16,14th_gen,_intel</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>ASUS Zenbook 14 (2026),Smartchoice,Intel Core Ultra 7 255H,32GB RAM,1TB SSD,OLED,Touchscreen,14"(35.5 cm),Win 11,M365 Basic(1Y)* Office 24,Ponder Blue,1.28 Kg,UX3405CA-QL1015WS,Thin &amp; Light Laptop</t>
+          <t>ASUS Vivobook S16,14th Gen, Intel Core 5-210H,Metallic Design Laptop(Intel UHD iGPU/16GB RAM/512GB SSD/FHD+/16"/144Hz/Windows 11/M365 Basic(1Year)*/Office Home 2024/Silver/1.7Kg) S3607VA-RP114WS</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="n">
-        <v>119990</v>
+        <v>68990</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ASUS Zenbook 14 (2026),Smartchoice,Intel Core</t>
+          <t>ASUS Vivobook S16,Intel Core Ultra</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>ASUS Zenbook 14 (2026),Smartchoice,Intel Core Ultra 9 285H,32GB RAM,1TB SSD,OLED,Touchscreen,14"(35.5 cm),Win 11,M365 Basic(1Y)* Office 24,Foggy Silver,1.28 Kg,UX3405CA-QL1113WS,Thin &amp; Light Laptop</t>
+          <t>ASUS Vivobook S16,Intel Core Ultra 5 225H,AI PC(Intel Arc iGPU/16GB RAM/512GB SSD/FHD/16/60Hz/Backlit Keyboard/70Whr/Windows 11/M365 Basic(1Year)*/Office Home 2024/Cool Silver/1.7 Kg) S3607CA-SH071WS</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="n">
-        <v>124990</v>
+        <v>81990</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ASUS Zenbook 14, Intel Core</t>
+          <t>ASUS Vivobook S16,Intel Core Ultra</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>ASUS Zenbook 14, Intel Core Ultra 5 Series 2, 16GB RAM, 1TB SSD, 3K OLED 14", Touchscreen, Win 11, Office Home 2024, Ponder Blue, 1.28kg, UX3405CA-PZ162WS, Intel Arc iGPU, M365 Basic (1Year)* Laptop</t>
+          <t>ASUS Vivobook S16,Intel Core Ultra 5 225H,AI PC(Intel Arc iGPU/16GB RAM/512GB SSD/FHD/16/60Hz/Backlit Keyboard/70Whr/Windows 11/M365 Basic(1Year)*/Office Home 2024/Cool Silver/1.7 Kg) S3607CA-SH071WS</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="n">
-        <v>106990</v>
+        <v>79990</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ASUS Zenbook 14, Smartchoice, Intel</t>
+          <t>ASUS Zenbook 14 (2026),Smartchoice,Intel Core</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>ASUS Zenbook 14, Smartchoice, Intel Core Ultra 5 Series 2,16GB RAM,1TB SSD,3K OLED 14", Touchscreen, Win 11, Office Home 2024,Blue, 1.28kg, UX3405CA-PZ162WS, Intel Arc iGPU, M365 Basic (1Year)* Laptop</t>
+          <t>ASUS Zenbook 14 (2026),Smartchoice,Intel Core Ultra 7 255H,32GB RAM,1TB SSD,OLED,Touchscreen,14"(35.5 cm),Win 11,M365 Basic(1Y)* Office 24,Ponder Blue,1.28 Kg,UX3405CA-QL1015WS,Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="n">
-        <v>108990</v>
+        <v>119990</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-22</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ASUS Zenbook 14, Smartchoice, Intel</t>
+          <t>ASUS Zenbook 14 (2026),Smartchoice,Intel Core</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>ASUS Zenbook 14, Smartchoice, Intel Core Ultra 5 Series 2,16GB RAM,1TB SSD,3K OLED 14", Touchscreen, Win 11, Office Home 2024,Blue, 1.28kg, UX3405CA-PZ162WS, Intel iGPU, M365 Basic (1Year)* Laptop</t>
+          <t>ASUS Zenbook 14 (2026),Smartchoice,Intel Core Ultra 7 255H,32GB RAM,1TB SSD,OLED,Touchscreen,14"(35.5 cm),Win 11,M365 Basic(1Y)* Office 24,Ponder Blue,1.28 Kg,UX3405CA-QL1015WS,Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="n">
-        <v>114990</v>
+        <v>119990</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>asus_zenbook_14,smartchoice,intel_core_ultra</t>
+          <t>ASUS Zenbook 14 (2026),Smartchoice,Intel Core</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ASUS Zenbook 14,Smartchoice,Intel Core Ultra 5 (Series 2),16GB,1TB,3K OLED Touch Screen,14",120Hz,Win 11,M365 Basic (1Y)*,Office 2024, Silver,1.28 kg,UX3405CA-PZ345WS,Thin &amp; Light Laptop</t>
+          <t>ASUS Zenbook 14 (2026),Smartchoice,Intel Core Ultra 9 285H,32GB RAM,1TB SSD,OLED,Touchscreen,14"(35.5 cm),Win 11,M365 Basic(1Y)* Office 24,Foggy Silver,1.28 Kg,UX3405CA-QL1113WS,Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
       <c r="D81" t="n">
-        <v>117990</v>
+        <v>124990</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>asus_zenbook_s14_(2026),smartchoice,intel_core</t>
+          <t>ASUS Zenbook 14, Intel Core</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>ASUS Zenbook S14 (2026),Smartchoice,Intel Core Ultra 5 226V,Intel Arc iGPU,16GB/512GB,3K OLED,Touchscreen,14"(35.5 cm),Windows 11,M365 Basic(1Y),Office 2024,Gray,1.2 Kg,UX5406SA-PZ658WS,Copilot+ PC</t>
+          <t>ASUS Zenbook 14, Intel Core Ultra 5 Series 2, 16GB RAM, 1TB SSD, 3K OLED 14", Touchscreen, Win 11, Office Home 2024, Ponder Blue, 1.28kg, UX3405CA-PZ162WS, Intel Arc iGPU, M365 Basic (1Year)* Laptop</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="n">
-        <v>134990</v>
+        <v>106990</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-05-14</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Acer Aspire 3 Laptop Intel</t>
+          <t>ASUS Zenbook 14, Smartchoice, Intel</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Acer Aspire 3 Laptop Intel Core Celeron N4500 Processor Laptop (8 GB LPDDR4X SDRAM/256 GB SSD/Win11 Home/38 WHR/HD Webcam) A325-45 with 39.63 cm (15.6") HD Display, Pure Silver, 1.5 KG</t>
+          <t>ASUS Zenbook 14, Smartchoice, Intel Core Ultra 5 Series 2,16GB RAM,1TB SSD,3K OLED 14", Touchscreen, Win 11, Office Home 2024,Blue, 1.28kg, UX3405CA-PZ162WS, Intel Arc iGPU, M365 Basic (1Year)* Laptop</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="n">
-        <v>36990</v>
+        <v>108990</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Acer Aspire 3 Laptop Intel</t>
+          <t>ASUS Zenbook 14, Smartchoice, Intel</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Acer Aspire 3 Laptop Intel Core Celeron N4500 Processor Laptop (8 GB LPDDR4X SDRAM/256 GB SSD/Win11 Home/38 WHR/HD Webcam) A325-45 with 39.63 cm (15.6") HD Display, Pure Silver, 1.5 KG</t>
+          <t>ASUS Zenbook 14, Smartchoice, Intel Core Ultra 5 Series 2,16GB RAM,1TB SSD,3K OLED 14", Touchscreen, Win 11, Office Home 2024,Blue, 1.28kg, UX3405CA-PZ162WS, Intel iGPU, M365 Basic (1Year)* Laptop</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="n">
-        <v>36990</v>
+        <v>114990</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Acer Aspire Lite 12th Gen,</t>
+          <t>asus_zenbook_14,smartchoice,intel_core_ultra</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Acer Aspire Lite 12th Gen, Intel Core i5-12450H, Office 2024 + M365 Basic, 12GB RAM/512GB SSD, 39.62cm 15.6" FHD IPS Display, Win 11 Home, Pure Silver, 1.7KG,AL15-52H, Backlit KB, Thin &amp; Light Laptop</t>
+          <t>ASUS Zenbook 14,Smartchoice,Intel Core Ultra 5 (Series 2),16GB,1TB,3K OLED Touch Screen,14",120Hz,Win 11,M365 Basic (1Y)*,Office 2024, Silver,1.28 kg,UX3405CA-PZ345WS,Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="n">
-        <v>52990</v>
+        <v>117990</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Acer Aspire Lite 12th Gen,</t>
+          <t>asus_zenbook_a14_oled_(2025),smartchoice,qualcomm</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Acer Aspire Lite 12th Gen, Intel Core i5-12450H, Office 2024 + M365 Basic, 12GB RAM/512GB SSD, 39.62cm 15.6" FHD IPS Display, Win 11 Home, Pure Silver, 1.7KG,AL15-52H, Backlit KB, Thin &amp; Light Laptop</t>
+          <t>ASUS Zenbook A14 OLED (2025),Smartchoice,Qualcomm Snapdragon X,Copilot+PC,0.9kg Light-Weight,14"(35 cm),32hrs Battery Life*,16GB,512GB,Win 11,MSO 2024,M365 Basic-1yr,AI PC,Metal Body,UX3407QA-QD259WS</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="n">
-        <v>47990</v>
+        <v>86990</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Acer Aspire Lite 12th Gen,</t>
+          <t>asus_zenbook_s14_(2026),smartchoice,intel_core</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Acer Aspire Lite 12th Gen, Intel Core i5-12450H, Office 2024 + M365 Basic, 12GB RAM/512GB SSD, 39.62cm 15.6" FHD IPS Display, Win 11 Home, Pure Silver, 1.7KG,AL15-52H, Backlit KB, Thin &amp; Light Laptop</t>
+          <t>ASUS Zenbook S14 (2026),Smartchoice,Intel Core Ultra 5 226V,Intel Arc iGPU,16GB/512GB,3K OLED,Touchscreen,14"(35.5 cm),Windows 11,M365 Basic(1Y),Office 2024,Gray,1.2 Kg,UX5406SA-PZ658WS,Copilot+ PC</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="n">
-        <v>53990</v>
+        <v>134990</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Acer Aspire Lite 12th Gen,</t>
+          <t>Acer Aspire 3 Laptop Intel</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Acer Aspire Lite 12th Gen, Intel Core i5-12450H, Office 2024 + M365 Basic, 12GB RAM/512GB SSD, 39.62cm 15.6" FHD IPS Display, Win 11 Home, Pure Silver, 1.7KG,AL15-52H, Backlit KB, Thin &amp; Light Laptop</t>
+          <t>Acer Aspire 3 Laptop Intel Core Celeron N4500 Processor Laptop (8 GB LPDDR4X SDRAM/256 GB SSD/Win11 Home/38 WHR/HD Webcam) A325-45 with 39.63 cm (15.6") HD Display, Pure Silver, 1.5 KG</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="n">
-        <v>53990</v>
+        <v>36990</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Acer Aspire Lite 12th Gen,</t>
+          <t>Acer Aspire 3 Laptop Intel</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Acer Aspire Lite 12th Gen, Intel Core i5-12450H, Office 2024 + M365 Basic, 12GB RAM/512GB SSD, 39.62cm 15.6" FHD IPS Display, Win 11 Home, Pure Silver, 1.7KG,AL15-52H, Backlit KB, Thin &amp; Light Laptop</t>
+          <t>Acer Aspire 3 Laptop Intel Core Celeron N4500 Processor Laptop (8 GB LPDDR4X SDRAM/256 GB SSD/Win11 Home/38 WHR/HD Webcam) A325-45 with 39.63 cm (15.6") HD Display, Pure Silver, 1.5 KG</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="n">
-        <v>53990</v>
+        <v>36990</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
@@ -2304,11 +2304,11 @@
       </c>
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="n">
-        <v>53990</v>
+        <v>52990</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-08</t>
         </is>
       </c>
     </row>
@@ -2325,11 +2325,11 @@
       </c>
       <c r="C91" t="inlineStr"/>
       <c r="D91" t="n">
-        <v>49990</v>
+        <v>47990</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-17</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-19</t>
         </is>
       </c>
     </row>
@@ -2367,137 +2367,137 @@
       </c>
       <c r="C93" t="inlineStr"/>
       <c r="D93" t="n">
-        <v>50990</v>
+        <v>53990</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-20</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Acer Aspire One, Intel Core</t>
+          <t>Acer Aspire Lite 12th Gen,</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Acer Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X RAM/ 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
+          <t>Acer Aspire Lite 12th Gen, Intel Core i5-12450H, Office 2024 + M365 Basic, 12GB RAM/512GB SSD, 39.62cm 15.6" FHD IPS Display, Win 11 Home, Pure Silver, 1.7KG,AL15-52H, Backlit KB, Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="n">
-        <v>34990</v>
+        <v>53990</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-21</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Acer Aspire One, Intel Core</t>
+          <t>Acer Aspire Lite 12th Gen,</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Acer Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X RAM/ 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
+          <t>Acer Aspire Lite 12th Gen, Intel Core i5-12450H, Office 2024 + M365 Basic, 12GB RAM/512GB SSD, 39.62cm 15.6" FHD IPS Display, Win 11 Home, Pure Silver, 1.7KG,AL15-52H, Backlit KB, Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="n">
-        <v>34990</v>
+        <v>53990</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-22</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Acer Aspire One, Intel Core</t>
+          <t>Acer Aspire Lite 12th Gen,</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Acer Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X RAM/ 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
+          <t>Acer Aspire Lite 12th Gen, Intel Core i5-12450H, Office 2024 + M365 Basic, 12GB RAM/512GB SSD, 39.62cm 15.6" FHD IPS Display, Win 11 Home, Pure Silver, 1.7KG,AL15-52H, Backlit KB, Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="n">
-        <v>34990</v>
+        <v>49990</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-27</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Acer Aspire One, Intel Core</t>
+          <t>Acer Aspire Lite 12th Gen,</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Acer Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X RAM/ 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
+          <t>Acer Aspire Lite 12th Gen, Intel Core i5-12450H, Office 2024 + M365 Basic, 12GB RAM/512GB SSD, 39.62cm 15.6" FHD IPS Display, Win 11 Home, Pure Silver, 1.7KG,AL15-52H, Backlit KB, Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="n">
-        <v>33990</v>
+        <v>53990</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Acer Aspire One, Intel Core</t>
+          <t>Acer Aspire Lite 12th Gen,</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Acer Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X RAM/ 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
+          <t>Acer Aspire Lite 12th Gen, Intel Core i5-12450H, Office 2024 + M365 Basic, 12GB RAM/512GB SSD, 39.62cm 15.6" FHD IPS Display, Win 11 Home, Pure Silver, 1.7KG,AL15-52H, Backlit KB, Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="n">
-        <v>33990</v>
+        <v>50990</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Acer Aspire One, Intel Core</t>
+          <t>acer_aspire_lite,_intel_core</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Acer Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X RAM/ 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
+          <t>Acer Aspire Lite, Intel Core 3-100U Processor, 8GB DDR4 RAM/512GB SSD, 39.62cm/15.6" FHD IPS Display, Win 11 Home, Steel Gray, 1.59 Kg,AL15-53, Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
       <c r="D99" t="n">
-        <v>35990</v>
+        <v>57990</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -2514,11 +2514,11 @@
       </c>
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="n">
-        <v>35990</v>
+        <v>34990</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-08</t>
         </is>
       </c>
     </row>
@@ -2535,11 +2535,11 @@
       </c>
       <c r="C101" t="inlineStr"/>
       <c r="D101" t="n">
-        <v>35990</v>
+        <v>34990</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
@@ -2556,11 +2556,11 @@
       </c>
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="n">
-        <v>35990</v>
+        <v>34990</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-10</t>
         </is>
       </c>
     </row>
@@ -2572,432 +2572,432 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Acer Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X RAM/ 512GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
+          <t>Acer Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X RAM/ 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="n">
-        <v>38990</v>
+        <v>33990</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>acer_chromebook,_mediatek_kompanio_540</t>
+          <t>Acer Aspire One, Intel Core</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Acer Chromebook, MediaTek Kompanio 540 Octa-Core Processor, 4GB RAM, 64GB eMMC, Full HD, 11.6"/27.94cm Display, Chrome OS, Black, 1.2 KG, C725, Arm Mali G57 Graphics, WiFi 6E Laptop</t>
+          <t>Acer Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X RAM/ 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="n">
-        <v>23990</v>
+        <v>33990</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-05-17</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>acer_one_14_laptop_z14-55m</t>
+          <t>Acer Aspire One, Intel Core</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Acer One 14 Laptop Z14-55M | 14" HD Display | AMD Ryzen 3 7320U | 8GB LPDDR5 RAM | 256GB NVMe SSD | Windows 11 | Thin &amp; Light Design | AMD Radeon Graphics | Silver</t>
+          <t>Acer Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X RAM/ 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="n">
-        <v>38750</v>
+        <v>35990</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-19</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>acer_one_14_laptop_z14-55m</t>
+          <t>Acer Aspire One, Intel Core</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Acer One 14 Laptop Z14-55M | 14" HD Display | AMD Ryzen 3 7320U | 8GB LPDDR5 RAM | 256GB NVMe SSD | Windows 11 | Thin &amp; Light Design | AMD Radeon Graphics | Silver</t>
+          <t>Acer Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X RAM/ 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C106" t="inlineStr"/>
       <c r="D106" t="n">
-        <v>38500</v>
+        <v>35990</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-05-20</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>acer_one_14_laptop_z14-55m</t>
+          <t>Acer Aspire One, Intel Core</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Acer One 14 Laptop Z14-55M | 14" HD Display | AMD Ryzen 3 7320U | 8GB LPDDR5 RAM | 256GB NVMe SSD | Windows 11 | Thin &amp; Light Design | AMD Radeon Graphics | Silver</t>
+          <t>Acer Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X RAM/ 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
       <c r="D107" t="n">
-        <v>38500</v>
+        <v>35990</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-05-21</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>acer_one_14_laptop_z14-55m</t>
+          <t>Acer Aspire One, Intel Core</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Acer One 14 Laptop Z14-55M | 14" HD Display | AMD Ryzen 3 7320U | 8GB LPDDR5 RAM | 256GB NVMe SSD | Windows 11 | Thin &amp; Light Design | AMD Radeon Graphics | Silver</t>
+          <t>Acer Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X RAM/ 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="n">
-        <v>38500</v>
+        <v>35990</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-05-22</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>acer_one_14_laptop_z14-55m</t>
+          <t>Acer Aspire One, Intel Core</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Acer One 14 Laptop Z14-55M | 14" HD Display | AMD Ryzen 3 7320U | 8GB LPDDR5 RAM | 256GB NVMe SSD | Windows 11 | Thin &amp; Light Design | AMD Radeon Graphics | Silver</t>
+          <t>Acer Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X RAM/ 512GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
       <c r="D109" t="n">
-        <v>38500</v>
+        <v>38990</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-05-14</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Acer Smartchoice Aspire One, AMD</t>
+          <t>acer_chromebook,_mediatek_kompanio_540</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Acer Smartchoice Aspire One, AMD Ryzen 3-7320U, 8GB LPDDR5 RAM/ 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.48KG, A114-43, Thin and Light Laptop</t>
+          <t>Acer Chromebook, MediaTek Kompanio 540 Octa-Core Processor, 4GB RAM, 64GB eMMC, Full HD, 11.6"/27.94cm Display, Chrome OS, Black, 1.2 KG, C725, Arm Mali G57 Graphics, WiFi 6E Laptop</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="n">
-        <v>39990</v>
+        <v>23990</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-08-05</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Acer Smartchoice Aspire One, AMD</t>
+          <t>acer_chromebook,_mediatek_kompanio_540</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Acer Smartchoice Aspire One, AMD Ryzen 3-7320U, 8GB LPDDR5 RAM/ 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.48KG, A114-43, Thin and Light Laptop</t>
+          <t>Acer Chromebook, MediaTek Kompanio 540 Octa-Core Processor, 4GB RAM, 64GB eMMC, Full HD, 11.6"/27.94cm Display, Chrome OS, Black, 1.2 KG, C725, Arm Mali G57 Graphics, WiFi 6E Laptop</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
       <c r="D111" t="n">
-        <v>39990</v>
+        <v>23990</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>acer_smartchoice_aspire_one,_amd</t>
+          <t>acer_one_14_laptop_z14-55m</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Acer Smartchoice Aspire One, AMD Ryzen 3-7320U, 8GB LPDDR5 RAM/ 512GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.48KG, A114-43, Thin and Light Laptop</t>
+          <t>Acer One 14 Laptop Z14-55M | 14" HD Display | AMD Ryzen 3 7320U | 8GB LPDDR5 RAM | 256GB NVMe SSD | Windows 11 | Thin &amp; Light Design | AMD Radeon Graphics | Silver</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="n">
-        <v>41990</v>
+        <v>38750</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>acer_smartchoice_aspire_one,_amd</t>
+          <t>acer_one_14_laptop_z14-55m</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Acer Smartchoice Aspire One, AMD Ryzen 3-7320U, 8GB LPDDR5 RAM/ 512GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.48KG, A114-43, Thin and Light Laptop</t>
+          <t>Acer One 14 Laptop Z14-55M | 14" HD Display | AMD Ryzen 3 7320U | 8GB LPDDR5 RAM | 256GB NVMe SSD | Windows 11 | Thin &amp; Light Design | AMD Radeon Graphics | Silver</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
       <c r="D113" t="n">
-        <v>44990</v>
+        <v>38500</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>acer_smartchoice_aspire_one,_amd</t>
+          <t>acer_one_14_laptop_z14-55m</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Acer Smartchoice Aspire One, AMD Ryzen 5-40, 8GB LPDDR5 RAM/ 512GB SSD, 14.0"/35.56cm WXGA Display, Win 11 Home, Pure Silver, 1.48KG, A114-43, Thin and Light Laptop</t>
+          <t>Acer One 14 Laptop Z14-55M | 14" HD Display | AMD Ryzen 3 7320U | 8GB LPDDR5 RAM | 256GB NVMe SSD | Windows 11 | Thin &amp; Light Design | AMD Radeon Graphics | Silver</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
       <c r="D114" t="n">
-        <v>42990</v>
+        <v>38500</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Acer Smartchoice Aspire One, Intel</t>
+          <t>acer_one_14_laptop_z14-55m</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Acer Smartchoice Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X / 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
+          <t>Acer One 14 Laptop Z14-55M | 14" HD Display | AMD Ryzen 3 7320U | 8GB LPDDR5 RAM | 256GB NVMe SSD | Windows 11 | Thin &amp; Light Design | AMD Radeon Graphics | Silver</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
       <c r="D115" t="n">
-        <v>32990</v>
+        <v>38500</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Acer Smartchoice Aspire One, Intel</t>
+          <t>acer_one_14_laptop_z14-55m</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Acer Smartchoice Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X / 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
+          <t>Acer One 14 Laptop Z14-55M | 14" HD Display | AMD Ryzen 3 7320U | 8GB LPDDR5 RAM | 256GB NVMe SSD | Windows 11 | Thin &amp; Light Design | AMD Radeon Graphics | Silver</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="n">
-        <v>32990</v>
+        <v>38500</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-08-04</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Acer Smartchoice Aspire One, Intel</t>
+          <t>acer_one_14_laptop_z14-55m</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Acer Smartchoice Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X / 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
+          <t>Acer One 14 Laptop Z14-55M | 14" HD Display | AMD Ryzen 3 7320U | 8GB LPDDR5 RAM | 256GB NVMe SSD | Windows 11 | Thin &amp; Light Design | AMD Radeon Graphics | Silver</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
       <c r="D117" t="n">
-        <v>32990</v>
+        <v>38490</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Acer Smartchoice Aspire One, Intel</t>
+          <t>Acer Smartchoice Aspire One, AMD</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Acer Smartchoice Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X / 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
+          <t>Acer Smartchoice Aspire One, AMD Ryzen 3-7320U, 8GB LPDDR5 RAM/ 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.48KG, A114-43, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="n">
-        <v>32990</v>
+        <v>39990</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Acer Smartchoice Aspire One, Intel</t>
+          <t>Acer Smartchoice Aspire One, AMD</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Acer Smartchoice Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X / 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
+          <t>Acer Smartchoice Aspire One, AMD Ryzen 3-7320U, 8GB LPDDR5 RAM/ 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.48KG, A114-43, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="n">
-        <v>32990</v>
+        <v>39990</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-12</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Acer Smartchoice Aspire One, Intel</t>
+          <t>acer_smartchoice_aspire_one,_amd</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Acer Smartchoice Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X / 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
+          <t>Acer Smartchoice Aspire One, AMD Ryzen 3-7320U, 8GB LPDDR5 RAM/ 512GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.48KG, A114-43, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
       <c r="D120" t="n">
-        <v>35990</v>
+        <v>41990</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Acer Smartchoice Aspire One, Intel</t>
+          <t>acer_smartchoice_aspire_one,_amd</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Acer Smartchoice Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X / 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
+          <t>Acer Smartchoice Aspire One, AMD Ryzen 3-7320U, 8GB LPDDR5 RAM/ 512GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.48KG, A114-43, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
       <c r="D121" t="n">
-        <v>35990</v>
+        <v>44990</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-08-05</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Acer Smartchoice Aspire One, Intel</t>
+          <t>acer_smartchoice_aspire_one,_amd</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Acer Smartchoice Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X / 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
+          <t>Acer Smartchoice Aspire One, AMD Ryzen 3-7320U, 8GB LPDDR5 RAM/ 512GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.48KG, A114-43, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
       <c r="D122" t="n">
-        <v>35990</v>
+        <v>44990</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>acer_smartchoice_aspire_one,_intel</t>
+          <t>acer_smartchoice_aspire_one,_amd</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Acer Smartchoice Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X / 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
+          <t>Acer Smartchoice Aspire One, AMD Ryzen 5-40, 8GB LPDDR5 RAM/ 512GB SSD, 14.0"/35.56cm WXGA Display, Win 11 Home, Pure Silver, 1.48KG, A114-43, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
       <c r="D123" t="n">
-        <v>33990</v>
+        <v>42990</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>acer_smartchoice_aspire_one,_intel</t>
+          <t>Acer Smartchoice Aspire One, Intel</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3018,11 +3018,11 @@
       </c>
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="n">
-        <v>35990</v>
+        <v>32990</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>
@@ -3034,310 +3034,310 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Acer Smartchoice Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X / 512GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
+          <t>Acer Smartchoice Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X / 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
       <c r="D125" t="n">
-        <v>34990</v>
+        <v>32990</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-05-24</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>acer_smartchoice_aspire_one,_intel</t>
+          <t>Acer Smartchoice Aspire One, Intel</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Acer Smartchoice Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X / 512GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
+          <t>Acer Smartchoice Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X / 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
       <c r="D126" t="n">
-        <v>37990</v>
+        <v>32990</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>acer_smartchoice_aspire_one,_intel</t>
+          <t>Acer Smartchoice Aspire One, Intel</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Acer Smartchoice Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X / 512GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
+          <t>Acer Smartchoice Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X / 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
       <c r="D127" t="n">
-        <v>39990</v>
+        <v>32990</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-05-27</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Acer Swift Go 14 AI</t>
+          <t>Acer Smartchoice Aspire One, Intel</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Acer Swift Go 14 AI PC, Qualcomm SnapdragonX Plus X1P-42-100,Office 2024 + M365 Basic,(16GB LPDDR5X/ 512GB SSD/14.5-inch WUXGA//Qualcomm Adreno/1440p IR Camera with Shutter/Win11) 1.32 kg, Steel Grey.</t>
+          <t>Acer Smartchoice Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X / 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
       <c r="D128" t="n">
-        <v>79990</v>
+        <v>32990</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-28</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>acer_travellite_thin_laptop_amd</t>
+          <t>Acer Smartchoice Aspire One, Intel</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Acer TravelLite Thin Laptop AMD Ryzen 5 7430U (6-Core) 16GB RAM, 512GB SSD 14" Full HD Anti-Glare Display Privacy Shutter Windows 11 MS Office Metal Body 1.34Kg Black 30M Warranty</t>
+          <t>Acer Smartchoice Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X / 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
       <c r="D129" t="n">
-        <v>53450</v>
+        <v>35990</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Neo 13″</t>
+          <t>Acer Smartchoice Aspire One, Intel</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Citrus</t>
+          <t>Acer Smartchoice Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X / 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
       <c r="D130" t="n">
-        <v>65000</v>
+        <v>35990</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Neo 13″</t>
+          <t>Acer Smartchoice Aspire One, Intel</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Indigo</t>
+          <t>Acer Smartchoice Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X / 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
       <c r="D131" t="n">
-        <v>67900</v>
+        <v>35990</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Neo 13″</t>
+          <t>acer_smartchoice_aspire_one,_intel</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Indigo</t>
+          <t>Acer Smartchoice Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X / 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
       <c r="D132" t="n">
-        <v>65000</v>
+        <v>33990</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-08-04</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Neo 13″</t>
+          <t>acer_smartchoice_aspire_one,_intel</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Indigo</t>
+          <t>Acer Smartchoice Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X / 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="n">
-        <v>65700</v>
+        <v>35990</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-08-05</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Neo 13″</t>
+          <t>acer_smartchoice_aspire_one,_intel</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Indigo</t>
+          <t>Acer Smartchoice Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X / 256GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C134" t="inlineStr"/>
       <c r="D134" t="n">
-        <v>65000</v>
+        <v>35990</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Neo 13″</t>
+          <t>Acer Smartchoice Aspire One, Intel</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Indigo</t>
+          <t>Acer Smartchoice Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X / 512GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C135" t="inlineStr"/>
       <c r="D135" t="n">
-        <v>65000</v>
+        <v>34990</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-07-12</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Neo 13″</t>
+          <t>acer_smartchoice_aspire_one,_intel</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Indigo</t>
+          <t>Acer Smartchoice Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X / 512GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C136" t="inlineStr"/>
       <c r="D136" t="n">
-        <v>65000</v>
+        <v>37990</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Neo 13″</t>
+          <t>acer_smartchoice_aspire_one,_intel</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Silver</t>
+          <t>Acer Smartchoice Aspire One, Intel Core Celeron N4500, Office 2024 + M365 Basic, 12GB LPDDR4X / 512GB SSD, 14.0"/35.56cm TN HD Display, Win 11 Home, Pure Silver, 1.3KG, A114-45, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
       <c r="D137" t="n">
-        <v>65000</v>
+        <v>39990</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Neo 13″</t>
+          <t>Acer Swift Go 14 AI</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Silver</t>
+          <t>Acer Swift Go 14 AI PC, Qualcomm SnapdragonX Plus X1P-42-100,Office 2024 + M365 Basic,(16GB LPDDR5X/ 512GB SSD/14.5-inch WUXGA//Qualcomm Adreno/1440p IR Camera with Shutter/Win11) 1.32 kg, Steel Grey.</t>
         </is>
       </c>
       <c r="C138" t="inlineStr"/>
       <c r="D138" t="n">
-        <v>65000</v>
+        <v>79990</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Neo 13″</t>
+          <t>acer_travellite_thin_laptop_amd</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Silver</t>
+          <t>Acer TravelLite Thin Laptop AMD Ryzen 5 7430U (6-Core) 16GB RAM, 512GB SSD 14" Full HD Anti-Glare Display Privacy Shutter Windows 11 MS Office Metal Body 1.34Kg Black 30M Warranty</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
       <c r="D139" t="n">
-        <v>65700</v>
+        <v>53450</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -3349,16 +3349,16 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Silver</t>
+          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Citrus</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
       <c r="D140" t="n">
-        <v>67900</v>
+        <v>65000</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
@@ -3370,16 +3370,16 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Silver</t>
+          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Indigo</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
       <c r="D141" t="n">
-        <v>65000</v>
+        <v>67900</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3391,16 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Silver</t>
+          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Indigo</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
       <c r="D142" t="n">
-        <v>64990</v>
+        <v>65000</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
@@ -3412,16 +3412,16 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Silver</t>
+          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Indigo</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
       <c r="D143" t="n">
-        <v>63990</v>
+        <v>65700</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-05-28</t>
         </is>
       </c>
     </row>
@@ -3433,16 +3433,16 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Silver</t>
+          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Indigo</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
       <c r="D144" t="n">
-        <v>63990</v>
+        <v>65000</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -3454,436 +3454,436 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Silver</t>
+          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Indigo</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
       <c r="D145" t="n">
-        <v>63990</v>
+        <v>65000</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Pro Laptop</t>
+          <t>Apple 2026 MacBook Neo 13″</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Pro Laptop with M5 Max chip with 18‑core CPU and 40‑core GPU: Built for AI, 41.05 cm (16.2″) Liquid Retina XDR Display, 48GB Unified Memory, 2TB SSD Storage; Space Black</t>
+          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Indigo</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
       <c r="D146" t="n">
-        <v>499900</v>
+        <v>65000</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Pro Laptop</t>
+          <t>Apple 2026 MacBook Neo 13″</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Pro Laptop with M5 Max chip with 18‑core CPU and 40‑core GPU: Built for AI, 41.05 cm (16.2″) Liquid Retina XDR Display, 48GB Unified Memory, 2TB SSD Storage; Space Black</t>
+          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Silver</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
       <c r="D147" t="n">
-        <v>499900</v>
+        <v>65000</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-24</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Pro Laptop</t>
+          <t>Apple 2026 MacBook Neo 13″</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Pro Laptop with M5 Max chip with 18‑core CPU and 40‑core GPU: Built for AI, 41.05 cm (16.2″) Liquid Retina XDR Display, 48GB Unified Memory, 2TB SSD Storage; Space Black</t>
+          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Silver</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
       <c r="D148" t="n">
-        <v>499900</v>
+        <v>65000</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Pro Laptop</t>
+          <t>Apple 2026 MacBook Neo 13″</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Pro Laptop with M5 Pro chip with 15‑core CPU and 16‑core GPU: Built for AI, 35.97 cm (14.2″) Liquid Retina XDR Display, 24GB Unified Memory, 1TB SSD Storage; Silver</t>
+          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Silver</t>
         </is>
       </c>
       <c r="C149" t="inlineStr"/>
       <c r="D149" t="n">
-        <v>234900</v>
+        <v>65700</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-27</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Pro Laptop</t>
+          <t>Apple 2026 MacBook Neo 13″</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Apple 2026 MacBook Pro Laptop with M5 Pro chip with 15‑core CPU and 16‑core GPU: Built for AI, 35.97 cm (14.2″) Liquid Retina XDR Display, 24GB Unified Memory, 1TB SSD Storage; Silver</t>
+          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Silver</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
       <c r="D150" t="n">
-        <v>227400</v>
+        <v>67900</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-05-31</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>BrowseBook 14.1" FHD IPS Laptop</t>
+          <t>Apple 2026 MacBook Neo 13″</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>BrowseBook 14.1" FHD IPS Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB RAM | 128GB SSD | Windows 11 | 38Wh | 1.3kg | Grey</t>
+          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Silver</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
       <c r="D151" t="n">
-        <v>13990</v>
+        <v>65000</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-06-02</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>BrowseBook 14.1" FHD IPS Laptop</t>
+          <t>Apple 2026 MacBook Neo 13″</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>BrowseBook 14.1" FHD IPS Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB RAM | 128GB SSD | Windows 11 | 38Wh | 1.3kg | Grey</t>
+          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Silver</t>
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="n">
-        <v>13990</v>
+        <v>64990</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>BrowseBook 14.1" FHD IPS Laptop</t>
+          <t>Apple 2026 MacBook Neo 13″</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>BrowseBook 14.1" FHD IPS Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB RAM | 128GB SSD | Windows 11 | 38Wh | 1.3kg | Grey</t>
+          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Silver</t>
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
       <c r="D153" t="n">
-        <v>13990</v>
+        <v>63990</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>BrowseBook 14.1" FHD IPS Laptop</t>
+          <t>Apple 2026 MacBook Neo 13″</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>BrowseBook 14.1" FHD IPS Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB RAM | 128GB SSD | Windows 11 | 38Wh | 1.3kg | Grey</t>
+          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Silver</t>
         </is>
       </c>
       <c r="C154" t="inlineStr"/>
       <c r="D154" t="n">
-        <v>20990</v>
+        <v>63990</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>BrowseBook 14.1" FHD IPS Laptop</t>
+          <t>Apple 2026 MacBook Neo 13″</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>BrowseBook 14.1" FHD IPS Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 8GB RAM | 256GB SSD | Windows 11 | 38Wh | 1.3kg | Grey</t>
+          <t>Apple 2026 MacBook Neo 13″ Laptop with A18 Pro chip: Built for AI and Apple Intelligence, Liquid Retina Display, 8GB Unified Memory, 256GB SSD Storage, 1080p FaceTime HD Camera; Silver</t>
         </is>
       </c>
       <c r="C155" t="inlineStr"/>
       <c r="D155" t="n">
-        <v>18990</v>
+        <v>63990</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-06-12</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron) Laptop,</t>
+          <t>Apple 2026 MacBook Pro Laptop</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core 3 100U Processor, 8GB DDR4, 512 SSD, 15.6" NT FHD 120Hz IPS AG 250 nit Display, Win 11 + Office H&amp;S 2024, Carbon Black, Thin &amp; Light- 1.63Kg</t>
+          <t>Apple 2026 MacBook Pro Laptop with M5 Max chip with 18‑core CPU and 40‑core GPU: Built for AI, 41.05 cm (16.2″) Liquid Retina XDR Display, 48GB Unified Memory, 2TB SSD Storage; Space Black</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
       <c r="D156" t="n">
-        <v>46490</v>
+        <v>499900</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>dell_15_(previously_inspiron)_laptop,</t>
+          <t>Apple 2026 MacBook Pro Laptop</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 16GB DDR4, 512 SSD, Intel UHD Graphics, 15.6" FHD 120Hz IPS AG 250 nit Display, Win 11 + Office 2024, Black, 1.63Kg</t>
+          <t>Apple 2026 MacBook Pro Laptop with M5 Max chip with 18‑core CPU and 40‑core GPU: Built for AI, 41.05 cm (16.2″) Liquid Retina XDR Display, 48GB Unified Memory, 2TB SSD Storage; Space Black</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
       <c r="D157" t="n">
-        <v>58990</v>
+        <v>499900</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-28</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>dell_15_(previously_inspiron)_laptop,</t>
+          <t>Apple 2026 MacBook Pro Laptop</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 16GB DDR4, 512 SSD, Intel UHD Graphics, 15.6" FHD 120Hz IPS AG 250 nit Display, Win 11 + Office 2024, Black, 1.63Kg</t>
+          <t>Apple 2026 MacBook Pro Laptop with M5 Max chip with 18‑core CPU and 40‑core GPU: Built for AI, 41.05 cm (16.2″) Liquid Retina XDR Display, 48GB Unified Memory, 2TB SSD Storage; Space Black</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
       <c r="D158" t="n">
-        <v>59490</v>
+        <v>499900</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron) Laptop,</t>
+          <t>Apple 2026 MacBook Pro Laptop</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 8GB DDR4, 512 SSD, 15.6" FHD 120Hz IPS 250 nit Display, Win 11 + Office H&amp;S 2024, Carbon Black, Thin &amp; Light 1.63Kg</t>
+          <t>Apple 2026 MacBook Pro Laptop with M5 Pro chip with 15‑core CPU and 16‑core GPU: Built for AI, 35.97 cm (14.2″) Liquid Retina XDR Display, 24GB Unified Memory, 1TB SSD Storage; Silver</t>
         </is>
       </c>
       <c r="C159" t="inlineStr"/>
       <c r="D159" t="n">
-        <v>45490</v>
+        <v>234900</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-06-12</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron) Laptop,</t>
+          <t>Apple 2026 MacBook Pro Laptop</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 8GB DDR4, 512 SSD, 15.6" FHD 120Hz IPS 250 nit Display, Win 11 + Office H&amp;S 2024, Carbon Black, Thin &amp; Light 1.63Kg</t>
+          <t>Apple 2026 MacBook Pro Laptop with M5 Pro chip with 15‑core CPU and 16‑core GPU: Built for AI, 35.97 cm (14.2″) Liquid Retina XDR Display, 24GB Unified Memory, 1TB SSD Storage; Silver</t>
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
       <c r="D160" t="n">
-        <v>44990</v>
+        <v>227400</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron) Laptop,</t>
+          <t>BrowseBook 14.1" FHD IPS Laptop</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 8GB DDR4, 512 SSD, 15.6" FHD 120Hz IPS 250 nit Display, Win 11 + Office H&amp;S 2024, Carbon Black, Thin &amp; Light 1.63Kg</t>
+          <t>BrowseBook 14.1" FHD IPS Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB RAM | 128GB SSD | Windows 11 | 38Wh | 1.3kg | Grey</t>
         </is>
       </c>
       <c r="C161" t="inlineStr"/>
       <c r="D161" t="n">
-        <v>44990</v>
+        <v>13990</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron) Laptop,</t>
+          <t>BrowseBook 14.1" FHD IPS Laptop</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 8GB DDR4, 512 SSD, 15.6" FHD 120Hz IPS 250 nit Display, Win 11 + Office H&amp;S 2024, Carbon Black, Thin &amp; Light 1.63Kg</t>
+          <t>BrowseBook 14.1" FHD IPS Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB RAM | 128GB SSD | Windows 11 | 38Wh | 1.3kg | Grey</t>
         </is>
       </c>
       <c r="C162" t="inlineStr"/>
       <c r="D162" t="n">
-        <v>45490</v>
+        <v>13990</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-04-16</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron) Laptop,</t>
+          <t>BrowseBook 14.1" FHD IPS Laptop</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 8GB DDR4, 512 SSD, 15.6" FHD 120Hz IPS 250 nit Display, Win 11 + Office H&amp;S 2024, Carbon Black, Thin &amp; Light 1.63Kg</t>
+          <t>BrowseBook 14.1" FHD IPS Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB RAM | 128GB SSD | Windows 11 | 38Wh | 1.3kg | Grey</t>
         </is>
       </c>
       <c r="C163" t="inlineStr"/>
       <c r="D163" t="n">
-        <v>45490</v>
+        <v>13990</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron) Laptop,</t>
+          <t>BrowseBook 14.1" FHD IPS Laptop</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 8GB DDR4, 512 SSD, 15.6" FHD 120Hz IPS 250 nit Display, Win 11 + Office H&amp;S 2024, Carbon Black, Thin &amp; Light 1.63Kg</t>
+          <t>BrowseBook 14.1" FHD IPS Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB RAM | 128GB SSD | Windows 11 | 38Wh | 1.3kg | Grey</t>
         </is>
       </c>
       <c r="C164" t="inlineStr"/>
       <c r="D164" t="n">
-        <v>45490</v>
+        <v>20990</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron) Laptop,</t>
+          <t>BrowseBook 14.1" FHD IPS Laptop</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 8GB DDR4, 512 SSD, 15.6" FHD 120Hz IPS 250 nit Display, Win 11 + Office H&amp;S 2024, Carbon Black, Thin &amp; Light 1.63Kg</t>
+          <t>BrowseBook 14.1" FHD IPS Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 8GB RAM | 256GB SSD | Windows 11 | 38Wh | 1.3kg | Grey</t>
         </is>
       </c>
       <c r="C165" t="inlineStr"/>
       <c r="D165" t="n">
-        <v>46490</v>
+        <v>18990</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-15</t>
         </is>
       </c>
     </row>
@@ -3895,16 +3895,16 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 8GB DDR4, 512 SSD, 15.6" FHD 120Hz IPS 250 nit Display, Win 11 + Office H&amp;S 2024, Carbon Black, Thin &amp; Light 1.63Kg</t>
+          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core 3 100U Processor, 8GB DDR4, 512 SSD, 15.6" NT FHD 120Hz IPS AG 250 nit Display, Win 11 + Office H&amp;S 2024, Carbon Black, Thin &amp; Light- 1.63Kg</t>
         </is>
       </c>
       <c r="C166" t="inlineStr"/>
       <c r="D166" t="n">
-        <v>46990</v>
+        <v>46490</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
@@ -3916,16 +3916,16 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 8GB, 512GB, Intel UHD Graphics, 15.6" FHD IPS 250nit Display, 12m Mcafee, Win 11 + MSO'24, Platinum Silver, 1.63kg</t>
+          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 16GB DDR4, 512 SSD, Intel UHD Graphics, 15.6" FHD 120Hz IPS AG 250 nit Display, Win 11 + Office 2024, Black, 1.63Kg</t>
         </is>
       </c>
       <c r="C167" t="inlineStr"/>
       <c r="D167" t="n">
-        <v>47499</v>
+        <v>58990</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -3937,800 +3937,800 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 8GB, 512GB, Intel UHD Graphics, 15.6" FHD IPS 250nit Display, 12m Mcafee, Win 11 + MSO'24, Platinum Silver, 1.63kg</t>
+          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 16GB DDR4, 512 SSD, Intel UHD Graphics, 15.6" FHD 120Hz IPS AG 250 nit Display, Win 11 + Office 2024, Black, 1.63Kg</t>
         </is>
       </c>
       <c r="C168" t="inlineStr"/>
       <c r="D168" t="n">
-        <v>47499</v>
+        <v>59490</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>dell_15_(previously_inspiron)_laptop,</t>
+          <t>Dell 15 (Previously Inspiron) Laptop,</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 8GB, 512GB, Intel UHD Graphics, 15.6" FHD IPS 250nit Display, 12m Mcafee, Win 11 + MSO'24, Platinum Silver, 1.63kg</t>
+          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 8GB DDR4, 512 SSD, 15.6" FHD 120Hz IPS 250 nit Display, Win 11 + Office H&amp;S 2024, Carbon Black, Thin &amp; Light 1.63Kg</t>
         </is>
       </c>
       <c r="C169" t="inlineStr"/>
       <c r="D169" t="n">
-        <v>55700</v>
+        <v>45490</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-05-17</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>dell_15_(previously_inspiron)_laptop,</t>
+          <t>Dell 15 (Previously Inspiron) Laptop,</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 8GB, 512GB, Intel UHD Graphics, 15.6" FHD IPS 250nit Display, 12m Mcafee, Win 11 + MSO'24, Platinum Silver, 1.63kg</t>
+          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 8GB DDR4, 512 SSD, 15.6" FHD 120Hz IPS 250 nit Display, Win 11 + Office H&amp;S 2024, Carbon Black, Thin &amp; Light 1.63Kg</t>
         </is>
       </c>
       <c r="C170" t="inlineStr"/>
       <c r="D170" t="n">
-        <v>55700</v>
+        <v>44990</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron), 13th</t>
+          <t>Dell 15 (Previously Inspiron) Laptop,</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron), 13th Gen Intel Core i5-1334U (16GB RAM, 1TB SSD) FHD, Anti-Glare 15.6"/39.62cm, Windows 11 MSO'24, Silver, 1.62kg, 12 Month McAfee, Thin &amp; Light, Backlit Keyboard Laptop</t>
+          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 8GB DDR4, 512 SSD, 15.6" FHD 120Hz IPS 250 nit Display, Win 11 + Office H&amp;S 2024, Carbon Black, Thin &amp; Light 1.63Kg</t>
         </is>
       </c>
       <c r="C171" t="inlineStr"/>
       <c r="D171" t="n">
-        <v>63990</v>
+        <v>44990</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>dell_15_(previously_inspiron),_amd</t>
+          <t>Dell 15 (Previously Inspiron) Laptop,</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Dell 15 (Previously Inspiron), AMD Ryzen 5-7530U, 16GB RAM, 512GB SSD, FHD IPS, 15.6"/39.62cm, Win 11, MSO 2024, Platinum Silver, 1.67kg,Standard Keyboard, 12 Month McAfee, Thin &amp; Light, Laptop</t>
+          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 8GB DDR4, 512 SSD, 15.6" FHD 120Hz IPS 250 nit Display, Win 11 + Office H&amp;S 2024, Carbon Black, Thin &amp; Light 1.63Kg</t>
         </is>
       </c>
       <c r="C172" t="inlineStr"/>
       <c r="D172" t="n">
-        <v>56086</v>
+        <v>45490</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Dell 15 AI Powered Laptop,</t>
+          <t>Dell 15 (Previously Inspiron) Laptop,</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Dell 15 AI Powered Laptop, Intel Core Ultra 5 225H, 8GB DDR5 RAM, 512GB SSD, 15.6" FHD Anti-Glare Display, Intel Arc Graphics, Standard Keyboard, Dedicated Copilot Key, Black, Win11 Home + MSO H&amp;S'24</t>
+          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 8GB DDR4, 512 SSD, 15.6" FHD 120Hz IPS 250 nit Display, Win 11 + Office H&amp;S 2024, Carbon Black, Thin &amp; Light 1.63Kg</t>
         </is>
       </c>
       <c r="C173" t="inlineStr"/>
       <c r="D173" t="n">
-        <v>68990</v>
+        <v>45490</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>dell_15_ai_powered_laptop,</t>
+          <t>Dell 15 (Previously Inspiron) Laptop,</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Dell 15 Ai Powered Laptop, Intel Core Ultra 7 255H, 16GB DDR5 RAM, 512GB SSD, 15.6" FHD Anti-Glare Display, Intel Arc Graphics, Backlit Keyboard, Dedicated Copilot Key, Silver, Win11 Home + MSO H&amp;S'24</t>
+          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 8GB DDR4, 512 SSD, 15.6" FHD 120Hz IPS 250 nit Display, Win 11 + Office H&amp;S 2024, Carbon Black, Thin &amp; Light 1.63Kg</t>
         </is>
       </c>
       <c r="C174" t="inlineStr"/>
       <c r="D174" t="n">
-        <v>103990</v>
+        <v>45490</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Dell 15 Smart Choice (Previously</t>
+          <t>Dell 15 (Previously Inspiron) Laptop,</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Dell 15 Smart Choice (Previously Inspiron), 13th Gen Intel Core i5-1334U (16GB RAM, 1TB SSD) FHD, 15.6"/39.62cm, Windows 11 MSO'24, Silver, 1.62kg, 12 Month McAfee, Backlit KB, Thin &amp; Light Laptop</t>
+          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 8GB DDR4, 512 SSD, 15.6" FHD 120Hz IPS 250 nit Display, Win 11 + Office H&amp;S 2024, Carbon Black, Thin &amp; Light 1.63Kg</t>
         </is>
       </c>
       <c r="C175" t="inlineStr"/>
       <c r="D175" t="n">
-        <v>66990</v>
+        <v>46490</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-12</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Dell 15 Smart Choice (Previously</t>
+          <t>Dell 15 (Previously Inspiron) Laptop,</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Dell 15 Smart Choice (Previously Inspiron), 13th Gen Intel Core i5-1334U (16GB RAM, 1TB SSD) FHD, 15.6"/39.62cm, Windows 11 MSO'24, Silver, 1.62kg, 12 Month McAfee, Backlit KB, Thin &amp; Light Laptop</t>
+          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 8GB DDR4, 512 SSD, 15.6" FHD 120Hz IPS 250 nit Display, Win 11 + Office H&amp;S 2024, Carbon Black, Thin &amp; Light 1.63Kg</t>
         </is>
       </c>
       <c r="C176" t="inlineStr"/>
       <c r="D176" t="n">
-        <v>67990</v>
+        <v>46990</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Dell 15 Smart Choice (Previously</t>
+          <t>dell_15_(previously_inspiron)_laptop,</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Dell 15 Smart Choice (Previously Inspiron), 13th Gen Intel Core i5-1334U (16GB RAM, 1TB SSD) FHD, 15.6"/39.62cm, Windows 11 MSO'24, Silver, 1.62kg, 12 Month McAfee, Backlit KB, Thin &amp; Light Laptop</t>
+          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 8GB, 512GB, Intel UHD Graphics, 15.6" FHD IPS 250nit Display, 12m Mcafee, Win 11 + MSO'24, Platinum Silver, 1.63kg</t>
         </is>
       </c>
       <c r="C177" t="inlineStr"/>
       <c r="D177" t="n">
-        <v>67990</v>
+        <v>47499</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Dell 15 Smart Choice (Previously</t>
+          <t>dell_15_(previously_inspiron)_laptop,</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Dell 15 Smart Choice (Previously Inspiron), 13th Gen Intel Core i5-1334U (16GB RAM, 1TB SSD) FHD, 15.6"/39.62cm, Windows 11 MSO'24, Silver, 1.62kg, 12 Month McAfee, Backlit KB, Thin &amp; Light Laptop</t>
+          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 8GB, 512GB, Intel UHD Graphics, 15.6" FHD IPS 250nit Display, 12m Mcafee, Win 11 + MSO'24, Platinum Silver, 1.63kg</t>
         </is>
       </c>
       <c r="C178" t="inlineStr"/>
       <c r="D178" t="n">
-        <v>69990</v>
+        <v>47499</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Dell 15 Smart Choice (Previously</t>
+          <t>dell_15_(previously_inspiron)_laptop,</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Dell 15 Smart Choice (Previously Inspiron), 13th Gen Intel Core i5-1334U (16GB RAM, 1TB SSD) FHD, 15.6"/39.62cm, Windows 11 MSO'24, Silver, 1.62kg, 12 Month McAfee, Backlit KB, Thin &amp; Light Laptop</t>
+          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 8GB, 512GB, Intel UHD Graphics, 15.6" FHD IPS 250nit Display, 12m Mcafee, Win 11 + MSO'24, Platinum Silver, 1.63kg</t>
         </is>
       </c>
       <c r="C179" t="inlineStr"/>
       <c r="D179" t="n">
-        <v>67990</v>
+        <v>55700</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-08-04</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>dell_15_smartchoice_(previously_inspiron),</t>
+          <t>dell_15_(previously_inspiron)_laptop,</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Dell 15 SmartChoice (Previously Inspiron), Intel 13th Gen Core i5-1334U, 16GB, 1TB SSD, FHD,15.6"/39.62cm, Win 11, MSO'24, Silver, 1.62kg, [Dell 15], 12 Month McAfee, Backlit KB, Thin &amp; Light Laptop</t>
+          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 8GB, 512GB, Intel UHD Graphics, 15.6" FHD IPS 250nit Display, 12m Mcafee, Win 11 + MSO'24, Platinum Silver, 1.63kg</t>
         </is>
       </c>
       <c r="C180" t="inlineStr"/>
       <c r="D180" t="n">
-        <v>68990</v>
+        <v>55700</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-05</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>dell_15_smartchoice_(previously_inspiron),</t>
+          <t>dell_15_(previously_inspiron)_laptop,</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Dell 15 SmartChoice (Previously Inspiron), Intel 13th Gen Core i5-1334U, 16GB, 1TB SSD, FHD,15.6"/39.62cm, Win 11, MSO'24, Silver, 1.62kg, [Dell 15], 12 Month McAfee, Backlit KB, Thin &amp; Light Laptop</t>
+          <t>Dell 15 (Previously Inspiron) Laptop, 14th Gen Intel Core i3/Core 3 100U Processor, 8GB, 512GB, Intel UHD Graphics, 15.6" FHD IPS 250nit Display, 12m Mcafee, Win 11 + MSO'24, Platinum Silver, 1.63kg</t>
         </is>
       </c>
       <c r="C181" t="inlineStr"/>
       <c r="D181" t="n">
-        <v>68990</v>
+        <v>55800</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>dell_15_smartchoice_(previously_inspiron),</t>
+          <t>Dell 15 (Previously Inspiron), 13th</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Dell 15 SmartChoice (Previously Inspiron), Intel 13th Gen Core i5-1334U, 16GB, 1TB SSD, FHD,15.6"/39.62cm, Win 11, MSO'24, Silver, 1.62kg, [Dell 15], 12 Month McAfee, Backlit KB, Thin &amp; Light Laptop</t>
+          <t>Dell 15 (Previously Inspiron), 13th Gen Intel Core i5-1334U (16GB RAM, 1TB SSD) FHD, Anti-Glare 15.6"/39.62cm, Windows 11 MSO'24, Silver, 1.62kg, 12 Month McAfee, Thin &amp; Light, Backlit Keyboard Laptop</t>
         </is>
       </c>
       <c r="C182" t="inlineStr"/>
       <c r="D182" t="n">
-        <v>68990</v>
+        <v>63990</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-05-17</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Dell 15, 13th Gen Intel</t>
+          <t>dell_15_(previously_inspiron),_amd</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Dell 15, 13th Gen Intel Core i5-1334U (16GB DDR4, 512GB SSD) Anti-Glare FHD 15.6"/39.62cm, Windows 11, Microsoft Office Home 2024, Grey, 1.66kg, [Vostro 3530], 12 Month McAfee, Thin &amp; Light Laptop</t>
+          <t>Dell 15 (Previously Inspiron), AMD Ryzen 5-7530U, 16GB RAM, 512GB SSD, FHD IPS, 15.6"/39.62cm, Win 11, MSO 2024, Platinum Silver, 1.67kg,Standard Keyboard, 12 Month McAfee, Thin &amp; Light, Laptop</t>
         </is>
       </c>
       <c r="C183" t="inlineStr"/>
       <c r="D183" t="n">
-        <v>61490</v>
+        <v>56086</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Dell 15, 13th Gen Intel</t>
+          <t>Dell 15 AI Powered Laptop,</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Dell 15, 13th Gen Intel Core i5-1334U (16GB DDR4, 512GB SSD) Anti-Glare FHD 15.6"/39.62cm, Windows 11, Microsoft Office Home 2024, Grey, 1.66kg, [Vostro 3530], 12 Month McAfee, Thin &amp; Light Laptop</t>
+          <t>Dell 15 AI Powered Laptop, Intel Core Ultra 5 225H, 8GB DDR5 RAM, 512GB SSD, 15.6" FHD Anti-Glare Display, Intel Arc Graphics, Standard Keyboard, Dedicated Copilot Key, Black, Win11 Home + MSO H&amp;S'24</t>
         </is>
       </c>
       <c r="C184" t="inlineStr"/>
       <c r="D184" t="n">
-        <v>63490</v>
+        <v>68990</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-05-15</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Dell 15, AMD Ryzen 7-7730U,</t>
+          <t>dell_15_ai_powered_laptop,</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Dell 15, AMD Ryzen 7-7730U, 16GB DDR4, 512GB SSD, FHD, 15.6"/39.6cm, Windows 11, Microsoft Office Home 2024, Platinum Silver, 1.63Kg, [Dell 15], 120Hz 250nits, AMD Radeon Graphics,Thin &amp; Light, Laptop</t>
+          <t>Dell 15 Ai Powered Laptop, Intel Core Ultra 7 255H, 16GB DDR5 RAM, 512GB SSD, 15.6" FHD Anti-Glare Display, Intel Arc Graphics, Backlit Keyboard, Dedicated Copilot Key, Silver, Win11 Home + MSO H&amp;S'24</t>
         </is>
       </c>
       <c r="C185" t="inlineStr"/>
       <c r="D185" t="n">
-        <v>59957</v>
+        <v>103990</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Dell 15, AMD Ryzen 7-7730U,</t>
+          <t>Dell 15 Smart Choice (Previously</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Dell 15, AMD Ryzen 7-7730U, 16GB DDR4, 512GB SSD, FHD, 15.6"/39.6cm, Windows 11, Microsoft Office Home 2024, Platinum Silver, 1.63Kg, [Dell 15], 120Hz 250nits, AMD Radeon Graphics,Thin &amp; Light, Laptop</t>
+          <t>Dell 15 Smart Choice (Previously Inspiron), 13th Gen Intel Core i5-1334U (16GB RAM, 1TB SSD) FHD, 15.6"/39.62cm, Windows 11 MSO'24, Silver, 1.62kg, 12 Month McAfee, Backlit KB, Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C186" t="inlineStr"/>
       <c r="D186" t="n">
-        <v>58490</v>
+        <v>66990</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-28</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>dell_15,_intel_core_13th</t>
+          <t>Dell 15 Smart Choice (Previously</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Dell 15, Intel Core 13th Gen i5-1334U, FHD, 15.6"/39.62cm, Windows 11, MSO'24, Grey, 1.66kg, Vostro 3530, (16GB DDR4, 512GB SSD) Anti-Glare FHD 15.6"/39.62cm, 12 Month McAfee, Thin &amp; Light Laptop</t>
+          <t>Dell 15 Smart Choice (Previously Inspiron), 13th Gen Intel Core i5-1334U (16GB RAM, 1TB SSD) FHD, 15.6"/39.62cm, Windows 11 MSO'24, Silver, 1.62kg, 12 Month McAfee, Backlit KB, Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C187" t="inlineStr"/>
       <c r="D187" t="n">
-        <v>65490</v>
+        <v>67990</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Dell 15, Intel Core 3</t>
+          <t>Dell 15 Smart Choice (Previously</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Dell 15, Intel Core 3 14th Gen-100U, 16GB DDR4, 512GB SSD, FHD IPS, 15.6"/39.62cm, Windows 11, Microsoft Office Home 2024, Carbon Black, 1.63Kg, Thin &amp; Light, Laptop Model NO - Dell 15 DCU5250</t>
+          <t>Dell 15 Smart Choice (Previously Inspiron), 13th Gen Intel Core i5-1334U (16GB RAM, 1TB SSD) FHD, 15.6"/39.62cm, Windows 11 MSO'24, Silver, 1.62kg, 12 Month McAfee, Backlit KB, Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C188" t="inlineStr"/>
       <c r="D188" t="n">
-        <v>51868</v>
+        <v>67990</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Dell 15, Intel Core i3/Core</t>
+          <t>Dell 15 Smart Choice (Previously</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Dell 15, Intel Core i3/Core 3 14th Gen-100U, 16GB DDR4, 512GB SSD, FHD IPS, 15.6"/39.62cm, Windows 11, Microsoft Office Home 2024, Carbon Black, 1.63Kg, Thin &amp; Light, Laptop Model NO - Dell 15 DCU5250</t>
+          <t>Dell 15 Smart Choice (Previously Inspiron), 13th Gen Intel Core i5-1334U (16GB RAM, 1TB SSD) FHD, 15.6"/39.62cm, Windows 11 MSO'24, Silver, 1.62kg, 12 Month McAfee, Backlit KB, Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C189" t="inlineStr"/>
       <c r="D189" t="n">
-        <v>48990</v>
+        <v>69990</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-02</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Dell 15, R5-7520U Processor, 8GB</t>
+          <t>Dell 15 Smart Choice (Previously</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Dell 15, R5-7520U Processor, 8GB LPDDR5 RAM, 512GB SSD, FHD 15.6"/39.62 cm Display, Windows 11, MSO'24, Carbon Black, 1.63kg, Standard Keyboard, 15 Month McAfee, Thin &amp; Light Laptop</t>
+          <t>Dell 15 Smart Choice (Previously Inspiron), 13th Gen Intel Core i5-1334U (16GB RAM, 1TB SSD) FHD, 15.6"/39.62cm, Windows 11 MSO'24, Silver, 1.62kg, 12 Month McAfee, Backlit KB, Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C190" t="inlineStr"/>
       <c r="D190" t="n">
-        <v>53990</v>
+        <v>67990</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-06-14</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>dell_g_series,_intel_core</t>
+          <t>dell_15_smartchoice_(previously_inspiron),</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Dell G Series, Intel Core i5-13450HX, 13th Gen, NVIDIA RTX 3050-6GB, 16GB, 512GB SSD, FHD, 15.6"/39.62cm, Windows 11, MSO'24, Dark Shadow Gray, 2.65KG, [G15-5530], Backlit Keyboard, Gaming Laptop</t>
+          <t>Dell 15 SmartChoice (Previously Inspiron), Intel 13th Gen Core i5-1334U, 16GB, 1TB SSD, FHD,15.6"/39.62cm, Win 11, MSO'24, Silver, 1.62kg, [Dell 15], 12 Month McAfee, Backlit KB, Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C191" t="inlineStr"/>
       <c r="D191" t="n">
-        <v>89990</v>
+        <v>68990</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Dell G15, 13th Gen Intel</t>
+          <t>dell_15_smartchoice_(previously_inspiron),</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Dell G15, 13th Gen Intel Core i5-13450HX Processor, NVIDIA RTX 3050-6GB, (16GB RAM 1TB SSD) FHD 15.6"/39.62 cm, Orange Backlit Keyboard, Win 11, MS Office'24, Dark Shadow Grey, 2.65Kg Gaming Laptop</t>
+          <t>Dell 15 SmartChoice (Previously Inspiron), Intel 13th Gen Core i5-1334U, 16GB, 1TB SSD, FHD,15.6"/39.62cm, Win 11, MSO'24, Silver, 1.62kg, [Dell 15], 12 Month McAfee, Backlit KB, Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C192" t="inlineStr"/>
       <c r="D192" t="n">
-        <v>79590</v>
+        <v>68990</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Dell G15, 13th Gen Intel</t>
+          <t>dell_15_smartchoice_(previously_inspiron),</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Dell G15, 13th Gen Intel Core i5-13450HX Processor, NVIDIA RTX 3050-6GB, (16GB RAM 1TB SSD) FHD 15.6"/39.62 cm, Orange Backlit Keyboard, Win 11, MS Office'24, Dark Shadow Grey, 2.65Kg Gaming Laptop</t>
+          <t>Dell 15 SmartChoice (Previously Inspiron), Intel 13th Gen Core i5-1334U, 16GB, 1TB SSD, FHD,15.6"/39.62cm, Win 11, MSO'24, Silver, 1.62kg, [Dell 15], 12 Month McAfee, Backlit KB, Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C193" t="inlineStr"/>
       <c r="D193" t="n">
-        <v>79990</v>
+        <v>68990</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-08-05</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>EBook 11.6" HD Laptop |</t>
+          <t>dell_15_smartchoice_(previously_inspiron),</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>EBook 11.6" HD Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB DDR4 | 128GB eMMC + M.2 SSD Expandable Slot | Win 11 Home |31Wh Battery | UHD Graphics 600 | Black</t>
+          <t>Dell 15 SmartChoice (Previously Inspiron), Intel 13th Gen Core i5-1334U, 16GB, 1TB SSD, FHD,15.6"/39.62cm, Win 11, MSO'24, Silver, 1.62kg, [Dell 15], 12 Month McAfee, Backlit KB, Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C194" t="inlineStr"/>
       <c r="D194" t="n">
-        <v>11990</v>
+        <v>76990</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>EBook 11.6" HD Laptop |</t>
+          <t>Dell 15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>EBook 11.6" HD Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB DDR4 | 128GB eMMC + M.2 SSD Expandable Slot | Win 11 Home |31Wh Battery | UHD Graphics 600 | Black</t>
+          <t>Dell 15, 13th Gen Intel Core i5-1334U (16GB DDR4, 512GB SSD) Anti-Glare FHD 15.6"/39.62cm, Windows 11, Microsoft Office Home 2024, Grey, 1.66kg, [Vostro 3530], 12 Month McAfee, Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C195" t="inlineStr"/>
       <c r="D195" t="n">
-        <v>11990</v>
+        <v>61490</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>EBook 11.6" HD Laptop |</t>
+          <t>Dell 15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>EBook 11.6" HD Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB DDR4 | 128GB eMMC + M.2 SSD Expandable Slot | Win 11 Home |31Wh Battery | UHD Graphics 600 | Black</t>
+          <t>Dell 15, 13th Gen Intel Core i5-1334U (16GB DDR4, 512GB SSD) Anti-Glare FHD 15.6"/39.62cm, Windows 11, Microsoft Office Home 2024, Grey, 1.66kg, [Vostro 3530], 12 Month McAfee, Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C196" t="inlineStr"/>
       <c r="D196" t="n">
-        <v>11990</v>
+        <v>63490</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>EBook 11.6" HD Laptop |</t>
+          <t>Dell 15, AMD Ryzen 7-7730U,</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>EBook 11.6" HD Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB DDR4 | 128GB eMMC + M.2 SSD Expandable Slot | Win 11 Home |31Wh Battery | UHD Graphics 600 | Black</t>
+          <t>Dell 15, AMD Ryzen 7-7730U, 16GB DDR4, 512GB SSD, FHD, 15.6"/39.6cm, Windows 11, Microsoft Office Home 2024, Platinum Silver, 1.63Kg, [Dell 15], 120Hz 250nits, AMD Radeon Graphics,Thin &amp; Light, Laptop</t>
         </is>
       </c>
       <c r="C197" t="inlineStr"/>
       <c r="D197" t="n">
-        <v>11990</v>
+        <v>59957</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>EBook 11.6" HD Laptop |</t>
+          <t>Dell 15, AMD Ryzen 7-7730U,</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>EBook 11.6" HD Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB DDR4 | 128GB eMMC + M.2 SSD Expandable Slot | Win 11 Home |31Wh Battery | UHD Graphics 600 | Black</t>
+          <t>Dell 15, AMD Ryzen 7-7730U, 16GB DDR4, 512GB SSD, FHD, 15.6"/39.6cm, Windows 11, Microsoft Office Home 2024, Platinum Silver, 1.63Kg, [Dell 15], 120Hz 250nits, AMD Radeon Graphics,Thin &amp; Light, Laptop</t>
         </is>
       </c>
       <c r="C198" t="inlineStr"/>
       <c r="D198" t="n">
-        <v>11990</v>
+        <v>58490</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-17</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>EBook 11.6" HD Laptop |</t>
+          <t>dell_15,_intel_core_13th</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>EBook 11.6" HD Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB DDR4 | 128GB eMMC + M.2 SSD Expandable Slot | Win 11 Home |31Wh Battery | UHD Graphics 600 | Black</t>
+          <t>Dell 15, Intel Core 13th Gen i5-1334U, FHD, 15.6"/39.62cm, Windows 11, MSO'24, Grey, 1.66kg, Vostro 3530, (16GB DDR4, 512GB SSD) Anti-Glare FHD 15.6"/39.62cm, 12 Month McAfee, Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C199" t="inlineStr"/>
       <c r="D199" t="n">
-        <v>11990</v>
+        <v>65490</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>EBook 11.6" HD Laptop |</t>
+          <t>Dell 15, Intel Core 3</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>EBook 11.6" HD Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB DDR4 | 128GB eMMC + M.2 SSD Expandable Slot | Win 11 Home |31Wh Battery | UHD Graphics 600 | Black</t>
+          <t>Dell 15, Intel Core 3 14th Gen-100U, 16GB DDR4, 512GB SSD, FHD IPS, 15.6"/39.62cm, Windows 11, Microsoft Office Home 2024, Carbon Black, 1.63Kg, Thin &amp; Light, Laptop Model NO - Dell 15 DCU5250</t>
         </is>
       </c>
       <c r="C200" t="inlineStr"/>
       <c r="D200" t="n">
-        <v>11990</v>
+        <v>51868</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>EBook 11.6" HD Laptop |</t>
+          <t>Dell 15, Intel Core i3/Core</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>EBook 11.6" HD Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB DDR4 | 128GB eMMC + M.2 SSD Expandable Slot | Win 11 Home |31Wh Battery | UHD Graphics 600 | Black</t>
+          <t>Dell 15, Intel Core i3/Core 3 14th Gen-100U, 16GB DDR4, 512GB SSD, FHD IPS, 15.6"/39.62cm, Windows 11, Microsoft Office Home 2024, Carbon Black, 1.63Kg, Thin &amp; Light, Laptop Model NO - Dell 15 DCU5250</t>
         </is>
       </c>
       <c r="C201" t="inlineStr"/>
       <c r="D201" t="n">
-        <v>11990</v>
+        <v>48990</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>EBook 11.6" HD Laptop |</t>
+          <t>Dell 15, R5-7520U Processor, 8GB</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>EBook 11.6" HD Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB DDR4 | 128GB eMMC + M.2 SSD Expandable Slot | Win 11 Home |31Wh Battery | UHD Graphics 600 | Black</t>
+          <t>Dell 15, R5-7520U Processor, 8GB LPDDR5 RAM, 512GB SSD, FHD 15.6"/39.62 cm Display, Windows 11, MSO'24, Carbon Black, 1.63kg, Standard Keyboard, 15 Month McAfee, Thin &amp; Light Laptop</t>
         </is>
       </c>
       <c r="C202" t="inlineStr"/>
       <c r="D202" t="n">
-        <v>11990</v>
+        <v>53990</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-04-16</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>EBook 11.6" HD Laptop |</t>
+          <t>dell_g_series,_intel_core</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>EBook 11.6" HD Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB DDR4 | 128GB eMMC + M.2 SSD Expandable Slot | Win 11 Home |31Wh Battery | UHD Graphics 600 | Black</t>
+          <t>Dell G Series, Intel Core i5-13450HX, 13th Gen, NVIDIA RTX 3050-6GB, 16GB, 512GB SSD, FHD, 15.6"/39.62cm, Windows 11, MSO'24, Dark Shadow Gray, 2.65KG, [G15-5530], Backlit Keyboard, Gaming Laptop</t>
         </is>
       </c>
       <c r="C203" t="inlineStr"/>
       <c r="D203" t="n">
-        <v>11990</v>
+        <v>89990</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>EBook 11.6" HD Laptop |</t>
+          <t>Dell G15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>EBook 11.6" HD Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB DDR4 | 128GB eMMC + M.2 SSD Expandable Slot | Win 11 Home |31Wh Battery | UHD Graphics 600 | Black</t>
+          <t>Dell G15, 13th Gen Intel Core i5-13450HX Processor, NVIDIA RTX 3050-6GB, (16GB RAM 1TB SSD) FHD 15.6"/39.62 cm, Orange Backlit Keyboard, Win 11, MS Office'24, Dark Shadow Grey, 2.65Kg Gaming Laptop</t>
         </is>
       </c>
       <c r="C204" t="inlineStr"/>
       <c r="D204" t="n">
-        <v>16990</v>
+        <v>79590</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>EBook 11.6" HD Laptop |</t>
+          <t>Dell G15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>EBook 11.6" HD Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB DDR4 | 128GB eMMC + M.2 SSD Expandable Slot | Win 11 Home |31Wh Battery | UHD Graphics 600 | Black</t>
+          <t>Dell G15, 13th Gen Intel Core i5-13450HX Processor, NVIDIA RTX 3050-6GB, (16GB RAM 1TB SSD) FHD 15.6"/39.62 cm, Orange Backlit Keyboard, Win 11, MS Office'24, Dark Shadow Grey, 2.65Kg Gaming Laptop</t>
         </is>
       </c>
       <c r="C205" t="inlineStr"/>
       <c r="D205" t="n">
-        <v>16990</v>
+        <v>79990</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-05-08</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>ebook_11.6"_hd_laptop_|</t>
+          <t>EBook 11.6" HD Laptop |</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -4740,18 +4740,18 @@
       </c>
       <c r="C206" t="inlineStr"/>
       <c r="D206" t="n">
-        <v>10603</v>
+        <v>11990</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-04-16</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>ebook_11.6"_hd_laptop_|</t>
+          <t>EBook 11.6" HD Laptop |</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -4761,18 +4761,18 @@
       </c>
       <c r="C207" t="inlineStr"/>
       <c r="D207" t="n">
-        <v>10990</v>
+        <v>11990</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>ebook_11.6"_hd_laptop_|</t>
+          <t>EBook 11.6" HD Laptop |</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -4782,18 +4782,18 @@
       </c>
       <c r="C208" t="inlineStr"/>
       <c r="D208" t="n">
-        <v>10990</v>
+        <v>11990</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>ebook_11.6"_hd_laptop_|</t>
+          <t>EBook 11.6" HD Laptop |</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -4803,18 +4803,18 @@
       </c>
       <c r="C209" t="inlineStr"/>
       <c r="D209" t="n">
-        <v>10990</v>
+        <v>11990</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-05-19</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>ebook_11.6"_hd_laptop_|</t>
+          <t>EBook 11.6" HD Laptop |</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -4824,18 +4824,18 @@
       </c>
       <c r="C210" t="inlineStr"/>
       <c r="D210" t="n">
-        <v>10990</v>
+        <v>11990</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-05-20</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>ebook_11.6"_hd_laptop_|</t>
+          <t>EBook 11.6" HD Laptop |</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -4845,364 +4845,364 @@
       </c>
       <c r="C211" t="inlineStr"/>
       <c r="D211" t="n">
-        <v>10990</v>
+        <v>11990</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-05-21</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>hp_14_smartchoice,_intel_core</t>
+          <t>EBook 11.6" HD Laptop |</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>HP 14 Smartchoice, Intel Core Ultra 5 125H 12 TOPS, 24GB DDR5 (Upgradeable) 1TB SSD, Anti-Glare, FHD, 14''/35.6cm,Win11, M365*Office24, Silver, 1.4kg, ep1180tu, FHD Camera w/Shutter, Backlit AI Laptop</t>
+          <t>EBook 11.6" HD Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB DDR4 | 128GB eMMC + M.2 SSD Expandable Slot | Win 11 Home |31Wh Battery | UHD Graphics 600 | Black</t>
         </is>
       </c>
       <c r="C212" t="inlineStr"/>
       <c r="D212" t="n">
-        <v>77990</v>
+        <v>11990</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-31</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>hp_14_smartchoice,_intel_core</t>
+          <t>EBook 11.6" HD Laptop |</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>HP 14 Smartchoice, Intel Core Ultra 5 125H 12 TOPS, 24GB DDR5 (Upgradeable) 1TB SSD, Anti-Glare, FHD, 14''/35.6cm,Win11, M365*Office24, Silver, 1.4kg, ep1180tu, FHD Camera w/Shutter, Backlit AI Laptop</t>
+          <t>EBook 11.6" HD Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB DDR4 | 128GB eMMC + M.2 SSD Expandable Slot | Win 11 Home |31Wh Battery | UHD Graphics 600 | Black</t>
         </is>
       </c>
       <c r="C213" t="inlineStr"/>
       <c r="D213" t="n">
-        <v>77990</v>
+        <v>11990</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>hp_14_smartchoice,_intel_core</t>
+          <t>EBook 11.6" HD Laptop |</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>HP 14 Smartchoice, Intel Core Ultra 5 125H 12 TOPS, 24GB DDR5 (Upgradeable) 1TB SSD, Anti-Glare, FHD, 14''/35.6cm,Win11, M365*Office24, Silver, 1.4kg, ep1180tu, FHD Camera w/Shutter, Backlit AI Laptop</t>
+          <t>EBook 11.6" HD Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB DDR4 | 128GB eMMC + M.2 SSD Expandable Slot | Win 11 Home |31Wh Battery | UHD Graphics 600 | Black</t>
         </is>
       </c>
       <c r="C214" t="inlineStr"/>
       <c r="D214" t="n">
-        <v>79990</v>
+        <v>11990</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>hp_14_smartchoice,_intel_core</t>
+          <t>EBook 11.6" HD Laptop |</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>HP 14 Smartchoice, Intel Core Ultra 5 125H 12 TOPS, 24GB DDR5 (Upgradeable) 1TB SSD, Anti-Glare, FHD, 14''/35.6cm,Win11, M365*Office24, Silver, 1.4kg, ep1180tu, FHD Camera w/Shutter, Backlit AI Laptop</t>
+          <t>EBook 11.6" HD Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB DDR4 | 128GB eMMC + M.2 SSD Expandable Slot | Win 11 Home |31Wh Battery | UHD Graphics 600 | Black</t>
         </is>
       </c>
       <c r="C215" t="inlineStr"/>
       <c r="D215" t="n">
-        <v>79990</v>
+        <v>11990</v>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>hp_14,_amd_ryzen_7</t>
+          <t>EBook 11.6" HD Laptop |</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>HP 14, AMD Ryzen 7 7730U (16GB DDR4, 512GB SSD) FHD, Anti-Glare, Micro-Edge, 14''/35.6cm, Win11, M365 Basic(1yr), Office Home24, Silver,1.4kg, EM0104AU, FHD Camera w/Privacy Shutter, Backlit Laptop</t>
+          <t>EBook 11.6" HD Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB DDR4 | 128GB eMMC + M.2 SSD Expandable Slot | Win 11 Home |31Wh Battery | UHD Graphics 600 | Black</t>
         </is>
       </c>
       <c r="C216" t="inlineStr"/>
       <c r="D216" t="n">
-        <v>59990</v>
+        <v>16990</v>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>hp_14,_amd_ryzen_7</t>
+          <t>EBook 11.6" HD Laptop |</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>HP 14, AMD Ryzen 7 7730U (16GB DDR4, 512GB SSD) FHD, Anti-Glare, Micro-Edge, 14''/35.6cm, Win11, M365 Basic(1yr), Office Home24, Silver,1.4kg, EM0104AU, FHD Camera w/Privacy Shutter, Backlit Laptop</t>
+          <t>EBook 11.6" HD Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB DDR4 | 128GB eMMC + M.2 SSD Expandable Slot | Win 11 Home |31Wh Battery | UHD Graphics 600 | Black</t>
         </is>
       </c>
       <c r="C217" t="inlineStr"/>
       <c r="D217" t="n">
-        <v>64990</v>
+        <v>16990</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>HP 14s Intel Celeron Dual</t>
+          <t>ebook_11.6"_hd_laptop_|</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>HP 14s Intel Celeron Dual Core N4500 Laptop (8GB/512GB SSD/Win 11) 14.0" HD Display, MSO 24, Black, 1.46kg, DQ3149TU Thin and Light Business Laptop</t>
+          <t>EBook 11.6" HD Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB DDR4 | 128GB eMMC + M.2 SSD Expandable Slot | Win 11 Home |31Wh Battery | UHD Graphics 600 | Black</t>
         </is>
       </c>
       <c r="C218" t="inlineStr"/>
       <c r="D218" t="n">
-        <v>40400</v>
+        <v>10603</v>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>hp_15_(2025),_amd_athlon</t>
+          <t>ebook_11.6"_hd_laptop_|</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>HP 15 (2025), AMD Athlon 7120U Dual Core - (8 GB/256 GB SSD/AMD Radeon Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" HD Display/Black/1.5 kg/MS Office 2021</t>
+          <t>EBook 11.6" HD Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB DDR4 | 128GB eMMC + M.2 SSD Expandable Slot | Win 11 Home |31Wh Battery | UHD Graphics 600 | Black</t>
         </is>
       </c>
       <c r="C219" t="inlineStr"/>
       <c r="D219" t="n">
-        <v>41999</v>
+        <v>10990</v>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>hp_15_(2025),_amd_athlon</t>
+          <t>ebook_11.6"_hd_laptop_|</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>HP 15 (2025), AMD Athlon 7120U Dual Core - (8 GB/256 GB SSD/AMD Radeon Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" HD Display/Black/1.5 kg/MS Office 2021</t>
+          <t>EBook 11.6" HD Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB DDR4 | 128GB eMMC + M.2 SSD Expandable Slot | Win 11 Home |31Wh Battery | UHD Graphics 600 | Black</t>
         </is>
       </c>
       <c r="C220" t="inlineStr"/>
       <c r="D220" t="n">
-        <v>41999</v>
+        <v>10990</v>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>HP 15 (2026), AMD Athlon</t>
+          <t>ebook_11.6"_hd_laptop_|</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>HP 15 (2026), AMD Athlon Dual Core 7120U - (8 GB DDR5/512 GB SSD/AMD Radeon 610M Graphics/DOS) Thin and Light Business Laptop/15.6" HD Display/Turbo Silver/Copilot Key/1.5kg</t>
+          <t>EBook 11.6" HD Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB DDR4 | 128GB eMMC + M.2 SSD Expandable Slot | Win 11 Home |31Wh Battery | UHD Graphics 600 | Black</t>
         </is>
       </c>
       <c r="C221" t="inlineStr"/>
       <c r="D221" t="n">
-        <v>39999</v>
+        <v>10990</v>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>HP 15 (2026), AMD Athlon</t>
+          <t>ebook_11.6"_hd_laptop_|</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>HP 15 (2026), AMD Athlon Dual Core 7120U - (8 GB DDR5/512 GB SSD/AMD Radeon 610M Graphics/Windows 11 Pro) Thin and Light Business Laptop/15.6" HD Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
+          <t>EBook 11.6" HD Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB DDR4 | 128GB eMMC + M.2 SSD Expandable Slot | Win 11 Home |31Wh Battery | UHD Graphics 600 | Black</t>
         </is>
       </c>
       <c r="C222" t="inlineStr"/>
       <c r="D222" t="n">
-        <v>39660</v>
+        <v>10990</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-08-04</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>hp_15_(2026),_amd_athlon</t>
+          <t>ebook_11.6"_hd_laptop_|</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>HP 15 (2026), AMD Athlon Dual Core 7120U - (8 GB DDR5/512 GB SSD/AMD Radeon 610M Graphics/Windows 11 Pro) Thin and Light Business Laptop/15.6" HD Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
+          <t>EBook 11.6" HD Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB DDR4 | 128GB eMMC + M.2 SSD Expandable Slot | Win 11 Home |31Wh Battery | UHD Graphics 600 | Black</t>
         </is>
       </c>
       <c r="C223" t="inlineStr"/>
       <c r="D223" t="n">
-        <v>41999</v>
+        <v>10990</v>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-08-05</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>hp_15_(2026),_amd_athlon</t>
+          <t>ebook_11.6"_hd_laptop_|</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>HP 15 (2026), AMD Athlon Dual Core 7120U - (8 GB DDR5/512 GB SSD/AMD Radeon 610M Graphics/Windows 11 Pro) Thin and Light Business Laptop/15.6" HD Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
+          <t>EBook 11.6" HD Laptop | Best Student &amp; Office Work Laptop | Celeron N4020 | 4GB DDR4 | 128GB eMMC + M.2 SSD Expandable Slot | Win 11 Home |31Wh Battery | UHD Graphics 600 | Black</t>
         </is>
       </c>
       <c r="C224" t="inlineStr"/>
       <c r="D224" t="n">
-        <v>42840</v>
+        <v>11990</v>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>hp_15_(2026),_amd_athlon</t>
+          <t>hp_14_smartchoice,_intel_core</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>HP 15 (2026), AMD Athlon Dual Core 7120U - (8 GB DDR5/512 GB SSD/AMD Radeon 610M Graphics/Windows 11 Pro) Thin and Light Business Laptop/15.6" HD Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
+          <t>HP 14 Smartchoice, Intel Core Ultra 5 125H 12 TOPS, 24GB DDR5 (Upgradeable) 1TB SSD, Anti-Glare, FHD, 14''/35.6cm,Win11, M365*Office24, Silver, 1.4kg, ep1180tu, FHD Camera w/Shutter, Backlit AI Laptop</t>
         </is>
       </c>
       <c r="C225" t="inlineStr"/>
       <c r="D225" t="n">
-        <v>42840</v>
+        <v>77990</v>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>hp_15_(2026),_amd_athlon</t>
+          <t>hp_14_smartchoice,_intel_core</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>HP 15 (2026), AMD Athlon Dual Core 7120U - (8 GB DDR5/512 GB SSD/AMD Radeon 610M Graphics/Windows 11 Pro) Thin and Light Business Laptop/15.6" HD Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
+          <t>HP 14 Smartchoice, Intel Core Ultra 5 125H 12 TOPS, 24GB DDR5 (Upgradeable) 1TB SSD, Anti-Glare, FHD, 14''/35.6cm,Win11, M365*Office24, Silver, 1.4kg, ep1180tu, FHD Camera w/Shutter, Backlit AI Laptop</t>
         </is>
       </c>
       <c r="C226" t="inlineStr"/>
       <c r="D226" t="n">
-        <v>42840</v>
+        <v>77990</v>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>hp_15_(2026),_amd_athlon</t>
+          <t>hp_14_smartchoice,_intel_core</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>HP 15 (2026), AMD Athlon Dual Core 7120U - (8 GB DDR5/512 GB SSD/AMD Radeon 610M Graphics/Windows 11 Pro) Thin and Light Business Laptop/15.6" HD Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
+          <t>HP 14 Smartchoice, Intel Core Ultra 5 125H 12 TOPS, 24GB DDR5 (Upgradeable) 1TB SSD, Anti-Glare, FHD, 14''/35.6cm,Win11, M365*Office24, Silver, 1.4kg, ep1180tu, FHD Camera w/Shutter, Backlit AI Laptop</t>
         </is>
       </c>
       <c r="C227" t="inlineStr"/>
       <c r="D227" t="n">
-        <v>42840</v>
+        <v>79990</v>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>hp_15_(2026),_amd_athlon</t>
+          <t>hp_14_smartchoice,_intel_core</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>HP 15 (2026), AMD Athlon Dual Core 7120U - (8 GB DDR5/512 GB SSD/AMD Radeon 610M Graphics/Windows 11 Pro) Thin and Light Business Laptop/15.6" HD Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
+          <t>HP 14 Smartchoice, Intel Core Ultra 5 125H 12 TOPS, 24GB DDR5 (Upgradeable) 1TB SSD, Anti-Glare, FHD, 14''/35.6cm,Win11, M365*Office24, Silver, 1.4kg, ep1180tu, FHD Camera w/Shutter, Backlit AI Laptop</t>
         </is>
       </c>
       <c r="C228" t="inlineStr"/>
       <c r="D228" t="n">
-        <v>43450</v>
+        <v>79990</v>
       </c>
       <c r="E228" t="inlineStr">
         <is>
@@ -5213,38 +5213,38 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>HP 15 (2026), AMD Ryzen</t>
+          <t>hp_14_smartchoice,_intel_core</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>HP 15 (2026), AMD Ryzen 3 Quad Core 7335U - (8 GB DDR5/512 GB SSD/AMD Radeon 660M Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
+          <t>HP 14 Smartchoice, Intel Core Ultra 5 125H 12 TOPS, 24GB DDR5 (Upgradeable) 1TB SSD, Anti-Glare, FHD, 14''/35.6cm,Win11, M365*Office24, Silver, 1.4kg, ep1180tu, FHD Camera w/Shutter, Backlit AI Laptop</t>
         </is>
       </c>
       <c r="C229" t="inlineStr"/>
       <c r="D229" t="n">
-        <v>42780</v>
+        <v>79990</v>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>hp_15_(i5_14th_gen),</t>
+          <t>hp_14,_amd_ryzen_7</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>HP 15 (i5 14th Gen), Intel Core 5, 16GB RAM (Upgradeable), 512GB SSD, FHD, Anti-Glare, 15.6''/39.6cm, Win11, M365 Basic(1yr), Office24, Silver,1.59kg, fd0682tu, FHD Camera w/Shutter, Backlit Laptop</t>
+          <t>HP 14, AMD Ryzen 7 7730U (16GB DDR4, 512GB SSD) FHD, Anti-Glare, Micro-Edge, 14''/35.6cm, Win11, M365 Basic(1yr), Office Home24, Silver,1.4kg, EM0104AU, FHD Camera w/Privacy Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C230" t="inlineStr"/>
       <c r="D230" t="n">
-        <v>63990</v>
+        <v>59990</v>
       </c>
       <c r="E230" t="inlineStr">
         <is>
@@ -5255,374 +5255,374 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>hp_15_(i5_14th_gen),</t>
+          <t>hp_14,_amd_ryzen_7</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>HP 15 (i5 14th Gen), Intel Core 5, 16GB RAM (Upgradeable), 512GB SSD, FHD, Anti-Glare, 15.6''/39.6cm, Win11, M365 Basic(1yr), Office24, Silver,1.59kg, fd0682tu, FHD Camera w/Shutter, Backlit Laptop</t>
+          <t>HP 14, AMD Ryzen 7 7730U (16GB DDR4, 512GB SSD) FHD, Anti-Glare, Micro-Edge, 14''/35.6cm, Win11, M365 Basic(1yr), Office Home24, Silver,1.4kg, EM0104AU, FHD Camera w/Privacy Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C231" t="inlineStr"/>
       <c r="D231" t="n">
-        <v>67990</v>
+        <v>64990</v>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>hp_15_laptop_|_amd</t>
+          <t>HP 14s Intel Celeron Dual</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>HP 15 Laptop | AMD Ryzen 7 5825U |16GB DDR4 RAM | 512GB SSD |15.6" (39.6 cm) FHD Display |AMD Radeon Graphics| Backlit KB | FHD Camera| Win 11| MS Office 2024 + M365*(1-Yr) | Silver |1.59kg |fc0533AU</t>
+          <t>HP 14s Intel Celeron Dual Core N4500 Laptop (8GB/512GB SSD/Win 11) 14.0" HD Display, MSO 24, Black, 1.46kg, DQ3149TU Thin and Light Business Laptop</t>
         </is>
       </c>
       <c r="C232" t="inlineStr"/>
       <c r="D232" t="n">
-        <v>64990</v>
+        <v>40400</v>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-04-16</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>hp_15_laptop_|_intel</t>
+          <t>hp_15_(2025),_amd_athlon</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>HP 15 Laptop | Intel Core i5-13420H,13th Gen |16GB RAM | 512GB SSD | Win 11 |M365 Basic(1yr)* Office24|Anti-Glare, Micro-Edge, 15.6''/39.6cm|Backlit KB|FHD Camera w/Shutter|1.65kg, Silver -FR0045TU</t>
+          <t>HP 15 (2025), AMD Athlon 7120U Dual Core - (8 GB/256 GB SSD/AMD Radeon Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" HD Display/Black/1.5 kg/MS Office 2021</t>
         </is>
       </c>
       <c r="C233" t="inlineStr"/>
       <c r="D233" t="n">
-        <v>68990</v>
+        <v>41999</v>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>hp_15_laptop,_(14th_gen</t>
+          <t>hp_15_(2025),_amd_athlon</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>HP 15 Laptop, (14th Gen Core i5) Intel Core 5-120U (24GB RAM, 512GB SSD, Win 11, M365 Basic(1yr)* Office24,15.6''/39.6cm FHD Anti-Glare Display, Backlit KB, FHD Camera, Dual Speakers, Silver, 1.59kg)</t>
+          <t>HP 15 (2025), AMD Athlon 7120U Dual Core - (8 GB/256 GB SSD/AMD Radeon Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" HD Display/Black/1.5 kg/MS Office 2021</t>
         </is>
       </c>
       <c r="C234" t="inlineStr"/>
       <c r="D234" t="n">
-        <v>72800</v>
+        <v>41999</v>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-08-04</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>hp_15_laptop,_(14th_gen</t>
+          <t>hp_15_(2025),_amd_athlon</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>HP 15 Laptop, (14th Gen Core i5) Intel Core 5-120U (24GB RAM, 512GB SSD, Win 11, M365 Basic(1yr)* Office24,15.6''/39.6cm FHD Anti-Glare Display, Backlit KB, FHD Camera, Dual Speakers, Silver, 1.59kg)</t>
+          <t>HP 15 (2025), AMD Athlon 7120U Dual Core - (8 GB/256 GB SSD/AMD Radeon Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" HD Display/Black/1.5 kg/MS Office 2021</t>
         </is>
       </c>
       <c r="C235" t="inlineStr"/>
       <c r="D235" t="n">
-        <v>72900</v>
+        <v>41999</v>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>HP 15 Laptop, Intel (14th</t>
+          <t>HP 15 (2026), AMD Athlon</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>HP 15 Laptop, Intel (14th Gen) Core 5 120U (24GB DDR5, 512GB SSD), Micro-Edge, Anti-Glare, 15.6''/39.6cm, Win11, M365* Office24, Silver, 1.59kg, fd0262TU, FHD Camera, Backlit, Dual Speakers</t>
+          <t>HP 15 (2026), AMD Athlon Dual Core 7120U - (8 GB DDR5/512 GB SSD/AMD Radeon 610M Graphics/DOS) Thin and Light Business Laptop/15.6" HD Display/Turbo Silver/Copilot Key/1.5kg</t>
         </is>
       </c>
       <c r="C236" t="inlineStr"/>
       <c r="D236" t="n">
-        <v>67990</v>
+        <v>39999</v>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-08</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, 13th Gen</t>
+          <t>HP 15 (2026), AMD Athlon</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U (12GB DDR4, 512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver, 1.59kg, fd0573TU, FHD Camera w/Shutter Laptop</t>
+          <t>HP 15 (2026), AMD Athlon Dual Core 7120U - (8 GB DDR5/512 GB SSD/AMD Radeon 610M Graphics/Windows 11 Pro) Thin and Light Business Laptop/15.6" HD Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
         </is>
       </c>
       <c r="C237" t="inlineStr"/>
       <c r="D237" t="n">
-        <v>55990</v>
+        <v>39660</v>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, 13th Gen</t>
+          <t>hp_15_(2026),_amd_athlon</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U(8GB DDR4,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
+          <t>HP 15 (2026), AMD Athlon Dual Core 7120U - (8 GB DDR5/512 GB SSD/AMD Radeon 610M Graphics/Windows 11 Pro) Thin and Light Business Laptop/15.6" HD Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
         </is>
       </c>
       <c r="C238" t="inlineStr"/>
       <c r="D238" t="n">
-        <v>51990</v>
+        <v>41999</v>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, 13th Gen</t>
+          <t>hp_15_(2026),_amd_athlon</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U(8GB DDR4,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
+          <t>HP 15 (2026), AMD Athlon Dual Core 7120U - (8 GB DDR5/512 GB SSD/AMD Radeon 610M Graphics/Windows 11 Pro) Thin and Light Business Laptop/15.6" HD Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
         </is>
       </c>
       <c r="C239" t="inlineStr"/>
       <c r="D239" t="n">
-        <v>51990</v>
+        <v>42840</v>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, 13th Gen</t>
+          <t>hp_15_(2026),_amd_athlon</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U(8GB DDR4,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
+          <t>HP 15 (2026), AMD Athlon Dual Core 7120U - (8 GB DDR5/512 GB SSD/AMD Radeon 610M Graphics/Windows 11 Pro) Thin and Light Business Laptop/15.6" HD Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
         </is>
       </c>
       <c r="C240" t="inlineStr"/>
       <c r="D240" t="n">
-        <v>51990</v>
+        <v>42840</v>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, 13th Gen</t>
+          <t>hp_15_(2026),_amd_athlon</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U(8GB DDR4,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
+          <t>HP 15 (2026), AMD Athlon Dual Core 7120U - (8 GB DDR5/512 GB SSD/AMD Radeon 610M Graphics/Windows 11 Pro) Thin and Light Business Laptop/15.6" HD Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
         </is>
       </c>
       <c r="C241" t="inlineStr"/>
       <c r="D241" t="n">
-        <v>51990</v>
+        <v>42840</v>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, 13th Gen</t>
+          <t>hp_15_(2026),_amd_athlon</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U(8GB DDR4,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
+          <t>HP 15 (2026), AMD Athlon Dual Core 7120U - (8 GB DDR5/512 GB SSD/AMD Radeon 610M Graphics/Windows 11 Pro) Thin and Light Business Laptop/15.6" HD Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
         </is>
       </c>
       <c r="C242" t="inlineStr"/>
       <c r="D242" t="n">
-        <v>51990</v>
+        <v>42840</v>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-08-04</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>hp_15_smartchoice,_13th_gen</t>
+          <t>hp_15_(2026),_amd_athlon</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U(8GB DDR4,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
+          <t>HP 15 (2026), AMD Athlon Dual Core 7120U - (8 GB DDR5/512 GB SSD/AMD Radeon 610M Graphics/Windows 11 Pro) Thin and Light Business Laptop/15.6" HD Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
         </is>
       </c>
       <c r="C243" t="inlineStr"/>
       <c r="D243" t="n">
-        <v>49990</v>
+        <v>43450</v>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-08-05</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>hp_15_smartchoice,_13th_gen</t>
+          <t>hp_15_(2026),_amd_athlon</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U(8GB DDR4,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
+          <t>HP 15 (2026), AMD Athlon Dual Core 7120U - (8 GB DDR5/512 GB SSD/AMD Radeon 610M Graphics/Windows 11 Pro) Thin and Light Business Laptop/15.6" HD Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
         </is>
       </c>
       <c r="C244" t="inlineStr"/>
       <c r="D244" t="n">
-        <v>49990</v>
+        <v>42840</v>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>hp_15_smartchoice,_13th_gen</t>
+          <t>HP 15 (2026), AMD Ryzen</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U(8GB DDR4,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
+          <t>HP 15 (2026), AMD Ryzen 3 Quad Core 7335U - (8 GB DDR5/512 GB SSD/AMD Radeon 660M Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
         </is>
       </c>
       <c r="C245" t="inlineStr"/>
       <c r="D245" t="n">
-        <v>49990</v>
+        <v>42780</v>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>hp_15_smartchoice,_13th_gen</t>
+          <t>hp_15_(i5_14th_gen),</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U(8GB DDR4,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
+          <t>HP 15 (i5 14th Gen), Intel Core 5, 16GB RAM (Upgradeable), 512GB SSD, FHD, Anti-Glare, 15.6''/39.6cm, Win11, M365 Basic(1yr), Office24, Silver,1.59kg, fd0682tu, FHD Camera w/Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C246" t="inlineStr"/>
       <c r="D246" t="n">
-        <v>49990</v>
+        <v>63990</v>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>hp_15_smartchoice,_intel_core</t>
+          <t>hp_15_(i5_14th_gen),</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, Intel Core Ultra 5 125H, 12 Tops (16GB DDR5, 512GB SSD) FHD, IPS, 15.6''/39.6cm, Win11, M365(1yr)* Office24, Silver, 1.65kg, fd1254TU, FHD Camera w/Shutter, AI Powered Laptop</t>
+          <t>HP 15 (i5 14th Gen), Intel Core 5, 16GB RAM (Upgradeable), 512GB SSD, FHD, Anti-Glare, 15.6''/39.6cm, Win11, M365 Basic(1yr), Office24, Silver,1.59kg, fd0682tu, FHD Camera w/Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C247" t="inlineStr"/>
       <c r="D247" t="n">
-        <v>69990</v>
+        <v>67990</v>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>hp_15_smartchoice,_intel_core</t>
+          <t>hp_15_laptop_|_amd</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>HP 15 Smartchoice, Intel Core Ultra 5 125H, 12 Tops (16GB DDR5, 512GB SSD) FHD, IPS, 15.6''/39.6cm, Win11, M365(1yr)* Office24, Silver, 1.65kg, fd1254TU, FHD Camera w/Shutter, AI Powered Laptop</t>
+          <t>HP 15 Laptop | AMD Ryzen 7 5825U |16GB DDR4 RAM | 512GB SSD |15.6" (39.6 cm) FHD Display |AMD Radeon Graphics| Backlit KB | FHD Camera| Win 11| MS Office 2024 + M365*(1-Yr) | Silver |1.59kg |fc0533AU</t>
         </is>
       </c>
       <c r="C248" t="inlineStr"/>
       <c r="D248" t="n">
-        <v>69990</v>
+        <v>64990</v>
       </c>
       <c r="E248" t="inlineStr">
         <is>
@@ -5633,336 +5633,336 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel</t>
+          <t>hp_15_laptop_|_intel</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U (8GB DDR4, 512GB SSD), FHD, Micro -Edge, Anti-Glare, 15.6''/39.6cm, Win11, M365* Office24, Silver, 1.59kg, fd0624tu, FHD Camera, UHD Graphics Laptop</t>
+          <t>HP 15 Laptop | Intel Core i5-13420H,13th Gen |16GB RAM | 512GB SSD | Win 11 |M365 Basic(1yr)* Office24|Anti-Glare, Micro-Edge, 15.6''/39.6cm|Backlit KB|FHD Camera w/Shutter|1.65kg, Silver -FR0045TU</t>
         </is>
       </c>
       <c r="C249" t="inlineStr"/>
       <c r="D249" t="n">
-        <v>47490</v>
+        <v>68990</v>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>hp_15,_13th_gen_intel</t>
+          <t>hp_15_laptop,_(14th_gen</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U (8GB DDR4, 512GB SSD), FHD, Micro -Edge, Anti-Glare, 15.6''/39.6cm, Win11, M365* Office24, Silver, 1.59kg, fd0624tu, FHD Camera, UHD Graphics Laptop</t>
+          <t>HP 15 Laptop, (14th Gen Core i5) Intel Core 5-120U (24GB RAM, 512GB SSD, Win 11, M365 Basic(1yr)* Office24,15.6''/39.6cm FHD Anti-Glare Display, Backlit KB, FHD Camera, Dual Speakers, Silver, 1.59kg)</t>
         </is>
       </c>
       <c r="C250" t="inlineStr"/>
       <c r="D250" t="n">
-        <v>48990</v>
+        <v>72800</v>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>hp_15,_13th_gen_intel</t>
+          <t>hp_15_laptop,_(14th_gen</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U (8GB DDR4, 512GB SSD), FHD, Micro -Edge, Anti-Glare, 15.6''/39.6cm, Win11, M365* Office24, Silver, 1.59kg, fd0624tu, FHD Camera, UHD Graphics Laptop</t>
+          <t>HP 15 Laptop, (14th Gen Core i5) Intel Core 5-120U (24GB RAM, 512GB SSD, Win 11, M365 Basic(1yr)* Office24,15.6''/39.6cm FHD Anti-Glare Display, Backlit KB, FHD Camera, Dual Speakers, Silver, 1.59kg)</t>
         </is>
       </c>
       <c r="C251" t="inlineStr"/>
       <c r="D251" t="n">
-        <v>48990</v>
+        <v>72900</v>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>hp_15,_13th_gen_intel</t>
+          <t>HP 15 Laptop, Intel (14th</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U (8GB DDR4, 512GB SSD), FHD, Micro -Edge, Anti-Glare, 15.6''/39.6cm, Win11, M365* Office24, Silver, 1.59kg, fd0624tu, FHD Camera, UHD Graphics Laptop</t>
+          <t>HP 15 Laptop, Intel (14th Gen) Core 5 120U (24GB DDR5, 512GB SSD), Micro-Edge, Anti-Glare, 15.6''/39.6cm, Win11, M365* Office24, Silver, 1.59kg, fd0262TU, FHD Camera, Backlit, Dual Speakers</t>
         </is>
       </c>
       <c r="C252" t="inlineStr"/>
       <c r="D252" t="n">
-        <v>48990</v>
+        <v>67990</v>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>hp_15,_13th_gen_intel</t>
+          <t>HP 15 Smartchoice, 13th Gen</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U (8GB DDR4, 512GB SSD), FHD, Micro -Edge, Anti-Glare, 15.6''/39.6cm, Win11, M365* Office24, Silver, 1.59kg, fd0624tu, FHD Camera, UHD Graphics Laptop</t>
+          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U (12GB DDR4, 512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver, 1.59kg, fd0573TU, FHD Camera w/Shutter Laptop</t>
         </is>
       </c>
       <c r="C253" t="inlineStr"/>
       <c r="D253" t="n">
-        <v>48990</v>
+        <v>55990</v>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-06-12</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel</t>
+          <t>HP 15 Smartchoice, 13th Gen</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
+          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U(8GB DDR4,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C254" t="inlineStr"/>
       <c r="D254" t="n">
-        <v>47990</v>
+        <v>51990</v>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel</t>
+          <t>HP 15 Smartchoice, 13th Gen</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
+          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U(8GB DDR4,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C255" t="inlineStr"/>
       <c r="D255" t="n">
-        <v>47990</v>
+        <v>51990</v>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel</t>
+          <t>HP 15 Smartchoice, 13th Gen</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
+          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U(8GB DDR4,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C256" t="inlineStr"/>
       <c r="D256" t="n">
-        <v>46990</v>
+        <v>51990</v>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel</t>
+          <t>HP 15 Smartchoice, 13th Gen</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
+          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U(8GB DDR4,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C257" t="inlineStr"/>
       <c r="D257" t="n">
-        <v>46990</v>
+        <v>51990</v>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel</t>
+          <t>HP 15 Smartchoice, 13th Gen</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
+          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U(8GB DDR4,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C258" t="inlineStr"/>
       <c r="D258" t="n">
-        <v>46990</v>
+        <v>51990</v>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel</t>
+          <t>hp_15_smartchoice,_13th_gen</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
+          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U(8GB DDR4,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C259" t="inlineStr"/>
       <c r="D259" t="n">
-        <v>46990</v>
+        <v>49990</v>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel</t>
+          <t>hp_15_smartchoice,_13th_gen</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
+          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U(8GB DDR4,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C260" t="inlineStr"/>
       <c r="D260" t="n">
-        <v>46990</v>
+        <v>49990</v>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel</t>
+          <t>hp_15_smartchoice,_13th_gen</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
+          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U(8GB DDR4,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C261" t="inlineStr"/>
       <c r="D261" t="n">
-        <v>46990</v>
+        <v>49990</v>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel</t>
+          <t>hp_15_smartchoice,_13th_gen</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
+          <t>HP 15 Smartchoice, 13th Gen Intel Core i3-1315U(8GB DDR4,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365(1yr)*Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C262" t="inlineStr"/>
       <c r="D262" t="n">
-        <v>48900</v>
+        <v>49990</v>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel</t>
+          <t>hp_15_smartchoice,_intel_core</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
+          <t>HP 15 Smartchoice, Intel Core Ultra 5 125H, 12 Tops (16GB DDR5, 512GB SSD) FHD, IPS, 15.6''/39.6cm, Win11, M365(1yr)* Office24, Silver, 1.65kg, fd1254TU, FHD Camera w/Shutter, AI Powered Laptop</t>
         </is>
       </c>
       <c r="C263" t="inlineStr"/>
       <c r="D263" t="n">
-        <v>48900</v>
+        <v>69990</v>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel</t>
+          <t>hp_15_smartchoice,_intel_core</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
+          <t>HP 15 Smartchoice, Intel Core Ultra 5 125H, 12 Tops (16GB DDR5, 512GB SSD) FHD, IPS, 15.6''/39.6cm, Win11, M365(1yr)* Office24, Silver, 1.65kg, fd1254TU, FHD Camera w/Shutter, AI Powered Laptop</t>
         </is>
       </c>
       <c r="C264" t="inlineStr"/>
       <c r="D264" t="n">
-        <v>50000</v>
+        <v>69990</v>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -5974,100 +5974,100 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U (8GB DDR4, 512GB SSD), FHD, Micro -Edge, Anti-Glare, 15.6''/39.6cm, Win11, M365* Office24, Silver, 1.59kg, fd0624tu, FHD Camera, UHD Graphics Laptop</t>
         </is>
       </c>
       <c r="C265" t="inlineStr"/>
       <c r="D265" t="n">
-        <v>49850</v>
+        <v>47490</v>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-04-16</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel</t>
+          <t>hp_15,_13th_gen_intel</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U (8GB DDR4, 512GB SSD), FHD, Micro -Edge, Anti-Glare, 15.6''/39.6cm, Win11, M365* Office24, Silver, 1.59kg, fd0624tu, FHD Camera, UHD Graphics Laptop</t>
         </is>
       </c>
       <c r="C266" t="inlineStr"/>
       <c r="D266" t="n">
-        <v>49990</v>
+        <v>48990</v>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel</t>
+          <t>hp_15,_13th_gen_intel</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U (8GB DDR4, 512GB SSD), FHD, Micro -Edge, Anti-Glare, 15.6''/39.6cm, Win11, M365* Office24, Silver, 1.59kg, fd0624tu, FHD Camera, UHD Graphics Laptop</t>
         </is>
       </c>
       <c r="C267" t="inlineStr"/>
       <c r="D267" t="n">
-        <v>49820</v>
+        <v>48990</v>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel</t>
+          <t>hp_15,_13th_gen_intel</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U (8GB DDR4, 512GB SSD), FHD, Micro -Edge, Anti-Glare, 15.6''/39.6cm, Win11, M365* Office24, Silver, 1.59kg, fd0624tu, FHD Camera, UHD Graphics Laptop</t>
         </is>
       </c>
       <c r="C268" t="inlineStr"/>
       <c r="D268" t="n">
-        <v>49820</v>
+        <v>48990</v>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel</t>
+          <t>hp_15,_13th_gen_intel</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U (8GB DDR4, 512GB SSD), FHD, Micro -Edge, Anti-Glare, 15.6''/39.6cm, Win11, M365* Office24, Silver, 1.59kg, fd0624tu, FHD Camera, UHD Graphics Laptop</t>
         </is>
       </c>
       <c r="C269" t="inlineStr"/>
       <c r="D269" t="n">
-        <v>50400</v>
+        <v>48990</v>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-08-04</t>
         </is>
       </c>
     </row>
@@ -6084,11 +6084,11 @@
       </c>
       <c r="C270" t="inlineStr"/>
       <c r="D270" t="n">
-        <v>50390</v>
+        <v>47990</v>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -6105,11 +6105,11 @@
       </c>
       <c r="C271" t="inlineStr"/>
       <c r="D271" t="n">
-        <v>50150</v>
+        <v>47990</v>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -6126,11 +6126,11 @@
       </c>
       <c r="C272" t="inlineStr"/>
       <c r="D272" t="n">
-        <v>50040</v>
+        <v>46990</v>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-08</t>
         </is>
       </c>
     </row>
@@ -6147,11 +6147,11 @@
       </c>
       <c r="C273" t="inlineStr"/>
       <c r="D273" t="n">
-        <v>50040</v>
+        <v>46990</v>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
@@ -6168,11 +6168,11 @@
       </c>
       <c r="C274" t="inlineStr"/>
       <c r="D274" t="n">
-        <v>49670</v>
+        <v>46990</v>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-05-10</t>
         </is>
       </c>
     </row>
@@ -6189,11 +6189,11 @@
       </c>
       <c r="C275" t="inlineStr"/>
       <c r="D275" t="n">
-        <v>49480</v>
+        <v>46990</v>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-14</t>
         </is>
       </c>
     </row>
@@ -6210,11 +6210,11 @@
       </c>
       <c r="C276" t="inlineStr"/>
       <c r="D276" t="n">
-        <v>49470</v>
+        <v>46990</v>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-15</t>
         </is>
       </c>
     </row>
@@ -6231,11 +6231,11 @@
       </c>
       <c r="C277" t="inlineStr"/>
       <c r="D277" t="n">
-        <v>49300</v>
+        <v>46990</v>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-05-17</t>
         </is>
       </c>
     </row>
@@ -6247,453 +6247,453 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>HP 15, 13th Gen Intel Core i3-1315U, (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge, FHD,15.6''/39.6cm, Win11,M365 Basic(1yr),Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
         </is>
       </c>
       <c r="C278" t="inlineStr"/>
       <c r="D278" t="n">
-        <v>47990</v>
+        <v>48900</v>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-19</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>HP 15, AMD Ryzen 5</t>
+          <t>HP 15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>HP 15, AMD Ryzen 5 7520U,(16GB LPDDR5, 512GB SSD), Anti-Glare, Micro-Edge, FHD, 15.6''/39.6cm, Win 11, Office 24,M365 Basic(1yr)*,Silver, 1.59kg, fc0690au, FHD Camera, Backlit KB Laptop</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
         </is>
       </c>
       <c r="C279" t="inlineStr"/>
       <c r="D279" t="n">
-        <v>53990</v>
+        <v>48900</v>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-20</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>HP 15, AMD Ryzen 5</t>
+          <t>HP 15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>HP 15, AMD Ryzen 5 7520U,(16GB LPDDR5, 512GB SSD), Anti-Glare, Micro-Edge, FHD, 15.6''/39.6cm, Win 11, Office 24,M365 Basic(1yr)*,Silver, 1.59kg, fc0690au, FHD Camera, Backlit KB Laptop</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
         </is>
       </c>
       <c r="C280" t="inlineStr"/>
       <c r="D280" t="n">
-        <v>53990</v>
+        <v>50000</v>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-21</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>HP 15, AMD Ryzen 5</t>
+          <t>HP 15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>HP 15, AMD Ryzen 5 7520U,(16GB LPDDR5, 512GB SSD), Anti-Glare, Micro-Edge, FHD, 15.6''/39.6cm, Win 11, Office 24,M365 Basic(1yr)*,Silver, 1.59kg, fc0690au, FHD Camera, Backlit KB Laptop</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
         </is>
       </c>
       <c r="C281" t="inlineStr"/>
       <c r="D281" t="n">
-        <v>54990</v>
+        <v>49850</v>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-22</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>hp_15,_amd_ryzen_5</t>
+          <t>HP 15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>HP 15, AMD Ryzen 5 7520U,(16GB LPDDR5, 512GB SSD), Anti-Glare, Micro-Edge, FHD, 15.6''/39.6cm, Win 11, Office 24,M365 Basic(1yr)*,Silver, 1.59kg, fc0690au, FHD Camera, Backlit KB Laptop</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
         </is>
       </c>
       <c r="C282" t="inlineStr"/>
       <c r="D282" t="n">
-        <v>56830</v>
+        <v>49990</v>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>HP 15, AMD Ryzen 7</t>
+          <t>HP 15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>HP 15, AMD Ryzen 7 7735HS (16GB DDR5,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365 Basic(1yr)* Office24, Silver, 1.59kg, fc1038AU, AMD Radeon FHD Camera w/Shutter, Backlit Laptop</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
         </is>
       </c>
       <c r="C283" t="inlineStr"/>
       <c r="D283" t="n">
-        <v>59990</v>
+        <v>49820</v>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-24</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>HP 15, Intel Core 5</t>
+          <t>HP 15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>HP 15, Intel Core 5 120U (14th Gen) 16GB DDR4, 512GB SSD, FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365 Basic(1yr), Office24, Silver,1.59kg, FD0640TU/682tu, FHD Camera w/Shutter, BL Laptop</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
         </is>
       </c>
       <c r="C284" t="inlineStr"/>
       <c r="D284" t="n">
-        <v>65990</v>
+        <v>49820</v>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>hp_15,_intel_core_5-120u</t>
+          <t>HP 15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>HP 15, Intel Core 5-120U (8GB DDR4, 512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365 Basic(1yr), Office Home24, Silver,1.59kg, fd0651TU, FHD Camera w/Privacy Shutter, Backlit Laptop</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
         </is>
       </c>
       <c r="C285" t="inlineStr"/>
       <c r="D285" t="n">
-        <v>57500</v>
+        <v>50400</v>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>hp_15,_intel_core_5-120u</t>
+          <t>HP 15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>HP 15, Intel Core 5-120U (8GB DDR4, 512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365 Basic(1yr), Office Home24, Silver,1.59kg, fd0651TU, FHD Camera w/Privacy Shutter, Backlit Laptop</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
         </is>
       </c>
       <c r="C286" t="inlineStr"/>
       <c r="D286" t="n">
-        <v>57700</v>
+        <v>50390</v>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-05-27</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>hp_15,_intel_core_5-120u</t>
+          <t>HP 15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>HP 15, Intel Core 5-120U (8GB DDR4, 512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365 Basic(1yr), Office Home24, Silver,1.59kg, fd0651TU, FHD Camera w/Privacy Shutter, Backlit Laptop</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
         </is>
       </c>
       <c r="C287" t="inlineStr"/>
       <c r="D287" t="n">
-        <v>57700</v>
+        <v>50150</v>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-05-28</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>hp_15,_intel_core_ultra</t>
+          <t>HP 15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>HP 15, Intel Core Ultra 5 125H (16GB DDR5, 1TB SSD) FHD, IPS, 15.6''/39.6cm, Win11, M365 Basic(1yr)*Office24, Silver, 1.65kg, fd1354TU, Intel Arc Graphics, FHD Camera w/Shutter, AI Powered Laptop</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
         </is>
       </c>
       <c r="C288" t="inlineStr"/>
       <c r="D288" t="n">
-        <v>74990</v>
+        <v>50040</v>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>HP 15, Intel Core Ultra</t>
+          <t>HP 15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>HP 15, Intel Core Ultra 5 125H (24GB DDR5, 1TB SSD), Micro-Edge, Anti-Glare, FHD, 15''/39.6cm, Win11, M365* Office24, Silver, 1.65kg, FD1458TU, FHD Camera, Backlit Laptop</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
         </is>
       </c>
       <c r="C289" t="inlineStr"/>
       <c r="D289" t="n">
-        <v>84990</v>
+        <v>50040</v>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>hp_15,_intel_core_i3-1315u-13th</t>
+          <t>HP 15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>HP 15, Intel Core i3-1315U-13th Gen Laptop (8GB DDR4 Ram,512GB SSD) Anti-Glare, Micro-Edge,15.6'" FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera Shutter, 15-fd0569TU</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
         </is>
       </c>
       <c r="C290" t="inlineStr"/>
       <c r="D290" t="n">
-        <v>49490</v>
+        <v>49670</v>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>hp_15,_intel_core_i3-1315u-13th</t>
+          <t>HP 15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>HP 15, Intel Core i3-1315U-13th Gen Laptop (8GB DDR4 Ram,512GB SSD) Anti-Glare, Micro-Edge,15.6'" FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera Shutter, 15-fd0569TU</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
         </is>
       </c>
       <c r="C291" t="inlineStr"/>
       <c r="D291" t="n">
-        <v>50900</v>
+        <v>49480</v>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>HP 255R G10 Notebook (AMD</t>
+          <t>HP 15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>HP 255R G10 Notebook (AMD Athlon Silver 7120U /8GB/512GB/DOS) 15.6-inch(39.6cm), Anti-Glare, HD Laptop, Radeon Graphics, Silver,1.52kg</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
         </is>
       </c>
       <c r="C292" t="inlineStr"/>
       <c r="D292" t="n">
-        <v>41700</v>
+        <v>49470</v>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-06-12</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>HP 255R G10 Notebook (AMD</t>
+          <t>HP 15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>HP 255R G10 Notebook (AMD Athlon Silver 7120U /8GB/512GB/DOS) 15.6-inch(39.6cm), Anti-Glare, HD Laptop, Radeon Graphics, Silver,1.52kg</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U Laptop (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge,15.6''/39.6cm, FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera w/Privacy Shutter, fd0569TU</t>
         </is>
       </c>
       <c r="C293" t="inlineStr"/>
       <c r="D293" t="n">
-        <v>39340</v>
+        <v>49300</v>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>HP 255R G10 Notebook (AMD</t>
+          <t>HP 15, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>HP 255R G10 Notebook (AMD Athlon Silver 7120U /8GB/512GB/DOS) 15.6-inch(39.6cm), Anti-Glare, HD Laptop, Radeon Graphics, Silver,1.52kg</t>
+          <t>HP 15, 13th Gen Intel Core i3-1315U, (8GB DDR4,512GB SSD) Anti-Glare, Micro-Edge, FHD,15.6''/39.6cm, Win11,M365 Basic(1yr),Office24, Silver,1.59kg, fd0572TU, FHD Camera w/Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C294" t="inlineStr"/>
       <c r="D294" t="n">
-        <v>40409</v>
+        <v>47990</v>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>HP 255R G10 Notebook (AMD</t>
+          <t>HP 15, AMD Ryzen 5</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>HP 255R G10 Notebook (AMD Athlon Silver 7120U /8GB/512GB/DOS) 15.6-inch(39.6cm), Anti-Glare, HD Laptop, Radeon Graphics, Silver,1.52kg</t>
+          <t>HP 15, AMD Ryzen 5 7520U,(16GB LPDDR5, 512GB SSD), Anti-Glare, Micro-Edge, FHD, 15.6''/39.6cm, Win 11, Office 24,M365 Basic(1yr)*,Silver, 1.59kg, fc0690au, FHD Camera, Backlit KB Laptop</t>
         </is>
       </c>
       <c r="C295" t="inlineStr"/>
       <c r="D295" t="n">
-        <v>39618</v>
+        <v>53990</v>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-08</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>HP 255R G10 Notebook (AMD</t>
+          <t>HP 15, AMD Ryzen 5</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>HP 255R G10 Notebook (AMD Athlon Silver 7120U /8GB/512GB/DOS) 15.6-inch(39.6cm), Anti-Glare, HD Laptop, Radeon Graphics, Silver,1.52kg</t>
+          <t>HP 15, AMD Ryzen 5 7520U,(16GB LPDDR5, 512GB SSD), Anti-Glare, Micro-Edge, FHD, 15.6''/39.6cm, Win 11, Office 24,M365 Basic(1yr)*,Silver, 1.59kg, fc0690au, FHD Camera, Backlit KB Laptop</t>
         </is>
       </c>
       <c r="C296" t="inlineStr"/>
       <c r="D296" t="n">
-        <v>39525</v>
+        <v>53990</v>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>HP Omen, Intel Core Ultra</t>
+          <t>HP 15, AMD Ryzen 5</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>HP Omen, Intel Core Ultra 7 255H, 8GB RTX 5050, 24GB DDR5(Upgradeable) 1TB SSD, 2K, 165Hz, 3ms Response time, IPS, 16''/40.6cm, Win11, M365*Office24, Shadow Black, 2.43kg, am0240tx, RGB Gaming Laptop</t>
+          <t>HP 15, AMD Ryzen 5 7520U,(16GB LPDDR5, 512GB SSD), Anti-Glare, Micro-Edge, FHD, 15.6''/39.6cm, Win 11, Office 24,M365 Basic(1yr)*,Silver, 1.59kg, fc0690au, FHD Camera, Backlit KB Laptop</t>
         </is>
       </c>
       <c r="C297" t="inlineStr"/>
       <c r="D297" t="n">
-        <v>129990</v>
+        <v>54990</v>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-24</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>HP OmniBook 3, AMD Ryzen</t>
+          <t>hp_15,_amd_ryzen_5</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>HP OmniBook 3, AMD Ryzen AI 5 330 (24GB DDR5 RAM, 1TB SSD) FHD, Anti-Glare, 15.6''/39.6cm, Win11, Office24, Glacier Silver,1.7kg, fn0074AU, FHD Camera w/Shutter, FPR, Backlit KB, Next Gen AI Laptop</t>
+          <t>HP 15, AMD Ryzen 5 7520U,(16GB LPDDR5, 512GB SSD), Anti-Glare, Micro-Edge, FHD, 15.6''/39.6cm, Win 11, Office 24,M365 Basic(1yr)*,Silver, 1.59kg, fc0690au, FHD Camera, Backlit KB Laptop</t>
         </is>
       </c>
       <c r="C298" t="inlineStr"/>
       <c r="D298" t="n">
-        <v>69990</v>
+        <v>56830</v>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>HP OmniBook 5 OLED (Previously</t>
+          <t>HP 15, AMD Ryzen 7</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>HP OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x, 1TB SSD) 2K, 14''/35.6cm, Win11, M365 Basic(1yr)* Office24, Silver, 1.35kg, he0015QU, Light-Weight, Next-Gen AI Laptop</t>
+          <t>HP 15, AMD Ryzen 7 7735HS (16GB DDR5,512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365 Basic(1yr)* Office24, Silver, 1.59kg, fc1038AU, AMD Radeon FHD Camera w/Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C299" t="inlineStr"/>
       <c r="D299" t="n">
-        <v>69990</v>
+        <v>59990</v>
       </c>
       <c r="E299" t="inlineStr">
         <is>
@@ -6704,983 +6704,983 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>HP OmniBook 5 OLED (Previously</t>
+          <t>HP 15, Intel Core 5</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>HP OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x, 512GB SSD) 2K, 14''/35.6cm, Win11, M365 Basic(1yr)* Office24, Silver, 1.35kg, he0014QU, Light-Weight, Next-Gen AI Laptop</t>
+          <t>HP 15, Intel Core 5 120U (14th Gen) 16GB DDR4, 512GB SSD, FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365 Basic(1yr), Office24, Silver,1.59kg, FD0640TU/682tu, FHD Camera w/Shutter, BL Laptop</t>
         </is>
       </c>
       <c r="C300" t="inlineStr"/>
       <c r="D300" t="n">
-        <v>78990</v>
+        <v>65990</v>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>HP OmniBook 5 OLED (Previously</t>
+          <t>hp_15,_intel_core_5-120u</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>HP OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x, 512GB SSD) 2K, 14''/35.6cm, Win11, M365 Basic(1yr)* Office24, Silver, 1.35kg, he0014QU, Light-Weight, Next-Gen AI Laptop</t>
+          <t>HP 15, Intel Core 5-120U (8GB DDR4, 512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365 Basic(1yr), Office Home24, Silver,1.59kg, fd0651TU, FHD Camera w/Privacy Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C301" t="inlineStr"/>
       <c r="D301" t="n">
-        <v>66990</v>
+        <v>57500</v>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>hp_omnibook_5_oled_(previously</t>
+          <t>hp_15,_intel_core_5-120u</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>HP OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor 45 Tops (16GB LPDDR5x, 512GB SSD), 2K 14''/35.6cm, Win11, Office24, Silver, 1.29kg, he0014QU, Multi-Day Battery, AI Laptop</t>
+          <t>HP 15, Intel Core 5-120U (8GB DDR4, 512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365 Basic(1yr), Office Home24, Silver,1.59kg, fd0651TU, FHD Camera w/Privacy Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C302" t="inlineStr"/>
       <c r="D302" t="n">
-        <v>79990</v>
+        <v>57700</v>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>hp_omnibook_x_flip_oled</t>
+          <t>hp_15,_intel_core_5-120u</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>HP OmniBook X Flip OLED Intel Core Ultra 5 226V, 40 Tops (16GB LPDDR5x,1TB SSD) 3K, Touch, 120hz, 14''/35.6cm, Intel ARC Graphic,Win11, Office24, Meteor Silver, 1.38kg, fm0099TU,Pen, 2 in 1 AI Laptop</t>
+          <t>HP 15, Intel Core 5-120U (8GB DDR4, 512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365 Basic(1yr), Office Home24, Silver,1.59kg, fd0651TU, FHD Camera w/Privacy Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C303" t="inlineStr"/>
       <c r="D303" t="n">
-        <v>115990</v>
+        <v>57700</v>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-08-05</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>hp_omnibook_3,_snapdragon_x</t>
+          <t>hp_15,_intel_core_5-120u</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>HP Omnibook 3, Snapdragon X Processor 45 TOPS (16GB LPDDR5x,512GB SSD) 2K WUXGA, Anti-Glare, 14''/35.6cm, Win 11, M365*Office 24,Silver,1.42kg, hz0026QU, Lighter mini Charger, FHD IR Camera, AI Laptop</t>
+          <t>HP 15, Intel Core 5-120U (8GB DDR4, 512GB SSD) FHD, Anti-Glare, Micro-Edge, 15.6''/39.6cm, Win11, M365 Basic(1yr), Office Home24, Silver,1.59kg, fd0651TU, FHD Camera w/Privacy Shutter, Backlit Laptop</t>
         </is>
       </c>
       <c r="C304" t="inlineStr"/>
       <c r="D304" t="n">
-        <v>79990</v>
+        <v>57700</v>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>HP Omnibook 3, Snapdragon X</t>
+          <t>hp_15,_intel_core_ultra</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>HP Omnibook 3, Snapdragon X Processor, 45 TOPS (16GB LPDDR5x, 512GB SSD) 2K, WUXGA, IPS, 14''/35.6cm, Win 11, Office 24, Silver, 1.4kg, hz0026QU, FHD IR Camera, 42% Lighter mini GaN Charger, AI Laptop</t>
+          <t>HP 15, Intel Core Ultra 5 125H (16GB DDR5, 1TB SSD) FHD, IPS, 15.6''/39.6cm, Win11, M365 Basic(1yr)*Office24, Silver, 1.65kg, fd1354TU, Intel Arc Graphics, FHD Camera w/Shutter, AI Powered Laptop</t>
         </is>
       </c>
       <c r="C305" t="inlineStr"/>
       <c r="D305" t="n">
-        <v>69990</v>
+        <v>74990</v>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-08-04</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>HP Omnibook 3, Snapdragon X</t>
+          <t>HP 15, Intel Core Ultra</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>HP Omnibook 3, Snapdragon X Processor, 45 TOPS (16GB LPDDR5x, 512GB SSD) 2K, WUXGA, IPS, 14''/35.6cm, Win 11, Office 24, Silver, 1.4kg, hz0026QU, FHD IR Camera, 42% Lighter mini GaN Charger, AI Laptop</t>
+          <t>HP 15, Intel Core Ultra 5 125H (24GB DDR5, 1TB SSD), Micro-Edge, Anti-Glare, FHD, 15''/39.6cm, Win11, M365* Office24, Silver, 1.65kg, FD1458TU, FHD Camera, Backlit Laptop</t>
         </is>
       </c>
       <c r="C306" t="inlineStr"/>
       <c r="D306" t="n">
-        <v>73990</v>
+        <v>84990</v>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>HP Omnibook 5 OLED (Previously</t>
+          <t>hp_15,_intel_core_i3-1315u-13th</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>HP Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x,1TB SSD) 2K OLED,16''/40.6cm, Win11, M365*Office24, Glacier Silver, 1.59kg, fb0001QU, Backlit, Next-Gen AI Laptop</t>
+          <t>HP 15, Intel Core i3-1315U-13th Gen Laptop (8GB DDR4 Ram,512GB SSD) Anti-Glare, Micro-Edge,15.6'" FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera Shutter, 15-fd0569TU</t>
         </is>
       </c>
       <c r="C307" t="inlineStr"/>
       <c r="D307" t="n">
-        <v>78850</v>
+        <v>49490</v>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>hp_omnibook_5_oled_(previously</t>
+          <t>hp_15,_intel_core_i3-1315u-13th</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>HP Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor 45 Tops (16GB LPDDR5x, 1TB SSD) 2K,16''/40.6cm, Win11, Office24, Silver, 1.59kg, fb0001QU, Multi-Day Battery AI Laptop</t>
+          <t>HP 15, Intel Core i3-1315U-13th Gen Laptop (8GB DDR4 Ram,512GB SSD) Anti-Glare, Micro-Edge,15.6'" FHD, Win11,M365 Basic(1yr),Office Home24, Silver,1.59kg, FHD Camera Shutter, 15-fd0569TU</t>
         </is>
       </c>
       <c r="C308" t="inlineStr"/>
       <c r="D308" t="n">
-        <v>77900</v>
+        <v>50900</v>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>hp_pavilion_plus,_intel_core</t>
+          <t>HP 255R G10 Notebook (AMD</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>HP Pavilion Plus, Intel Core i5-1335U-13th Gen Laptop, (16GB LPDDR5x,512GB SSD),IPS, 300 nits, 14''(35.6cm) 2K,Win 11, M365 Basic(1yr), Office Home 24, Silver,1.38kg, 5MP Camera w/Shutter, ew0107TU</t>
+          <t>HP 255R G10 Notebook (AMD Athlon Silver 7120U /8GB/512GB/DOS) 15.6-inch(39.6cm), Anti-Glare, HD Laptop, Radeon Graphics, Silver,1.52kg</t>
         </is>
       </c>
       <c r="C309" t="inlineStr"/>
       <c r="D309" t="n">
-        <v>63990</v>
+        <v>41700</v>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-04-16</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>hp_professional_15_(2026),_intel</t>
+          <t>HP 255R G10 Notebook (AMD</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>HP Professional 15 (2026), Intel (i3 14th Gen) Core 3 100U - (8 GB/512 GB SSD/Intel UHD Graphics/Windows 11 Home) Thin &amp; Light Business Laptop/15.6" Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
+          <t>HP 255R G10 Notebook (AMD Athlon Silver 7120U /8GB/512GB/DOS) 15.6-inch(39.6cm), Anti-Glare, HD Laptop, Radeon Graphics, Silver,1.52kg</t>
         </is>
       </c>
       <c r="C310" t="inlineStr"/>
       <c r="D310" t="n">
-        <v>48990</v>
+        <v>39340</v>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-10</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>hp_professional_15_(2026),_intel</t>
+          <t>HP 255R G10 Notebook (AMD</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>HP Professional 15 (2026), Intel (i3 14th Gen) Core 3 100U - (8 GB/512 GB SSD/Intel UHD Graphics/Windows 11 Home) Thin &amp; Light Business Laptop/15.6" Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
+          <t>HP 255R G10 Notebook (AMD Athlon Silver 7120U /8GB/512GB/DOS) 15.6-inch(39.6cm), Anti-Glare, HD Laptop, Radeon Graphics, Silver,1.52kg</t>
         </is>
       </c>
       <c r="C311" t="inlineStr"/>
       <c r="D311" t="n">
-        <v>51899</v>
+        <v>40409</v>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-05-20</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>hp_professional_15_(2026),_intel</t>
+          <t>HP 255R G10 Notebook (AMD</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>HP Professional 15 (2026), Intel (i3 14th Gen) Core 3 100U - (8 GB/512 GB SSD/Intel UHD Graphics/Windows 11 Home) Thin &amp; Light Business Laptop/15.6" Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
+          <t>HP 255R G10 Notebook (AMD Athlon Silver 7120U /8GB/512GB/DOS) 15.6-inch(39.6cm), Anti-Glare, HD Laptop, Radeon Graphics, Silver,1.52kg</t>
         </is>
       </c>
       <c r="C312" t="inlineStr"/>
       <c r="D312" t="n">
-        <v>51840</v>
+        <v>39618</v>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>hp_professional_15_(2026),_intel</t>
+          <t>HP 255R G10 Notebook (AMD</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>HP Professional 15 (2026), Intel (i3 14th Gen) Core 3 100U - (8 GB/512 GB SSD/Intel UHD Graphics/Windows 11 Home) Thin &amp; Light Business Laptop/15.6" Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
+          <t>HP 255R G10 Notebook (AMD Athlon Silver 7120U /8GB/512GB/DOS) 15.6-inch(39.6cm), Anti-Glare, HD Laptop, Radeon Graphics, Silver,1.52kg</t>
         </is>
       </c>
       <c r="C313" t="inlineStr"/>
       <c r="D313" t="n">
-        <v>51840</v>
+        <v>39525</v>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>HP Smartchoice OmniBook 5 OLED</t>
+          <t>hp_chromebook_14,_mediatek_kompanio</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>HP Smartchoice OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x, 1TB SSD) 2K, 14''/35.6cm, Win11, M365(1yr)*Office24, Silver,1.35kg, he0015QU,Light-Weight,Next-Gen AI Laptop</t>
+          <t>HP Chromebook 14, MediaTek Kompanio 540 (4GB LPDDR5, 128GB UFS) HD, Anti-Glare, Micro-Edge, 14''/35.6cm, ChromeOS, 100 GB Google One(1yr), Modern Gray,1.35kg, nm0004MU, HD Camera w/Shutter Laptop</t>
         </is>
       </c>
       <c r="C314" t="inlineStr"/>
       <c r="D314" t="n">
-        <v>82990</v>
+        <v>58733</v>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>HP Smartchoice OmniBook 5 OLED</t>
+          <t>HP Omen, Intel Core Ultra</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>HP Smartchoice OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x, 1TB SSD) 2K, 14''/35.6cm, Win11, M365(1yr)*Office24, Silver,1.35kg, he0015QU,Light-Weight,Next-Gen AI Laptop</t>
+          <t>HP Omen, Intel Core Ultra 7 255H, 8GB RTX 5050, 24GB DDR5(Upgradeable) 1TB SSD, 2K, 165Hz, 3ms Response time, IPS, 16''/40.6cm, Win11, M365*Office24, Shadow Black, 2.43kg, am0240tx, RGB Gaming Laptop</t>
         </is>
       </c>
       <c r="C315" t="inlineStr"/>
       <c r="D315" t="n">
-        <v>76990</v>
+        <v>129990</v>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-05-10</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>HP Smartchoice OmniBook 5 OLED</t>
+          <t>HP OmniBook 3, AMD Ryzen</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>HP Smartchoice OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x, 512GB SSD) 2K, 14''/35.6cm, Win11, M365(1yr)* Office24, Silver, 1.35kg, he0014QU, Next-Gen AI Laptop</t>
+          <t>HP OmniBook 3, AMD Ryzen AI 5 330 (24GB DDR5 RAM, 1TB SSD) FHD, Anti-Glare, 15.6''/39.6cm, Win11, Office24, Glacier Silver,1.7kg, fn0074AU, FHD Camera w/Shutter, FPR, Backlit KB, Next Gen AI Laptop</t>
         </is>
       </c>
       <c r="C316" t="inlineStr"/>
       <c r="D316" t="n">
-        <v>78990</v>
+        <v>69990</v>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>HP Smartchoice OmniBook 5 OLED</t>
+          <t>HP OmniBook 5 OLED (Previously</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>HP Smartchoice OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x, 512GB SSD) 2K, 14''/35.6cm, Win11, M365(1yr)* Office24, Silver, 1.35kg, he0014QU, Next-Gen AI Laptop</t>
+          <t>HP OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x, 1TB SSD) 2K, 14''/35.6cm, Win11, M365 Basic(1yr)* Office24, Silver, 1.35kg, he0015QU, Light-Weight, Next-Gen AI Laptop</t>
         </is>
       </c>
       <c r="C317" t="inlineStr"/>
       <c r="D317" t="n">
-        <v>79990</v>
+        <v>69990</v>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-14</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>HP Smartchoice Omnibook 5 OLED</t>
+          <t>HP OmniBook 5 OLED (Previously</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>HP Smartchoice Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x,1TB SSD) 2K OLED,16''/40.6cm, Win11, M365(1yr)*Office24, Glacier Silver, 1.59kg, fb0001QU,Next-Gen AI Laptop</t>
+          <t>HP OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x, 512GB SSD) 2K, 14''/35.6cm, Win11, M365 Basic(1yr)* Office24, Silver, 1.35kg, he0014QU, Light-Weight, Next-Gen AI Laptop</t>
         </is>
       </c>
       <c r="C318" t="inlineStr"/>
       <c r="D318" t="n">
-        <v>68739</v>
+        <v>78990</v>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>HP Smartchoice Omnibook 5 OLED</t>
+          <t>HP OmniBook 5 OLED (Previously</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>HP Smartchoice Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x,1TB SSD) 2K OLED,16''/40.6cm, Win11, M365(1yr)*Office24, Glacier Silver, 1.59kg, fb0001QU,Next-Gen AI Laptop</t>
+          <t>HP OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x, 512GB SSD) 2K, 14''/35.6cm, Win11, M365 Basic(1yr)* Office24, Silver, 1.35kg, he0014QU, Light-Weight, Next-Gen AI Laptop</t>
         </is>
       </c>
       <c r="C319" t="inlineStr"/>
       <c r="D319" t="n">
-        <v>68739</v>
+        <v>66990</v>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>HP Smartchoice Omnibook 5 OLED</t>
+          <t>hp_omnibook_5_oled_(previously</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>HP Smartchoice Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x,1TB SSD) 2K OLED,16''/40.6cm, Win11, M365(1yr)*Office24, Glacier Silver, 1.59kg, fb0001QU,Next-Gen AI Laptop</t>
+          <t>HP OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor 45 Tops (16GB LPDDR5x, 512GB SSD), 2K 14''/35.6cm, Win11, Office24, Silver, 1.29kg, he0014QU, Multi-Day Battery, AI Laptop</t>
         </is>
       </c>
       <c r="C320" t="inlineStr"/>
       <c r="D320" t="n">
-        <v>68739</v>
+        <v>79990</v>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>HP Smartchoice Omnibook 5 OLED</t>
+          <t>hp_omnibook_5_oled_(previously</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>HP Smartchoice Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x,1TB SSD) 2K OLED,16''/40.6cm, Win11, M365(1yr)*Office24, Glacier Silver, 1.59kg, fb0001QU,Next-Gen AI Laptop</t>
+          <t>HP OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor 45 Tops (16GB LPDDR5x, 512GB SSD), 2K 14''/35.6cm, Win11, Office24, Silver, 1.29kg, he0014QU, Multi-Day Battery, AI Laptop</t>
         </is>
       </c>
       <c r="C321" t="inlineStr"/>
       <c r="D321" t="n">
-        <v>68323</v>
+        <v>76990</v>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>HP Smartchoice Omnibook 5 OLED</t>
+          <t>hp_omnibook_x_flip_oled</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>HP Smartchoice Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x,1TB SSD) 2K OLED,16''/40.6cm, Win11, M365(1yr)*Office24, Glacier Silver, 1.59kg, fb0001QU,Next-Gen AI Laptop</t>
+          <t>HP OmniBook X Flip OLED Intel Core Ultra 5 226V, 40 Tops (16GB LPDDR5x,1TB SSD) 3K, Touch, 120hz, 14''/35.6cm, Intel ARC Graphic,Win11, Office24, Meteor Silver, 1.38kg, fm0099TU,Pen, 2 in 1 AI Laptop</t>
         </is>
       </c>
       <c r="C322" t="inlineStr"/>
       <c r="D322" t="n">
-        <v>67940</v>
+        <v>115990</v>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>HP Smartchoice Omnibook 5 OLED</t>
+          <t>hp_omnibook_3,_snapdragon_x</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>HP Smartchoice Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x,1TB SSD) 2K OLED,16''/40.6cm, Win11, M365(1yr)*Office24, Glacier Silver, 1.59kg, fb0001QU,Next-Gen AI Laptop</t>
+          <t>HP Omnibook 3, Snapdragon X Processor 45 TOPS (16GB LPDDR5x,512GB SSD) 2K WUXGA, Anti-Glare, 14''/35.6cm, Win 11, M365*Office 24,Silver,1.42kg, hz0026QU, Lighter mini Charger, FHD IR Camera, AI Laptop</t>
         </is>
       </c>
       <c r="C323" t="inlineStr"/>
       <c r="D323" t="n">
-        <v>67940</v>
+        <v>79990</v>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>HP Smartchoice Victus, 13th Gen</t>
+          <t>HP Omnibook 3, Snapdragon X</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>HP Smartchoice Victus, 13th Gen Intel Core i7-13620H, 8GB RTX 5050, 24GB DDR5(Upgradeable) 1TB SSD, 144Hz, FHD, 15.6''/39.6cm, Win11, M365* Office24, Mica Silver, 2.29kg, fa2309TX, RGB Gaming Laptop</t>
+          <t>HP Omnibook 3, Snapdragon X Processor, 45 TOPS (16GB LPDDR5x, 512GB SSD) 2K, WUXGA, IPS, 14''/35.6cm, Win 11, Office 24, Silver, 1.4kg, hz0026QU, FHD IR Camera, 42% Lighter mini GaN Charger, AI Laptop</t>
         </is>
       </c>
       <c r="C324" t="inlineStr"/>
       <c r="D324" t="n">
-        <v>112990</v>
+        <v>69990</v>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-27</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>HP Smartchoice Victus, AMD Ryzen</t>
+          <t>HP Omnibook 3, Snapdragon X</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>HP Smartchoice Victus, AMD Ryzen 7 7445HS, 6GB RTX 3050, 16GB DDR5(Upgradeable) 512GB SSD, FHD, 144Hz, 300 nits, 15.6''/39.6cm, Win 11, M365* Office24, Blue, 2.29kg, fb3134AX/3120ax, Gaming Laptop</t>
+          <t>HP Omnibook 3, Snapdragon X Processor, 45 TOPS (16GB LPDDR5x, 512GB SSD) 2K, WUXGA, IPS, 14''/35.6cm, Win 11, Office 24, Silver, 1.4kg, hz0026QU, FHD IR Camera, 42% Lighter mini GaN Charger, AI Laptop</t>
         </is>
       </c>
       <c r="C325" t="inlineStr"/>
       <c r="D325" t="n">
-        <v>78990</v>
+        <v>73990</v>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>HP Smartchoice Victus, AMD Ryzen</t>
+          <t>HP Omnibook 5 OLED (Previously</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>HP Smartchoice Victus, AMD Ryzen 7 7445HS, 6GB RTX 3050, 16GB DDR5(Upgradeable) 512GB SSD, FHD, 144Hz, 300 nits, 15.6''/39.6cm, Win 11, M365* Office24, Blue, 2.29kg, fb3134AX/3120ax, Gaming Laptop</t>
+          <t>HP Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x,1TB SSD) 2K OLED,16''/40.6cm, Win11, M365*Office24, Glacier Silver, 1.59kg, fb0001QU, Backlit, Next-Gen AI Laptop</t>
         </is>
       </c>
       <c r="C326" t="inlineStr"/>
       <c r="D326" t="n">
-        <v>86990</v>
+        <v>78850</v>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>HP Smartchoice Victus, AMD Ryzen</t>
+          <t>hp_omnibook_5_oled_(previously</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>HP Smartchoice Victus, AMD Ryzen 7 7445HS, 6GB RTX 3050, 16GB DDR5(Upgradeable) 512GB SSD, FHD, 144Hz, 300 nits, 15.6''/39.6cm, Win 11, M365* Office24, Blue, 2.29kg, fb3134AX/3120ax, Gaming Laptop</t>
+          <t>HP Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor 45 Tops (16GB LPDDR5x, 1TB SSD) 2K,16''/40.6cm, Win11, Office24, Silver, 1.59kg, fb0001QU, Multi-Day Battery AI Laptop</t>
         </is>
       </c>
       <c r="C327" t="inlineStr"/>
       <c r="D327" t="n">
-        <v>86990</v>
+        <v>77900</v>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>HP Victus, 14th Gen Intel</t>
+          <t>hp_pavilion_plus,_intel_core</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>HP Victus, 14th Gen Intel Core i5-14450HX, 6GB RTX 3050, 24GB DDR5, 512GB SSD, FHD, 144Hz, 300 nits, IPS,15.6''/39.6cm, Win11, M365* Office24, Mica Silver, 2.3kg, fa2303tx/fa2315tx, RGB Gaming Laptop</t>
+          <t>HP Pavilion Plus, Intel Core i5-1335U-13th Gen Laptop, (16GB LPDDR5x,512GB SSD),IPS, 300 nits, 14''(35.6cm) 2K,Win 11, M365 Basic(1yr), Office Home 24, Silver,1.38kg, 5MP Camera w/Shutter, ew0107TU</t>
         </is>
       </c>
       <c r="C328" t="inlineStr"/>
       <c r="D328" t="n">
-        <v>103990</v>
+        <v>63990</v>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>HP Victus, AMD Ryzen 7</t>
+          <t>hp_professional_15_(2026),_intel</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>HP Victus, AMD Ryzen 7 7445HS, 4GB RTX 2050, 16GB DDR5(Upgradeable) 512GB SSD, FHD, 144Hz, 300 nits, IPS, 15.6'', Win11, M365* Office24, Blue, 2.29kg, fb3189ax /3122/ 23ax Backlit, Gaming Laptop</t>
+          <t>HP Professional 15 (2026), Intel (i3 14th Gen) Core 3 100U - (8 GB/512 GB SSD/Intel UHD Graphics/Windows 11 Home) Thin &amp; Light Business Laptop/15.6" Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
         </is>
       </c>
       <c r="C329" t="inlineStr"/>
       <c r="D329" t="n">
-        <v>65990</v>
+        <v>48990</v>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>HP Victus, AMD Ryzen 7</t>
+          <t>hp_professional_15_(2026),_intel</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>HP Victus, AMD Ryzen 7 7445HS, 4GB RTX 2050, 16GB DDR5(Upgradeable) 512GB SSD, FHD, 144Hz, 300 nits, IPS, 15.6'', Win11, M365* Office24, Blue, 2.29kg, fb3189ax /3122/ 23ax Backlit, Gaming Laptop</t>
+          <t>HP Professional 15 (2026), Intel (i3 14th Gen) Core 3 100U - (8 GB/512 GB SSD/Intel UHD Graphics/Windows 11 Home) Thin &amp; Light Business Laptop/15.6" Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
         </is>
       </c>
       <c r="C330" t="inlineStr"/>
       <c r="D330" t="n">
-        <v>65990</v>
+        <v>51899</v>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>HP Victus, AMD Ryzen 7</t>
+          <t>hp_professional_15_(2026),_intel</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>HP Victus, AMD Ryzen 7 7445HS, 6GB RTX 4050, 16GB DDR5(Upgradeable) 512GB SSD, 144Hz, IPS, 300nits, FHD, 15.6''/39.6cm, Win11, M365* Office24, Blue, 2.29kg, fb3130AX, Backlit, DTS Audio, Gaming Laptop</t>
+          <t>HP Professional 15 (2026), Intel (i3 14th Gen) Core 3 100U - (8 GB/512 GB SSD/Intel UHD Graphics/Windows 11 Home) Thin &amp; Light Business Laptop/15.6" Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
         </is>
       </c>
       <c r="C331" t="inlineStr"/>
       <c r="D331" t="n">
-        <v>90990</v>
+        <v>51840</v>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>HP Victus, AMD Ryzen 7</t>
+          <t>hp_professional_15_(2026),_intel</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>HP Victus, AMD Ryzen 7 7445HS, 6GB RTX 4050, 16GB DDR5(Upgradeable) 512GB SSD, 144Hz, IPS, 300nits, FHD, 15.6''/39.6cm, Win11, M365* Office24, Blue, 2.29kg, fb3130AX, Backlit, DTS Audio, Gaming Laptop</t>
+          <t>HP Professional 15 (2026), Intel (i3 14th Gen) Core 3 100U - (8 GB/512 GB SSD/Intel UHD Graphics/Windows 11 Home) Thin &amp; Light Business Laptop/15.6" Display/Turbo Silver/Copilot Key/1.5kg/MS Office</t>
         </is>
       </c>
       <c r="C332" t="inlineStr"/>
       <c r="D332" t="n">
-        <v>91990</v>
+        <v>51840</v>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>jiobook_11_with_lifetime_office</t>
+          <t>HP Smartchoice OmniBook 5 OLED</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>JioBook 11 with Lifetime Office | Android 4G Laptop Mediatek 8788 (JioOS) | Octa-core | 4GB RAM | 64 eMMC Storage | Thin and Light Laptop (11.6 inch, 990 Grams) | Dual Band WiFi + SIM | Blue</t>
+          <t>HP Smartchoice OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x, 1TB SSD) 2K, 14''/35.6cm, Win11, M365(1yr)*Office24, Silver,1.35kg, he0015QU,Light-Weight,Next-Gen AI Laptop</t>
         </is>
       </c>
       <c r="C333" t="inlineStr"/>
       <c r="D333" t="n">
-        <v>10990</v>
+        <v>82990</v>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Lenovo Chromebook Intel Celeron N4500</t>
+          <t>HP Smartchoice OmniBook 5 OLED</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Lenovo Chromebook Intel Celeron N4500 (4GB RAM/64GB eMMC 5.1/11.6 Inch (29.46cm)/HD Display/2Wx2 Stereo Speakers/HD Camera/Chrome OS/Blue/1.21Kg), 82UY0014HA</t>
+          <t>HP Smartchoice OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x, 1TB SSD) 2K, 14''/35.6cm, Win11, M365(1yr)*Office24, Silver,1.35kg, he0015QU,Light-Weight,Next-Gen AI Laptop</t>
         </is>
       </c>
       <c r="C334" t="inlineStr"/>
       <c r="D334" t="n">
-        <v>21990</v>
+        <v>76990</v>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Lenovo Chromebook Intel Celeron N4500</t>
+          <t>HP Smartchoice OmniBook 5 OLED</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Lenovo Chromebook Intel Celeron N4500 (4GB RAM/64GB eMMC 5.1/11.6 Inch (29.46cm)/HD Display/2Wx2 Stereo Speakers/HD Camera/Chrome OS/Blue/1.21Kg), 82UY0014HA</t>
+          <t>HP Smartchoice OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x, 512GB SSD) 2K, 14''/35.6cm, Win11, M365(1yr)* Office24, Silver, 1.35kg, he0014QU, Next-Gen AI Laptop</t>
         </is>
       </c>
       <c r="C335" t="inlineStr"/>
       <c r="D335" t="n">
-        <v>18990</v>
+        <v>78990</v>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-24</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Lenovo IdeaPad Slim 3 13th</t>
+          <t>HP Smartchoice OmniBook 5 OLED</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Lenovo IdeaPad Slim 3 13th Gen Intel Core i5-13420H 15.3 inch (38.8cm) WUXGA IPS Laptop (16GB RAM/1TB SSD/Windows 11/MSO 365 Basic+Office 2024/Top Metal Cover/Backlit KB/Grey/1.6Kg), 83K100S0IN</t>
+          <t>HP Smartchoice OmniBook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x, 512GB SSD) 2K, 14''/35.6cm, Win11, M365(1yr)* Office24, Silver, 1.35kg, he0014QU, Next-Gen AI Laptop</t>
         </is>
       </c>
       <c r="C336" t="inlineStr"/>
       <c r="D336" t="n">
-        <v>70990</v>
+        <v>79990</v>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>lenovo_ideapad_slim_3_13th</t>
+          <t>HP Smartchoice Omnibook 5 OLED</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Lenovo IdeaPad Slim 3 13th Gen Intel Core i7 13620H, 16GB RAM, 512GB SSD, WUXGA IPS, 15.3"/38.8cm, Win 11, Office 2024, Top Metal Cover Grey, 1.6Kg, 83K100CJIN/S1IN, Backlit KB, Laptop</t>
+          <t>HP Smartchoice Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x,1TB SSD) 2K OLED,16''/40.6cm, Win11, M365(1yr)*Office24, Glacier Silver, 1.59kg, fb0001QU,Next-Gen AI Laptop</t>
         </is>
       </c>
       <c r="C337" t="inlineStr"/>
       <c r="D337" t="n">
-        <v>81990</v>
+        <v>68739</v>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>lenovo_ideapad_slim_3_13th</t>
+          <t>HP Smartchoice Omnibook 5 OLED</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Lenovo IdeaPad Slim 3 13th Gen Intel Core i7 13620H, 16GB RAM, 512GB SSD, WUXGA IPS, 15.3"/38.8cm, Win 11, Office 2024, Top Metal Cover Grey, 1.6Kg, 83K100CJIN/S1IN, Backlit KB, Laptop</t>
+          <t>HP Smartchoice Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x,1TB SSD) 2K OLED,16''/40.6cm, Win11, M365(1yr)*Office24, Glacier Silver, 1.59kg, fb0001QU,Next-Gen AI Laptop</t>
         </is>
       </c>
       <c r="C338" t="inlineStr"/>
       <c r="D338" t="n">
-        <v>79990</v>
+        <v>68739</v>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>lenovo_ideapad_slim_3,_13th</t>
+          <t>HP Smartchoice Omnibook 5 OLED</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Lenovo IdeaPad Slim 3, 13th Gen Intel Core i5 13420H, 24GB RAM, 1TB SSD, WUXGA IPS, 15.3"/38.8cm, Windows 11, Office Home 2024, Grey, 1.6Kg, Backlit Keyboard, 1Yr ADP Free, 83K100PLIN, Laptop</t>
+          <t>HP Smartchoice Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x,1TB SSD) 2K OLED,16''/40.6cm, Win11, M365(1yr)*Office24, Glacier Silver, 1.59kg, fb0001QU,Next-Gen AI Laptop</t>
         </is>
       </c>
       <c r="C339" t="inlineStr"/>
       <c r="D339" t="n">
-        <v>79990</v>
+        <v>68739</v>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-27</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>lenovo_ideapad_slim_3,_amd</t>
+          <t>HP Smartchoice Omnibook 5 OLED</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Lenovo IdeaPad Slim 3, AMD Ryzen 7 8840HS, 24GB RAM, 1TB SSD, WUXGA IPS, AI PC, 15.3"/38.8cm, Backlit Keyboard, Windows 11, Office Home 2024, Grey, 1.6Kg, 1Yr ADP Free, 83KA004TIN, AI Powered Laptop</t>
+          <t>HP Smartchoice Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x,1TB SSD) 2K OLED,16''/40.6cm, Win11, M365(1yr)*Office24, Glacier Silver, 1.59kg, fb0001QU,Next-Gen AI Laptop</t>
         </is>
       </c>
       <c r="C340" t="inlineStr"/>
       <c r="D340" t="n">
-        <v>87990</v>
+        <v>68323</v>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-31</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>lenovo_ideapad_slim_3,_amd</t>
+          <t>HP Smartchoice Omnibook 5 OLED</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Lenovo IdeaPad Slim 3, AMD Ryzen 7 8840HS, 24GB RAM, 1TB SSD, WUXGA IPS, AI PC, 15.3"/38.8cm, Backlit Keyboard, Windows 11, Office Home 2024, Grey, 1.6Kg, 1Yr ADP Free, 83KA004TIN, AI Powered Laptop</t>
+          <t>HP Smartchoice Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x,1TB SSD) 2K OLED,16''/40.6cm, Win11, M365(1yr)*Office24, Glacier Silver, 1.59kg, fb0001QU,Next-Gen AI Laptop</t>
         </is>
       </c>
       <c r="C341" t="inlineStr"/>
       <c r="D341" t="n">
-        <v>79990</v>
+        <v>67940</v>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>lenovo_ideapad_slim_3,_amd</t>
+          <t>HP Smartchoice Omnibook 5 OLED</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Lenovo IdeaPad Slim 3, AMD Ryzen 7 8840HS, 24GB RAM, 1TB SSD, WUXGA IPS, AI PC, 15.3"/38.8cm, Backlit Keyboard, Windows 11, Office Home 2024, Grey, 1.6Kg, 1Yr ADP Free, 83KA004TIN, AI Powered Laptop</t>
+          <t>HP Smartchoice Omnibook 5 OLED (Previously Pavilion), Snapdragon X Processor (16GB LPDDR5x,1TB SSD) 2K OLED,16''/40.6cm, Win11, M365(1yr)*Office24, Glacier Silver, 1.59kg, fb0001QU,Next-Gen AI Laptop</t>
         </is>
       </c>
       <c r="C342" t="inlineStr"/>
       <c r="D342" t="n">
-        <v>79990</v>
+        <v>67940</v>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-06-02</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>lenovo_ideapad_slim_3,_amd</t>
+          <t>HP Smartchoice Victus, 13th Gen</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Lenovo IdeaPad Slim 3, AMD Ryzen 7 8840HS, 24GB RAM, 1TB SSD, WUXGA IPS, AI PC, 15.3"/38.8cm, Backlit Keyboard, Windows 11, Office Home 2024, Grey, 1.6Kg, 1Yr ADP Free, 83KA004TIN, AI Powered Laptop</t>
+          <t>HP Smartchoice Victus, 13th Gen Intel Core i7-13620H, 8GB RTX 5050, 24GB DDR5(Upgradeable) 1TB SSD, 144Hz, FHD, 15.6''/39.6cm, Win11, M365* Office24, Mica Silver, 2.29kg, fa2309TX, RGB Gaming Laptop</t>
         </is>
       </c>
       <c r="C343" t="inlineStr"/>
       <c r="D343" t="n">
-        <v>84990</v>
+        <v>112990</v>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-05-10</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>lenovo_ideapad_slim_5,_amd</t>
+          <t>HP Smartchoice Victus, AMD Ryzen</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Lenovo IdeaPad Slim 5, AMD Ryzen 5 7535HS, 16GB RAM, 512GB SSD, WUXGA IPS, 13.3"/33.7cm, Windows 11, Microsoft 365 Basic + Office 2024, Grey, 1.6Kg, Backlit KB, 1Yr ADP Free, 83J2004HIN, Laptop</t>
+          <t>HP Smartchoice Victus, AMD Ryzen 7 7445HS, 6GB RTX 3050, 16GB DDR5(Upgradeable) 512GB SSD, FHD, 144Hz, 300 nits, 15.6''/39.6cm, Win 11, M365* Office24, Blue, 2.29kg, fb3134AX/3120ax, Gaming Laptop</t>
         </is>
       </c>
       <c r="C344" t="inlineStr"/>
       <c r="D344" t="n">
-        <v>72990</v>
+        <v>78990</v>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Lenovo Ideapad Slim 3 AMD</t>
+          <t>HP Smartchoice Victus, AMD Ryzen</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Lenovo Ideapad Slim 3 AMD Ryzen 5 7520U 15.6" (39.6cm) FHD Thin and Light Laptop (16GB/512GB SSD/Windows 11/Microsoft 365 Basic + Office Home 2024/Backlit Keyboard/Grey/1.6Kg), 82XQ00XDIN</t>
+          <t>HP Smartchoice Victus, AMD Ryzen 7 7445HS, 6GB RTX 3050, 16GB DDR5(Upgradeable) 512GB SSD, FHD, 144Hz, 300 nits, 15.6''/39.6cm, Win 11, M365* Office24, Blue, 2.29kg, fb3134AX/3120ax, Gaming Laptop</t>
         </is>
       </c>
       <c r="C345" t="inlineStr"/>
       <c r="D345" t="n">
-        <v>50750</v>
+        <v>86990</v>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Lenovo LOQ 2024, Intel Core</t>
+          <t>HP Smartchoice Victus, AMD Ryzen</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Lenovo LOQ 2024, Intel Core i5-13450HX, 13th Gen, NVIDIA RTX 4050-6GB, 16GB RAM, 512GB SSD, FHD 144Hz, 15.6"/39.6cm, Windows 11, Office Home 2024, Grey, 2.4Kg, 83DV018JIN, 1Yr ADP Free Gaming Laptop</t>
+          <t>HP Smartchoice Victus, AMD Ryzen 7 7445HS, 6GB RTX 3050, 16GB DDR5(Upgradeable) 512GB SSD, FHD, 144Hz, 300 nits, 15.6''/39.6cm, Win 11, M365* Office24, Blue, 2.29kg, fb3134AX/3120ax, Gaming Laptop</t>
         </is>
       </c>
       <c r="C346" t="inlineStr"/>
       <c r="D346" t="n">
-        <v>100544</v>
+        <v>86990</v>
       </c>
       <c r="E346" t="inlineStr">
         <is>
@@ -7691,2077 +7691,2518 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Lenovo LOQ 2025 AMD Ryzen</t>
+          <t>HP Victus, 14th Gen Intel</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Lenovo LOQ 2025 AMD Ryzen 7 250| NVIDIA RTX 5050 8GB (16GB RAM/1TB SSD/144Hz Refresh Rate/440 AI TOPS/15.6" (39.6cm)/Windows 11/Office 2024/3 Mon. Game Pass/Grey/2.4Kg), 83JG008KIN</t>
+          <t>HP Victus, 14th Gen Intel Core i5-14450HX, 6GB RTX 3050, 24GB DDR5, 512GB SSD, FHD, 144Hz, 300 nits, IPS,15.6''/39.6cm, Win11, M365* Office24, Mica Silver, 2.3kg, fa2303tx/fa2315tx, RGB Gaming Laptop</t>
         </is>
       </c>
       <c r="C347" t="inlineStr"/>
       <c r="D347" t="n">
-        <v>134990</v>
+        <v>103990</v>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-10</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Lenovo LOQ 2025 Intel Core</t>
+          <t>HP Victus, AMD Ryzen 7</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Lenovo LOQ 2025 Intel Core i7-14700HX| NVIDIA RTX 5060 8GB (32GB RAM/1TB SSD/144Hz Refresh Rate/572 AI TOPS/15.6" (39.6cm)/Windows 11/Office 2024/3 Mon. Game Pass/Grey/2.4Kg), 83JE00T3IN</t>
+          <t>HP Victus, AMD Ryzen 7 7445HS, 4GB RTX 2050, 16GB DDR5(Upgradeable) 512GB SSD, FHD, 144Hz, 300 nits, IPS, 15.6'', Win11, M365* Office24, Blue, 2.29kg, fb3189ax /3122/ 23ax Backlit, Gaming Laptop</t>
         </is>
       </c>
       <c r="C348" t="inlineStr"/>
       <c r="D348" t="n">
-        <v>157990</v>
+        <v>65990</v>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-21</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Lenovo LOQ AMD Ryzen 5</t>
+          <t>HP Victus, AMD Ryzen 7</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Lenovo LOQ AMD Ryzen 5 7235HS | NVIDIA RTX 4050 6GB (16GB RAM/512GB SSD/144Hz Refresh Rate/15.6" (39.6cm)/Windows 11/Office Home 2024/3 Mon. Game Pass/Grey/2.4Kg), 83JC00NYIN AI Gaming Laptop</t>
+          <t>HP Victus, AMD Ryzen 7 7445HS, 4GB RTX 2050, 16GB DDR5(Upgradeable) 512GB SSD, FHD, 144Hz, 300 nits, IPS, 15.6'', Win11, M365* Office24, Blue, 2.29kg, fb3189ax /3122/ 23ax Backlit, Gaming Laptop</t>
         </is>
       </c>
       <c r="C349" t="inlineStr"/>
       <c r="D349" t="n">
-        <v>88990</v>
+        <v>65990</v>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-22</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Lenovo LOQ, 13th Gen Intel</t>
+          <t>HP Victus, AMD Ryzen 7</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Lenovo LOQ, 13th Gen Intel Core i7 13700HX, RTX 5050-8GB, 16GB RAM, 1TB SSD, FHD, 15.6"/39.6cm, 144Hz, Windows 11, Office 2024, Grey, 2.4Kg, 440 AI Tops, 3 Mon. Game Pass, 83JE00U7IN, AI Gaming Laptop</t>
+          <t>HP Victus, AMD Ryzen 7 7445HS, 6GB RTX 4050, 16GB DDR5(Upgradeable) 512GB SSD, 144Hz, IPS, 300nits, FHD, 15.6''/39.6cm, Win11, M365* Office24, Blue, 2.29kg, fb3130AX, Backlit, DTS Audio, Gaming Laptop</t>
         </is>
       </c>
       <c r="C350" t="inlineStr"/>
       <c r="D350" t="n">
-        <v>121869</v>
+        <v>90990</v>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Lenovo Legion 7 2025 Intel</t>
+          <t>HP Victus, AMD Ryzen 7</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Lenovo Legion 7 2025 Intel Core Ultra 9 275HX| NVIDIA RTX 5070 8GB (32GB RAM/1TB SSD/WQXGA OLED/240Hz/16(40.64cm)/Windows 11/Office 2024+AI Now/White/2.0Kg), 83KY001GIN AI Powered Gaming Laptop</t>
+          <t>HP Victus, AMD Ryzen 7 7445HS, 6GB RTX 4050, 16GB DDR5(Upgradeable) 512GB SSD, 144Hz, IPS, 300nits, FHD, 15.6''/39.6cm, Win11, M365* Office24, Blue, 2.29kg, fb3130AX, Backlit, DTS Audio, Gaming Laptop</t>
         </is>
       </c>
       <c r="C351" t="inlineStr"/>
       <c r="D351" t="n">
-        <v>239391</v>
+        <v>91990</v>
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Lenovo Legion Pro 5 2025</t>
+          <t>jiobook_11_with_lifetime_office</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Lenovo Legion Pro 5 2025 AMD Ryzen 9 9955HX | NVIDIA RTX 5060 8GB (32GB RAM/1TB SSD/WQXGA OLED/165Hz/16 (40.6cm)/Windows 11/Office 2024+AI Now/Black/2.3Kg), 83F2004CIN AI Powered Gaming Laptop</t>
+          <t>JioBook 11 with Lifetime Office | Android 4G Laptop Mediatek 8788 (JioOS) | Octa-core | 4GB RAM | 64 eMMC Storage | Thin and Light Laptop (11.6 inch, 990 Grams) | Dual Band WiFi + SIM | Blue</t>
         </is>
       </c>
       <c r="C352" t="inlineStr"/>
       <c r="D352" t="n">
-        <v>245490</v>
+        <v>10990</v>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-08-05</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Lenovo Legion Pro 5 2025</t>
+          <t>Lenovo Chromebook Intel Celeron N4500</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Lenovo Legion Pro 5 2025 AMD Ryzen 9 9955HX | NVIDIA RTX 5060 8GB (32GB RAM/1TB SSD/WQXGA OLED/165Hz/16 (40.6cm)/Windows 11/Office 2024+AI Now/Black/2.3Kg), 83F2004CIN AI Powered Gaming Laptop</t>
+          <t>Lenovo Chromebook Intel Celeron N4500 (4GB RAM/64GB eMMC 5.1/11.6 Inch (29.46cm)/HD Display/2Wx2 Stereo Speakers/HD Camera/Chrome OS/Blue/1.21Kg), 82UY0014HA</t>
         </is>
       </c>
       <c r="C353" t="inlineStr"/>
       <c r="D353" t="n">
-        <v>245490</v>
+        <v>21990</v>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Lenovo Legion Pro 5 2025</t>
+          <t>Lenovo Chromebook Intel Celeron N4500</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Lenovo Legion Pro 5 2025 AMD Ryzen 9 9955HX | NVIDIA RTX 5060 8GB (32GB RAM/1TB SSD/WQXGA OLED/165Hz/16 (40.6cm)/Windows 11/Office 2024+AI Now/Black/2.3Kg), 83F2004CIN AI Powered Gaming Laptop</t>
+          <t>Lenovo Chromebook Intel Celeron N4500 (4GB RAM/64GB eMMC 5.1/11.6 Inch (29.46cm)/HD Display/2Wx2 Stereo Speakers/HD Camera/Chrome OS/Blue/1.21Kg), 82UY0014HA</t>
         </is>
       </c>
       <c r="C354" t="inlineStr"/>
       <c r="D354" t="n">
-        <v>245490</v>
+        <v>18990</v>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Lenovo Legion Pro 5 2025</t>
+          <t>Lenovo IdeaPad Slim 3 13th</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Lenovo Legion Pro 5 2025 AMD Ryzen 9 9955HX | NVIDIA RTX 5060 8GB (32GB RAM/1TB SSD/WQXGA OLED/165Hz/16 (40.6cm)/Windows 11/Office 2024+AI Now/Black/2.3Kg), 83F2004CIN AI Powered Gaming Laptop</t>
+          <t>Lenovo IdeaPad Slim 3 13th Gen Intel Core i5-13420H 15.3 inch (38.8cm) WUXGA IPS Laptop (16GB RAM/1TB SSD/Windows 11/MSO 365 Basic+Office 2024/Top Metal Cover/Backlit KB/Grey/1.6Kg), 83K100S0IN</t>
         </is>
       </c>
       <c r="C355" t="inlineStr"/>
       <c r="D355" t="n">
-        <v>245490</v>
+        <v>70990</v>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-08</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Lenovo Legion Pro 7 FIFA</t>
+          <t>lenovo_ideapad_slim_3_13th</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Lenovo Legion Pro 7 FIFA World Cup 26 Edition Intel Core Ultra 9 275HX | NVIDIA RTX 5070Ti 12GB (32GB RAM/1TB SSD/WQXGA OLED/240Hz/16(40.6cm)/Windows 11/Black/2.4Kg), 83F500HPIN AI Gaming Laptop</t>
+          <t>Lenovo IdeaPad Slim 3 13th Gen Intel Core i7 13620H, 16GB RAM, 512GB SSD, WUXGA IPS, 15.3"/38.8cm, Win 11, Office 2024, Top Metal Cover Grey, 1.6Kg, 83K100CJIN/S1IN, Backlit KB, Laptop</t>
         </is>
       </c>
       <c r="C356" t="inlineStr"/>
       <c r="D356" t="n">
-        <v>319990</v>
+        <v>81990</v>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Lenovo Smartchoice Ideapad 5 2-in-1</t>
+          <t>lenovo_ideapad_slim_3_13th</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Lenovo Smartchoice Ideapad 5 2-in-1 13th Gen Intel Core i5-13420H (16GB RAM/512GB SSD/Windows 11/Office Home 2024/WUXGA IPS/14 (35.5cm)/Touchscreen 2-in-1/3Mon.Game Pass/Grey/1.6kg), 83KX0059IN Laptop</t>
+          <t>Lenovo IdeaPad Slim 3 13th Gen Intel Core i7 13620H, 16GB RAM, 512GB SSD, WUXGA IPS, 15.3"/38.8cm, Win 11, Office 2024, Top Metal Cover Grey, 1.6Kg, 83K100CJIN/S1IN, Backlit KB, Laptop</t>
         </is>
       </c>
       <c r="C357" t="inlineStr"/>
       <c r="D357" t="n">
-        <v>74490</v>
+        <v>79990</v>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>lenovo_thinkbook_14,_amd_ryzen</t>
+          <t>lenovo_ideapad_slim_3_ryzen</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Lenovo ThinkBook 14, AMD Ryzen 5 220, 16GB RAM, 1TB SSD, WUXGA IPS 14” (35.56cm), Windows 11 Home, Arctic Grey, 1.36Kg, 21V0A01SIG, Fingerprint, Backlit, 400 Nits, 1Y Warranty, Laptop</t>
+          <t>Lenovo IdeaPad Slim 3 Ryzen 5 7520U 15.6" (39.6cm) FHD Thin and Light Laptop (16GB RAM/512GB SSD/Backlit Keyboard/Windows 11/ Office 2024/Grey/1.6Kg), 82XQ01RYIN</t>
         </is>
       </c>
       <c r="C358" t="inlineStr"/>
       <c r="D358" t="n">
-        <v>90990</v>
+        <v>62990</v>
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>lenovo_thinkbook_14,_amd_ryzen</t>
+          <t>lenovo_ideapad_slim_3,_13th</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Lenovo ThinkBook 14, AMD Ryzen 5 220, 16GB RAM, 1TB SSD, WUXGA IPS 14” (35.56cm), Windows 11 Home, Arctic Grey, 1.36Kg, 21V0A01SIG, Fingerprint, Backlit, 400 Nits, 1Y Warranty, Laptop</t>
+          <t>Lenovo IdeaPad Slim 3, 13th Gen Intel Core i5 13420H, 24GB RAM, 1TB SSD, WUXGA IPS, 15.3"/38.8cm, Windows 11, Office Home 2024, Grey, 1.6Kg, Backlit Keyboard, 1Yr ADP Free, 83K100PLIN, Laptop</t>
         </is>
       </c>
       <c r="C359" t="inlineStr"/>
       <c r="D359" t="n">
-        <v>92990</v>
+        <v>79990</v>
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>lenovo_thinkbook_14,_amd_ryzen</t>
+          <t>lenovo_ideapad_slim_3,_amd</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Lenovo ThinkBook 14, AMD Ryzen 5 220, 16GB RAM, 1TB SSD, WUXGA IPS 14” (35.56cm), Windows 11 Home, Arctic Grey, 1.36Kg, 21V0A01SIG, Fingerprint, Backlit, 400 Nits, 1Y Warranty, Laptop</t>
+          <t>Lenovo IdeaPad Slim 3, AMD Ryzen 7 8840HS, 24GB RAM, 1TB SSD, WUXGA IPS, AI PC, 15.3"/38.8cm, Backlit Keyboard, Windows 11, Office Home 2024, Grey, 1.6Kg, 1Yr ADP Free, 83KA004TIN, AI Powered Laptop</t>
         </is>
       </c>
       <c r="C360" t="inlineStr"/>
       <c r="D360" t="n">
-        <v>92990</v>
+        <v>87990</v>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Lenovo ThinkBook 15 G5 AMD</t>
+          <t>lenovo_ideapad_slim_3,_amd</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Lenovo ThinkBook 15 G5 AMD Ryzen 7 7730U 15.6" FHD Antiglare 250 Nits Thin and Light Laptop (8GB RAM/512GB SSD/Windows 11 Home/Fingerprint Reader/Backlit/Mineral Grey/1 Year Onsite/1.7 kg), 21JFA00BIN</t>
+          <t>Lenovo IdeaPad Slim 3, AMD Ryzen 7 8840HS, 24GB RAM, 1TB SSD, WUXGA IPS, AI PC, 15.3"/38.8cm, Backlit Keyboard, Windows 11, Office Home 2024, Grey, 1.6Kg, 1Yr ADP Free, 83KA004TIN, AI Powered Laptop</t>
         </is>
       </c>
       <c r="C361" t="inlineStr"/>
       <c r="D361" t="n">
-        <v>59999</v>
+        <v>79990</v>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>lenovo_thinkbook_16_amd_ryzen</t>
+          <t>lenovo_ideapad_slim_3,_amd</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Lenovo ThinkBook 16 AMD Ryzen 5 7535HS (8GB RAM/512GB SSD/Win 11 Home/Office 2024/Backlit Keyboard/Fingerprint) 16" WUXGA IPS 300 Nits Thin &amp; Light Laptop/1Y Warranty/Aluminium Top/1.7kg, 21MWA0BRIN</t>
+          <t>Lenovo IdeaPad Slim 3, AMD Ryzen 7 8840HS, 24GB RAM, 1TB SSD, WUXGA IPS, AI PC, 15.3"/38.8cm, Backlit Keyboard, Windows 11, Office Home 2024, Grey, 1.6Kg, 1Yr ADP Free, 83KA004TIN, AI Powered Laptop</t>
         </is>
       </c>
       <c r="C362" t="inlineStr"/>
       <c r="D362" t="n">
-        <v>65063</v>
+        <v>79990</v>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>lenovo_thinkbook_16_amd_ryzen</t>
+          <t>lenovo_ideapad_slim_3,_amd</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Lenovo ThinkBook 16 AMD Ryzen 5 7535HS (8GB RAM/512GB SSD/Win 11 Home/Office 2024/Backlit Keyboard/Fingerprint) 16" WUXGA IPS 300 Nits Thin &amp; Light Laptop/1Y Warranty/Aluminium Top/1.7kg, 21MWA0BRIN</t>
+          <t>Lenovo IdeaPad Slim 3, AMD Ryzen 7 8840HS, 24GB RAM, 1TB SSD, WUXGA IPS, AI PC, 15.3"/38.8cm, Backlit Keyboard, Windows 11, Office Home 2024, Grey, 1.6Kg, 1Yr ADP Free, 83KA004TIN, AI Powered Laptop</t>
         </is>
       </c>
       <c r="C363" t="inlineStr"/>
       <c r="D363" t="n">
-        <v>65063</v>
+        <v>84990</v>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>lenovo_thinkbook_16,_amd_ryzen</t>
+          <t>lenovo_ideapad_slim_5,_amd</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Lenovo ThinkBook 16, AMD Ryzen 5 7535HS, 16GB RAM, 512GB SSD, WUXGA IPS 16", Windows 11 Home, Office 2024, 1.7kg, 21MWA0BSIN, Backlit Keyboard, Fingerprint, 300 Nits, 1Y Warranty, Aluminium Top Laptop</t>
+          <t>Lenovo IdeaPad Slim 5, AMD Ryzen 5 7535HS, 16GB RAM, 512GB SSD, WUXGA IPS, 13.3"/33.7cm, Windows 11, Microsoft 365 Basic + Office 2024, Grey, 1.6Kg, Backlit KB, 1Yr ADP Free, 83J2004HIN, Laptop</t>
         </is>
       </c>
       <c r="C364" t="inlineStr"/>
       <c r="D364" t="n">
-        <v>84500</v>
+        <v>72990</v>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Lenovo ThinkBook 16, Intel Core</t>
+          <t>Lenovo Ideapad Slim 3 AMD</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Lenovo ThinkBook 16, Intel Core Ultra 9 185H, 16GB RAM, 512GB SSD, WUXGA IPS 16” (40.64cm), Win 11 Home, Arctic Grey, 1.7Kg, 21SKA0J5IG, Fingerprint, Backlit, 300 Nits, 1Y Warranty, AI Powered Laptop</t>
+          <t>Lenovo Ideapad Slim 3 AMD Ryzen 5 7520U 15.6" (39.6cm) FHD Thin and Light Laptop (16GB/512GB SSD/Windows 11/Microsoft 365 Basic + Office Home 2024/Backlit Keyboard/Grey/1.6Kg), 82XQ00XDIN</t>
         </is>
       </c>
       <c r="C365" t="inlineStr"/>
       <c r="D365" t="n">
-        <v>94990</v>
+        <v>50750</v>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-14</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Lenovo V14 Intel Core i3</t>
+          <t>Lenovo LOQ 2024, Intel Core</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Lenovo V14 Intel Core i3 13th Gen 14" FHD (1920x1080) Antiglare 250 Nits Thin and Light Laptop (16GB RAM/512GB SSD/Windows 11 Home/Office Home 2024/Iron Grey/1.43 kg), 83A0A0PCIN</t>
+          <t>Lenovo LOQ 2024, Intel Core i5-13450HX, 13th Gen, NVIDIA RTX 4050-6GB, 16GB RAM, 512GB SSD, FHD 144Hz, 15.6"/39.6cm, Windows 11, Office Home 2024, Grey, 2.4Kg, 83DV018JIN, 1Yr ADP Free Gaming Laptop</t>
         </is>
       </c>
       <c r="C366" t="inlineStr"/>
       <c r="D366" t="n">
-        <v>70990</v>
+        <v>100544</v>
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>Lenovo V14 Intel Core i3</t>
+          <t>Lenovo LOQ 2025 AMD Ryzen</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Lenovo V14 Intel Core i3 13th Gen 14" FHD (1920x1080) Antiglare 250 Nits Thin and Light Laptop (16GB RAM/512GB SSD/Windows 11 Home/Office Home 2024/Iron Grey/1.43 kg), 83A0A0PCIN</t>
+          <t>Lenovo LOQ 2025 AMD Ryzen 7 250| NVIDIA RTX 5050 8GB (16GB RAM/1TB SSD/144Hz Refresh Rate/440 AI TOPS/15.6" (39.6cm)/Windows 11/Office 2024/3 Mon. Game Pass/Grey/2.4Kg), 83JG008KIN</t>
         </is>
       </c>
       <c r="C367" t="inlineStr"/>
       <c r="D367" t="n">
-        <v>70990</v>
+        <v>134990</v>
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>lenovo_v14_intel_core_i3</t>
+          <t>Lenovo LOQ 2025 Intel Core</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Lenovo V14 Intel Core i3 13th Gen 14" FHD (1920x1080) Antiglare 250 Nits Thin and Light Laptop (16GB RAM/512GB SSD/Windows 11 Home/Office Home 2024/Iron Grey/1.43 kg), 83A0A0PCIN</t>
+          <t>Lenovo LOQ 2025 Intel Core i7-14700HX| NVIDIA RTX 5060 8GB (32GB RAM/1TB SSD/144Hz Refresh Rate/572 AI TOPS/15.6" (39.6cm)/Windows 11/Office 2024/3 Mon. Game Pass/Grey/2.4Kg), 83JE00T3IN</t>
         </is>
       </c>
       <c r="C368" t="inlineStr"/>
       <c r="D368" t="n">
-        <v>70990</v>
+        <v>157990</v>
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>lenovo_v15_amd_ryzen_7</t>
+          <t>Lenovo LOQ AMD Ryzen 5</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Lenovo V15 AMD Ryzen 7 7730U 15.6" (39.62cm) FHD 250 Nits Antiglare Thin and Light Laptop (16GB/512GB SSD/Windows 11/Iron Grey/1.65 Kg) Grey</t>
+          <t>Lenovo LOQ AMD Ryzen 5 7235HS | NVIDIA RTX 4050 6GB (16GB RAM/512GB SSD/144Hz Refresh Rate/15.6" (39.6cm)/Windows 11/Office Home 2024/3 Mon. Game Pass/Grey/2.4Kg), 83JC00NYIN AI Gaming Laptop</t>
         </is>
       </c>
       <c r="C369" t="inlineStr"/>
       <c r="D369" t="n">
-        <v>64999</v>
+        <v>88990</v>
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-05-19</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 (2024), AMD</t>
+          <t>Lenovo LOQ, 13th Gen Intel</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 (2024), AMD Ryzen 3 7320U Quad Core - (8GB/512GB SSD/AMD Radeon Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" FHD Display/Arctic Grey/1.57 kg/MS Office 2021</t>
+          <t>Lenovo LOQ, 13th Gen Intel Core i7 13700HX, RTX 5050-8GB, 16GB RAM, 1TB SSD, FHD, 15.6"/39.6cm, 144Hz, Windows 11, Office 2024, Grey, 2.4Kg, 440 AI Tops, 3 Mon. Game Pass, 83JE00U7IN, AI Gaming Laptop</t>
         </is>
       </c>
       <c r="C370" t="inlineStr"/>
       <c r="D370" t="n">
-        <v>44200</v>
+        <v>121869</v>
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 (2024), AMD</t>
+          <t>Lenovo Legion 7 2025 Intel</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 (2024), AMD Ryzen 3 7320U Quad Core - (8GB/512GB SSD/AMD Radeon Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" FHD Display/Arctic Grey/1.57 kg/MS Office 2021</t>
+          <t>Lenovo Legion 7 2025 Intel Core Ultra 9 275HX| NVIDIA RTX 5070 8GB (32GB RAM/1TB SSD/WQXGA OLED/240Hz/16(40.64cm)/Windows 11/Office 2024+AI Now/White/2.0Kg), 83KY001GIN AI Powered Gaming Laptop</t>
         </is>
       </c>
       <c r="C371" t="inlineStr"/>
       <c r="D371" t="n">
-        <v>44490</v>
+        <v>239391</v>
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-08</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 (2024), AMD</t>
+          <t>Lenovo Legion Pro 5 2025</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 (2024), AMD Ryzen 3 7320U Quad Core - (8GB/512GB SSD/AMD Radeon Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" FHD Display/Arctic Grey/1.57 kg/MS Office 2021</t>
+          <t>Lenovo Legion Pro 5 2025 AMD Ryzen 9 9955HX | NVIDIA RTX 5060 8GB (32GB RAM/1TB SSD/WQXGA OLED/165Hz/16 (40.6cm)/Windows 11/Office 2024+AI Now/Black/2.3Kg), 83F2004CIN AI Powered Gaming Laptop</t>
         </is>
       </c>
       <c r="C372" t="inlineStr"/>
       <c r="D372" t="n">
-        <v>44490</v>
+        <v>245490</v>
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-22</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 (2024), AMD</t>
+          <t>Lenovo Legion Pro 5 2025</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 (2024), AMD Ryzen 3 7320U Quad Core - (8GB/512GB SSD/AMD Radeon Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" FHD Display/Arctic Grey/1.57 kg/MS Office 2021</t>
+          <t>Lenovo Legion Pro 5 2025 AMD Ryzen 9 9955HX | NVIDIA RTX 5060 8GB (32GB RAM/1TB SSD/WQXGA OLED/165Hz/16 (40.6cm)/Windows 11/Office 2024+AI Now/Black/2.3Kg), 83F2004CIN AI Powered Gaming Laptop</t>
         </is>
       </c>
       <c r="C373" t="inlineStr"/>
       <c r="D373" t="n">
-        <v>44500</v>
+        <v>245490</v>
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-24</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 (2024), AMD</t>
+          <t>Lenovo Legion Pro 5 2025</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 (2024), AMD Ryzen 3 7320U Quad Core - (8GB/512GB SSD/AMD Radeon Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" FHD Display/Arctic Grey/1.57 kg/MS Office 2021</t>
+          <t>Lenovo Legion Pro 5 2025 AMD Ryzen 9 9955HX | NVIDIA RTX 5060 8GB (32GB RAM/1TB SSD/WQXGA OLED/165Hz/16 (40.6cm)/Windows 11/Office 2024+AI Now/Black/2.3Kg), 83F2004CIN AI Powered Gaming Laptop</t>
         </is>
       </c>
       <c r="C374" t="inlineStr"/>
       <c r="D374" t="n">
-        <v>49999</v>
+        <v>245490</v>
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 (2024), AMD</t>
+          <t>Lenovo Legion Pro 5 2025</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 (2024), AMD Ryzen 3 7320U Quad Core - (8GB/512GB SSD/AMD Radeon Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" FHD Display/Arctic Grey/1.57 kg/MS Office 2021</t>
+          <t>Lenovo Legion Pro 5 2025 AMD Ryzen 9 9955HX | NVIDIA RTX 5060 8GB (32GB RAM/1TB SSD/WQXGA OLED/165Hz/16 (40.6cm)/Windows 11/Office 2024+AI Now/Black/2.3Kg), 83F2004CIN AI Powered Gaming Laptop</t>
         </is>
       </c>
       <c r="C375" t="inlineStr"/>
       <c r="D375" t="n">
-        <v>49890</v>
+        <v>245490</v>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon</t>
+          <t>Lenovo Legion Pro 7 FIFA</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo Legion Pro 7 FIFA World Cup 26 Edition Intel Core Ultra 9 275HX | NVIDIA RTX 5070Ti 12GB (32GB RAM/1TB SSD/WQXGA OLED/240Hz/16(40.6cm)/Windows 11/Black/2.4Kg), 83F500HPIN AI Gaming Laptop</t>
         </is>
       </c>
       <c r="C376" t="inlineStr"/>
       <c r="D376" t="n">
-        <v>41999</v>
+        <v>319990</v>
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-15</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon</t>
+          <t>Lenovo Smartchoice Ideapad 5 2-in-1</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo Smartchoice Ideapad 5 2-in-1 13th Gen Intel Core i5-13420H (16GB RAM/512GB SSD/Windows 11/Office Home 2024/WUXGA IPS/14 (35.5cm)/Touchscreen 2-in-1/3Mon.Game Pass/Grey/1.6kg), 83KX0059IN Laptop</t>
         </is>
       </c>
       <c r="C377" t="inlineStr"/>
       <c r="D377" t="n">
-        <v>41999</v>
+        <v>74490</v>
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon</t>
+          <t>lenovo_thinkbook_14,_amd_ryzen</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo ThinkBook 14, AMD Ryzen 5 220, 16GB RAM, 1TB SSD, WUXGA IPS 14” (35.56cm), Windows 11 Home, Arctic Grey, 1.36Kg, 21V0A01SIG, Fingerprint, Backlit, 400 Nits, 1Y Warranty, Laptop</t>
         </is>
       </c>
       <c r="C378" t="inlineStr"/>
       <c r="D378" t="n">
-        <v>41999</v>
+        <v>90990</v>
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon</t>
+          <t>lenovo_thinkbook_14,_amd_ryzen</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo ThinkBook 14, AMD Ryzen 5 220, 16GB RAM, 1TB SSD, WUXGA IPS 14” (35.56cm), Windows 11 Home, Arctic Grey, 1.36Kg, 21V0A01SIG, Fingerprint, Backlit, 400 Nits, 1Y Warranty, Laptop</t>
         </is>
       </c>
       <c r="C379" t="inlineStr"/>
       <c r="D379" t="n">
-        <v>42999</v>
+        <v>92990</v>
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon</t>
+          <t>lenovo_thinkbook_14,_amd_ryzen</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo ThinkBook 14, AMD Ryzen 5 220, 16GB RAM, 1TB SSD, WUXGA IPS 14” (35.56cm), Windows 11 Home, Arctic Grey, 1.36Kg, 21V0A01SIG, Fingerprint, Backlit, 400 Nits, 1Y Warranty, Laptop</t>
         </is>
       </c>
       <c r="C380" t="inlineStr"/>
       <c r="D380" t="n">
-        <v>42999</v>
+        <v>92990</v>
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon</t>
+          <t>Lenovo ThinkBook 15 G5 AMD</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo ThinkBook 15 G5 AMD Ryzen 7 7730U 15.6" FHD Antiglare 250 Nits Thin and Light Laptop (8GB RAM/512GB SSD/Windows 11 Home/Fingerprint Reader/Backlit/Mineral Grey/1 Year Onsite/1.7 kg), 21JFA00BIN</t>
         </is>
       </c>
       <c r="C381" t="inlineStr"/>
       <c r="D381" t="n">
-        <v>42999</v>
+        <v>59999</v>
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-22</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon</t>
+          <t>lenovo_thinkbook_16_amd_ryzen</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo ThinkBook 16 AMD Ryzen 5 7535HS (8GB RAM/512GB SSD/Win 11 Home/Office 2024/Backlit Keyboard/Fingerprint) 16" WUXGA IPS 300 Nits Thin &amp; Light Laptop/1Y Warranty/Aluminium Top/1.7kg, 21MWA0BRIN</t>
         </is>
       </c>
       <c r="C382" t="inlineStr"/>
       <c r="D382" t="n">
-        <v>42999</v>
+        <v>65063</v>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon</t>
+          <t>lenovo_thinkbook_16_amd_ryzen</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo ThinkBook 16 AMD Ryzen 5 7535HS (8GB RAM/512GB SSD/Win 11 Home/Office 2024/Backlit Keyboard/Fingerprint) 16" WUXGA IPS 300 Nits Thin &amp; Light Laptop/1Y Warranty/Aluminium Top/1.7kg, 21MWA0BRIN</t>
         </is>
       </c>
       <c r="C383" t="inlineStr"/>
       <c r="D383" t="n">
-        <v>42999</v>
+        <v>65063</v>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon</t>
+          <t>lenovo_thinkbook_16,_amd_ryzen</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo ThinkBook 16, AMD Ryzen 5 7535HS, 16GB RAM, 512GB SSD, WUXGA IPS 16", Windows 11 Home, Office 2024, 1.7kg, 21MWA0BSIN, Backlit Keyboard, Fingerprint, 300 Nits, 1Y Warranty, Aluminium Top Laptop</t>
         </is>
       </c>
       <c r="C384" t="inlineStr"/>
       <c r="D384" t="n">
-        <v>44999</v>
+        <v>84500</v>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon</t>
+          <t>Lenovo ThinkBook 16, Intel Core</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo ThinkBook 16, Intel Core Ultra 9 185H, 16GB RAM, 512GB SSD, WUXGA IPS 16” (40.64cm), Win 11 Home, Arctic Grey, 1.7Kg, 21SKA0J5IG, Fingerprint, Backlit, 300 Nits, 1Y Warranty, AI Powered Laptop</t>
         </is>
       </c>
       <c r="C385" t="inlineStr"/>
       <c r="D385" t="n">
-        <v>43999</v>
+        <v>94990</v>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-20</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon</t>
+          <t>Lenovo V14 Intel Core i3</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo V14 Intel Core i3 13th Gen 14" FHD (1920x1080) Antiglare 250 Nits Thin and Light Laptop (16GB RAM/512GB SSD/Windows 11 Home/Office Home 2024/Iron Grey/1.43 kg), 83A0A0PCIN</t>
         </is>
       </c>
       <c r="C386" t="inlineStr"/>
       <c r="D386" t="n">
-        <v>43999</v>
+        <v>70990</v>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-05-20</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon</t>
+          <t>Lenovo V14 Intel Core i3</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo V14 Intel Core i3 13th Gen 14" FHD (1920x1080) Antiglare 250 Nits Thin and Light Laptop (16GB RAM/512GB SSD/Windows 11 Home/Office Home 2024/Iron Grey/1.43 kg), 83A0A0PCIN</t>
         </is>
       </c>
       <c r="C387" t="inlineStr"/>
       <c r="D387" t="n">
-        <v>43999</v>
+        <v>70990</v>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon</t>
+          <t>lenovo_v14_intel_core_i3</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo V14 Intel Core i3 13th Gen 14" FHD (1920x1080) Antiglare 250 Nits Thin and Light Laptop (16GB RAM/512GB SSD/Windows 11 Home/Office Home 2024/Iron Grey/1.43 kg), 83A0A0PCIN</t>
         </is>
       </c>
       <c r="C388" t="inlineStr"/>
       <c r="D388" t="n">
-        <v>44999</v>
+        <v>70990</v>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon</t>
+          <t>lenovo_v15_amd_ryzen_7</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo V15 AMD Ryzen 7 7730U 15.6" (39.62cm) FHD 250 Nits Antiglare Thin and Light Laptop (16GB/512GB SSD/Windows 11/Iron Grey/1.65 Kg) Grey</t>
         </is>
       </c>
       <c r="C389" t="inlineStr"/>
       <c r="D389" t="n">
-        <v>44999</v>
+        <v>64999</v>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-08-04</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>lenovo_v15_g4_amd_athlon</t>
+          <t>Lenovo V15 G4 (2024), AMD</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo V15 G4 (2024), AMD Ryzen 3 7320U Quad Core - (8GB/512GB SSD/AMD Radeon Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" FHD Display/Arctic Grey/1.57 kg/MS Office 2021</t>
         </is>
       </c>
       <c r="C390" t="inlineStr"/>
       <c r="D390" t="n">
-        <v>44999</v>
+        <v>44200</v>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>lenovo_v15_g4_amd_athlon</t>
+          <t>Lenovo V15 G4 (2024), AMD</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo V15 G4 (2024), AMD Ryzen 3 7320U Quad Core - (8GB/512GB SSD/AMD Radeon Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" FHD Display/Arctic Grey/1.57 kg/MS Office 2021</t>
         </is>
       </c>
       <c r="C391" t="inlineStr"/>
       <c r="D391" t="n">
-        <v>44999</v>
+        <v>44490</v>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-05-24</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>lenovo_v15_g4_amd_athlon</t>
+          <t>Lenovo V15 G4 (2024), AMD</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo V15 G4 (2024), AMD Ryzen 3 7320U Quad Core - (8GB/512GB SSD/AMD Radeon Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" FHD Display/Arctic Grey/1.57 kg/MS Office 2021</t>
         </is>
       </c>
       <c r="C392" t="inlineStr"/>
       <c r="D392" t="n">
-        <v>44999</v>
+        <v>44490</v>
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>lenovo_v15_g4_amd_athlon</t>
+          <t>Lenovo V15 G4 (2024), AMD</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo V15 G4 (2024), AMD Ryzen 3 7320U Quad Core - (8GB/512GB SSD/AMD Radeon Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" FHD Display/Arctic Grey/1.57 kg/MS Office 2021</t>
         </is>
       </c>
       <c r="C393" t="inlineStr"/>
       <c r="D393" t="n">
-        <v>44999</v>
+        <v>44500</v>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>lenovo_v15_g4_amd_athlon</t>
+          <t>Lenovo V15 G4 (2024), AMD</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo V15 G4 (2024), AMD Ryzen 3 7320U Quad Core - (8GB/512GB SSD/AMD Radeon Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" FHD Display/Arctic Grey/1.57 kg/MS Office 2021</t>
         </is>
       </c>
       <c r="C394" t="inlineStr"/>
       <c r="D394" t="n">
-        <v>44999</v>
+        <v>49999</v>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>lenovo_v15_g4_amd_athlon</t>
+          <t>Lenovo V15 G4 (2024), AMD</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
+          <t>Lenovo V15 G4 (2024), AMD Ryzen 3 7320U Quad Core - (8GB/512GB SSD/AMD Radeon Graphics/Windows 11 Home) Thin and Light Business Laptop/15.6" FHD Display/Arctic Grey/1.57 kg/MS Office 2021</t>
         </is>
       </c>
       <c r="C395" t="inlineStr"/>
       <c r="D395" t="n">
-        <v>44999</v>
+        <v>49890</v>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen</t>
+          <t>Lenovo V15 G4 AMD Athlon</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C396" t="inlineStr"/>
       <c r="D396" t="n">
-        <v>49999</v>
+        <v>41999</v>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen</t>
+          <t>Lenovo V15 G4 AMD Athlon</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C397" t="inlineStr"/>
       <c r="D397" t="n">
-        <v>52760</v>
+        <v>41999</v>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-28</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen</t>
+          <t>Lenovo V15 G4 AMD Athlon</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C398" t="inlineStr"/>
       <c r="D398" t="n">
-        <v>52300</v>
+        <v>41999</v>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-31</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen</t>
+          <t>Lenovo V15 G4 AMD Athlon</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C399" t="inlineStr"/>
       <c r="D399" t="n">
-        <v>52490</v>
+        <v>42999</v>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen</t>
+          <t>Lenovo V15 G4 AMD Athlon</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C400" t="inlineStr"/>
       <c r="D400" t="n">
-        <v>52300</v>
+        <v>42999</v>
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-02</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen</t>
+          <t>Lenovo V15 G4 AMD Athlon</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C401" t="inlineStr"/>
       <c r="D401" t="n">
-        <v>52890</v>
+        <v>42999</v>
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen</t>
+          <t>Lenovo V15 G4 AMD Athlon</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C402" t="inlineStr"/>
       <c r="D402" t="n">
-        <v>53999</v>
+        <v>42999</v>
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen</t>
+          <t>Lenovo V15 G4 AMD Athlon</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C403" t="inlineStr"/>
       <c r="D403" t="n">
-        <v>53999</v>
+        <v>42999</v>
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen</t>
+          <t>Lenovo V15 G4 AMD Athlon</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C404" t="inlineStr"/>
       <c r="D404" t="n">
-        <v>54790</v>
+        <v>44999</v>
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>lenovo_v15_g4_amd_ryzen</t>
+          <t>Lenovo V15 G4 AMD Athlon</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C405" t="inlineStr"/>
       <c r="D405" t="n">
-        <v>54740</v>
+        <v>43999</v>
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>lenovo_v15_g6_amd_ryzen</t>
+          <t>Lenovo V15 G4 AMD Athlon</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Lenovo V15 G6 AMD Ryzen 7 170 (Coequal 7735HS) 15.6" (39.62cm) FHD Thin and Light Business Laptop (16GB RAM DDR5/ 512GB SSD/Windows 11/ MS Office 2024/ AMD Radeon Graphics/Luna Grey/ 1.6 kg)</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C406" t="inlineStr"/>
       <c r="D406" t="n">
-        <v>64999</v>
+        <v>43999</v>
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>lenovo_v15_g6_amd_ryzen</t>
+          <t>Lenovo V15 G4 AMD Athlon</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Lenovo V15 G6 AMD Ryzen 7 170 (Coequal 7735HS) 15.6" (39.62cm) FHD Thin and Light Business Laptop (16GB RAM DDR5/ 512GB SSD/Windows 11/ MS Office 2024/ AMD Radeon Graphics/Luna Grey/ 1.6 kg)</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C407" t="inlineStr"/>
       <c r="D407" t="n">
-        <v>66999</v>
+        <v>43999</v>
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>Lenovo Yoga Slim 7 (Smartchoice)</t>
+          <t>Lenovo V15 G4 AMD Athlon</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Lenovo Yoga Slim 7 (Smartchoice) Aura Edition, Intel Core Ultra 5 226V, 16GB RAM, 1TB SSD, WUXGA OLED, Copilot+ AI PC, 40 TOPS, 14"/35.5cm, Windows 11, Office 2024, Grey, 1.19Kg, 83JX005FIN, AI Laptop</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C408" t="inlineStr"/>
       <c r="D408" t="n">
-        <v>99990</v>
+        <v>44999</v>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-06-12</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>Lenovo Yoga Slim 7 (Smartchoice)</t>
+          <t>Lenovo V15 G4 AMD Athlon</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Lenovo Yoga Slim 7 (Smartchoice) Aura Edition, Intel Core Ultra 5 226V, 16GB RAM, 1TB SSD, WUXGA OLED, Copilot+ AI PC, 40 TOPS, 14"/35.5cm, Windows 11, Office 2024, Grey, 1.19Kg, 83JX005FIN, AI Laptop</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C409" t="inlineStr"/>
       <c r="D409" t="n">
-        <v>105939</v>
+        <v>44999</v>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>Lenovo Yoga Slim 7, Intel</t>
+          <t>lenovo_v15_g4_amd_athlon</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Lenovo Yoga Slim 7, Intel Core Ultra 5 125H, 16GB RAM, 512GB SSD, AI PC, WUXGA-OLED, 14"/35.5cm, Windows 11, Microsoft 365 Basic + Office 2024, Grey, 1.39Kg, 83CV00DFIN, AI Powered Laptop</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C410" t="inlineStr"/>
       <c r="D410" t="n">
-        <v>77990</v>
+        <v>44999</v>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>Lenovo Yoga Slim 7, Intel</t>
+          <t>lenovo_v15_g4_amd_athlon</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Lenovo Yoga Slim 7, Intel Core Ultra 5 125H, 16GB RAM, 512GB SSD, AI PC, WUXGA-OLED, 14"/35.5cm, Windows 11, Microsoft 365 Basic + Office 2024, Grey, 1.39Kg, 83CV00DFIN, AI Powered Laptop</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C411" t="inlineStr"/>
       <c r="D411" t="n">
-        <v>84990</v>
+        <v>44999</v>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>Lenovo {SmartChoice Chromebook, Intel Celeron</t>
+          <t>lenovo_v15_g4_amd_athlon</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Lenovo {SmartChoice Chromebook, Intel Celeron N4500, 4GB RAM, 64GB eMMC, HD, 11.6"/29.46cm, Chrome OS, Blue, 1.21Kg, 2Wx2 Stereo Speakers, HD Camera, 82UY0014HA, Laptop</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C412" t="inlineStr"/>
       <c r="D412" t="n">
-        <v>21990</v>
+        <v>44999</v>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>Lenovo {SmartChoice Chromebook, Intel Celeron</t>
+          <t>lenovo_v15_g4_amd_athlon</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Lenovo {SmartChoice Chromebook, Intel Celeron N4500, 4GB RAM, 64GB eMMC, HD, 11.6"/29.46cm, Chrome OS, Blue, 1.21Kg, 2Wx2 Stereo Speakers, HD Camera, 82UY0014HA, Laptop</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C413" t="inlineStr"/>
       <c r="D413" t="n">
-        <v>17990</v>
+        <v>44999</v>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>msi_cyborg_15,_intel_12th</t>
+          <t>lenovo_v15_g4_amd_athlon</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>MSI Cyborg 15, Intel 12th Gen. i5-12450H, 40CM FHD 144Hz Gaming Laptop (16GB/512GB NVMe SSD/Windows 11 Home/MSO 2021/NVIDIA GeForce RTX 3050, GDDR6 6GB/Translucent Black/1.9Kg) A12UDX-1468IN</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C414" t="inlineStr"/>
       <c r="D414" t="n">
-        <v>72990</v>
+        <v>44999</v>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-04</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>primebook_2_max_(2026)_|</t>
+          <t>lenovo_v15_g4_amd_athlon</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Primebook 2 Max (2026) | 8GB RAM, 256GB UFS Storage | 15.6-Inch Full HD IPS Display | 12hrs Battery | MediaTek Helio G99 | Android 15 (PrimeOS 3.0) | Backlit Keyboard | in-Built AI (Gray)</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C415" t="inlineStr"/>
       <c r="D415" t="n">
-        <v>29990</v>
+        <v>44999</v>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-08-05</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>primebook_2_max_(2026)_|</t>
+          <t>lenovo_v15_g4_amd_athlon</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Primebook 2 Max (2026) | 8GB RAM, 256GB UFS Storage | 15.6-Inch Full HD IPS Display | 12hrs Battery | MediaTek Helio G99 | Android 15 (PrimeOS 3.0) | Backlit Keyboard | in-Built AI (Gray)</t>
+          <t>Lenovo V15 G4 AMD Athlon Silver 7120U Laptop 8GB LPDDR5 Ram, 512 GB SSD PCIe, Windows 11 Lifetime Validity,15.6" FHD Screen, AMD Radeon 610M, Silver, 1 Year Brand Warranty</t>
         </is>
       </c>
       <c r="C416" t="inlineStr"/>
       <c r="D416" t="n">
-        <v>31990</v>
+        <v>44999</v>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>primebook_2_pro_(2026)_|</t>
+          <t>Lenovo V15 G4 AMD Ryzen</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Primebook 2 Pro (2026) | 8GB RAM, 128GB UFS Storage | 14.1-Inch FHD IPS Display | 14 Hours Battery | MediaTek Helio G99 | Android 15 (PrimeOS 3.0) | Backlit Keyboard | in-Built AI (Gray)</t>
+          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
         </is>
       </c>
       <c r="C417" t="inlineStr"/>
       <c r="D417" t="n">
-        <v>26990</v>
+        <v>49999</v>
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-05-21</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>Samsung Galaxy Book6 (Gray, 16GB</t>
+          <t>Lenovo V15 G4 AMD Ryzen</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Samsung Galaxy Book6 (Gray, 16GB RAM, 1TB SSD) | Intel Core Ultra 5 (Series 3) | 16" WUXGA+ Display with Touchscreen | 24Hrs Battery Life | 120 Hz Refresh Rate | Dolby Atmos Stereo Speakers | AI PC</t>
+          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
         </is>
       </c>
       <c r="C418" t="inlineStr"/>
       <c r="D418" t="n">
-        <v>146990</v>
+        <v>52760</v>
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-24</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>Thomson NEO 14.1 Inch IN-P14C</t>
+          <t>Lenovo V15 G4 AMD Ryzen</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Thomson NEO 14.1 Inch IN-P14C Intel Celeron Dual Core N4020 Processor &amp; Window 11 Home Notebook (4 GB RAM DDR4/ 128 GB SSD/Numeric Touch Pad/Thin &amp; Light Weight/Silver)</t>
+          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
         </is>
       </c>
       <c r="C419" t="inlineStr"/>
       <c r="D419" t="n">
-        <v>12990</v>
+        <v>52300</v>
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>Thomson NEO 14.1 Inch IN-P14C</t>
+          <t>Lenovo V15 G4 AMD Ryzen</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Thomson NEO 14.1 Inch IN-P14C Intel Celeron Dual Core N4020 Processor &amp; Window 11 Home Notebook (4 GB RAM DDR4/ 128 GB SSD/Numeric Touch Pad/Thin &amp; Light Weight/Silver)</t>
+          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
         </is>
       </c>
       <c r="C420" t="inlineStr"/>
       <c r="D420" t="n">
-        <v>12990</v>
+        <v>52490</v>
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>Thomson NEO 14.1 Inch IN-P14C</t>
+          <t>Lenovo V15 G4 AMD Ryzen</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Thomson NEO 14.1 Inch IN-P14C Intel Celeron Dual Core N4020 Processor &amp; Window 11 Home Notebook (4 GB RAM DDR4/ 128 GB SSD/Numeric Touch Pad/Thin &amp; Light Weight/Silver)</t>
+          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
         </is>
       </c>
       <c r="C421" t="inlineStr"/>
       <c r="D421" t="n">
-        <v>22990</v>
+        <v>52300</v>
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-27</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>Thomson NEO 14.1 Inch IN-P14C</t>
+          <t>Lenovo V15 G4 AMD Ryzen</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Thomson NEO 14.1 Inch IN-P14C Intel Celeron Dual Core N4020 Processor &amp; Window 11 Home Notebook (4 GB RAM DDR4/ 128 GB SSD/Numeric Touch Pad/Thin &amp; Light Weight/Silver)</t>
+          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
         </is>
       </c>
       <c r="C422" t="inlineStr"/>
       <c r="D422" t="n">
-        <v>22990</v>
+        <v>52890</v>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-31</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>acer Aspire 3, Intel Core</t>
+          <t>Lenovo V15 G4 AMD Ryzen</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>acer Aspire 3, Intel Core Celeron N4500, 12GB LPDDR4X RAM, 512GB SSD, HD, 15.6"/39.62cm, Windows 11 Home, Pure Silver, 1.5KG, A325-45, Thin and Light Laptop</t>
+          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
         </is>
       </c>
       <c r="C423" t="inlineStr"/>
       <c r="D423" t="n">
-        <v>39890</v>
+        <v>53999</v>
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>acer Aspire Lite, AMD Ryzen</t>
+          <t>Lenovo V15 G4 AMD Ryzen</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>acer Aspire Lite, AMD Ryzen 3 5300U Processor, 16 GB RAM, 512GB SSD, Full HD, 15.6"/39.62cm, Windows 11 Home, Steel Gray, 1.59KG, AL15-41, Metal Body, Premium Thin and Light Laptop</t>
+          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
         </is>
       </c>
       <c r="C424" t="inlineStr"/>
       <c r="D424" t="n">
-        <v>42990</v>
+        <v>53999</v>
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-06-02</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD</t>
+          <t>Lenovo V15 G4 AMD Ryzen</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
+          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
         </is>
       </c>
       <c r="C425" t="inlineStr"/>
       <c r="D425" t="n">
-        <v>45990</v>
+        <v>54790</v>
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD</t>
+          <t>lenovo_v15_g4_amd_ryzen</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
+          <t>Lenovo V15 G4 AMD Ryzen 5 7520U 15.6 inch FHD Laptop, AMD Graphics, 16GB DDR5 5500Mhz Ram, 512GB SSD NVMe, Windows 11, Dolby Audio, Arctic Grey, 1 Year Onsite Brand Warranty</t>
         </is>
       </c>
       <c r="C426" t="inlineStr"/>
       <c r="D426" t="n">
-        <v>45990</v>
+        <v>54740</v>
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD</t>
+          <t>lenovo_v15_g6_amd_ryzen</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
+          <t>Lenovo V15 G6 AMD Ryzen 7 170 (Coequal 7735HS) 15.6" (39.62cm) FHD Thin and Light Business Laptop (16GB RAM DDR5/ 512GB SSD/Windows 11/ MS Office 2024/ AMD Radeon Graphics/Luna Grey/ 1.6 kg)</t>
         </is>
       </c>
       <c r="C427" t="inlineStr"/>
       <c r="D427" t="n">
-        <v>45990</v>
+        <v>64999</v>
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD</t>
+          <t>lenovo_v15_g6_amd_ryzen</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
+          <t>Lenovo V15 G6 AMD Ryzen 7 170 (Coequal 7735HS) 15.6" (39.62cm) FHD Thin and Light Business Laptop (16GB RAM DDR5/ 512GB SSD/Windows 11/ MS Office 2024/ AMD Radeon Graphics/Luna Grey/ 1.6 kg)</t>
         </is>
       </c>
       <c r="C428" t="inlineStr"/>
       <c r="D428" t="n">
-        <v>43990</v>
+        <v>66999</v>
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-08-04</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD</t>
+          <t>Lenovo Yoga Slim 7 (Smartchoice)</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
+          <t>Lenovo Yoga Slim 7 (Smartchoice) Aura Edition, Intel Core Ultra 5 226V, 16GB RAM, 1TB SSD, WUXGA OLED, Copilot+ AI PC, 40 TOPS, 14"/35.5cm, Windows 11, Office 2024, Grey, 1.19Kg, 83JX005FIN, AI Laptop</t>
         </is>
       </c>
       <c r="C429" t="inlineStr"/>
       <c r="D429" t="n">
-        <v>43990</v>
+        <v>99990</v>
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-15</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD</t>
+          <t>Lenovo Yoga Slim 7 (Smartchoice)</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
+          <t>Lenovo Yoga Slim 7 (Smartchoice) Aura Edition, Intel Core Ultra 5 226V, 16GB RAM, 1TB SSD, WUXGA OLED, Copilot+ AI PC, 40 TOPS, 14"/35.5cm, Windows 11, Office 2024, Grey, 1.19Kg, 83JX005FIN, AI Laptop</t>
         </is>
       </c>
       <c r="C430" t="inlineStr"/>
       <c r="D430" t="n">
-        <v>43990</v>
+        <v>105939</v>
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-19</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD</t>
+          <t>Lenovo Yoga Slim 7, Intel</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
+          <t>Lenovo Yoga Slim 7, Intel Core Ultra 5 125H, 16GB RAM, 512GB SSD, AI PC, WUXGA-OLED, 14"/35.5cm, Windows 11, Microsoft 365 Basic + Office 2024, Grey, 1.39Kg, 83CV00DFIN, AI Powered Laptop</t>
         </is>
       </c>
       <c r="C431" t="inlineStr"/>
       <c r="D431" t="n">
-        <v>43990</v>
+        <v>77990</v>
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD</t>
+          <t>Lenovo Yoga Slim 7, Intel</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
+          <t>Lenovo Yoga Slim 7, Intel Core Ultra 5 125H, 16GB RAM, 512GB SSD, AI PC, WUXGA-OLED, 14"/35.5cm, Windows 11, Microsoft 365 Basic + Office 2024, Grey, 1.39Kg, 83CV00DFIN, AI Powered Laptop</t>
         </is>
       </c>
       <c r="C432" t="inlineStr"/>
       <c r="D432" t="n">
-        <v>43990</v>
+        <v>84990</v>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-19</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop ModeI 7410 Laptop |</t>
+          <t>Lenovo {SmartChoice Chromebook, Intel Celeron</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop ModeI 7410 Laptop | InteI Core i5 10th Gen | 16GB DDR4 RAM | 256GB SSD | 14" Full HD Display | Win 10 Pro | InteI UHD Graphics 620 | 3 Months Seller Warranty | A+ Condition (Refab)</t>
+          <t>Lenovo {SmartChoice Chromebook, Intel Celeron N4500, 4GB RAM, 64GB eMMC, HD, 11.6"/29.46cm, Chrome OS, Blue, 1.21Kg, 2Wx2 Stereo Speakers, HD Camera, 82UY0014HA, Laptop</t>
         </is>
       </c>
       <c r="C433" t="inlineStr"/>
       <c r="D433" t="n">
-        <v>27299</v>
+        <v>21990</v>
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5</t>
+          <t>Lenovo {SmartChoice Chromebook, Intel Celeron</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5 11th Gen Processor |8GB DDR4 RAM |256GB SSD |14" FHD Display | Win10 | A+ Condition Laptop (Refab)</t>
+          <t>Lenovo {SmartChoice Chromebook, Intel Celeron N4500, 4GB RAM, 64GB eMMC, HD, 11.6"/29.46cm, Chrome OS, Blue, 1.21Kg, 2Wx2 Stereo Speakers, HD Camera, 82UY0014HA, Laptop</t>
         </is>
       </c>
       <c r="C434" t="inlineStr"/>
       <c r="D434" t="n">
-        <v>26999</v>
+        <v>17990</v>
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-08</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5</t>
+          <t>msi_cyborg_15,_intel_12th</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5 11th Gen Processor |8GB DDR4 RAM |256GB SSD |14" FHD Display | Win10 | A+ Condition Laptop (Refab)</t>
+          <t>MSI Cyborg 15, Intel 12th Gen. i5-12450H, 40CM FHD 144Hz Gaming Laptop (16GB/512GB NVMe SSD/Windows 11 Home/MSO 2021/NVIDIA GeForce RTX 3050, GDDR6 6GB/Translucent Black/1.9Kg) A12UDX-1468IN</t>
         </is>
       </c>
       <c r="C435" t="inlineStr"/>
       <c r="D435" t="n">
-        <v>26400</v>
+        <v>72990</v>
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5</t>
+          <t>primebook_2_max_(2026)_|</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5 11th Gen Processor |8GB DDR4 RAM |256GB SSD |14" FHD Display | Win10 | A+ Condition Laptop (Refab)</t>
+          <t>Primebook 2 Max (2026) | 8GB RAM, 256GB UFS Storage | 15.6-Inch Full HD IPS Display | 12hrs Battery | MediaTek Helio G99 | Android 15 (PrimeOS 3.0) | Backlit Keyboard | in-Built AI (Gray)</t>
         </is>
       </c>
       <c r="C436" t="inlineStr"/>
       <c r="D436" t="n">
-        <v>28599</v>
+        <v>29990</v>
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5</t>
+          <t>primebook_2_max_(2026)_|</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5 11th Gen Processor |8GB DDR4 RAM |256GB SSD |14" FHD Display | Win10 | A+ Condition Laptop (Refab)</t>
+          <t>Primebook 2 Max (2026) | 8GB RAM, 256GB UFS Storage | 15.6-Inch Full HD IPS Display | 12hrs Battery | MediaTek Helio G99 | Android 15 (PrimeOS 3.0) | Backlit Keyboard | in-Built AI (Gray)</t>
         </is>
       </c>
       <c r="C437" t="inlineStr"/>
       <c r="D437" t="n">
-        <v>28999</v>
+        <v>31990</v>
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-08-04</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5</t>
+          <t>primebook_2_pro_(2026)_|</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5 11th Gen Processor |8GB DDR4 RAM |256GB SSD |14" FHD Display | Win10 | A+ Condition Laptop (Refab)</t>
+          <t>Primebook 2 Pro (2026) | 8GB RAM, 128GB UFS Storage | 14.1-Inch FHD IPS Display | 14 Hours Battery | MediaTek Helio G99 | Android 15 (PrimeOS 3.0) | Backlit Keyboard | in-Built AI (Gray)</t>
         </is>
       </c>
       <c r="C438" t="inlineStr"/>
       <c r="D438" t="n">
-        <v>31990</v>
+        <v>26990</v>
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5</t>
+          <t>Samsung Galaxy Book6 (Gray, 16GB</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5 11th Gen Processor |8GB DDR4 RAM |256GB SSD |14" FHD Display | Win10 | A+ Condition Laptop (Refab)</t>
+          <t>Samsung Galaxy Book6 (Gray, 16GB RAM, 1TB SSD) | Intel Core Ultra 5 (Series 3) | 16" WUXGA+ Display with Touchscreen | 24Hrs Battery Life | 120 Hz Refresh Rate | Dolby Atmos Stereo Speakers | AI PC</t>
         </is>
       </c>
       <c r="C439" t="inlineStr"/>
       <c r="D439" t="n">
-        <v>35490</v>
+        <v>146990</v>
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5</t>
+          <t>Thomson NEO 14.1 Inch IN-P14C</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5 11th Gen Processor |8GB DDR4 RAM |256GB SSD |14" FHD Display | Win10 | A+ Condition Laptop (Refab)</t>
+          <t>Thomson NEO 14.1 Inch IN-P14C Intel Celeron Dual Core N4020 Processor &amp; Window 11 Home Notebook (4 GB RAM DDR4/ 128 GB SSD/Numeric Touch Pad/Thin &amp; Light Weight/Silver)</t>
         </is>
       </c>
       <c r="C440" t="inlineStr"/>
       <c r="D440" t="n">
-        <v>37490</v>
+        <v>12990</v>
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Model E5570 Laptop | Core</t>
+          <t>Thomson NEO 14.1 Inch IN-P14C</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>𝗗𝗲𝗹𝗹Model E5570 Laptop | Core i7 6th Gen | 8GB Fast RAM | 256GB SSD | 15.6" HD Display | HD Graphics | Win 10 | WiFi| (Pre-Owned &amp; Tested)</t>
+          <t>Thomson NEO 14.1 Inch IN-P14C Intel Celeron Dual Core N4020 Processor &amp; Window 11 Home Notebook (4 GB RAM DDR4/ 128 GB SSD/Numeric Touch Pad/Thin &amp; Light Weight/Silver)</t>
         </is>
       </c>
       <c r="C441" t="inlineStr"/>
       <c r="D441" t="n">
-        <v>20599</v>
+        <v>12990</v>
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>𝗛𝗣𝗣𝗿𝗼𝗯𝗼𝗼𝗸Model 430 G3 Business Laptop</t>
+          <t>Thomson NEO 14.1 Inch IN-P14C</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>𝗛𝗣𝗣𝗿𝗼𝗯𝗼𝗼𝗸Model 430 G3 Business Laptop | InteI i5 6th Gen | 8GB RAM | 256GB SSD | WiFi | Webcam | Win10 Pro (Refab)</t>
+          <t>Thomson NEO 14.1 Inch IN-P14C Intel Celeron Dual Core N4020 Processor &amp; Window 11 Home Notebook (4 GB RAM DDR4/ 128 GB SSD/Numeric Touch Pad/Thin &amp; Light Weight/Silver)</t>
         </is>
       </c>
       <c r="C442" t="inlineStr"/>
       <c r="D442" t="n">
-        <v>20299</v>
+        <v>22990</v>
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-08</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>𝗛𝗣𝗣𝗿𝗼𝗯𝗼𝗼𝗸Model 430 G3 Business Laptop</t>
+          <t>Thomson NEO 14.1 Inch IN-P14C</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>𝗛𝗣𝗣𝗿𝗼𝗯𝗼𝗼𝗸Model 430 G3 Business Laptop | 𝗜𝗡𝗧𝗘𝗟i5 6th Gen | 8GB RAM | 256GB SSD | WiFi | Webcam | Win10 Pro (Refab)</t>
+          <t>Thomson NEO 14.1 Inch IN-P14C Intel Celeron Dual Core N4020 Processor &amp; Window 11 Home Notebook (4 GB RAM DDR4/ 128 GB SSD/Numeric Touch Pad/Thin &amp; Light Weight/Silver)</t>
         </is>
       </c>
       <c r="C443" t="inlineStr"/>
       <c r="D443" t="n">
-        <v>20499</v>
+        <v>22990</v>
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-10</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>𝗛𝗣𝗣𝗿𝗼𝗯𝗼𝗼𝗸Model 430 G3 Business Laptop</t>
+          <t>acer Aspire 3, Intel Core</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>𝗛𝗣𝗣𝗿𝗼𝗯𝗼𝗼𝗸Model 430 G3 Business Laptop | 𝗜𝗡𝗧𝗘𝗟i5 6th Gen | 8GB RAM | 256GB SSD | WiFi | Webcam | Win10 Pro (Refab)</t>
+          <t>acer Aspire 3, Intel Core Celeron N4500, 12GB LPDDR4X RAM, 512GB SSD, HD, 15.6"/39.62cm, Windows 11 Home, Pure Silver, 1.5KG, A325-45, Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C444" t="inlineStr"/>
       <c r="D444" t="n">
-        <v>19999</v>
+        <v>39890</v>
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>𝗟𝗲𝗻𝗼𝘃𝗼model_l14_laptop|_core_i5</t>
+          <t>acer Aspire Lite, AMD Ryzen</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>𝗟𝗲𝗻𝗼𝘃𝗼Model L14 Laptop| Core i5 11th Gen Processor | 16GB Fast RAM/ 256GB SSD | 14″ HD Display | A+ (Pre-Owned &amp; Tested)</t>
+          <t>acer Aspire Lite, AMD Ryzen 3 5300U Processor, 16 GB RAM, 512GB SSD, Full HD, 15.6"/39.62cm, Windows 11 Home, Steel Gray, 1.59KG, AL15-41, Metal Body, Premium Thin and Light Laptop</t>
         </is>
       </c>
       <c r="C445" t="inlineStr"/>
       <c r="D445" t="n">
+        <v>42990</v>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>acer SmartChoice Aspire Lite, AMD</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr"/>
+      <c r="D446" t="n">
+        <v>45990</v>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>acer SmartChoice Aspire Lite, AMD</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr"/>
+      <c r="D447" t="n">
+        <v>45990</v>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>acer SmartChoice Aspire Lite, AMD</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr"/>
+      <c r="D448" t="n">
+        <v>45990</v>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>acer SmartChoice Aspire Lite, AMD</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr"/>
+      <c r="D449" t="n">
+        <v>43990</v>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>acer SmartChoice Aspire Lite, AMD</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr"/>
+      <c r="D450" t="n">
+        <v>43990</v>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>acer SmartChoice Aspire Lite, AMD</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr"/>
+      <c r="D451" t="n">
+        <v>43990</v>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>acer SmartChoice Aspire Lite, AMD</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr"/>
+      <c r="D452" t="n">
+        <v>43990</v>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>acer SmartChoice Aspire Lite, AMD</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>acer SmartChoice Aspire Lite, AMD Ryzen 5-5625U Processor, 16 GB/512 GB, Full HD, 15.6"/39.62 cm, Windows 11 Home, Steel Gray, 1.59 kg, AL15-41, Metal Body, Thin and Light Laptop</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr"/>
+      <c r="D453" t="n">
+        <v>43990</v>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop ModeI 7410 Laptop |</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop ModeI 7410 Laptop | InteI Core i5 10th Gen | 16GB DDR4 RAM | 256GB SSD | 14" Full HD Display | Win 10 Pro | InteI UHD Graphics 620 | 3 Months Seller Warranty | A+ Condition (Refab)</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr"/>
+      <c r="D454" t="n">
+        <v>27299</v>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5 11th Gen Processor |8GB DDR4 RAM |256GB SSD |14" FHD Display | Win10 | A+ Condition Laptop (Refab)</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr"/>
+      <c r="D455" t="n">
+        <v>26999</v>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5 11th Gen Processor |8GB DDR4 RAM |256GB SSD |14" FHD Display | Win10 | A+ Condition Laptop (Refab)</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr"/>
+      <c r="D456" t="n">
+        <v>26400</v>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5 11th Gen Processor |8GB DDR4 RAM |256GB SSD |14" FHD Display | Win10 | A+ Condition Laptop (Refab)</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr"/>
+      <c r="D457" t="n">
+        <v>28599</v>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5 11th Gen Processor |8GB DDR4 RAM |256GB SSD |14" FHD Display | Win10 | A+ Condition Laptop (Refab)</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr"/>
+      <c r="D458" t="n">
+        <v>28999</v>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5 11th Gen Processor |8GB DDR4 RAM |256GB SSD |14" FHD Display | Win10 | A+ Condition Laptop (Refab)</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr"/>
+      <c r="D459" t="n">
+        <v>31990</v>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5 11th Gen Processor |8GB DDR4 RAM |256GB SSD |14" FHD Display | Win10 | A+ Condition Laptop (Refab)</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr"/>
+      <c r="D460" t="n">
+        <v>35490</v>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Laptop Model 5420 | 𝗜𝗡𝗧𝗘𝗟i5 11th Gen Processor |8GB DDR4 RAM |256GB SSD |14" FHD Display | Win10 | A+ Condition Laptop (Refab)</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr"/>
+      <c r="D461" t="n">
+        <v>37490</v>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Model E5570 Laptop | Core</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>𝗗𝗲𝗹𝗹Model E5570 Laptop | Core i7 6th Gen | 8GB Fast RAM | 256GB SSD | 15.6" HD Display | HD Graphics | Win 10 | WiFi| (Pre-Owned &amp; Tested)</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr"/>
+      <c r="D462" t="n">
+        <v>20599</v>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>𝗛𝗣𝗣𝗿𝗼𝗯𝗼𝗼𝗸Model 430 G3 Business Laptop</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>𝗛𝗣𝗣𝗿𝗼𝗯𝗼𝗼𝗸Model 430 G3 Business Laptop | InteI i5 6th Gen | 8GB RAM | 256GB SSD | WiFi | Webcam | Win10 Pro (Refab)</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr"/>
+      <c r="D463" t="n">
+        <v>20299</v>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>𝗛𝗣𝗣𝗿𝗼𝗯𝗼𝗼𝗸Model 430 G3 Business Laptop</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>𝗛𝗣𝗣𝗿𝗼𝗯𝗼𝗼𝗸Model 430 G3 Business Laptop | 𝗜𝗡𝗧𝗘𝗟i5 6th Gen | 8GB RAM | 256GB SSD | WiFi | Webcam | Win10 Pro (Refab)</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr"/>
+      <c r="D464" t="n">
+        <v>20499</v>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>𝗛𝗣𝗣𝗿𝗼𝗯𝗼𝗼𝗸Model 430 G3 Business Laptop</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>𝗛𝗣𝗣𝗿𝗼𝗯𝗼𝗼𝗸Model 430 G3 Business Laptop | 𝗜𝗡𝗧𝗘𝗟i5 6th Gen | 8GB RAM | 256GB SSD | WiFi | Webcam | Win10 Pro (Refab)</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr"/>
+      <c r="D465" t="n">
+        <v>19999</v>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>𝗟𝗲𝗻𝗼𝘃𝗼model_l14_laptop|_core_i5</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>𝗟𝗲𝗻𝗼𝘃𝗼Model L14 Laptop| Core i5 11th Gen Processor | 16GB Fast RAM/ 256GB SSD | 14″ HD Display | A+ (Pre-Owned &amp; Tested)</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr"/>
+      <c r="D466" t="n">
         <v>31599</v>
       </c>
-      <c r="E445" t="inlineStr">
+      <c r="E466" t="inlineStr">
         <is>
           <t>2026-07-21</t>
         </is>
